--- a/financial_models/opportunities/0398.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0398.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3BFEEAC-EEB0-41B2-956C-35ED609639CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5F66945-78AF-4FA6-BAFA-B23696F60EAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -22,12 +22,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Valuation_Model!$B$73:$H$73</definedName>
-    <definedName name="Common_Shares">Thesis!$C$7</definedName>
+    <definedName name="Common_Shares">Thesis!$C$6</definedName>
     <definedName name="Equity_Cost">Valuation_Model!$C$5</definedName>
-    <definedName name="Exchange_Rate">Thesis!$C$17</definedName>
-    <definedName name="Market_currency">Thesis!$D$6</definedName>
-    <definedName name="Market_Price">Thesis!$C$6</definedName>
-    <definedName name="Reporting_currency">Thesis!$C$16</definedName>
+    <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
+    <definedName name="Market_currency">Thesis!$C$13</definedName>
+    <definedName name="Market_Price">Thesis!$C$12</definedName>
+    <definedName name="Reporting_currency">Thesis!$C$22</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
     <definedName name="Terminal_Growth">Valuation_Model!$F$4</definedName>
   </definedNames>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="439">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1414,10 +1414,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Y</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Base Cost of Equity</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1579,10 +1575,6 @@
   </si>
   <si>
     <t>Operating Cash Requirement</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>N</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1790,14 +1782,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>CNS_05</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Historical Average or D&amp;A</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Step 1: Establishing the Company’s Sustainable Earning Power (Calculating Normalized FCFE)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2374,10 +2358,49 @@
     <t>@ Entry Yield</t>
   </si>
   <si>
+    <t>Company Information</t>
+  </si>
+  <si>
+    <t>Market Currency</t>
+  </si>
+  <si>
+    <t>Symbol:</t>
+  </si>
+  <si>
+    <t>Listing Information</t>
+  </si>
+  <si>
+    <t>Forex Symbol:</t>
+  </si>
+  <si>
+    <t>Capitalization:</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>東方表行集團</t>
+  </si>
+  <si>
     <t>0398.HK</t>
   </si>
   <si>
-    <t>東方表行集團</t>
+    <t/>
+  </si>
+  <si>
+    <t>CNS_05</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Latest Asset Value</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Historical Average or D&amp;A</t>
   </si>
 </sst>
 </file>
@@ -3051,7 +3074,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="352">
+  <cellXfs count="355">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3752,29 +3775,36 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4064,13 +4094,12 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J168"/>
+  <dimension ref="A1:J179"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.59765625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="25.59765625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="22.86328125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.59765625" style="1" customWidth="1"/>
     <col min="5" max="6" width="15.59765625" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
@@ -4084,10 +4113,10 @@
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="331" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>288</v>
+        <v>430</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4105,9 +4134,8 @@
       <c r="J2" s="22"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="B4" s="45" t="str">
-        <f>D5&amp;" Stock Information"</f>
-        <v>0398.HK Stock Information</v>
+      <c r="B4" s="45" t="s">
+        <v>424</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4116,343 +4144,335 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>429</v>
-      </c>
-      <c r="D5" s="49" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="51">
+        <v>487358224</v>
+      </c>
+      <c r="E6" s="48"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="B7" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C7" s="279">
+        <v>6</v>
+      </c>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="B8" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C8" s="33">
+        <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
+        <v>45808</v>
+      </c>
+      <c r="E8" s="48"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="E9" s="34"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="B10" s="45" t="s">
+        <v>427</v>
+      </c>
+      <c r="C10" s="46"/>
+      <c r="E10" s="34"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="B11" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C11" s="49" t="s">
+        <v>432</v>
+      </c>
+      <c r="D11" s="49" t="s">
+        <v>433</v>
+      </c>
+      <c r="E11" s="34"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="B12" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C6" s="50">
+      <c r="C12" s="50">
         <v>3.57</v>
       </c>
-      <c r="D6" s="48" t="s">
-        <v>408</v>
-      </c>
-      <c r="E6" s="48"/>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="B7" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C7" s="51">
-        <v>487358224</v>
-      </c>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="B8" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="C8" s="279">
-        <v>6</v>
-      </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="48"/>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="B9" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="C9" s="33">
-        <f>EOMONTH(EDATE(BS!C1,C8+2),0)</f>
-        <v>45808</v>
-      </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="B10" s="4" t="str">
-        <f>"Capitalization ("&amp;Market_currency&amp;"):"</f>
-        <v>Capitalization (HKD):</v>
-      </c>
-      <c r="C10" s="35">
-        <f>Thesis!C6*Thesis!C7/1000000</f>
+      <c r="D12" s="50"/>
+      <c r="E12" s="48"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="B13" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="C13" s="48" t="s">
+        <v>404</v>
+      </c>
+      <c r="D13" s="48"/>
+      <c r="E13" s="5"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="B14" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="C14" s="35">
+        <f>Thesis!C12*Common_Shares/1000000</f>
         <v>1739.8688596799998</v>
       </c>
-      <c r="D10" s="32"/>
-      <c r="E10" s="5"/>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-    </row>
-    <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="342" t="s">
-        <v>371</v>
-      </c>
-      <c r="C12" s="342"/>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="B14" s="45" t="s">
-        <v>314</v>
-      </c>
-      <c r="C14" s="46"/>
-      <c r="D14" s="5"/>
+      <c r="D14" s="35" t="str">
+        <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
+        <v/>
+      </c>
+      <c r="E14" s="5"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="B15" s="2" t="s">
-        <v>358</v>
+      <c r="B15" s="4" t="s">
+        <v>428</v>
       </c>
       <c r="C15" s="32" t="str">
+        <f>IF(C22=C13,C13,C22&amp;"/"&amp;C13)</f>
+        <v>HKD</v>
+      </c>
+      <c r="D15" s="32" t="str">
+        <f>IF(D11="","",IF(C22=D13,D13,C22&amp;"/"&amp;D13))</f>
+        <v/>
+      </c>
+      <c r="E15" s="5"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="B16" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="50">
+        <v>1</v>
+      </c>
+      <c r="D16" s="50"/>
+      <c r="E16" s="5"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+    </row>
+    <row r="18" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B18" s="343" t="s">
+        <v>367</v>
+      </c>
+      <c r="C18" s="343"/>
+      <c r="D18" s="343"/>
+      <c r="E18" s="343"/>
+      <c r="F18" s="343"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="B20" s="45" t="s">
+        <v>313</v>
+      </c>
+      <c r="C20" s="46"/>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="B21" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
         <v xml:space="preserve">Low Growth </v>
       </c>
-      <c r="E15" s="5"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="B16" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="C16" s="48" t="s">
-        <v>408</v>
-      </c>
-      <c r="D16" s="32"/>
-      <c r="E16" s="5"/>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="B17" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C17" s="50">
-        <v>1</v>
-      </c>
-      <c r="D17" s="32" t="str">
-        <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
-        <v>HKD</v>
-      </c>
-      <c r="E17" s="5"/>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="B18" s="2" t="s">
+      <c r="E21" s="5"/>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="B22" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="C22" s="48" t="s">
+        <v>404</v>
+      </c>
+      <c r="D22" s="32" t="str">
+        <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
+        <v/>
+      </c>
+      <c r="E22" s="341" t="str">
+        <f>IF(D11="","",1/Exchange_Rate*D16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="B23" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C18" s="48" t="s">
-        <v>364</v>
-      </c>
-      <c r="E18" s="5"/>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="B19" s="2" t="s">
+      <c r="C23" s="48" t="s">
+        <v>434</v>
+      </c>
+      <c r="E23" s="5"/>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="B24" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="C19" s="249">
+      <c r="C24" s="249">
         <v>0.3</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="E19" s="339">
+      <c r="D24" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="E24" s="339">
         <v>0.2</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
-      <c r="B20" s="2" t="str">
+    <row r="25" spans="1:6">
+      <c r="B25" s="2" t="str">
         <f>"Target Buy Price ("&amp;Market_currency&amp;"):"</f>
         <v>Target Buy Price (HKD):</v>
       </c>
-      <c r="C20" s="252">
-        <f>C133</f>
+      <c r="C25" s="252">
+        <f>C139</f>
         <v>2.4911701525888064</v>
       </c>
-      <c r="D20" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="E20" s="330">
+      <c r="D25" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="E25" s="330">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
-      <c r="B21" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="C21" s="280">
+    <row r="26" spans="1:6">
+      <c r="B26" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C26" s="280">
         <f ca="1">Scenarios!C87</f>
         <v>0.14834835832623461</v>
       </c>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-    </row>
-    <row r="23" spans="1:6" ht="13.9">
-      <c r="A23" s="247" t="s">
-        <v>366</v>
-      </c>
-      <c r="B23" s="36"/>
-      <c r="C23" s="36"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="36"/>
-    </row>
-    <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="342" t="s">
-        <v>372</v>
-      </c>
-      <c r="C25" s="342"/>
-      <c r="D25" s="342"/>
-      <c r="E25" s="342"/>
-      <c r="F25" s="342"/>
-    </row>
-    <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="345" t="s">
-        <v>349</v>
-      </c>
-      <c r="C26" s="345"/>
-      <c r="D26" s="345"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="B28" s="234" t="s">
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+    </row>
+    <row r="28" spans="1:6" ht="13.9">
+      <c r="A28" s="247" t="s">
+        <v>362</v>
+      </c>
+      <c r="B28" s="36"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="36"/>
+      <c r="E28" s="36"/>
+      <c r="F28" s="36"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B30" s="343" t="s">
+        <v>368</v>
+      </c>
+      <c r="C30" s="343"/>
+      <c r="D30" s="343"/>
+      <c r="E30" s="343"/>
+      <c r="F30" s="343"/>
+    </row>
+    <row r="31" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B31" s="345" t="s">
+        <v>347</v>
+      </c>
+      <c r="C31" s="345"/>
+      <c r="D31" s="345"/>
+      <c r="E31" s="345"/>
+      <c r="F31" s="345"/>
+    </row>
+    <row r="33" spans="2:6">
+      <c r="B33" s="234" t="s">
         <v>231</v>
       </c>
-      <c r="C28" s="108">
+      <c r="C33" s="108">
         <f>scaling_factor</f>
         <v>1000</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="343" t="s">
+    <row r="34" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B34" s="344" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="343"/>
-      <c r="D29" s="343"/>
-      <c r="E29" s="343"/>
-      <c r="F29" s="343"/>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="B30" s="47" t="s">
+      <c r="C34" s="344"/>
+      <c r="D34" s="344"/>
+      <c r="E34" s="344"/>
+      <c r="F34" s="344"/>
+    </row>
+    <row r="35" spans="2:6">
+      <c r="B35" s="47" t="s">
         <v>233</v>
       </c>
-      <c r="C30" s="188">
+      <c r="C35" s="188">
         <f>Normalized_FCF!C8</f>
         <v>198948.88436097838</v>
       </c>
-      <c r="D30" s="1" t="str">
+      <c r="D35" s="1" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
-      <c r="B31" s="47"/>
-      <c r="C31" s="76"/>
-    </row>
-    <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="343" t="s">
+    <row r="36" spans="2:6">
+      <c r="B36" s="47"/>
+      <c r="C36" s="76"/>
+    </row>
+    <row r="37" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B37" s="344" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="343"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
-    </row>
-    <row r="33" spans="2:6">
-      <c r="B33" s="47" t="s">
+      <c r="C37" s="344"/>
+      <c r="D37" s="344"/>
+      <c r="E37" s="344"/>
+      <c r="F37" s="344"/>
+    </row>
+    <row r="38" spans="2:6">
+      <c r="B38" s="47" t="s">
         <v>235</v>
       </c>
-      <c r="C33" s="188">
+      <c r="C38" s="188">
         <f>Normalized_FCF!C9</f>
         <v>0</v>
       </c>
-      <c r="D33" s="1" t="str">
+      <c r="D38" s="1" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="34" spans="2:6">
-      <c r="B34" s="52" t="s">
+    <row r="39" spans="2:6">
+      <c r="B39" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="C34" s="188">
+      <c r="C39" s="188">
         <f>Normalized_FCF!C10</f>
         <v>0</v>
       </c>
-      <c r="D34" s="1" t="str">
+      <c r="D39" s="1" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="36" spans="2:6">
-      <c r="B36" s="343" t="s">
+    <row r="41" spans="2:6">
+      <c r="B41" s="344" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="343"/>
-      <c r="D36" s="343"/>
-      <c r="E36" s="343"/>
-      <c r="F36" s="343"/>
-    </row>
-    <row r="37" spans="2:6">
-      <c r="B37" s="47" t="s">
-        <v>238</v>
-      </c>
-      <c r="C37" s="188">
-        <f>Normalized_FCF!C11</f>
-        <v>0</v>
-      </c>
-      <c r="D37" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="39" spans="2:6">
-      <c r="B39" s="343" t="s">
-        <v>241</v>
-      </c>
-      <c r="C39" s="343"/>
-      <c r="D39" s="343"/>
-      <c r="E39" s="343"/>
-      <c r="F39" s="343"/>
-    </row>
-    <row r="40" spans="2:6">
-      <c r="B40" s="47" t="s">
-        <v>350</v>
-      </c>
-      <c r="C40" s="322">
-        <f>Normalized_FCF!C48</f>
-        <v>0</v>
-      </c>
-      <c r="D40" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-      <c r="E40" s="321"/>
-      <c r="F40" s="321"/>
-    </row>
-    <row r="41" spans="2:6">
-      <c r="B41" s="47" t="s">
-        <v>351</v>
-      </c>
-      <c r="C41" s="322">
-        <f>Normalized_FCF!C47</f>
-        <v>-13663</v>
-      </c>
-      <c r="D41" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-      <c r="E41" s="321"/>
-      <c r="F41" s="321"/>
+      <c r="C41" s="344"/>
+      <c r="D41" s="344"/>
+      <c r="E41" s="344"/>
+      <c r="F41" s="344"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C42" s="188">
-        <f>Normalized_FCF!C12</f>
-        <v>-13663</v>
+        <f>Normalized_FCF!C11</f>
+        <v>0</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4460,405 +4480,413 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="1" t="s">
-        <v>247</v>
-      </c>
+      <c r="B44" s="344" t="s">
+        <v>241</v>
+      </c>
+      <c r="C44" s="344"/>
+      <c r="D44" s="344"/>
+      <c r="E44" s="344"/>
+      <c r="F44" s="344"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
-        <v>266</v>
-      </c>
-      <c r="C45" s="188">
-        <f>Normalized_FCF!C15</f>
-        <v>-572.93535914055167</v>
+        <v>348</v>
+      </c>
+      <c r="C45" s="322">
+        <f>Normalized_FCF!C48</f>
+        <v>0</v>
       </c>
       <c r="D45" s="1" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
+      <c r="E45" s="321"/>
+      <c r="F45" s="321"/>
+    </row>
+    <row r="46" spans="2:6">
+      <c r="B46" s="47" t="s">
+        <v>349</v>
+      </c>
+      <c r="C46" s="322">
+        <f>Normalized_FCF!C47</f>
+        <v>-13663</v>
+      </c>
+      <c r="D46" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="E46" s="321"/>
+      <c r="F46" s="321"/>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="343" t="s">
+      <c r="B47" s="47" t="s">
+        <v>239</v>
+      </c>
+      <c r="C47" s="188">
+        <f>Normalized_FCF!C12</f>
+        <v>-13663</v>
+      </c>
+      <c r="D47" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6">
+      <c r="B49" s="1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6">
+      <c r="B50" s="47" t="s">
+        <v>266</v>
+      </c>
+      <c r="C50" s="188">
+        <f>Normalized_FCF!C15</f>
+        <v>-572.93535914055167</v>
+      </c>
+      <c r="D50" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6">
+      <c r="B52" s="344" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="343"/>
-      <c r="D47" s="343"/>
-      <c r="E47" s="343"/>
-      <c r="F47" s="343"/>
-    </row>
-    <row r="48" spans="2:6">
-      <c r="B48" s="47" t="s">
+      <c r="C52" s="344"/>
+      <c r="D52" s="344"/>
+      <c r="E52" s="344"/>
+      <c r="F52" s="344"/>
+    </row>
+    <row r="53" spans="2:6">
+      <c r="B53" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="C48" s="188">
+      <c r="C53" s="188">
         <f>Normalized_FCF!C14</f>
         <v>-46321.471090244595</v>
       </c>
-      <c r="D48" s="1" t="str">
+      <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
-      <c r="B50" s="343" t="s">
-        <v>348</v>
-      </c>
-      <c r="C50" s="344"/>
-      <c r="D50" s="344"/>
-      <c r="E50" s="344"/>
-      <c r="F50" s="344"/>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="B51" s="47" t="s">
+    <row r="55" spans="2:6">
+      <c r="B55" s="344" t="s">
+        <v>346</v>
+      </c>
+      <c r="C55" s="347"/>
+      <c r="D55" s="347"/>
+      <c r="E55" s="347"/>
+      <c r="F55" s="347"/>
+    </row>
+    <row r="56" spans="2:6">
+      <c r="B56" s="47" t="s">
         <v>243</v>
       </c>
-      <c r="C51" s="1">
+      <c r="C56" s="1">
         <f>Normalized_FCF!C17</f>
         <v>0</v>
-      </c>
-      <c r="D51" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="342" t="s">
-        <v>353</v>
-      </c>
-      <c r="C53" s="342"/>
-      <c r="D53" s="342"/>
-      <c r="E53" s="342"/>
-      <c r="F53" s="342"/>
-    </row>
-    <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="342" t="s">
-        <v>373</v>
-      </c>
-      <c r="C54" s="342"/>
-      <c r="D54" s="342"/>
-      <c r="E54" s="342"/>
-      <c r="F54" s="342"/>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="B56" s="47" t="s">
-        <v>271</v>
-      </c>
-      <c r="C56" s="188">
-        <f>Normalized_FCF!G19</f>
-        <v>194373</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="57" spans="1:6">
-      <c r="B57" s="47" t="s">
+    <row r="58" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B58" s="343" t="s">
+        <v>351</v>
+      </c>
+      <c r="C58" s="343"/>
+      <c r="D58" s="343"/>
+      <c r="E58" s="343"/>
+      <c r="F58" s="343"/>
+    </row>
+    <row r="59" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B59" s="343" t="s">
+        <v>369</v>
+      </c>
+      <c r="C59" s="343"/>
+      <c r="D59" s="343"/>
+      <c r="E59" s="343"/>
+      <c r="F59" s="343"/>
+    </row>
+    <row r="61" spans="2:6">
+      <c r="B61" s="47" t="s">
+        <v>271</v>
+      </c>
+      <c r="C61" s="188">
+        <f>Normalized_FCF!G19</f>
+        <v>194373</v>
+      </c>
+      <c r="D61" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="62" spans="2:6">
+      <c r="B62" s="47" t="s">
         <v>249</v>
       </c>
-      <c r="C57" s="188">
+      <c r="C62" s="188">
         <f>Normalized_FCF!C19</f>
         <v>138391.47791159325</v>
       </c>
-      <c r="D57" s="1" t="str">
+      <c r="D62" s="1" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
-      <c r="B58" s="254" t="s">
-        <v>402</v>
-      </c>
-      <c r="C58" s="92">
+    <row r="63" spans="2:6">
+      <c r="B63" s="254" t="s">
+        <v>398</v>
+      </c>
+      <c r="C63" s="92">
         <f>Normalized_FCF!C125</f>
         <v>7.9541327003833207E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:6">
-      <c r="B59" s="254" t="s">
-        <v>317</v>
-      </c>
-      <c r="C59" s="92">
+    <row r="64" spans="2:6">
+      <c r="B64" s="254" t="s">
+        <v>316</v>
+      </c>
+      <c r="C64" s="92">
         <f>Normalized_FCF!C93</f>
         <v>3.5854341736694682E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="13.9">
-      <c r="A61" s="247" t="s">
-        <v>367</v>
-      </c>
-      <c r="B61" s="36"/>
-      <c r="C61" s="36"/>
-      <c r="D61" s="36"/>
-      <c r="E61" s="36"/>
-      <c r="F61" s="36"/>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62" s="233"/>
-    </row>
-    <row r="63" spans="1:6" ht="24.4" customHeight="1">
-      <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
-        <v>374</v>
-      </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="B64" s="345" t="s">
+    <row r="66" spans="1:6" ht="13.9">
+      <c r="A66" s="247" t="s">
+        <v>363</v>
+      </c>
+      <c r="B66" s="36"/>
+      <c r="C66" s="36"/>
+      <c r="D66" s="36"/>
+      <c r="E66" s="36"/>
+      <c r="F66" s="36"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67" s="233"/>
+    </row>
+    <row r="68" spans="1:6" ht="24.4" customHeight="1">
+      <c r="A68" s="17"/>
+      <c r="B68" s="343" t="s">
+        <v>370</v>
+      </c>
+      <c r="C68" s="343"/>
+      <c r="D68" s="343"/>
+      <c r="E68" s="343"/>
+      <c r="F68" s="343"/>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="B69" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="345"/>
-      <c r="D64" s="345"/>
-      <c r="E64" s="345"/>
-      <c r="F64" s="345"/>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="B66" s="234" t="s">
+      <c r="C69" s="345"/>
+      <c r="D69" s="345"/>
+      <c r="E69" s="345"/>
+      <c r="F69" s="345"/>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="B71" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
-      <c r="B67" s="1" t="s">
+    <row r="72" spans="1:6">
+      <c r="B72" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="C72" s="311">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="B73" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="C73" s="263">
+        <f>IF(D73="Y",1%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D73" s="286" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="B74" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="C67" s="311">
+      <c r="C74" s="263">
+        <f>IF(D74="Y",1%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D74" s="286" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="B75" s="80" t="s">
+        <v>248</v>
+      </c>
+      <c r="C75" s="263">
+        <f>SUM(C72:C74)</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
-      <c r="B68" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="C68" s="263">
-        <f>IF(D68="Y",1%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D68" s="286" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="B69" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="C69" s="263">
-        <f>IF(D69="Y",1%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D69" s="286" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="B70" s="80" t="s">
-        <v>248</v>
-      </c>
-      <c r="C70" s="263">
-        <f>SUM(C67:C69)</f>
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="C71" s="122"/>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="B72" s="332" t="s">
-        <v>368</v>
-      </c>
-      <c r="C72" s="122"/>
-    </row>
-    <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="342" t="s">
-        <v>375</v>
-      </c>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
-    </row>
-    <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="342" t="s">
-        <v>376</v>
-      </c>
-      <c r="C74" s="342"/>
-      <c r="D74" s="342"/>
-      <c r="E74" s="342"/>
-      <c r="F74" s="342"/>
-    </row>
     <row r="76" spans="1:6">
-      <c r="B76" s="47" t="s">
+      <c r="C76" s="122"/>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="B77" s="332" t="s">
+        <v>364</v>
+      </c>
+      <c r="C77" s="122"/>
+    </row>
+    <row r="78" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B78" s="343" t="s">
+        <v>371</v>
+      </c>
+      <c r="C78" s="343"/>
+      <c r="D78" s="343"/>
+      <c r="E78" s="343"/>
+      <c r="F78" s="343"/>
+    </row>
+    <row r="79" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B79" s="343" t="s">
+        <v>372</v>
+      </c>
+      <c r="C79" s="343"/>
+      <c r="D79" s="343"/>
+      <c r="E79" s="343"/>
+      <c r="F79" s="343"/>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="B81" s="47" t="s">
         <v>252</v>
       </c>
-      <c r="C76" s="263">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="B77" s="47" t="s">
+      <c r="C81" s="263">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="B82" s="47" t="s">
         <v>284</v>
       </c>
-      <c r="C77" s="248">
+      <c r="C82" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>3.5495317175460563</v>
       </c>
-      <c r="D77" s="1" t="str">
+      <c r="D82" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="13.9">
-      <c r="A79" s="247" t="s">
-        <v>369</v>
-      </c>
-      <c r="B79" s="36"/>
-      <c r="C79" s="36"/>
-      <c r="D79" s="36"/>
-      <c r="E79" s="36"/>
-      <c r="F79" s="36"/>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80" s="233"/>
-    </row>
-    <row r="81" spans="2:6">
-      <c r="B81" s="342" t="s">
-        <v>377</v>
-      </c>
-      <c r="C81" s="342"/>
-      <c r="D81" s="342"/>
-      <c r="E81" s="342"/>
-      <c r="F81" s="342"/>
-    </row>
-    <row r="82" spans="2:6">
-      <c r="B82" s="1" t="s">
+    <row r="84" spans="1:6" ht="13.9">
+      <c r="A84" s="247" t="s">
+        <v>365</v>
+      </c>
+      <c r="B84" s="36"/>
+      <c r="C84" s="36"/>
+      <c r="D84" s="36"/>
+      <c r="E84" s="36"/>
+      <c r="F84" s="36"/>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="A85" s="233"/>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="B86" s="343" t="s">
+        <v>373</v>
+      </c>
+      <c r="C86" s="343"/>
+      <c r="D86" s="343"/>
+      <c r="E86" s="343"/>
+      <c r="F86" s="343"/>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="B87" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="84" spans="2:6">
-      <c r="B84" s="234" t="s">
+    <row r="89" spans="1:6">
+      <c r="B89" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="342" t="s">
-        <v>354</v>
-      </c>
-      <c r="C85" s="342"/>
-      <c r="D85" s="342"/>
-      <c r="E85" s="342"/>
-      <c r="F85" s="342"/>
-    </row>
-    <row r="86" spans="2:6">
-      <c r="B86" s="47" t="s">
+    <row r="90" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B90" s="343" t="s">
+        <v>352</v>
+      </c>
+      <c r="C90" s="343"/>
+      <c r="D90" s="343"/>
+      <c r="E90" s="343"/>
+      <c r="F90" s="343"/>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="B91" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="C86" s="188">
+      <c r="C91" s="188">
         <f>Valuation_Model!C7</f>
         <v>195066</v>
       </c>
-      <c r="D86" s="1" t="str">
+      <c r="D91" s="1" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:6">
-      <c r="B87" s="47" t="s">
+    <row r="92" spans="1:6">
+      <c r="B92" s="47" t="s">
         <v>285</v>
       </c>
-      <c r="C87" s="248">
-        <f>C86*scaling_factor*Exchange_Rate/Common_Shares</f>
+      <c r="C92" s="248">
+        <f>C91*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>0.40025178686632773</v>
       </c>
-      <c r="D87" s="1" t="str">
+      <c r="D92" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="2:6">
-      <c r="B88" s="336" t="s">
-        <v>416</v>
-      </c>
-      <c r="C88" s="337">
+    <row r="93" spans="1:6">
+      <c r="B93" s="336" t="s">
+        <v>412</v>
+      </c>
+      <c r="C93" s="337">
         <f>BS!G30/BS!G27</f>
         <v>0.40000523965699897</v>
       </c>
     </row>
-    <row r="89" spans="2:6">
-      <c r="B89" s="336" t="s">
-        <v>417</v>
-      </c>
-      <c r="C89" s="337">
+    <row r="94" spans="1:6">
+      <c r="B94" s="336" t="s">
+        <v>413</v>
+      </c>
+      <c r="C94" s="337">
         <f>BS!G31/BS!G27</f>
         <v>0.10646655543311496</v>
       </c>
     </row>
-    <row r="90" spans="2:6">
-      <c r="B90" s="336" t="s">
-        <v>419</v>
-      </c>
-      <c r="C90" s="338">
+    <row r="95" spans="1:6">
+      <c r="B95" s="336" t="s">
+        <v>415</v>
+      </c>
+      <c r="C95" s="338">
         <f>BS!C50</f>
         <v>0.9804830051022897</v>
       </c>
     </row>
-    <row r="92" spans="2:6">
-      <c r="B92" s="1" t="s">
+    <row r="97" spans="1:6">
+      <c r="B97" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="93" spans="2:6">
-      <c r="B93" s="47" t="s">
+    <row r="98" spans="1:6">
+      <c r="B98" s="47" t="s">
         <v>265</v>
       </c>
-      <c r="C93" s="188">
+      <c r="C98" s="188">
         <f>BS!C66</f>
         <v>1089388</v>
-      </c>
-      <c r="D93" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="94" spans="2:6">
-      <c r="B94" s="47" t="s">
-        <v>267</v>
-      </c>
-      <c r="C94" s="188">
-        <f>Valuation_Model!C8</f>
-        <v>587281.82009631116</v>
-      </c>
-      <c r="D94" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="95" spans="2:6">
-      <c r="B95" s="47" t="s">
-        <v>286</v>
-      </c>
-      <c r="C95" s="248">
-        <f>C94*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.2050311068441337</v>
-      </c>
-      <c r="D95" s="1" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
-      <c r="B97" s="1" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
-      <c r="B98" s="47" t="s">
-        <v>258</v>
-      </c>
-      <c r="C98" s="188">
-        <f>Valuation_Model!C9</f>
-        <v>18907.900000000001</v>
       </c>
       <c r="D98" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4867,591 +4895,688 @@
     </row>
     <row r="99" spans="1:6">
       <c r="B99" s="47" t="s">
-        <v>287</v>
-      </c>
-      <c r="C99" s="248">
-        <f>C98*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.8796718858693152E-2</v>
+        <v>267</v>
+      </c>
+      <c r="C99" s="188">
+        <f>Valuation_Model!C8</f>
+        <v>587281.82009631116</v>
       </c>
       <c r="D99" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6">
+      <c r="B100" s="47" t="s">
+        <v>286</v>
+      </c>
+      <c r="C100" s="248">
+        <f>C99*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>1.2050311068441337</v>
+      </c>
+      <c r="D100" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="342" t="s">
-        <v>378</v>
-      </c>
-      <c r="C101" s="342"/>
-      <c r="D101" s="342"/>
-      <c r="E101" s="342"/>
-      <c r="F101" s="342"/>
+    <row r="102" spans="1:6">
+      <c r="B102" s="1" t="s">
+        <v>257</v>
+      </c>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
-        <v>283</v>
-      </c>
-      <c r="C103" s="248">
-        <f>Valuation_Model!C12</f>
-        <v>4.3931077563825554</v>
+        <v>258</v>
+      </c>
+      <c r="C103" s="188">
+        <f>Valuation_Model!C9</f>
+        <v>18907.900000000001</v>
       </c>
       <c r="D103" s="1" t="str">
-        <f>Market_currency</f>
+        <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="104" spans="1:6">
-      <c r="B104" s="336" t="s">
-        <v>418</v>
+      <c r="B104" s="47" t="s">
+        <v>287</v>
       </c>
       <c r="C104" s="248">
-        <f>BS!D47</f>
-        <v>1.6698226477450393</v>
+        <f>C103*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>3.8796718858693152E-2</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="13.9">
-      <c r="A106" s="247" t="s">
-        <v>370</v>
-      </c>
-      <c r="B106" s="36"/>
-      <c r="C106" s="36"/>
-      <c r="D106" s="36"/>
-      <c r="E106" s="36"/>
-      <c r="F106" s="36"/>
-    </row>
-    <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="343" t="s">
-        <v>379</v>
-      </c>
-      <c r="C108" s="343"/>
-      <c r="D108" s="343"/>
-      <c r="E108" s="343"/>
-      <c r="F108" s="343"/>
-    </row>
-    <row r="110" spans="1:6" ht="12.4">
-      <c r="B110" s="260" t="s">
+    <row r="106" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B106" s="343" t="s">
+        <v>374</v>
+      </c>
+      <c r="C106" s="343"/>
+      <c r="D106" s="343"/>
+      <c r="E106" s="343"/>
+      <c r="F106" s="343"/>
+    </row>
+    <row r="108" spans="1:6">
+      <c r="B108" s="47" t="s">
+        <v>283</v>
+      </c>
+      <c r="C108" s="248">
+        <f>Valuation_Model!C12</f>
+        <v>4.3931077563825554</v>
+      </c>
+      <c r="D108" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6">
+      <c r="B109" s="336" t="s">
+        <v>414</v>
+      </c>
+      <c r="C109" s="248">
+        <f>BS!D47</f>
+        <v>1.6698226477450393</v>
+      </c>
+      <c r="D109" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" ht="13.9">
+      <c r="A111" s="247" t="s">
+        <v>366</v>
+      </c>
+      <c r="B111" s="36"/>
+      <c r="C111" s="36"/>
+      <c r="D111" s="36"/>
+      <c r="E111" s="36"/>
+      <c r="F111" s="36"/>
+    </row>
+    <row r="113" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B113" s="344" t="s">
+        <v>375</v>
+      </c>
+      <c r="C113" s="344"/>
+      <c r="D113" s="344"/>
+      <c r="E113" s="344"/>
+      <c r="F113" s="344"/>
+    </row>
+    <row r="115" spans="1:6" ht="12.4">
+      <c r="B115" s="260" t="s">
         <v>118</v>
       </c>
-      <c r="C110" s="260" t="s">
+      <c r="C115" s="260" t="s">
         <v>133</v>
       </c>
-      <c r="D110" s="260" t="s">
+      <c r="D115" s="260" t="s">
         <v>113</v>
       </c>
-      <c r="E110" s="260" t="s">
+      <c r="E115" s="260" t="s">
         <v>260</v>
       </c>
-      <c r="F110" s="260" t="s">
+      <c r="F115" s="260" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="111" spans="1:6">
-      <c r="B111" s="255" t="str">
+    <row r="116" spans="1:6">
+      <c r="B116" s="255" t="str">
         <f>Valuation_Model!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C111" s="256">
+      <c r="C116" s="256">
         <f>Valuation_Model!C74</f>
         <v>0.1</v>
       </c>
-      <c r="D111" s="257">
+      <c r="D116" s="257">
         <f>Valuation_Model!D74</f>
         <v>15</v>
       </c>
-      <c r="E111" s="258" t="str">
+      <c r="E116" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
         <v>7.02 HKD</v>
       </c>
-      <c r="F111" s="259">
+      <c r="F116" s="259">
         <f>Valuation_Model!F74</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="112" spans="1:6">
-      <c r="B112" s="242" t="str">
+    <row r="117" spans="1:6">
+      <c r="B117" s="242" t="str">
         <f>Valuation_Model!B75</f>
         <v>Optimistic</v>
       </c>
-      <c r="C112" s="243">
+      <c r="C117" s="243">
         <f>Valuation_Model!C75</f>
         <v>0.06</v>
       </c>
-      <c r="D112" s="244">
+      <c r="D117" s="244">
         <f>Valuation_Model!D75</f>
         <v>10</v>
       </c>
-      <c r="E112" s="245" t="str">
+      <c r="E117" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
         <v>5.15 HKD</v>
       </c>
-      <c r="F112" s="246">
+      <c r="F117" s="246">
         <f>Valuation_Model!F75</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
-      <c r="B113" s="242" t="str">
+    <row r="118" spans="1:6">
+      <c r="B118" s="242" t="str">
         <f>Valuation_Model!B76</f>
         <v>Base</v>
       </c>
-      <c r="C113" s="243">
+      <c r="C118" s="243">
         <f>Valuation_Model!C76</f>
         <v>0.04</v>
       </c>
-      <c r="D113" s="244">
+      <c r="D118" s="244">
         <f>Valuation_Model!D76</f>
         <v>10</v>
       </c>
-      <c r="E113" s="245" t="str">
+      <c r="E118" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
         <v>4.87 HKD</v>
       </c>
-      <c r="F113" s="246">
+      <c r="F118" s="246">
         <f>Valuation_Model!F76</f>
         <v>0.53999999999999992</v>
       </c>
     </row>
-    <row r="114" spans="1:6">
-      <c r="B114" s="242" t="str">
+    <row r="119" spans="1:6">
+      <c r="B119" s="242" t="str">
         <f>Valuation_Model!B77</f>
         <v>Pessimistic</v>
       </c>
-      <c r="C114" s="243">
+      <c r="C119" s="243">
         <f>Valuation_Model!C77</f>
         <v>0.02</v>
       </c>
-      <c r="D114" s="244">
+      <c r="D119" s="244">
         <f>Valuation_Model!D77</f>
         <v>10</v>
       </c>
-      <c r="E114" s="245" t="str">
+      <c r="E119" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
         <v>4.62 HKD</v>
       </c>
-      <c r="F114" s="246">
+      <c r="F119" s="246">
         <f>Valuation_Model!F77</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="115" spans="1:6">
-      <c r="B115" s="242" t="str">
+    <row r="120" spans="1:6">
+      <c r="B120" s="242" t="str">
         <f>Valuation_Model!B78</f>
         <v>Devil's advocate</v>
       </c>
-      <c r="C115" s="243">
+      <c r="C120" s="243">
         <f>Valuation_Model!C78</f>
         <v>0</v>
       </c>
-      <c r="D115" s="244">
+      <c r="D120" s="244">
         <f>Valuation_Model!D78</f>
         <v>15</v>
       </c>
-      <c r="E115" s="245" t="str">
+      <c r="E120" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
         <v>4.39 HKD</v>
       </c>
-      <c r="F115" s="246">
+      <c r="F120" s="246">
         <f>Valuation_Model!F78</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
-      <c r="B117" s="235" t="s">
+    <row r="122" spans="1:6">
+      <c r="B122" s="235" t="s">
         <v>259</v>
       </c>
-      <c r="C117" s="241">
+      <c r="C122" s="241">
         <f>Scenarios!C60</f>
         <v>4.9623808252376094</v>
       </c>
-      <c r="D117" s="236" t="str">
+      <c r="D122" s="236" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="346" t="s">
-        <v>382</v>
-      </c>
-      <c r="C119" s="346"/>
-      <c r="D119" s="346"/>
-      <c r="E119" s="346"/>
-      <c r="F119" s="346"/>
-    </row>
-    <row r="121" spans="1:6" ht="13.9">
-      <c r="A121" s="247" t="s">
-        <v>414</v>
-      </c>
-      <c r="B121" s="36"/>
-      <c r="C121" s="36"/>
-      <c r="D121" s="36"/>
-      <c r="E121" s="36"/>
-      <c r="F121" s="36"/>
-    </row>
-    <row r="123" spans="1:6">
-      <c r="B123" s="347" t="s">
-        <v>380</v>
-      </c>
-      <c r="C123" s="347"/>
-      <c r="D123" s="347"/>
-      <c r="E123" s="347"/>
-      <c r="F123" s="347"/>
-    </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="342" t="s">
-        <v>381</v>
-      </c>
-      <c r="C124" s="342"/>
-      <c r="D124" s="342"/>
-      <c r="E124" s="342"/>
-      <c r="F124" s="342"/>
-    </row>
-    <row r="125" spans="1:6">
-      <c r="B125" s="234" t="s">
+      <c r="B124" s="348" t="s">
+        <v>378</v>
+      </c>
+      <c r="C124" s="348"/>
+      <c r="D124" s="348"/>
+      <c r="E124" s="348"/>
+      <c r="F124" s="348"/>
+    </row>
+    <row r="126" spans="1:6" ht="13.9">
+      <c r="A126" s="247" t="s">
+        <v>410</v>
+      </c>
+      <c r="B126" s="36"/>
+      <c r="C126" s="36"/>
+      <c r="D126" s="36"/>
+      <c r="E126" s="36"/>
+      <c r="F126" s="36"/>
+    </row>
+    <row r="128" spans="1:6">
+      <c r="B128" s="346" t="s">
+        <v>376</v>
+      </c>
+      <c r="C128" s="346"/>
+      <c r="D128" s="346"/>
+      <c r="E128" s="346"/>
+      <c r="F128" s="346"/>
+    </row>
+    <row r="129" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B129" s="343" t="s">
+        <v>377</v>
+      </c>
+      <c r="C129" s="343"/>
+      <c r="D129" s="343"/>
+      <c r="E129" s="343"/>
+      <c r="F129" s="343"/>
+    </row>
+    <row r="130" spans="2:6">
+      <c r="B130" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="126" spans="1:6">
-      <c r="B126" s="1" t="s">
+    <row r="131" spans="2:6">
+      <c r="B131" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C126" s="251">
-        <f>E20</f>
+      <c r="C131" s="251">
+        <f>E25</f>
         <v>3</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
-      <c r="B127" s="1" t="s">
+    <row r="132" spans="2:6">
+      <c r="B132" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="C127" s="250">
-        <f>C19</f>
+      <c r="C132" s="250">
+        <f>C24</f>
         <v>0.3</v>
       </c>
     </row>
-    <row r="128" spans="1:6">
-      <c r="B128" s="236" t="s">
+    <row r="133" spans="2:6">
+      <c r="B133" s="236" t="s">
         <v>262</v>
       </c>
-      <c r="C128" s="237">
+      <c r="C133" s="237">
         <f>Scenarios!C77</f>
         <v>0.128</v>
       </c>
-      <c r="D128" s="236" t="str">
+      <c r="D133" s="236" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="130" spans="2:4">
-      <c r="B130" s="234" t="s">
-        <v>422</v>
-      </c>
-      <c r="C130" s="337">
-        <f>C19</f>
+    <row r="135" spans="2:6">
+      <c r="B135" s="234" t="s">
+        <v>418</v>
+      </c>
+      <c r="C135" s="270" t="str">
+        <f>C11</f>
+        <v>0398.HK</v>
+      </c>
+      <c r="D135" s="270" t="str">
+        <f>IF(D11="","",D11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136" spans="2:6">
+      <c r="B136" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="C136" s="337">
+        <f>C24</f>
         <v>0.3</v>
       </c>
-      <c r="D130" s="1" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="131" spans="2:4">
-      <c r="B131" s="236" t="str">
-        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
+    </row>
+    <row r="137" spans="2:6">
+      <c r="B137" s="236" t="str">
+        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C131" s="240">
+      <c r="C137" s="240">
         <f>Scenarios!C81</f>
         <v>0.23246244879380981</v>
       </c>
     </row>
-    <row r="132" spans="2:4">
-      <c r="B132" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
+    <row r="138" spans="2:6">
+      <c r="B138" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C132" s="240">
+      <c r="C138" s="240">
         <f>Scenarios!C82</f>
         <v>2.2587077037949967</v>
       </c>
     </row>
-    <row r="133" spans="2:4">
-      <c r="B133" s="80" t="s">
+    <row r="139" spans="2:6">
+      <c r="B139" s="80" t="s">
         <v>261</v>
       </c>
-      <c r="C133" s="239">
+      <c r="C139" s="239">
         <f>Scenarios!C83</f>
         <v>2.4911701525888064</v>
       </c>
-      <c r="D133" s="47" t="str">
-        <f>Reporting_currency</f>
+      <c r="D139" s="342" t="str">
+        <f>IF($D$11="","",C139*$E$22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140" spans="2:6">
+      <c r="B140" s="290" t="s">
+        <v>425</v>
+      </c>
+      <c r="C140" s="340" t="str">
+        <f>Market_currency</f>
         <v>HKD</v>
       </c>
-    </row>
-    <row r="134" spans="2:4">
-      <c r="B134" s="238" t="s">
+      <c r="D140" s="340" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="141" spans="2:6">
+      <c r="B141" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C134" s="92">
+      <c r="C141" s="92">
         <f>Scenarios!F83</f>
         <v>0.49798892097937209</v>
       </c>
     </row>
-    <row r="136" spans="2:4">
-      <c r="B136" s="234" t="s">
-        <v>425</v>
-      </c>
-      <c r="C136" s="337">
+    <row r="143" spans="2:6">
+      <c r="B143" s="234" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="144" spans="2:6">
+      <c r="B144" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="C144" s="337">
         <f>Scenarios!C90</f>
         <v>0.2</v>
       </c>
-      <c r="D136" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="137" spans="2:4">
-      <c r="B137" s="236" t="str">
-        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
+    </row>
+    <row r="145" spans="1:6">
+      <c r="B145" s="236" t="str">
+        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C137" s="240">
+      <c r="C145" s="240">
         <f>Scenarios!C91</f>
         <v>0.26962962962962961</v>
       </c>
     </row>
-    <row r="138" spans="2:4">
-      <c r="B138" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
+    <row r="146" spans="1:6">
+      <c r="B146" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C138" s="240">
+      <c r="C146" s="240">
         <f>Scenarios!C92</f>
         <v>2.8717481627532462</v>
       </c>
     </row>
-    <row r="139" spans="2:4">
-      <c r="B139" s="80" t="s">
+    <row r="147" spans="1:6">
+      <c r="B147" s="80" t="s">
         <v>261</v>
       </c>
-      <c r="C139" s="239">
+      <c r="C147" s="239">
         <f>Scenarios!C93</f>
         <v>3.1413777923828756</v>
       </c>
-      <c r="D139" s="47" t="str">
-        <f>Reporting_currency</f>
+      <c r="D147" s="342" t="str">
+        <f>IF($D$11="","",C147*$E$22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148" spans="1:6">
+      <c r="B148" s="290" t="s">
+        <v>425</v>
+      </c>
+      <c r="C148" s="340" t="str">
+        <f>Market_currency</f>
         <v>HKD</v>
       </c>
-    </row>
-    <row r="140" spans="2:4">
-      <c r="B140" s="238" t="s">
+      <c r="D148" s="340" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="149" spans="1:6">
+      <c r="B149" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C140" s="92">
+      <c r="C149" s="92">
         <f>Scenarios!F93</f>
         <v>0.36696156481854458</v>
       </c>
     </row>
-    <row r="142" spans="2:4">
-      <c r="B142" s="234" t="s">
-        <v>412</v>
-      </c>
-      <c r="C142" s="92">
+    <row r="151" spans="1:6">
+      <c r="B151" s="234" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6">
+      <c r="B152" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="C152" s="92">
         <f>Scenarios!C96</f>
         <v>0.08</v>
       </c>
-      <c r="D142" s="1" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="143" spans="2:4">
-      <c r="B143" s="236" t="str">
-        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
+    </row>
+    <row r="153" spans="1:6">
+      <c r="B153" s="236" t="str">
+        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C143" s="240">
+      <c r="C153" s="240">
         <f>Scenarios!C97</f>
         <v>0.32986841436772868</v>
       </c>
     </row>
-    <row r="144" spans="2:4">
-      <c r="B144" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
+    <row r="154" spans="1:6">
+      <c r="B154" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C144" s="240">
+      <c r="C154" s="240">
         <f>Scenarios!C98</f>
         <v>3.9392978912938901</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
-      <c r="B145" s="80" t="s">
-        <v>413</v>
-      </c>
-      <c r="C145" s="239">
+    <row r="155" spans="1:6">
+      <c r="B155" s="80" t="s">
+        <v>409</v>
+      </c>
+      <c r="C155" s="239">
         <f>Scenarios!C99</f>
         <v>4.2691663056616189</v>
       </c>
-      <c r="D145" s="101" t="str">
-        <f>Reporting_currency</f>
+      <c r="D155" s="342" t="str">
+        <f>IF($D$11="","",C155*$E$22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="156" spans="1:6">
+      <c r="B156" s="290" t="s">
+        <v>425</v>
+      </c>
+      <c r="C156" s="340" t="str">
+        <f>Market_currency</f>
         <v>HKD</v>
       </c>
-    </row>
-    <row r="146" spans="1:6">
-      <c r="B146" s="238" t="s">
+      <c r="D156" s="340" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="157" spans="1:6">
+      <c r="B157" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C146" s="92">
+      <c r="C157" s="92">
         <f>Scenarios!F99</f>
         <v>0.13969393804894004</v>
       </c>
     </row>
-    <row r="148" spans="1:6" ht="13.9">
-      <c r="A148" s="247" t="s">
-        <v>386</v>
-      </c>
-      <c r="B148" s="36"/>
-      <c r="C148" s="36"/>
-      <c r="D148" s="36"/>
-      <c r="E148" s="36"/>
-      <c r="F148" s="36"/>
-    </row>
-    <row r="150" spans="1:6">
-      <c r="B150" s="341" t="s">
+    <row r="159" spans="1:6" ht="13.9">
+      <c r="A159" s="247" t="s">
+        <v>382</v>
+      </c>
+      <c r="B159" s="36"/>
+      <c r="C159" s="36"/>
+      <c r="D159" s="36"/>
+      <c r="E159" s="36"/>
+      <c r="F159" s="36"/>
+    </row>
+    <row r="161" spans="2:6">
+      <c r="B161" s="350" t="s">
+        <v>384</v>
+      </c>
+      <c r="C161" s="343"/>
+      <c r="D161" s="343"/>
+      <c r="E161" s="343"/>
+      <c r="F161" s="343"/>
+    </row>
+    <row r="163" spans="2:6">
+      <c r="B163" s="234" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="164" spans="2:6">
+      <c r="B164" s="347" t="s">
         <v>388</v>
       </c>
-      <c r="C150" s="342"/>
-      <c r="D150" s="342"/>
-      <c r="E150" s="342"/>
-      <c r="F150" s="342"/>
-    </row>
-    <row r="152" spans="1:6">
-      <c r="B152" s="234" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6">
-      <c r="B153" s="344" t="s">
-        <v>392</v>
-      </c>
-      <c r="C153" s="344"/>
-      <c r="D153" s="344"/>
-      <c r="E153" s="344"/>
-      <c r="F153" s="344"/>
-    </row>
-    <row r="154" spans="1:6">
-      <c r="B154" s="238" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6">
-      <c r="B155" s="238" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6">
-      <c r="B156" s="238" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6">
-      <c r="B158" s="1" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="343" t="s">
-        <v>393</v>
-      </c>
-      <c r="C159" s="343"/>
-      <c r="D159" s="343"/>
-      <c r="E159" s="343"/>
-      <c r="F159" s="343"/>
-    </row>
-    <row r="161" spans="2:6">
-      <c r="B161" s="1" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="340" t="s">
-        <v>394</v>
-      </c>
-      <c r="C162" s="340"/>
-      <c r="D162" s="340"/>
-      <c r="E162" s="340"/>
-      <c r="F162" s="340"/>
-    </row>
-    <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="340" t="s">
-        <v>395</v>
-      </c>
-      <c r="C163" s="340"/>
-      <c r="D163" s="340"/>
-      <c r="E163" s="340"/>
-      <c r="F163" s="340"/>
+      <c r="C164" s="347"/>
+      <c r="D164" s="347"/>
+      <c r="E164" s="347"/>
+      <c r="F164" s="347"/>
     </row>
     <row r="165" spans="2:6">
-      <c r="B165" s="1" t="s">
-        <v>401</v>
+      <c r="B165" s="238" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="166" spans="2:6">
       <c r="B166" s="238" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
     </row>
     <row r="167" spans="2:6">
       <c r="B167" s="238" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="168" spans="2:6">
-      <c r="B168" s="238" t="s">
-        <v>400</v>
+        <v>387</v>
+      </c>
+    </row>
+    <row r="169" spans="2:6">
+      <c r="B169" s="1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="170" spans="2:6" ht="46.5" customHeight="1">
+      <c r="B170" s="344" t="s">
+        <v>389</v>
+      </c>
+      <c r="C170" s="344"/>
+      <c r="D170" s="344"/>
+      <c r="E170" s="344"/>
+      <c r="F170" s="344"/>
+    </row>
+    <row r="172" spans="2:6">
+      <c r="B172" s="1" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="173" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B173" s="349" t="s">
+        <v>390</v>
+      </c>
+      <c r="C173" s="349"/>
+      <c r="D173" s="349"/>
+      <c r="E173" s="349"/>
+      <c r="F173" s="349"/>
+    </row>
+    <row r="174" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B174" s="349" t="s">
+        <v>391</v>
+      </c>
+      <c r="C174" s="349"/>
+      <c r="D174" s="349"/>
+      <c r="E174" s="349"/>
+      <c r="F174" s="349"/>
+    </row>
+    <row r="176" spans="2:6">
+      <c r="B176" s="1" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="177" spans="2:2">
+      <c r="B177" s="238" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="178" spans="2:2">
+      <c r="B178" s="238" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="179" spans="2:2">
+      <c r="B179" s="238" t="s">
+        <v>396</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B74:F74"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B39:F39"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B50:F50"/>
-    <mergeCell ref="B54:F54"/>
-    <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B79:F79"/>
+    <mergeCell ref="B86:F86"/>
+    <mergeCell ref="B106:F106"/>
+    <mergeCell ref="B128:F128"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="B55:F55"/>
+    <mergeCell ref="B59:F59"/>
+    <mergeCell ref="B68:F68"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="C16" xr:uid="{00000000-0002-0000-0000-000001000000}">
-      <formula1>"HKD,USD,CNY,EUR"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{45F807FD-9E0F-415A-9BBD-D5FB6470B56D}">
       <formula1>"Y, N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D68:D69" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D73:D74" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
       <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C22:D22" xr:uid="{00000000-0002-0000-0000-000001000000}">
+      <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5475,7 +5600,7 @@
   <sheetData>
     <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
-        <f>Thesis!C16</f>
+        <f>Thesis!C22</f>
         <v>HKD</v>
       </c>
       <c r="C1" s="104">
@@ -5954,7 +6079,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="C22" s="181">
         <v>346987</v>
@@ -5988,7 +6113,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="C23" s="181">
         <v>-67837</v>
@@ -6022,7 +6147,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="C24" s="181">
         <v>-423459</v>
@@ -6088,7 +6213,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>220</v>
+        <v>436</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -7383,7 +7508,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -7986,7 +8111,7 @@
       <formula>ISBLANK(C36)</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1" xr:uid="{87139493-416E-4F03-A3A9-B1C3E5C019E4}"/>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8761,7 +8886,7 @@
         <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="F45" s="287" t="s">
         <v>59</v>
@@ -8967,7 +9092,7 @@
         <v>137</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F65" s="287" t="s">
         <v>59</v>
@@ -9034,7 +9159,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="285" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C72" s="261" t="s">
         <v>96</v>
@@ -9046,7 +9171,7 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -9057,12 +9182,12 @@
         <v>-251053.08995184439</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="288" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
@@ -9073,12 +9198,12 @@
         <v>4.3392734190563456</v>
       </c>
       <c r="F74" s="283" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C75" s="293"/>
       <c r="D75" s="292">
@@ -9086,12 +9211,12 @@
         <v>502106.17990368878</v>
       </c>
       <c r="F75" s="283" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="290" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C76" s="291"/>
       <c r="D76" s="327">
@@ -9099,7 +9224,7 @@
         <v>2</v>
       </c>
       <c r="F76" s="283" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
@@ -9175,7 +9300,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9186,15 +9311,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="D85" s="270" t="s">
         <v>297</v>
-      </c>
-      <c r="D85" s="270" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="267" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
@@ -9211,7 +9336,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="267" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
@@ -9245,7 +9370,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
@@ -9289,7 +9414,7 @@
     <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
-        <f>Thesis!C16</f>
+        <f>Thesis!C22</f>
         <v>HKD</v>
       </c>
       <c r="C1" s="53" t="s">
@@ -10116,7 +10241,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="301" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -10141,7 +10266,7 @@
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="301" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10469,7 +10594,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="300" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10529,7 +10654,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="300" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10653,7 +10778,7 @@
         <v>-253206</v>
       </c>
       <c r="E33" s="300" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -10711,7 +10836,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="300" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -11019,7 +11144,7 @@
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="299" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -11158,7 +11283,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
@@ -11213,7 +11338,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="323" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C49" s="324">
         <f>BS!$C$66*C53</f>
@@ -11346,7 +11471,7 @@
         <v>0</v>
       </c>
       <c r="E53" s="299" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11373,7 +11498,7 @@
         <v>7.0042959818728018E-2</v>
       </c>
       <c r="E54" s="299" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11688,7 +11813,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="300" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -11917,7 +12042,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>59</v>
+        <v>437</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12249,7 +12374,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>365</v>
+        <v>438</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12928,7 +13053,7 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
@@ -13622,7 +13747,7 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="C113" s="170"/>
       <c r="E113" s="302"/>
@@ -13674,7 +13799,7 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="C114" s="170"/>
       <c r="E114" s="302"/>
@@ -14183,7 +14308,7 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -14984,7 +15109,7 @@
         <v>251</v>
       </c>
       <c r="F4" s="135">
-        <f>Thesis!C76</f>
+        <f>Thesis!C81</f>
         <v>0</v>
       </c>
       <c r="H4" s="121"/>
@@ -14994,7 +15119,7 @@
         <v>124</v>
       </c>
       <c r="C5" s="228">
-        <f>Thesis!C70</f>
+        <f>Thesis!C75</f>
         <v>0.08</v>
       </c>
       <c r="E5" s="149"/>
@@ -15012,10 +15137,10 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="348" t="s">
+      <c r="E6" s="351" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="348"/>
+      <c r="F6" s="351"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8">
@@ -15030,8 +15155,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="348"/>
-      <c r="F7" s="348"/>
+      <c r="E7" s="351"/>
+      <c r="F7" s="351"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8">
@@ -15046,8 +15171,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="348"/>
-      <c r="F8" s="348"/>
+      <c r="E8" s="351"/>
+      <c r="F8" s="351"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8">
@@ -15062,8 +15187,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="348"/>
-      <c r="F9" s="348"/>
+      <c r="E9" s="351"/>
+      <c r="F9" s="351"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -15089,7 +15214,7 @@
         <v>1</v>
       </c>
       <c r="D11" t="str">
-        <f>Thesis!D17</f>
+        <f>Thesis!C15</f>
         <v>HKD</v>
       </c>
       <c r="H11" s="121"/>
@@ -16408,7 +16533,7 @@
     </row>
     <row r="80" spans="1:8">
       <c r="B80" s="156" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C80" s="156" t="s">
         <v>106</v>
@@ -16480,7 +16605,7 @@
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="277" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I2" s="278"/>
     </row>
@@ -16557,11 +16682,11 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="350" t="str">
-        <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
+      <c r="E7" s="353" t="str">
+        <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 東方表行集團(0398.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="350"/>
+      <c r="F7" s="353"/>
       <c r="H7" s="276">
         <v>4</v>
       </c>
@@ -16582,8 +16707,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="350"/>
-      <c r="F8" s="350"/>
+      <c r="E8" s="353"/>
+      <c r="F8" s="353"/>
       <c r="H8" s="276">
         <v>5</v>
       </c>
@@ -16604,8 +16729,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="350"/>
-      <c r="F9" s="350"/>
+      <c r="E9" s="353"/>
+      <c r="F9" s="353"/>
       <c r="H9" s="276">
         <v>6</v>
       </c>
@@ -16615,8 +16740,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="350"/>
-      <c r="F10" s="350"/>
+      <c r="E10" s="353"/>
+      <c r="F10" s="353"/>
       <c r="H10" s="276">
         <v>7</v>
       </c>
@@ -16629,8 +16754,8 @@
       <c r="B11" s="160" t="s">
         <v>279</v>
       </c>
-      <c r="E11" s="350"/>
-      <c r="F11" s="350"/>
+      <c r="E11" s="353"/>
+      <c r="F11" s="353"/>
       <c r="H11" s="276">
         <v>8</v>
       </c>
@@ -16648,8 +16773,8 @@
         <v>1.2656410607081225E-2</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="350"/>
-      <c r="F12" s="350"/>
+      <c r="E12" s="353"/>
+      <c r="F12" s="353"/>
       <c r="H12" s="276">
         <v>9</v>
       </c>
@@ -16666,8 +16791,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>3.5687612277801151E-2</v>
       </c>
-      <c r="E13" s="350"/>
-      <c r="F13" s="350"/>
+      <c r="E13" s="353"/>
+      <c r="F13" s="353"/>
       <c r="H13" s="276">
         <v>10</v>
       </c>
@@ -16684,8 +16809,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>1.5957752466103425E-2</v>
       </c>
-      <c r="E14" s="350"/>
-      <c r="F14" s="350"/>
+      <c r="E14" s="353"/>
+      <c r="F14" s="353"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -16701,7 +16826,7 @@
         <v>152</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="18" spans="2:6">
@@ -16711,21 +16836,21 @@
       <c r="C18" s="151">
         <v>10</v>
       </c>
-      <c r="E18" s="350" t="s">
-        <v>340</v>
-      </c>
-      <c r="F18" s="351"/>
+      <c r="E18" s="353" t="s">
+        <v>338</v>
+      </c>
+      <c r="F18" s="354"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="351"/>
-      <c r="F19" s="351"/>
+      <c r="E19" s="354"/>
+      <c r="F19" s="354"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
-        <v>311</v>
-      </c>
-      <c r="E20" s="351"/>
-      <c r="F20" s="351"/>
+        <v>310</v>
+      </c>
+      <c r="E20" s="354"/>
+      <c r="F20" s="354"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -16739,8 +16864,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="351"/>
-      <c r="F21" s="351"/>
+      <c r="E21" s="354"/>
+      <c r="F21" s="354"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -16754,8 +16879,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="351"/>
-      <c r="F22" s="351"/>
+      <c r="E22" s="354"/>
+      <c r="F22" s="354"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
@@ -16775,8 +16900,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="349"/>
-      <c r="F25" s="349"/>
+      <c r="E25" s="352"/>
+      <c r="F25" s="352"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
@@ -16786,8 +16911,8 @@
         <v>0.04</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="349"/>
-      <c r="F26" s="349"/>
+      <c r="E26" s="352"/>
+      <c r="F26" s="352"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -16801,8 +16926,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="349"/>
-      <c r="F27" s="349"/>
+      <c r="E27" s="352"/>
+      <c r="F27" s="352"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -16812,8 +16937,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="349"/>
-      <c r="F28" s="349"/>
+      <c r="E28" s="352"/>
+      <c r="F28" s="352"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
@@ -16833,8 +16958,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="349"/>
-      <c r="F31" s="349"/>
+      <c r="E31" s="352"/>
+      <c r="F31" s="352"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
@@ -16844,8 +16969,8 @@
         <v>0.02</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="349"/>
-      <c r="F32" s="349"/>
+      <c r="E32" s="352"/>
+      <c r="F32" s="352"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -16859,8 +16984,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="349"/>
-      <c r="F33" s="349"/>
+      <c r="E33" s="352"/>
+      <c r="F33" s="352"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -16870,8 +16995,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="349"/>
-      <c r="F34" s="349"/>
+      <c r="E34" s="352"/>
+      <c r="F34" s="352"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
@@ -16891,8 +17016,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="349"/>
-      <c r="F37" s="349"/>
+      <c r="E37" s="352"/>
+      <c r="F37" s="352"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
@@ -16902,8 +17027,8 @@
         <v>0.06</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="349"/>
-      <c r="F38" s="349"/>
+      <c r="E38" s="352"/>
+      <c r="F38" s="352"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -16917,8 +17042,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="349"/>
-      <c r="F39" s="349"/>
+      <c r="E39" s="352"/>
+      <c r="F39" s="352"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -16929,8 +17054,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="349"/>
-      <c r="F40" s="349"/>
+      <c r="E40" s="352"/>
+      <c r="F40" s="352"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -16992,8 +17117,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="349"/>
-      <c r="F49" s="349"/>
+      <c r="E49" s="352"/>
+      <c r="F49" s="352"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
@@ -17003,8 +17128,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="349"/>
-      <c r="F50" s="349"/>
+      <c r="E50" s="352"/>
+      <c r="F50" s="352"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -17018,8 +17143,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="349"/>
-      <c r="F51" s="349"/>
+      <c r="E51" s="352"/>
+      <c r="F51" s="352"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -17029,12 +17154,12 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="349"/>
-      <c r="F52" s="349"/>
+      <c r="E52" s="352"/>
+      <c r="F52" s="352"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E54" s="160" t="s">
         <v>150</v>
@@ -17050,8 +17175,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="349"/>
-      <c r="F55" s="349"/>
+      <c r="E55" s="352"/>
+      <c r="F55" s="352"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
@@ -17061,8 +17186,8 @@
         <v>0.1</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="349"/>
-      <c r="F56" s="349"/>
+      <c r="E56" s="352"/>
+      <c r="F56" s="352"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -17076,8 +17201,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="349"/>
-      <c r="F57" s="349"/>
+      <c r="E57" s="352"/>
+      <c r="F57" s="352"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -17087,8 +17212,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="349"/>
-      <c r="F58" s="349"/>
+      <c r="E58" s="352"/>
+      <c r="F58" s="352"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -17103,16 +17228,16 @@
         <v>HKD</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F60" s="312">
-        <f>Thesis!E20</f>
+        <f>Thesis!E25</f>
         <v>3</v>
       </c>
     </row>
     <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -17121,10 +17246,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E63" s="282" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -17137,7 +17262,7 @@
       </c>
       <c r="D64" s="151"/>
       <c r="E64" s="281" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
     </row>
     <row r="65" spans="2:6">
@@ -17149,7 +17274,7 @@
       </c>
       <c r="D65" s="152"/>
       <c r="E65" s="281" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="66" spans="2:6">
@@ -17165,20 +17290,20 @@
         <v>HKD</v>
       </c>
       <c r="E66" s="281" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E68" s="282" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C69" s="273" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -17188,19 +17313,19 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C70" s="273" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="281" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C71" s="273" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -17210,14 +17335,14 @@
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C72" s="272" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
@@ -17240,7 +17365,7 @@
     </row>
     <row r="76" spans="2:6">
       <c r="B76" s="275" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C76" s="274">
         <f>F60</f>
@@ -17263,15 +17388,15 @@
     </row>
     <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="149" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C80" s="168">
-        <f>Thesis!C127</f>
+        <f>Thesis!C132</f>
         <v>0.3</v>
       </c>
     </row>
@@ -17322,12 +17447,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="86" spans="2:8">
       <c r="B86" s="149" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
@@ -17340,7 +17465,7 @@
     </row>
     <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
@@ -17352,15 +17477,15 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="C90" s="168">
-        <f>Thesis!E19</f>
+        <f>Thesis!E24</f>
         <v>0.2</v>
       </c>
     </row>
@@ -17408,17 +17533,17 @@
     </row>
     <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="316"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="C96" s="135">
-        <f>Thesis!C67</f>
+        <f>Thesis!C72</f>
         <v>0.08</v>
       </c>
       <c r="G96" s="2"/>
@@ -17450,14 +17575,14 @@
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="111" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
         <v>4.2691663056616189</v>
       </c>
       <c r="D99" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="E99" s="147" t="s">
         <v>127</v>
@@ -17472,32 +17597,32 @@
     </row>
     <row r="101" spans="2:8" ht="14.65">
       <c r="E101" s="320" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="F101" s="317"/>
     </row>
     <row r="102" spans="2:8" ht="13.9">
       <c r="E102" s="313" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F102" s="318" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="103" spans="2:8" ht="13.9">
       <c r="E103" s="314" t="s">
+        <v>333</v>
+      </c>
+      <c r="F103" s="318" t="s">
         <v>335</v>
-      </c>
-      <c r="F103" s="318" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="104" spans="2:8" ht="13.9">
       <c r="E104" s="315" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F104" s="319" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/opportunities/0398.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0398.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5F66945-78AF-4FA6-BAFA-B23696F60EAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1091592-3A49-46A1-A667-0F8D61184680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3782,29 +3782,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4264,13 +4264,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="343" t="s">
+      <c r="B18" s="345" t="s">
         <v>367</v>
       </c>
-      <c r="C18" s="343"/>
-      <c r="D18" s="343"/>
-      <c r="E18" s="343"/>
-      <c r="F18" s="343"/>
+      <c r="C18" s="345"/>
+      <c r="D18" s="345"/>
+      <c r="E18" s="345"/>
+      <c r="F18" s="345"/>
     </row>
     <row r="20" spans="1:6">
       <c r="B20" s="45" t="s">
@@ -4370,22 +4370,22 @@
       <c r="F28" s="36"/>
     </row>
     <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="343" t="s">
+      <c r="B30" s="345" t="s">
         <v>368</v>
       </c>
-      <c r="C30" s="343"/>
-      <c r="D30" s="343"/>
-      <c r="E30" s="343"/>
-      <c r="F30" s="343"/>
+      <c r="C30" s="345"/>
+      <c r="D30" s="345"/>
+      <c r="E30" s="345"/>
+      <c r="F30" s="345"/>
     </row>
     <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="345" t="s">
+      <c r="B31" s="348" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="345"/>
-      <c r="D31" s="345"/>
-      <c r="E31" s="345"/>
-      <c r="F31" s="345"/>
+      <c r="C31" s="348"/>
+      <c r="D31" s="348"/>
+      <c r="E31" s="348"/>
+      <c r="F31" s="348"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="234" t="s">
@@ -4397,13 +4397,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="344" t="s">
+      <c r="B34" s="346" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="344"/>
-      <c r="D34" s="344"/>
-      <c r="E34" s="344"/>
-      <c r="F34" s="344"/>
+      <c r="C34" s="346"/>
+      <c r="D34" s="346"/>
+      <c r="E34" s="346"/>
+      <c r="F34" s="346"/>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="47" t="s">
@@ -4423,13 +4423,13 @@
       <c r="C36" s="76"/>
     </row>
     <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="344" t="s">
+      <c r="B37" s="346" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="344"/>
-      <c r="D37" s="344"/>
-      <c r="E37" s="344"/>
-      <c r="F37" s="344"/>
+      <c r="C37" s="346"/>
+      <c r="D37" s="346"/>
+      <c r="E37" s="346"/>
+      <c r="F37" s="346"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="47" t="s">
@@ -4458,13 +4458,13 @@
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="344" t="s">
+      <c r="B41" s="346" t="s">
         <v>237</v>
       </c>
-      <c r="C41" s="344"/>
-      <c r="D41" s="344"/>
-      <c r="E41" s="344"/>
-      <c r="F41" s="344"/>
+      <c r="C41" s="346"/>
+      <c r="D41" s="346"/>
+      <c r="E41" s="346"/>
+      <c r="F41" s="346"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
@@ -4480,13 +4480,13 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="344" t="s">
+      <c r="B44" s="346" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="344"/>
-      <c r="D44" s="344"/>
-      <c r="E44" s="344"/>
-      <c r="F44" s="344"/>
+      <c r="C44" s="346"/>
+      <c r="D44" s="346"/>
+      <c r="E44" s="346"/>
+      <c r="F44" s="346"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
@@ -4550,13 +4550,13 @@
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="344" t="s">
+      <c r="B52" s="346" t="s">
         <v>242</v>
       </c>
-      <c r="C52" s="344"/>
-      <c r="D52" s="344"/>
-      <c r="E52" s="344"/>
-      <c r="F52" s="344"/>
+      <c r="C52" s="346"/>
+      <c r="D52" s="346"/>
+      <c r="E52" s="346"/>
+      <c r="F52" s="346"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4572,7 +4572,7 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="344" t="s">
+      <c r="B55" s="346" t="s">
         <v>346</v>
       </c>
       <c r="C55" s="347"/>
@@ -4594,22 +4594,22 @@
       </c>
     </row>
     <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="343" t="s">
+      <c r="B58" s="345" t="s">
         <v>351</v>
       </c>
-      <c r="C58" s="343"/>
-      <c r="D58" s="343"/>
-      <c r="E58" s="343"/>
-      <c r="F58" s="343"/>
+      <c r="C58" s="345"/>
+      <c r="D58" s="345"/>
+      <c r="E58" s="345"/>
+      <c r="F58" s="345"/>
     </row>
     <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="343" t="s">
+      <c r="B59" s="345" t="s">
         <v>369</v>
       </c>
-      <c r="C59" s="343"/>
-      <c r="D59" s="343"/>
-      <c r="E59" s="343"/>
-      <c r="F59" s="343"/>
+      <c r="C59" s="345"/>
+      <c r="D59" s="345"/>
+      <c r="E59" s="345"/>
+      <c r="F59" s="345"/>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="47" t="s">
@@ -4670,22 +4670,22 @@
     </row>
     <row r="68" spans="1:6" ht="24.4" customHeight="1">
       <c r="A68" s="17"/>
-      <c r="B68" s="343" t="s">
+      <c r="B68" s="345" t="s">
         <v>370</v>
       </c>
-      <c r="C68" s="343"/>
-      <c r="D68" s="343"/>
-      <c r="E68" s="343"/>
-      <c r="F68" s="343"/>
+      <c r="C68" s="345"/>
+      <c r="D68" s="345"/>
+      <c r="E68" s="345"/>
+      <c r="F68" s="345"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="345" t="s">
+      <c r="B69" s="348" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="345"/>
-      <c r="D69" s="345"/>
-      <c r="E69" s="345"/>
-      <c r="F69" s="345"/>
+      <c r="C69" s="348"/>
+      <c r="D69" s="348"/>
+      <c r="E69" s="348"/>
+      <c r="F69" s="348"/>
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="234" t="s">
@@ -4743,22 +4743,22 @@
       <c r="C77" s="122"/>
     </row>
     <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="343" t="s">
+      <c r="B78" s="345" t="s">
         <v>371</v>
       </c>
-      <c r="C78" s="343"/>
-      <c r="D78" s="343"/>
-      <c r="E78" s="343"/>
-      <c r="F78" s="343"/>
+      <c r="C78" s="345"/>
+      <c r="D78" s="345"/>
+      <c r="E78" s="345"/>
+      <c r="F78" s="345"/>
     </row>
     <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="343" t="s">
+      <c r="B79" s="345" t="s">
         <v>372</v>
       </c>
-      <c r="C79" s="343"/>
-      <c r="D79" s="343"/>
-      <c r="E79" s="343"/>
-      <c r="F79" s="343"/>
+      <c r="C79" s="345"/>
+      <c r="D79" s="345"/>
+      <c r="E79" s="345"/>
+      <c r="F79" s="345"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="47" t="s">
@@ -4795,13 +4795,13 @@
       <c r="A85" s="233"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="B86" s="343" t="s">
+      <c r="B86" s="345" t="s">
         <v>373</v>
       </c>
-      <c r="C86" s="343"/>
-      <c r="D86" s="343"/>
-      <c r="E86" s="343"/>
-      <c r="F86" s="343"/>
+      <c r="C86" s="345"/>
+      <c r="D86" s="345"/>
+      <c r="E86" s="345"/>
+      <c r="F86" s="345"/>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="1" t="s">
@@ -4814,13 +4814,13 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="343" t="s">
+      <c r="B90" s="345" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="343"/>
-      <c r="D90" s="343"/>
-      <c r="E90" s="343"/>
-      <c r="F90" s="343"/>
+      <c r="C90" s="345"/>
+      <c r="D90" s="345"/>
+      <c r="E90" s="345"/>
+      <c r="F90" s="345"/>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" s="47" t="s">
@@ -4951,13 +4951,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="343" t="s">
+      <c r="B106" s="345" t="s">
         <v>374</v>
       </c>
-      <c r="C106" s="343"/>
-      <c r="D106" s="343"/>
-      <c r="E106" s="343"/>
-      <c r="F106" s="343"/>
+      <c r="C106" s="345"/>
+      <c r="D106" s="345"/>
+      <c r="E106" s="345"/>
+      <c r="F106" s="345"/>
     </row>
     <row r="108" spans="1:6">
       <c r="B108" s="47" t="s">
@@ -4996,13 +4996,13 @@
       <c r="F111" s="36"/>
     </row>
     <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="344" t="s">
+      <c r="B113" s="346" t="s">
         <v>375</v>
       </c>
-      <c r="C113" s="344"/>
-      <c r="D113" s="344"/>
-      <c r="E113" s="344"/>
-      <c r="F113" s="344"/>
+      <c r="C113" s="346"/>
+      <c r="D113" s="346"/>
+      <c r="E113" s="346"/>
+      <c r="F113" s="346"/>
     </row>
     <row r="115" spans="1:6" ht="12.4">
       <c r="B115" s="260" t="s">
@@ -5145,13 +5145,13 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="348" t="s">
+      <c r="B124" s="349" t="s">
         <v>378</v>
       </c>
-      <c r="C124" s="348"/>
-      <c r="D124" s="348"/>
-      <c r="E124" s="348"/>
-      <c r="F124" s="348"/>
+      <c r="C124" s="349"/>
+      <c r="D124" s="349"/>
+      <c r="E124" s="349"/>
+      <c r="F124" s="349"/>
     </row>
     <row r="126" spans="1:6" ht="13.9">
       <c r="A126" s="247" t="s">
@@ -5164,22 +5164,22 @@
       <c r="F126" s="36"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="B128" s="346" t="s">
+      <c r="B128" s="350" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="346"/>
-      <c r="D128" s="346"/>
-      <c r="E128" s="346"/>
-      <c r="F128" s="346"/>
+      <c r="C128" s="350"/>
+      <c r="D128" s="350"/>
+      <c r="E128" s="350"/>
+      <c r="F128" s="350"/>
     </row>
     <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="343" t="s">
+      <c r="B129" s="345" t="s">
         <v>377</v>
       </c>
-      <c r="C129" s="343"/>
-      <c r="D129" s="343"/>
-      <c r="E129" s="343"/>
-      <c r="F129" s="343"/>
+      <c r="C129" s="345"/>
+      <c r="D129" s="345"/>
+      <c r="E129" s="345"/>
+      <c r="F129" s="345"/>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="234" t="s">
@@ -5443,13 +5443,13 @@
       <c r="F159" s="36"/>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="350" t="s">
+      <c r="B161" s="344" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="343"/>
-      <c r="D161" s="343"/>
-      <c r="E161" s="343"/>
-      <c r="F161" s="343"/>
+      <c r="C161" s="345"/>
+      <c r="D161" s="345"/>
+      <c r="E161" s="345"/>
+      <c r="F161" s="345"/>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="234" t="s">
@@ -5486,13 +5486,13 @@
       </c>
     </row>
     <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="344" t="s">
+      <c r="B170" s="346" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="344"/>
-      <c r="D170" s="344"/>
-      <c r="E170" s="344"/>
-      <c r="F170" s="344"/>
+      <c r="C170" s="346"/>
+      <c r="D170" s="346"/>
+      <c r="E170" s="346"/>
+      <c r="F170" s="346"/>
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="1" t="s">
@@ -5500,22 +5500,22 @@
       </c>
     </row>
     <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="349" t="s">
+      <c r="B173" s="343" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="349"/>
-      <c r="D173" s="349"/>
-      <c r="E173" s="349"/>
-      <c r="F173" s="349"/>
+      <c r="C173" s="343"/>
+      <c r="D173" s="343"/>
+      <c r="E173" s="343"/>
+      <c r="F173" s="343"/>
     </row>
     <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="349" t="s">
+      <c r="B174" s="343" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="349"/>
-      <c r="D174" s="349"/>
-      <c r="E174" s="349"/>
-      <c r="F174" s="349"/>
+      <c r="C174" s="343"/>
+      <c r="D174" s="343"/>
+      <c r="E174" s="343"/>
+      <c r="F174" s="343"/>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="1" t="s">
@@ -5539,17 +5539,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B18:F18"/>
@@ -5566,6 +5555,17 @@
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B68:F68"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -8621,7 +8621,7 @@
       <c r="F28" s="210" t="s">
         <v>245</v>
       </c>
-      <c r="G28" s="181">
+      <c r="G28" s="12">
         <v>1765</v>
       </c>
       <c r="H28" s="209"/>

--- a/financial_models/opportunities/0398.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0398.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1091592-3A49-46A1-A667-0F8D61184680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8418E759-37DA-42D1-8A99-6D8F51A01D3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3782,29 +3782,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4226,8 +4226,7 @@
         <v>429</v>
       </c>
       <c r="C14" s="35">
-        <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>1739.8688596799998</v>
+        <v>1</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4264,13 +4263,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="345" t="s">
+      <c r="B18" s="343" t="s">
         <v>367</v>
       </c>
-      <c r="C18" s="345"/>
-      <c r="D18" s="345"/>
-      <c r="E18" s="345"/>
-      <c r="F18" s="345"/>
+      <c r="C18" s="343"/>
+      <c r="D18" s="343"/>
+      <c r="E18" s="343"/>
+      <c r="F18" s="343"/>
     </row>
     <row r="20" spans="1:6">
       <c r="B20" s="45" t="s">
@@ -4319,7 +4318,7 @@
         <v>277</v>
       </c>
       <c r="C24" s="249">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>417</v>
@@ -4335,7 +4334,7 @@
       </c>
       <c r="C25" s="252">
         <f>C139</f>
-        <v>2.4911701525888064</v>
+        <v>2.0118297468067095</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>315</v>
@@ -4370,22 +4369,22 @@
       <c r="F28" s="36"/>
     </row>
     <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="345" t="s">
+      <c r="B30" s="343" t="s">
         <v>368</v>
       </c>
-      <c r="C30" s="345"/>
-      <c r="D30" s="345"/>
-      <c r="E30" s="345"/>
-      <c r="F30" s="345"/>
+      <c r="C30" s="343"/>
+      <c r="D30" s="343"/>
+      <c r="E30" s="343"/>
+      <c r="F30" s="343"/>
     </row>
     <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="348" t="s">
+      <c r="B31" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="348"/>
-      <c r="D31" s="348"/>
-      <c r="E31" s="348"/>
-      <c r="F31" s="348"/>
+      <c r="C31" s="345"/>
+      <c r="D31" s="345"/>
+      <c r="E31" s="345"/>
+      <c r="F31" s="345"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="234" t="s">
@@ -4397,13 +4396,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="346" t="s">
+      <c r="B34" s="344" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="346"/>
-      <c r="D34" s="346"/>
-      <c r="E34" s="346"/>
-      <c r="F34" s="346"/>
+      <c r="C34" s="344"/>
+      <c r="D34" s="344"/>
+      <c r="E34" s="344"/>
+      <c r="F34" s="344"/>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="47" t="s">
@@ -4423,13 +4422,13 @@
       <c r="C36" s="76"/>
     </row>
     <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="346" t="s">
+      <c r="B37" s="344" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="346"/>
-      <c r="D37" s="346"/>
-      <c r="E37" s="346"/>
-      <c r="F37" s="346"/>
+      <c r="C37" s="344"/>
+      <c r="D37" s="344"/>
+      <c r="E37" s="344"/>
+      <c r="F37" s="344"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="47" t="s">
@@ -4458,13 +4457,13 @@
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="346" t="s">
+      <c r="B41" s="344" t="s">
         <v>237</v>
       </c>
-      <c r="C41" s="346"/>
-      <c r="D41" s="346"/>
-      <c r="E41" s="346"/>
-      <c r="F41" s="346"/>
+      <c r="C41" s="344"/>
+      <c r="D41" s="344"/>
+      <c r="E41" s="344"/>
+      <c r="F41" s="344"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
@@ -4480,13 +4479,13 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="346" t="s">
+      <c r="B44" s="344" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="346"/>
-      <c r="D44" s="346"/>
-      <c r="E44" s="346"/>
-      <c r="F44" s="346"/>
+      <c r="C44" s="344"/>
+      <c r="D44" s="344"/>
+      <c r="E44" s="344"/>
+      <c r="F44" s="344"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
@@ -4550,13 +4549,13 @@
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="346" t="s">
+      <c r="B52" s="344" t="s">
         <v>242</v>
       </c>
-      <c r="C52" s="346"/>
-      <c r="D52" s="346"/>
-      <c r="E52" s="346"/>
-      <c r="F52" s="346"/>
+      <c r="C52" s="344"/>
+      <c r="D52" s="344"/>
+      <c r="E52" s="344"/>
+      <c r="F52" s="344"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4572,7 +4571,7 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="346" t="s">
+      <c r="B55" s="344" t="s">
         <v>346</v>
       </c>
       <c r="C55" s="347"/>
@@ -4594,22 +4593,22 @@
       </c>
     </row>
     <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="345" t="s">
+      <c r="B58" s="343" t="s">
         <v>351</v>
       </c>
-      <c r="C58" s="345"/>
-      <c r="D58" s="345"/>
-      <c r="E58" s="345"/>
-      <c r="F58" s="345"/>
+      <c r="C58" s="343"/>
+      <c r="D58" s="343"/>
+      <c r="E58" s="343"/>
+      <c r="F58" s="343"/>
     </row>
     <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="345" t="s">
+      <c r="B59" s="343" t="s">
         <v>369</v>
       </c>
-      <c r="C59" s="345"/>
-      <c r="D59" s="345"/>
-      <c r="E59" s="345"/>
-      <c r="F59" s="345"/>
+      <c r="C59" s="343"/>
+      <c r="D59" s="343"/>
+      <c r="E59" s="343"/>
+      <c r="F59" s="343"/>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="47" t="s">
@@ -4670,22 +4669,22 @@
     </row>
     <row r="68" spans="1:6" ht="24.4" customHeight="1">
       <c r="A68" s="17"/>
-      <c r="B68" s="345" t="s">
+      <c r="B68" s="343" t="s">
         <v>370</v>
       </c>
-      <c r="C68" s="345"/>
-      <c r="D68" s="345"/>
-      <c r="E68" s="345"/>
-      <c r="F68" s="345"/>
+      <c r="C68" s="343"/>
+      <c r="D68" s="343"/>
+      <c r="E68" s="343"/>
+      <c r="F68" s="343"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="348" t="s">
+      <c r="B69" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="348"/>
-      <c r="D69" s="348"/>
-      <c r="E69" s="348"/>
-      <c r="F69" s="348"/>
+      <c r="C69" s="345"/>
+      <c r="D69" s="345"/>
+      <c r="E69" s="345"/>
+      <c r="F69" s="345"/>
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="234" t="s">
@@ -4743,22 +4742,22 @@
       <c r="C77" s="122"/>
     </row>
     <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="345" t="s">
+      <c r="B78" s="343" t="s">
         <v>371</v>
       </c>
-      <c r="C78" s="345"/>
-      <c r="D78" s="345"/>
-      <c r="E78" s="345"/>
-      <c r="F78" s="345"/>
+      <c r="C78" s="343"/>
+      <c r="D78" s="343"/>
+      <c r="E78" s="343"/>
+      <c r="F78" s="343"/>
     </row>
     <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="345" t="s">
+      <c r="B79" s="343" t="s">
         <v>372</v>
       </c>
-      <c r="C79" s="345"/>
-      <c r="D79" s="345"/>
-      <c r="E79" s="345"/>
-      <c r="F79" s="345"/>
+      <c r="C79" s="343"/>
+      <c r="D79" s="343"/>
+      <c r="E79" s="343"/>
+      <c r="F79" s="343"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="47" t="s">
@@ -4795,13 +4794,13 @@
       <c r="A85" s="233"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="B86" s="345" t="s">
+      <c r="B86" s="343" t="s">
         <v>373</v>
       </c>
-      <c r="C86" s="345"/>
-      <c r="D86" s="345"/>
-      <c r="E86" s="345"/>
-      <c r="F86" s="345"/>
+      <c r="C86" s="343"/>
+      <c r="D86" s="343"/>
+      <c r="E86" s="343"/>
+      <c r="F86" s="343"/>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="1" t="s">
@@ -4814,13 +4813,13 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="345" t="s">
+      <c r="B90" s="343" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="345"/>
-      <c r="D90" s="345"/>
-      <c r="E90" s="345"/>
-      <c r="F90" s="345"/>
+      <c r="C90" s="343"/>
+      <c r="D90" s="343"/>
+      <c r="E90" s="343"/>
+      <c r="F90" s="343"/>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" s="47" t="s">
@@ -4951,13 +4950,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="345" t="s">
+      <c r="B106" s="343" t="s">
         <v>374</v>
       </c>
-      <c r="C106" s="345"/>
-      <c r="D106" s="345"/>
-      <c r="E106" s="345"/>
-      <c r="F106" s="345"/>
+      <c r="C106" s="343"/>
+      <c r="D106" s="343"/>
+      <c r="E106" s="343"/>
+      <c r="F106" s="343"/>
     </row>
     <row r="108" spans="1:6">
       <c r="B108" s="47" t="s">
@@ -4996,13 +4995,13 @@
       <c r="F111" s="36"/>
     </row>
     <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="346" t="s">
+      <c r="B113" s="344" t="s">
         <v>375</v>
       </c>
-      <c r="C113" s="346"/>
-      <c r="D113" s="346"/>
-      <c r="E113" s="346"/>
-      <c r="F113" s="346"/>
+      <c r="C113" s="344"/>
+      <c r="D113" s="344"/>
+      <c r="E113" s="344"/>
+      <c r="F113" s="344"/>
     </row>
     <row r="115" spans="1:6" ht="12.4">
       <c r="B115" s="260" t="s">
@@ -5145,13 +5144,13 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="349" t="s">
+      <c r="B124" s="348" t="s">
         <v>378</v>
       </c>
-      <c r="C124" s="349"/>
-      <c r="D124" s="349"/>
-      <c r="E124" s="349"/>
-      <c r="F124" s="349"/>
+      <c r="C124" s="348"/>
+      <c r="D124" s="348"/>
+      <c r="E124" s="348"/>
+      <c r="F124" s="348"/>
     </row>
     <row r="126" spans="1:6" ht="13.9">
       <c r="A126" s="247" t="s">
@@ -5164,22 +5163,22 @@
       <c r="F126" s="36"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="B128" s="350" t="s">
+      <c r="B128" s="346" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="350"/>
-      <c r="D128" s="350"/>
-      <c r="E128" s="350"/>
-      <c r="F128" s="350"/>
+      <c r="C128" s="346"/>
+      <c r="D128" s="346"/>
+      <c r="E128" s="346"/>
+      <c r="F128" s="346"/>
     </row>
     <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="345" t="s">
+      <c r="B129" s="343" t="s">
         <v>377</v>
       </c>
-      <c r="C129" s="345"/>
-      <c r="D129" s="345"/>
-      <c r="E129" s="345"/>
-      <c r="F129" s="345"/>
+      <c r="C129" s="343"/>
+      <c r="D129" s="343"/>
+      <c r="E129" s="343"/>
+      <c r="F129" s="343"/>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="234" t="s">
@@ -5201,7 +5200,7 @@
       </c>
       <c r="C132" s="250">
         <f>C24</f>
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="133" spans="2:6">
@@ -5236,7 +5235,7 @@
       </c>
       <c r="C136" s="337">
         <f>C24</f>
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="137" spans="2:6">
@@ -5246,7 +5245,7 @@
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C81</f>
-        <v>0.23246244879380981</v>
+        <v>0.20338192419825066</v>
       </c>
     </row>
     <row r="138" spans="2:6">
@@ -5256,7 +5255,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C82</f>
-        <v>2.2587077037949967</v>
+        <v>1.8084478226084586</v>
       </c>
     </row>
     <row r="139" spans="2:6">
@@ -5265,7 +5264,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C83</f>
-        <v>2.4911701525888064</v>
+        <v>2.0118297468067095</v>
       </c>
       <c r="D139" s="342" t="str">
         <f>IF($D$11="","",C139*$E$22)</f>
@@ -5291,7 +5290,7 @@
       </c>
       <c r="C141" s="92">
         <f>Scenarios!F83</f>
-        <v>0.49798892097937209</v>
+        <v>0.59458376580552363</v>
       </c>
     </row>
     <row r="143" spans="2:6">
@@ -5443,13 +5442,13 @@
       <c r="F159" s="36"/>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="344" t="s">
+      <c r="B161" s="350" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="345"/>
-      <c r="D161" s="345"/>
-      <c r="E161" s="345"/>
-      <c r="F161" s="345"/>
+      <c r="C161" s="343"/>
+      <c r="D161" s="343"/>
+      <c r="E161" s="343"/>
+      <c r="F161" s="343"/>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="234" t="s">
@@ -5486,13 +5485,13 @@
       </c>
     </row>
     <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="346" t="s">
+      <c r="B170" s="344" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="346"/>
-      <c r="D170" s="346"/>
-      <c r="E170" s="346"/>
-      <c r="F170" s="346"/>
+      <c r="C170" s="344"/>
+      <c r="D170" s="344"/>
+      <c r="E170" s="344"/>
+      <c r="F170" s="344"/>
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="1" t="s">
@@ -5500,22 +5499,22 @@
       </c>
     </row>
     <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="343" t="s">
+      <c r="B173" s="349" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="343"/>
-      <c r="D173" s="343"/>
-      <c r="E173" s="343"/>
-      <c r="F173" s="343"/>
+      <c r="C173" s="349"/>
+      <c r="D173" s="349"/>
+      <c r="E173" s="349"/>
+      <c r="F173" s="349"/>
     </row>
     <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="343" t="s">
+      <c r="B174" s="349" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="343"/>
-      <c r="D174" s="343"/>
-      <c r="E174" s="343"/>
-      <c r="F174" s="343"/>
+      <c r="C174" s="349"/>
+      <c r="D174" s="349"/>
+      <c r="E174" s="349"/>
+      <c r="F174" s="349"/>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="1" t="s">
@@ -5539,6 +5538,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B18:F18"/>
@@ -5555,17 +5565,6 @@
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B68:F68"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -17397,7 +17396,7 @@
       </c>
       <c r="C80" s="168">
         <f>Thesis!C132</f>
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -17406,7 +17405,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.23246244879380981</v>
+        <v>0.20338192419825066</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17418,7 +17417,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>2.2587077037949967</v>
+        <v>1.8084478226084586</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17428,7 +17427,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>2.4911701525888064</v>
+        <v>2.0118297468067095</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17439,7 +17438,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.49798892097937209</v>
+        <v>0.59458376580552363</v>
       </c>
     </row>
     <row r="84" spans="2:8">

--- a/financial_models/opportunities/0398.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0398.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8418E759-37DA-42D1-8A99-6D8F51A01D3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AFCCBF1-1E2A-4BEE-878D-41374224D27A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3782,29 +3782,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4226,7 +4226,8 @@
         <v>429</v>
       </c>
       <c r="C14" s="35">
-        <v>1</v>
+        <f>Thesis!C12*Common_Shares/1000000</f>
+        <v>1739.8688596799998</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4263,13 +4264,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="343" t="s">
+      <c r="B18" s="345" t="s">
         <v>367</v>
       </c>
-      <c r="C18" s="343"/>
-      <c r="D18" s="343"/>
-      <c r="E18" s="343"/>
-      <c r="F18" s="343"/>
+      <c r="C18" s="345"/>
+      <c r="D18" s="345"/>
+      <c r="E18" s="345"/>
+      <c r="F18" s="345"/>
     </row>
     <row r="20" spans="1:6">
       <c r="B20" s="45" t="s">
@@ -4369,22 +4370,22 @@
       <c r="F28" s="36"/>
     </row>
     <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="343" t="s">
+      <c r="B30" s="345" t="s">
         <v>368</v>
       </c>
-      <c r="C30" s="343"/>
-      <c r="D30" s="343"/>
-      <c r="E30" s="343"/>
-      <c r="F30" s="343"/>
+      <c r="C30" s="345"/>
+      <c r="D30" s="345"/>
+      <c r="E30" s="345"/>
+      <c r="F30" s="345"/>
     </row>
     <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="345" t="s">
+      <c r="B31" s="348" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="345"/>
-      <c r="D31" s="345"/>
-      <c r="E31" s="345"/>
-      <c r="F31" s="345"/>
+      <c r="C31" s="348"/>
+      <c r="D31" s="348"/>
+      <c r="E31" s="348"/>
+      <c r="F31" s="348"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="234" t="s">
@@ -4396,13 +4397,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="344" t="s">
+      <c r="B34" s="346" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="344"/>
-      <c r="D34" s="344"/>
-      <c r="E34" s="344"/>
-      <c r="F34" s="344"/>
+      <c r="C34" s="346"/>
+      <c r="D34" s="346"/>
+      <c r="E34" s="346"/>
+      <c r="F34" s="346"/>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="47" t="s">
@@ -4422,13 +4423,13 @@
       <c r="C36" s="76"/>
     </row>
     <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="344" t="s">
+      <c r="B37" s="346" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="344"/>
-      <c r="D37" s="344"/>
-      <c r="E37" s="344"/>
-      <c r="F37" s="344"/>
+      <c r="C37" s="346"/>
+      <c r="D37" s="346"/>
+      <c r="E37" s="346"/>
+      <c r="F37" s="346"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="47" t="s">
@@ -4457,13 +4458,13 @@
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="344" t="s">
+      <c r="B41" s="346" t="s">
         <v>237</v>
       </c>
-      <c r="C41" s="344"/>
-      <c r="D41" s="344"/>
-      <c r="E41" s="344"/>
-      <c r="F41" s="344"/>
+      <c r="C41" s="346"/>
+      <c r="D41" s="346"/>
+      <c r="E41" s="346"/>
+      <c r="F41" s="346"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
@@ -4479,13 +4480,13 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="344" t="s">
+      <c r="B44" s="346" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="344"/>
-      <c r="D44" s="344"/>
-      <c r="E44" s="344"/>
-      <c r="F44" s="344"/>
+      <c r="C44" s="346"/>
+      <c r="D44" s="346"/>
+      <c r="E44" s="346"/>
+      <c r="F44" s="346"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
@@ -4549,13 +4550,13 @@
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="344" t="s">
+      <c r="B52" s="346" t="s">
         <v>242</v>
       </c>
-      <c r="C52" s="344"/>
-      <c r="D52" s="344"/>
-      <c r="E52" s="344"/>
-      <c r="F52" s="344"/>
+      <c r="C52" s="346"/>
+      <c r="D52" s="346"/>
+      <c r="E52" s="346"/>
+      <c r="F52" s="346"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4571,7 +4572,7 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="344" t="s">
+      <c r="B55" s="346" t="s">
         <v>346</v>
       </c>
       <c r="C55" s="347"/>
@@ -4593,22 +4594,22 @@
       </c>
     </row>
     <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="343" t="s">
+      <c r="B58" s="345" t="s">
         <v>351</v>
       </c>
-      <c r="C58" s="343"/>
-      <c r="D58" s="343"/>
-      <c r="E58" s="343"/>
-      <c r="F58" s="343"/>
+      <c r="C58" s="345"/>
+      <c r="D58" s="345"/>
+      <c r="E58" s="345"/>
+      <c r="F58" s="345"/>
     </row>
     <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="343" t="s">
+      <c r="B59" s="345" t="s">
         <v>369</v>
       </c>
-      <c r="C59" s="343"/>
-      <c r="D59" s="343"/>
-      <c r="E59" s="343"/>
-      <c r="F59" s="343"/>
+      <c r="C59" s="345"/>
+      <c r="D59" s="345"/>
+      <c r="E59" s="345"/>
+      <c r="F59" s="345"/>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="47" t="s">
@@ -4669,22 +4670,22 @@
     </row>
     <row r="68" spans="1:6" ht="24.4" customHeight="1">
       <c r="A68" s="17"/>
-      <c r="B68" s="343" t="s">
+      <c r="B68" s="345" t="s">
         <v>370</v>
       </c>
-      <c r="C68" s="343"/>
-      <c r="D68" s="343"/>
-      <c r="E68" s="343"/>
-      <c r="F68" s="343"/>
+      <c r="C68" s="345"/>
+      <c r="D68" s="345"/>
+      <c r="E68" s="345"/>
+      <c r="F68" s="345"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="345" t="s">
+      <c r="B69" s="348" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="345"/>
-      <c r="D69" s="345"/>
-      <c r="E69" s="345"/>
-      <c r="F69" s="345"/>
+      <c r="C69" s="348"/>
+      <c r="D69" s="348"/>
+      <c r="E69" s="348"/>
+      <c r="F69" s="348"/>
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="234" t="s">
@@ -4742,22 +4743,22 @@
       <c r="C77" s="122"/>
     </row>
     <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="343" t="s">
+      <c r="B78" s="345" t="s">
         <v>371</v>
       </c>
-      <c r="C78" s="343"/>
-      <c r="D78" s="343"/>
-      <c r="E78" s="343"/>
-      <c r="F78" s="343"/>
+      <c r="C78" s="345"/>
+      <c r="D78" s="345"/>
+      <c r="E78" s="345"/>
+      <c r="F78" s="345"/>
     </row>
     <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="343" t="s">
+      <c r="B79" s="345" t="s">
         <v>372</v>
       </c>
-      <c r="C79" s="343"/>
-      <c r="D79" s="343"/>
-      <c r="E79" s="343"/>
-      <c r="F79" s="343"/>
+      <c r="C79" s="345"/>
+      <c r="D79" s="345"/>
+      <c r="E79" s="345"/>
+      <c r="F79" s="345"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="47" t="s">
@@ -4794,13 +4795,13 @@
       <c r="A85" s="233"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="B86" s="343" t="s">
+      <c r="B86" s="345" t="s">
         <v>373</v>
       </c>
-      <c r="C86" s="343"/>
-      <c r="D86" s="343"/>
-      <c r="E86" s="343"/>
-      <c r="F86" s="343"/>
+      <c r="C86" s="345"/>
+      <c r="D86" s="345"/>
+      <c r="E86" s="345"/>
+      <c r="F86" s="345"/>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="1" t="s">
@@ -4813,13 +4814,13 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="343" t="s">
+      <c r="B90" s="345" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="343"/>
-      <c r="D90" s="343"/>
-      <c r="E90" s="343"/>
-      <c r="F90" s="343"/>
+      <c r="C90" s="345"/>
+      <c r="D90" s="345"/>
+      <c r="E90" s="345"/>
+      <c r="F90" s="345"/>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" s="47" t="s">
@@ -4950,13 +4951,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="343" t="s">
+      <c r="B106" s="345" t="s">
         <v>374</v>
       </c>
-      <c r="C106" s="343"/>
-      <c r="D106" s="343"/>
-      <c r="E106" s="343"/>
-      <c r="F106" s="343"/>
+      <c r="C106" s="345"/>
+      <c r="D106" s="345"/>
+      <c r="E106" s="345"/>
+      <c r="F106" s="345"/>
     </row>
     <row r="108" spans="1:6">
       <c r="B108" s="47" t="s">
@@ -4995,13 +4996,13 @@
       <c r="F111" s="36"/>
     </row>
     <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="344" t="s">
+      <c r="B113" s="346" t="s">
         <v>375</v>
       </c>
-      <c r="C113" s="344"/>
-      <c r="D113" s="344"/>
-      <c r="E113" s="344"/>
-      <c r="F113" s="344"/>
+      <c r="C113" s="346"/>
+      <c r="D113" s="346"/>
+      <c r="E113" s="346"/>
+      <c r="F113" s="346"/>
     </row>
     <row r="115" spans="1:6" ht="12.4">
       <c r="B115" s="260" t="s">
@@ -5144,13 +5145,13 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="348" t="s">
+      <c r="B124" s="349" t="s">
         <v>378</v>
       </c>
-      <c r="C124" s="348"/>
-      <c r="D124" s="348"/>
-      <c r="E124" s="348"/>
-      <c r="F124" s="348"/>
+      <c r="C124" s="349"/>
+      <c r="D124" s="349"/>
+      <c r="E124" s="349"/>
+      <c r="F124" s="349"/>
     </row>
     <row r="126" spans="1:6" ht="13.9">
       <c r="A126" s="247" t="s">
@@ -5163,22 +5164,22 @@
       <c r="F126" s="36"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="B128" s="346" t="s">
+      <c r="B128" s="350" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="346"/>
-      <c r="D128" s="346"/>
-      <c r="E128" s="346"/>
-      <c r="F128" s="346"/>
+      <c r="C128" s="350"/>
+      <c r="D128" s="350"/>
+      <c r="E128" s="350"/>
+      <c r="F128" s="350"/>
     </row>
     <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="343" t="s">
+      <c r="B129" s="345" t="s">
         <v>377</v>
       </c>
-      <c r="C129" s="343"/>
-      <c r="D129" s="343"/>
-      <c r="E129" s="343"/>
-      <c r="F129" s="343"/>
+      <c r="C129" s="345"/>
+      <c r="D129" s="345"/>
+      <c r="E129" s="345"/>
+      <c r="F129" s="345"/>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="234" t="s">
@@ -5442,13 +5443,13 @@
       <c r="F159" s="36"/>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="350" t="s">
+      <c r="B161" s="344" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="343"/>
-      <c r="D161" s="343"/>
-      <c r="E161" s="343"/>
-      <c r="F161" s="343"/>
+      <c r="C161" s="345"/>
+      <c r="D161" s="345"/>
+      <c r="E161" s="345"/>
+      <c r="F161" s="345"/>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="234" t="s">
@@ -5485,13 +5486,13 @@
       </c>
     </row>
     <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="344" t="s">
+      <c r="B170" s="346" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="344"/>
-      <c r="D170" s="344"/>
-      <c r="E170" s="344"/>
-      <c r="F170" s="344"/>
+      <c r="C170" s="346"/>
+      <c r="D170" s="346"/>
+      <c r="E170" s="346"/>
+      <c r="F170" s="346"/>
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="1" t="s">
@@ -5499,22 +5500,22 @@
       </c>
     </row>
     <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="349" t="s">
+      <c r="B173" s="343" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="349"/>
-      <c r="D173" s="349"/>
-      <c r="E173" s="349"/>
-      <c r="F173" s="349"/>
+      <c r="C173" s="343"/>
+      <c r="D173" s="343"/>
+      <c r="E173" s="343"/>
+      <c r="F173" s="343"/>
     </row>
     <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="349" t="s">
+      <c r="B174" s="343" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="349"/>
-      <c r="D174" s="349"/>
-      <c r="E174" s="349"/>
-      <c r="F174" s="349"/>
+      <c r="C174" s="343"/>
+      <c r="D174" s="343"/>
+      <c r="E174" s="343"/>
+      <c r="F174" s="343"/>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="1" t="s">
@@ -5538,17 +5539,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B18:F18"/>
@@ -5565,6 +5555,17 @@
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B68:F68"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">

--- a/financial_models/opportunities/0398.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0398.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AFCCBF1-1E2A-4BEE-878D-41374224D27A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1936D1D5-8FBC-43F7-9C61-7F7C39996199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -7413,11 +7413,11 @@
         <v>53</v>
       </c>
       <c r="C62" s="183">
-        <f>IF(C$4="","",-C20)</f>
+        <f>IF(C$4="","",IF(C20=0,C61,-C20))</f>
         <v>0</v>
       </c>
       <c r="D62" s="183">
-        <f t="shared" ref="D62:M62" si="30">IF(D$4="","",-D20)</f>
+        <f t="shared" ref="D62:M62" si="30">IF(D$4="","",IF(D20=0,D61,-D20))</f>
         <v>0</v>
       </c>
       <c r="E62" s="183">

--- a/financial_models/opportunities/0398.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0398.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1936D1D5-8FBC-43F7-9C61-7F7C39996199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1444D7E8-B5A1-475B-A9CC-52B2B19D1751}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3782,29 +3782,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4264,13 +4264,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="345" t="s">
+      <c r="B18" s="343" t="s">
         <v>367</v>
       </c>
-      <c r="C18" s="345"/>
-      <c r="D18" s="345"/>
-      <c r="E18" s="345"/>
-      <c r="F18" s="345"/>
+      <c r="C18" s="343"/>
+      <c r="D18" s="343"/>
+      <c r="E18" s="343"/>
+      <c r="F18" s="343"/>
     </row>
     <row r="20" spans="1:6">
       <c r="B20" s="45" t="s">
@@ -4370,22 +4370,22 @@
       <c r="F28" s="36"/>
     </row>
     <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="345" t="s">
+      <c r="B30" s="343" t="s">
         <v>368</v>
       </c>
-      <c r="C30" s="345"/>
-      <c r="D30" s="345"/>
-      <c r="E30" s="345"/>
-      <c r="F30" s="345"/>
+      <c r="C30" s="343"/>
+      <c r="D30" s="343"/>
+      <c r="E30" s="343"/>
+      <c r="F30" s="343"/>
     </row>
     <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="348" t="s">
+      <c r="B31" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="348"/>
-      <c r="D31" s="348"/>
-      <c r="E31" s="348"/>
-      <c r="F31" s="348"/>
+      <c r="C31" s="345"/>
+      <c r="D31" s="345"/>
+      <c r="E31" s="345"/>
+      <c r="F31" s="345"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="234" t="s">
@@ -4397,13 +4397,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="346" t="s">
+      <c r="B34" s="344" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="346"/>
-      <c r="D34" s="346"/>
-      <c r="E34" s="346"/>
-      <c r="F34" s="346"/>
+      <c r="C34" s="344"/>
+      <c r="D34" s="344"/>
+      <c r="E34" s="344"/>
+      <c r="F34" s="344"/>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="47" t="s">
@@ -4423,13 +4423,13 @@
       <c r="C36" s="76"/>
     </row>
     <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="346" t="s">
+      <c r="B37" s="344" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="346"/>
-      <c r="D37" s="346"/>
-      <c r="E37" s="346"/>
-      <c r="F37" s="346"/>
+      <c r="C37" s="344"/>
+      <c r="D37" s="344"/>
+      <c r="E37" s="344"/>
+      <c r="F37" s="344"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="47" t="s">
@@ -4458,13 +4458,13 @@
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="346" t="s">
+      <c r="B41" s="344" t="s">
         <v>237</v>
       </c>
-      <c r="C41" s="346"/>
-      <c r="D41" s="346"/>
-      <c r="E41" s="346"/>
-      <c r="F41" s="346"/>
+      <c r="C41" s="344"/>
+      <c r="D41" s="344"/>
+      <c r="E41" s="344"/>
+      <c r="F41" s="344"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
@@ -4480,13 +4480,13 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="346" t="s">
+      <c r="B44" s="344" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="346"/>
-      <c r="D44" s="346"/>
-      <c r="E44" s="346"/>
-      <c r="F44" s="346"/>
+      <c r="C44" s="344"/>
+      <c r="D44" s="344"/>
+      <c r="E44" s="344"/>
+      <c r="F44" s="344"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
@@ -4550,13 +4550,13 @@
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="346" t="s">
+      <c r="B52" s="344" t="s">
         <v>242</v>
       </c>
-      <c r="C52" s="346"/>
-      <c r="D52" s="346"/>
-      <c r="E52" s="346"/>
-      <c r="F52" s="346"/>
+      <c r="C52" s="344"/>
+      <c r="D52" s="344"/>
+      <c r="E52" s="344"/>
+      <c r="F52" s="344"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4572,7 +4572,7 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="346" t="s">
+      <c r="B55" s="344" t="s">
         <v>346</v>
       </c>
       <c r="C55" s="347"/>
@@ -4594,22 +4594,22 @@
       </c>
     </row>
     <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="345" t="s">
+      <c r="B58" s="343" t="s">
         <v>351</v>
       </c>
-      <c r="C58" s="345"/>
-      <c r="D58" s="345"/>
-      <c r="E58" s="345"/>
-      <c r="F58" s="345"/>
+      <c r="C58" s="343"/>
+      <c r="D58" s="343"/>
+      <c r="E58" s="343"/>
+      <c r="F58" s="343"/>
     </row>
     <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="345" t="s">
+      <c r="B59" s="343" t="s">
         <v>369</v>
       </c>
-      <c r="C59" s="345"/>
-      <c r="D59" s="345"/>
-      <c r="E59" s="345"/>
-      <c r="F59" s="345"/>
+      <c r="C59" s="343"/>
+      <c r="D59" s="343"/>
+      <c r="E59" s="343"/>
+      <c r="F59" s="343"/>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="47" t="s">
@@ -4670,22 +4670,22 @@
     </row>
     <row r="68" spans="1:6" ht="24.4" customHeight="1">
       <c r="A68" s="17"/>
-      <c r="B68" s="345" t="s">
+      <c r="B68" s="343" t="s">
         <v>370</v>
       </c>
-      <c r="C68" s="345"/>
-      <c r="D68" s="345"/>
-      <c r="E68" s="345"/>
-      <c r="F68" s="345"/>
+      <c r="C68" s="343"/>
+      <c r="D68" s="343"/>
+      <c r="E68" s="343"/>
+      <c r="F68" s="343"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="348" t="s">
+      <c r="B69" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="348"/>
-      <c r="D69" s="348"/>
-      <c r="E69" s="348"/>
-      <c r="F69" s="348"/>
+      <c r="C69" s="345"/>
+      <c r="D69" s="345"/>
+      <c r="E69" s="345"/>
+      <c r="F69" s="345"/>
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="234" t="s">
@@ -4743,22 +4743,22 @@
       <c r="C77" s="122"/>
     </row>
     <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="345" t="s">
+      <c r="B78" s="343" t="s">
         <v>371</v>
       </c>
-      <c r="C78" s="345"/>
-      <c r="D78" s="345"/>
-      <c r="E78" s="345"/>
-      <c r="F78" s="345"/>
+      <c r="C78" s="343"/>
+      <c r="D78" s="343"/>
+      <c r="E78" s="343"/>
+      <c r="F78" s="343"/>
     </row>
     <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="345" t="s">
+      <c r="B79" s="343" t="s">
         <v>372</v>
       </c>
-      <c r="C79" s="345"/>
-      <c r="D79" s="345"/>
-      <c r="E79" s="345"/>
-      <c r="F79" s="345"/>
+      <c r="C79" s="343"/>
+      <c r="D79" s="343"/>
+      <c r="E79" s="343"/>
+      <c r="F79" s="343"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="47" t="s">
@@ -4795,13 +4795,13 @@
       <c r="A85" s="233"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="B86" s="345" t="s">
+      <c r="B86" s="343" t="s">
         <v>373</v>
       </c>
-      <c r="C86" s="345"/>
-      <c r="D86" s="345"/>
-      <c r="E86" s="345"/>
-      <c r="F86" s="345"/>
+      <c r="C86" s="343"/>
+      <c r="D86" s="343"/>
+      <c r="E86" s="343"/>
+      <c r="F86" s="343"/>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="1" t="s">
@@ -4814,13 +4814,13 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="345" t="s">
+      <c r="B90" s="343" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="345"/>
-      <c r="D90" s="345"/>
-      <c r="E90" s="345"/>
-      <c r="F90" s="345"/>
+      <c r="C90" s="343"/>
+      <c r="D90" s="343"/>
+      <c r="E90" s="343"/>
+      <c r="F90" s="343"/>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" s="47" t="s">
@@ -4951,13 +4951,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="345" t="s">
+      <c r="B106" s="343" t="s">
         <v>374</v>
       </c>
-      <c r="C106" s="345"/>
-      <c r="D106" s="345"/>
-      <c r="E106" s="345"/>
-      <c r="F106" s="345"/>
+      <c r="C106" s="343"/>
+      <c r="D106" s="343"/>
+      <c r="E106" s="343"/>
+      <c r="F106" s="343"/>
     </row>
     <row r="108" spans="1:6">
       <c r="B108" s="47" t="s">
@@ -4996,13 +4996,13 @@
       <c r="F111" s="36"/>
     </row>
     <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="346" t="s">
+      <c r="B113" s="344" t="s">
         <v>375</v>
       </c>
-      <c r="C113" s="346"/>
-      <c r="D113" s="346"/>
-      <c r="E113" s="346"/>
-      <c r="F113" s="346"/>
+      <c r="C113" s="344"/>
+      <c r="D113" s="344"/>
+      <c r="E113" s="344"/>
+      <c r="F113" s="344"/>
     </row>
     <row r="115" spans="1:6" ht="12.4">
       <c r="B115" s="260" t="s">
@@ -5145,13 +5145,13 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="349" t="s">
+      <c r="B124" s="348" t="s">
         <v>378</v>
       </c>
-      <c r="C124" s="349"/>
-      <c r="D124" s="349"/>
-      <c r="E124" s="349"/>
-      <c r="F124" s="349"/>
+      <c r="C124" s="348"/>
+      <c r="D124" s="348"/>
+      <c r="E124" s="348"/>
+      <c r="F124" s="348"/>
     </row>
     <row r="126" spans="1:6" ht="13.9">
       <c r="A126" s="247" t="s">
@@ -5164,22 +5164,22 @@
       <c r="F126" s="36"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="B128" s="350" t="s">
+      <c r="B128" s="346" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="350"/>
-      <c r="D128" s="350"/>
-      <c r="E128" s="350"/>
-      <c r="F128" s="350"/>
+      <c r="C128" s="346"/>
+      <c r="D128" s="346"/>
+      <c r="E128" s="346"/>
+      <c r="F128" s="346"/>
     </row>
     <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="345" t="s">
+      <c r="B129" s="343" t="s">
         <v>377</v>
       </c>
-      <c r="C129" s="345"/>
-      <c r="D129" s="345"/>
-      <c r="E129" s="345"/>
-      <c r="F129" s="345"/>
+      <c r="C129" s="343"/>
+      <c r="D129" s="343"/>
+      <c r="E129" s="343"/>
+      <c r="F129" s="343"/>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="234" t="s">
@@ -5443,13 +5443,13 @@
       <c r="F159" s="36"/>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="344" t="s">
+      <c r="B161" s="350" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="345"/>
-      <c r="D161" s="345"/>
-      <c r="E161" s="345"/>
-      <c r="F161" s="345"/>
+      <c r="C161" s="343"/>
+      <c r="D161" s="343"/>
+      <c r="E161" s="343"/>
+      <c r="F161" s="343"/>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="234" t="s">
@@ -5486,13 +5486,13 @@
       </c>
     </row>
     <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="346" t="s">
+      <c r="B170" s="344" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="346"/>
-      <c r="D170" s="346"/>
-      <c r="E170" s="346"/>
-      <c r="F170" s="346"/>
+      <c r="C170" s="344"/>
+      <c r="D170" s="344"/>
+      <c r="E170" s="344"/>
+      <c r="F170" s="344"/>
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="1" t="s">
@@ -5500,22 +5500,22 @@
       </c>
     </row>
     <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="343" t="s">
+      <c r="B173" s="349" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="343"/>
-      <c r="D173" s="343"/>
-      <c r="E173" s="343"/>
-      <c r="F173" s="343"/>
+      <c r="C173" s="349"/>
+      <c r="D173" s="349"/>
+      <c r="E173" s="349"/>
+      <c r="F173" s="349"/>
     </row>
     <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="343" t="s">
+      <c r="B174" s="349" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="343"/>
-      <c r="D174" s="343"/>
-      <c r="E174" s="343"/>
-      <c r="F174" s="343"/>
+      <c r="C174" s="349"/>
+      <c r="D174" s="349"/>
+      <c r="E174" s="349"/>
+      <c r="F174" s="349"/>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="1" t="s">
@@ -5539,6 +5539,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B18:F18"/>
@@ -5555,17 +5566,6 @@
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B68:F68"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">

--- a/financial_models/opportunities/0398.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0398.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1444D7E8-B5A1-475B-A9CC-52B2B19D1751}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B756BF5C-DD12-4EB2-942F-CECFF7961A04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="443">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2374,6 +2374,18 @@
   </si>
   <si>
     <t>Capitalization:</t>
+  </si>
+  <si>
+    <t>@Benchmark Yield</t>
+  </si>
+  <si>
+    <t>in contrast to a benchmark yield of</t>
+  </si>
+  <si>
+    <t>Exit Price Output</t>
+  </si>
+  <si>
+    <t>Benchmark Yield</t>
   </si>
   <si>
     <t>Y</t>
@@ -4094,7 +4106,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J179"/>
+  <dimension ref="A1:J187"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -4116,7 +4128,7 @@
         <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4147,7 +4159,7 @@
         <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4194,10 +4206,10 @@
         <v>426</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4310,7 +4322,7 @@
         <v>56</v>
       </c>
       <c r="C23" s="48" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="E23" s="5"/>
     </row>
@@ -4352,8 +4364,12 @@
         <f ca="1">Scenarios!C87</f>
         <v>0.14834835832623461</v>
       </c>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
+      <c r="D26" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="E26" s="339">
+        <v>0.1174</v>
+      </c>
     </row>
     <row r="27" spans="1:6">
       <c r="D27" s="5"/>
@@ -4709,7 +4725,7 @@
         <v>0</v>
       </c>
       <c r="D73" s="286" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -4721,7 +4737,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="286" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -5308,7 +5324,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
+    <row r="145" spans="2:4">
       <c r="B145" s="236" t="str">
         <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5318,7 +5334,7 @@
         <v>0.26962962962962961</v>
       </c>
     </row>
-    <row r="146" spans="1:6">
+    <row r="146" spans="2:4">
       <c r="B146" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5328,7 +5344,7 @@
         <v>2.8717481627532462</v>
       </c>
     </row>
-    <row r="147" spans="1:6">
+    <row r="147" spans="2:4">
       <c r="B147" s="80" t="s">
         <v>261</v>
       </c>
@@ -5341,7 +5357,7 @@
         <v/>
       </c>
     </row>
-    <row r="148" spans="1:6">
+    <row r="148" spans="2:4">
       <c r="B148" s="290" t="s">
         <v>425</v>
       </c>
@@ -5354,7 +5370,7 @@
         <v/>
       </c>
     </row>
-    <row r="149" spans="1:6">
+    <row r="149" spans="2:4">
       <c r="B149" s="238" t="s">
         <v>263</v>
       </c>
@@ -5363,12 +5379,12 @@
         <v>0.36696156481854458</v>
       </c>
     </row>
-    <row r="151" spans="1:6">
+    <row r="151" spans="2:4">
       <c r="B151" s="234" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="152" spans="1:6">
+    <row r="152" spans="2:4">
       <c r="B152" s="1" t="s">
         <v>419</v>
       </c>
@@ -5377,7 +5393,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="153" spans="1:6">
+    <row r="153" spans="2:4">
       <c r="B153" s="236" t="str">
         <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5387,7 +5403,7 @@
         <v>0.32986841436772868</v>
       </c>
     </row>
-    <row r="154" spans="1:6">
+    <row r="154" spans="2:4">
       <c r="B154" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5397,7 +5413,7 @@
         <v>3.9392978912938901</v>
       </c>
     </row>
-    <row r="155" spans="1:6">
+    <row r="155" spans="2:4">
       <c r="B155" s="80" t="s">
         <v>409</v>
       </c>
@@ -5410,7 +5426,7 @@
         <v/>
       </c>
     </row>
-    <row r="156" spans="1:6">
+    <row r="156" spans="2:4">
       <c r="B156" s="290" t="s">
         <v>425</v>
       </c>
@@ -5423,7 +5439,7 @@
         <v/>
       </c>
     </row>
-    <row r="157" spans="1:6">
+    <row r="157" spans="2:4">
       <c r="B157" s="238" t="s">
         <v>263</v>
       </c>
@@ -5432,118 +5448,187 @@
         <v>0.13969393804894004</v>
       </c>
     </row>
-    <row r="159" spans="1:6" ht="13.9">
-      <c r="A159" s="247" t="s">
+    <row r="159" spans="2:4">
+      <c r="B159" s="234" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="160" spans="2:4">
+      <c r="B160" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="C160" s="92">
+        <f>E26</f>
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6">
+      <c r="B161" s="236" t="str">
+        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C161" s="240">
+        <f>Scenarios!C103</f>
+        <v>0.30881320012014707</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6">
+      <c r="B162" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C162" s="240">
+        <f>Scenarios!C104</f>
+        <v>3.5568380305864293</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6">
+      <c r="B163" s="80" t="s">
+        <v>409</v>
+      </c>
+      <c r="C163" s="239">
+        <f>Scenarios!C105</f>
+        <v>3.8656512307065762</v>
+      </c>
+      <c r="D163" s="342" t="str">
+        <f>IF($D$11="","",C163*$E$22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
+      <c r="B164" s="290" t="s">
+        <v>425</v>
+      </c>
+      <c r="C164" s="340" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D164" s="340" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
+      <c r="B165" s="238" t="s">
+        <v>263</v>
+      </c>
+      <c r="C165" s="92">
+        <f>Scenarios!F105</f>
+        <v>0.22106689885075603</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" ht="13.9">
+      <c r="A167" s="247" t="s">
         <v>382</v>
       </c>
-      <c r="B159" s="36"/>
-      <c r="C159" s="36"/>
-      <c r="D159" s="36"/>
-      <c r="E159" s="36"/>
-      <c r="F159" s="36"/>
-    </row>
-    <row r="161" spans="2:6">
-      <c r="B161" s="350" t="s">
+      <c r="B167" s="36"/>
+      <c r="C167" s="36"/>
+      <c r="D167" s="36"/>
+      <c r="E167" s="36"/>
+      <c r="F167" s="36"/>
+    </row>
+    <row r="169" spans="1:6">
+      <c r="B169" s="350" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="343"/>
-      <c r="D161" s="343"/>
-      <c r="E161" s="343"/>
-      <c r="F161" s="343"/>
-    </row>
-    <row r="163" spans="2:6">
-      <c r="B163" s="234" t="s">
+      <c r="C169" s="343"/>
+      <c r="D169" s="343"/>
+      <c r="E169" s="343"/>
+      <c r="F169" s="343"/>
+    </row>
+    <row r="171" spans="1:6">
+      <c r="B171" s="234" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="164" spans="2:6">
-      <c r="B164" s="347" t="s">
+    <row r="172" spans="1:6">
+      <c r="B172" s="347" t="s">
         <v>388</v>
       </c>
-      <c r="C164" s="347"/>
-      <c r="D164" s="347"/>
-      <c r="E164" s="347"/>
-      <c r="F164" s="347"/>
-    </row>
-    <row r="165" spans="2:6">
-      <c r="B165" s="238" t="s">
+      <c r="C172" s="347"/>
+      <c r="D172" s="347"/>
+      <c r="E172" s="347"/>
+      <c r="F172" s="347"/>
+    </row>
+    <row r="173" spans="1:6">
+      <c r="B173" s="238" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="166" spans="2:6">
-      <c r="B166" s="238" t="s">
+    <row r="174" spans="1:6">
+      <c r="B174" s="238" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="167" spans="2:6">
-      <c r="B167" s="238" t="s">
+    <row r="175" spans="1:6">
+      <c r="B175" s="238" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="169" spans="2:6">
-      <c r="B169" s="1" t="s">
+    <row r="177" spans="2:6">
+      <c r="B177" s="1" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="344" t="s">
+    <row r="178" spans="2:6" ht="46.5" customHeight="1">
+      <c r="B178" s="344" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="344"/>
-      <c r="D170" s="344"/>
-      <c r="E170" s="344"/>
-      <c r="F170" s="344"/>
-    </row>
-    <row r="172" spans="2:6">
-      <c r="B172" s="1" t="s">
+      <c r="C178" s="344"/>
+      <c r="D178" s="344"/>
+      <c r="E178" s="344"/>
+      <c r="F178" s="344"/>
+    </row>
+    <row r="180" spans="2:6">
+      <c r="B180" s="1" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="349" t="s">
+    <row r="181" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B181" s="349" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="349"/>
-      <c r="D173" s="349"/>
-      <c r="E173" s="349"/>
-      <c r="F173" s="349"/>
-    </row>
-    <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="349" t="s">
+      <c r="C181" s="349"/>
+      <c r="D181" s="349"/>
+      <c r="E181" s="349"/>
+      <c r="F181" s="349"/>
+    </row>
+    <row r="182" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B182" s="349" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="349"/>
-      <c r="D174" s="349"/>
-      <c r="E174" s="349"/>
-      <c r="F174" s="349"/>
-    </row>
-    <row r="176" spans="2:6">
-      <c r="B176" s="1" t="s">
+      <c r="C182" s="349"/>
+      <c r="D182" s="349"/>
+      <c r="E182" s="349"/>
+      <c r="F182" s="349"/>
+    </row>
+    <row r="184" spans="2:6">
+      <c r="B184" s="1" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="177" spans="2:2">
-      <c r="B177" s="238" t="s">
+    <row r="185" spans="2:6">
+      <c r="B185" s="238" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="178" spans="2:2">
-      <c r="B178" s="238" t="s">
+    <row r="186" spans="2:6">
+      <c r="B186" s="238" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="179" spans="2:2">
-      <c r="B179" s="238" t="s">
+    <row r="187" spans="2:6">
+      <c r="B187" s="238" t="s">
         <v>396</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B181:F181"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B169:F169"/>
+    <mergeCell ref="B178:F178"/>
+    <mergeCell ref="B172:F172"/>
     <mergeCell ref="B69:F69"/>
     <mergeCell ref="B113:F113"/>
     <mergeCell ref="B78:F78"/>
@@ -6213,7 +6298,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -12042,7 +12127,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12374,7 +12459,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -16585,7 +16670,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
-  <dimension ref="B2:I104"/>
+  <dimension ref="B2:I110"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
@@ -17595,33 +17680,89 @@
     <row r="100" spans="2:8">
       <c r="B100" s="100"/>
     </row>
-    <row r="101" spans="2:8" ht="14.65">
-      <c r="E101" s="320" t="s">
+    <row r="101" spans="2:8" ht="13.15">
+      <c r="B101" s="109" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="102" spans="2:8">
+      <c r="B102" s="149" t="s">
+        <v>430</v>
+      </c>
+      <c r="C102" s="135">
+        <f>Thesis!E26</f>
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="103" spans="2:8">
+      <c r="B103" s="100" t="s">
+        <v>122</v>
+      </c>
+      <c r="C103" s="117">
+        <f>PV(C102, C76, -C77, 0)</f>
+        <v>0.30881320012014707</v>
+      </c>
+      <c r="D103" s="117"/>
+    </row>
+    <row r="104" spans="2:8">
+      <c r="B104" s="100" t="s">
+        <v>123</v>
+      </c>
+      <c r="C104" s="117">
+        <f>C60/(1+C102)^C76</f>
+        <v>3.5568380305864293</v>
+      </c>
+      <c r="D104" s="117"/>
+    </row>
+    <row r="105" spans="2:8" ht="13.15">
+      <c r="B105" s="111" t="s">
+        <v>406</v>
+      </c>
+      <c r="C105" s="112">
+        <f>C103+C104</f>
+        <v>3.8656512307065762</v>
+      </c>
+      <c r="D105" t="s">
+        <v>404</v>
+      </c>
+      <c r="E105" s="147" t="s">
+        <v>127</v>
+      </c>
+      <c r="F105" s="329">
+        <f>(1-C105/C66)</f>
+        <v>0.22106689885075603</v>
+      </c>
+    </row>
+    <row r="106" spans="2:8">
+      <c r="B106" s="100"/>
+    </row>
+    <row r="107" spans="2:8" ht="14.65">
+      <c r="E107" s="320" t="s">
         <v>332</v>
       </c>
-      <c r="F101" s="317"/>
-    </row>
-    <row r="102" spans="2:8" ht="13.9">
-      <c r="E102" s="313" t="s">
+      <c r="F107" s="317"/>
+    </row>
+    <row r="108" spans="2:8" ht="13.9">
+      <c r="E108" s="313" t="s">
         <v>333</v>
       </c>
-      <c r="F102" s="318" t="s">
+      <c r="F108" s="318" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="103" spans="2:8" ht="13.9">
-      <c r="E103" s="314" t="s">
+    <row r="109" spans="2:8" ht="13.9">
+      <c r="E109" s="314" t="s">
         <v>333</v>
       </c>
-      <c r="F103" s="318" t="s">
+      <c r="F109" s="318" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="104" spans="2:8" ht="13.9">
-      <c r="E104" s="315" t="s">
+    <row r="110" spans="2:8" ht="13.9">
+      <c r="E110" s="315" t="s">
         <v>333</v>
       </c>
-      <c r="F104" s="319" t="s">
+      <c r="F110" s="319" t="s">
         <v>336</v>
       </c>
     </row>

--- a/financial_models/opportunities/0398.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0398.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B756BF5C-DD12-4EB2-942F-CECFF7961A04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F8E0918-40CD-44BC-BF9C-EBF34D1F107C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
-    <definedName name="Reporting_currency">Thesis!$C$22</definedName>
+    <definedName name="Reporting_currency">Thesis!$C$25</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
     <definedName name="Terminal_Growth">Valuation_Model!$F$4</definedName>
   </definedNames>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="453">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1370,10 +1370,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Target Annual Return:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Target Annual Return =</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1411,18 +1407,6 @@
   </si>
   <si>
     <t>Other Non-Operating Assets per share =</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Cost of Equity</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Management Risk Premium</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Business Model Risk Premium</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1519,10 +1503,6 @@
   </si>
   <si>
     <t>Report Interval:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>assuming a holding period of</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2337,9 +2317,6 @@
     <t>Target Return</t>
   </si>
   <si>
-    <t>in contrast to a position yield of</t>
-  </si>
-  <si>
     <t>Result (Target)</t>
   </si>
   <si>
@@ -2379,13 +2356,61 @@
     <t>@Benchmark Yield</t>
   </si>
   <si>
-    <t>in contrast to a benchmark yield of</t>
-  </si>
-  <si>
     <t>Exit Price Output</t>
   </si>
   <si>
     <t>Benchmark Yield</t>
+  </si>
+  <si>
+    <t>Target return</t>
+  </si>
+  <si>
+    <t>Target Price</t>
+  </si>
+  <si>
+    <t>Entry Price</t>
+  </si>
+  <si>
+    <t>Sell Price</t>
+  </si>
+  <si>
+    <t>Exit Price</t>
+  </si>
+  <si>
+    <t>Holding Period</t>
+  </si>
+  <si>
+    <t>Risk Premium</t>
+  </si>
+  <si>
+    <t>Base Cost of Equity</t>
+  </si>
+  <si>
+    <t>Result (Exit)</t>
+  </si>
+  <si>
+    <t>Valuation Outputs</t>
+  </si>
+  <si>
+    <t>Business Model Risk Premium:</t>
+  </si>
+  <si>
+    <t>Management Risk Premium:</t>
+  </si>
+  <si>
+    <t>Base equity cost</t>
+  </si>
+  <si>
+    <t>Entry yield</t>
+  </si>
+  <si>
+    <t>Benchmark yield</t>
+  </si>
+  <si>
+    <t>DCF</t>
+  </si>
+  <si>
+    <t>Valuation Method</t>
   </si>
   <si>
     <t>Y</t>
@@ -3086,7 +3111,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="355">
+  <cellXfs count="358">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3600,14 +3625,8 @@
     </xf>
     <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="175" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="10" fontId="8" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3665,9 +3684,6 @@
     <xf numFmtId="179" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3675,7 +3691,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3767,9 +3782,6 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="175" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3784,9 +3796,6 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3794,6 +3803,33 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="175" fontId="46" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="40" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4106,10 +4142,10 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J187"/>
+  <dimension ref="A1:J192"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.59765625" style="1" customWidth="1"/>
     <col min="3" max="4" width="25.59765625" style="1" customWidth="1"/>
     <col min="5" max="6" width="15.59765625" style="1" customWidth="1"/>
@@ -4124,11 +4160,11 @@
         <v>45786</v>
       </c>
       <c r="D1" s="52"/>
-      <c r="E1" s="331" t="s">
-        <v>361</v>
-      </c>
-      <c r="F1" s="284" t="s">
-        <v>434</v>
+      <c r="E1" s="326" t="s">
+        <v>356</v>
+      </c>
+      <c r="F1" s="281" t="s">
+        <v>444</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4147,7 +4183,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4156,10 +4192,10 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="C5" s="333" t="s">
-        <v>435</v>
+        <v>318</v>
+      </c>
+      <c r="C5" s="328" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4173,9 +4209,9 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="C7" s="279">
+        <v>310</v>
+      </c>
+      <c r="C7" s="277">
         <v>6</v>
       </c>
       <c r="D7" s="48"/>
@@ -4196,20 +4232,20 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4225,17 +4261,17 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
@@ -4249,14 +4285,14 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="C15" s="32" t="str">
-        <f>IF(C22=C13,C13,C22&amp;"/"&amp;C13)</f>
+        <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
         <v>HKD</v>
       </c>
       <c r="D15" s="32" t="str">
-        <f>IF(D11="","",IF(C22=D13,D13,C22&amp;"/"&amp;D13))</f>
+        <f>IF(D11="","",IF(C25=D13,D13,C25&amp;"/"&amp;D13))</f>
         <v/>
       </c>
       <c r="E15" s="5"/>
@@ -4271,29 +4307,29 @@
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="2:6">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="343" t="s">
-        <v>367</v>
-      </c>
-      <c r="C18" s="343"/>
-      <c r="D18" s="343"/>
-      <c r="E18" s="343"/>
-      <c r="F18" s="343"/>
-    </row>
-    <row r="20" spans="1:6">
+    <row r="18" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B18" s="346" t="s">
+        <v>362</v>
+      </c>
+      <c r="C18" s="346"/>
+      <c r="D18" s="346"/>
+      <c r="E18" s="346"/>
+      <c r="F18" s="346"/>
+    </row>
+    <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -4301,286 +4337,338 @@
       </c>
       <c r="E21" s="5"/>
     </row>
-    <row r="22" spans="1:6">
-      <c r="B22" s="4" t="s">
-        <v>355</v>
+    <row r="22" spans="2:6">
+      <c r="B22" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>404</v>
-      </c>
-      <c r="D22" s="32" t="str">
+        <v>448</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="E22" s="345" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6">
+      <c r="B23" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="C23" s="291" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6">
+      <c r="B24" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="C24" s="291" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6">
+      <c r="B25" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="C25" s="48" t="s">
+        <v>399</v>
+      </c>
+      <c r="D25" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
         <v/>
       </c>
-      <c r="E22" s="341" t="str">
+      <c r="E25" s="335" t="str">
         <f>IF(D11="","",1/Exchange_Rate*D16)</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:6">
-      <c r="B23" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C23" s="48" t="s">
-        <v>438</v>
-      </c>
-      <c r="E23" s="5"/>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="B24" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="C24" s="249">
-        <v>0.4</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="E24" s="339">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="B25" s="2" t="str">
-        <f>"Target Buy Price ("&amp;Market_currency&amp;"):"</f>
-        <v>Target Buy Price (HKD):</v>
-      </c>
-      <c r="C25" s="252">
-        <f>C139</f>
-        <v>2.0118297468067095</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="E25" s="330">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="B26" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="C26" s="280">
+    <row r="26" spans="2:6">
+      <c r="B26" s="1" t="str">
+        <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
+        <v>Expected Equity Value (HKD) :</v>
+      </c>
+      <c r="C26" s="341">
+        <f>C127</f>
+        <v>4.9623808252376094</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="E26" s="337">
         <f ca="1">Scenarios!C87</f>
         <v>0.14834835832623461</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="E26" s="339">
-        <v>0.1174</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
+    </row>
+    <row r="27" spans="2:6">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="1:6" ht="13.9">
-      <c r="A28" s="247" t="s">
-        <v>362</v>
-      </c>
-      <c r="B28" s="36"/>
-      <c r="C28" s="36"/>
-      <c r="D28" s="36"/>
-      <c r="E28" s="36"/>
-      <c r="F28" s="36"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="343" t="s">
-        <v>368</v>
-      </c>
-      <c r="C30" s="343"/>
-      <c r="D30" s="343"/>
-      <c r="E30" s="343"/>
-      <c r="F30" s="343"/>
-    </row>
-    <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="345" t="s">
-        <v>347</v>
-      </c>
-      <c r="C31" s="345"/>
-      <c r="D31" s="345"/>
-      <c r="E31" s="345"/>
-      <c r="F31" s="345"/>
-    </row>
-    <row r="33" spans="2:6">
-      <c r="B33" s="234" t="s">
+    <row r="28" spans="2:6">
+      <c r="B28" s="45" t="s">
+        <v>436</v>
+      </c>
+      <c r="C28" s="268" t="str">
+        <f>C140&amp;" ("&amp;Market_currency&amp;")"</f>
+        <v>0398.HK (HKD)</v>
+      </c>
+      <c r="D28" s="268" t="str">
+        <f>IF(D11="","",D140&amp;" ("&amp;D13&amp;")")</f>
+        <v/>
+      </c>
+      <c r="E28" s="342" t="s">
+        <v>432</v>
+      </c>
+      <c r="F28" s="340">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6">
+      <c r="B29" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C29" s="339">
+        <f>C144</f>
+        <v>2.0118297468067095</v>
+      </c>
+      <c r="D29" s="339" t="str">
+        <f>D144</f>
+        <v/>
+      </c>
+      <c r="E29" s="343" t="s">
+        <v>427</v>
+      </c>
+      <c r="F29" s="338">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="B30" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="C30" s="148">
+        <f>C152</f>
+        <v>3.1413777923828756</v>
+      </c>
+      <c r="D30" s="148" t="str">
+        <f>D152</f>
+        <v/>
+      </c>
+      <c r="E30" s="344" t="s">
+        <v>440</v>
+      </c>
+      <c r="F30" s="307">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
+      <c r="B31" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="C31" s="148">
+        <f>C160</f>
+        <v>4.2691663056616189</v>
+      </c>
+      <c r="D31" s="148" t="str">
+        <f>D160</f>
+        <v/>
+      </c>
+      <c r="E31" s="344" t="s">
+        <v>439</v>
+      </c>
+      <c r="F31" s="307">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
+      <c r="B32" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C32" s="148">
+        <f>C168</f>
+        <v>3.8656512307065762</v>
+      </c>
+      <c r="D32" s="148" t="str">
+        <f>D168</f>
+        <v/>
+      </c>
+      <c r="E32" s="344" t="s">
+        <v>441</v>
+      </c>
+      <c r="F32" s="307">
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+    </row>
+    <row r="34" spans="1:6" ht="13.9">
+      <c r="A34" s="247" t="s">
+        <v>357</v>
+      </c>
+      <c r="B34" s="36"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="36"/>
+    </row>
+    <row r="36" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B36" s="346" t="s">
+        <v>363</v>
+      </c>
+      <c r="C36" s="346"/>
+      <c r="D36" s="346"/>
+      <c r="E36" s="346"/>
+      <c r="F36" s="346"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B37" s="348" t="s">
+        <v>342</v>
+      </c>
+      <c r="C37" s="348"/>
+      <c r="D37" s="348"/>
+      <c r="E37" s="348"/>
+      <c r="F37" s="348"/>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="B39" s="234" t="s">
         <v>231</v>
       </c>
-      <c r="C33" s="108">
+      <c r="C39" s="108">
         <f>scaling_factor</f>
         <v>1000</v>
       </c>
     </row>
-    <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="344" t="s">
+    <row r="40" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B40" s="347" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="344"/>
-      <c r="D34" s="344"/>
-      <c r="E34" s="344"/>
-      <c r="F34" s="344"/>
-    </row>
-    <row r="35" spans="2:6">
-      <c r="B35" s="47" t="s">
+      <c r="C40" s="347"/>
+      <c r="D40" s="347"/>
+      <c r="E40" s="347"/>
+      <c r="F40" s="347"/>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="B41" s="47" t="s">
         <v>233</v>
       </c>
-      <c r="C35" s="188">
+      <c r="C41" s="188">
         <f>Normalized_FCF!C8</f>
         <v>198948.88436097838</v>
       </c>
-      <c r="D35" s="1" t="str">
+      <c r="D41" s="1" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="36" spans="2:6">
-      <c r="B36" s="47"/>
-      <c r="C36" s="76"/>
-    </row>
-    <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="344" t="s">
+    <row r="42" spans="1:6">
+      <c r="B42" s="47"/>
+      <c r="C42" s="76"/>
+    </row>
+    <row r="43" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B43" s="347" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="344"/>
-      <c r="D37" s="344"/>
-      <c r="E37" s="344"/>
-      <c r="F37" s="344"/>
-    </row>
-    <row r="38" spans="2:6">
-      <c r="B38" s="47" t="s">
+      <c r="C43" s="347"/>
+      <c r="D43" s="347"/>
+      <c r="E43" s="347"/>
+      <c r="F43" s="347"/>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="B44" s="47" t="s">
         <v>235</v>
       </c>
-      <c r="C38" s="188">
+      <c r="C44" s="188">
         <f>Normalized_FCF!C9</f>
         <v>0</v>
       </c>
-      <c r="D38" s="1" t="str">
+      <c r="D44" s="1" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="39" spans="2:6">
-      <c r="B39" s="52" t="s">
+    <row r="45" spans="1:6">
+      <c r="B45" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="C39" s="188">
+      <c r="C45" s="188">
         <f>Normalized_FCF!C10</f>
-        <v>0</v>
-      </c>
-      <c r="D39" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="41" spans="2:6">
-      <c r="B41" s="344" t="s">
-        <v>237</v>
-      </c>
-      <c r="C41" s="344"/>
-      <c r="D41" s="344"/>
-      <c r="E41" s="344"/>
-      <c r="F41" s="344"/>
-    </row>
-    <row r="42" spans="2:6">
-      <c r="B42" s="47" t="s">
-        <v>238</v>
-      </c>
-      <c r="C42" s="188">
-        <f>Normalized_FCF!C11</f>
-        <v>0</v>
-      </c>
-      <c r="D42" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="44" spans="2:6">
-      <c r="B44" s="344" t="s">
-        <v>241</v>
-      </c>
-      <c r="C44" s="344"/>
-      <c r="D44" s="344"/>
-      <c r="E44" s="344"/>
-      <c r="F44" s="344"/>
-    </row>
-    <row r="45" spans="2:6">
-      <c r="B45" s="47" t="s">
-        <v>348</v>
-      </c>
-      <c r="C45" s="322">
-        <f>Normalized_FCF!C48</f>
         <v>0</v>
       </c>
       <c r="D45" s="1" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E45" s="321"/>
-      <c r="F45" s="321"/>
-    </row>
-    <row r="46" spans="2:6">
-      <c r="B46" s="47" t="s">
-        <v>349</v>
-      </c>
-      <c r="C46" s="322">
+    </row>
+    <row r="47" spans="1:6">
+      <c r="B47" s="347" t="s">
+        <v>237</v>
+      </c>
+      <c r="C47" s="347"/>
+      <c r="D47" s="347"/>
+      <c r="E47" s="347"/>
+      <c r="F47" s="347"/>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="B48" s="47" t="s">
+        <v>238</v>
+      </c>
+      <c r="C48" s="188">
+        <f>Normalized_FCF!C11</f>
+        <v>0</v>
+      </c>
+      <c r="D48" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6">
+      <c r="B50" s="347" t="s">
+        <v>241</v>
+      </c>
+      <c r="C50" s="347"/>
+      <c r="D50" s="347"/>
+      <c r="E50" s="347"/>
+      <c r="F50" s="347"/>
+    </row>
+    <row r="51" spans="2:6">
+      <c r="B51" s="47" t="s">
+        <v>343</v>
+      </c>
+      <c r="C51" s="318">
+        <f>Normalized_FCF!C48</f>
+        <v>0</v>
+      </c>
+      <c r="D51" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="E51" s="317"/>
+      <c r="F51" s="317"/>
+    </row>
+    <row r="52" spans="2:6">
+      <c r="B52" s="47" t="s">
+        <v>344</v>
+      </c>
+      <c r="C52" s="318">
         <f>Normalized_FCF!C47</f>
         <v>-13663</v>
       </c>
-      <c r="D46" s="1" t="str">
+      <c r="D52" s="1" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E46" s="321"/>
-      <c r="F46" s="321"/>
-    </row>
-    <row r="47" spans="2:6">
-      <c r="B47" s="47" t="s">
+      <c r="E52" s="317"/>
+      <c r="F52" s="317"/>
+    </row>
+    <row r="53" spans="2:6">
+      <c r="B53" s="47" t="s">
         <v>239</v>
       </c>
-      <c r="C47" s="188">
+      <c r="C53" s="188">
         <f>Normalized_FCF!C12</f>
         <v>-13663</v>
-      </c>
-      <c r="D47" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="49" spans="2:6">
-      <c r="B49" s="1" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="50" spans="2:6">
-      <c r="B50" s="47" t="s">
-        <v>266</v>
-      </c>
-      <c r="C50" s="188">
-        <f>Normalized_FCF!C15</f>
-        <v>-572.93535914055167</v>
-      </c>
-      <c r="D50" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="52" spans="2:6">
-      <c r="B52" s="344" t="s">
-        <v>242</v>
-      </c>
-      <c r="C52" s="344"/>
-      <c r="D52" s="344"/>
-      <c r="E52" s="344"/>
-      <c r="F52" s="344"/>
-    </row>
-    <row r="53" spans="2:6">
-      <c r="B53" s="47" t="s">
-        <v>240</v>
-      </c>
-      <c r="C53" s="188">
-        <f>Normalized_FCF!C14</f>
-        <v>-46321.471090244595</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4588,1080 +4676,1109 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="344" t="s">
-        <v>346</v>
-      </c>
-      <c r="C55" s="347"/>
-      <c r="D55" s="347"/>
-      <c r="E55" s="347"/>
-      <c r="F55" s="347"/>
+      <c r="B55" s="1" t="s">
+        <v>247</v>
+      </c>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
-        <v>243</v>
-      </c>
-      <c r="C56" s="1">
-        <f>Normalized_FCF!C17</f>
-        <v>0</v>
+        <v>266</v>
+      </c>
+      <c r="C56" s="188">
+        <f>Normalized_FCF!C15</f>
+        <v>-572.93535914055167</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="343" t="s">
-        <v>351</v>
-      </c>
-      <c r="C58" s="343"/>
-      <c r="D58" s="343"/>
-      <c r="E58" s="343"/>
-      <c r="F58" s="343"/>
-    </row>
-    <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="343" t="s">
-        <v>369</v>
-      </c>
-      <c r="C59" s="343"/>
-      <c r="D59" s="343"/>
-      <c r="E59" s="343"/>
-      <c r="F59" s="343"/>
-    </row>
-    <row r="61" spans="2:6">
-      <c r="B61" s="47" t="s">
-        <v>271</v>
-      </c>
-      <c r="C61" s="188">
-        <f>Normalized_FCF!G19</f>
-        <v>194373</v>
-      </c>
-      <c r="D61" s="1" t="str">
+    <row r="58" spans="2:6">
+      <c r="B58" s="347" t="s">
+        <v>242</v>
+      </c>
+      <c r="C58" s="347"/>
+      <c r="D58" s="347"/>
+      <c r="E58" s="347"/>
+      <c r="F58" s="347"/>
+    </row>
+    <row r="59" spans="2:6">
+      <c r="B59" s="47" t="s">
+        <v>240</v>
+      </c>
+      <c r="C59" s="188">
+        <f>Normalized_FCF!C14</f>
+        <v>-46321.471090244595</v>
+      </c>
+      <c r="D59" s="1" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
+    <row r="61" spans="2:6">
+      <c r="B61" s="347" t="s">
+        <v>341</v>
+      </c>
+      <c r="C61" s="350"/>
+      <c r="D61" s="350"/>
+      <c r="E61" s="350"/>
+      <c r="F61" s="350"/>
+    </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
-        <v>249</v>
-      </c>
-      <c r="C62" s="188">
-        <f>Normalized_FCF!C19</f>
-        <v>138391.47791159325</v>
+        <v>243</v>
+      </c>
+      <c r="C62" s="1">
+        <f>Normalized_FCF!C17</f>
+        <v>0</v>
       </c>
       <c r="D62" s="1" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="63" spans="2:6">
-      <c r="B63" s="254" t="s">
-        <v>398</v>
-      </c>
-      <c r="C63" s="92">
+    <row r="64" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B64" s="346" t="s">
+        <v>346</v>
+      </c>
+      <c r="C64" s="346"/>
+      <c r="D64" s="346"/>
+      <c r="E64" s="346"/>
+      <c r="F64" s="346"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B65" s="346" t="s">
+        <v>364</v>
+      </c>
+      <c r="C65" s="346"/>
+      <c r="D65" s="346"/>
+      <c r="E65" s="346"/>
+      <c r="F65" s="346"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="B67" s="47" t="s">
+        <v>271</v>
+      </c>
+      <c r="C67" s="188">
+        <f>Normalized_FCF!G19</f>
+        <v>194373</v>
+      </c>
+      <c r="D67" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="B68" s="47" t="s">
+        <v>249</v>
+      </c>
+      <c r="C68" s="188">
+        <f>Normalized_FCF!C19</f>
+        <v>138391.47791159325</v>
+      </c>
+      <c r="D68" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="B69" s="252" t="s">
+        <v>393</v>
+      </c>
+      <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
         <v>7.9541327003833207E-2</v>
       </c>
     </row>
-    <row r="64" spans="2:6">
-      <c r="B64" s="254" t="s">
-        <v>316</v>
-      </c>
-      <c r="C64" s="92">
+    <row r="70" spans="1:6">
+      <c r="B70" s="252" t="s">
+        <v>311</v>
+      </c>
+      <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
         <v>3.5854341736694682E-2</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="13.9">
-      <c r="A66" s="247" t="s">
-        <v>363</v>
-      </c>
-      <c r="B66" s="36"/>
-      <c r="C66" s="36"/>
-      <c r="D66" s="36"/>
-      <c r="E66" s="36"/>
-      <c r="F66" s="36"/>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67" s="233"/>
-    </row>
-    <row r="68" spans="1:6" ht="24.4" customHeight="1">
-      <c r="A68" s="17"/>
-      <c r="B68" s="343" t="s">
-        <v>370</v>
-      </c>
-      <c r="C68" s="343"/>
-      <c r="D68" s="343"/>
-      <c r="E68" s="343"/>
-      <c r="F68" s="343"/>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="B69" s="345" t="s">
+    <row r="72" spans="1:6" ht="13.9">
+      <c r="A72" s="247" t="s">
+        <v>358</v>
+      </c>
+      <c r="B72" s="36"/>
+      <c r="C72" s="36"/>
+      <c r="D72" s="36"/>
+      <c r="E72" s="36"/>
+      <c r="F72" s="36"/>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73" s="233"/>
+    </row>
+    <row r="74" spans="1:6" ht="24.4" customHeight="1">
+      <c r="A74" s="17"/>
+      <c r="B74" s="346" t="s">
+        <v>365</v>
+      </c>
+      <c r="C74" s="346"/>
+      <c r="D74" s="346"/>
+      <c r="E74" s="346"/>
+      <c r="F74" s="346"/>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="B75" s="348" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="345"/>
-      <c r="D69" s="345"/>
-      <c r="E69" s="345"/>
-      <c r="F69" s="345"/>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="B71" s="234" t="s">
+      <c r="C75" s="348"/>
+      <c r="D75" s="348"/>
+      <c r="E75" s="348"/>
+      <c r="F75" s="348"/>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="B77" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
-      <c r="B72" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="C72" s="311">
+    <row r="78" spans="1:6">
+      <c r="B78" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C78" s="92">
+        <f>F31</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
-      <c r="B73" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="C73" s="263">
-        <f>IF(D73="Y",1%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D73" s="286" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="B74" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="C74" s="263">
-        <f>IF(D74="Y",1%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D74" s="286" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="B75" s="80" t="s">
+    <row r="79" spans="1:6">
+      <c r="B79" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="C79" s="92">
+        <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="B80" s="80" t="s">
         <v>248</v>
       </c>
-      <c r="C75" s="263">
-        <f>SUM(C72:C74)</f>
+      <c r="C80" s="261">
+        <f>F31+C79</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
-      <c r="C76" s="122"/>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="B77" s="332" t="s">
-        <v>364</v>
-      </c>
-      <c r="C77" s="122"/>
-    </row>
-    <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="343" t="s">
-        <v>371</v>
-      </c>
-      <c r="C78" s="343"/>
-      <c r="D78" s="343"/>
-      <c r="E78" s="343"/>
-      <c r="F78" s="343"/>
-    </row>
-    <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="343" t="s">
-        <v>372</v>
-      </c>
-      <c r="C79" s="343"/>
-      <c r="D79" s="343"/>
-      <c r="E79" s="343"/>
-      <c r="F79" s="343"/>
-    </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="47" t="s">
+      <c r="C81" s="122"/>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="B82" s="327" t="s">
+        <v>359</v>
+      </c>
+      <c r="C82" s="122"/>
+    </row>
+    <row r="83" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B83" s="346" t="s">
+        <v>366</v>
+      </c>
+      <c r="C83" s="346"/>
+      <c r="D83" s="346"/>
+      <c r="E83" s="346"/>
+      <c r="F83" s="346"/>
+    </row>
+    <row r="84" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B84" s="346" t="s">
+        <v>367</v>
+      </c>
+      <c r="C84" s="346"/>
+      <c r="D84" s="346"/>
+      <c r="E84" s="346"/>
+      <c r="F84" s="346"/>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="B86" s="47" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="263">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="B82" s="47" t="s">
-        <v>284</v>
-      </c>
-      <c r="C82" s="248">
+      <c r="C86" s="261">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="B87" s="47" t="s">
+        <v>283</v>
+      </c>
+      <c r="C87" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>3.5495317175460563</v>
       </c>
-      <c r="D82" s="1" t="str">
+      <c r="D87" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="13.9">
-      <c r="A84" s="247" t="s">
-        <v>365</v>
-      </c>
-      <c r="B84" s="36"/>
-      <c r="C84" s="36"/>
-      <c r="D84" s="36"/>
-      <c r="E84" s="36"/>
-      <c r="F84" s="36"/>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85" s="233"/>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="B86" s="343" t="s">
-        <v>373</v>
-      </c>
-      <c r="C86" s="343"/>
-      <c r="D86" s="343"/>
-      <c r="E86" s="343"/>
-      <c r="F86" s="343"/>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="B87" s="1" t="s">
+    <row r="89" spans="1:6" ht="13.9">
+      <c r="A89" s="247" t="s">
+        <v>360</v>
+      </c>
+      <c r="B89" s="36"/>
+      <c r="C89" s="36"/>
+      <c r="D89" s="36"/>
+      <c r="E89" s="36"/>
+      <c r="F89" s="36"/>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="A90" s="233"/>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="B91" s="346" t="s">
+        <v>368</v>
+      </c>
+      <c r="C91" s="346"/>
+      <c r="D91" s="346"/>
+      <c r="E91" s="346"/>
+      <c r="F91" s="346"/>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="B92" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
-      <c r="B89" s="234" t="s">
+    <row r="94" spans="1:6">
+      <c r="B94" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="343" t="s">
-        <v>352</v>
-      </c>
-      <c r="C90" s="343"/>
-      <c r="D90" s="343"/>
-      <c r="E90" s="343"/>
-      <c r="F90" s="343"/>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="B91" s="47" t="s">
+    <row r="95" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B95" s="346" t="s">
+        <v>347</v>
+      </c>
+      <c r="C95" s="346"/>
+      <c r="D95" s="346"/>
+      <c r="E95" s="346"/>
+      <c r="F95" s="346"/>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="B96" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="C91" s="188">
+      <c r="C96" s="188">
         <f>Valuation_Model!C7</f>
         <v>195066</v>
       </c>
-      <c r="D91" s="1" t="str">
+      <c r="D96" s="1" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="92" spans="1:6">
-      <c r="B92" s="47" t="s">
-        <v>285</v>
-      </c>
-      <c r="C92" s="248">
-        <f>C91*scaling_factor*Exchange_Rate/Common_Shares</f>
+    <row r="97" spans="2:6">
+      <c r="B97" s="47" t="s">
+        <v>284</v>
+      </c>
+      <c r="C97" s="248">
+        <f>C96*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>0.40025178686632773</v>
       </c>
-      <c r="D92" s="1" t="str">
+      <c r="D97" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
-      <c r="B93" s="336" t="s">
-        <v>412</v>
-      </c>
-      <c r="C93" s="337">
+    <row r="98" spans="2:6">
+      <c r="B98" s="331" t="s">
+        <v>407</v>
+      </c>
+      <c r="C98" s="332">
         <f>BS!G30/BS!G27</f>
         <v>0.40000523965699897</v>
       </c>
     </row>
-    <row r="94" spans="1:6">
-      <c r="B94" s="336" t="s">
-        <v>413</v>
-      </c>
-      <c r="C94" s="337">
+    <row r="99" spans="2:6">
+      <c r="B99" s="331" t="s">
+        <v>408</v>
+      </c>
+      <c r="C99" s="332">
         <f>BS!G31/BS!G27</f>
         <v>0.10646655543311496</v>
       </c>
     </row>
-    <row r="95" spans="1:6">
-      <c r="B95" s="336" t="s">
-        <v>415</v>
-      </c>
-      <c r="C95" s="338">
+    <row r="100" spans="2:6">
+      <c r="B100" s="331" t="s">
+        <v>410</v>
+      </c>
+      <c r="C100" s="333">
         <f>BS!C50</f>
         <v>0.9804830051022897</v>
       </c>
     </row>
-    <row r="97" spans="1:6">
-      <c r="B97" s="1" t="s">
+    <row r="102" spans="2:6">
+      <c r="B102" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="98" spans="1:6">
-      <c r="B98" s="47" t="s">
+    <row r="103" spans="2:6">
+      <c r="B103" s="47" t="s">
         <v>265</v>
       </c>
-      <c r="C98" s="188">
+      <c r="C103" s="188">
         <f>BS!C66</f>
         <v>1089388</v>
-      </c>
-      <c r="D98" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
-      <c r="B99" s="47" t="s">
-        <v>267</v>
-      </c>
-      <c r="C99" s="188">
-        <f>Valuation_Model!C8</f>
-        <v>587281.82009631116</v>
-      </c>
-      <c r="D99" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
-      <c r="B100" s="47" t="s">
-        <v>286</v>
-      </c>
-      <c r="C100" s="248">
-        <f>C99*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.2050311068441337</v>
-      </c>
-      <c r="D100" s="1" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6">
-      <c r="B102" s="1" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6">
-      <c r="B103" s="47" t="s">
-        <v>258</v>
-      </c>
-      <c r="C103" s="188">
-        <f>Valuation_Model!C9</f>
-        <v>18907.900000000001</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="104" spans="1:6">
+    <row r="104" spans="2:6">
       <c r="B104" s="47" t="s">
-        <v>287</v>
-      </c>
-      <c r="C104" s="248">
-        <f>C103*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.8796718858693152E-2</v>
+        <v>267</v>
+      </c>
+      <c r="C104" s="188">
+        <f>Valuation_Model!C8</f>
+        <v>587281.82009631116</v>
       </c>
       <c r="D104" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="105" spans="2:6">
+      <c r="B105" s="47" t="s">
+        <v>285</v>
+      </c>
+      <c r="C105" s="248">
+        <f>C104*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>1.2050311068441337</v>
+      </c>
+      <c r="D105" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="343" t="s">
-        <v>374</v>
-      </c>
-      <c r="C106" s="343"/>
-      <c r="D106" s="343"/>
-      <c r="E106" s="343"/>
-      <c r="F106" s="343"/>
-    </row>
-    <row r="108" spans="1:6">
+    <row r="107" spans="2:6">
+      <c r="B107" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
-        <v>283</v>
-      </c>
-      <c r="C108" s="248">
-        <f>Valuation_Model!C12</f>
-        <v>4.3931077563825554</v>
+        <v>258</v>
+      </c>
+      <c r="C108" s="188">
+        <f>Valuation_Model!C9</f>
+        <v>18907.900000000001</v>
       </c>
       <c r="D108" s="1" t="str">
-        <f>Market_currency</f>
+        <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="109" spans="1:6">
-      <c r="B109" s="336" t="s">
-        <v>414</v>
+    <row r="109" spans="2:6">
+      <c r="B109" s="47" t="s">
+        <v>286</v>
       </c>
       <c r="C109" s="248">
-        <f>BS!D47</f>
-        <v>1.6698226477450393</v>
+        <f>C108*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>3.8796718858693152E-2</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="111" spans="1:6" ht="13.9">
-      <c r="A111" s="247" t="s">
-        <v>366</v>
-      </c>
-      <c r="B111" s="36"/>
-      <c r="C111" s="36"/>
-      <c r="D111" s="36"/>
-      <c r="E111" s="36"/>
-      <c r="F111" s="36"/>
-    </row>
-    <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="344" t="s">
-        <v>375</v>
-      </c>
-      <c r="C113" s="344"/>
-      <c r="D113" s="344"/>
-      <c r="E113" s="344"/>
-      <c r="F113" s="344"/>
-    </row>
-    <row r="115" spans="1:6" ht="12.4">
-      <c r="B115" s="260" t="s">
+    <row r="111" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B111" s="346" t="s">
+        <v>369</v>
+      </c>
+      <c r="C111" s="346"/>
+      <c r="D111" s="346"/>
+      <c r="E111" s="346"/>
+      <c r="F111" s="346"/>
+    </row>
+    <row r="113" spans="1:6">
+      <c r="B113" s="47" t="s">
+        <v>282</v>
+      </c>
+      <c r="C113" s="248">
+        <f>Valuation_Model!C12</f>
+        <v>4.3931077563825554</v>
+      </c>
+      <c r="D113" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
+      <c r="B114" s="331" t="s">
+        <v>409</v>
+      </c>
+      <c r="C114" s="248">
+        <f>BS!D47</f>
+        <v>1.6698226477450393</v>
+      </c>
+      <c r="D114" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" ht="13.9">
+      <c r="A116" s="247" t="s">
+        <v>361</v>
+      </c>
+      <c r="B116" s="36"/>
+      <c r="C116" s="36"/>
+      <c r="D116" s="36"/>
+      <c r="E116" s="36"/>
+      <c r="F116" s="36"/>
+    </row>
+    <row r="118" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B118" s="347" t="s">
+        <v>370</v>
+      </c>
+      <c r="C118" s="347"/>
+      <c r="D118" s="347"/>
+      <c r="E118" s="347"/>
+      <c r="F118" s="347"/>
+    </row>
+    <row r="120" spans="1:6" ht="12.4">
+      <c r="B120" s="258" t="s">
         <v>118</v>
       </c>
-      <c r="C115" s="260" t="s">
+      <c r="C120" s="258" t="s">
         <v>133</v>
       </c>
-      <c r="D115" s="260" t="s">
+      <c r="D120" s="258" t="s">
         <v>113</v>
       </c>
-      <c r="E115" s="260" t="s">
+      <c r="E120" s="258" t="s">
         <v>260</v>
       </c>
-      <c r="F115" s="260" t="s">
+      <c r="F120" s="258" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="116" spans="1:6">
-      <c r="B116" s="255" t="str">
+    <row r="121" spans="1:6">
+      <c r="B121" s="253" t="str">
         <f>Valuation_Model!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C116" s="256">
+      <c r="C121" s="254">
         <f>Valuation_Model!C74</f>
         <v>0.1</v>
       </c>
-      <c r="D116" s="257">
+      <c r="D121" s="255">
         <f>Valuation_Model!D74</f>
         <v>15</v>
       </c>
-      <c r="E116" s="258" t="str">
+      <c r="E121" s="256" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
         <v>7.02 HKD</v>
       </c>
-      <c r="F116" s="259">
+      <c r="F121" s="257">
         <f>Valuation_Model!F74</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
-      <c r="B117" s="242" t="str">
+    <row r="122" spans="1:6">
+      <c r="B122" s="242" t="str">
         <f>Valuation_Model!B75</f>
         <v>Optimistic</v>
       </c>
-      <c r="C117" s="243">
+      <c r="C122" s="243">
         <f>Valuation_Model!C75</f>
         <v>0.06</v>
       </c>
-      <c r="D117" s="244">
+      <c r="D122" s="244">
         <f>Valuation_Model!D75</f>
         <v>10</v>
       </c>
-      <c r="E117" s="245" t="str">
+      <c r="E122" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
         <v>5.15 HKD</v>
       </c>
-      <c r="F117" s="246">
+      <c r="F122" s="246">
         <f>Valuation_Model!F75</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="118" spans="1:6">
-      <c r="B118" s="242" t="str">
+    <row r="123" spans="1:6">
+      <c r="B123" s="242" t="str">
         <f>Valuation_Model!B76</f>
         <v>Base</v>
       </c>
-      <c r="C118" s="243">
+      <c r="C123" s="243">
         <f>Valuation_Model!C76</f>
         <v>0.04</v>
       </c>
-      <c r="D118" s="244">
+      <c r="D123" s="244">
         <f>Valuation_Model!D76</f>
         <v>10</v>
       </c>
-      <c r="E118" s="245" t="str">
+      <c r="E123" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
         <v>4.87 HKD</v>
       </c>
-      <c r="F118" s="246">
+      <c r="F123" s="246">
         <f>Valuation_Model!F76</f>
         <v>0.53999999999999992</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
-      <c r="B119" s="242" t="str">
+    <row r="124" spans="1:6">
+      <c r="B124" s="242" t="str">
         <f>Valuation_Model!B77</f>
         <v>Pessimistic</v>
       </c>
-      <c r="C119" s="243">
+      <c r="C124" s="243">
         <f>Valuation_Model!C77</f>
         <v>0.02</v>
       </c>
-      <c r="D119" s="244">
+      <c r="D124" s="244">
         <f>Valuation_Model!D77</f>
         <v>10</v>
       </c>
-      <c r="E119" s="245" t="str">
+      <c r="E124" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
         <v>4.62 HKD</v>
       </c>
-      <c r="F119" s="246">
+      <c r="F124" s="246">
         <f>Valuation_Model!F77</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="120" spans="1:6">
-      <c r="B120" s="242" t="str">
+    <row r="125" spans="1:6">
+      <c r="B125" s="242" t="str">
         <f>Valuation_Model!B78</f>
         <v>Devil's advocate</v>
       </c>
-      <c r="C120" s="243">
+      <c r="C125" s="243">
         <f>Valuation_Model!C78</f>
         <v>0</v>
       </c>
-      <c r="D120" s="244">
+      <c r="D125" s="244">
         <f>Valuation_Model!D78</f>
         <v>15</v>
       </c>
-      <c r="E120" s="245" t="str">
+      <c r="E125" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
         <v>4.39 HKD</v>
       </c>
-      <c r="F120" s="246">
+      <c r="F125" s="246">
         <f>Valuation_Model!F78</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="122" spans="1:6">
-      <c r="B122" s="235" t="s">
+    <row r="127" spans="1:6">
+      <c r="B127" s="235" t="s">
         <v>259</v>
       </c>
-      <c r="C122" s="241">
+      <c r="C127" s="241">
         <f>Scenarios!C60</f>
         <v>4.9623808252376094</v>
       </c>
-      <c r="D122" s="236" t="str">
+      <c r="D127" s="236" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="348" t="s">
-        <v>378</v>
-      </c>
-      <c r="C124" s="348"/>
-      <c r="D124" s="348"/>
-      <c r="E124" s="348"/>
-      <c r="F124" s="348"/>
-    </row>
-    <row r="126" spans="1:6" ht="13.9">
-      <c r="A126" s="247" t="s">
-        <v>410</v>
-      </c>
-      <c r="B126" s="36"/>
-      <c r="C126" s="36"/>
-      <c r="D126" s="36"/>
-      <c r="E126" s="36"/>
-      <c r="F126" s="36"/>
-    </row>
-    <row r="128" spans="1:6">
-      <c r="B128" s="346" t="s">
-        <v>376</v>
-      </c>
-      <c r="C128" s="346"/>
-      <c r="D128" s="346"/>
-      <c r="E128" s="346"/>
-      <c r="F128" s="346"/>
-    </row>
-    <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="343" t="s">
-        <v>377</v>
-      </c>
-      <c r="C129" s="343"/>
-      <c r="D129" s="343"/>
-      <c r="E129" s="343"/>
-      <c r="F129" s="343"/>
-    </row>
-    <row r="130" spans="2:6">
-      <c r="B130" s="234" t="s">
+    <row r="129" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B129" s="351" t="s">
+        <v>373</v>
+      </c>
+      <c r="C129" s="351"/>
+      <c r="D129" s="351"/>
+      <c r="E129" s="351"/>
+      <c r="F129" s="351"/>
+    </row>
+    <row r="131" spans="1:6" ht="13.9">
+      <c r="A131" s="247" t="s">
+        <v>405</v>
+      </c>
+      <c r="B131" s="36"/>
+      <c r="C131" s="36"/>
+      <c r="D131" s="36"/>
+      <c r="E131" s="36"/>
+      <c r="F131" s="36"/>
+    </row>
+    <row r="133" spans="1:6">
+      <c r="B133" s="349" t="s">
+        <v>371</v>
+      </c>
+      <c r="C133" s="349"/>
+      <c r="D133" s="349"/>
+      <c r="E133" s="349"/>
+      <c r="F133" s="349"/>
+    </row>
+    <row r="134" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B134" s="346" t="s">
+        <v>372</v>
+      </c>
+      <c r="C134" s="346"/>
+      <c r="D134" s="346"/>
+      <c r="E134" s="346"/>
+      <c r="F134" s="346"/>
+    </row>
+    <row r="135" spans="1:6">
+      <c r="B135" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="131" spans="2:6">
-      <c r="B131" s="1" t="s">
+    <row r="136" spans="1:6">
+      <c r="B136" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C131" s="251">
-        <f>E25</f>
+      <c r="C136" s="250">
+        <f>F28</f>
         <v>3</v>
       </c>
     </row>
-    <row r="132" spans="2:6">
-      <c r="B132" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="C132" s="250">
-        <f>C24</f>
+    <row r="137" spans="1:6">
+      <c r="B137" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C137" s="249">
+        <f>F29</f>
         <v>0.4</v>
       </c>
     </row>
-    <row r="133" spans="2:6">
-      <c r="B133" s="236" t="s">
+    <row r="138" spans="1:6">
+      <c r="B138" s="236" t="s">
         <v>262</v>
       </c>
-      <c r="C133" s="237">
+      <c r="C138" s="237">
         <f>Scenarios!C77</f>
         <v>0.128</v>
       </c>
-      <c r="D133" s="236" t="str">
+      <c r="D138" s="236" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="135" spans="2:6">
-      <c r="B135" s="234" t="s">
-        <v>418</v>
-      </c>
-      <c r="C135" s="270" t="str">
+    <row r="140" spans="1:6">
+      <c r="B140" s="234" t="s">
+        <v>412</v>
+      </c>
+      <c r="C140" s="268" t="str">
         <f>C11</f>
         <v>0398.HK</v>
       </c>
-      <c r="D135" s="270" t="str">
+      <c r="D140" s="268" t="str">
         <f>IF(D11="","",D11)</f>
         <v/>
       </c>
     </row>
-    <row r="136" spans="2:6">
-      <c r="B136" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="C136" s="337">
-        <f>C24</f>
+    <row r="141" spans="1:6">
+      <c r="B141" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C141" s="332">
+        <f>F29</f>
         <v>0.4</v>
       </c>
     </row>
-    <row r="137" spans="2:6">
-      <c r="B137" s="236" t="str">
-        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+    <row r="142" spans="1:6">
+      <c r="B142" s="236" t="str">
+        <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C137" s="240">
+      <c r="C142" s="240">
         <f>Scenarios!C81</f>
         <v>0.20338192419825066</v>
       </c>
     </row>
-    <row r="138" spans="2:6">
-      <c r="B138" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+    <row r="143" spans="1:6">
+      <c r="B143" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C138" s="240">
+      <c r="C143" s="240">
         <f>Scenarios!C82</f>
         <v>1.8084478226084586</v>
       </c>
     </row>
-    <row r="139" spans="2:6">
-      <c r="B139" s="80" t="s">
+    <row r="144" spans="1:6">
+      <c r="B144" s="80" t="s">
         <v>261</v>
       </c>
-      <c r="C139" s="239">
+      <c r="C144" s="239">
         <f>Scenarios!C83</f>
         <v>2.0118297468067095</v>
       </c>
-      <c r="D139" s="342" t="str">
-        <f>IF($D$11="","",C139*$E$22)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="140" spans="2:6">
-      <c r="B140" s="290" t="s">
-        <v>425</v>
-      </c>
-      <c r="C140" s="340" t="str">
+      <c r="D144" s="336" t="str">
+        <f>IF($D$11="","",C144*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="145" spans="2:4">
+      <c r="B145" s="286" t="s">
+        <v>419</v>
+      </c>
+      <c r="C145" s="334" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D140" s="340" t="str">
+      <c r="D145" s="334" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
     </row>
-    <row r="141" spans="2:6">
-      <c r="B141" s="238" t="s">
+    <row r="146" spans="2:4">
+      <c r="B146" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C141" s="92">
+      <c r="C146" s="92">
         <f>Scenarios!F83</f>
         <v>0.59458376580552363</v>
       </c>
     </row>
-    <row r="143" spans="2:6">
-      <c r="B143" s="234" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="144" spans="2:6">
-      <c r="B144" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="C144" s="337">
+    <row r="148" spans="2:4">
+      <c r="B148" s="234" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="149" spans="2:4">
+      <c r="B149" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="C149" s="332">
         <f>Scenarios!C90</f>
         <v>0.2</v>
       </c>
     </row>
-    <row r="145" spans="2:4">
-      <c r="B145" s="236" t="str">
-        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+    <row r="150" spans="2:4">
+      <c r="B150" s="236" t="str">
+        <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C145" s="240">
+      <c r="C150" s="240">
         <f>Scenarios!C91</f>
         <v>0.26962962962962961</v>
       </c>
     </row>
-    <row r="146" spans="2:4">
-      <c r="B146" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+    <row r="151" spans="2:4">
+      <c r="B151" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C146" s="240">
+      <c r="C151" s="240">
         <f>Scenarios!C92</f>
         <v>2.8717481627532462</v>
       </c>
     </row>
-    <row r="147" spans="2:4">
-      <c r="B147" s="80" t="s">
+    <row r="152" spans="2:4">
+      <c r="B152" s="80" t="s">
         <v>261</v>
       </c>
-      <c r="C147" s="239">
+      <c r="C152" s="239">
         <f>Scenarios!C93</f>
         <v>3.1413777923828756</v>
       </c>
-      <c r="D147" s="342" t="str">
-        <f>IF($D$11="","",C147*$E$22)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="148" spans="2:4">
-      <c r="B148" s="290" t="s">
-        <v>425</v>
-      </c>
-      <c r="C148" s="340" t="str">
+      <c r="D152" s="336" t="str">
+        <f>IF($D$11="","",C152*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="153" spans="2:4">
+      <c r="B153" s="286" t="s">
+        <v>419</v>
+      </c>
+      <c r="C153" s="334" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D148" s="340" t="str">
+      <c r="D153" s="334" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
     </row>
-    <row r="149" spans="2:4">
-      <c r="B149" s="238" t="s">
+    <row r="154" spans="2:4">
+      <c r="B154" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C149" s="92">
+      <c r="C154" s="92">
         <f>Scenarios!F93</f>
         <v>0.36696156481854458</v>
       </c>
     </row>
-    <row r="151" spans="2:4">
-      <c r="B151" s="234" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="152" spans="2:4">
-      <c r="B152" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="C152" s="92">
+    <row r="156" spans="2:4">
+      <c r="B156" s="234" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="157" spans="2:4">
+      <c r="B157" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C157" s="92">
         <f>Scenarios!C96</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="153" spans="2:4">
-      <c r="B153" s="236" t="str">
-        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+    <row r="158" spans="2:4">
+      <c r="B158" s="236" t="str">
+        <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C153" s="240">
+      <c r="C158" s="240">
         <f>Scenarios!C97</f>
         <v>0.32986841436772868</v>
       </c>
     </row>
-    <row r="154" spans="2:4">
-      <c r="B154" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+    <row r="159" spans="2:4">
+      <c r="B159" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C154" s="240">
+      <c r="C159" s="240">
         <f>Scenarios!C98</f>
         <v>3.9392978912938901</v>
       </c>
     </row>
-    <row r="155" spans="2:4">
-      <c r="B155" s="80" t="s">
-        <v>409</v>
-      </c>
-      <c r="C155" s="239">
+    <row r="160" spans="2:4">
+      <c r="B160" s="80" t="s">
+        <v>404</v>
+      </c>
+      <c r="C160" s="239">
         <f>Scenarios!C99</f>
         <v>4.2691663056616189</v>
       </c>
-      <c r="D155" s="342" t="str">
-        <f>IF($D$11="","",C155*$E$22)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="156" spans="2:4">
-      <c r="B156" s="290" t="s">
-        <v>425</v>
-      </c>
-      <c r="C156" s="340" t="str">
+      <c r="D160" s="336" t="str">
+        <f>IF($D$11="","",C160*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="161" spans="1:6">
+      <c r="B161" s="286" t="s">
+        <v>419</v>
+      </c>
+      <c r="C161" s="334" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D156" s="340" t="str">
+      <c r="D161" s="334" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
     </row>
-    <row r="157" spans="2:4">
-      <c r="B157" s="238" t="s">
+    <row r="162" spans="1:6">
+      <c r="B162" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C157" s="92">
+      <c r="C162" s="92">
         <f>Scenarios!F99</f>
         <v>0.13969393804894004</v>
       </c>
     </row>
-    <row r="159" spans="2:4">
-      <c r="B159" s="234" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="160" spans="2:4">
-      <c r="B160" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="C160" s="92">
-        <f>E26</f>
+    <row r="164" spans="1:6">
+      <c r="B164" s="234" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
+      <c r="B165" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C165" s="92">
+        <f>F32</f>
         <v>0.1174</v>
       </c>
     </row>
-    <row r="161" spans="1:6">
-      <c r="B161" s="236" t="str">
-        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+    <row r="166" spans="1:6">
+      <c r="B166" s="236" t="str">
+        <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C161" s="240">
+      <c r="C166" s="240">
         <f>Scenarios!C103</f>
         <v>0.30881320012014707</v>
       </c>
     </row>
-    <row r="162" spans="1:6">
-      <c r="B162" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+    <row r="167" spans="1:6">
+      <c r="B167" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C162" s="240">
+      <c r="C167" s="240">
         <f>Scenarios!C104</f>
         <v>3.5568380305864293</v>
       </c>
     </row>
-    <row r="163" spans="1:6">
-      <c r="B163" s="80" t="s">
-        <v>409</v>
-      </c>
-      <c r="C163" s="239">
+    <row r="168" spans="1:6">
+      <c r="B168" s="80" t="s">
+        <v>404</v>
+      </c>
+      <c r="C168" s="239">
         <f>Scenarios!C105</f>
         <v>3.8656512307065762</v>
       </c>
-      <c r="D163" s="342" t="str">
-        <f>IF($D$11="","",C163*$E$22)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="164" spans="1:6">
-      <c r="B164" s="290" t="s">
-        <v>425</v>
-      </c>
-      <c r="C164" s="340" t="str">
+      <c r="D168" s="336" t="str">
+        <f>IF($D$11="","",C168*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="169" spans="1:6">
+      <c r="B169" s="286" t="s">
+        <v>419</v>
+      </c>
+      <c r="C169" s="334" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D164" s="340" t="str">
+      <c r="D169" s="334" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
     </row>
-    <row r="165" spans="1:6">
-      <c r="B165" s="238" t="s">
+    <row r="170" spans="1:6">
+      <c r="B170" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C165" s="92">
+      <c r="C170" s="92">
         <f>Scenarios!F105</f>
         <v>0.22106689885075603</v>
       </c>
     </row>
-    <row r="167" spans="1:6" ht="13.9">
-      <c r="A167" s="247" t="s">
+    <row r="172" spans="1:6" ht="13.9">
+      <c r="A172" s="247" t="s">
+        <v>377</v>
+      </c>
+      <c r="B172" s="36"/>
+      <c r="C172" s="36"/>
+      <c r="D172" s="36"/>
+      <c r="E172" s="36"/>
+      <c r="F172" s="36"/>
+    </row>
+    <row r="174" spans="1:6">
+      <c r="B174" s="353" t="s">
+        <v>379</v>
+      </c>
+      <c r="C174" s="346"/>
+      <c r="D174" s="346"/>
+      <c r="E174" s="346"/>
+      <c r="F174" s="346"/>
+    </row>
+    <row r="176" spans="1:6">
+      <c r="B176" s="234" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="177" spans="2:6">
+      <c r="B177" s="350" t="s">
+        <v>383</v>
+      </c>
+      <c r="C177" s="350"/>
+      <c r="D177" s="350"/>
+      <c r="E177" s="350"/>
+      <c r="F177" s="350"/>
+    </row>
+    <row r="178" spans="2:6">
+      <c r="B178" s="238" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="179" spans="2:6">
+      <c r="B179" s="238" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="180" spans="2:6">
+      <c r="B180" s="238" t="s">
         <v>382</v>
       </c>
-      <c r="B167" s="36"/>
-      <c r="C167" s="36"/>
-      <c r="D167" s="36"/>
-      <c r="E167" s="36"/>
-      <c r="F167" s="36"/>
-    </row>
-    <row r="169" spans="1:6">
-      <c r="B169" s="350" t="s">
+    </row>
+    <row r="182" spans="2:6">
+      <c r="B182" s="1" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="183" spans="2:6" ht="46.5" customHeight="1">
+      <c r="B183" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C169" s="343"/>
-      <c r="D169" s="343"/>
-      <c r="E169" s="343"/>
-      <c r="F169" s="343"/>
-    </row>
-    <row r="171" spans="1:6">
-      <c r="B171" s="234" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6">
-      <c r="B172" s="347" t="s">
+      <c r="C183" s="347"/>
+      <c r="D183" s="347"/>
+      <c r="E183" s="347"/>
+      <c r="F183" s="347"/>
+    </row>
+    <row r="185" spans="2:6">
+      <c r="B185" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="C172" s="347"/>
-      <c r="D172" s="347"/>
-      <c r="E172" s="347"/>
-      <c r="F172" s="347"/>
-    </row>
-    <row r="173" spans="1:6">
-      <c r="B173" s="238" t="s">
+    </row>
+    <row r="186" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B186" s="352" t="s">
         <v>385</v>
       </c>
-    </row>
-    <row r="174" spans="1:6">
-      <c r="B174" s="238" t="s">
+      <c r="C186" s="352"/>
+      <c r="D186" s="352"/>
+      <c r="E186" s="352"/>
+      <c r="F186" s="352"/>
+    </row>
+    <row r="187" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B187" s="352" t="s">
         <v>386</v>
       </c>
-    </row>
-    <row r="175" spans="1:6">
-      <c r="B175" s="238" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="177" spans="2:6">
-      <c r="B177" s="1" t="s">
+      <c r="C187" s="352"/>
+      <c r="D187" s="352"/>
+      <c r="E187" s="352"/>
+      <c r="F187" s="352"/>
+    </row>
+    <row r="189" spans="2:6">
+      <c r="B189" s="1" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="178" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B178" s="344" t="s">
+    <row r="190" spans="2:6">
+      <c r="B190" s="238" t="s">
         <v>389</v>
       </c>
-      <c r="C178" s="344"/>
-      <c r="D178" s="344"/>
-      <c r="E178" s="344"/>
-      <c r="F178" s="344"/>
-    </row>
-    <row r="180" spans="2:6">
-      <c r="B180" s="1" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="181" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B181" s="349" t="s">
+    </row>
+    <row r="191" spans="2:6">
+      <c r="B191" s="238" t="s">
         <v>390</v>
       </c>
-      <c r="C181" s="349"/>
-      <c r="D181" s="349"/>
-      <c r="E181" s="349"/>
-      <c r="F181" s="349"/>
-    </row>
-    <row r="182" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B182" s="349" t="s">
+    </row>
+    <row r="192" spans="2:6">
+      <c r="B192" s="238" t="s">
         <v>391</v>
-      </c>
-      <c r="C182" s="349"/>
-      <c r="D182" s="349"/>
-      <c r="E182" s="349"/>
-      <c r="F182" s="349"/>
-    </row>
-    <row r="184" spans="2:6">
-      <c r="B184" s="1" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="185" spans="2:6">
-      <c r="B185" s="238" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="186" spans="2:6">
-      <c r="B186" s="238" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="187" spans="2:6">
-      <c r="B187" s="238" t="s">
-        <v>396</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B181:F181"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B169:F169"/>
-    <mergeCell ref="B178:F178"/>
-    <mergeCell ref="B172:F172"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B84:F84"/>
+    <mergeCell ref="B91:F91"/>
+    <mergeCell ref="B111:F111"/>
+    <mergeCell ref="B133:F133"/>
+    <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B79:F79"/>
-    <mergeCell ref="B86:F86"/>
-    <mergeCell ref="B106:F106"/>
-    <mergeCell ref="B128:F128"/>
-    <mergeCell ref="B44:F44"/>
-    <mergeCell ref="B52:F52"/>
-    <mergeCell ref="B55:F55"/>
-    <mergeCell ref="B59:F59"/>
-    <mergeCell ref="B68:F68"/>
+    <mergeCell ref="B61:F61"/>
+    <mergeCell ref="B65:F65"/>
+    <mergeCell ref="B74:F74"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{45F807FD-9E0F-415A-9BBD-D5FB6470B56D}">
       <formula1>"Y, N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D73:D74" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C23:C25" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C22:D22" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C25:D25" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E22 E25" xr:uid="{788B6937-776F-41CC-B9B1-7986DB35B57D}">
+      <formula1>"DCF,DDM"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5675,17 +5792,17 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
-    <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
-    <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.796875" style="1"/>
+    <col min="2" max="2" width="27.265625" style="1" customWidth="1"/>
+    <col min="3" max="13" width="20.73046875" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.86328125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
-        <f>Thesis!C22</f>
+        <f>Thesis!C25</f>
         <v>HKD</v>
       </c>
       <c r="C1" s="104">
@@ -6164,7 +6281,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="C22" s="181">
         <v>346987</v>
@@ -6198,7 +6315,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="C23" s="181">
         <v>-67837</v>
@@ -6232,7 +6349,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="C24" s="181">
         <v>-423459</v>
@@ -6298,7 +6415,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -7593,7 +7710,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8041,11 +8158,11 @@
         <f t="shared" si="40"/>
         <v>86046</v>
       </c>
-      <c r="I77" s="335"/>
-      <c r="J77" s="335"/>
-      <c r="K77" s="335"/>
-      <c r="L77" s="335"/>
-      <c r="M77" s="335"/>
+      <c r="I77" s="330"/>
+      <c r="J77" s="330"/>
+      <c r="K77" s="330"/>
+      <c r="L77" s="330"/>
+      <c r="M77" s="330"/>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
@@ -8075,11 +8192,11 @@
         <f t="shared" si="40"/>
         <v>823654</v>
       </c>
-      <c r="I78" s="335"/>
-      <c r="J78" s="335"/>
-      <c r="K78" s="335"/>
-      <c r="L78" s="335"/>
-      <c r="M78" s="335"/>
+      <c r="I78" s="330"/>
+      <c r="J78" s="330"/>
+      <c r="K78" s="330"/>
+      <c r="L78" s="330"/>
+      <c r="M78" s="330"/>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
@@ -8211,15 +8328,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.265625" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="18.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="25.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="18.6640625" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="12.33203125" style="1"/>
+    <col min="3" max="4" width="18.73046875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.73046875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="18.73046875" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="12.265625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="15" customHeight="1">
@@ -8277,7 +8394,7 @@
         <f>83075+265532</f>
         <v>348607</v>
       </c>
-      <c r="D4" s="294">
+      <c r="D4" s="290">
         <v>0.6</v>
       </c>
       <c r="E4" s="25"/>
@@ -8287,7 +8404,7 @@
       <c r="G4" s="19">
         <v>1089388</v>
       </c>
-      <c r="H4" s="294">
+      <c r="H4" s="290">
         <v>0.9</v>
       </c>
     </row>
@@ -8298,7 +8415,7 @@
       <c r="C5" s="19">
         <v>0</v>
       </c>
-      <c r="D5" s="294">
+      <c r="D5" s="290">
         <v>0.6</v>
       </c>
       <c r="E5" s="25"/>
@@ -8308,7 +8425,7 @@
       <c r="G5" s="19">
         <v>0</v>
       </c>
-      <c r="H5" s="294">
+      <c r="H5" s="290">
         <v>0.7</v>
       </c>
     </row>
@@ -8319,7 +8436,7 @@
       <c r="C6" s="19">
         <v>506592</v>
       </c>
-      <c r="D6" s="294">
+      <c r="D6" s="290">
         <v>0.5</v>
       </c>
       <c r="E6" s="25"/>
@@ -8329,7 +8446,7 @@
       <c r="G6" s="19">
         <v>0</v>
       </c>
-      <c r="H6" s="294">
+      <c r="H6" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8340,7 +8457,7 @@
       <c r="C7" s="19">
         <v>0</v>
       </c>
-      <c r="D7" s="294">
+      <c r="D7" s="290">
         <v>0.6</v>
       </c>
       <c r="E7" s="25"/>
@@ -8350,7 +8467,7 @@
       <c r="G7" s="19">
         <v>10851</v>
       </c>
-      <c r="H7" s="294">
+      <c r="H7" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8361,7 +8478,7 @@
       <c r="C8" s="19">
         <v>0</v>
       </c>
-      <c r="D8" s="294">
+      <c r="D8" s="290">
         <v>0.6</v>
       </c>
       <c r="E8" s="25"/>
@@ -8371,7 +8488,7 @@
       <c r="G8" s="19">
         <v>0</v>
       </c>
-      <c r="H8" s="294">
+      <c r="H8" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8382,7 +8499,7 @@
       <c r="C9" s="19">
         <v>0</v>
       </c>
-      <c r="D9" s="294">
+      <c r="D9" s="290">
         <v>0.1</v>
       </c>
       <c r="E9" s="25"/>
@@ -8392,7 +8509,7 @@
       <c r="G9" s="19">
         <v>0</v>
       </c>
-      <c r="H9" s="294">
+      <c r="H9" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8403,10 +8520,10 @@
       <c r="C10" s="19">
         <v>8727</v>
       </c>
-      <c r="D10" s="294">
+      <c r="D10" s="290">
         <v>0.9</v>
       </c>
-      <c r="H10" s="295"/>
+      <c r="H10" s="291"/>
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
@@ -8415,10 +8532,10 @@
       <c r="C11" s="19">
         <v>0</v>
       </c>
-      <c r="D11" s="294">
+      <c r="D11" s="290">
         <v>0.05</v>
       </c>
-      <c r="H11" s="295"/>
+      <c r="H11" s="291"/>
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
@@ -8476,7 +8593,7 @@
       <c r="C15" s="19">
         <v>0</v>
       </c>
-      <c r="D15" s="294">
+      <c r="D15" s="290">
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
@@ -8485,7 +8602,7 @@
       <c r="G15" s="19">
         <v>0</v>
       </c>
-      <c r="H15" s="294">
+      <c r="H15" s="290">
         <v>0.8</v>
       </c>
     </row>
@@ -8496,7 +8613,7 @@
       <c r="C16" s="19">
         <v>0</v>
       </c>
-      <c r="D16" s="294">
+      <c r="D16" s="290">
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
@@ -8506,7 +8623,7 @@
         <f>29657+19498</f>
         <v>49155</v>
       </c>
-      <c r="H16" s="294">
+      <c r="H16" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8517,7 +8634,7 @@
       <c r="C17" s="19">
         <v>0</v>
       </c>
-      <c r="D17" s="294">
+      <c r="D17" s="290">
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
@@ -8526,7 +8643,7 @@
       <c r="G17" s="19">
         <v>0</v>
       </c>
-      <c r="H17" s="294">
+      <c r="H17" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8537,7 +8654,7 @@
       <c r="C18" s="19">
         <v>0</v>
       </c>
-      <c r="D18" s="294">
+      <c r="D18" s="290">
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
@@ -8546,7 +8663,7 @@
       <c r="G18" s="19">
         <v>0</v>
       </c>
-      <c r="H18" s="294">
+      <c r="H18" s="290">
         <v>0.1</v>
       </c>
     </row>
@@ -8558,7 +8675,7 @@
         <f>233391+169651+360+16234</f>
         <v>419636</v>
       </c>
-      <c r="D19" s="294">
+      <c r="D19" s="290">
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
@@ -8568,7 +8685,7 @@
         <f>64831+22181</f>
         <v>87012</v>
       </c>
-      <c r="H19" s="294">
+      <c r="H19" s="290">
         <v>0.1</v>
       </c>
     </row>
@@ -8579,7 +8696,7 @@
       <c r="C20" s="19">
         <v>0</v>
       </c>
-      <c r="D20" s="294">
+      <c r="D20" s="290">
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
@@ -8588,7 +8705,7 @@
       <c r="G20" s="19">
         <v>0</v>
       </c>
-      <c r="H20" s="294">
+      <c r="H20" s="290">
         <v>0.2</v>
       </c>
     </row>
@@ -8599,7 +8716,7 @@
       <c r="C21" s="19">
         <v>0</v>
       </c>
-      <c r="D21" s="294">
+      <c r="D21" s="290">
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
@@ -8608,7 +8725,7 @@
       <c r="G21" s="19">
         <v>36961</v>
       </c>
-      <c r="H21" s="294">
+      <c r="H21" s="290">
         <v>0.1</v>
       </c>
     </row>
@@ -8619,10 +8736,10 @@
       <c r="C22" s="19">
         <v>8134</v>
       </c>
-      <c r="D22" s="294">
+      <c r="D22" s="290">
         <v>0.9</v>
       </c>
-      <c r="H22" s="295"/>
+      <c r="H22" s="291"/>
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
@@ -8631,10 +8748,10 @@
       <c r="C23" s="19">
         <v>0</v>
       </c>
-      <c r="D23" s="294">
-        <v>0</v>
-      </c>
-      <c r="H23" s="295"/>
+      <c r="D23" s="290">
+        <v>0</v>
+      </c>
+      <c r="H23" s="291"/>
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
@@ -8967,13 +9084,13 @@
       <c r="B45" s="16" t="s">
         <v>272</v>
       </c>
-      <c r="C45" s="261" t="s">
+      <c r="C45" s="259" t="s">
         <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>414</v>
-      </c>
-      <c r="F45" s="287" t="s">
+        <v>409</v>
+      </c>
+      <c r="F45" s="283" t="s">
         <v>59</v>
       </c>
     </row>
@@ -8989,7 +9106,7 @@
         <f>H29</f>
         <v>813801.8</v>
       </c>
-      <c r="F46" s="283"/>
+      <c r="F46" s="280"/>
     </row>
     <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
@@ -9004,23 +9121,23 @@
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
         <v>1.6698226477450393</v>
       </c>
-      <c r="F47" s="283"/>
+      <c r="F47" s="280"/>
     </row>
     <row r="48" spans="2:8" ht="15" customHeight="1">
-      <c r="F48" s="283"/>
+      <c r="F48" s="280"/>
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="158" t="s">
         <v>144</v>
       </c>
-      <c r="C49" s="262" t="s">
+      <c r="C49" s="260" t="s">
         <v>57</v>
       </c>
       <c r="D49" s="218" t="s">
         <v>96</v>
       </c>
       <c r="E49" s="2"/>
-      <c r="F49" s="283"/>
+      <c r="F49" s="280"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
@@ -9034,7 +9151,7 @@
         <f>G31/Normalized_FCF!G8</f>
         <v>0.55099965538864815</v>
       </c>
-      <c r="F50" s="283"/>
+      <c r="F50" s="280"/>
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
@@ -9045,22 +9162,22 @@
         <f>G29/G32</f>
         <v>0.71359494874005047</v>
       </c>
-      <c r="F51" s="283"/>
+      <c r="F51" s="280"/>
     </row>
     <row r="52" spans="2:8" ht="15" customHeight="1">
-      <c r="F52" s="283"/>
+      <c r="F52" s="280"/>
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="158" t="s">
         <v>143</v>
       </c>
-      <c r="C53" s="262" t="s">
+      <c r="C53" s="260" t="s">
         <v>57</v>
       </c>
       <c r="D53" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F53" s="283"/>
+      <c r="F53" s="280"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
@@ -9074,7 +9191,7 @@
         <f>Normalized_FCF!G8/G35</f>
         <v>0.274075324224895</v>
       </c>
-      <c r="F54" s="283"/>
+      <c r="F54" s="280"/>
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
@@ -9088,22 +9205,22 @@
         <f>Normalized_FCF!G11/G40</f>
         <v>0</v>
       </c>
-      <c r="F55" s="283"/>
+      <c r="F55" s="280"/>
     </row>
     <row r="56" spans="2:8" ht="15" customHeight="1">
-      <c r="F56" s="283"/>
+      <c r="F56" s="280"/>
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="158" t="s">
         <v>176</v>
       </c>
-      <c r="C57" s="262" t="s">
+      <c r="C57" s="260" t="s">
         <v>57</v>
       </c>
       <c r="D57" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F57" s="283"/>
+      <c r="F57" s="280"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
@@ -9125,22 +9242,22 @@
         <f>G39/G32</f>
         <v>0.1635967615610221</v>
       </c>
-      <c r="F59" s="283"/>
+      <c r="F59" s="280"/>
     </row>
     <row r="60" spans="2:8" ht="15" customHeight="1">
-      <c r="F60" s="283"/>
+      <c r="F60" s="280"/>
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="158" t="s">
         <v>275</v>
       </c>
-      <c r="C61" s="262" t="s">
+      <c r="C61" s="260" t="s">
         <v>138</v>
       </c>
       <c r="D61" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F61" s="283"/>
+      <c r="F61" s="280"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
@@ -9154,7 +9271,7 @@
         <f>G28/G29</f>
         <v>9.6426167603430037E-4</v>
       </c>
-      <c r="F62" s="283" t="s">
+      <c r="F62" s="280" t="s">
         <v>273</v>
       </c>
     </row>
@@ -9173,13 +9290,13 @@
       <c r="B65" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="C65" s="261" t="s">
+      <c r="C65" s="259" t="s">
         <v>137</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>292</v>
-      </c>
-      <c r="F65" s="287" t="s">
+        <v>288</v>
+      </c>
+      <c r="F65" s="283" t="s">
         <v>59</v>
       </c>
     </row>
@@ -9207,7 +9324,7 @@
         <f>G6+G16</f>
         <v>49155</v>
       </c>
-      <c r="F67" s="283"/>
+      <c r="F67" s="280"/>
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
@@ -9217,7 +9334,7 @@
         <f>G18</f>
         <v>0</v>
       </c>
-      <c r="F68" s="283"/>
+      <c r="F68" s="280"/>
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
@@ -9227,7 +9344,7 @@
         <f>G8+G20</f>
         <v>0</v>
       </c>
-      <c r="F69" s="283"/>
+      <c r="F69" s="280"/>
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
@@ -9237,26 +9354,26 @@
         <f>SUM(C66:C69)</f>
         <v>1138543</v>
       </c>
-      <c r="F70" s="283"/>
+      <c r="F70" s="280"/>
     </row>
     <row r="71" spans="2:6" ht="15" customHeight="1">
-      <c r="F71" s="283"/>
+      <c r="F71" s="280"/>
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
-      <c r="B72" s="285" t="s">
-        <v>326</v>
-      </c>
-      <c r="C72" s="261" t="s">
+      <c r="B72" s="282" t="s">
+        <v>321</v>
+      </c>
+      <c r="C72" s="259" t="s">
         <v>96</v>
       </c>
       <c r="D72" s="203" t="s">
         <v>57</v>
       </c>
-      <c r="F72" s="283"/>
+      <c r="F72" s="280"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -9267,65 +9384,65 @@
         <v>-251053.08995184439</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
-      <c r="B74" s="288" t="s">
-        <v>329</v>
-      </c>
-      <c r="C74" s="289">
+      <c r="B74" s="284" t="s">
+        <v>324</v>
+      </c>
+      <c r="C74" s="285">
         <f>-$C$66/C73</f>
         <v>3.9056455659498561</v>
       </c>
-      <c r="D74" s="289">
+      <c r="D74" s="285">
         <f>-$C$66/D73</f>
         <v>4.3392734190563456</v>
       </c>
-      <c r="F74" s="283" t="s">
-        <v>327</v>
+      <c r="F74" s="280" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
-        <v>328</v>
-      </c>
-      <c r="C75" s="293"/>
-      <c r="D75" s="292">
+        <v>323</v>
+      </c>
+      <c r="C75" s="289"/>
+      <c r="D75" s="288">
         <f>MAX(-D73*D76,G5)</f>
         <v>502106.17990368878</v>
       </c>
-      <c r="F75" s="283" t="s">
-        <v>360</v>
+      <c r="F75" s="280" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
-      <c r="B76" s="290" t="s">
-        <v>330</v>
-      </c>
-      <c r="C76" s="291"/>
-      <c r="D76" s="327">
+      <c r="B76" s="286" t="s">
+        <v>325</v>
+      </c>
+      <c r="C76" s="287"/>
+      <c r="D76" s="323">
         <f>IF(D74&lt;=3,1,IF(D74&gt;18,6,2))</f>
         <v>2</v>
       </c>
-      <c r="F76" s="283" t="s">
-        <v>331</v>
+      <c r="F76" s="280" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
-      <c r="F77" s="283"/>
+      <c r="F77" s="280"/>
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="C78" s="261" t="s">
+      <c r="C78" s="259" t="s">
         <v>137</v>
       </c>
       <c r="D78" s="204" t="s">
         <v>35</v>
       </c>
-      <c r="F78" s="283"/>
+      <c r="F78" s="280"/>
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
@@ -9339,7 +9456,7 @@
         <f>G7*H7+G17*H17</f>
         <v>6510.5999999999995</v>
       </c>
-      <c r="F79" s="283"/>
+      <c r="F79" s="280"/>
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
@@ -9353,7 +9470,7 @@
         <f>G19*H19</f>
         <v>8701.2000000000007</v>
       </c>
-      <c r="F80" s="283"/>
+      <c r="F80" s="280"/>
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
@@ -9367,7 +9484,7 @@
         <f>G9*H9+G21*H21</f>
         <v>3696.1000000000004</v>
       </c>
-      <c r="F81" s="283"/>
+      <c r="F81" s="280"/>
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
@@ -9381,11 +9498,11 @@
         <f>SUM(D79:D81)</f>
         <v>18907.900000000001</v>
       </c>
-      <c r="F82" s="283"/>
+      <c r="F82" s="280"/>
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9396,15 +9513,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
-        <v>296</v>
-      </c>
-      <c r="D85" s="270" t="s">
-        <v>297</v>
+        <v>292</v>
+      </c>
+      <c r="D85" s="268" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
-      <c r="B86" s="267" t="s">
-        <v>293</v>
+      <c r="B86" s="265" t="s">
+        <v>289</v>
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
@@ -9414,14 +9531,14 @@
         <f>C86*scaling_factor/Common_Shares</f>
         <v>-0.40025178686632773</v>
       </c>
-      <c r="E86" s="269" t="str">
+      <c r="E86" s="267" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
-      <c r="B87" s="267" t="s">
-        <v>294</v>
+      <c r="B87" s="265" t="s">
+        <v>290</v>
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
@@ -9431,13 +9548,13 @@
         <f>C87*scaling_factor/Common_Shares</f>
         <v>1.2050311068441337</v>
       </c>
-      <c r="E87" s="269" t="str">
+      <c r="E87" s="267" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1">
-      <c r="B88" s="268" t="s">
+      <c r="B88" s="266" t="s">
         <v>190</v>
       </c>
       <c r="C88" s="188">
@@ -9448,24 +9565,24 @@
         <f>C88*scaling_factor/Common_Shares</f>
         <v>3.8796718858693152E-2</v>
       </c>
-      <c r="E88" s="269" t="str">
+      <c r="E88" s="267" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
         <v>411123.72009631118</v>
       </c>
-      <c r="D89" s="271">
+      <c r="D89" s="269">
         <f>SUM(D86:D88)</f>
         <v>0.84357603883649912</v>
       </c>
-      <c r="E89" s="269" t="str">
+      <c r="E89" s="267" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
@@ -9484,22 +9601,22 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="1.265625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.265625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.73046875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="2.73046875" style="2" customWidth="1"/>
     <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
-    <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
-    <col min="18" max="16384" width="12.33203125" style="2"/>
+    <col min="6" max="6" width="2.73046875" style="2" customWidth="1"/>
+    <col min="7" max="17" width="20.73046875" style="2" customWidth="1"/>
+    <col min="18" max="16384" width="12.265625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
-        <f>Thesis!C22</f>
+        <f>Thesis!C25</f>
         <v>HKD</v>
       </c>
       <c r="C1" s="53" t="s">
@@ -9586,7 +9703,7 @@
         <v>1000</v>
       </c>
       <c r="D3" s="9"/>
-      <c r="E3" s="302"/>
+      <c r="E3" s="298"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
@@ -9600,7 +9717,7 @@
         <v>3149204.111111111</v>
       </c>
       <c r="D4" s="57"/>
-      <c r="E4" s="300"/>
+      <c r="E4" s="296"/>
       <c r="F4" s="57"/>
       <c r="G4" s="183">
         <f>Data!C36</f>
@@ -9656,7 +9773,7 @@
         <f>C25</f>
         <v>-2697049.2267501326</v>
       </c>
-      <c r="E5" s="302"/>
+      <c r="E5" s="298"/>
       <c r="G5" s="183">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
         <v>-3031530</v>
@@ -9711,7 +9828,7 @@
         <f>C4+C5</f>
         <v>452154.88436097838</v>
       </c>
-      <c r="E6" s="302"/>
+      <c r="E6" s="298"/>
       <c r="G6" s="184">
         <f>IF(G4="","",G4+G5)</f>
         <v>607228</v>
@@ -9766,7 +9883,7 @@
         <f>C35</f>
         <v>-253206</v>
       </c>
-      <c r="E7" s="302"/>
+      <c r="E7" s="298"/>
       <c r="G7" s="191">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
         <v>-253206</v>
@@ -9822,7 +9939,7 @@
         <v>198948.88436097838</v>
       </c>
       <c r="D8" s="59"/>
-      <c r="E8" s="308"/>
+      <c r="E8" s="304"/>
       <c r="F8" s="59"/>
       <c r="G8" s="184">
         <f>IF(G$4="","",G6+G7)</f>
@@ -9878,7 +9995,7 @@
         <f>BS!$G$39*BS!D58</f>
         <v>0</v>
       </c>
-      <c r="E9" s="302"/>
+      <c r="E9" s="298"/>
       <c r="G9" s="191">
         <f>IF(Data!C61="","",-Data!C61)</f>
         <v>0</v>
@@ -9933,7 +10050,7 @@
         <f>-C4*C78</f>
         <v>0</v>
       </c>
-      <c r="E10" s="302"/>
+      <c r="E10" s="298"/>
       <c r="G10" s="191">
         <f>Data!C62</f>
         <v>0</v>
@@ -9989,7 +10106,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="169"/>
-      <c r="E11" s="301"/>
+      <c r="E11" s="297"/>
       <c r="F11" s="169"/>
       <c r="G11" s="186">
         <f>G61</f>
@@ -10045,7 +10162,7 @@
         <f>C50</f>
         <v>-13663</v>
       </c>
-      <c r="E12" s="302"/>
+      <c r="E12" s="298"/>
       <c r="G12" s="191">
         <f>G50</f>
         <v>-13663</v>
@@ -10100,7 +10217,7 @@
         <f>SUM(C8:C12)</f>
         <v>185285.88436097838</v>
       </c>
-      <c r="E13" s="302"/>
+      <c r="E13" s="298"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
         <v>340359</v>
@@ -10155,7 +10272,7 @@
         <f>-SUM(C8+C11,C12)*C43</f>
         <v>-46321.471090244595</v>
       </c>
-      <c r="E14" s="302"/>
+      <c r="E14" s="298"/>
       <c r="G14" s="191">
         <f>Data!C46</f>
         <v>-145324</v>
@@ -10211,7 +10328,7 @@
         <v>-572.93535914055167</v>
       </c>
       <c r="D15" s="60"/>
-      <c r="E15" s="309"/>
+      <c r="E15" s="305"/>
       <c r="F15" s="60"/>
       <c r="G15" s="183">
         <f>Data!C48</f>
@@ -10268,7 +10385,7 @@
         <v>138391.47791159325</v>
       </c>
       <c r="D16" s="61"/>
-      <c r="E16" s="310"/>
+      <c r="E16" s="306"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
@@ -10325,8 +10442,8 @@
         <v>0</v>
       </c>
       <c r="D17" s="58"/>
-      <c r="E17" s="301" t="s">
-        <v>339</v>
+      <c r="E17" s="297" t="s">
+        <v>334</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -10350,8 +10467,8 @@
         <v>0</v>
       </c>
       <c r="D18" s="58"/>
-      <c r="E18" s="301" t="s">
-        <v>340</v>
+      <c r="E18" s="297" t="s">
+        <v>335</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10376,7 +10493,7 @@
         <v>138391.47791159325</v>
       </c>
       <c r="D19" s="27"/>
-      <c r="E19" s="299"/>
+      <c r="E19" s="295"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
@@ -10472,7 +10589,7 @@
       </c>
       <c r="C22" s="62"/>
       <c r="D22" s="27"/>
-      <c r="E22" s="299"/>
+      <c r="E22" s="295"/>
       <c r="F22" s="27"/>
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
@@ -10496,7 +10613,7 @@
         <v>-2226669.2968957396</v>
       </c>
       <c r="D23" s="58"/>
-      <c r="E23" s="301"/>
+      <c r="E23" s="297"/>
       <c r="F23" s="58"/>
       <c r="G23" s="183">
         <f>Data!C37</f>
@@ -10553,7 +10670,7 @@
         <v>-470379.92985439295</v>
       </c>
       <c r="D24" s="27"/>
-      <c r="E24" s="299"/>
+      <c r="E24" s="295"/>
       <c r="F24" s="27"/>
       <c r="G24" s="183">
         <f>Data!C40</f>
@@ -10610,7 +10727,7 @@
         <v>-2697049.2267501326</v>
       </c>
       <c r="D25" s="9"/>
-      <c r="E25" s="307"/>
+      <c r="E25" s="303"/>
       <c r="F25" s="9"/>
       <c r="G25" s="184">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
@@ -10659,14 +10776,14 @@
     </row>
     <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
-      <c r="E26" s="302"/>
+      <c r="E26" s="298"/>
     </row>
     <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>207</v>
       </c>
-      <c r="E27" s="302"/>
+      <c r="E27" s="298"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
@@ -10678,8 +10795,8 @@
         <v>0.70705778931239871</v>
       </c>
       <c r="D28" s="26"/>
-      <c r="E28" s="300" t="s">
-        <v>341</v>
+      <c r="E28" s="296" t="s">
+        <v>336</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10738,8 +10855,8 @@
         <v>0.14936470081274986</v>
       </c>
       <c r="D29" s="26"/>
-      <c r="E29" s="300" t="s">
-        <v>341</v>
+      <c r="E29" s="296" t="s">
+        <v>336</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10796,7 +10913,7 @@
         <f>ABS(C25/$C$4)</f>
         <v>0.85642249012514848</v>
       </c>
-      <c r="E30" s="302"/>
+      <c r="E30" s="298"/>
       <c r="G30" s="30">
         <f t="shared" ref="G30:Q30" si="13">IF(G$4="","",ABS(G25/G$4))</f>
         <v>0.83312218070011801</v>
@@ -10844,14 +10961,14 @@
     </row>
     <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
-      <c r="E31" s="302"/>
+      <c r="E31" s="298"/>
     </row>
     <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="E32" s="302"/>
+      <c r="E32" s="298"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
@@ -10862,8 +10979,8 @@
         <f>G33</f>
         <v>-253206</v>
       </c>
-      <c r="E33" s="300" t="s">
-        <v>341</v>
+      <c r="E33" s="296" t="s">
+        <v>336</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -10920,8 +11037,8 @@
         <v>0</v>
       </c>
       <c r="D34" s="58"/>
-      <c r="E34" s="300" t="s">
-        <v>341</v>
+      <c r="E34" s="296" t="s">
+        <v>336</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -10979,7 +11096,7 @@
         <v>-253206</v>
       </c>
       <c r="D35" s="58"/>
-      <c r="E35" s="301"/>
+      <c r="E35" s="297"/>
       <c r="F35" s="58"/>
       <c r="G35" s="184">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
@@ -11028,14 +11145,14 @@
     </row>
     <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
-      <c r="E36" s="302"/>
+      <c r="E36" s="298"/>
     </row>
     <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>208</v>
       </c>
-      <c r="E37" s="302"/>
+      <c r="E37" s="298"/>
     </row>
     <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
@@ -11048,7 +11165,7 @@
         <v>8.0403172060722089E-2</v>
       </c>
       <c r="D38" s="27"/>
-      <c r="E38" s="299"/>
+      <c r="E38" s="295"/>
       <c r="F38" s="27"/>
       <c r="G38" s="13">
         <f t="shared" ref="G38:Q38" si="15">IF(G$4="","",ABS(G33/G$4))</f>
@@ -11106,7 +11223,7 @@
         <v>0</v>
       </c>
       <c r="D39" s="27"/>
-      <c r="E39" s="299"/>
+      <c r="E39" s="295"/>
       <c r="F39" s="27"/>
       <c r="G39" s="13">
         <f t="shared" ref="G39:Q39" si="16">IF(G$4="","",ABS(G34/G$4))</f>
@@ -11162,7 +11279,7 @@
         <f>ABS(C35/$C$4)</f>
         <v>8.0403172060722089E-2</v>
       </c>
-      <c r="E40" s="302"/>
+      <c r="E40" s="298"/>
       <c r="G40" s="30">
         <f t="shared" ref="G40:Q40" si="17">IF(G$4="","",ABS(G35/G$4))</f>
         <v>6.9585831209440147E-2</v>
@@ -11210,26 +11327,26 @@
     </row>
     <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
-      <c r="E41" s="302"/>
+      <c r="E41" s="298"/>
     </row>
     <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>209</v>
       </c>
-      <c r="E42" s="302"/>
+      <c r="E42" s="298"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>172</v>
       </c>
-      <c r="C43" s="296">
+      <c r="C43" s="292">
         <v>0.25</v>
       </c>
       <c r="D43" s="27"/>
-      <c r="E43" s="299" t="s">
-        <v>342</v>
+      <c r="E43" s="295" t="s">
+        <v>337</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -11308,7 +11425,7 @@
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
-      <c r="E46" s="302"/>
+      <c r="E46" s="298"/>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
@@ -11319,7 +11436,7 @@
         <f>-BS!G31*Normalized_FCF!C54</f>
         <v>-13663</v>
       </c>
-      <c r="E47" s="302"/>
+      <c r="E47" s="298"/>
       <c r="G47" s="191">
         <f>Data!C51</f>
         <v>-13663</v>
@@ -11368,111 +11485,111 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
         <v>0</v>
       </c>
-      <c r="E48" s="302"/>
-      <c r="G48" s="328">
+      <c r="E48" s="298"/>
+      <c r="G48" s="324">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>0</v>
       </c>
-      <c r="H48" s="328">
+      <c r="H48" s="324">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v>0</v>
       </c>
-      <c r="I48" s="328">
+      <c r="I48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="J48" s="328">
+      <c r="J48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="K48" s="328">
+      <c r="K48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="L48" s="328">
+      <c r="L48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="M48" s="328">
+      <c r="M48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="N48" s="328">
+      <c r="N48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="O48" s="328">
+      <c r="O48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="P48" s="328" t="str">
+      <c r="P48" s="324" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="Q48" s="328" t="str">
+      <c r="Q48" s="324" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
-      <c r="B49" s="323" t="s">
-        <v>350</v>
-      </c>
-      <c r="C49" s="324">
+      <c r="B49" s="319" t="s">
+        <v>345</v>
+      </c>
+      <c r="C49" s="320">
         <f>BS!$C$66*C53</f>
         <v>0</v>
       </c>
-      <c r="D49" s="325"/>
-      <c r="E49" s="326"/>
-      <c r="F49" s="325"/>
-      <c r="G49" s="324">
+      <c r="D49" s="321"/>
+      <c r="E49" s="322"/>
+      <c r="F49" s="321"/>
+      <c r="G49" s="320">
         <f>Data!C52</f>
         <v>0</v>
       </c>
-      <c r="H49" s="324">
+      <c r="H49" s="320">
         <f>Data!D52</f>
         <v>0</v>
       </c>
-      <c r="I49" s="324">
+      <c r="I49" s="320">
         <f>Data!E52</f>
         <v>0</v>
       </c>
-      <c r="J49" s="324">
+      <c r="J49" s="320">
         <f>Data!F52</f>
         <v>0</v>
       </c>
-      <c r="K49" s="324">
+      <c r="K49" s="320">
         <f>Data!G52</f>
         <v>0</v>
       </c>
-      <c r="L49" s="324">
+      <c r="L49" s="320">
         <f>Data!H52</f>
         <v>0</v>
       </c>
-      <c r="M49" s="324">
+      <c r="M49" s="320">
         <f>Data!I52</f>
         <v>0</v>
       </c>
-      <c r="N49" s="324">
+      <c r="N49" s="320">
         <f>Data!J52</f>
         <v>0</v>
       </c>
-      <c r="O49" s="324">
+      <c r="O49" s="320">
         <f>Data!K52</f>
         <v>0</v>
       </c>
-      <c r="P49" s="324" t="str">
+      <c r="P49" s="320" t="str">
         <f>Data!L52</f>
         <v/>
       </c>
-      <c r="Q49" s="324" t="str">
+      <c r="Q49" s="320" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -11486,7 +11603,7 @@
         <f>C47+C48</f>
         <v>-13663</v>
       </c>
-      <c r="E50" s="302"/>
+      <c r="E50" s="298"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
         <v>-13663</v>
@@ -11534,14 +11651,14 @@
     </row>
     <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
-      <c r="E51" s="302"/>
+      <c r="E51" s="298"/>
     </row>
     <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>156</v>
       </c>
-      <c r="E52" s="302"/>
+      <c r="E52" s="298"/>
       <c r="G52" s="97" t="s">
         <v>220</v>
       </c>
@@ -11555,8 +11672,8 @@
         <f>G53</f>
         <v>0</v>
       </c>
-      <c r="E53" s="299" t="s">
-        <v>343</v>
+      <c r="E53" s="295" t="s">
+        <v>338</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11582,8 +11699,8 @@
         <f>G54</f>
         <v>7.0042959818728018E-2</v>
       </c>
-      <c r="E54" s="299" t="s">
-        <v>344</v>
+      <c r="E54" s="295" t="s">
+        <v>339</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11609,7 +11726,7 @@
         <f>-C8/C47</f>
         <v>14.561142088924715</v>
       </c>
-      <c r="E55" s="302"/>
+      <c r="E55" s="298"/>
       <c r="G55" s="42">
         <f t="shared" ref="G55:Q55" si="21">IF(G4="","",-G8/G47)</f>
         <v>25.911000512332578</v>
@@ -11657,14 +11774,14 @@
     </row>
     <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
-      <c r="E56" s="302"/>
+      <c r="E56" s="298"/>
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>169</v>
       </c>
-      <c r="E57" s="302"/>
+      <c r="E57" s="298"/>
       <c r="G57" s="97" t="s">
         <v>220</v>
       </c>
@@ -11678,7 +11795,7 @@
         <f>BS!$C67*C66</f>
         <v>0</v>
       </c>
-      <c r="E58" s="302"/>
+      <c r="E58" s="298"/>
       <c r="G58" s="191">
         <f>Data!C56</f>
         <v>0</v>
@@ -11733,7 +11850,7 @@
         <f>BS!$C68*C67</f>
         <v>0</v>
       </c>
-      <c r="E59" s="302"/>
+      <c r="E59" s="298"/>
       <c r="G59" s="191">
         <f>Data!C55</f>
         <v>0</v>
@@ -11788,7 +11905,7 @@
         <f>BS!$C69*C68</f>
         <v>0</v>
       </c>
-      <c r="E60" s="302"/>
+      <c r="E60" s="298"/>
       <c r="G60" s="191">
         <f>Data!C57</f>
         <v>0</v>
@@ -11843,7 +11960,7 @@
         <f>SUM(C58:C60)</f>
         <v>0</v>
       </c>
-      <c r="E61" s="302"/>
+      <c r="E61" s="298"/>
       <c r="G61" s="184">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
         <v>0</v>
@@ -11894,11 +12011,11 @@
       <c r="B62" s="40" t="s">
         <v>161</v>
       </c>
-      <c r="C62" s="297">
-        <v>0</v>
-      </c>
-      <c r="E62" s="300" t="s">
-        <v>345</v>
+      <c r="C62" s="293">
+        <v>0</v>
+      </c>
+      <c r="E62" s="296" t="s">
+        <v>340</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -11954,7 +12071,7 @@
         <f>C61+C62</f>
         <v>0</v>
       </c>
-      <c r="E63" s="302"/>
+      <c r="E63" s="298"/>
       <c r="G63" s="184">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
         <v>56115</v>
@@ -12002,14 +12119,14 @@
     </row>
     <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
-      <c r="E64" s="302"/>
+      <c r="E64" s="298"/>
     </row>
     <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>170</v>
       </c>
-      <c r="E65" s="302"/>
+      <c r="E65" s="298"/>
       <c r="G65" s="97" t="s">
         <v>220</v>
       </c>
@@ -12023,7 +12140,7 @@
         <f>G66</f>
         <v>0</v>
       </c>
-      <c r="E66" s="302"/>
+      <c r="E66" s="298"/>
       <c r="G66" s="23">
         <f>IFERROR(G58/BS!$C$67,0)</f>
         <v>0</v>
@@ -12048,7 +12165,7 @@
         <f>G67</f>
         <v>0</v>
       </c>
-      <c r="E67" s="302"/>
+      <c r="E67" s="298"/>
       <c r="G67" s="23">
         <f>IFERROR(G59/BS!$C$68,0)</f>
         <v>0</v>
@@ -12073,7 +12190,7 @@
         <f>G68</f>
         <v>0</v>
       </c>
-      <c r="E68" s="302"/>
+      <c r="E68" s="298"/>
       <c r="G68" s="23">
         <f>IFERROR(G60/BS!$C$69,0)</f>
         <v>0</v>
@@ -12099,7 +12216,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="9"/>
-      <c r="E69" s="307"/>
+      <c r="E69" s="303"/>
       <c r="F69" s="9"/>
       <c r="G69" s="71">
         <f>G61/BS!C70</f>
@@ -12127,7 +12244,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12149,7 +12266,7 @@
       </c>
       <c r="C72" s="62"/>
       <c r="D72" s="27"/>
-      <c r="E72" s="299"/>
+      <c r="E72" s="295"/>
       <c r="F72" s="27"/>
       <c r="G72" s="97"/>
       <c r="H72" s="12"/>
@@ -12173,7 +12290,7 @@
         <v>0.85642249012514848</v>
       </c>
       <c r="D73" s="27"/>
-      <c r="E73" s="299"/>
+      <c r="E73" s="295"/>
       <c r="F73" s="27"/>
       <c r="G73" s="6">
         <f t="shared" ref="G73:Q73" si="24">IF(G$4="","",ABS(G5/G$4))</f>
@@ -12230,7 +12347,7 @@
         <v>0.14357750987485146</v>
       </c>
       <c r="D74" s="27"/>
-      <c r="E74" s="299"/>
+      <c r="E74" s="295"/>
       <c r="F74" s="27"/>
       <c r="G74" s="65">
         <f t="shared" ref="G74:Q74" si="25">IF(G$4="","",ABS(G6/G$4))</f>
@@ -12287,7 +12404,7 @@
         <v>8.0403172060722089E-2</v>
       </c>
       <c r="D75" s="27"/>
-      <c r="E75" s="299"/>
+      <c r="E75" s="295"/>
       <c r="F75" s="27"/>
       <c r="G75" s="6">
         <f t="shared" ref="G75:Q75" si="26">IF(G$4="","",ABS(G7/G$4))</f>
@@ -12344,7 +12461,7 @@
         <v>6.3174337814129386E-2</v>
       </c>
       <c r="D76" s="27"/>
-      <c r="E76" s="299"/>
+      <c r="E76" s="295"/>
       <c r="F76" s="27"/>
       <c r="G76" s="65">
         <f t="shared" ref="G76:Q76" si="27">IF(G$4="","",ABS(G8/G$4))</f>
@@ -12401,7 +12518,7 @@
         <v>0</v>
       </c>
       <c r="D77" s="27"/>
-      <c r="E77" s="299"/>
+      <c r="E77" s="295"/>
       <c r="F77" s="27"/>
       <c r="G77" s="6">
         <f t="shared" ref="G77:Q77" si="28">IF(G$4="","",G9/G$4)</f>
@@ -12458,8 +12575,8 @@
         <v>0</v>
       </c>
       <c r="D78" s="27"/>
-      <c r="E78" s="300" t="s">
-        <v>442</v>
+      <c r="E78" s="296" t="s">
+        <v>452</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12517,7 +12634,7 @@
         <v>0</v>
       </c>
       <c r="D79" s="27"/>
-      <c r="E79" s="299"/>
+      <c r="E79" s="295"/>
       <c r="F79" s="27"/>
       <c r="G79" s="65">
         <f t="shared" ref="G79:Q79" si="30">IF(G$4="","",G11/G$4)</f>
@@ -12574,7 +12691,7 @@
         <v>4.3385565107684878E-3</v>
       </c>
       <c r="D80" s="27"/>
-      <c r="E80" s="299"/>
+      <c r="E80" s="295"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
@@ -12631,7 +12748,7 @@
         <v>5.8835781303360896E-2</v>
       </c>
       <c r="D81" s="27"/>
-      <c r="E81" s="299"/>
+      <c r="E81" s="295"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
@@ -12688,7 +12805,7 @@
         <v>1.4708945325840224E-2</v>
       </c>
       <c r="D82" s="27"/>
-      <c r="E82" s="299"/>
+      <c r="E82" s="295"/>
       <c r="F82" s="27"/>
       <c r="G82" s="6">
         <f t="shared" ref="G82:Q82" si="33">IF(G$4="","",ABS(G14/G$4))</f>
@@ -12741,12 +12858,12 @@
         <f>B15</f>
         <v>NCI’s Share of Profits</v>
       </c>
-      <c r="C83" s="298">
+      <c r="C83" s="294">
         <f>MIN(BS!C62,MAX(G83:K83))</f>
         <v>1.819302080545065E-4</v>
       </c>
       <c r="D83" s="27"/>
-      <c r="E83" s="299"/>
+      <c r="E83" s="295"/>
       <c r="F83" s="27"/>
       <c r="G83" s="6">
         <f t="shared" ref="G83:Q83" si="34">IF(G$4="","",-G15/G$4)</f>
@@ -12803,7 +12920,7 @@
         <v>4.3944905769466171E-2</v>
       </c>
       <c r="D84" s="27"/>
-      <c r="E84" s="299"/>
+      <c r="E84" s="295"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
@@ -12855,26 +12972,26 @@
       <c r="B85" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C85" s="298">
+      <c r="C85" s="294">
         <v>0</v>
       </c>
       <c r="D85" s="27"/>
-      <c r="E85" s="301" t="str">
+      <c r="E85" s="297" t="str">
         <f>E17</f>
         <v>WCInv is by default excluded</v>
       </c>
       <c r="F85" s="27"/>
-      <c r="G85" s="253"/>
-      <c r="H85" s="253"/>
-      <c r="I85" s="253"/>
-      <c r="J85" s="253"/>
-      <c r="K85" s="253"/>
-      <c r="L85" s="253"/>
-      <c r="M85" s="253"/>
-      <c r="N85" s="253"/>
-      <c r="O85" s="253"/>
-      <c r="P85" s="253"/>
-      <c r="Q85" s="253"/>
+      <c r="G85" s="251"/>
+      <c r="H85" s="251"/>
+      <c r="I85" s="251"/>
+      <c r="J85" s="251"/>
+      <c r="K85" s="251"/>
+      <c r="L85" s="251"/>
+      <c r="M85" s="251"/>
+      <c r="N85" s="251"/>
+      <c r="O85" s="251"/>
+      <c r="P85" s="251"/>
+      <c r="Q85" s="251"/>
     </row>
     <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
@@ -12884,7 +13001,7 @@
       <c r="C86" s="77">
         <v>0</v>
       </c>
-      <c r="E86" s="301" t="str">
+      <c r="E86" s="297" t="str">
         <f>E18</f>
         <v>Net borrowing is excluded</v>
       </c>
@@ -12910,7 +13027,7 @@
         <v>4.3944905769466171E-2</v>
       </c>
       <c r="D87" s="75"/>
-      <c r="E87" s="299"/>
+      <c r="E87" s="295"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
@@ -12959,14 +13076,14 @@
     </row>
     <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
-      <c r="E88" s="302"/>
+      <c r="E88" s="298"/>
     </row>
     <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>215</v>
       </c>
-      <c r="E89" s="302"/>
+      <c r="E89" s="298"/>
     </row>
     <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
@@ -12978,7 +13095,7 @@
         <f>G90</f>
         <v>0.128</v>
       </c>
-      <c r="E90" s="302"/>
+      <c r="E90" s="298"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
         <v>0.128</v>
@@ -13034,7 +13151,7 @@
         <f>C90*Common_Shares/scaling_factor</f>
         <v>62381.852672000001</v>
       </c>
-      <c r="E91" s="302"/>
+      <c r="E91" s="298"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
         <v>62381.852672000001</v>
@@ -13089,7 +13206,7 @@
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
         <v>0.45076368583801485</v>
       </c>
-      <c r="E92" s="302"/>
+      <c r="E92" s="298"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
         <v>0.32093887871257842</v>
@@ -13138,13 +13255,13 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
         <v>3.5854341736694682E-2</v>
       </c>
-      <c r="E93" s="302"/>
+      <c r="E93" s="298"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
         <v>3.5854341736694682E-2</v>
@@ -13192,7 +13309,7 @@
     </row>
     <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
-      <c r="E94" s="302"/>
+      <c r="E94" s="298"/>
     </row>
     <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
@@ -13201,7 +13318,7 @@
       </c>
       <c r="C95" s="62"/>
       <c r="D95" s="27"/>
-      <c r="E95" s="299"/>
+      <c r="E95" s="295"/>
       <c r="F95" s="27"/>
       <c r="G95" s="12"/>
       <c r="H95" s="12"/>
@@ -13225,7 +13342,7 @@
         <v>-0.13453873241608505</v>
       </c>
       <c r="D96" s="27"/>
-      <c r="E96" s="299"/>
+      <c r="E96" s="295"/>
       <c r="F96" s="27"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H4="","",G4/H4-1)</f>
@@ -13282,7 +13399,7 @@
         <v>-0.45561632170449917</v>
       </c>
       <c r="D97" s="27"/>
-      <c r="E97" s="299"/>
+      <c r="E97" s="295"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
@@ -13360,7 +13477,7 @@
       <c r="B100" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="E100" s="302"/>
+      <c r="E100" s="298"/>
       <c r="G100" s="97" t="s">
         <v>220</v>
       </c>
@@ -13375,7 +13492,7 @@
         <v>2565063</v>
       </c>
       <c r="D101" s="26"/>
-      <c r="E101" s="303"/>
+      <c r="E101" s="299"/>
       <c r="F101" s="26"/>
       <c r="G101" s="183">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
@@ -13432,7 +13549,7 @@
         <v>348607</v>
       </c>
       <c r="D102" s="89"/>
-      <c r="E102" s="304"/>
+      <c r="E102" s="300"/>
       <c r="F102" s="89"/>
       <c r="G102" s="185">
         <f>IF(G$4="","",Data!D77)</f>
@@ -13489,7 +13606,7 @@
         <v>506592</v>
       </c>
       <c r="D103" s="89"/>
-      <c r="E103" s="304"/>
+      <c r="E103" s="300"/>
       <c r="F103" s="89"/>
       <c r="G103" s="185">
         <f>IF(G$4="","",Data!D78)</f>
@@ -13546,7 +13663,7 @@
         <v>732882</v>
       </c>
       <c r="D104" s="26"/>
-      <c r="E104" s="303"/>
+      <c r="E104" s="299"/>
       <c r="F104" s="26"/>
       <c r="G104" s="183">
         <f>Data!C79</f>
@@ -13603,7 +13720,7 @@
         <v>1832181</v>
       </c>
       <c r="D105" s="26"/>
-      <c r="E105" s="303"/>
+      <c r="E105" s="299"/>
       <c r="F105" s="26"/>
       <c r="G105" s="183">
         <f>Data!C80</f>
@@ -13652,7 +13769,7 @@
     </row>
     <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
-      <c r="E106" s="302"/>
+      <c r="E106" s="298"/>
     </row>
     <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
@@ -13661,7 +13778,7 @@
       </c>
       <c r="C107" s="26"/>
       <c r="D107" s="26"/>
-      <c r="E107" s="303"/>
+      <c r="E107" s="299"/>
       <c r="F107" s="26"/>
       <c r="G107" s="97" t="s">
         <v>220</v>
@@ -13687,7 +13804,7 @@
         <v>0.110696857904521</v>
       </c>
       <c r="D108" s="26"/>
-      <c r="E108" s="303"/>
+      <c r="E108" s="299"/>
       <c r="F108" s="26"/>
       <c r="G108" s="94">
         <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
@@ -13744,7 +13861,7 @@
         <v>0.16086350142012953</v>
       </c>
       <c r="D109" s="26"/>
-      <c r="E109" s="303"/>
+      <c r="E109" s="299"/>
       <c r="F109" s="26"/>
       <c r="G109" s="94">
         <f t="shared" ref="G109:Q109" si="44">IF(G$4="","",G103/G$4)</f>
@@ -13801,7 +13918,7 @@
         <v>0</v>
       </c>
       <c r="D110" s="26"/>
-      <c r="E110" s="303"/>
+      <c r="E110" s="299"/>
       <c r="F110" s="26"/>
       <c r="G110" s="94">
         <f>BS!$G$38/G$4</f>
@@ -13820,63 +13937,63 @@
     </row>
     <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
-      <c r="E111" s="302"/>
+      <c r="E111" s="298"/>
     </row>
     <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="E112" s="302"/>
+      <c r="E112" s="298"/>
     </row>
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="C113" s="170"/>
-      <c r="E113" s="302"/>
-      <c r="G113" s="334">
+      <c r="E113" s="298"/>
+      <c r="G113" s="329">
         <f>IF(G$4="","",Data!C$22/Data!C15)</f>
         <v>1.3815926737009756</v>
       </c>
-      <c r="H113" s="334">
+      <c r="H113" s="329">
         <f>IF(H$4="","",Data!D$22/Data!D15)</f>
         <v>1.4278840297234743</v>
       </c>
-      <c r="I113" s="334">
+      <c r="I113" s="329">
         <f>IF(I$4="","",Data!E$22/Data!E15)</f>
         <v>2.018494335713656</v>
       </c>
-      <c r="J113" s="334">
+      <c r="J113" s="329">
         <f>IF(J$4="","",Data!F$22/Data!F15)</f>
         <v>2.7662579957356077</v>
       </c>
-      <c r="K113" s="334">
+      <c r="K113" s="329">
         <f>IF(K$4="","",Data!G$22/Data!G15)</f>
         <v>3.0919089083736089</v>
       </c>
-      <c r="L113" s="334">
+      <c r="L113" s="329">
         <f>IF(L$4="","",Data!H$22/Data!H15)</f>
         <v>1.9543752128021792</v>
       </c>
-      <c r="M113" s="334">
+      <c r="M113" s="329">
         <f>IF(M$4="","",Data!I$22/Data!I15)</f>
         <v>3.6274434870389731</v>
       </c>
-      <c r="N113" s="334">
+      <c r="N113" s="329">
         <f>IF(N$4="","",Data!J$22/Data!J15)</f>
         <v>16.560663477666647</v>
       </c>
-      <c r="O113" s="334">
+      <c r="O113" s="329">
         <f>IF(O$4="","",Data!K$22/Data!K15)</f>
         <v>-12.951392854876579</v>
       </c>
-      <c r="P113" s="334" t="str">
+      <c r="P113" s="329" t="str">
         <f>IF(P$4="","",Data!L$22/Data!L15)</f>
         <v/>
       </c>
-      <c r="Q113" s="334" t="str">
+      <c r="Q113" s="329" t="str">
         <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
         <v/>
       </c>
@@ -13884,58 +14001,58 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="C114" s="170"/>
-      <c r="E114" s="302"/>
-      <c r="G114" s="334">
+      <c r="E114" s="298"/>
+      <c r="G114" s="329">
         <f>IF(G$4="","",Data!C$22/G19)</f>
         <v>1.7851604903973288</v>
       </c>
-      <c r="H114" s="334">
+      <c r="H114" s="329">
         <f>IF(H$4="","",Data!D$22/H19)</f>
         <v>1.6914819417164388</v>
       </c>
-      <c r="I114" s="334">
+      <c r="I114" s="329">
         <f>IF(I$4="","",Data!E$22/I19)</f>
         <v>2.7239958805355302</v>
       </c>
-      <c r="J114" s="334">
+      <c r="J114" s="329">
         <f>IF(J$4="","",Data!F$22/J19)</f>
         <v>3.4716681862567911</v>
       </c>
-      <c r="K114" s="334">
+      <c r="K114" s="329">
         <f>IF(K$4="","",Data!G$22/K19)</f>
         <v>2.7106236178681997</v>
       </c>
-      <c r="L114" s="334">
+      <c r="L114" s="329">
         <f>IF(L$4="","",Data!H$22/L19)</f>
         <v>2.6053869257438653</v>
       </c>
-      <c r="M114" s="334">
+      <c r="M114" s="329">
         <f>IF(M$4="","",Data!I$22/M19)</f>
         <v>5.1767562950843287</v>
       </c>
-      <c r="N114" s="334">
+      <c r="N114" s="329">
         <f>IF(N$4="","",Data!J$22/N19)</f>
         <v>-40.213757731181175</v>
       </c>
-      <c r="O114" s="334">
+      <c r="O114" s="329">
         <f>IF(O$4="","",Data!K$22/O19)</f>
         <v>-3.6225373611160414</v>
       </c>
-      <c r="P114" s="334" t="str">
+      <c r="P114" s="329" t="str">
         <f>IF(P$4="","",Data!L$22/P19)</f>
         <v/>
       </c>
-      <c r="Q114" s="334" t="str">
+      <c r="Q114" s="329" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
         <v/>
       </c>
     </row>
     <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
-      <c r="E115" s="302"/>
+      <c r="E115" s="298"/>
     </row>
     <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
@@ -13944,7 +14061,7 @@
       </c>
       <c r="C116" s="55"/>
       <c r="D116" s="55"/>
-      <c r="E116" s="305"/>
+      <c r="E116" s="301"/>
       <c r="F116" s="55"/>
       <c r="G116" s="23" t="str">
         <f>IFERROR(IF(#REF!*G118*(1/#REF!)=G120,"","Error"),"")</f>
@@ -14000,7 +14117,7 @@
         <f>C81</f>
         <v>5.8835781303360896E-2</v>
       </c>
-      <c r="E117" s="302"/>
+      <c r="E117" s="298"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
         <v>9.3537135473147709E-2</v>
@@ -14054,7 +14171,7 @@
         <f>C4/C101</f>
         <v>1.2277297326073906</v>
       </c>
-      <c r="E118" s="302"/>
+      <c r="E118" s="298"/>
       <c r="G118" s="42">
         <f t="shared" ref="G118:Q118" si="46">IF(G4="","",G4/G101)</f>
         <v>1.4185842608933972</v>
@@ -14109,7 +14226,7 @@
         <v>1.4000052396569989</v>
       </c>
       <c r="D119" s="11"/>
-      <c r="E119" s="306"/>
+      <c r="E119" s="302"/>
       <c r="F119" s="11"/>
       <c r="G119" s="15">
         <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G101/G105)</f>
@@ -14166,7 +14283,7 @@
         <v>0.10858582441416999</v>
       </c>
       <c r="D120" s="103"/>
-      <c r="E120" s="305"/>
+      <c r="E120" s="301"/>
       <c r="F120" s="103"/>
       <c r="G120" s="102">
         <f t="shared" ref="G120:Q120" si="48">IF(G$4="","",G8/G105)</f>
@@ -14262,7 +14379,7 @@
       </c>
       <c r="C123" s="180"/>
       <c r="D123" s="27"/>
-      <c r="E123" s="299"/>
+      <c r="E123" s="295"/>
       <c r="F123" s="27"/>
       <c r="G123" s="12"/>
       <c r="H123" s="12"/>
@@ -14287,7 +14404,7 @@
         <v>0.28396253740368455</v>
       </c>
       <c r="D124" s="27"/>
-      <c r="E124" s="299"/>
+      <c r="E124" s="295"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
@@ -14344,7 +14461,7 @@
         <v>7.9541327003833207E-2</v>
       </c>
       <c r="D125" s="27"/>
-      <c r="E125" s="299"/>
+      <c r="E125" s="295"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
@@ -14393,7 +14510,7 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -15144,13 +15261,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H94"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.73046875" customWidth="1"/>
-    <col min="3" max="6" width="20.6640625" customWidth="1"/>
-    <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="20.73046875" customWidth="1"/>
+    <col min="7" max="7" width="5.73046875" customWidth="1"/>
+    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="13.9">
@@ -15194,7 +15311,7 @@
         <v>251</v>
       </c>
       <c r="F4" s="135">
-        <f>Thesis!C81</f>
+        <f>Thesis!C86</f>
         <v>0</v>
       </c>
       <c r="H4" s="121"/>
@@ -15204,7 +15321,7 @@
         <v>124</v>
       </c>
       <c r="C5" s="228">
-        <f>Thesis!C75</f>
+        <f>Thesis!C80</f>
         <v>0.08</v>
       </c>
       <c r="E5" s="149"/>
@@ -15222,10 +15339,10 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="351" t="s">
+      <c r="E6" s="354" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="351"/>
+      <c r="F6" s="354"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8">
@@ -15240,8 +15357,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="351"/>
-      <c r="F7" s="351"/>
+      <c r="E7" s="354"/>
+      <c r="F7" s="354"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8">
@@ -15256,8 +15373,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="351"/>
-      <c r="F8" s="351"/>
+      <c r="E8" s="354"/>
+      <c r="F8" s="354"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8">
@@ -15272,8 +15389,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="351"/>
-      <c r="F9" s="351"/>
+      <c r="E9" s="354"/>
+      <c r="F9" s="354"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -15337,7 +15454,7 @@
       </c>
       <c r="H15" s="121"/>
     </row>
-    <row r="16" spans="2:8" ht="13.25" customHeight="1">
+    <row r="16" spans="2:8" ht="13.35" customHeight="1">
       <c r="B16" s="153" t="s">
         <v>134</v>
       </c>
@@ -15347,7 +15464,7 @@
       </c>
       <c r="H16" s="121"/>
     </row>
-    <row r="17" spans="2:8" ht="13.25" customHeight="1">
+    <row r="17" spans="2:8" ht="13.35" customHeight="1">
       <c r="B17" s="119" t="s">
         <v>135</v>
       </c>
@@ -15357,7 +15474,7 @@
       </c>
       <c r="H17" s="121"/>
     </row>
-    <row r="18" spans="2:8" ht="13.25" customHeight="1">
+    <row r="18" spans="2:8" ht="13.35" customHeight="1">
       <c r="B18" s="154" t="s">
         <v>107</v>
       </c>
@@ -16618,7 +16735,7 @@
     </row>
     <row r="80" spans="1:8">
       <c r="B80" s="156" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="C80" s="156" t="s">
         <v>106</v>
@@ -16671,12 +16788,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" customWidth="1"/>
-    <col min="3" max="3" width="13.9296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="2.73046875" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" customWidth="1"/>
+    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.73046875" customWidth="1"/>
     <col min="5" max="6" width="42.59765625" customWidth="1"/>
     <col min="8" max="9" width="15.59765625" customWidth="1"/>
   </cols>
@@ -16689,19 +16806,19 @@
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
-      <c r="H2" s="277" t="s">
-        <v>302</v>
-      </c>
-      <c r="I2" s="278"/>
+      <c r="H2" s="275" t="s">
+        <v>298</v>
+      </c>
+      <c r="I2" s="276"/>
     </row>
     <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="160" t="s">
         <v>149</v>
       </c>
-      <c r="H3" s="276">
-        <v>0</v>
-      </c>
-      <c r="I3" s="264">
+      <c r="H3" s="274">
+        <v>0</v>
+      </c>
+      <c r="I3" s="262">
         <f>-Market_Price</f>
         <v>-3.57</v>
       </c>
@@ -16718,19 +16835,19 @@
         <v>151</v>
       </c>
       <c r="F4" s="156"/>
-      <c r="H4" s="276">
+      <c r="H4" s="274">
         <v>1</v>
       </c>
-      <c r="I4" s="264">
+      <c r="I4" s="262">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
         <v>0.128</v>
       </c>
     </row>
     <row r="5" spans="2:9">
-      <c r="H5" s="276">
+      <c r="H5" s="274">
         <v>2</v>
       </c>
-      <c r="I5" s="264">
+      <c r="I5" s="262">
         <f t="shared" si="0"/>
         <v>0.128</v>
       </c>
@@ -16744,13 +16861,13 @@
         <v>1000</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F6" s="100"/>
-      <c r="H6" s="276">
+      <c r="H6" s="274">
         <v>3</v>
       </c>
-      <c r="I6" s="264">
+      <c r="I6" s="262">
         <f t="shared" si="0"/>
         <v>5.0903808252376095</v>
       </c>
@@ -16767,15 +16884,15 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="353" t="str">
+      <c r="E7" s="356" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 東方表行集團(0398.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="353"/>
-      <c r="H7" s="276">
+      <c r="F7" s="356"/>
+      <c r="H7" s="274">
         <v>4</v>
       </c>
-      <c r="I7" s="264" t="str">
+      <c r="I7" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16792,12 +16909,12 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="353"/>
-      <c r="F8" s="353"/>
-      <c r="H8" s="276">
+      <c r="E8" s="356"/>
+      <c r="F8" s="356"/>
+      <c r="H8" s="274">
         <v>5</v>
       </c>
-      <c r="I8" s="264" t="str">
+      <c r="I8" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16814,37 +16931,37 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="353"/>
-      <c r="F9" s="353"/>
-      <c r="H9" s="276">
+      <c r="E9" s="356"/>
+      <c r="F9" s="356"/>
+      <c r="H9" s="274">
         <v>6</v>
       </c>
-      <c r="I9" s="264" t="str">
+      <c r="I9" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="353"/>
-      <c r="F10" s="353"/>
-      <c r="H10" s="276">
+      <c r="E10" s="356"/>
+      <c r="F10" s="356"/>
+      <c r="H10" s="274">
         <v>7</v>
       </c>
-      <c r="I10" s="264" t="str">
+      <c r="I10" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="160" t="s">
-        <v>279</v>
-      </c>
-      <c r="E11" s="353"/>
-      <c r="F11" s="353"/>
-      <c r="H11" s="276">
+        <v>278</v>
+      </c>
+      <c r="E11" s="356"/>
+      <c r="F11" s="356"/>
+      <c r="H11" s="274">
         <v>8</v>
       </c>
-      <c r="I11" s="264" t="str">
+      <c r="I11" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16858,12 +16975,12 @@
         <v>1.2656410607081225E-2</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="353"/>
-      <c r="F12" s="353"/>
-      <c r="H12" s="276">
+      <c r="E12" s="356"/>
+      <c r="F12" s="356"/>
+      <c r="H12" s="274">
         <v>9</v>
       </c>
-      <c r="I12" s="264" t="str">
+      <c r="I12" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16876,12 +16993,12 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>3.5687612277801151E-2</v>
       </c>
-      <c r="E13" s="353"/>
-      <c r="F13" s="353"/>
-      <c r="H13" s="276">
+      <c r="E13" s="356"/>
+      <c r="F13" s="356"/>
+      <c r="H13" s="274">
         <v>10</v>
       </c>
-      <c r="I13" s="264" t="str">
+      <c r="I13" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16894,8 +17011,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>1.5957752466103425E-2</v>
       </c>
-      <c r="E14" s="353"/>
-      <c r="F14" s="353"/>
+      <c r="E14" s="356"/>
+      <c r="F14" s="356"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -16911,7 +17028,7 @@
         <v>152</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
     </row>
     <row r="18" spans="2:6">
@@ -16921,25 +17038,25 @@
       <c r="C18" s="151">
         <v>10</v>
       </c>
-      <c r="E18" s="353" t="s">
-        <v>338</v>
-      </c>
-      <c r="F18" s="354"/>
+      <c r="E18" s="356" t="s">
+        <v>333</v>
+      </c>
+      <c r="F18" s="357"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="354"/>
-      <c r="F19" s="354"/>
+      <c r="E19" s="357"/>
+      <c r="F19" s="357"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
-        <v>310</v>
-      </c>
-      <c r="E20" s="354"/>
-      <c r="F20" s="354"/>
+        <v>306</v>
+      </c>
+      <c r="E20" s="357"/>
+      <c r="F20" s="357"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
@@ -16949,12 +17066,12 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="354"/>
-      <c r="F21" s="354"/>
+      <c r="E21" s="357"/>
+      <c r="F21" s="357"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
@@ -16964,8 +17081,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="354"/>
-      <c r="F22" s="354"/>
+      <c r="E22" s="357"/>
+      <c r="F22" s="357"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
@@ -16985,8 +17102,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="352"/>
-      <c r="F25" s="352"/>
+      <c r="E25" s="355"/>
+      <c r="F25" s="355"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
@@ -16996,8 +17113,8 @@
         <v>0.04</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="352"/>
-      <c r="F26" s="352"/>
+      <c r="E26" s="355"/>
+      <c r="F26" s="355"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -17011,8 +17128,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="352"/>
-      <c r="F27" s="352"/>
+      <c r="E27" s="355"/>
+      <c r="F27" s="355"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -17022,8 +17139,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="352"/>
-      <c r="F28" s="352"/>
+      <c r="E28" s="355"/>
+      <c r="F28" s="355"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
@@ -17043,8 +17160,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="352"/>
-      <c r="F31" s="352"/>
+      <c r="E31" s="355"/>
+      <c r="F31" s="355"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
@@ -17054,8 +17171,8 @@
         <v>0.02</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="352"/>
-      <c r="F32" s="352"/>
+      <c r="E32" s="355"/>
+      <c r="F32" s="355"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -17069,8 +17186,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="352"/>
-      <c r="F33" s="352"/>
+      <c r="E33" s="355"/>
+      <c r="F33" s="355"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -17080,8 +17197,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="352"/>
-      <c r="F34" s="352"/>
+      <c r="E34" s="355"/>
+      <c r="F34" s="355"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
@@ -17101,8 +17218,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="352"/>
-      <c r="F37" s="352"/>
+      <c r="E37" s="355"/>
+      <c r="F37" s="355"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
@@ -17112,8 +17229,8 @@
         <v>0.06</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="352"/>
-      <c r="F38" s="352"/>
+      <c r="E38" s="355"/>
+      <c r="F38" s="355"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -17127,8 +17244,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="352"/>
-      <c r="F39" s="352"/>
+      <c r="E39" s="355"/>
+      <c r="F39" s="355"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -17139,8 +17256,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="352"/>
-      <c r="F40" s="352"/>
+      <c r="E40" s="355"/>
+      <c r="F40" s="355"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -17202,8 +17319,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="352"/>
-      <c r="F49" s="352"/>
+      <c r="E49" s="355"/>
+      <c r="F49" s="355"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
@@ -17213,8 +17330,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="352"/>
-      <c r="F50" s="352"/>
+      <c r="E50" s="355"/>
+      <c r="F50" s="355"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -17228,8 +17345,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="352"/>
-      <c r="F51" s="352"/>
+      <c r="E51" s="355"/>
+      <c r="F51" s="355"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -17239,12 +17356,12 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="352"/>
-      <c r="F52" s="352"/>
+      <c r="E52" s="355"/>
+      <c r="F52" s="355"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="E54" s="160" t="s">
         <v>150</v>
@@ -17260,8 +17377,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="352"/>
-      <c r="F55" s="352"/>
+      <c r="E55" s="355"/>
+      <c r="F55" s="355"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
@@ -17271,8 +17388,8 @@
         <v>0.1</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="352"/>
-      <c r="F56" s="352"/>
+      <c r="E56" s="355"/>
+      <c r="F56" s="355"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -17286,8 +17403,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="352"/>
-      <c r="F57" s="352"/>
+      <c r="E57" s="355"/>
+      <c r="F57" s="355"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -17297,8 +17414,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="352"/>
-      <c r="F58" s="352"/>
+      <c r="E58" s="355"/>
+      <c r="F58" s="355"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -17313,16 +17430,16 @@
         <v>HKD</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>303</v>
-      </c>
-      <c r="F60" s="312">
-        <f>Thesis!E25</f>
+        <v>299</v>
+      </c>
+      <c r="F60" s="308">
+        <f>Thesis!F28</f>
         <v>3</v>
       </c>
     </row>
     <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -17331,10 +17448,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
-        <v>311</v>
-      </c>
-      <c r="E63" s="282" t="s">
-        <v>319</v>
+        <v>307</v>
+      </c>
+      <c r="E63" s="279" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -17346,8 +17463,8 @@
         <v>10</v>
       </c>
       <c r="D64" s="151"/>
-      <c r="E64" s="281" t="s">
-        <v>403</v>
+      <c r="E64" s="278" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="65" spans="2:6">
@@ -17358,8 +17475,8 @@
         <v>4.6574870890079501E-2</v>
       </c>
       <c r="D65" s="152"/>
-      <c r="E65" s="281" t="s">
-        <v>320</v>
+      <c r="E65" s="278" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="66" spans="2:6">
@@ -17374,23 +17491,23 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E66" s="281" t="s">
-        <v>321</v>
+      <c r="E66" s="278" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
-        <v>358</v>
-      </c>
-      <c r="E68" s="282" t="s">
-        <v>322</v>
+        <v>353</v>
+      </c>
+      <c r="E68" s="279" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
-        <v>312</v>
-      </c>
-      <c r="C69" s="273" t="str">
+        <v>308</v>
+      </c>
+      <c r="C69" s="271" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
         <v>N</v>
       </c>
@@ -17398,38 +17515,38 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
-        <v>300</v>
-      </c>
-      <c r="C70" s="273" t="str">
+        <v>296</v>
+      </c>
+      <c r="C70" s="271" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
-      <c r="E70" s="281" t="s">
-        <v>301</v>
+      <c r="E70" s="278" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
-        <v>299</v>
-      </c>
-      <c r="C71" s="273" t="str">
+        <v>295</v>
+      </c>
+      <c r="C71" s="271" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
         <v>N</v>
       </c>
-      <c r="E71" s="281"/>
+      <c r="E71" s="278"/>
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
-        <v>291</v>
-      </c>
-      <c r="C72" s="272" t="str">
+        <v>287</v>
+      </c>
+      <c r="C72" s="270" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>354</v>
-      </c>
-      <c r="F72" s="329">
+        <v>349</v>
+      </c>
+      <c r="F72" s="325">
         <f>BS!D89/C60</f>
         <v>0.16999421619281041</v>
       </c>
@@ -17449,10 +17566,10 @@
       </c>
     </row>
     <row r="76" spans="2:6">
-      <c r="B76" s="275" t="s">
-        <v>304</v>
-      </c>
-      <c r="C76" s="274">
+      <c r="B76" s="273" t="s">
+        <v>300</v>
+      </c>
+      <c r="C76" s="272">
         <f>F60</f>
         <v>3</v>
       </c>
@@ -17473,15 +17590,15 @@
     </row>
     <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="149" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="C80" s="168">
-        <f>Thesis!C132</f>
+        <f>Thesis!F29</f>
         <v>0.4</v>
       </c>
     </row>
@@ -17522,7 +17639,7 @@
       <c r="E83" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F83" s="329">
+      <c r="F83" s="325">
         <f>(1-C83/C60)</f>
         <v>0.59458376580552363</v>
       </c>
@@ -17532,14 +17649,14 @@
     </row>
     <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="86" spans="2:8">
       <c r="B86" s="149" t="s">
-        <v>307</v>
-      </c>
-      <c r="C86" s="266">
+        <v>303</v>
+      </c>
+      <c r="C86" s="264">
         <f>Market_Price</f>
         <v>3.57</v>
       </c>
@@ -17550,9 +17667,9 @@
     </row>
     <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
-        <v>305</v>
-      </c>
-      <c r="C87" s="265">
+        <v>301</v>
+      </c>
+      <c r="C87" s="263">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
         <v>0.14834835832623461</v>
       </c>
@@ -17562,15 +17679,15 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="C90" s="168">
-        <f>Thesis!E24</f>
+        <f>Thesis!F30</f>
         <v>0.2</v>
       </c>
     </row>
@@ -17611,28 +17728,28 @@
       <c r="E93" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F93" s="329">
+      <c r="F93" s="325">
         <f>(1-C93/C60)</f>
         <v>0.36696156481854458</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="G95" s="2"/>
-      <c r="H95" s="316"/>
+      <c r="H95" s="312"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="C96" s="135">
-        <f>Thesis!C72</f>
+        <f>Thesis!F31</f>
         <v>0.08</v>
       </c>
       <c r="G96" s="2"/>
-      <c r="H96" s="316"/>
+      <c r="H96" s="312"/>
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
@@ -17644,7 +17761,7 @@
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
-      <c r="H97" s="316"/>
+      <c r="H97" s="312"/>
     </row>
     <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
@@ -17656,23 +17773,23 @@
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
-      <c r="H98" s="316"/>
+      <c r="H98" s="312"/>
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="111" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
         <v>4.2691663056616189</v>
       </c>
       <c r="D99" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="E99" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F99" s="329">
+      <c r="F99" s="325">
         <f>(1-C99/C60)</f>
         <v>0.13969393804894004</v>
       </c>
@@ -17682,15 +17799,15 @@
     </row>
     <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
     </row>
     <row r="102" spans="2:8">
       <c r="B102" s="149" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="C102" s="135">
-        <f>Thesis!E26</f>
+        <f>Thesis!F32</f>
         <v>0.1174</v>
       </c>
     </row>
@@ -17716,19 +17833,19 @@
     </row>
     <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="111" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="C105" s="112">
         <f>C103+C104</f>
         <v>3.8656512307065762</v>
       </c>
       <c r="D105" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="E105" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F105" s="329">
+      <c r="F105" s="325">
         <f>(1-C105/C66)</f>
         <v>0.22106689885075603</v>
       </c>
@@ -17737,33 +17854,33 @@
       <c r="B106" s="100"/>
     </row>
     <row r="107" spans="2:8" ht="14.65">
-      <c r="E107" s="320" t="s">
-        <v>332</v>
-      </c>
-      <c r="F107" s="317"/>
+      <c r="E107" s="316" t="s">
+        <v>327</v>
+      </c>
+      <c r="F107" s="313"/>
     </row>
     <row r="108" spans="2:8" ht="13.9">
-      <c r="E108" s="313" t="s">
-        <v>333</v>
-      </c>
-      <c r="F108" s="318" t="s">
-        <v>334</v>
+      <c r="E108" s="309" t="s">
+        <v>328</v>
+      </c>
+      <c r="F108" s="314" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="13.9">
-      <c r="E109" s="314" t="s">
-        <v>333</v>
-      </c>
-      <c r="F109" s="318" t="s">
-        <v>335</v>
+      <c r="E109" s="310" t="s">
+        <v>328</v>
+      </c>
+      <c r="F109" s="314" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="110" spans="2:8" ht="13.9">
-      <c r="E110" s="315" t="s">
-        <v>333</v>
-      </c>
-      <c r="F110" s="319" t="s">
-        <v>336</v>
+      <c r="E110" s="311" t="s">
+        <v>328</v>
+      </c>
+      <c r="F110" s="315" t="s">
+        <v>331</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/opportunities/0398.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0398.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F8E0918-40CD-44BC-BF9C-EBF34D1F107C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1B4C53F-E6F8-4F7C-8CA8-94971F608416}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3830,29 +3830,29 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4312,13 +4312,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B18" s="346" t="s">
+      <c r="B18" s="348" t="s">
         <v>362</v>
       </c>
-      <c r="C18" s="346"/>
-      <c r="D18" s="346"/>
-      <c r="E18" s="346"/>
-      <c r="F18" s="346"/>
+      <c r="C18" s="348"/>
+      <c r="D18" s="348"/>
+      <c r="E18" s="348"/>
+      <c r="F18" s="348"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="C30" s="148">
         <f>C152</f>
-        <v>3.1413777923828756</v>
+        <v>3.012815450868831</v>
       </c>
       <c r="D30" s="148" t="str">
         <f>D152</f>
@@ -4458,7 +4458,7 @@
         <v>440</v>
       </c>
       <c r="F30" s="307">
-        <v>0.2</v>
+        <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="31" spans="2:6">
@@ -4514,22 +4514,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B36" s="346" t="s">
+      <c r="B36" s="348" t="s">
         <v>363</v>
       </c>
-      <c r="C36" s="346"/>
-      <c r="D36" s="346"/>
-      <c r="E36" s="346"/>
-      <c r="F36" s="346"/>
+      <c r="C36" s="348"/>
+      <c r="D36" s="348"/>
+      <c r="E36" s="348"/>
+      <c r="F36" s="348"/>
     </row>
     <row r="37" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B37" s="348" t="s">
+      <c r="B37" s="351" t="s">
         <v>342</v>
       </c>
-      <c r="C37" s="348"/>
-      <c r="D37" s="348"/>
-      <c r="E37" s="348"/>
-      <c r="F37" s="348"/>
+      <c r="C37" s="351"/>
+      <c r="D37" s="351"/>
+      <c r="E37" s="351"/>
+      <c r="F37" s="351"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="234" t="s">
@@ -4541,13 +4541,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B40" s="347" t="s">
+      <c r="B40" s="349" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="347"/>
-      <c r="D40" s="347"/>
-      <c r="E40" s="347"/>
-      <c r="F40" s="347"/>
+      <c r="C40" s="349"/>
+      <c r="D40" s="349"/>
+      <c r="E40" s="349"/>
+      <c r="F40" s="349"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4567,13 +4567,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B43" s="347" t="s">
+      <c r="B43" s="349" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="347"/>
-      <c r="D43" s="347"/>
-      <c r="E43" s="347"/>
-      <c r="F43" s="347"/>
+      <c r="C43" s="349"/>
+      <c r="D43" s="349"/>
+      <c r="E43" s="349"/>
+      <c r="F43" s="349"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4602,13 +4602,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="347" t="s">
+      <c r="B47" s="349" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="347"/>
-      <c r="D47" s="347"/>
-      <c r="E47" s="347"/>
-      <c r="F47" s="347"/>
+      <c r="C47" s="349"/>
+      <c r="D47" s="349"/>
+      <c r="E47" s="349"/>
+      <c r="F47" s="349"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4624,13 +4624,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="347" t="s">
+      <c r="B50" s="349" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="347"/>
-      <c r="D50" s="347"/>
-      <c r="E50" s="347"/>
-      <c r="F50" s="347"/>
+      <c r="C50" s="349"/>
+      <c r="D50" s="349"/>
+      <c r="E50" s="349"/>
+      <c r="F50" s="349"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4694,13 +4694,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="347" t="s">
+      <c r="B58" s="349" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="347"/>
-      <c r="D58" s="347"/>
-      <c r="E58" s="347"/>
-      <c r="F58" s="347"/>
+      <c r="C58" s="349"/>
+      <c r="D58" s="349"/>
+      <c r="E58" s="349"/>
+      <c r="F58" s="349"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4716,7 +4716,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="347" t="s">
+      <c r="B61" s="349" t="s">
         <v>341</v>
       </c>
       <c r="C61" s="350"/>
@@ -4738,22 +4738,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B64" s="346" t="s">
+      <c r="B64" s="348" t="s">
         <v>346</v>
       </c>
-      <c r="C64" s="346"/>
-      <c r="D64" s="346"/>
-      <c r="E64" s="346"/>
-      <c r="F64" s="346"/>
+      <c r="C64" s="348"/>
+      <c r="D64" s="348"/>
+      <c r="E64" s="348"/>
+      <c r="F64" s="348"/>
     </row>
     <row r="65" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B65" s="346" t="s">
+      <c r="B65" s="348" t="s">
         <v>364</v>
       </c>
-      <c r="C65" s="346"/>
-      <c r="D65" s="346"/>
-      <c r="E65" s="346"/>
-      <c r="F65" s="346"/>
+      <c r="C65" s="348"/>
+      <c r="D65" s="348"/>
+      <c r="E65" s="348"/>
+      <c r="F65" s="348"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4814,22 +4814,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="346" t="s">
+      <c r="B74" s="348" t="s">
         <v>365</v>
       </c>
-      <c r="C74" s="346"/>
-      <c r="D74" s="346"/>
-      <c r="E74" s="346"/>
-      <c r="F74" s="346"/>
+      <c r="C74" s="348"/>
+      <c r="D74" s="348"/>
+      <c r="E74" s="348"/>
+      <c r="F74" s="348"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="348" t="s">
+      <c r="B75" s="351" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="348"/>
-      <c r="D75" s="348"/>
-      <c r="E75" s="348"/>
-      <c r="F75" s="348"/>
+      <c r="C75" s="351"/>
+      <c r="D75" s="351"/>
+      <c r="E75" s="351"/>
+      <c r="F75" s="351"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="234" t="s">
@@ -4873,22 +4873,22 @@
       <c r="C82" s="122"/>
     </row>
     <row r="83" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B83" s="346" t="s">
+      <c r="B83" s="348" t="s">
         <v>366</v>
       </c>
-      <c r="C83" s="346"/>
-      <c r="D83" s="346"/>
-      <c r="E83" s="346"/>
-      <c r="F83" s="346"/>
+      <c r="C83" s="348"/>
+      <c r="D83" s="348"/>
+      <c r="E83" s="348"/>
+      <c r="F83" s="348"/>
     </row>
     <row r="84" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B84" s="346" t="s">
+      <c r="B84" s="348" t="s">
         <v>367</v>
       </c>
-      <c r="C84" s="346"/>
-      <c r="D84" s="346"/>
-      <c r="E84" s="346"/>
-      <c r="F84" s="346"/>
+      <c r="C84" s="348"/>
+      <c r="D84" s="348"/>
+      <c r="E84" s="348"/>
+      <c r="F84" s="348"/>
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
@@ -4925,13 +4925,13 @@
       <c r="A90" s="233"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="B91" s="346" t="s">
+      <c r="B91" s="348" t="s">
         <v>368</v>
       </c>
-      <c r="C91" s="346"/>
-      <c r="D91" s="346"/>
-      <c r="E91" s="346"/>
-      <c r="F91" s="346"/>
+      <c r="C91" s="348"/>
+      <c r="D91" s="348"/>
+      <c r="E91" s="348"/>
+      <c r="F91" s="348"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
@@ -4944,13 +4944,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B95" s="346" t="s">
+      <c r="B95" s="348" t="s">
         <v>347</v>
       </c>
-      <c r="C95" s="346"/>
-      <c r="D95" s="346"/>
-      <c r="E95" s="346"/>
-      <c r="F95" s="346"/>
+      <c r="C95" s="348"/>
+      <c r="D95" s="348"/>
+      <c r="E95" s="348"/>
+      <c r="F95" s="348"/>
     </row>
     <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
@@ -5081,13 +5081,13 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B111" s="346" t="s">
+      <c r="B111" s="348" t="s">
         <v>369</v>
       </c>
-      <c r="C111" s="346"/>
-      <c r="D111" s="346"/>
-      <c r="E111" s="346"/>
-      <c r="F111" s="346"/>
+      <c r="C111" s="348"/>
+      <c r="D111" s="348"/>
+      <c r="E111" s="348"/>
+      <c r="F111" s="348"/>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
@@ -5126,13 +5126,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B118" s="347" t="s">
+      <c r="B118" s="349" t="s">
         <v>370</v>
       </c>
-      <c r="C118" s="347"/>
-      <c r="D118" s="347"/>
-      <c r="E118" s="347"/>
-      <c r="F118" s="347"/>
+      <c r="C118" s="349"/>
+      <c r="D118" s="349"/>
+      <c r="E118" s="349"/>
+      <c r="F118" s="349"/>
     </row>
     <row r="120" spans="1:6" ht="12.4">
       <c r="B120" s="258" t="s">
@@ -5275,13 +5275,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B129" s="351" t="s">
+      <c r="B129" s="352" t="s">
         <v>373</v>
       </c>
-      <c r="C129" s="351"/>
-      <c r="D129" s="351"/>
-      <c r="E129" s="351"/>
-      <c r="F129" s="351"/>
+      <c r="C129" s="352"/>
+      <c r="D129" s="352"/>
+      <c r="E129" s="352"/>
+      <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="247" t="s">
@@ -5294,22 +5294,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="349" t="s">
+      <c r="B133" s="353" t="s">
         <v>371</v>
       </c>
-      <c r="C133" s="349"/>
-      <c r="D133" s="349"/>
-      <c r="E133" s="349"/>
-      <c r="F133" s="349"/>
+      <c r="C133" s="353"/>
+      <c r="D133" s="353"/>
+      <c r="E133" s="353"/>
+      <c r="F133" s="353"/>
     </row>
     <row r="134" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B134" s="346" t="s">
+      <c r="B134" s="348" t="s">
         <v>372</v>
       </c>
-      <c r="C134" s="346"/>
-      <c r="D134" s="346"/>
-      <c r="E134" s="346"/>
-      <c r="F134" s="346"/>
+      <c r="C134" s="348"/>
+      <c r="D134" s="348"/>
+      <c r="E134" s="348"/>
+      <c r="F134" s="348"/>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="234" t="s">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="C149" s="332">
         <f>Scenarios!C90</f>
-        <v>0.2</v>
+        <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="150" spans="2:4">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="C150" s="240">
         <f>Scenarios!C91</f>
-        <v>0.26962962962962961</v>
+        <v>0.2624513054547119</v>
       </c>
     </row>
     <row r="151" spans="2:4">
@@ -5455,7 +5455,7 @@
       </c>
       <c r="C151" s="240">
         <f>Scenarios!C92</f>
-        <v>2.8717481627532462</v>
+        <v>2.7503641454141192</v>
       </c>
     </row>
     <row r="152" spans="2:4">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="C152" s="239">
         <f>Scenarios!C93</f>
-        <v>3.1413777923828756</v>
+        <v>3.012815450868831</v>
       </c>
       <c r="D152" s="336" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="C154" s="92">
         <f>Scenarios!F93</f>
-        <v>0.36696156481854458</v>
+        <v>0.3928689560570815</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5642,13 +5642,13 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="353" t="s">
+      <c r="B174" s="347" t="s">
         <v>379</v>
       </c>
-      <c r="C174" s="346"/>
-      <c r="D174" s="346"/>
-      <c r="E174" s="346"/>
-      <c r="F174" s="346"/>
+      <c r="C174" s="348"/>
+      <c r="D174" s="348"/>
+      <c r="E174" s="348"/>
+      <c r="F174" s="348"/>
     </row>
     <row r="176" spans="1:6">
       <c r="B176" s="234" t="s">
@@ -5685,13 +5685,13 @@
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B183" s="347" t="s">
+      <c r="B183" s="349" t="s">
         <v>384</v>
       </c>
-      <c r="C183" s="347"/>
-      <c r="D183" s="347"/>
-      <c r="E183" s="347"/>
-      <c r="F183" s="347"/>
+      <c r="C183" s="349"/>
+      <c r="D183" s="349"/>
+      <c r="E183" s="349"/>
+      <c r="F183" s="349"/>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
@@ -5699,22 +5699,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B186" s="352" t="s">
+      <c r="B186" s="346" t="s">
         <v>385</v>
       </c>
-      <c r="C186" s="352"/>
-      <c r="D186" s="352"/>
-      <c r="E186" s="352"/>
-      <c r="F186" s="352"/>
+      <c r="C186" s="346"/>
+      <c r="D186" s="346"/>
+      <c r="E186" s="346"/>
+      <c r="F186" s="346"/>
     </row>
     <row r="187" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B187" s="352" t="s">
+      <c r="B187" s="346" t="s">
         <v>386</v>
       </c>
-      <c r="C187" s="352"/>
-      <c r="D187" s="352"/>
-      <c r="E187" s="352"/>
-      <c r="F187" s="352"/>
+      <c r="C187" s="346"/>
+      <c r="D187" s="346"/>
+      <c r="E187" s="346"/>
+      <c r="F187" s="346"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
@@ -5738,17 +5738,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5765,6 +5754,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -17688,7 +17688,7 @@
       </c>
       <c r="C90" s="168">
         <f>Thesis!F30</f>
-        <v>0.2</v>
+        <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -17697,7 +17697,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>0.26962962962962961</v>
+        <v>0.2624513054547119</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
@@ -17709,7 +17709,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>2.8717481627532462</v>
+        <v>2.7503641454141192</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17719,7 +17719,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>3.1413777923828756</v>
+        <v>3.012815450868831</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17730,7 +17730,7 @@
       </c>
       <c r="F93" s="325">
         <f>(1-C93/C60)</f>
-        <v>0.36696156481854458</v>
+        <v>0.3928689560570815</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">

--- a/financial_models/opportunities/0398.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0398.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1B4C53F-E6F8-4F7C-8CA8-94971F608416}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AC23400-E9E3-404D-A5A4-5C8C75A489A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3111,7 +3111,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="358">
+  <cellXfs count="360">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3745,7 +3745,6 @@
     <xf numFmtId="37" fontId="48" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="10" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -3809,9 +3808,6 @@
     <xf numFmtId="9" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="175" fontId="46" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3830,29 +3826,39 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="9" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4160,7 +4166,7 @@
         <v>45786</v>
       </c>
       <c r="D1" s="52"/>
-      <c r="E1" s="326" t="s">
+      <c r="E1" s="325" t="s">
         <v>356</v>
       </c>
       <c r="F1" s="281" t="s">
@@ -4194,7 +4200,7 @@
       <c r="B5" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="C5" s="328" t="s">
+      <c r="C5" s="327" t="s">
         <v>445</v>
       </c>
     </row>
@@ -4347,7 +4353,7 @@
       <c r="D22" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="E22" s="345" t="s">
+      <c r="E22" s="343" t="s">
         <v>442</v>
       </c>
     </row>
@@ -4378,7 +4384,7 @@
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
         <v/>
       </c>
-      <c r="E25" s="335" t="str">
+      <c r="E25" s="334" t="str">
         <f>IF(D11="","",1/Exchange_Rate*D16)</f>
         <v/>
       </c>
@@ -4388,14 +4394,14 @@
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (HKD) :</v>
       </c>
-      <c r="C26" s="341">
+      <c r="C26" s="339">
         <f>C127</f>
         <v>4.9623808252376094</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="E26" s="337">
+      <c r="E26" s="336">
         <f ca="1">Scenarios!C87</f>
         <v>0.14834835832623461</v>
       </c>
@@ -4408,18 +4414,18 @@
       <c r="B28" s="45" t="s">
         <v>436</v>
       </c>
-      <c r="C28" s="268" t="str">
+      <c r="C28" s="344" t="str">
         <f>C140&amp;" ("&amp;Market_currency&amp;")"</f>
         <v>0398.HK (HKD)</v>
       </c>
-      <c r="D28" s="268" t="str">
+      <c r="D28" s="344" t="str">
         <f>IF(D11="","",D140&amp;" ("&amp;D13&amp;")")</f>
         <v/>
       </c>
-      <c r="E28" s="342" t="s">
+      <c r="E28" s="340" t="s">
         <v>432</v>
       </c>
-      <c r="F28" s="340">
+      <c r="F28" s="338">
         <v>3</v>
       </c>
     </row>
@@ -4427,18 +4433,18 @@
       <c r="B29" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="C29" s="339">
+      <c r="C29" s="345">
         <f>C144</f>
         <v>2.0118297468067095</v>
       </c>
-      <c r="D29" s="339" t="str">
+      <c r="D29" s="345" t="str">
         <f>D144</f>
         <v/>
       </c>
-      <c r="E29" s="343" t="s">
+      <c r="E29" s="341" t="s">
         <v>427</v>
       </c>
-      <c r="F29" s="338">
+      <c r="F29" s="337">
         <v>0.4</v>
       </c>
     </row>
@@ -4446,18 +4452,18 @@
       <c r="B30" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="C30" s="148">
+      <c r="C30" s="346">
         <f>C152</f>
         <v>3.012815450868831</v>
       </c>
-      <c r="D30" s="148" t="str">
+      <c r="D30" s="346" t="str">
         <f>D152</f>
         <v/>
       </c>
-      <c r="E30" s="344" t="s">
+      <c r="E30" s="342" t="s">
         <v>440</v>
       </c>
-      <c r="F30" s="307">
+      <c r="F30" s="347">
         <v>0.21740000000000001</v>
       </c>
     </row>
@@ -4465,18 +4471,18 @@
       <c r="B31" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="C31" s="148">
+      <c r="C31" s="346">
         <f>C160</f>
         <v>4.2691663056616189</v>
       </c>
-      <c r="D31" s="148" t="str">
+      <c r="D31" s="346" t="str">
         <f>D160</f>
         <v/>
       </c>
-      <c r="E31" s="344" t="s">
+      <c r="E31" s="342" t="s">
         <v>439</v>
       </c>
-      <c r="F31" s="307">
+      <c r="F31" s="347">
         <v>0.08</v>
       </c>
     </row>
@@ -4484,18 +4490,18 @@
       <c r="B32" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="C32" s="148">
+      <c r="C32" s="346">
         <f>C168</f>
         <v>3.8656512307065762</v>
       </c>
-      <c r="D32" s="148" t="str">
+      <c r="D32" s="346" t="str">
         <f>D168</f>
         <v/>
       </c>
-      <c r="E32" s="344" t="s">
+      <c r="E32" s="342" t="s">
         <v>441</v>
       </c>
-      <c r="F32" s="307">
+      <c r="F32" s="347">
         <v>0.1174</v>
       </c>
     </row>
@@ -4523,13 +4529,13 @@
       <c r="F36" s="348"/>
     </row>
     <row r="37" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B37" s="351" t="s">
+      <c r="B37" s="350" t="s">
         <v>342</v>
       </c>
-      <c r="C37" s="351"/>
-      <c r="D37" s="351"/>
-      <c r="E37" s="351"/>
-      <c r="F37" s="351"/>
+      <c r="C37" s="350"/>
+      <c r="D37" s="350"/>
+      <c r="E37" s="350"/>
+      <c r="F37" s="350"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="234" t="s">
@@ -4636,7 +4642,7 @@
       <c r="B51" s="47" t="s">
         <v>343</v>
       </c>
-      <c r="C51" s="318">
+      <c r="C51" s="317">
         <f>Normalized_FCF!C48</f>
         <v>0</v>
       </c>
@@ -4644,14 +4650,14 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="317"/>
-      <c r="F51" s="317"/>
+      <c r="E51" s="316"/>
+      <c r="F51" s="316"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
         <v>344</v>
       </c>
-      <c r="C52" s="318">
+      <c r="C52" s="317">
         <f>Normalized_FCF!C47</f>
         <v>-13663</v>
       </c>
@@ -4659,8 +4665,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E52" s="317"/>
-      <c r="F52" s="317"/>
+      <c r="E52" s="316"/>
+      <c r="F52" s="316"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4719,10 +4725,10 @@
       <c r="B61" s="349" t="s">
         <v>341</v>
       </c>
-      <c r="C61" s="350"/>
-      <c r="D61" s="350"/>
-      <c r="E61" s="350"/>
-      <c r="F61" s="350"/>
+      <c r="C61" s="352"/>
+      <c r="D61" s="352"/>
+      <c r="E61" s="352"/>
+      <c r="F61" s="352"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -4823,13 +4829,13 @@
       <c r="F74" s="348"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="351" t="s">
+      <c r="B75" s="350" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="351"/>
-      <c r="D75" s="351"/>
-      <c r="E75" s="351"/>
-      <c r="F75" s="351"/>
+      <c r="C75" s="350"/>
+      <c r="D75" s="350"/>
+      <c r="E75" s="350"/>
+      <c r="F75" s="350"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="234" t="s">
@@ -4867,7 +4873,7 @@
       <c r="C81" s="122"/>
     </row>
     <row r="82" spans="1:6">
-      <c r="B82" s="327" t="s">
+      <c r="B82" s="326" t="s">
         <v>359</v>
       </c>
       <c r="C82" s="122"/>
@@ -4979,28 +4985,28 @@
       </c>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="331" t="s">
+      <c r="B98" s="330" t="s">
         <v>407</v>
       </c>
-      <c r="C98" s="332">
+      <c r="C98" s="331">
         <f>BS!G30/BS!G27</f>
         <v>0.40000523965699897</v>
       </c>
     </row>
     <row r="99" spans="2:6">
-      <c r="B99" s="331" t="s">
+      <c r="B99" s="330" t="s">
         <v>408</v>
       </c>
-      <c r="C99" s="332">
+      <c r="C99" s="331">
         <f>BS!G31/BS!G27</f>
         <v>0.10646655543311496</v>
       </c>
     </row>
     <row r="100" spans="2:6">
-      <c r="B100" s="331" t="s">
+      <c r="B100" s="330" t="s">
         <v>410</v>
       </c>
-      <c r="C100" s="333">
+      <c r="C100" s="332">
         <f>BS!C50</f>
         <v>0.9804830051022897</v>
       </c>
@@ -5103,7 +5109,7 @@
       </c>
     </row>
     <row r="114" spans="1:6">
-      <c r="B114" s="331" t="s">
+      <c r="B114" s="330" t="s">
         <v>409</v>
       </c>
       <c r="C114" s="248">
@@ -5275,13 +5281,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B129" s="352" t="s">
+      <c r="B129" s="353" t="s">
         <v>373</v>
       </c>
-      <c r="C129" s="352"/>
-      <c r="D129" s="352"/>
-      <c r="E129" s="352"/>
-      <c r="F129" s="352"/>
+      <c r="C129" s="353"/>
+      <c r="D129" s="353"/>
+      <c r="E129" s="353"/>
+      <c r="F129" s="353"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="247" t="s">
@@ -5294,13 +5300,13 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="353" t="s">
+      <c r="B133" s="351" t="s">
         <v>371</v>
       </c>
-      <c r="C133" s="353"/>
-      <c r="D133" s="353"/>
-      <c r="E133" s="353"/>
-      <c r="F133" s="353"/>
+      <c r="C133" s="351"/>
+      <c r="D133" s="351"/>
+      <c r="E133" s="351"/>
+      <c r="F133" s="351"/>
     </row>
     <row r="134" spans="1:6" ht="24.4" customHeight="1">
       <c r="B134" s="348" t="s">
@@ -5364,7 +5370,7 @@
       <c r="B141" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="C141" s="332">
+      <c r="C141" s="331">
         <f>F29</f>
         <v>0.4</v>
       </c>
@@ -5397,7 +5403,7 @@
         <f>Scenarios!C83</f>
         <v>2.0118297468067095</v>
       </c>
-      <c r="D144" s="336" t="str">
+      <c r="D144" s="335" t="str">
         <f>IF($D$11="","",C144*$E$25)</f>
         <v/>
       </c>
@@ -5406,11 +5412,11 @@
       <c r="B145" s="286" t="s">
         <v>419</v>
       </c>
-      <c r="C145" s="334" t="str">
+      <c r="C145" s="333" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D145" s="334" t="str">
+      <c r="D145" s="333" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5433,7 +5439,7 @@
       <c r="B149" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="C149" s="332">
+      <c r="C149" s="331">
         <f>Scenarios!C90</f>
         <v>0.21740000000000001</v>
       </c>
@@ -5466,7 +5472,7 @@
         <f>Scenarios!C93</f>
         <v>3.012815450868831</v>
       </c>
-      <c r="D152" s="336" t="str">
+      <c r="D152" s="335" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
         <v/>
       </c>
@@ -5475,11 +5481,11 @@
       <c r="B153" s="286" t="s">
         <v>419</v>
       </c>
-      <c r="C153" s="334" t="str">
+      <c r="C153" s="333" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D153" s="334" t="str">
+      <c r="D153" s="333" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5535,7 +5541,7 @@
         <f>Scenarios!C99</f>
         <v>4.2691663056616189</v>
       </c>
-      <c r="D160" s="336" t="str">
+      <c r="D160" s="335" t="str">
         <f>IF($D$11="","",C160*$E$25)</f>
         <v/>
       </c>
@@ -5544,11 +5550,11 @@
       <c r="B161" s="286" t="s">
         <v>419</v>
       </c>
-      <c r="C161" s="334" t="str">
+      <c r="C161" s="333" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D161" s="334" t="str">
+      <c r="D161" s="333" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5604,7 +5610,7 @@
         <f>Scenarios!C105</f>
         <v>3.8656512307065762</v>
       </c>
-      <c r="D168" s="336" t="str">
+      <c r="D168" s="335" t="str">
         <f>IF($D$11="","",C168*$E$25)</f>
         <v/>
       </c>
@@ -5613,11 +5619,11 @@
       <c r="B169" s="286" t="s">
         <v>419</v>
       </c>
-      <c r="C169" s="334" t="str">
+      <c r="C169" s="333" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D169" s="334" t="str">
+      <c r="D169" s="333" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5642,7 +5648,7 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="347" t="s">
+      <c r="B174" s="355" t="s">
         <v>379</v>
       </c>
       <c r="C174" s="348"/>
@@ -5656,13 +5662,13 @@
       </c>
     </row>
     <row r="177" spans="2:6">
-      <c r="B177" s="350" t="s">
+      <c r="B177" s="352" t="s">
         <v>383</v>
       </c>
-      <c r="C177" s="350"/>
-      <c r="D177" s="350"/>
-      <c r="E177" s="350"/>
-      <c r="F177" s="350"/>
+      <c r="C177" s="352"/>
+      <c r="D177" s="352"/>
+      <c r="E177" s="352"/>
+      <c r="F177" s="352"/>
     </row>
     <row r="178" spans="2:6">
       <c r="B178" s="238" t="s">
@@ -5699,22 +5705,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B186" s="346" t="s">
+      <c r="B186" s="354" t="s">
         <v>385</v>
       </c>
-      <c r="C186" s="346"/>
-      <c r="D186" s="346"/>
-      <c r="E186" s="346"/>
-      <c r="F186" s="346"/>
+      <c r="C186" s="354"/>
+      <c r="D186" s="354"/>
+      <c r="E186" s="354"/>
+      <c r="F186" s="354"/>
     </row>
     <row r="187" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B187" s="346" t="s">
+      <c r="B187" s="354" t="s">
         <v>386</v>
       </c>
-      <c r="C187" s="346"/>
-      <c r="D187" s="346"/>
-      <c r="E187" s="346"/>
-      <c r="F187" s="346"/>
+      <c r="C187" s="354"/>
+      <c r="D187" s="354"/>
+      <c r="E187" s="354"/>
+      <c r="F187" s="354"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
@@ -5738,6 +5744,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5754,17 +5771,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -8158,11 +8164,11 @@
         <f t="shared" si="40"/>
         <v>86046</v>
       </c>
-      <c r="I77" s="330"/>
-      <c r="J77" s="330"/>
-      <c r="K77" s="330"/>
-      <c r="L77" s="330"/>
-      <c r="M77" s="330"/>
+      <c r="I77" s="329"/>
+      <c r="J77" s="329"/>
+      <c r="K77" s="329"/>
+      <c r="L77" s="329"/>
+      <c r="M77" s="329"/>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
@@ -8192,11 +8198,11 @@
         <f t="shared" si="40"/>
         <v>823654</v>
       </c>
-      <c r="I78" s="330"/>
-      <c r="J78" s="330"/>
-      <c r="K78" s="330"/>
-      <c r="L78" s="330"/>
-      <c r="M78" s="330"/>
+      <c r="I78" s="329"/>
+      <c r="J78" s="329"/>
+      <c r="K78" s="329"/>
+      <c r="L78" s="329"/>
+      <c r="M78" s="329"/>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
@@ -9421,7 +9427,7 @@
         <v>325</v>
       </c>
       <c r="C76" s="287"/>
-      <c r="D76" s="323">
+      <c r="D76" s="322">
         <f>IF(D74&lt;=3,1,IF(D74&gt;18,6,2))</f>
         <v>2</v>
       </c>
@@ -11492,104 +11498,104 @@
         <v>0</v>
       </c>
       <c r="E48" s="298"/>
-      <c r="G48" s="324">
+      <c r="G48" s="323">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>0</v>
       </c>
-      <c r="H48" s="324">
+      <c r="H48" s="323">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v>0</v>
       </c>
-      <c r="I48" s="324">
+      <c r="I48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="J48" s="324">
+      <c r="J48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="K48" s="324">
+      <c r="K48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="L48" s="324">
+      <c r="L48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="M48" s="324">
+      <c r="M48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="N48" s="324">
+      <c r="N48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="O48" s="324">
+      <c r="O48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="P48" s="324" t="str">
+      <c r="P48" s="323" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="Q48" s="324" t="str">
+      <c r="Q48" s="323" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
-      <c r="B49" s="319" t="s">
+      <c r="B49" s="318" t="s">
         <v>345</v>
       </c>
-      <c r="C49" s="320">
+      <c r="C49" s="319">
         <f>BS!$C$66*C53</f>
         <v>0</v>
       </c>
-      <c r="D49" s="321"/>
-      <c r="E49" s="322"/>
-      <c r="F49" s="321"/>
-      <c r="G49" s="320">
+      <c r="D49" s="320"/>
+      <c r="E49" s="321"/>
+      <c r="F49" s="320"/>
+      <c r="G49" s="319">
         <f>Data!C52</f>
         <v>0</v>
       </c>
-      <c r="H49" s="320">
+      <c r="H49" s="319">
         <f>Data!D52</f>
         <v>0</v>
       </c>
-      <c r="I49" s="320">
+      <c r="I49" s="319">
         <f>Data!E52</f>
         <v>0</v>
       </c>
-      <c r="J49" s="320">
+      <c r="J49" s="319">
         <f>Data!F52</f>
         <v>0</v>
       </c>
-      <c r="K49" s="320">
+      <c r="K49" s="319">
         <f>Data!G52</f>
         <v>0</v>
       </c>
-      <c r="L49" s="320">
+      <c r="L49" s="319">
         <f>Data!H52</f>
         <v>0</v>
       </c>
-      <c r="M49" s="320">
+      <c r="M49" s="319">
         <f>Data!I52</f>
         <v>0</v>
       </c>
-      <c r="N49" s="320">
+      <c r="N49" s="319">
         <f>Data!J52</f>
         <v>0</v>
       </c>
-      <c r="O49" s="320">
+      <c r="O49" s="319">
         <f>Data!K52</f>
         <v>0</v>
       </c>
-      <c r="P49" s="320" t="str">
+      <c r="P49" s="319" t="str">
         <f>Data!L52</f>
         <v/>
       </c>
-      <c r="Q49" s="320" t="str">
+      <c r="Q49" s="319" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -13953,47 +13959,47 @@
       </c>
       <c r="C113" s="170"/>
       <c r="E113" s="298"/>
-      <c r="G113" s="329">
+      <c r="G113" s="328">
         <f>IF(G$4="","",Data!C$22/Data!C15)</f>
         <v>1.3815926737009756</v>
       </c>
-      <c r="H113" s="329">
+      <c r="H113" s="328">
         <f>IF(H$4="","",Data!D$22/Data!D15)</f>
         <v>1.4278840297234743</v>
       </c>
-      <c r="I113" s="329">
+      <c r="I113" s="328">
         <f>IF(I$4="","",Data!E$22/Data!E15)</f>
         <v>2.018494335713656</v>
       </c>
-      <c r="J113" s="329">
+      <c r="J113" s="328">
         <f>IF(J$4="","",Data!F$22/Data!F15)</f>
         <v>2.7662579957356077</v>
       </c>
-      <c r="K113" s="329">
+      <c r="K113" s="328">
         <f>IF(K$4="","",Data!G$22/Data!G15)</f>
         <v>3.0919089083736089</v>
       </c>
-      <c r="L113" s="329">
+      <c r="L113" s="328">
         <f>IF(L$4="","",Data!H$22/Data!H15)</f>
         <v>1.9543752128021792</v>
       </c>
-      <c r="M113" s="329">
+      <c r="M113" s="328">
         <f>IF(M$4="","",Data!I$22/Data!I15)</f>
         <v>3.6274434870389731</v>
       </c>
-      <c r="N113" s="329">
+      <c r="N113" s="328">
         <f>IF(N$4="","",Data!J$22/Data!J15)</f>
         <v>16.560663477666647</v>
       </c>
-      <c r="O113" s="329">
+      <c r="O113" s="328">
         <f>IF(O$4="","",Data!K$22/Data!K15)</f>
         <v>-12.951392854876579</v>
       </c>
-      <c r="P113" s="329" t="str">
+      <c r="P113" s="328" t="str">
         <f>IF(P$4="","",Data!L$22/Data!L15)</f>
         <v/>
       </c>
-      <c r="Q113" s="329" t="str">
+      <c r="Q113" s="328" t="str">
         <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
         <v/>
       </c>
@@ -14005,47 +14011,47 @@
       </c>
       <c r="C114" s="170"/>
       <c r="E114" s="298"/>
-      <c r="G114" s="329">
+      <c r="G114" s="328">
         <f>IF(G$4="","",Data!C$22/G19)</f>
         <v>1.7851604903973288</v>
       </c>
-      <c r="H114" s="329">
+      <c r="H114" s="328">
         <f>IF(H$4="","",Data!D$22/H19)</f>
         <v>1.6914819417164388</v>
       </c>
-      <c r="I114" s="329">
+      <c r="I114" s="328">
         <f>IF(I$4="","",Data!E$22/I19)</f>
         <v>2.7239958805355302</v>
       </c>
-      <c r="J114" s="329">
+      <c r="J114" s="328">
         <f>IF(J$4="","",Data!F$22/J19)</f>
         <v>3.4716681862567911</v>
       </c>
-      <c r="K114" s="329">
+      <c r="K114" s="328">
         <f>IF(K$4="","",Data!G$22/K19)</f>
         <v>2.7106236178681997</v>
       </c>
-      <c r="L114" s="329">
+      <c r="L114" s="328">
         <f>IF(L$4="","",Data!H$22/L19)</f>
         <v>2.6053869257438653</v>
       </c>
-      <c r="M114" s="329">
+      <c r="M114" s="328">
         <f>IF(M$4="","",Data!I$22/M19)</f>
         <v>5.1767562950843287</v>
       </c>
-      <c r="N114" s="329">
+      <c r="N114" s="328">
         <f>IF(N$4="","",Data!J$22/N19)</f>
         <v>-40.213757731181175</v>
       </c>
-      <c r="O114" s="329">
+      <c r="O114" s="328">
         <f>IF(O$4="","",Data!K$22/O19)</f>
         <v>-3.6225373611160414</v>
       </c>
-      <c r="P114" s="329" t="str">
+      <c r="P114" s="328" t="str">
         <f>IF(P$4="","",Data!L$22/P19)</f>
         <v/>
       </c>
-      <c r="Q114" s="329" t="str">
+      <c r="Q114" s="328" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
         <v/>
       </c>
@@ -15339,10 +15345,10 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="354" t="s">
+      <c r="E6" s="356" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="354"/>
+      <c r="F6" s="356"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8">
@@ -15357,8 +15363,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="354"/>
-      <c r="F7" s="354"/>
+      <c r="E7" s="356"/>
+      <c r="F7" s="356"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8">
@@ -15373,8 +15379,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="354"/>
-      <c r="F8" s="354"/>
+      <c r="E8" s="356"/>
+      <c r="F8" s="356"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8">
@@ -15389,8 +15395,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="354"/>
-      <c r="F9" s="354"/>
+      <c r="E9" s="356"/>
+      <c r="F9" s="356"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -16884,11 +16890,11 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="356" t="str">
+      <c r="E7" s="358" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 東方表行集團(0398.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="356"/>
+      <c r="F7" s="358"/>
       <c r="H7" s="274">
         <v>4</v>
       </c>
@@ -16909,8 +16915,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="356"/>
-      <c r="F8" s="356"/>
+      <c r="E8" s="358"/>
+      <c r="F8" s="358"/>
       <c r="H8" s="274">
         <v>5</v>
       </c>
@@ -16931,8 +16937,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
+      <c r="E9" s="358"/>
+      <c r="F9" s="358"/>
       <c r="H9" s="274">
         <v>6</v>
       </c>
@@ -16942,8 +16948,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="356"/>
-      <c r="F10" s="356"/>
+      <c r="E10" s="358"/>
+      <c r="F10" s="358"/>
       <c r="H10" s="274">
         <v>7</v>
       </c>
@@ -16956,8 +16962,8 @@
       <c r="B11" s="160" t="s">
         <v>278</v>
       </c>
-      <c r="E11" s="356"/>
-      <c r="F11" s="356"/>
+      <c r="E11" s="358"/>
+      <c r="F11" s="358"/>
       <c r="H11" s="274">
         <v>8</v>
       </c>
@@ -16975,8 +16981,8 @@
         <v>1.2656410607081225E-2</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="356"/>
-      <c r="F12" s="356"/>
+      <c r="E12" s="358"/>
+      <c r="F12" s="358"/>
       <c r="H12" s="274">
         <v>9</v>
       </c>
@@ -16993,8 +16999,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>3.5687612277801151E-2</v>
       </c>
-      <c r="E13" s="356"/>
-      <c r="F13" s="356"/>
+      <c r="E13" s="358"/>
+      <c r="F13" s="358"/>
       <c r="H13" s="274">
         <v>10</v>
       </c>
@@ -17011,8 +17017,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>1.5957752466103425E-2</v>
       </c>
-      <c r="E14" s="356"/>
-      <c r="F14" s="356"/>
+      <c r="E14" s="358"/>
+      <c r="F14" s="358"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -17038,21 +17044,21 @@
       <c r="C18" s="151">
         <v>10</v>
       </c>
-      <c r="E18" s="356" t="s">
+      <c r="E18" s="358" t="s">
         <v>333</v>
       </c>
-      <c r="F18" s="357"/>
+      <c r="F18" s="359"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="357"/>
-      <c r="F19" s="357"/>
+      <c r="E19" s="359"/>
+      <c r="F19" s="359"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
         <v>306</v>
       </c>
-      <c r="E20" s="357"/>
-      <c r="F20" s="357"/>
+      <c r="E20" s="359"/>
+      <c r="F20" s="359"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -17066,8 +17072,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="357"/>
-      <c r="F21" s="357"/>
+      <c r="E21" s="359"/>
+      <c r="F21" s="359"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -17081,8 +17087,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="357"/>
-      <c r="F22" s="357"/>
+      <c r="E22" s="359"/>
+      <c r="F22" s="359"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
@@ -17102,8 +17108,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="355"/>
-      <c r="F25" s="355"/>
+      <c r="E25" s="357"/>
+      <c r="F25" s="357"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
@@ -17113,8 +17119,8 @@
         <v>0.04</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="355"/>
-      <c r="F26" s="355"/>
+      <c r="E26" s="357"/>
+      <c r="F26" s="357"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -17128,8 +17134,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="355"/>
-      <c r="F27" s="355"/>
+      <c r="E27" s="357"/>
+      <c r="F27" s="357"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -17139,8 +17145,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="355"/>
-      <c r="F28" s="355"/>
+      <c r="E28" s="357"/>
+      <c r="F28" s="357"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
@@ -17160,8 +17166,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="355"/>
-      <c r="F31" s="355"/>
+      <c r="E31" s="357"/>
+      <c r="F31" s="357"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
@@ -17171,8 +17177,8 @@
         <v>0.02</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="355"/>
-      <c r="F32" s="355"/>
+      <c r="E32" s="357"/>
+      <c r="F32" s="357"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -17186,8 +17192,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="355"/>
-      <c r="F33" s="355"/>
+      <c r="E33" s="357"/>
+      <c r="F33" s="357"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -17197,8 +17203,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="355"/>
-      <c r="F34" s="355"/>
+      <c r="E34" s="357"/>
+      <c r="F34" s="357"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
@@ -17218,8 +17224,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="355"/>
-      <c r="F37" s="355"/>
+      <c r="E37" s="357"/>
+      <c r="F37" s="357"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
@@ -17229,8 +17235,8 @@
         <v>0.06</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="355"/>
-      <c r="F38" s="355"/>
+      <c r="E38" s="357"/>
+      <c r="F38" s="357"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -17244,8 +17250,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="355"/>
-      <c r="F39" s="355"/>
+      <c r="E39" s="357"/>
+      <c r="F39" s="357"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -17256,8 +17262,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="355"/>
-      <c r="F40" s="355"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -17319,8 +17325,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="355"/>
-      <c r="F49" s="355"/>
+      <c r="E49" s="357"/>
+      <c r="F49" s="357"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
@@ -17330,8 +17336,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="355"/>
-      <c r="F50" s="355"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -17345,8 +17351,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="355"/>
-      <c r="F51" s="355"/>
+      <c r="E51" s="357"/>
+      <c r="F51" s="357"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -17356,8 +17362,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="355"/>
-      <c r="F52" s="355"/>
+      <c r="E52" s="357"/>
+      <c r="F52" s="357"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
@@ -17377,8 +17383,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="355"/>
-      <c r="F55" s="355"/>
+      <c r="E55" s="357"/>
+      <c r="F55" s="357"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
@@ -17388,8 +17394,8 @@
         <v>0.1</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="355"/>
-      <c r="F56" s="355"/>
+      <c r="E56" s="357"/>
+      <c r="F56" s="357"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -17403,8 +17409,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="355"/>
-      <c r="F57" s="355"/>
+      <c r="E57" s="357"/>
+      <c r="F57" s="357"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -17414,8 +17420,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="355"/>
-      <c r="F58" s="355"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -17432,7 +17438,7 @@
       <c r="E60" s="100" t="s">
         <v>299</v>
       </c>
-      <c r="F60" s="308">
+      <c r="F60" s="307">
         <f>Thesis!F28</f>
         <v>3</v>
       </c>
@@ -17546,7 +17552,7 @@
       <c r="E72" s="135" t="s">
         <v>349</v>
       </c>
-      <c r="F72" s="325">
+      <c r="F72" s="324">
         <f>BS!D89/C60</f>
         <v>0.16999421619281041</v>
       </c>
@@ -17639,7 +17645,7 @@
       <c r="E83" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F83" s="325">
+      <c r="F83" s="324">
         <f>(1-C83/C60)</f>
         <v>0.59458376580552363</v>
       </c>
@@ -17728,7 +17734,7 @@
       <c r="E93" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F93" s="325">
+      <c r="F93" s="324">
         <f>(1-C93/C60)</f>
         <v>0.3928689560570815</v>
       </c>
@@ -17738,7 +17744,7 @@
         <v>400</v>
       </c>
       <c r="G95" s="2"/>
-      <c r="H95" s="312"/>
+      <c r="H95" s="311"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
@@ -17749,7 +17755,7 @@
         <v>0.08</v>
       </c>
       <c r="G96" s="2"/>
-      <c r="H96" s="312"/>
+      <c r="H96" s="311"/>
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
@@ -17761,7 +17767,7 @@
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
-      <c r="H97" s="312"/>
+      <c r="H97" s="311"/>
     </row>
     <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
@@ -17773,7 +17779,7 @@
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
-      <c r="H98" s="312"/>
+      <c r="H98" s="311"/>
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="111" t="s">
@@ -17789,7 +17795,7 @@
       <c r="E99" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F99" s="325">
+      <c r="F99" s="324">
         <f>(1-C99/C60)</f>
         <v>0.13969393804894004</v>
       </c>
@@ -17845,7 +17851,7 @@
       <c r="E105" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F105" s="325">
+      <c r="F105" s="324">
         <f>(1-C105/C66)</f>
         <v>0.22106689885075603</v>
       </c>
@@ -17854,32 +17860,32 @@
       <c r="B106" s="100"/>
     </row>
     <row r="107" spans="2:8" ht="14.65">
-      <c r="E107" s="316" t="s">
+      <c r="E107" s="315" t="s">
         <v>327</v>
       </c>
-      <c r="F107" s="313"/>
+      <c r="F107" s="312"/>
     </row>
     <row r="108" spans="2:8" ht="13.9">
-      <c r="E108" s="309" t="s">
+      <c r="E108" s="308" t="s">
         <v>328</v>
       </c>
-      <c r="F108" s="314" t="s">
+      <c r="F108" s="313" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="13.9">
-      <c r="E109" s="310" t="s">
+      <c r="E109" s="309" t="s">
         <v>328</v>
       </c>
-      <c r="F109" s="314" t="s">
+      <c r="F109" s="313" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="110" spans="2:8" ht="13.9">
-      <c r="E110" s="311" t="s">
+      <c r="E110" s="310" t="s">
         <v>328</v>
       </c>
-      <c r="F110" s="315" t="s">
+      <c r="F110" s="314" t="s">
         <v>331</v>
       </c>
     </row>

--- a/financial_models/opportunities/0398.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0398.HK_Valuation.xlsx
@@ -8,28 +8,28 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AC23400-E9E3-404D-A5A4-5C8C75A489A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B521658-F3B2-40D3-9E84-266B7FF2CB71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
     <sheet name="Data" sheetId="4" r:id="rId2"/>
     <sheet name="BS" sheetId="3" r:id="rId3"/>
     <sheet name="Normalized_FCF" sheetId="2" r:id="rId4"/>
-    <sheet name="Valuation_Model" sheetId="8" r:id="rId5"/>
+    <sheet name="DCF" sheetId="8" r:id="rId5"/>
     <sheet name="Scenarios" sheetId="9" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Valuation_Model!$B$73:$H$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
-    <definedName name="Equity_Cost">Valuation_Model!$C$5</definedName>
+    <definedName name="Equity_Cost">DCF!$C$5</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
     <definedName name="Reporting_currency">Thesis!$C$25</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
-    <definedName name="Terminal_Growth">Valuation_Model!$F$4</definedName>
+    <definedName name="Terminal_Growth">DCF!$F$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -4909,7 +4909,7 @@
         <v>283</v>
       </c>
       <c r="C87" s="248">
-        <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>3.5495317175460563</v>
       </c>
       <c r="D87" s="1" t="str">
@@ -4963,7 +4963,7 @@
         <v>256</v>
       </c>
       <c r="C96" s="188">
-        <f>Valuation_Model!C7</f>
+        <f>DCF!C7</f>
         <v>195066</v>
       </c>
       <c r="D96" s="1" t="str">
@@ -5034,7 +5034,7 @@
         <v>267</v>
       </c>
       <c r="C104" s="188">
-        <f>Valuation_Model!C8</f>
+        <f>DCF!C8</f>
         <v>587281.82009631116</v>
       </c>
       <c r="D104" s="1" t="str">
@@ -5065,7 +5065,7 @@
         <v>258</v>
       </c>
       <c r="C108" s="188">
-        <f>Valuation_Model!C9</f>
+        <f>DCF!C9</f>
         <v>18907.900000000001</v>
       </c>
       <c r="D108" s="1" t="str">
@@ -5100,7 +5100,7 @@
         <v>282</v>
       </c>
       <c r="C113" s="248">
-        <f>Valuation_Model!C12</f>
+        <f>DCF!C12</f>
         <v>4.3931077563825554</v>
       </c>
       <c r="D113" s="1" t="str">
@@ -5159,111 +5159,111 @@
     </row>
     <row r="121" spans="1:6">
       <c r="B121" s="253" t="str">
-        <f>Valuation_Model!B74</f>
+        <f>DCF!B74</f>
         <v>Snowball Scenario</v>
       </c>
       <c r="C121" s="254">
-        <f>Valuation_Model!C74</f>
+        <f>DCF!C74</f>
         <v>0.1</v>
       </c>
       <c r="D121" s="255">
-        <f>Valuation_Model!D74</f>
+        <f>DCF!D74</f>
         <v>15</v>
       </c>
       <c r="E121" s="256" t="str">
-        <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E74,2)&amp;" "&amp;Market_currency</f>
         <v>7.02 HKD</v>
       </c>
       <c r="F121" s="257">
-        <f>Valuation_Model!F74</f>
+        <f>DCF!F74</f>
         <v>0.05</v>
       </c>
     </row>
     <row r="122" spans="1:6">
       <c r="B122" s="242" t="str">
-        <f>Valuation_Model!B75</f>
+        <f>DCF!B75</f>
         <v>Optimistic</v>
       </c>
       <c r="C122" s="243">
-        <f>Valuation_Model!C75</f>
+        <f>DCF!C75</f>
         <v>0.06</v>
       </c>
       <c r="D122" s="244">
-        <f>Valuation_Model!D75</f>
+        <f>DCF!D75</f>
         <v>10</v>
       </c>
       <c r="E122" s="245" t="str">
-        <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E75,2)&amp;" "&amp;Market_currency</f>
         <v>5.15 HKD</v>
       </c>
       <c r="F122" s="246">
-        <f>Valuation_Model!F75</f>
+        <f>DCF!F75</f>
         <v>0.18</v>
       </c>
     </row>
     <row r="123" spans="1:6">
       <c r="B123" s="242" t="str">
-        <f>Valuation_Model!B76</f>
+        <f>DCF!B76</f>
         <v>Base</v>
       </c>
       <c r="C123" s="243">
-        <f>Valuation_Model!C76</f>
+        <f>DCF!C76</f>
         <v>0.04</v>
       </c>
       <c r="D123" s="244">
-        <f>Valuation_Model!D76</f>
+        <f>DCF!D76</f>
         <v>10</v>
       </c>
       <c r="E123" s="245" t="str">
-        <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E76,2)&amp;" "&amp;Market_currency</f>
         <v>4.87 HKD</v>
       </c>
       <c r="F123" s="246">
-        <f>Valuation_Model!F76</f>
+        <f>DCF!F76</f>
         <v>0.53999999999999992</v>
       </c>
     </row>
     <row r="124" spans="1:6">
       <c r="B124" s="242" t="str">
-        <f>Valuation_Model!B77</f>
+        <f>DCF!B77</f>
         <v>Pessimistic</v>
       </c>
       <c r="C124" s="243">
-        <f>Valuation_Model!C77</f>
+        <f>DCF!C77</f>
         <v>0.02</v>
       </c>
       <c r="D124" s="244">
-        <f>Valuation_Model!D77</f>
+        <f>DCF!D77</f>
         <v>10</v>
       </c>
       <c r="E124" s="245" t="str">
-        <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E77,2)&amp;" "&amp;Market_currency</f>
         <v>4.62 HKD</v>
       </c>
       <c r="F124" s="246">
-        <f>Valuation_Model!F77</f>
+        <f>DCF!F77</f>
         <v>0.18</v>
       </c>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="242" t="str">
-        <f>Valuation_Model!B78</f>
+        <f>DCF!B78</f>
         <v>Devil's advocate</v>
       </c>
       <c r="C125" s="243">
-        <f>Valuation_Model!C78</f>
+        <f>DCF!C78</f>
         <v>0</v>
       </c>
       <c r="D125" s="244">
-        <f>Valuation_Model!D78</f>
+        <f>DCF!D78</f>
         <v>15</v>
       </c>
       <c r="E125" s="245" t="str">
-        <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E78,2)&amp;" "&amp;Market_currency</f>
         <v>4.39 HKD</v>
       </c>
       <c r="F125" s="246">
-        <f>Valuation_Model!F78</f>
+        <f>DCF!F78</f>
         <v>0.05</v>
       </c>
     </row>
@@ -9530,7 +9530,7 @@
         <v>289</v>
       </c>
       <c r="C86" s="188">
-        <f>-Valuation_Model!C7*Exchange_Rate</f>
+        <f>-DCF!C7*Exchange_Rate</f>
         <v>-195066</v>
       </c>
       <c r="D86" s="248">
@@ -9547,7 +9547,7 @@
         <v>290</v>
       </c>
       <c r="C87" s="188">
-        <f>Valuation_Model!C8*Exchange_Rate</f>
+        <f>DCF!C8*Exchange_Rate</f>
         <v>587281.82009631116</v>
       </c>
       <c r="D87" s="248">
@@ -9564,7 +9564,7 @@
         <v>190</v>
       </c>
       <c r="C88" s="188">
-        <f>Valuation_Model!C9*Exchange_Rate</f>
+        <f>DCF!C9*Exchange_Rate</f>
         <v>18907.900000000001</v>
       </c>
       <c r="D88" s="248">
@@ -15524,7 +15524,7 @@
         <v>144837.043127613</v>
       </c>
       <c r="D21" s="139">
-        <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B21,0,DCF!$C$16)</f>
         <v>4.6574870890079501E-2</v>
       </c>
       <c r="E21" s="125">
@@ -15546,7 +15546,7 @@
         <v>151582.80971138246</v>
       </c>
       <c r="D22" s="139">
-        <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B22,0,DCF!$C$16)</f>
         <v>4.6574870890079501E-2</v>
       </c>
       <c r="E22" s="125">
@@ -15568,7 +15568,7 @@
         <v>158642.75950284558</v>
       </c>
       <c r="D23" s="139">
-        <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B23,0,DCF!$C$16)</f>
         <v>4.6574870890079501E-2</v>
       </c>
       <c r="E23" s="125">
@@ -15590,7 +15590,7 @@
         <v>166031.52554433656</v>
       </c>
       <c r="D24" s="139">
-        <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B24,0,DCF!$C$16)</f>
         <v>4.6574870890079501E-2</v>
       </c>
       <c r="E24" s="125">
@@ -15612,7 +15612,7 @@
         <v>173764.422410247</v>
       </c>
       <c r="D25" s="139">
-        <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B25,0,DCF!$C$16)</f>
         <v>4.6574870890079501E-2</v>
       </c>
       <c r="E25" s="125">
@@ -15634,7 +15634,7 @@
         <v>181857.47794929348</v>
       </c>
       <c r="D26" s="139">
-        <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B26,0,DCF!$C$16)</f>
         <v>4.6574870890079501E-2</v>
       </c>
       <c r="E26" s="125">
@@ -15656,7 +15656,7 @@
         <v>190327.46650517735</v>
       </c>
       <c r="D27" s="139">
-        <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B27,0,DCF!$C$16)</f>
         <v>4.6574870890079501E-2</v>
       </c>
       <c r="E27" s="125">
@@ -15678,7 +15678,7 @@
         <v>199191.94368449191</v>
       </c>
       <c r="D28" s="139">
-        <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B28,0,DCF!$C$16)</f>
         <v>4.6574870890079501E-2</v>
       </c>
       <c r="E28" s="125">
@@ -15700,7 +15700,7 @@
         <v>208469.28274394112</v>
       </c>
       <c r="D29" s="139">
-        <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B29,0,DCF!$C$16)</f>
         <v>4.6574870890079501E-2</v>
       </c>
       <c r="E29" s="125">
@@ -15722,7 +15722,7 @@
         <v>218178.71267228766</v>
       </c>
       <c r="D30" s="139">
-        <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B30,0,DCF!$C$16)</f>
         <v>4.6574870890079501E-2</v>
       </c>
       <c r="E30" s="125">
@@ -15744,7 +15744,7 @@
         <v>0</v>
       </c>
       <c r="D31" s="139">
-        <f>IF($C$17&lt;B31,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B31,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E31" s="125">
@@ -15766,7 +15766,7 @@
         <v>0</v>
       </c>
       <c r="D32" s="139">
-        <f>IF($C$17&lt;B32,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B32,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E32" s="125">
@@ -15788,7 +15788,7 @@
         <v>0</v>
       </c>
       <c r="D33" s="139">
-        <f>IF($C$17&lt;B33,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B33,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E33" s="125">
@@ -15810,7 +15810,7 @@
         <v>0</v>
       </c>
       <c r="D34" s="139">
-        <f>IF($C$17&lt;B34,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B34,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E34" s="125">
@@ -15832,7 +15832,7 @@
         <v>0</v>
       </c>
       <c r="D35" s="139">
-        <f>IF($C$17&lt;B35,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B35,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E35" s="125">
@@ -15854,7 +15854,7 @@
         <v>0</v>
       </c>
       <c r="D36" s="139">
-        <f>IF($C$17&lt;B36,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B36,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E36" s="125">
@@ -15876,7 +15876,7 @@
         <v>0</v>
       </c>
       <c r="D37" s="139">
-        <f>IF($C$17&lt;B37,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B37,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E37" s="125">
@@ -15898,7 +15898,7 @@
         <v>0</v>
       </c>
       <c r="D38" s="139">
-        <f>IF($C$17&lt;B38,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B38,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E38" s="125">
@@ -15920,7 +15920,7 @@
         <v>0</v>
       </c>
       <c r="D39" s="139">
-        <f>IF($C$17&lt;B39,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B39,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E39" s="125">
@@ -15942,7 +15942,7 @@
         <v>0</v>
       </c>
       <c r="D40" s="139">
-        <f>IF($C$17&lt;B40,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B40,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E40" s="125">
@@ -15964,7 +15964,7 @@
         <v>0</v>
       </c>
       <c r="D41" s="139">
-        <f>IF($C$17&lt;B41,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B41,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E41" s="125">
@@ -15986,7 +15986,7 @@
         <v>0</v>
       </c>
       <c r="D42" s="139">
-        <f>IF($C$17&lt;B42,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B42,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E42" s="125">
@@ -16008,7 +16008,7 @@
         <v>0</v>
       </c>
       <c r="D43" s="139">
-        <f>IF($C$17&lt;B43,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B43,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E43" s="125">
@@ -16030,7 +16030,7 @@
         <v>0</v>
       </c>
       <c r="D44" s="139">
-        <f>IF($C$17&lt;B44,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B44,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E44" s="125">
@@ -16052,7 +16052,7 @@
         <v>0</v>
       </c>
       <c r="D45" s="139">
-        <f>IF($C$17&lt;B45,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B45,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E45" s="125">
@@ -16074,7 +16074,7 @@
         <v>0</v>
       </c>
       <c r="D46" s="139">
-        <f>IF($C$17&lt;B46,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B46,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E46" s="125">
@@ -16096,7 +16096,7 @@
         <v>0</v>
       </c>
       <c r="D47" s="139">
-        <f>IF($C$17&lt;B47,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B47,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E47" s="125">
@@ -16118,7 +16118,7 @@
         <v>0</v>
       </c>
       <c r="D48" s="139">
-        <f>IF($C$17&lt;B48,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B48,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E48" s="125">
@@ -16140,7 +16140,7 @@
         <v>0</v>
       </c>
       <c r="D49" s="139">
-        <f>IF($C$17&lt;B49,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B49,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E49" s="125">
@@ -16162,7 +16162,7 @@
         <v>0</v>
       </c>
       <c r="D50" s="139">
-        <f>IF($C$17&lt;B50,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B50,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E50" s="125">
@@ -16863,7 +16863,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="107">
-        <f>Valuation_Model!C3</f>
+        <f>DCF!C3</f>
         <v>1000</v>
       </c>
       <c r="E6" s="100" t="s">
@@ -17080,7 +17080,7 @@
         <v>280</v>
       </c>
       <c r="C22" s="161">
-        <f>Valuation_Model!C12</f>
+        <f>DCF!C12</f>
         <v>4.3931077563825554</v>
       </c>
       <c r="D22" t="str">
@@ -17127,7 +17127,7 @@
         <v>114</v>
       </c>
       <c r="C27" s="161">
-        <f>Valuation_Model!E76</f>
+        <f>DCF!E76</f>
         <v>4.874392451442584</v>
       </c>
       <c r="D27" s="161" t="str">
@@ -17185,7 +17185,7 @@
         <v>114</v>
       </c>
       <c r="C33" s="161">
-        <f>Valuation_Model!E77</f>
+        <f>DCF!E77</f>
         <v>4.6222661652764234</v>
       </c>
       <c r="D33" t="str">
@@ -17243,7 +17243,7 @@
         <v>114</v>
       </c>
       <c r="C39" s="161">
-        <f>Valuation_Model!E75</f>
+        <f>DCF!E75</f>
         <v>5.1522353664999905</v>
       </c>
       <c r="D39" t="str">
@@ -17344,7 +17344,7 @@
         <v>114</v>
       </c>
       <c r="C51" s="161">
-        <f>Valuation_Model!E78</f>
+        <f>DCF!E78</f>
         <v>4.3931077563825536</v>
       </c>
       <c r="D51" t="str">
@@ -17402,7 +17402,7 @@
         <v>114</v>
       </c>
       <c r="C57" s="161">
-        <f>Valuation_Model!E74</f>
+        <f>DCF!E74</f>
         <v>7.0228647583946318</v>
       </c>
       <c r="D57" t="str">
@@ -17490,7 +17490,7 @@
         <v>103</v>
       </c>
       <c r="C66" s="161">
-        <f>Valuation_Model!C18</f>
+        <f>DCF!C18</f>
         <v>4.9627512619545433</v>
       </c>
       <c r="D66" s="161" t="str">

--- a/financial_models/opportunities/0398.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0398.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B521658-F3B2-40D3-9E84-266B7FF2CB71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C70721C-3A79-4C1D-890A-7BB0607DA09E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/financial_models/opportunities/0398.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0398.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C70721C-3A79-4C1D-890A-7BB0607DA09E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C3B05BB-A551-4219-99E0-7F5F3EBB9C03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -18,18 +18,21 @@
     <sheet name="BS" sheetId="3" r:id="rId3"/>
     <sheet name="Normalized_FCF" sheetId="2" r:id="rId4"/>
     <sheet name="DCF" sheetId="8" r:id="rId5"/>
-    <sheet name="Scenarios" sheetId="9" r:id="rId6"/>
+    <sheet name="DDM" sheetId="10" r:id="rId6"/>
+    <sheet name="Scenarios" sheetId="9" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DDM!$B$68:$H$68</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
-    <definedName name="Equity_Cost">DCF!$C$5</definedName>
+    <definedName name="Equity_Cost">Thesis!$C$80</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
     <definedName name="Reporting_currency">Thesis!$C$25</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
-    <definedName name="Terminal_Growth">DCF!$F$4</definedName>
+    <definedName name="Terminal_Growth">Thesis!$C$86</definedName>
+    <definedName name="valuation_method">Thesis!$E$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="461">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1374,10 +1377,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>CAGR</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Market Price</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1387,10 +1386,6 @@
   </si>
   <si>
     <t>Prompt for fundamental Analysis</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>No Growth Equity Value per share =</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2407,28 +2402,58 @@
     <t>Benchmark yield</t>
   </si>
   <si>
+    <t>Valuation Method</t>
+  </si>
+  <si>
+    <t>Dividend</t>
+  </si>
+  <si>
+    <t>Dividend Value</t>
+  </si>
+  <si>
+    <t>No-Growth DDM</t>
+  </si>
+  <si>
+    <t>No-Growth DDM Valuation</t>
+  </si>
+  <si>
+    <t>Dividend Value per share</t>
+  </si>
+  <si>
+    <t>PV of Dividends</t>
+  </si>
+  <si>
+    <t>Dividends</t>
+  </si>
+  <si>
+    <t>YoY CAGR</t>
+  </si>
+  <si>
+    <t>Payout Ratio:</t>
+  </si>
+  <si>
+    <t>No Growth Equity Value per share =</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>東方表行集團</t>
+  </si>
+  <si>
+    <t>0398.HK</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>CNS_05</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
     <t>DCF</t>
-  </si>
-  <si>
-    <t>Valuation Method</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>東方表行集團</t>
-  </si>
-  <si>
-    <t>0398.HK</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>CNS_05</t>
-  </si>
-  <si>
-    <t>N</t>
   </si>
   <si>
     <t>Latest Asset Value</t>
@@ -2444,7 +2469,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="18">
+  <numFmts count="19">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0.00&quot;x&quot;"/>
@@ -2463,6 +2488,7 @@
     <numFmt numFmtId="179" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
     <numFmt numFmtId="180" formatCode="0.0\x"/>
     <numFmt numFmtId="181" formatCode="0\x"/>
+    <numFmt numFmtId="182" formatCode="0.000000000000000%"/>
   </numFmts>
   <fonts count="59">
     <font>
@@ -3111,7 +3137,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="360">
+  <cellXfs count="362">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3617,9 +3643,6 @@
     <xf numFmtId="175" fontId="43" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="39" fontId="42" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="10" fontId="42" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3836,29 +3859,36 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="9" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3877,7 +3907,21 @@
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="8">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -3924,8 +3968,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF0000"/>
       <color rgb="FF0000FF"/>
-      <color rgb="FFFF0000"/>
       <color rgb="FF003871"/>
       <color rgb="FF005078"/>
       <color rgb="FF002850"/>
@@ -4166,15 +4210,15 @@
         <v>45786</v>
       </c>
       <c r="D1" s="52"/>
-      <c r="E1" s="325" t="s">
-        <v>356</v>
-      </c>
-      <c r="F1" s="281" t="s">
-        <v>444</v>
+      <c r="E1" s="324" t="s">
+        <v>354</v>
+      </c>
+      <c r="F1" s="280" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
-      <c r="A2" s="247" t="s">
+      <c r="A2" s="246" t="s">
         <v>268</v>
       </c>
       <c r="B2" s="36"/>
@@ -4189,7 +4233,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4198,10 +4242,10 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="C5" s="327" t="s">
-        <v>445</v>
+        <v>316</v>
+      </c>
+      <c r="C5" s="326" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4215,9 +4259,9 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="C7" s="277">
+        <v>308</v>
+      </c>
+      <c r="C7" s="276">
         <v>6</v>
       </c>
       <c r="D7" s="48"/>
@@ -4238,20 +4282,20 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4267,17 +4311,17 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
@@ -4291,7 +4335,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
@@ -4318,73 +4362,77 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B18" s="348" t="s">
-        <v>362</v>
-      </c>
-      <c r="C18" s="348"/>
-      <c r="D18" s="348"/>
-      <c r="E18" s="348"/>
-      <c r="F18" s="348"/>
+      <c r="B18" s="352" t="s">
+        <v>360</v>
+      </c>
+      <c r="C18" s="352"/>
+      <c r="D18" s="352"/>
+      <c r="E18" s="352"/>
+      <c r="F18" s="352"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
         <v xml:space="preserve">Low Growth </v>
       </c>
-      <c r="E21" s="5"/>
+      <c r="D21" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="E21" s="342" t="s">
+        <v>457</v>
+      </c>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>448</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="E22" s="343" t="s">
-        <v>442</v>
-      </c>
+        <v>455</v>
+      </c>
+      <c r="D22" s="1" t="str">
+        <f>IF(valuation_method="DDM","DDM Terminal Value","")</f>
+        <v/>
+      </c>
+      <c r="E22" s="347"/>
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="C23" s="291" t="s">
-        <v>449</v>
+        <v>435</v>
+      </c>
+      <c r="C23" s="290" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="C24" s="291" t="s">
-        <v>449</v>
+        <v>436</v>
+      </c>
+      <c r="C24" s="290" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C25" s="48" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D25" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
         <v/>
       </c>
-      <c r="E25" s="334" t="str">
+      <c r="E25" s="333" t="str">
         <f>IF(D11="","",1/Exchange_Rate*D16)</f>
         <v/>
       </c>
@@ -4394,14 +4442,14 @@
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (HKD) :</v>
       </c>
-      <c r="C26" s="339">
+      <c r="C26" s="338">
         <f>C127</f>
         <v>4.9623808252376094</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="E26" s="336">
+        <v>400</v>
+      </c>
+      <c r="E26" s="335">
         <f ca="1">Scenarios!C87</f>
         <v>0.14834835832623461</v>
       </c>
@@ -4412,96 +4460,96 @@
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
-        <v>436</v>
-      </c>
-      <c r="C28" s="344" t="str">
+        <v>434</v>
+      </c>
+      <c r="C28" s="343" t="str">
         <f>C140&amp;" ("&amp;Market_currency&amp;")"</f>
         <v>0398.HK (HKD)</v>
       </c>
-      <c r="D28" s="344" t="str">
+      <c r="D28" s="343" t="str">
         <f>IF(D11="","",D140&amp;" ("&amp;D13&amp;")")</f>
         <v/>
       </c>
-      <c r="E28" s="340" t="s">
-        <v>432</v>
-      </c>
-      <c r="F28" s="338">
+      <c r="E28" s="339" t="s">
+        <v>430</v>
+      </c>
+      <c r="F28" s="337">
         <v>3</v>
       </c>
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="C29" s="345">
+        <v>426</v>
+      </c>
+      <c r="C29" s="344">
         <f>C144</f>
         <v>2.0118297468067095</v>
       </c>
-      <c r="D29" s="345" t="str">
+      <c r="D29" s="344" t="str">
         <f>D144</f>
         <v/>
       </c>
-      <c r="E29" s="341" t="s">
-        <v>427</v>
-      </c>
-      <c r="F29" s="337">
+      <c r="E29" s="340" t="s">
+        <v>425</v>
+      </c>
+      <c r="F29" s="336">
         <v>0.4</v>
       </c>
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="C30" s="346">
+        <v>427</v>
+      </c>
+      <c r="C30" s="345">
         <f>C152</f>
         <v>3.012815450868831</v>
       </c>
-      <c r="D30" s="346" t="str">
+      <c r="D30" s="345" t="str">
         <f>D152</f>
         <v/>
       </c>
-      <c r="E30" s="342" t="s">
-        <v>440</v>
-      </c>
-      <c r="F30" s="347">
+      <c r="E30" s="341" t="s">
+        <v>438</v>
+      </c>
+      <c r="F30" s="346">
         <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="C31" s="346">
+        <v>428</v>
+      </c>
+      <c r="C31" s="345">
         <f>C160</f>
         <v>4.2691663056616189</v>
       </c>
-      <c r="D31" s="346" t="str">
+      <c r="D31" s="345" t="str">
         <f>D160</f>
         <v/>
       </c>
-      <c r="E31" s="342" t="s">
-        <v>439</v>
-      </c>
-      <c r="F31" s="347">
+      <c r="E31" s="341" t="s">
+        <v>437</v>
+      </c>
+      <c r="F31" s="346">
         <v>0.08</v>
       </c>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="C32" s="346">
+        <v>429</v>
+      </c>
+      <c r="C32" s="345">
         <f>C168</f>
         <v>3.8656512307065762</v>
       </c>
-      <c r="D32" s="346" t="str">
+      <c r="D32" s="345" t="str">
         <f>D168</f>
         <v/>
       </c>
-      <c r="E32" s="342" t="s">
-        <v>441</v>
-      </c>
-      <c r="F32" s="347">
+      <c r="E32" s="341" t="s">
+        <v>439</v>
+      </c>
+      <c r="F32" s="346">
         <v>0.1174</v>
       </c>
     </row>
@@ -4510,8 +4558,8 @@
       <c r="E33" s="5"/>
     </row>
     <row r="34" spans="1:6" ht="13.9">
-      <c r="A34" s="247" t="s">
-        <v>357</v>
+      <c r="A34" s="246" t="s">
+        <v>355</v>
       </c>
       <c r="B34" s="36"/>
       <c r="C34" s="36"/>
@@ -4520,22 +4568,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B36" s="348" t="s">
-        <v>363</v>
-      </c>
-      <c r="C36" s="348"/>
-      <c r="D36" s="348"/>
-      <c r="E36" s="348"/>
-      <c r="F36" s="348"/>
+      <c r="B36" s="352" t="s">
+        <v>361</v>
+      </c>
+      <c r="C36" s="352"/>
+      <c r="D36" s="352"/>
+      <c r="E36" s="352"/>
+      <c r="F36" s="352"/>
     </row>
     <row r="37" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B37" s="350" t="s">
-        <v>342</v>
-      </c>
-      <c r="C37" s="350"/>
-      <c r="D37" s="350"/>
-      <c r="E37" s="350"/>
-      <c r="F37" s="350"/>
+      <c r="B37" s="355" t="s">
+        <v>340</v>
+      </c>
+      <c r="C37" s="355"/>
+      <c r="D37" s="355"/>
+      <c r="E37" s="355"/>
+      <c r="F37" s="355"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="234" t="s">
@@ -4547,13 +4595,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B40" s="349" t="s">
+      <c r="B40" s="353" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="349"/>
-      <c r="D40" s="349"/>
-      <c r="E40" s="349"/>
-      <c r="F40" s="349"/>
+      <c r="C40" s="353"/>
+      <c r="D40" s="353"/>
+      <c r="E40" s="353"/>
+      <c r="F40" s="353"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4573,13 +4621,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B43" s="349" t="s">
+      <c r="B43" s="353" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="349"/>
-      <c r="D43" s="349"/>
-      <c r="E43" s="349"/>
-      <c r="F43" s="349"/>
+      <c r="C43" s="353"/>
+      <c r="D43" s="353"/>
+      <c r="E43" s="353"/>
+      <c r="F43" s="353"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4608,13 +4656,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="349" t="s">
+      <c r="B47" s="353" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="349"/>
-      <c r="D47" s="349"/>
-      <c r="E47" s="349"/>
-      <c r="F47" s="349"/>
+      <c r="C47" s="353"/>
+      <c r="D47" s="353"/>
+      <c r="E47" s="353"/>
+      <c r="F47" s="353"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4630,19 +4678,19 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="349" t="s">
+      <c r="B50" s="353" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="349"/>
-      <c r="D50" s="349"/>
-      <c r="E50" s="349"/>
-      <c r="F50" s="349"/>
+      <c r="C50" s="353"/>
+      <c r="D50" s="353"/>
+      <c r="E50" s="353"/>
+      <c r="F50" s="353"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
-        <v>343</v>
-      </c>
-      <c r="C51" s="317">
+        <v>341</v>
+      </c>
+      <c r="C51" s="316">
         <f>Normalized_FCF!C48</f>
         <v>0</v>
       </c>
@@ -4650,14 +4698,14 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="316"/>
-      <c r="F51" s="316"/>
+      <c r="E51" s="315"/>
+      <c r="F51" s="315"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
-        <v>344</v>
-      </c>
-      <c r="C52" s="317">
+        <v>342</v>
+      </c>
+      <c r="C52" s="316">
         <f>Normalized_FCF!C47</f>
         <v>-13663</v>
       </c>
@@ -4665,8 +4713,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E52" s="316"/>
-      <c r="F52" s="316"/>
+      <c r="E52" s="315"/>
+      <c r="F52" s="315"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4700,13 +4748,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="349" t="s">
+      <c r="B58" s="353" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="349"/>
-      <c r="D58" s="349"/>
-      <c r="E58" s="349"/>
-      <c r="F58" s="349"/>
+      <c r="C58" s="353"/>
+      <c r="D58" s="353"/>
+      <c r="E58" s="353"/>
+      <c r="F58" s="353"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4722,13 +4770,13 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="349" t="s">
-        <v>341</v>
-      </c>
-      <c r="C61" s="352"/>
-      <c r="D61" s="352"/>
-      <c r="E61" s="352"/>
-      <c r="F61" s="352"/>
+      <c r="B61" s="353" t="s">
+        <v>339</v>
+      </c>
+      <c r="C61" s="354"/>
+      <c r="D61" s="354"/>
+      <c r="E61" s="354"/>
+      <c r="F61" s="354"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -4744,22 +4792,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B64" s="348" t="s">
-        <v>346</v>
-      </c>
-      <c r="C64" s="348"/>
-      <c r="D64" s="348"/>
-      <c r="E64" s="348"/>
-      <c r="F64" s="348"/>
+      <c r="B64" s="352" t="s">
+        <v>344</v>
+      </c>
+      <c r="C64" s="352"/>
+      <c r="D64" s="352"/>
+      <c r="E64" s="352"/>
+      <c r="F64" s="352"/>
     </row>
     <row r="65" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B65" s="348" t="s">
-        <v>364</v>
-      </c>
-      <c r="C65" s="348"/>
-      <c r="D65" s="348"/>
-      <c r="E65" s="348"/>
-      <c r="F65" s="348"/>
+      <c r="B65" s="352" t="s">
+        <v>362</v>
+      </c>
+      <c r="C65" s="352"/>
+      <c r="D65" s="352"/>
+      <c r="E65" s="352"/>
+      <c r="F65" s="352"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4788,26 +4836,34 @@
       </c>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="252" t="s">
-        <v>393</v>
+      <c r="B69" s="251" t="s">
+        <v>391</v>
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
         <v>7.9541327003833207E-2</v>
       </c>
+      <c r="F69" s="348"/>
     </row>
     <row r="70" spans="1:6">
-      <c r="B70" s="252" t="s">
-        <v>311</v>
+      <c r="B70" s="251" t="s">
+        <v>309</v>
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
         <v>3.5854341736694682E-2</v>
       </c>
+      <c r="E70" s="47" t="s">
+        <v>449</v>
+      </c>
+      <c r="F70" s="349">
+        <f>Normalized_FCF!C92</f>
+        <v>0.45076368583801485</v>
+      </c>
     </row>
     <row r="72" spans="1:6" ht="13.9">
-      <c r="A72" s="247" t="s">
-        <v>358</v>
+      <c r="A72" s="246" t="s">
+        <v>356</v>
       </c>
       <c r="B72" s="36"/>
       <c r="C72" s="36"/>
@@ -4820,22 +4876,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="348" t="s">
-        <v>365</v>
-      </c>
-      <c r="C74" s="348"/>
-      <c r="D74" s="348"/>
-      <c r="E74" s="348"/>
-      <c r="F74" s="348"/>
+      <c r="B74" s="352" t="s">
+        <v>363</v>
+      </c>
+      <c r="C74" s="352"/>
+      <c r="D74" s="352"/>
+      <c r="E74" s="352"/>
+      <c r="F74" s="352"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="350" t="s">
+      <c r="B75" s="355" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="350"/>
-      <c r="D75" s="350"/>
-      <c r="E75" s="350"/>
-      <c r="F75" s="350"/>
+      <c r="C75" s="355"/>
+      <c r="D75" s="355"/>
+      <c r="E75" s="355"/>
+      <c r="F75" s="355"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="234" t="s">
@@ -4844,7 +4900,7 @@
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C78" s="92">
         <f>F31</f>
@@ -4853,7 +4909,7 @@
     </row>
     <row r="79" spans="1:6">
       <c r="B79" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C79" s="92">
         <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
@@ -4864,7 +4920,7 @@
       <c r="B80" s="80" t="s">
         <v>248</v>
       </c>
-      <c r="C80" s="261">
+      <c r="C80" s="260">
         <f>F31+C79</f>
         <v>0.08</v>
       </c>
@@ -4873,42 +4929,42 @@
       <c r="C81" s="122"/>
     </row>
     <row r="82" spans="1:6">
-      <c r="B82" s="326" t="s">
-        <v>359</v>
+      <c r="B82" s="325" t="s">
+        <v>357</v>
       </c>
       <c r="C82" s="122"/>
     </row>
     <row r="83" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B83" s="348" t="s">
-        <v>366</v>
-      </c>
-      <c r="C83" s="348"/>
-      <c r="D83" s="348"/>
-      <c r="E83" s="348"/>
-      <c r="F83" s="348"/>
+      <c r="B83" s="352" t="s">
+        <v>364</v>
+      </c>
+      <c r="C83" s="352"/>
+      <c r="D83" s="352"/>
+      <c r="E83" s="352"/>
+      <c r="F83" s="352"/>
     </row>
     <row r="84" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B84" s="348" t="s">
-        <v>367</v>
-      </c>
-      <c r="C84" s="348"/>
-      <c r="D84" s="348"/>
-      <c r="E84" s="348"/>
-      <c r="F84" s="348"/>
+      <c r="B84" s="352" t="s">
+        <v>365</v>
+      </c>
+      <c r="C84" s="352"/>
+      <c r="D84" s="352"/>
+      <c r="E84" s="352"/>
+      <c r="F84" s="352"/>
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
         <v>252</v>
       </c>
-      <c r="C86" s="261">
+      <c r="C86" s="260">
         <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="47" t="s">
-        <v>283</v>
-      </c>
-      <c r="C87" s="248">
+        <v>281</v>
+      </c>
+      <c r="C87" s="247">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>3.5495317175460563</v>
       </c>
@@ -4918,8 +4974,8 @@
       </c>
     </row>
     <row r="89" spans="1:6" ht="13.9">
-      <c r="A89" s="247" t="s">
-        <v>360</v>
+      <c r="A89" s="246" t="s">
+        <v>358</v>
       </c>
       <c r="B89" s="36"/>
       <c r="C89" s="36"/>
@@ -4931,13 +4987,13 @@
       <c r="A90" s="233"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="B91" s="348" t="s">
-        <v>368</v>
-      </c>
-      <c r="C91" s="348"/>
-      <c r="D91" s="348"/>
-      <c r="E91" s="348"/>
-      <c r="F91" s="348"/>
+      <c r="B91" s="352" t="s">
+        <v>366</v>
+      </c>
+      <c r="C91" s="352"/>
+      <c r="D91" s="352"/>
+      <c r="E91" s="352"/>
+      <c r="F91" s="352"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
@@ -4950,13 +5006,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B95" s="348" t="s">
-        <v>347</v>
-      </c>
-      <c r="C95" s="348"/>
-      <c r="D95" s="348"/>
-      <c r="E95" s="348"/>
-      <c r="F95" s="348"/>
+      <c r="B95" s="352" t="s">
+        <v>345</v>
+      </c>
+      <c r="C95" s="352"/>
+      <c r="D95" s="352"/>
+      <c r="E95" s="352"/>
+      <c r="F95" s="352"/>
     </row>
     <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
@@ -4973,9 +5029,9 @@
     </row>
     <row r="97" spans="2:6">
       <c r="B97" s="47" t="s">
-        <v>284</v>
-      </c>
-      <c r="C97" s="248">
+        <v>282</v>
+      </c>
+      <c r="C97" s="247">
         <f>C96*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>0.40025178686632773</v>
       </c>
@@ -4985,28 +5041,28 @@
       </c>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="330" t="s">
-        <v>407</v>
-      </c>
-      <c r="C98" s="331">
+      <c r="B98" s="329" t="s">
+        <v>405</v>
+      </c>
+      <c r="C98" s="330">
         <f>BS!G30/BS!G27</f>
         <v>0.40000523965699897</v>
       </c>
     </row>
     <row r="99" spans="2:6">
-      <c r="B99" s="330" t="s">
-        <v>408</v>
-      </c>
-      <c r="C99" s="331">
+      <c r="B99" s="329" t="s">
+        <v>406</v>
+      </c>
+      <c r="C99" s="330">
         <f>BS!G31/BS!G27</f>
         <v>0.10646655543311496</v>
       </c>
     </row>
     <row r="100" spans="2:6">
-      <c r="B100" s="330" t="s">
-        <v>410</v>
-      </c>
-      <c r="C100" s="332">
+      <c r="B100" s="329" t="s">
+        <v>408</v>
+      </c>
+      <c r="C100" s="331">
         <f>BS!C50</f>
         <v>0.9804830051022897</v>
       </c>
@@ -5044,9 +5100,9 @@
     </row>
     <row r="105" spans="2:6">
       <c r="B105" s="47" t="s">
-        <v>285</v>
-      </c>
-      <c r="C105" s="248">
+        <v>283</v>
+      </c>
+      <c r="C105" s="247">
         <f>C104*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>1.2050311068441337</v>
       </c>
@@ -5075,9 +5131,9 @@
     </row>
     <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
-        <v>286</v>
-      </c>
-      <c r="C109" s="248">
+        <v>284</v>
+      </c>
+      <c r="C109" s="247">
         <f>C108*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>3.8796718858693152E-2</v>
       </c>
@@ -5087,20 +5143,20 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B111" s="348" t="s">
-        <v>369</v>
-      </c>
-      <c r="C111" s="348"/>
-      <c r="D111" s="348"/>
-      <c r="E111" s="348"/>
-      <c r="F111" s="348"/>
+      <c r="B111" s="352" t="s">
+        <v>367</v>
+      </c>
+      <c r="C111" s="352"/>
+      <c r="D111" s="352"/>
+      <c r="E111" s="352"/>
+      <c r="F111" s="352"/>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
-        <v>282</v>
-      </c>
-      <c r="C113" s="248">
-        <f>DCF!C12</f>
+        <v>450</v>
+      </c>
+      <c r="C113" s="247">
+        <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
         <v>4.3931077563825554</v>
       </c>
       <c r="D113" s="1" t="str">
@@ -5109,10 +5165,10 @@
       </c>
     </row>
     <row r="114" spans="1:6">
-      <c r="B114" s="330" t="s">
-        <v>409</v>
-      </c>
-      <c r="C114" s="248">
+      <c r="B114" s="329" t="s">
+        <v>407</v>
+      </c>
+      <c r="C114" s="247">
         <f>BS!D47</f>
         <v>1.6698226477450393</v>
       </c>
@@ -5122,8 +5178,8 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="13.9">
-      <c r="A116" s="247" t="s">
-        <v>361</v>
+      <c r="A116" s="246" t="s">
+        <v>359</v>
       </c>
       <c r="B116" s="36"/>
       <c r="C116" s="36"/>
@@ -5132,49 +5188,49 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B118" s="349" t="s">
-        <v>370</v>
-      </c>
-      <c r="C118" s="349"/>
-      <c r="D118" s="349"/>
-      <c r="E118" s="349"/>
-      <c r="F118" s="349"/>
+      <c r="B118" s="353" t="s">
+        <v>368</v>
+      </c>
+      <c r="C118" s="353"/>
+      <c r="D118" s="353"/>
+      <c r="E118" s="353"/>
+      <c r="F118" s="353"/>
     </row>
     <row r="120" spans="1:6" ht="12.4">
-      <c r="B120" s="258" t="s">
+      <c r="B120" s="257" t="s">
         <v>118</v>
       </c>
-      <c r="C120" s="258" t="s">
+      <c r="C120" s="257" t="s">
         <v>133</v>
       </c>
-      <c r="D120" s="258" t="s">
+      <c r="D120" s="257" t="s">
         <v>113</v>
       </c>
-      <c r="E120" s="258" t="s">
+      <c r="E120" s="257" t="s">
         <v>260</v>
       </c>
-      <c r="F120" s="258" t="s">
+      <c r="F120" s="257" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="121" spans="1:6">
-      <c r="B121" s="253" t="str">
+      <c r="B121" s="252" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C121" s="254">
+      <c r="C121" s="253">
         <f>DCF!C74</f>
         <v>0.1</v>
       </c>
-      <c r="D121" s="255">
+      <c r="D121" s="254">
         <f>DCF!D74</f>
         <v>15</v>
       </c>
-      <c r="E121" s="256" t="str">
-        <f>ROUND(DCF!E74,2)&amp;" "&amp;Market_currency</f>
+      <c r="E121" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
         <v>7.02 HKD</v>
       </c>
-      <c r="F121" s="257">
+      <c r="F121" s="256">
         <f>DCF!F74</f>
         <v>0.05</v>
       </c>
@@ -5192,11 +5248,11 @@
         <f>DCF!D75</f>
         <v>10</v>
       </c>
-      <c r="E122" s="245" t="str">
-        <f>ROUND(DCF!E75,2)&amp;" "&amp;Market_currency</f>
+      <c r="E122" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
         <v>5.15 HKD</v>
       </c>
-      <c r="F122" s="246">
+      <c r="F122" s="245">
         <f>DCF!F75</f>
         <v>0.18</v>
       </c>
@@ -5214,11 +5270,11 @@
         <f>DCF!D76</f>
         <v>10</v>
       </c>
-      <c r="E123" s="245" t="str">
-        <f>ROUND(DCF!E76,2)&amp;" "&amp;Market_currency</f>
+      <c r="E123" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
         <v>4.87 HKD</v>
       </c>
-      <c r="F123" s="246">
+      <c r="F123" s="245">
         <f>DCF!F76</f>
         <v>0.53999999999999992</v>
       </c>
@@ -5236,11 +5292,11 @@
         <f>DCF!D77</f>
         <v>10</v>
       </c>
-      <c r="E124" s="245" t="str">
-        <f>ROUND(DCF!E77,2)&amp;" "&amp;Market_currency</f>
+      <c r="E124" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
         <v>4.62 HKD</v>
       </c>
-      <c r="F124" s="246">
+      <c r="F124" s="245">
         <f>DCF!F77</f>
         <v>0.18</v>
       </c>
@@ -5258,11 +5314,11 @@
         <f>DCF!D78</f>
         <v>15</v>
       </c>
-      <c r="E125" s="245" t="str">
-        <f>ROUND(DCF!E78,2)&amp;" "&amp;Market_currency</f>
+      <c r="E125" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
         <v>4.39 HKD</v>
       </c>
-      <c r="F125" s="246">
+      <c r="F125" s="245">
         <f>DCF!F78</f>
         <v>0.05</v>
       </c>
@@ -5281,17 +5337,17 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B129" s="353" t="s">
-        <v>373</v>
-      </c>
-      <c r="C129" s="353"/>
-      <c r="D129" s="353"/>
-      <c r="E129" s="353"/>
-      <c r="F129" s="353"/>
+      <c r="B129" s="356" t="s">
+        <v>371</v>
+      </c>
+      <c r="C129" s="356"/>
+      <c r="D129" s="356"/>
+      <c r="E129" s="356"/>
+      <c r="F129" s="356"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
-      <c r="A131" s="247" t="s">
-        <v>405</v>
+      <c r="A131" s="246" t="s">
+        <v>403</v>
       </c>
       <c r="B131" s="36"/>
       <c r="C131" s="36"/>
@@ -5300,22 +5356,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="351" t="s">
-        <v>371</v>
-      </c>
-      <c r="C133" s="351"/>
-      <c r="D133" s="351"/>
-      <c r="E133" s="351"/>
-      <c r="F133" s="351"/>
+      <c r="B133" s="357" t="s">
+        <v>369</v>
+      </c>
+      <c r="C133" s="357"/>
+      <c r="D133" s="357"/>
+      <c r="E133" s="357"/>
+      <c r="F133" s="357"/>
     </row>
     <row r="134" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B134" s="348" t="s">
-        <v>372</v>
-      </c>
-      <c r="C134" s="348"/>
-      <c r="D134" s="348"/>
-      <c r="E134" s="348"/>
-      <c r="F134" s="348"/>
+      <c r="B134" s="352" t="s">
+        <v>370</v>
+      </c>
+      <c r="C134" s="352"/>
+      <c r="D134" s="352"/>
+      <c r="E134" s="352"/>
+      <c r="F134" s="352"/>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="234" t="s">
@@ -5326,7 +5382,7 @@
       <c r="B136" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C136" s="250">
+      <c r="C136" s="249">
         <f>F28</f>
         <v>3</v>
       </c>
@@ -5335,7 +5391,7 @@
       <c r="B137" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="C137" s="249">
+      <c r="C137" s="248">
         <f>F29</f>
         <v>0.4</v>
       </c>
@@ -5355,22 +5411,22 @@
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="234" t="s">
-        <v>412</v>
-      </c>
-      <c r="C140" s="268" t="str">
+        <v>410</v>
+      </c>
+      <c r="C140" s="267" t="str">
         <f>C11</f>
         <v>0398.HK</v>
       </c>
-      <c r="D140" s="268" t="str">
+      <c r="D140" s="267" t="str">
         <f>IF(D11="","",D11)</f>
         <v/>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="C141" s="331">
+        <v>409</v>
+      </c>
+      <c r="C141" s="330">
         <f>F29</f>
         <v>0.4</v>
       </c>
@@ -5403,20 +5459,20 @@
         <f>Scenarios!C83</f>
         <v>2.0118297468067095</v>
       </c>
-      <c r="D144" s="335" t="str">
+      <c r="D144" s="334" t="str">
         <f>IF($D$11="","",C144*$E$25)</f>
         <v/>
       </c>
     </row>
     <row r="145" spans="2:4">
-      <c r="B145" s="286" t="s">
-        <v>419</v>
-      </c>
-      <c r="C145" s="333" t="str">
+      <c r="B145" s="285" t="s">
+        <v>417</v>
+      </c>
+      <c r="C145" s="332" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D145" s="333" t="str">
+      <c r="D145" s="332" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5432,14 +5488,14 @@
     </row>
     <row r="148" spans="2:4">
       <c r="B148" s="234" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="2:4">
       <c r="B149" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="C149" s="331">
+        <v>412</v>
+      </c>
+      <c r="C149" s="330">
         <f>Scenarios!C90</f>
         <v>0.21740000000000001</v>
       </c>
@@ -5472,20 +5528,20 @@
         <f>Scenarios!C93</f>
         <v>3.012815450868831</v>
       </c>
-      <c r="D152" s="335" t="str">
+      <c r="D152" s="334" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
         <v/>
       </c>
     </row>
     <row r="153" spans="2:4">
-      <c r="B153" s="286" t="s">
-        <v>419</v>
-      </c>
-      <c r="C153" s="333" t="str">
+      <c r="B153" s="285" t="s">
+        <v>417</v>
+      </c>
+      <c r="C153" s="332" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D153" s="333" t="str">
+      <c r="D153" s="332" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5501,12 +5557,12 @@
     </row>
     <row r="156" spans="2:4">
       <c r="B156" s="234" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="157" spans="2:4">
       <c r="B157" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C157" s="92">
         <f>Scenarios!C96</f>
@@ -5535,26 +5591,26 @@
     </row>
     <row r="160" spans="2:4">
       <c r="B160" s="80" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C160" s="239">
         <f>Scenarios!C99</f>
         <v>4.2691663056616189</v>
       </c>
-      <c r="D160" s="335" t="str">
+      <c r="D160" s="334" t="str">
         <f>IF($D$11="","",C160*$E$25)</f>
         <v/>
       </c>
     </row>
     <row r="161" spans="1:6">
-      <c r="B161" s="286" t="s">
-        <v>419</v>
-      </c>
-      <c r="C161" s="333" t="str">
+      <c r="B161" s="285" t="s">
+        <v>417</v>
+      </c>
+      <c r="C161" s="332" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D161" s="333" t="str">
+      <c r="D161" s="332" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5570,12 +5626,12 @@
     </row>
     <row r="164" spans="1:6">
       <c r="B164" s="234" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="165" spans="1:6">
       <c r="B165" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C165" s="92">
         <f>F32</f>
@@ -5604,26 +5660,26 @@
     </row>
     <row r="168" spans="1:6">
       <c r="B168" s="80" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C168" s="239">
         <f>Scenarios!C105</f>
         <v>3.8656512307065762</v>
       </c>
-      <c r="D168" s="335" t="str">
+      <c r="D168" s="334" t="str">
         <f>IF($D$11="","",C168*$E$25)</f>
         <v/>
       </c>
     </row>
     <row r="169" spans="1:6">
-      <c r="B169" s="286" t="s">
-        <v>419</v>
-      </c>
-      <c r="C169" s="333" t="str">
+      <c r="B169" s="285" t="s">
+        <v>417</v>
+      </c>
+      <c r="C169" s="332" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D169" s="333" t="str">
+      <c r="D169" s="332" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5638,8 +5694,8 @@
       </c>
     </row>
     <row r="172" spans="1:6" ht="13.9">
-      <c r="A172" s="247" t="s">
-        <v>377</v>
+      <c r="A172" s="246" t="s">
+        <v>375</v>
       </c>
       <c r="B172" s="36"/>
       <c r="C172" s="36"/>
@@ -5648,113 +5704,102 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="355" t="s">
-        <v>379</v>
-      </c>
-      <c r="C174" s="348"/>
-      <c r="D174" s="348"/>
-      <c r="E174" s="348"/>
-      <c r="F174" s="348"/>
+      <c r="B174" s="351" t="s">
+        <v>377</v>
+      </c>
+      <c r="C174" s="352"/>
+      <c r="D174" s="352"/>
+      <c r="E174" s="352"/>
+      <c r="F174" s="352"/>
     </row>
     <row r="176" spans="1:6">
       <c r="B176" s="234" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="177" spans="2:6">
-      <c r="B177" s="352" t="s">
-        <v>383</v>
-      </c>
-      <c r="C177" s="352"/>
-      <c r="D177" s="352"/>
-      <c r="E177" s="352"/>
-      <c r="F177" s="352"/>
+      <c r="B177" s="354" t="s">
+        <v>381</v>
+      </c>
+      <c r="C177" s="354"/>
+      <c r="D177" s="354"/>
+      <c r="E177" s="354"/>
+      <c r="F177" s="354"/>
     </row>
     <row r="178" spans="2:6">
       <c r="B178" s="238" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="179" spans="2:6">
       <c r="B179" s="238" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="180" spans="2:6">
       <c r="B180" s="238" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="182" spans="2:6">
       <c r="B182" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B183" s="349" t="s">
-        <v>384</v>
-      </c>
-      <c r="C183" s="349"/>
-      <c r="D183" s="349"/>
-      <c r="E183" s="349"/>
-      <c r="F183" s="349"/>
+      <c r="B183" s="353" t="s">
+        <v>382</v>
+      </c>
+      <c r="C183" s="353"/>
+      <c r="D183" s="353"/>
+      <c r="E183" s="353"/>
+      <c r="F183" s="353"/>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B186" s="354" t="s">
-        <v>385</v>
-      </c>
-      <c r="C186" s="354"/>
-      <c r="D186" s="354"/>
-      <c r="E186" s="354"/>
-      <c r="F186" s="354"/>
+      <c r="B186" s="350" t="s">
+        <v>383</v>
+      </c>
+      <c r="C186" s="350"/>
+      <c r="D186" s="350"/>
+      <c r="E186" s="350"/>
+      <c r="F186" s="350"/>
     </row>
     <row r="187" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B187" s="354" t="s">
-        <v>386</v>
-      </c>
-      <c r="C187" s="354"/>
-      <c r="D187" s="354"/>
-      <c r="E187" s="354"/>
-      <c r="F187" s="354"/>
+      <c r="B187" s="350" t="s">
+        <v>384</v>
+      </c>
+      <c r="C187" s="350"/>
+      <c r="D187" s="350"/>
+      <c r="E187" s="350"/>
+      <c r="F187" s="350"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="190" spans="2:6">
       <c r="B190" s="238" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="191" spans="2:6">
       <c r="B191" s="238" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="192" spans="2:6">
       <c r="B192" s="238" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5771,6 +5816,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -5783,7 +5839,7 @@
     <dataValidation type="list" allowBlank="1" sqref="C25:D25" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E22 E25" xr:uid="{788B6937-776F-41CC-B9B1-7986DB35B57D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E21 E25" xr:uid="{788B6937-776F-41CC-B9B1-7986DB35B57D}">
       <formula1>"DCF,DDM"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6287,7 +6343,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C22" s="181">
         <v>346987</v>
@@ -6321,7 +6377,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C23" s="181">
         <v>-67837</v>
@@ -6355,7 +6411,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C24" s="181">
         <v>-423459</v>
@@ -6421,7 +6477,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -7716,7 +7772,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8164,11 +8220,11 @@
         <f t="shared" si="40"/>
         <v>86046</v>
       </c>
-      <c r="I77" s="329"/>
-      <c r="J77" s="329"/>
-      <c r="K77" s="329"/>
-      <c r="L77" s="329"/>
-      <c r="M77" s="329"/>
+      <c r="I77" s="328"/>
+      <c r="J77" s="328"/>
+      <c r="K77" s="328"/>
+      <c r="L77" s="328"/>
+      <c r="M77" s="328"/>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
@@ -8198,11 +8254,11 @@
         <f t="shared" si="40"/>
         <v>823654</v>
       </c>
-      <c r="I78" s="329"/>
-      <c r="J78" s="329"/>
-      <c r="K78" s="329"/>
-      <c r="L78" s="329"/>
-      <c r="M78" s="329"/>
+      <c r="I78" s="328"/>
+      <c r="J78" s="328"/>
+      <c r="K78" s="328"/>
+      <c r="L78" s="328"/>
+      <c r="M78" s="328"/>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
@@ -8305,17 +8361,17 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="C4:M16 C19:M25 C39:M43 C45:M48 C51:M52 C55:M58 C77:H78 C79:M80">
-    <cfRule type="expression" dxfId="5" priority="4">
+    <cfRule type="expression" dxfId="7" priority="4">
       <formula>ISBLANK(C4)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C28:M32">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>ISBLANK(C28)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C36:M37 C61:M65">
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="5" priority="2">
       <formula>ISBLANK(C36)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8400,7 +8456,7 @@
         <f>83075+265532</f>
         <v>348607</v>
       </c>
-      <c r="D4" s="290">
+      <c r="D4" s="289">
         <v>0.6</v>
       </c>
       <c r="E4" s="25"/>
@@ -8410,7 +8466,7 @@
       <c r="G4" s="19">
         <v>1089388</v>
       </c>
-      <c r="H4" s="290">
+      <c r="H4" s="289">
         <v>0.9</v>
       </c>
     </row>
@@ -8421,7 +8477,7 @@
       <c r="C5" s="19">
         <v>0</v>
       </c>
-      <c r="D5" s="290">
+      <c r="D5" s="289">
         <v>0.6</v>
       </c>
       <c r="E5" s="25"/>
@@ -8431,7 +8487,7 @@
       <c r="G5" s="19">
         <v>0</v>
       </c>
-      <c r="H5" s="290">
+      <c r="H5" s="289">
         <v>0.7</v>
       </c>
     </row>
@@ -8442,7 +8498,7 @@
       <c r="C6" s="19">
         <v>506592</v>
       </c>
-      <c r="D6" s="290">
+      <c r="D6" s="289">
         <v>0.5</v>
       </c>
       <c r="E6" s="25"/>
@@ -8452,7 +8508,7 @@
       <c r="G6" s="19">
         <v>0</v>
       </c>
-      <c r="H6" s="290">
+      <c r="H6" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8463,7 +8519,7 @@
       <c r="C7" s="19">
         <v>0</v>
       </c>
-      <c r="D7" s="290">
+      <c r="D7" s="289">
         <v>0.6</v>
       </c>
       <c r="E7" s="25"/>
@@ -8473,7 +8529,7 @@
       <c r="G7" s="19">
         <v>10851</v>
       </c>
-      <c r="H7" s="290">
+      <c r="H7" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8484,7 +8540,7 @@
       <c r="C8" s="19">
         <v>0</v>
       </c>
-      <c r="D8" s="290">
+      <c r="D8" s="289">
         <v>0.6</v>
       </c>
       <c r="E8" s="25"/>
@@ -8494,7 +8550,7 @@
       <c r="G8" s="19">
         <v>0</v>
       </c>
-      <c r="H8" s="290">
+      <c r="H8" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8505,7 +8561,7 @@
       <c r="C9" s="19">
         <v>0</v>
       </c>
-      <c r="D9" s="290">
+      <c r="D9" s="289">
         <v>0.1</v>
       </c>
       <c r="E9" s="25"/>
@@ -8515,7 +8571,7 @@
       <c r="G9" s="19">
         <v>0</v>
       </c>
-      <c r="H9" s="290">
+      <c r="H9" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8526,10 +8582,10 @@
       <c r="C10" s="19">
         <v>8727</v>
       </c>
-      <c r="D10" s="290">
+      <c r="D10" s="289">
         <v>0.9</v>
       </c>
-      <c r="H10" s="291"/>
+      <c r="H10" s="290"/>
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
@@ -8538,10 +8594,10 @@
       <c r="C11" s="19">
         <v>0</v>
       </c>
-      <c r="D11" s="290">
+      <c r="D11" s="289">
         <v>0.05</v>
       </c>
-      <c r="H11" s="291"/>
+      <c r="H11" s="290"/>
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
@@ -8599,7 +8655,7 @@
       <c r="C15" s="19">
         <v>0</v>
       </c>
-      <c r="D15" s="290">
+      <c r="D15" s="289">
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
@@ -8608,7 +8664,7 @@
       <c r="G15" s="19">
         <v>0</v>
       </c>
-      <c r="H15" s="290">
+      <c r="H15" s="289">
         <v>0.8</v>
       </c>
     </row>
@@ -8619,7 +8675,7 @@
       <c r="C16" s="19">
         <v>0</v>
       </c>
-      <c r="D16" s="290">
+      <c r="D16" s="289">
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
@@ -8629,7 +8685,7 @@
         <f>29657+19498</f>
         <v>49155</v>
       </c>
-      <c r="H16" s="290">
+      <c r="H16" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8640,7 +8696,7 @@
       <c r="C17" s="19">
         <v>0</v>
       </c>
-      <c r="D17" s="290">
+      <c r="D17" s="289">
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
@@ -8649,7 +8705,7 @@
       <c r="G17" s="19">
         <v>0</v>
       </c>
-      <c r="H17" s="290">
+      <c r="H17" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8660,7 +8716,7 @@
       <c r="C18" s="19">
         <v>0</v>
       </c>
-      <c r="D18" s="290">
+      <c r="D18" s="289">
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
@@ -8669,7 +8725,7 @@
       <c r="G18" s="19">
         <v>0</v>
       </c>
-      <c r="H18" s="290">
+      <c r="H18" s="289">
         <v>0.1</v>
       </c>
     </row>
@@ -8681,7 +8737,7 @@
         <f>233391+169651+360+16234</f>
         <v>419636</v>
       </c>
-      <c r="D19" s="290">
+      <c r="D19" s="289">
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
@@ -8691,7 +8747,7 @@
         <f>64831+22181</f>
         <v>87012</v>
       </c>
-      <c r="H19" s="290">
+      <c r="H19" s="289">
         <v>0.1</v>
       </c>
     </row>
@@ -8702,7 +8758,7 @@
       <c r="C20" s="19">
         <v>0</v>
       </c>
-      <c r="D20" s="290">
+      <c r="D20" s="289">
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
@@ -8711,7 +8767,7 @@
       <c r="G20" s="19">
         <v>0</v>
       </c>
-      <c r="H20" s="290">
+      <c r="H20" s="289">
         <v>0.2</v>
       </c>
     </row>
@@ -8722,7 +8778,7 @@
       <c r="C21" s="19">
         <v>0</v>
       </c>
-      <c r="D21" s="290">
+      <c r="D21" s="289">
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
@@ -8731,7 +8787,7 @@
       <c r="G21" s="19">
         <v>36961</v>
       </c>
-      <c r="H21" s="290">
+      <c r="H21" s="289">
         <v>0.1</v>
       </c>
     </row>
@@ -8742,10 +8798,10 @@
       <c r="C22" s="19">
         <v>8134</v>
       </c>
-      <c r="D22" s="290">
+      <c r="D22" s="289">
         <v>0.9</v>
       </c>
-      <c r="H22" s="291"/>
+      <c r="H22" s="290"/>
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
@@ -8754,10 +8810,10 @@
       <c r="C23" s="19">
         <v>0</v>
       </c>
-      <c r="D23" s="290">
-        <v>0</v>
-      </c>
-      <c r="H23" s="291"/>
+      <c r="D23" s="289">
+        <v>0</v>
+      </c>
+      <c r="H23" s="290"/>
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
@@ -9090,13 +9146,13 @@
       <c r="B45" s="16" t="s">
         <v>272</v>
       </c>
-      <c r="C45" s="259" t="s">
+      <c r="C45" s="258" t="s">
         <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>409</v>
-      </c>
-      <c r="F45" s="283" t="s">
+        <v>407</v>
+      </c>
+      <c r="F45" s="282" t="s">
         <v>59</v>
       </c>
     </row>
@@ -9112,7 +9168,7 @@
         <f>H29</f>
         <v>813801.8</v>
       </c>
-      <c r="F46" s="280"/>
+      <c r="F46" s="279"/>
     </row>
     <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
@@ -9127,23 +9183,23 @@
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
         <v>1.6698226477450393</v>
       </c>
-      <c r="F47" s="280"/>
+      <c r="F47" s="279"/>
     </row>
     <row r="48" spans="2:8" ht="15" customHeight="1">
-      <c r="F48" s="280"/>
+      <c r="F48" s="279"/>
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="158" t="s">
         <v>144</v>
       </c>
-      <c r="C49" s="260" t="s">
+      <c r="C49" s="259" t="s">
         <v>57</v>
       </c>
       <c r="D49" s="218" t="s">
         <v>96</v>
       </c>
       <c r="E49" s="2"/>
-      <c r="F49" s="280"/>
+      <c r="F49" s="279"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
@@ -9157,7 +9213,7 @@
         <f>G31/Normalized_FCF!G8</f>
         <v>0.55099965538864815</v>
       </c>
-      <c r="F50" s="280"/>
+      <c r="F50" s="279"/>
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
@@ -9168,22 +9224,22 @@
         <f>G29/G32</f>
         <v>0.71359494874005047</v>
       </c>
-      <c r="F51" s="280"/>
+      <c r="F51" s="279"/>
     </row>
     <row r="52" spans="2:8" ht="15" customHeight="1">
-      <c r="F52" s="280"/>
+      <c r="F52" s="279"/>
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="158" t="s">
         <v>143</v>
       </c>
-      <c r="C53" s="260" t="s">
+      <c r="C53" s="259" t="s">
         <v>57</v>
       </c>
       <c r="D53" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F53" s="280"/>
+      <c r="F53" s="279"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
@@ -9197,7 +9253,7 @@
         <f>Normalized_FCF!G8/G35</f>
         <v>0.274075324224895</v>
       </c>
-      <c r="F54" s="280"/>
+      <c r="F54" s="279"/>
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
@@ -9211,22 +9267,22 @@
         <f>Normalized_FCF!G11/G40</f>
         <v>0</v>
       </c>
-      <c r="F55" s="280"/>
+      <c r="F55" s="279"/>
     </row>
     <row r="56" spans="2:8" ht="15" customHeight="1">
-      <c r="F56" s="280"/>
+      <c r="F56" s="279"/>
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="158" t="s">
         <v>176</v>
       </c>
-      <c r="C57" s="260" t="s">
+      <c r="C57" s="259" t="s">
         <v>57</v>
       </c>
       <c r="D57" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F57" s="280"/>
+      <c r="F57" s="279"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
@@ -9248,22 +9304,22 @@
         <f>G39/G32</f>
         <v>0.1635967615610221</v>
       </c>
-      <c r="F59" s="280"/>
+      <c r="F59" s="279"/>
     </row>
     <row r="60" spans="2:8" ht="15" customHeight="1">
-      <c r="F60" s="280"/>
+      <c r="F60" s="279"/>
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="158" t="s">
         <v>275</v>
       </c>
-      <c r="C61" s="260" t="s">
+      <c r="C61" s="259" t="s">
         <v>138</v>
       </c>
       <c r="D61" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F61" s="280"/>
+      <c r="F61" s="279"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
@@ -9277,7 +9333,7 @@
         <f>G28/G29</f>
         <v>9.6426167603430037E-4</v>
       </c>
-      <c r="F62" s="280" t="s">
+      <c r="F62" s="279" t="s">
         <v>273</v>
       </c>
     </row>
@@ -9296,13 +9352,13 @@
       <c r="B65" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="C65" s="259" t="s">
+      <c r="C65" s="258" t="s">
         <v>137</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>288</v>
-      </c>
-      <c r="F65" s="283" t="s">
+        <v>286</v>
+      </c>
+      <c r="F65" s="282" t="s">
         <v>59</v>
       </c>
     </row>
@@ -9330,7 +9386,7 @@
         <f>G6+G16</f>
         <v>49155</v>
       </c>
-      <c r="F67" s="280"/>
+      <c r="F67" s="279"/>
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
@@ -9340,7 +9396,7 @@
         <f>G18</f>
         <v>0</v>
       </c>
-      <c r="F68" s="280"/>
+      <c r="F68" s="279"/>
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
@@ -9350,7 +9406,7 @@
         <f>G8+G20</f>
         <v>0</v>
       </c>
-      <c r="F69" s="280"/>
+      <c r="F69" s="279"/>
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
@@ -9360,26 +9416,26 @@
         <f>SUM(C66:C69)</f>
         <v>1138543</v>
       </c>
-      <c r="F70" s="280"/>
+      <c r="F70" s="279"/>
     </row>
     <row r="71" spans="2:6" ht="15" customHeight="1">
-      <c r="F71" s="280"/>
+      <c r="F71" s="279"/>
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
-      <c r="B72" s="282" t="s">
-        <v>321</v>
-      </c>
-      <c r="C72" s="259" t="s">
+      <c r="B72" s="281" t="s">
+        <v>319</v>
+      </c>
+      <c r="C72" s="258" t="s">
         <v>96</v>
       </c>
       <c r="D72" s="203" t="s">
         <v>57</v>
       </c>
-      <c r="F72" s="280"/>
+      <c r="F72" s="279"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -9390,65 +9446,65 @@
         <v>-251053.08995184439</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
-      <c r="B74" s="284" t="s">
-        <v>324</v>
-      </c>
-      <c r="C74" s="285">
+      <c r="B74" s="283" t="s">
+        <v>322</v>
+      </c>
+      <c r="C74" s="284">
         <f>-$C$66/C73</f>
         <v>3.9056455659498561</v>
       </c>
-      <c r="D74" s="285">
+      <c r="D74" s="284">
         <f>-$C$66/D73</f>
         <v>4.3392734190563456</v>
       </c>
-      <c r="F74" s="280" t="s">
-        <v>322</v>
+      <c r="F74" s="279" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
-        <v>323</v>
-      </c>
-      <c r="C75" s="289"/>
-      <c r="D75" s="288">
+        <v>321</v>
+      </c>
+      <c r="C75" s="288"/>
+      <c r="D75" s="287">
         <f>MAX(-D73*D76,G5)</f>
         <v>502106.17990368878</v>
       </c>
-      <c r="F75" s="280" t="s">
-        <v>355</v>
+      <c r="F75" s="279" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
-      <c r="B76" s="286" t="s">
-        <v>325</v>
-      </c>
-      <c r="C76" s="287"/>
-      <c r="D76" s="322">
+      <c r="B76" s="285" t="s">
+        <v>323</v>
+      </c>
+      <c r="C76" s="286"/>
+      <c r="D76" s="321">
         <f>IF(D74&lt;=3,1,IF(D74&gt;18,6,2))</f>
         <v>2</v>
       </c>
-      <c r="F76" s="280" t="s">
-        <v>326</v>
+      <c r="F76" s="279" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
-      <c r="F77" s="280"/>
+      <c r="F77" s="279"/>
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="258" t="s">
         <v>137</v>
       </c>
       <c r="D78" s="204" t="s">
         <v>35</v>
       </c>
-      <c r="F78" s="280"/>
+      <c r="F78" s="279"/>
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
@@ -9462,7 +9518,7 @@
         <f>G7*H7+G17*H17</f>
         <v>6510.5999999999995</v>
       </c>
-      <c r="F79" s="280"/>
+      <c r="F79" s="279"/>
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
@@ -9476,7 +9532,7 @@
         <f>G19*H19</f>
         <v>8701.2000000000007</v>
       </c>
-      <c r="F80" s="280"/>
+      <c r="F80" s="279"/>
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
@@ -9490,7 +9546,7 @@
         <f>G9*H9+G21*H21</f>
         <v>3696.1000000000004</v>
       </c>
-      <c r="F81" s="280"/>
+      <c r="F81" s="279"/>
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
@@ -9504,11 +9560,11 @@
         <f>SUM(D79:D81)</f>
         <v>18907.900000000001</v>
       </c>
-      <c r="F82" s="280"/>
+      <c r="F82" s="279"/>
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9519,76 +9575,76 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
-        <v>292</v>
-      </c>
-      <c r="D85" s="268" t="s">
-        <v>293</v>
+        <v>290</v>
+      </c>
+      <c r="D85" s="267" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
-      <c r="B86" s="265" t="s">
-        <v>289</v>
+      <c r="B86" s="264" t="s">
+        <v>287</v>
       </c>
       <c r="C86" s="188">
         <f>-DCF!C7*Exchange_Rate</f>
         <v>-195066</v>
       </c>
-      <c r="D86" s="248">
+      <c r="D86" s="247">
         <f>C86*scaling_factor/Common_Shares</f>
         <v>-0.40025178686632773</v>
       </c>
-      <c r="E86" s="267" t="str">
+      <c r="E86" s="266" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
-      <c r="B87" s="265" t="s">
-        <v>290</v>
+      <c r="B87" s="264" t="s">
+        <v>288</v>
       </c>
       <c r="C87" s="188">
         <f>DCF!C8*Exchange_Rate</f>
         <v>587281.82009631116</v>
       </c>
-      <c r="D87" s="248">
+      <c r="D87" s="247">
         <f>C87*scaling_factor/Common_Shares</f>
         <v>1.2050311068441337</v>
       </c>
-      <c r="E87" s="267" t="str">
+      <c r="E87" s="266" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1">
-      <c r="B88" s="266" t="s">
+      <c r="B88" s="265" t="s">
         <v>190</v>
       </c>
       <c r="C88" s="188">
         <f>DCF!C9*Exchange_Rate</f>
         <v>18907.900000000001</v>
       </c>
-      <c r="D88" s="248">
+      <c r="D88" s="247">
         <f>C88*scaling_factor/Common_Shares</f>
         <v>3.8796718858693152E-2</v>
       </c>
-      <c r="E88" s="267" t="str">
+      <c r="E88" s="266" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
         <v>411123.72009631118</v>
       </c>
-      <c r="D89" s="269">
+      <c r="D89" s="268">
         <f>SUM(D86:D88)</f>
         <v>0.84357603883649912</v>
       </c>
-      <c r="E89" s="267" t="str">
+      <c r="E89" s="266" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
@@ -9709,7 +9765,7 @@
         <v>1000</v>
       </c>
       <c r="D3" s="9"/>
-      <c r="E3" s="298"/>
+      <c r="E3" s="297"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
@@ -9723,7 +9779,7 @@
         <v>3149204.111111111</v>
       </c>
       <c r="D4" s="57"/>
-      <c r="E4" s="296"/>
+      <c r="E4" s="295"/>
       <c r="F4" s="57"/>
       <c r="G4" s="183">
         <f>Data!C36</f>
@@ -9779,7 +9835,7 @@
         <f>C25</f>
         <v>-2697049.2267501326</v>
       </c>
-      <c r="E5" s="298"/>
+      <c r="E5" s="297"/>
       <c r="G5" s="183">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
         <v>-3031530</v>
@@ -9834,7 +9890,7 @@
         <f>C4+C5</f>
         <v>452154.88436097838</v>
       </c>
-      <c r="E6" s="298"/>
+      <c r="E6" s="297"/>
       <c r="G6" s="184">
         <f>IF(G4="","",G4+G5)</f>
         <v>607228</v>
@@ -9889,7 +9945,7 @@
         <f>C35</f>
         <v>-253206</v>
       </c>
-      <c r="E7" s="298"/>
+      <c r="E7" s="297"/>
       <c r="G7" s="191">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
         <v>-253206</v>
@@ -9945,7 +10001,7 @@
         <v>198948.88436097838</v>
       </c>
       <c r="D8" s="59"/>
-      <c r="E8" s="304"/>
+      <c r="E8" s="303"/>
       <c r="F8" s="59"/>
       <c r="G8" s="184">
         <f>IF(G$4="","",G6+G7)</f>
@@ -10001,7 +10057,7 @@
         <f>BS!$G$39*BS!D58</f>
         <v>0</v>
       </c>
-      <c r="E9" s="298"/>
+      <c r="E9" s="297"/>
       <c r="G9" s="191">
         <f>IF(Data!C61="","",-Data!C61)</f>
         <v>0</v>
@@ -10056,7 +10112,7 @@
         <f>-C4*C78</f>
         <v>0</v>
       </c>
-      <c r="E10" s="298"/>
+      <c r="E10" s="297"/>
       <c r="G10" s="191">
         <f>Data!C62</f>
         <v>0</v>
@@ -10112,7 +10168,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="169"/>
-      <c r="E11" s="297"/>
+      <c r="E11" s="296"/>
       <c r="F11" s="169"/>
       <c r="G11" s="186">
         <f>G61</f>
@@ -10168,7 +10224,7 @@
         <f>C50</f>
         <v>-13663</v>
       </c>
-      <c r="E12" s="298"/>
+      <c r="E12" s="297"/>
       <c r="G12" s="191">
         <f>G50</f>
         <v>-13663</v>
@@ -10223,7 +10279,7 @@
         <f>SUM(C8:C12)</f>
         <v>185285.88436097838</v>
       </c>
-      <c r="E13" s="298"/>
+      <c r="E13" s="297"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
         <v>340359</v>
@@ -10278,7 +10334,7 @@
         <f>-SUM(C8+C11,C12)*C43</f>
         <v>-46321.471090244595</v>
       </c>
-      <c r="E14" s="298"/>
+      <c r="E14" s="297"/>
       <c r="G14" s="191">
         <f>Data!C46</f>
         <v>-145324</v>
@@ -10334,7 +10390,7 @@
         <v>-572.93535914055167</v>
       </c>
       <c r="D15" s="60"/>
-      <c r="E15" s="305"/>
+      <c r="E15" s="304"/>
       <c r="F15" s="60"/>
       <c r="G15" s="183">
         <f>Data!C48</f>
@@ -10391,7 +10447,7 @@
         <v>138391.47791159325</v>
       </c>
       <c r="D16" s="61"/>
-      <c r="E16" s="306"/>
+      <c r="E16" s="305"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
@@ -10448,8 +10504,8 @@
         <v>0</v>
       </c>
       <c r="D17" s="58"/>
-      <c r="E17" s="297" t="s">
-        <v>334</v>
+      <c r="E17" s="296" t="s">
+        <v>332</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -10473,8 +10529,8 @@
         <v>0</v>
       </c>
       <c r="D18" s="58"/>
-      <c r="E18" s="297" t="s">
-        <v>335</v>
+      <c r="E18" s="296" t="s">
+        <v>333</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10499,7 +10555,7 @@
         <v>138391.47791159325</v>
       </c>
       <c r="D19" s="27"/>
-      <c r="E19" s="295"/>
+      <c r="E19" s="294"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
@@ -10595,7 +10651,7 @@
       </c>
       <c r="C22" s="62"/>
       <c r="D22" s="27"/>
-      <c r="E22" s="295"/>
+      <c r="E22" s="294"/>
       <c r="F22" s="27"/>
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
@@ -10619,7 +10675,7 @@
         <v>-2226669.2968957396</v>
       </c>
       <c r="D23" s="58"/>
-      <c r="E23" s="297"/>
+      <c r="E23" s="296"/>
       <c r="F23" s="58"/>
       <c r="G23" s="183">
         <f>Data!C37</f>
@@ -10676,7 +10732,7 @@
         <v>-470379.92985439295</v>
       </c>
       <c r="D24" s="27"/>
-      <c r="E24" s="295"/>
+      <c r="E24" s="294"/>
       <c r="F24" s="27"/>
       <c r="G24" s="183">
         <f>Data!C40</f>
@@ -10733,7 +10789,7 @@
         <v>-2697049.2267501326</v>
       </c>
       <c r="D25" s="9"/>
-      <c r="E25" s="303"/>
+      <c r="E25" s="302"/>
       <c r="F25" s="9"/>
       <c r="G25" s="184">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
@@ -10782,14 +10838,14 @@
     </row>
     <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
-      <c r="E26" s="298"/>
+      <c r="E26" s="297"/>
     </row>
     <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>207</v>
       </c>
-      <c r="E27" s="298"/>
+      <c r="E27" s="297"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
@@ -10801,8 +10857,8 @@
         <v>0.70705778931239871</v>
       </c>
       <c r="D28" s="26"/>
-      <c r="E28" s="296" t="s">
-        <v>336</v>
+      <c r="E28" s="295" t="s">
+        <v>334</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10861,8 +10917,8 @@
         <v>0.14936470081274986</v>
       </c>
       <c r="D29" s="26"/>
-      <c r="E29" s="296" t="s">
-        <v>336</v>
+      <c r="E29" s="295" t="s">
+        <v>334</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10919,7 +10975,7 @@
         <f>ABS(C25/$C$4)</f>
         <v>0.85642249012514848</v>
       </c>
-      <c r="E30" s="298"/>
+      <c r="E30" s="297"/>
       <c r="G30" s="30">
         <f t="shared" ref="G30:Q30" si="13">IF(G$4="","",ABS(G25/G$4))</f>
         <v>0.83312218070011801</v>
@@ -10967,14 +11023,14 @@
     </row>
     <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
-      <c r="E31" s="298"/>
+      <c r="E31" s="297"/>
     </row>
     <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="E32" s="298"/>
+      <c r="E32" s="297"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
@@ -10985,8 +11041,8 @@
         <f>G33</f>
         <v>-253206</v>
       </c>
-      <c r="E33" s="296" t="s">
-        <v>336</v>
+      <c r="E33" s="295" t="s">
+        <v>334</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -11043,8 +11099,8 @@
         <v>0</v>
       </c>
       <c r="D34" s="58"/>
-      <c r="E34" s="296" t="s">
-        <v>336</v>
+      <c r="E34" s="295" t="s">
+        <v>334</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -11102,7 +11158,7 @@
         <v>-253206</v>
       </c>
       <c r="D35" s="58"/>
-      <c r="E35" s="297"/>
+      <c r="E35" s="296"/>
       <c r="F35" s="58"/>
       <c r="G35" s="184">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
@@ -11151,14 +11207,14 @@
     </row>
     <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
-      <c r="E36" s="298"/>
+      <c r="E36" s="297"/>
     </row>
     <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>208</v>
       </c>
-      <c r="E37" s="298"/>
+      <c r="E37" s="297"/>
     </row>
     <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
@@ -11171,7 +11227,7 @@
         <v>8.0403172060722089E-2</v>
       </c>
       <c r="D38" s="27"/>
-      <c r="E38" s="295"/>
+      <c r="E38" s="294"/>
       <c r="F38" s="27"/>
       <c r="G38" s="13">
         <f t="shared" ref="G38:Q38" si="15">IF(G$4="","",ABS(G33/G$4))</f>
@@ -11229,7 +11285,7 @@
         <v>0</v>
       </c>
       <c r="D39" s="27"/>
-      <c r="E39" s="295"/>
+      <c r="E39" s="294"/>
       <c r="F39" s="27"/>
       <c r="G39" s="13">
         <f t="shared" ref="G39:Q39" si="16">IF(G$4="","",ABS(G34/G$4))</f>
@@ -11285,7 +11341,7 @@
         <f>ABS(C35/$C$4)</f>
         <v>8.0403172060722089E-2</v>
       </c>
-      <c r="E40" s="298"/>
+      <c r="E40" s="297"/>
       <c r="G40" s="30">
         <f t="shared" ref="G40:Q40" si="17">IF(G$4="","",ABS(G35/G$4))</f>
         <v>6.9585831209440147E-2</v>
@@ -11333,26 +11389,26 @@
     </row>
     <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
-      <c r="E41" s="298"/>
+      <c r="E41" s="297"/>
     </row>
     <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>209</v>
       </c>
-      <c r="E42" s="298"/>
+      <c r="E42" s="297"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>172</v>
       </c>
-      <c r="C43" s="292">
+      <c r="C43" s="291">
         <v>0.25</v>
       </c>
       <c r="D43" s="27"/>
-      <c r="E43" s="295" t="s">
-        <v>337</v>
+      <c r="E43" s="294" t="s">
+        <v>335</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -11431,7 +11487,7 @@
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
-      <c r="E46" s="298"/>
+      <c r="E46" s="297"/>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
@@ -11442,7 +11498,7 @@
         <f>-BS!G31*Normalized_FCF!C54</f>
         <v>-13663</v>
       </c>
-      <c r="E47" s="298"/>
+      <c r="E47" s="297"/>
       <c r="G47" s="191">
         <f>Data!C51</f>
         <v>-13663</v>
@@ -11491,111 +11547,111 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
         <v>0</v>
       </c>
-      <c r="E48" s="298"/>
-      <c r="G48" s="323">
+      <c r="E48" s="297"/>
+      <c r="G48" s="322">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>0</v>
       </c>
-      <c r="H48" s="323">
+      <c r="H48" s="322">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v>0</v>
       </c>
-      <c r="I48" s="323">
+      <c r="I48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="J48" s="323">
+      <c r="J48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="K48" s="323">
+      <c r="K48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="L48" s="323">
+      <c r="L48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="M48" s="323">
+      <c r="M48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="N48" s="323">
+      <c r="N48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="O48" s="323">
+      <c r="O48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="P48" s="323" t="str">
+      <c r="P48" s="322" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="Q48" s="323" t="str">
+      <c r="Q48" s="322" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
-      <c r="B49" s="318" t="s">
-        <v>345</v>
-      </c>
-      <c r="C49" s="319">
+      <c r="B49" s="317" t="s">
+        <v>343</v>
+      </c>
+      <c r="C49" s="318">
         <f>BS!$C$66*C53</f>
         <v>0</v>
       </c>
-      <c r="D49" s="320"/>
-      <c r="E49" s="321"/>
-      <c r="F49" s="320"/>
-      <c r="G49" s="319">
+      <c r="D49" s="319"/>
+      <c r="E49" s="320"/>
+      <c r="F49" s="319"/>
+      <c r="G49" s="318">
         <f>Data!C52</f>
         <v>0</v>
       </c>
-      <c r="H49" s="319">
+      <c r="H49" s="318">
         <f>Data!D52</f>
         <v>0</v>
       </c>
-      <c r="I49" s="319">
+      <c r="I49" s="318">
         <f>Data!E52</f>
         <v>0</v>
       </c>
-      <c r="J49" s="319">
+      <c r="J49" s="318">
         <f>Data!F52</f>
         <v>0</v>
       </c>
-      <c r="K49" s="319">
+      <c r="K49" s="318">
         <f>Data!G52</f>
         <v>0</v>
       </c>
-      <c r="L49" s="319">
+      <c r="L49" s="318">
         <f>Data!H52</f>
         <v>0</v>
       </c>
-      <c r="M49" s="319">
+      <c r="M49" s="318">
         <f>Data!I52</f>
         <v>0</v>
       </c>
-      <c r="N49" s="319">
+      <c r="N49" s="318">
         <f>Data!J52</f>
         <v>0</v>
       </c>
-      <c r="O49" s="319">
+      <c r="O49" s="318">
         <f>Data!K52</f>
         <v>0</v>
       </c>
-      <c r="P49" s="319" t="str">
+      <c r="P49" s="318" t="str">
         <f>Data!L52</f>
         <v/>
       </c>
-      <c r="Q49" s="319" t="str">
+      <c r="Q49" s="318" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -11609,7 +11665,7 @@
         <f>C47+C48</f>
         <v>-13663</v>
       </c>
-      <c r="E50" s="298"/>
+      <c r="E50" s="297"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
         <v>-13663</v>
@@ -11657,14 +11713,14 @@
     </row>
     <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
-      <c r="E51" s="298"/>
+      <c r="E51" s="297"/>
     </row>
     <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>156</v>
       </c>
-      <c r="E52" s="298"/>
+      <c r="E52" s="297"/>
       <c r="G52" s="97" t="s">
         <v>220</v>
       </c>
@@ -11678,8 +11734,8 @@
         <f>G53</f>
         <v>0</v>
       </c>
-      <c r="E53" s="295" t="s">
-        <v>338</v>
+      <c r="E53" s="294" t="s">
+        <v>336</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11705,8 +11761,8 @@
         <f>G54</f>
         <v>7.0042959818728018E-2</v>
       </c>
-      <c r="E54" s="295" t="s">
-        <v>339</v>
+      <c r="E54" s="294" t="s">
+        <v>337</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11732,7 +11788,7 @@
         <f>-C8/C47</f>
         <v>14.561142088924715</v>
       </c>
-      <c r="E55" s="298"/>
+      <c r="E55" s="297"/>
       <c r="G55" s="42">
         <f t="shared" ref="G55:Q55" si="21">IF(G4="","",-G8/G47)</f>
         <v>25.911000512332578</v>
@@ -11780,14 +11836,14 @@
     </row>
     <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
-      <c r="E56" s="298"/>
+      <c r="E56" s="297"/>
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>169</v>
       </c>
-      <c r="E57" s="298"/>
+      <c r="E57" s="297"/>
       <c r="G57" s="97" t="s">
         <v>220</v>
       </c>
@@ -11801,7 +11857,7 @@
         <f>BS!$C67*C66</f>
         <v>0</v>
       </c>
-      <c r="E58" s="298"/>
+      <c r="E58" s="297"/>
       <c r="G58" s="191">
         <f>Data!C56</f>
         <v>0</v>
@@ -11856,7 +11912,7 @@
         <f>BS!$C68*C67</f>
         <v>0</v>
       </c>
-      <c r="E59" s="298"/>
+      <c r="E59" s="297"/>
       <c r="G59" s="191">
         <f>Data!C55</f>
         <v>0</v>
@@ -11911,7 +11967,7 @@
         <f>BS!$C69*C68</f>
         <v>0</v>
       </c>
-      <c r="E60" s="298"/>
+      <c r="E60" s="297"/>
       <c r="G60" s="191">
         <f>Data!C57</f>
         <v>0</v>
@@ -11966,7 +12022,7 @@
         <f>SUM(C58:C60)</f>
         <v>0</v>
       </c>
-      <c r="E61" s="298"/>
+      <c r="E61" s="297"/>
       <c r="G61" s="184">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
         <v>0</v>
@@ -12017,11 +12073,11 @@
       <c r="B62" s="40" t="s">
         <v>161</v>
       </c>
-      <c r="C62" s="293">
-        <v>0</v>
-      </c>
-      <c r="E62" s="296" t="s">
-        <v>340</v>
+      <c r="C62" s="292">
+        <v>0</v>
+      </c>
+      <c r="E62" s="295" t="s">
+        <v>338</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -12077,7 +12133,7 @@
         <f>C61+C62</f>
         <v>0</v>
       </c>
-      <c r="E63" s="298"/>
+      <c r="E63" s="297"/>
       <c r="G63" s="184">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
         <v>56115</v>
@@ -12125,14 +12181,14 @@
     </row>
     <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
-      <c r="E64" s="298"/>
+      <c r="E64" s="297"/>
     </row>
     <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>170</v>
       </c>
-      <c r="E65" s="298"/>
+      <c r="E65" s="297"/>
       <c r="G65" s="97" t="s">
         <v>220</v>
       </c>
@@ -12146,7 +12202,7 @@
         <f>G66</f>
         <v>0</v>
       </c>
-      <c r="E66" s="298"/>
+      <c r="E66" s="297"/>
       <c r="G66" s="23">
         <f>IFERROR(G58/BS!$C$67,0)</f>
         <v>0</v>
@@ -12171,7 +12227,7 @@
         <f>G67</f>
         <v>0</v>
       </c>
-      <c r="E67" s="298"/>
+      <c r="E67" s="297"/>
       <c r="G67" s="23">
         <f>IFERROR(G59/BS!$C$68,0)</f>
         <v>0</v>
@@ -12196,7 +12252,7 @@
         <f>G68</f>
         <v>0</v>
       </c>
-      <c r="E68" s="298"/>
+      <c r="E68" s="297"/>
       <c r="G68" s="23">
         <f>IFERROR(G60/BS!$C$69,0)</f>
         <v>0</v>
@@ -12222,7 +12278,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="9"/>
-      <c r="E69" s="303"/>
+      <c r="E69" s="302"/>
       <c r="F69" s="9"/>
       <c r="G69" s="71">
         <f>G61/BS!C70</f>
@@ -12250,7 +12306,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12272,7 +12328,7 @@
       </c>
       <c r="C72" s="62"/>
       <c r="D72" s="27"/>
-      <c r="E72" s="295"/>
+      <c r="E72" s="294"/>
       <c r="F72" s="27"/>
       <c r="G72" s="97"/>
       <c r="H72" s="12"/>
@@ -12296,7 +12352,7 @@
         <v>0.85642249012514848</v>
       </c>
       <c r="D73" s="27"/>
-      <c r="E73" s="295"/>
+      <c r="E73" s="294"/>
       <c r="F73" s="27"/>
       <c r="G73" s="6">
         <f t="shared" ref="G73:Q73" si="24">IF(G$4="","",ABS(G5/G$4))</f>
@@ -12353,7 +12409,7 @@
         <v>0.14357750987485146</v>
       </c>
       <c r="D74" s="27"/>
-      <c r="E74" s="295"/>
+      <c r="E74" s="294"/>
       <c r="F74" s="27"/>
       <c r="G74" s="65">
         <f t="shared" ref="G74:Q74" si="25">IF(G$4="","",ABS(G6/G$4))</f>
@@ -12410,7 +12466,7 @@
         <v>8.0403172060722089E-2</v>
       </c>
       <c r="D75" s="27"/>
-      <c r="E75" s="295"/>
+      <c r="E75" s="294"/>
       <c r="F75" s="27"/>
       <c r="G75" s="6">
         <f t="shared" ref="G75:Q75" si="26">IF(G$4="","",ABS(G7/G$4))</f>
@@ -12467,7 +12523,7 @@
         <v>6.3174337814129386E-2</v>
       </c>
       <c r="D76" s="27"/>
-      <c r="E76" s="295"/>
+      <c r="E76" s="294"/>
       <c r="F76" s="27"/>
       <c r="G76" s="65">
         <f t="shared" ref="G76:Q76" si="27">IF(G$4="","",ABS(G8/G$4))</f>
@@ -12524,7 +12580,7 @@
         <v>0</v>
       </c>
       <c r="D77" s="27"/>
-      <c r="E77" s="295"/>
+      <c r="E77" s="294"/>
       <c r="F77" s="27"/>
       <c r="G77" s="6">
         <f t="shared" ref="G77:Q77" si="28">IF(G$4="","",G9/G$4)</f>
@@ -12581,8 +12637,8 @@
         <v>0</v>
       </c>
       <c r="D78" s="27"/>
-      <c r="E78" s="296" t="s">
-        <v>452</v>
+      <c r="E78" s="295" t="s">
+        <v>460</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12640,7 +12696,7 @@
         <v>0</v>
       </c>
       <c r="D79" s="27"/>
-      <c r="E79" s="295"/>
+      <c r="E79" s="294"/>
       <c r="F79" s="27"/>
       <c r="G79" s="65">
         <f t="shared" ref="G79:Q79" si="30">IF(G$4="","",G11/G$4)</f>
@@ -12697,7 +12753,7 @@
         <v>4.3385565107684878E-3</v>
       </c>
       <c r="D80" s="27"/>
-      <c r="E80" s="295"/>
+      <c r="E80" s="294"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
@@ -12754,7 +12810,7 @@
         <v>5.8835781303360896E-2</v>
       </c>
       <c r="D81" s="27"/>
-      <c r="E81" s="295"/>
+      <c r="E81" s="294"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
@@ -12811,7 +12867,7 @@
         <v>1.4708945325840224E-2</v>
       </c>
       <c r="D82" s="27"/>
-      <c r="E82" s="295"/>
+      <c r="E82" s="294"/>
       <c r="F82" s="27"/>
       <c r="G82" s="6">
         <f t="shared" ref="G82:Q82" si="33">IF(G$4="","",ABS(G14/G$4))</f>
@@ -12864,12 +12920,12 @@
         <f>B15</f>
         <v>NCI’s Share of Profits</v>
       </c>
-      <c r="C83" s="294">
+      <c r="C83" s="293">
         <f>MIN(BS!C62,MAX(G83:K83))</f>
         <v>1.819302080545065E-4</v>
       </c>
       <c r="D83" s="27"/>
-      <c r="E83" s="295"/>
+      <c r="E83" s="294"/>
       <c r="F83" s="27"/>
       <c r="G83" s="6">
         <f t="shared" ref="G83:Q83" si="34">IF(G$4="","",-G15/G$4)</f>
@@ -12926,7 +12982,7 @@
         <v>4.3944905769466171E-2</v>
       </c>
       <c r="D84" s="27"/>
-      <c r="E84" s="295"/>
+      <c r="E84" s="294"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
@@ -12978,26 +13034,26 @@
       <c r="B85" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C85" s="294">
+      <c r="C85" s="293">
         <v>0</v>
       </c>
       <c r="D85" s="27"/>
-      <c r="E85" s="297" t="str">
+      <c r="E85" s="296" t="str">
         <f>E17</f>
         <v>WCInv is by default excluded</v>
       </c>
       <c r="F85" s="27"/>
-      <c r="G85" s="251"/>
-      <c r="H85" s="251"/>
-      <c r="I85" s="251"/>
-      <c r="J85" s="251"/>
-      <c r="K85" s="251"/>
-      <c r="L85" s="251"/>
-      <c r="M85" s="251"/>
-      <c r="N85" s="251"/>
-      <c r="O85" s="251"/>
-      <c r="P85" s="251"/>
-      <c r="Q85" s="251"/>
+      <c r="G85" s="250"/>
+      <c r="H85" s="250"/>
+      <c r="I85" s="250"/>
+      <c r="J85" s="250"/>
+      <c r="K85" s="250"/>
+      <c r="L85" s="250"/>
+      <c r="M85" s="250"/>
+      <c r="N85" s="250"/>
+      <c r="O85" s="250"/>
+      <c r="P85" s="250"/>
+      <c r="Q85" s="250"/>
     </row>
     <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
@@ -13007,7 +13063,7 @@
       <c r="C86" s="77">
         <v>0</v>
       </c>
-      <c r="E86" s="297" t="str">
+      <c r="E86" s="296" t="str">
         <f>E18</f>
         <v>Net borrowing is excluded</v>
       </c>
@@ -13033,7 +13089,7 @@
         <v>4.3944905769466171E-2</v>
       </c>
       <c r="D87" s="75"/>
-      <c r="E87" s="295"/>
+      <c r="E87" s="294"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
@@ -13082,14 +13138,14 @@
     </row>
     <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
-      <c r="E88" s="298"/>
+      <c r="E88" s="297"/>
     </row>
     <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>215</v>
       </c>
-      <c r="E89" s="298"/>
+      <c r="E89" s="297"/>
     </row>
     <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
@@ -13101,7 +13157,7 @@
         <f>G90</f>
         <v>0.128</v>
       </c>
-      <c r="E90" s="298"/>
+      <c r="E90" s="297"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
         <v>0.128</v>
@@ -13157,7 +13213,7 @@
         <f>C90*Common_Shares/scaling_factor</f>
         <v>62381.852672000001</v>
       </c>
-      <c r="E91" s="298"/>
+      <c r="E91" s="297"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
         <v>62381.852672000001</v>
@@ -13212,7 +13268,7 @@
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
         <v>0.45076368583801485</v>
       </c>
-      <c r="E92" s="298"/>
+      <c r="E92" s="297"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
         <v>0.32093887871257842</v>
@@ -13261,13 +13317,13 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
         <v>3.5854341736694682E-2</v>
       </c>
-      <c r="E93" s="298"/>
+      <c r="E93" s="297"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
         <v>3.5854341736694682E-2</v>
@@ -13315,7 +13371,7 @@
     </row>
     <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
-      <c r="E94" s="298"/>
+      <c r="E94" s="297"/>
     </row>
     <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
@@ -13324,7 +13380,7 @@
       </c>
       <c r="C95" s="62"/>
       <c r="D95" s="27"/>
-      <c r="E95" s="295"/>
+      <c r="E95" s="294"/>
       <c r="F95" s="27"/>
       <c r="G95" s="12"/>
       <c r="H95" s="12"/>
@@ -13348,7 +13404,7 @@
         <v>-0.13453873241608505</v>
       </c>
       <c r="D96" s="27"/>
-      <c r="E96" s="295"/>
+      <c r="E96" s="294"/>
       <c r="F96" s="27"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H4="","",G4/H4-1)</f>
@@ -13405,7 +13461,7 @@
         <v>-0.45561632170449917</v>
       </c>
       <c r="D97" s="27"/>
-      <c r="E97" s="295"/>
+      <c r="E97" s="294"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
@@ -13483,7 +13539,7 @@
       <c r="B100" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="E100" s="298"/>
+      <c r="E100" s="297"/>
       <c r="G100" s="97" t="s">
         <v>220</v>
       </c>
@@ -13498,7 +13554,7 @@
         <v>2565063</v>
       </c>
       <c r="D101" s="26"/>
-      <c r="E101" s="299"/>
+      <c r="E101" s="298"/>
       <c r="F101" s="26"/>
       <c r="G101" s="183">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
@@ -13555,7 +13611,7 @@
         <v>348607</v>
       </c>
       <c r="D102" s="89"/>
-      <c r="E102" s="300"/>
+      <c r="E102" s="299"/>
       <c r="F102" s="89"/>
       <c r="G102" s="185">
         <f>IF(G$4="","",Data!D77)</f>
@@ -13612,7 +13668,7 @@
         <v>506592</v>
       </c>
       <c r="D103" s="89"/>
-      <c r="E103" s="300"/>
+      <c r="E103" s="299"/>
       <c r="F103" s="89"/>
       <c r="G103" s="185">
         <f>IF(G$4="","",Data!D78)</f>
@@ -13669,7 +13725,7 @@
         <v>732882</v>
       </c>
       <c r="D104" s="26"/>
-      <c r="E104" s="299"/>
+      <c r="E104" s="298"/>
       <c r="F104" s="26"/>
       <c r="G104" s="183">
         <f>Data!C79</f>
@@ -13726,7 +13782,7 @@
         <v>1832181</v>
       </c>
       <c r="D105" s="26"/>
-      <c r="E105" s="299"/>
+      <c r="E105" s="298"/>
       <c r="F105" s="26"/>
       <c r="G105" s="183">
         <f>Data!C80</f>
@@ -13775,7 +13831,7 @@
     </row>
     <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
-      <c r="E106" s="298"/>
+      <c r="E106" s="297"/>
     </row>
     <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
@@ -13784,7 +13840,7 @@
       </c>
       <c r="C107" s="26"/>
       <c r="D107" s="26"/>
-      <c r="E107" s="299"/>
+      <c r="E107" s="298"/>
       <c r="F107" s="26"/>
       <c r="G107" s="97" t="s">
         <v>220</v>
@@ -13810,7 +13866,7 @@
         <v>0.110696857904521</v>
       </c>
       <c r="D108" s="26"/>
-      <c r="E108" s="299"/>
+      <c r="E108" s="298"/>
       <c r="F108" s="26"/>
       <c r="G108" s="94">
         <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
@@ -13867,7 +13923,7 @@
         <v>0.16086350142012953</v>
       </c>
       <c r="D109" s="26"/>
-      <c r="E109" s="299"/>
+      <c r="E109" s="298"/>
       <c r="F109" s="26"/>
       <c r="G109" s="94">
         <f t="shared" ref="G109:Q109" si="44">IF(G$4="","",G103/G$4)</f>
@@ -13924,7 +13980,7 @@
         <v>0</v>
       </c>
       <c r="D110" s="26"/>
-      <c r="E110" s="299"/>
+      <c r="E110" s="298"/>
       <c r="F110" s="26"/>
       <c r="G110" s="94">
         <f>BS!$G$38/G$4</f>
@@ -13943,63 +13999,63 @@
     </row>
     <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
-      <c r="E111" s="298"/>
+      <c r="E111" s="297"/>
     </row>
     <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="E112" s="298"/>
+      <c r="E112" s="297"/>
     </row>
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C113" s="170"/>
-      <c r="E113" s="298"/>
-      <c r="G113" s="328">
+      <c r="E113" s="297"/>
+      <c r="G113" s="327">
         <f>IF(G$4="","",Data!C$22/Data!C15)</f>
         <v>1.3815926737009756</v>
       </c>
-      <c r="H113" s="328">
+      <c r="H113" s="327">
         <f>IF(H$4="","",Data!D$22/Data!D15)</f>
         <v>1.4278840297234743</v>
       </c>
-      <c r="I113" s="328">
+      <c r="I113" s="327">
         <f>IF(I$4="","",Data!E$22/Data!E15)</f>
         <v>2.018494335713656</v>
       </c>
-      <c r="J113" s="328">
+      <c r="J113" s="327">
         <f>IF(J$4="","",Data!F$22/Data!F15)</f>
         <v>2.7662579957356077</v>
       </c>
-      <c r="K113" s="328">
+      <c r="K113" s="327">
         <f>IF(K$4="","",Data!G$22/Data!G15)</f>
         <v>3.0919089083736089</v>
       </c>
-      <c r="L113" s="328">
+      <c r="L113" s="327">
         <f>IF(L$4="","",Data!H$22/Data!H15)</f>
         <v>1.9543752128021792</v>
       </c>
-      <c r="M113" s="328">
+      <c r="M113" s="327">
         <f>IF(M$4="","",Data!I$22/Data!I15)</f>
         <v>3.6274434870389731</v>
       </c>
-      <c r="N113" s="328">
+      <c r="N113" s="327">
         <f>IF(N$4="","",Data!J$22/Data!J15)</f>
         <v>16.560663477666647</v>
       </c>
-      <c r="O113" s="328">
+      <c r="O113" s="327">
         <f>IF(O$4="","",Data!K$22/Data!K15)</f>
         <v>-12.951392854876579</v>
       </c>
-      <c r="P113" s="328" t="str">
+      <c r="P113" s="327" t="str">
         <f>IF(P$4="","",Data!L$22/Data!L15)</f>
         <v/>
       </c>
-      <c r="Q113" s="328" t="str">
+      <c r="Q113" s="327" t="str">
         <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
         <v/>
       </c>
@@ -14007,58 +14063,58 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C114" s="170"/>
-      <c r="E114" s="298"/>
-      <c r="G114" s="328">
+      <c r="E114" s="297"/>
+      <c r="G114" s="327">
         <f>IF(G$4="","",Data!C$22/G19)</f>
         <v>1.7851604903973288</v>
       </c>
-      <c r="H114" s="328">
+      <c r="H114" s="327">
         <f>IF(H$4="","",Data!D$22/H19)</f>
         <v>1.6914819417164388</v>
       </c>
-      <c r="I114" s="328">
+      <c r="I114" s="327">
         <f>IF(I$4="","",Data!E$22/I19)</f>
         <v>2.7239958805355302</v>
       </c>
-      <c r="J114" s="328">
+      <c r="J114" s="327">
         <f>IF(J$4="","",Data!F$22/J19)</f>
         <v>3.4716681862567911</v>
       </c>
-      <c r="K114" s="328">
+      <c r="K114" s="327">
         <f>IF(K$4="","",Data!G$22/K19)</f>
         <v>2.7106236178681997</v>
       </c>
-      <c r="L114" s="328">
+      <c r="L114" s="327">
         <f>IF(L$4="","",Data!H$22/L19)</f>
         <v>2.6053869257438653</v>
       </c>
-      <c r="M114" s="328">
+      <c r="M114" s="327">
         <f>IF(M$4="","",Data!I$22/M19)</f>
         <v>5.1767562950843287</v>
       </c>
-      <c r="N114" s="328">
+      <c r="N114" s="327">
         <f>IF(N$4="","",Data!J$22/N19)</f>
         <v>-40.213757731181175</v>
       </c>
-      <c r="O114" s="328">
+      <c r="O114" s="327">
         <f>IF(O$4="","",Data!K$22/O19)</f>
         <v>-3.6225373611160414</v>
       </c>
-      <c r="P114" s="328" t="str">
+      <c r="P114" s="327" t="str">
         <f>IF(P$4="","",Data!L$22/P19)</f>
         <v/>
       </c>
-      <c r="Q114" s="328" t="str">
+      <c r="Q114" s="327" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
         <v/>
       </c>
     </row>
     <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
-      <c r="E115" s="298"/>
+      <c r="E115" s="297"/>
     </row>
     <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
@@ -14067,7 +14123,7 @@
       </c>
       <c r="C116" s="55"/>
       <c r="D116" s="55"/>
-      <c r="E116" s="301"/>
+      <c r="E116" s="300"/>
       <c r="F116" s="55"/>
       <c r="G116" s="23" t="str">
         <f>IFERROR(IF(#REF!*G118*(1/#REF!)=G120,"","Error"),"")</f>
@@ -14123,7 +14179,7 @@
         <f>C81</f>
         <v>5.8835781303360896E-2</v>
       </c>
-      <c r="E117" s="298"/>
+      <c r="E117" s="297"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
         <v>9.3537135473147709E-2</v>
@@ -14177,7 +14233,7 @@
         <f>C4/C101</f>
         <v>1.2277297326073906</v>
       </c>
-      <c r="E118" s="298"/>
+      <c r="E118" s="297"/>
       <c r="G118" s="42">
         <f t="shared" ref="G118:Q118" si="46">IF(G4="","",G4/G101)</f>
         <v>1.4185842608933972</v>
@@ -14232,7 +14288,7 @@
         <v>1.4000052396569989</v>
       </c>
       <c r="D119" s="11"/>
-      <c r="E119" s="302"/>
+      <c r="E119" s="301"/>
       <c r="F119" s="11"/>
       <c r="G119" s="15">
         <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G101/G105)</f>
@@ -14289,7 +14345,7 @@
         <v>0.10858582441416999</v>
       </c>
       <c r="D120" s="103"/>
-      <c r="E120" s="301"/>
+      <c r="E120" s="300"/>
       <c r="F120" s="103"/>
       <c r="G120" s="102">
         <f t="shared" ref="G120:Q120" si="48">IF(G$4="","",G8/G105)</f>
@@ -14385,7 +14441,7 @@
       </c>
       <c r="C123" s="180"/>
       <c r="D123" s="27"/>
-      <c r="E123" s="295"/>
+      <c r="E123" s="294"/>
       <c r="F123" s="27"/>
       <c r="G123" s="12"/>
       <c r="H123" s="12"/>
@@ -14410,7 +14466,7 @@
         <v>0.28396253740368455</v>
       </c>
       <c r="D124" s="27"/>
-      <c r="E124" s="295"/>
+      <c r="E124" s="294"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
@@ -14467,7 +14523,7 @@
         <v>7.9541327003833207E-2</v>
       </c>
       <c r="D125" s="27"/>
-      <c r="E125" s="295"/>
+      <c r="E125" s="294"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
@@ -14516,7 +14572,7 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -15249,7 +15305,7 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>ISBLANK(G4)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15317,7 +15373,7 @@
         <v>251</v>
       </c>
       <c r="F4" s="135">
-        <f>Thesis!C86</f>
+        <f>Terminal_Growth</f>
         <v>0</v>
       </c>
       <c r="H4" s="121"/>
@@ -15327,7 +15383,7 @@
         <v>124</v>
       </c>
       <c r="C5" s="228">
-        <f>Thesis!C80</f>
+        <f>Equity_Cost</f>
         <v>0.08</v>
       </c>
       <c r="E5" s="149"/>
@@ -15345,10 +15401,10 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="356" t="s">
+      <c r="E6" s="358" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="356"/>
+      <c r="F6" s="358"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8">
@@ -15363,8 +15419,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="356"/>
-      <c r="F7" s="356"/>
+      <c r="E7" s="358"/>
+      <c r="F7" s="358"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8">
@@ -15379,8 +15435,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="356"/>
-      <c r="F8" s="356"/>
+      <c r="E8" s="358"/>
+      <c r="F8" s="358"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8">
@@ -15395,8 +15451,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
+      <c r="E9" s="358"/>
+      <c r="F9" s="358"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -16741,7 +16797,7 @@
     </row>
     <row r="80" spans="1:8">
       <c r="B80" s="156" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C80" s="156" t="s">
         <v>106</v>
@@ -16772,12 +16828,12 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="C21:F50">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E65 B66:F71">
-    <cfRule type="expression" dxfId="0" priority="14">
+    <cfRule type="expression" dxfId="2" priority="14">
       <formula>ISNUMBER(MATCH(B65, $E$75:$E$78, 0))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16792,6 +16848,1457 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A27DB9BF-8D77-49A8-A09B-23E6CA7BEA90}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:H89"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
+    <col min="2" max="2" width="24.73046875" customWidth="1"/>
+    <col min="3" max="6" width="20.73046875" customWidth="1"/>
+    <col min="7" max="7" width="5.73046875" customWidth="1"/>
+    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:8" ht="13.9">
+      <c r="B2" s="36" t="s">
+        <v>444</v>
+      </c>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="H2" s="131" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" ht="13.15">
+      <c r="B3" s="109" t="s">
+        <v>443</v>
+      </c>
+      <c r="C3" s="107">
+        <f>scaling_factor</f>
+        <v>1000</v>
+      </c>
+      <c r="E3" s="109" t="s">
+        <v>125</v>
+      </c>
+      <c r="H3" s="121"/>
+    </row>
+    <row r="4" spans="2:8">
+      <c r="B4" s="100" t="s">
+        <v>441</v>
+      </c>
+      <c r="C4" s="110">
+        <f>Normalized_FCF!C91</f>
+        <v>62381.852672000001</v>
+      </c>
+      <c r="D4" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="E4" s="100" t="s">
+        <v>251</v>
+      </c>
+      <c r="F4" s="135">
+        <f>Thesis!E22</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="121"/>
+    </row>
+    <row r="5" spans="2:8">
+      <c r="B5" s="227" t="s">
+        <v>124</v>
+      </c>
+      <c r="C5" s="228">
+        <f>Equity_Cost</f>
+        <v>0.08</v>
+      </c>
+      <c r="E5" s="149"/>
+      <c r="H5" s="121"/>
+    </row>
+    <row r="6" spans="2:8" ht="13.15" customHeight="1">
+      <c r="B6" s="150" t="s">
+        <v>442</v>
+      </c>
+      <c r="C6" s="232">
+        <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
+        <v>779773.15839999996</v>
+      </c>
+      <c r="D6" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="E6" s="358"/>
+      <c r="F6" s="358"/>
+      <c r="H6" s="121"/>
+    </row>
+    <row r="7" spans="2:8" ht="13.15">
+      <c r="B7" s="150" t="s">
+        <v>445</v>
+      </c>
+      <c r="C7" s="112">
+        <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
+        <v>1.5999999999999999</v>
+      </c>
+      <c r="D7" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="H7" s="121"/>
+    </row>
+    <row r="8" spans="2:8">
+      <c r="H8" s="121"/>
+    </row>
+    <row r="9" spans="2:8" ht="13.9">
+      <c r="B9" s="36" t="s">
+        <v>230</v>
+      </c>
+      <c r="C9" s="37"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="37"/>
+      <c r="H9" s="121"/>
+    </row>
+    <row r="10" spans="2:8" ht="13.15">
+      <c r="B10" s="120" t="s">
+        <v>136</v>
+      </c>
+      <c r="H10" s="121"/>
+    </row>
+    <row r="11" spans="2:8" ht="13.35" customHeight="1">
+      <c r="B11" s="153" t="s">
+        <v>134</v>
+      </c>
+      <c r="C11" s="162">
+        <f>Scenarios!C65</f>
+        <v>4.6574870890079501E-2</v>
+      </c>
+      <c r="H11" s="121"/>
+    </row>
+    <row r="12" spans="2:8" ht="13.35" customHeight="1">
+      <c r="B12" s="119" t="s">
+        <v>135</v>
+      </c>
+      <c r="C12" s="163">
+        <f>Scenarios!C64</f>
+        <v>10</v>
+      </c>
+      <c r="H12" s="121"/>
+    </row>
+    <row r="13" spans="2:8" ht="13.35" customHeight="1">
+      <c r="B13" s="154" t="s">
+        <v>107</v>
+      </c>
+      <c r="C13" s="141">
+        <f>F47/Common_Shares*scaling_factor</f>
+        <v>1.8567746061853174</v>
+      </c>
+      <c r="D13" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="H13" s="121"/>
+    </row>
+    <row r="14" spans="2:8">
+      <c r="H14" s="121"/>
+    </row>
+    <row r="15" spans="2:8" ht="13.15">
+      <c r="B15" s="129" t="s">
+        <v>108</v>
+      </c>
+      <c r="C15" s="129" t="s">
+        <v>447</v>
+      </c>
+      <c r="D15" s="129" t="s">
+        <v>119</v>
+      </c>
+      <c r="E15" s="129" t="s">
+        <v>110</v>
+      </c>
+      <c r="F15" s="130" t="s">
+        <v>446</v>
+      </c>
+      <c r="H15" s="121"/>
+    </row>
+    <row r="16" spans="2:8">
+      <c r="B16" s="123">
+        <v>1</v>
+      </c>
+      <c r="C16" s="124">
+        <f>C4*(1+D16)</f>
+        <v>65287.279406082365</v>
+      </c>
+      <c r="D16" s="139">
+        <f>IF($C$12&lt;B16,0,DDM!$C$11)</f>
+        <v>4.6574870890079501E-2</v>
+      </c>
+      <c r="E16" s="125">
+        <f t="shared" ref="E16:E45" si="0">IF($C$12&lt;B16,0,1/(1+Equity_Cost)^B16)</f>
+        <v>0.92592592592592582</v>
+      </c>
+      <c r="F16" s="126">
+        <f t="shared" ref="F16:F46" si="1">C16*E16</f>
+        <v>60451.184635261445</v>
+      </c>
+      <c r="H16" s="121"/>
+    </row>
+    <row r="17" spans="2:8">
+      <c r="B17" s="123">
+        <v>2</v>
+      </c>
+      <c r="C17" s="124">
+        <f t="shared" ref="C17:C45" si="2">IF(ROW()-ROW($C$16)&lt;$C$12, $C$16*(1+D17)^(ROW()-ROW($C$16)), 0)</f>
+        <v>68328.026015185198</v>
+      </c>
+      <c r="D17" s="139">
+        <f>IF($C$12&lt;B17,0,DDM!$C$11)</f>
+        <v>4.6574870890079501E-2</v>
+      </c>
+      <c r="E17" s="125">
+        <f t="shared" si="0"/>
+        <v>0.85733882030178321</v>
+      </c>
+      <c r="F17" s="126">
+        <f t="shared" si="1"/>
+        <v>58580.26921740843</v>
+      </c>
+      <c r="H17" s="121"/>
+    </row>
+    <row r="18" spans="2:8">
+      <c r="B18" s="123">
+        <v>3</v>
+      </c>
+      <c r="C18" s="124">
+        <f t="shared" si="2"/>
+        <v>71510.395005016442</v>
+      </c>
+      <c r="D18" s="139">
+        <f>IF($C$12&lt;B18,0,DDM!$C$11)</f>
+        <v>4.6574870890079501E-2</v>
+      </c>
+      <c r="E18" s="125">
+        <f t="shared" si="0"/>
+        <v>0.79383224102016958</v>
+      </c>
+      <c r="F18" s="126">
+        <f t="shared" si="1"/>
+        <v>56767.257123069743</v>
+      </c>
+      <c r="H18" s="121"/>
+    </row>
+    <row r="19" spans="2:8">
+      <c r="B19" s="123">
+        <v>4</v>
+      </c>
+      <c r="C19" s="124">
+        <f t="shared" si="2"/>
+        <v>74840.982419673674</v>
+      </c>
+      <c r="D19" s="139">
+        <f>IF($C$12&lt;B19,0,DDM!$C$11)</f>
+        <v>4.6574870890079501E-2</v>
+      </c>
+      <c r="E19" s="125">
+        <f t="shared" si="0"/>
+        <v>0.73502985279645328</v>
+      </c>
+      <c r="F19" s="126">
+        <f t="shared" si="1"/>
+        <v>55010.356291074691</v>
+      </c>
+      <c r="H19" s="121"/>
+    </row>
+    <row r="20" spans="2:8">
+      <c r="B20" s="123">
+        <v>5</v>
+      </c>
+      <c r="C20" s="124">
+        <f t="shared" si="2"/>
+        <v>78326.691513156693</v>
+      </c>
+      <c r="D20" s="139">
+        <f>IF($C$12&lt;B20,0,DDM!$C$11)</f>
+        <v>4.6574870890079501E-2</v>
+      </c>
+      <c r="E20" s="125">
+        <f t="shared" si="0"/>
+        <v>0.68058319703375303</v>
+      </c>
+      <c r="F20" s="126">
+        <f t="shared" si="1"/>
+        <v>53307.830123100714</v>
+      </c>
+      <c r="H20" s="121"/>
+    </row>
+    <row r="21" spans="2:8">
+      <c r="B21" s="123">
+        <v>6</v>
+      </c>
+      <c r="C21" s="124">
+        <f t="shared" si="2"/>
+        <v>81974.747057629051</v>
+      </c>
+      <c r="D21" s="139">
+        <f>IF($C$12&lt;B21,0,DDM!$C$11)</f>
+        <v>4.6574870890079501E-2</v>
+      </c>
+      <c r="E21" s="125">
+        <f t="shared" si="0"/>
+        <v>0.63016962688310452</v>
+      </c>
+      <c r="F21" s="126">
+        <f t="shared" si="1"/>
+        <v>51657.995767142966</v>
+      </c>
+      <c r="H21" s="121"/>
+    </row>
+    <row r="22" spans="2:8">
+      <c r="B22" s="123">
+        <v>7</v>
+      </c>
+      <c r="C22" s="124">
+        <f t="shared" si="2"/>
+        <v>85792.710318085068</v>
+      </c>
+      <c r="D22" s="139">
+        <f>IF($C$12&lt;B22,0,DDM!$C$11)</f>
+        <v>4.6574870890079501E-2</v>
+      </c>
+      <c r="E22" s="125">
+        <f t="shared" si="0"/>
+        <v>0.58349039526213387</v>
+      </c>
+      <c r="F22" s="126">
+        <f t="shared" si="1"/>
+        <v>50059.222454109207</v>
+      </c>
+      <c r="H22" s="121"/>
+    </row>
+    <row r="23" spans="2:8">
+      <c r="B23" s="123">
+        <v>8</v>
+      </c>
+      <c r="C23" s="124">
+        <f t="shared" si="2"/>
+        <v>89788.494724459873</v>
+      </c>
+      <c r="D23" s="139">
+        <f>IF($C$12&lt;B23,0,DDM!$C$11)</f>
+        <v>4.6574870890079501E-2</v>
+      </c>
+      <c r="E23" s="125">
+        <f t="shared" si="0"/>
+        <v>0.54026888450197574</v>
+      </c>
+      <c r="F23" s="126">
+        <f t="shared" si="1"/>
+        <v>48509.929885895472</v>
+      </c>
+      <c r="H23" s="121"/>
+    </row>
+    <row r="24" spans="2:8">
+      <c r="B24" s="123">
+        <v>9</v>
+      </c>
+      <c r="C24" s="124">
+        <f t="shared" si="2"/>
+        <v>93970.382273666182</v>
+      </c>
+      <c r="D24" s="139">
+        <f>IF($C$12&lt;B24,0,DDM!$C$11)</f>
+        <v>4.6574870890079501E-2</v>
+      </c>
+      <c r="E24" s="125">
+        <f t="shared" si="0"/>
+        <v>0.50024896713145905</v>
+      </c>
+      <c r="F24" s="126">
+        <f t="shared" si="1"/>
+        <v>47008.586673349877</v>
+      </c>
+      <c r="H24" s="121"/>
+    </row>
+    <row r="25" spans="2:8">
+      <c r="B25" s="123">
+        <v>10</v>
+      </c>
+      <c r="C25" s="124">
+        <f t="shared" si="2"/>
+        <v>98347.040695553602</v>
+      </c>
+      <c r="D25" s="139">
+        <f>IF($C$12&lt;B25,0,DDM!$C$11)</f>
+        <v>4.6574870890079501E-2</v>
+      </c>
+      <c r="E25" s="125">
+        <f t="shared" si="0"/>
+        <v>0.46319348808468425</v>
+      </c>
+      <c r="F25" s="126">
+        <f t="shared" si="1"/>
+        <v>45553.708822579865</v>
+      </c>
+      <c r="H25" s="121"/>
+    </row>
+    <row r="26" spans="2:8">
+      <c r="B26" s="123">
+        <v>11</v>
+      </c>
+      <c r="C26" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D26" s="139">
+        <f>IF($C$12&lt;B26,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F26" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H26" s="121"/>
+    </row>
+    <row r="27" spans="2:8">
+      <c r="B27" s="123">
+        <v>12</v>
+      </c>
+      <c r="C27" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D27" s="139">
+        <f>IF($C$12&lt;B27,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E27" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F27" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H27" s="121"/>
+    </row>
+    <row r="28" spans="2:8">
+      <c r="B28" s="123">
+        <v>13</v>
+      </c>
+      <c r="C28" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D28" s="139">
+        <f>IF($C$12&lt;B28,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F28" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H28" s="121"/>
+    </row>
+    <row r="29" spans="2:8">
+      <c r="B29" s="123">
+        <v>14</v>
+      </c>
+      <c r="C29" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D29" s="139">
+        <f>IF($C$12&lt;B29,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E29" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F29" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H29" s="121"/>
+    </row>
+    <row r="30" spans="2:8">
+      <c r="B30" s="123">
+        <v>15</v>
+      </c>
+      <c r="C30" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D30" s="139">
+        <f>IF($C$12&lt;B30,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E30" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F30" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H30" s="121"/>
+    </row>
+    <row r="31" spans="2:8">
+      <c r="B31" s="123">
+        <v>16</v>
+      </c>
+      <c r="C31" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D31" s="139">
+        <f>IF($C$12&lt;B31,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E31" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F31" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H31" s="121"/>
+    </row>
+    <row r="32" spans="2:8">
+      <c r="B32" s="123">
+        <v>17</v>
+      </c>
+      <c r="C32" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D32" s="139">
+        <f>IF($C$12&lt;B32,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E32" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F32" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H32" s="121"/>
+    </row>
+    <row r="33" spans="2:8">
+      <c r="B33" s="123">
+        <v>18</v>
+      </c>
+      <c r="C33" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D33" s="139">
+        <f>IF($C$12&lt;B33,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E33" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F33" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H33" s="121"/>
+    </row>
+    <row r="34" spans="2:8">
+      <c r="B34" s="123">
+        <v>19</v>
+      </c>
+      <c r="C34" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D34" s="139">
+        <f>IF($C$12&lt;B34,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E34" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F34" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H34" s="121"/>
+    </row>
+    <row r="35" spans="2:8">
+      <c r="B35" s="123">
+        <v>20</v>
+      </c>
+      <c r="C35" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D35" s="139">
+        <f>IF($C$12&lt;B35,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E35" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F35" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H35" s="121"/>
+    </row>
+    <row r="36" spans="2:8">
+      <c r="B36" s="123">
+        <v>21</v>
+      </c>
+      <c r="C36" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D36" s="139">
+        <f>IF($C$12&lt;B36,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E36" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F36" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H36" s="121"/>
+    </row>
+    <row r="37" spans="2:8">
+      <c r="B37" s="123">
+        <v>22</v>
+      </c>
+      <c r="C37" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D37" s="139">
+        <f>IF($C$12&lt;B37,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E37" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F37" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H37" s="121"/>
+    </row>
+    <row r="38" spans="2:8">
+      <c r="B38" s="123">
+        <v>23</v>
+      </c>
+      <c r="C38" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D38" s="139">
+        <f>IF($C$12&lt;B38,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E38" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F38" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H38" s="121"/>
+    </row>
+    <row r="39" spans="2:8">
+      <c r="B39" s="123">
+        <v>24</v>
+      </c>
+      <c r="C39" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D39" s="139">
+        <f>IF($C$12&lt;B39,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E39" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F39" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H39" s="121"/>
+    </row>
+    <row r="40" spans="2:8">
+      <c r="B40" s="123">
+        <v>25</v>
+      </c>
+      <c r="C40" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D40" s="139">
+        <f>IF($C$12&lt;B40,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E40" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F40" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H40" s="121"/>
+    </row>
+    <row r="41" spans="2:8">
+      <c r="B41" s="123">
+        <v>26</v>
+      </c>
+      <c r="C41" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D41" s="139">
+        <f>IF($C$12&lt;B41,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E41" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F41" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H41" s="121"/>
+    </row>
+    <row r="42" spans="2:8">
+      <c r="B42" s="123">
+        <v>27</v>
+      </c>
+      <c r="C42" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D42" s="139">
+        <f>IF($C$12&lt;B42,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E42" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F42" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H42" s="121"/>
+    </row>
+    <row r="43" spans="2:8">
+      <c r="B43" s="123">
+        <v>28</v>
+      </c>
+      <c r="C43" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D43" s="139">
+        <f>IF($C$12&lt;B43,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E43" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F43" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H43" s="121"/>
+    </row>
+    <row r="44" spans="2:8">
+      <c r="B44" s="123">
+        <v>29</v>
+      </c>
+      <c r="C44" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D44" s="139">
+        <f>IF($C$12&lt;B44,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E44" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F44" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H44" s="121"/>
+    </row>
+    <row r="45" spans="2:8">
+      <c r="B45" s="123">
+        <v>30</v>
+      </c>
+      <c r="C45" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D45" s="139">
+        <f>IF($C$12&lt;B45,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E45" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F45" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H45" s="121"/>
+    </row>
+    <row r="46" spans="2:8">
+      <c r="B46" s="127" t="s">
+        <v>132</v>
+      </c>
+      <c r="C46" s="124">
+        <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
+        <v>816090.9925760295</v>
+      </c>
+      <c r="D46" s="140">
+        <f>Terminal_Growth</f>
+        <v>0</v>
+      </c>
+      <c r="E46" s="125">
+        <f>1/(1+Equity_Cost)^C12</f>
+        <v>0.46319348808468425</v>
+      </c>
+      <c r="F46" s="126">
+        <f t="shared" si="1"/>
+        <v>378008.03344578325</v>
+      </c>
+      <c r="H46" s="121"/>
+    </row>
+    <row r="47" spans="2:8">
+      <c r="C47" s="115"/>
+      <c r="E47" s="128" t="s">
+        <v>101</v>
+      </c>
+      <c r="F47" s="138">
+        <f>SUM(F16:F46)</f>
+        <v>904914.3744387757</v>
+      </c>
+      <c r="H47" s="121"/>
+    </row>
+    <row r="48" spans="2:8">
+      <c r="C48" s="115"/>
+      <c r="H48" s="121"/>
+    </row>
+    <row r="49" spans="1:8" ht="13.15">
+      <c r="B49" s="120" t="s">
+        <v>130</v>
+      </c>
+      <c r="C49" s="137"/>
+      <c r="D49" s="137"/>
+      <c r="E49" s="118"/>
+      <c r="F49" s="118"/>
+      <c r="H49" s="121"/>
+    </row>
+    <row r="50" spans="1:8" ht="13.15">
+      <c r="A50" s="134">
+        <f>F47</f>
+        <v>904914.3744387757</v>
+      </c>
+      <c r="B50" s="132">
+        <f>C73</f>
+        <v>0</v>
+      </c>
+      <c r="C50" s="132">
+        <f>C72</f>
+        <v>0.02</v>
+      </c>
+      <c r="D50" s="132">
+        <f>C71</f>
+        <v>0.04</v>
+      </c>
+      <c r="E50" s="132">
+        <f>C70</f>
+        <v>0.06</v>
+      </c>
+      <c r="F50" s="132">
+        <f>C69</f>
+        <v>0.1</v>
+      </c>
+      <c r="H50" s="121"/>
+    </row>
+    <row r="51" spans="1:8" ht="13.15">
+      <c r="A51" s="144">
+        <v>5</v>
+      </c>
+      <c r="B51" s="124">
+        <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
+        <v>779773.15839999984</v>
+      </c>
+      <c r="C51" s="124">
+        <v>804932.72239334544</v>
+      </c>
+      <c r="D51" s="124">
+        <v>830845.8043490987</v>
+      </c>
+      <c r="E51" s="124">
+        <v>857545.47106966842</v>
+      </c>
+      <c r="F51" s="124">
+        <v>913441.96149758133</v>
+      </c>
+      <c r="H51" s="121"/>
+    </row>
+    <row r="52" spans="1:8" ht="13.15">
+      <c r="A52" s="144">
+        <v>10</v>
+      </c>
+      <c r="B52" s="124">
+        <v>779773.15839999961</v>
+      </c>
+      <c r="C52" s="124">
+        <v>830115.45436929131</v>
+      </c>
+      <c r="D52" s="124">
+        <v>885503.41146447905</v>
+      </c>
+      <c r="E52" s="124">
+        <v>946540.88475776184</v>
+      </c>
+      <c r="F52" s="124">
+        <v>1088324.0580379562</v>
+      </c>
+      <c r="H52" s="121"/>
+    </row>
+    <row r="53" spans="1:8" ht="13.15">
+      <c r="A53" s="144">
+        <v>15</v>
+      </c>
+      <c r="B53" s="124">
+        <v>779773.15839999961</v>
+      </c>
+      <c r="C53" s="124">
+        <v>861286.06770679553</v>
+      </c>
+      <c r="D53" s="124">
+        <v>956756.53375149774</v>
+      </c>
+      <c r="E53" s="124">
+        <v>1068957.5098304939</v>
+      </c>
+      <c r="F53" s="124">
+        <v>1357487.0898312563</v>
+      </c>
+      <c r="H53" s="121"/>
+    </row>
+    <row r="54" spans="1:8" ht="13.15">
+      <c r="A54" s="145">
+        <v>20</v>
+      </c>
+      <c r="B54" s="124">
+        <v>779773.15839999937</v>
+      </c>
+      <c r="C54" s="124">
+        <v>893043.92394302087</v>
+      </c>
+      <c r="D54" s="124">
+        <v>1033448.1257643478</v>
+      </c>
+      <c r="E54" s="124">
+        <v>1208601.604479718</v>
+      </c>
+      <c r="F54" s="124">
+        <v>1705242.6174882664</v>
+      </c>
+      <c r="H54" s="121"/>
+    </row>
+    <row r="55" spans="1:8" ht="13.15">
+      <c r="A55" s="145">
+        <v>25</v>
+      </c>
+      <c r="B55" s="124">
+        <v>779773.15839999926</v>
+      </c>
+      <c r="C55" s="124">
+        <v>922580.49248645816</v>
+      </c>
+      <c r="D55" s="124">
+        <v>1108991.9528898629</v>
+      </c>
+      <c r="E55" s="124">
+        <v>1354944.3698076683</v>
+      </c>
+      <c r="F55" s="124">
+        <v>2122299.5357449865</v>
+      </c>
+      <c r="H55" s="121"/>
+    </row>
+    <row r="56" spans="1:8" ht="13.15">
+      <c r="A56" s="145">
+        <v>30</v>
+      </c>
+      <c r="B56" s="124">
+        <v>779773.15839999926</v>
+      </c>
+      <c r="C56" s="124">
+        <v>948635.85472004674</v>
+      </c>
+      <c r="D56" s="124">
+        <v>1179739.4164792774</v>
+      </c>
+      <c r="E56" s="124">
+        <v>1501268.5378346723</v>
+      </c>
+      <c r="F56" s="124">
+        <v>2603853.8502877932</v>
+      </c>
+      <c r="H56" s="121"/>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="C57" s="115"/>
+      <c r="D57" s="115"/>
+      <c r="E57" s="115"/>
+      <c r="F57" s="115"/>
+      <c r="H57" s="121"/>
+    </row>
+    <row r="58" spans="1:8" ht="13.15">
+      <c r="B58" s="120" t="s">
+        <v>131</v>
+      </c>
+      <c r="C58" s="115"/>
+      <c r="D58" s="115"/>
+      <c r="E58" s="115"/>
+      <c r="F58" s="115"/>
+      <c r="H58" s="121"/>
+    </row>
+    <row r="59" spans="1:8" ht="13.15">
+      <c r="B59" s="133">
+        <f>B50</f>
+        <v>0</v>
+      </c>
+      <c r="C59" s="133">
+        <f>C50</f>
+        <v>0.02</v>
+      </c>
+      <c r="D59" s="133">
+        <f>D50</f>
+        <v>0.04</v>
+      </c>
+      <c r="E59" s="133">
+        <f>E50</f>
+        <v>0.06</v>
+      </c>
+      <c r="F59" s="133">
+        <f>F50</f>
+        <v>0.1</v>
+      </c>
+      <c r="H59" s="121"/>
+    </row>
+    <row r="60" spans="1:8" ht="13.15">
+      <c r="A60" s="144">
+        <v>0</v>
+      </c>
+      <c r="B60" s="125">
+        <f>C7</f>
+        <v>1.5999999999999999</v>
+      </c>
+      <c r="C60" s="125">
+        <f>C7</f>
+        <v>1.5999999999999999</v>
+      </c>
+      <c r="D60" s="125">
+        <f>C7</f>
+        <v>1.5999999999999999</v>
+      </c>
+      <c r="E60" s="142">
+        <f>C7</f>
+        <v>1.5999999999999999</v>
+      </c>
+      <c r="F60" s="125">
+        <f>C7</f>
+        <v>1.5999999999999999</v>
+      </c>
+      <c r="H60" s="121"/>
+    </row>
+    <row r="61" spans="1:8" ht="13.15">
+      <c r="A61" s="144">
+        <f t="shared" ref="A61:A66" si="3">A51</f>
+        <v>5</v>
+      </c>
+      <c r="B61" s="125">
+        <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
+        <v>1.5999999999999996</v>
+      </c>
+      <c r="C61" s="125">
+        <f t="shared" si="4"/>
+        <v>1.6516243755709052</v>
+      </c>
+      <c r="D61" s="125">
+        <f t="shared" si="4"/>
+        <v>1.7047948786621865</v>
+      </c>
+      <c r="E61" s="125">
+        <f t="shared" si="4"/>
+        <v>1.7595793583441579</v>
+      </c>
+      <c r="F61" s="125">
+        <f t="shared" si="4"/>
+        <v>1.874272181149407</v>
+      </c>
+      <c r="H61" s="121"/>
+    </row>
+    <row r="62" spans="1:8" ht="13.15">
+      <c r="A62" s="144">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="B62" s="125">
+        <f t="shared" si="4"/>
+        <v>1.5999999999999992</v>
+      </c>
+      <c r="C62" s="125">
+        <f t="shared" si="4"/>
+        <v>1.7032962890337753</v>
+      </c>
+      <c r="D62" s="125">
+        <f t="shared" si="4"/>
+        <v>1.8169456630826835</v>
+      </c>
+      <c r="E62" s="125">
+        <f t="shared" si="4"/>
+        <v>1.942187159557939</v>
+      </c>
+      <c r="F62" s="125">
+        <f t="shared" si="4"/>
+        <v>2.2331090447300141</v>
+      </c>
+      <c r="H62" s="121"/>
+    </row>
+    <row r="63" spans="1:8" ht="13.15">
+      <c r="A63" s="144">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="B63" s="125">
+        <f t="shared" si="4"/>
+        <v>1.5999999999999992</v>
+      </c>
+      <c r="C63" s="125">
+        <f t="shared" si="4"/>
+        <v>1.7672546092231236</v>
+      </c>
+      <c r="D63" s="125">
+        <f t="shared" si="4"/>
+        <v>1.9631484329922742</v>
+      </c>
+      <c r="E63" s="125">
+        <f t="shared" si="4"/>
+        <v>2.1933712353451411</v>
+      </c>
+      <c r="F63" s="125">
+        <f t="shared" si="4"/>
+        <v>2.7853989590852914</v>
+      </c>
+      <c r="H63" s="121"/>
+    </row>
+    <row r="64" spans="1:8" ht="13.15">
+      <c r="A64" s="145">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="B64" s="125">
+        <f t="shared" si="4"/>
+        <v>1.5999999999999988</v>
+      </c>
+      <c r="C64" s="125">
+        <f t="shared" si="4"/>
+        <v>1.8324178806573721</v>
+      </c>
+      <c r="D64" s="125">
+        <f t="shared" si="4"/>
+        <v>2.1205102835493506</v>
+      </c>
+      <c r="E64" s="125">
+        <f t="shared" si="4"/>
+        <v>2.4799039904571676</v>
+      </c>
+      <c r="F64" s="125">
+        <f t="shared" si="4"/>
+        <v>3.4989511482795179</v>
+      </c>
+      <c r="H64" s="121"/>
+    </row>
+    <row r="65" spans="1:8" ht="13.15">
+      <c r="A65" s="145">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="B65" s="125">
+        <f t="shared" si="4"/>
+        <v>1.5999999999999985</v>
+      </c>
+      <c r="C65" s="125">
+        <f t="shared" si="4"/>
+        <v>1.8930233390017814</v>
+      </c>
+      <c r="D65" s="125">
+        <f t="shared" si="4"/>
+        <v>2.2755170596851628</v>
+      </c>
+      <c r="E65" s="125">
+        <f t="shared" si="4"/>
+        <v>2.7801816058154141</v>
+      </c>
+      <c r="F65" s="125">
+        <f t="shared" si="4"/>
+        <v>4.3547013905422194</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="13.15">
+      <c r="A66" s="145">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="B66" s="125">
+        <f t="shared" si="4"/>
+        <v>1.5999999999999985</v>
+      </c>
+      <c r="C66" s="125">
+        <f t="shared" si="4"/>
+        <v>1.9464857839765248</v>
+      </c>
+      <c r="D66" s="125">
+        <f t="shared" si="4"/>
+        <v>2.420682279241229</v>
+      </c>
+      <c r="E66" s="125">
+        <f t="shared" si="4"/>
+        <v>3.080421061766411</v>
+      </c>
+      <c r="F66" s="125">
+        <f t="shared" si="4"/>
+        <v>5.3427924718631461</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="13.15">
+      <c r="B68" s="172" t="s">
+        <v>118</v>
+      </c>
+      <c r="C68" s="172" t="s">
+        <v>133</v>
+      </c>
+      <c r="D68" s="172" t="s">
+        <v>113</v>
+      </c>
+      <c r="E68" s="173" t="s">
+        <v>114</v>
+      </c>
+      <c r="F68" s="173" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="B69" s="128" t="str">
+        <f>Scenarios!B54</f>
+        <v>Snowball Scenario</v>
+      </c>
+      <c r="C69" s="143">
+        <f>Scenarios!C56</f>
+        <v>0.1</v>
+      </c>
+      <c r="D69" s="146">
+        <f>Scenarios!C55</f>
+        <v>15</v>
+      </c>
+      <c r="E69" s="136">
+        <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
+        <v>2.7853989590852914</v>
+      </c>
+      <c r="F69" s="143">
+        <f>Scenarios!C58</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="B70" s="128" t="str">
+        <f>Scenarios!B36</f>
+        <v>Optimistic</v>
+      </c>
+      <c r="C70" s="143">
+        <f>Scenarios!C38</f>
+        <v>0.06</v>
+      </c>
+      <c r="D70" s="146">
+        <f>Scenarios!C37</f>
+        <v>10</v>
+      </c>
+      <c r="E70" s="136">
+        <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
+        <v>1.942187159557939</v>
+      </c>
+      <c r="F70" s="143">
+        <f>Scenarios!C40*(1-F$69-F$73)</f>
+        <v>0.18</v>
+      </c>
+      <c r="H70" s="121"/>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="B71" s="128" t="str">
+        <f>Scenarios!B24</f>
+        <v>Base</v>
+      </c>
+      <c r="C71" s="143">
+        <f>Scenarios!C26</f>
+        <v>0.04</v>
+      </c>
+      <c r="D71" s="146">
+        <f>Scenarios!C25</f>
+        <v>10</v>
+      </c>
+      <c r="E71" s="136">
+        <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
+        <v>1.8169456630826835</v>
+      </c>
+      <c r="F71" s="143">
+        <f>Scenarios!C28*(1-F$69-F$73)</f>
+        <v>0.53999999999999992</v>
+      </c>
+      <c r="H71" s="121"/>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="B72" s="128" t="str">
+        <f>Scenarios!B30</f>
+        <v>Pessimistic</v>
+      </c>
+      <c r="C72" s="143">
+        <f>Scenarios!C32</f>
+        <v>0.02</v>
+      </c>
+      <c r="D72" s="146">
+        <f>Scenarios!C31</f>
+        <v>10</v>
+      </c>
+      <c r="E72" s="136">
+        <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
+        <v>1.7032962890337753</v>
+      </c>
+      <c r="F72" s="143">
+        <f>Scenarios!C34*(1-F$69-F$73)</f>
+        <v>0.18</v>
+      </c>
+      <c r="H72" s="121"/>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="B73" s="128" t="str">
+        <f>Scenarios!B48</f>
+        <v>Devil's advocate</v>
+      </c>
+      <c r="C73" s="143">
+        <f>Scenarios!C50</f>
+        <v>0</v>
+      </c>
+      <c r="D73" s="146">
+        <f>Scenarios!C49</f>
+        <v>15</v>
+      </c>
+      <c r="E73" s="136">
+        <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
+        <v>1.5999999999999992</v>
+      </c>
+      <c r="F73" s="143">
+        <f>Scenarios!C52</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="B74" s="156"/>
+      <c r="C74" s="156"/>
+      <c r="D74" s="156"/>
+      <c r="E74" s="156"/>
+      <c r="F74" s="157"/>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="B75" s="156" t="s">
+        <v>311</v>
+      </c>
+      <c r="C75" s="156" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="C76" s="156" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="C77" s="156" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="87" spans="3:3">
+      <c r="C87" s="116"/>
+    </row>
+    <row r="88" spans="3:3">
+      <c r="C88" s="116"/>
+    </row>
+    <row r="89" spans="3:3">
+      <c r="C89" s="116"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="E6:F6"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C16:F45">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E60 B61:F66">
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>ISNUMBER(MATCH(B60, $E$70:$E$73, 0))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C12" xr:uid="{0679E683-700B-4E49-B936-C44C7B75B2A2}">
+      <formula1>$A$51:$A$56</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="59" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
@@ -16812,19 +18319,19 @@
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
-      <c r="H2" s="275" t="s">
-        <v>298</v>
-      </c>
-      <c r="I2" s="276"/>
+      <c r="H2" s="274" t="s">
+        <v>296</v>
+      </c>
+      <c r="I2" s="275"/>
     </row>
     <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="160" t="s">
         <v>149</v>
       </c>
-      <c r="H3" s="274">
-        <v>0</v>
-      </c>
-      <c r="I3" s="262">
+      <c r="H3" s="273">
+        <v>0</v>
+      </c>
+      <c r="I3" s="261">
         <f>-Market_Price</f>
         <v>-3.57</v>
       </c>
@@ -16841,19 +18348,19 @@
         <v>151</v>
       </c>
       <c r="F4" s="156"/>
-      <c r="H4" s="274">
+      <c r="H4" s="273">
         <v>1</v>
       </c>
-      <c r="I4" s="262">
+      <c r="I4" s="261">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
         <v>0.128</v>
       </c>
     </row>
     <row r="5" spans="2:9">
-      <c r="H5" s="274">
+      <c r="H5" s="273">
         <v>2</v>
       </c>
-      <c r="I5" s="262">
+      <c r="I5" s="261">
         <f t="shared" si="0"/>
         <v>0.128</v>
       </c>
@@ -16867,13 +18374,13 @@
         <v>1000</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F6" s="100"/>
-      <c r="H6" s="274">
+      <c r="H6" s="273">
         <v>3</v>
       </c>
-      <c r="I6" s="262">
+      <c r="I6" s="261">
         <f t="shared" si="0"/>
         <v>5.0903808252376095</v>
       </c>
@@ -16890,15 +18397,15 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="358" t="str">
+      <c r="E7" s="360" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 東方表行集團(0398.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="358"/>
-      <c r="H7" s="274">
+      <c r="F7" s="360"/>
+      <c r="H7" s="273">
         <v>4</v>
       </c>
-      <c r="I7" s="262" t="str">
+      <c r="I7" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16915,12 +18422,12 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="358"/>
-      <c r="F8" s="358"/>
-      <c r="H8" s="274">
+      <c r="E8" s="360"/>
+      <c r="F8" s="360"/>
+      <c r="H8" s="273">
         <v>5</v>
       </c>
-      <c r="I8" s="262" t="str">
+      <c r="I8" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16937,37 +18444,37 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="358"/>
-      <c r="F9" s="358"/>
-      <c r="H9" s="274">
+      <c r="E9" s="360"/>
+      <c r="F9" s="360"/>
+      <c r="H9" s="273">
         <v>6</v>
       </c>
-      <c r="I9" s="262" t="str">
+      <c r="I9" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="358"/>
-      <c r="F10" s="358"/>
-      <c r="H10" s="274">
+      <c r="E10" s="360"/>
+      <c r="F10" s="360"/>
+      <c r="H10" s="273">
         <v>7</v>
       </c>
-      <c r="I10" s="262" t="str">
+      <c r="I10" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="160" t="s">
-        <v>278</v>
-      </c>
-      <c r="E11" s="358"/>
-      <c r="F11" s="358"/>
-      <c r="H11" s="274">
+        <v>448</v>
+      </c>
+      <c r="E11" s="360"/>
+      <c r="F11" s="360"/>
+      <c r="H11" s="273">
         <v>8</v>
       </c>
-      <c r="I11" s="262" t="str">
+      <c r="I11" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16981,12 +18488,12 @@
         <v>1.2656410607081225E-2</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="358"/>
-      <c r="F12" s="358"/>
-      <c r="H12" s="274">
+      <c r="E12" s="360"/>
+      <c r="F12" s="360"/>
+      <c r="H12" s="273">
         <v>9</v>
       </c>
-      <c r="I12" s="262" t="str">
+      <c r="I12" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16999,12 +18506,12 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>3.5687612277801151E-2</v>
       </c>
-      <c r="E13" s="358"/>
-      <c r="F13" s="358"/>
-      <c r="H13" s="274">
+      <c r="E13" s="360"/>
+      <c r="F13" s="360"/>
+      <c r="H13" s="273">
         <v>10</v>
       </c>
-      <c r="I13" s="262" t="str">
+      <c r="I13" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -17017,8 +18524,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>1.5957752466103425E-2</v>
       </c>
-      <c r="E14" s="358"/>
-      <c r="F14" s="358"/>
+      <c r="E14" s="360"/>
+      <c r="F14" s="360"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -17034,7 +18541,7 @@
         <v>152</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="18" spans="2:6">
@@ -17044,25 +18551,25 @@
       <c r="C18" s="151">
         <v>10</v>
       </c>
-      <c r="E18" s="358" t="s">
-        <v>333</v>
-      </c>
-      <c r="F18" s="359"/>
+      <c r="E18" s="360" t="s">
+        <v>331</v>
+      </c>
+      <c r="F18" s="361"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="359"/>
-      <c r="F19" s="359"/>
+      <c r="E19" s="361"/>
+      <c r="F19" s="361"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
-        <v>306</v>
-      </c>
-      <c r="E20" s="359"/>
-      <c r="F20" s="359"/>
+        <v>304</v>
+      </c>
+      <c r="E20" s="361"/>
+      <c r="F20" s="361"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
@@ -17072,23 +18579,23 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="359"/>
-      <c r="F21" s="359"/>
+      <c r="E21" s="361"/>
+      <c r="F21" s="361"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C22" s="161">
-        <f>DCF!C12</f>
+        <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
         <v>4.3931077563825554</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="359"/>
-      <c r="F22" s="359"/>
+      <c r="E22" s="361"/>
+      <c r="F22" s="361"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
@@ -17108,8 +18615,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="357"/>
-      <c r="F25" s="357"/>
+      <c r="E25" s="359"/>
+      <c r="F25" s="359"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
@@ -17119,23 +18626,23 @@
         <v>0.04</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="357"/>
-      <c r="F26" s="357"/>
+      <c r="E26" s="359"/>
+      <c r="F26" s="359"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C27" s="161">
-        <f>DCF!E76</f>
+        <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
         <v>4.874392451442584</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="357"/>
-      <c r="F27" s="357"/>
+      <c r="E27" s="359"/>
+      <c r="F27" s="359"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -17145,8 +18652,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="357"/>
-      <c r="F28" s="357"/>
+      <c r="E28" s="359"/>
+      <c r="F28" s="359"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
@@ -17166,8 +18673,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="357"/>
-      <c r="F31" s="357"/>
+      <c r="E31" s="359"/>
+      <c r="F31" s="359"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
@@ -17177,23 +18684,23 @@
         <v>0.02</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="357"/>
-      <c r="F32" s="357"/>
+      <c r="E32" s="359"/>
+      <c r="F32" s="359"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C33" s="161">
-        <f>DCF!E77</f>
+        <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
         <v>4.6222661652764234</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="357"/>
-      <c r="F33" s="357"/>
+      <c r="E33" s="359"/>
+      <c r="F33" s="359"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -17203,8 +18710,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="357"/>
-      <c r="F34" s="357"/>
+      <c r="E34" s="359"/>
+      <c r="F34" s="359"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
@@ -17224,8 +18731,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="357"/>
-      <c r="F37" s="357"/>
+      <c r="E37" s="359"/>
+      <c r="F37" s="359"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
@@ -17235,23 +18742,23 @@
         <v>0.06</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="357"/>
-      <c r="F38" s="357"/>
+      <c r="E38" s="359"/>
+      <c r="F38" s="359"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C39" s="161">
-        <f>DCF!E75</f>
+        <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
         <v>5.1522353664999905</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="357"/>
-      <c r="F39" s="357"/>
+      <c r="E39" s="359"/>
+      <c r="F39" s="359"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -17262,8 +18769,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -17325,8 +18832,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="357"/>
-      <c r="F49" s="357"/>
+      <c r="E49" s="359"/>
+      <c r="F49" s="359"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
@@ -17336,23 +18843,23 @@
         <v>0</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C51" s="161">
-        <f>DCF!E78</f>
+        <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
         <v>4.3931077563825536</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="357"/>
-      <c r="F51" s="357"/>
+      <c r="E51" s="359"/>
+      <c r="F51" s="359"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -17362,12 +18869,12 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="357"/>
-      <c r="F52" s="357"/>
+      <c r="E52" s="359"/>
+      <c r="F52" s="359"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E54" s="160" t="s">
         <v>150</v>
@@ -17383,8 +18890,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="357"/>
-      <c r="F55" s="357"/>
+      <c r="E55" s="359"/>
+      <c r="F55" s="359"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
@@ -17394,23 +18901,23 @@
         <v>0.1</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="357"/>
-      <c r="F56" s="357"/>
+      <c r="E56" s="359"/>
+      <c r="F56" s="359"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C57" s="161">
-        <f>DCF!E74</f>
+        <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
         <v>7.0228647583946318</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="357"/>
-      <c r="F57" s="357"/>
+      <c r="E57" s="359"/>
+      <c r="F57" s="359"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -17420,8 +18927,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -17436,16 +18943,16 @@
         <v>HKD</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>299</v>
-      </c>
-      <c r="F60" s="307">
+        <v>297</v>
+      </c>
+      <c r="F60" s="306">
         <f>Thesis!F28</f>
         <v>3</v>
       </c>
     </row>
     <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -17454,10 +18961,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
-        <v>307</v>
-      </c>
-      <c r="E63" s="279" t="s">
-        <v>314</v>
+        <v>305</v>
+      </c>
+      <c r="E63" s="278" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -17469,8 +18976,8 @@
         <v>10</v>
       </c>
       <c r="D64" s="151"/>
-      <c r="E64" s="278" t="s">
-        <v>398</v>
+      <c r="E64" s="277" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="65" spans="2:6">
@@ -17481,8 +18988,8 @@
         <v>4.6574870890079501E-2</v>
       </c>
       <c r="D65" s="152"/>
-      <c r="E65" s="278" t="s">
-        <v>315</v>
+      <c r="E65" s="277" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="66" spans="2:6">
@@ -17490,30 +18997,30 @@
         <v>103</v>
       </c>
       <c r="C66" s="161">
-        <f>DCF!C18</f>
+        <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
         <v>4.9627512619545433</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E66" s="278" t="s">
-        <v>316</v>
+      <c r="E66" s="277" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
-        <v>353</v>
-      </c>
-      <c r="E68" s="279" t="s">
-        <v>317</v>
+        <v>351</v>
+      </c>
+      <c r="E68" s="278" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
-        <v>308</v>
-      </c>
-      <c r="C69" s="271" t="str">
+        <v>306</v>
+      </c>
+      <c r="C69" s="270" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
         <v>N</v>
       </c>
@@ -17521,38 +19028,38 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
-        <v>296</v>
-      </c>
-      <c r="C70" s="271" t="str">
+        <v>294</v>
+      </c>
+      <c r="C70" s="270" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
-      <c r="E70" s="278" t="s">
-        <v>297</v>
+      <c r="E70" s="277" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
-        <v>295</v>
-      </c>
-      <c r="C71" s="271" t="str">
+        <v>293</v>
+      </c>
+      <c r="C71" s="270" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
         <v>N</v>
       </c>
-      <c r="E71" s="278"/>
+      <c r="E71" s="277"/>
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
-        <v>287</v>
-      </c>
-      <c r="C72" s="270" t="str">
+        <v>285</v>
+      </c>
+      <c r="C72" s="269" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>349</v>
-      </c>
-      <c r="F72" s="324">
+        <v>347</v>
+      </c>
+      <c r="F72" s="323">
         <f>BS!D89/C60</f>
         <v>0.16999421619281041</v>
       </c>
@@ -17572,10 +19079,10 @@
       </c>
     </row>
     <row r="76" spans="2:6">
-      <c r="B76" s="273" t="s">
-        <v>300</v>
-      </c>
-      <c r="C76" s="272">
+      <c r="B76" s="272" t="s">
+        <v>298</v>
+      </c>
+      <c r="C76" s="271">
         <f>F60</f>
         <v>3</v>
       </c>
@@ -17596,12 +19103,12 @@
     </row>
     <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="149" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C80" s="168">
         <f>Thesis!F29</f>
@@ -17645,7 +19152,7 @@
       <c r="E83" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F83" s="324">
+      <c r="F83" s="323">
         <f>(1-C83/C60)</f>
         <v>0.59458376580552363</v>
       </c>
@@ -17655,14 +19162,14 @@
     </row>
     <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="86" spans="2:8">
       <c r="B86" s="149" t="s">
-        <v>303</v>
-      </c>
-      <c r="C86" s="264">
+        <v>301</v>
+      </c>
+      <c r="C86" s="263">
         <f>Market_Price</f>
         <v>3.57</v>
       </c>
@@ -17673,9 +19180,9 @@
     </row>
     <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
-        <v>301</v>
-      </c>
-      <c r="C87" s="263">
+        <v>299</v>
+      </c>
+      <c r="C87" s="262">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
         <v>0.14834835832623461</v>
       </c>
@@ -17685,12 +19192,12 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C90" s="168">
         <f>Thesis!F30</f>
@@ -17734,28 +19241,28 @@
       <c r="E93" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F93" s="324">
+      <c r="F93" s="323">
         <f>(1-C93/C60)</f>
         <v>0.3928689560570815</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G95" s="2"/>
-      <c r="H95" s="311"/>
+      <c r="H95" s="310"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C96" s="135">
         <f>Thesis!F31</f>
         <v>0.08</v>
       </c>
       <c r="G96" s="2"/>
-      <c r="H96" s="311"/>
+      <c r="H96" s="310"/>
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
@@ -17767,7 +19274,7 @@
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
-      <c r="H97" s="311"/>
+      <c r="H97" s="310"/>
     </row>
     <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
@@ -17779,23 +19286,23 @@
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
-      <c r="H98" s="311"/>
+      <c r="H98" s="310"/>
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="111" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
         <v>4.2691663056616189</v>
       </c>
       <c r="D99" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E99" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F99" s="324">
+      <c r="F99" s="323">
         <f>(1-C99/C60)</f>
         <v>0.13969393804894004</v>
       </c>
@@ -17805,12 +19312,12 @@
     </row>
     <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="102" spans="2:8">
       <c r="B102" s="149" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C102" s="135">
         <f>Thesis!F32</f>
@@ -17839,19 +19346,19 @@
     </row>
     <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="111" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C105" s="112">
         <f>C103+C104</f>
         <v>3.8656512307065762</v>
       </c>
       <c r="D105" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E105" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F105" s="324">
+      <c r="F105" s="323">
         <f>(1-C105/C66)</f>
         <v>0.22106689885075603</v>
       </c>
@@ -17860,33 +19367,33 @@
       <c r="B106" s="100"/>
     </row>
     <row r="107" spans="2:8" ht="14.65">
-      <c r="E107" s="315" t="s">
+      <c r="E107" s="314" t="s">
+        <v>325</v>
+      </c>
+      <c r="F107" s="311"/>
+    </row>
+    <row r="108" spans="2:8" ht="13.9">
+      <c r="E108" s="307" t="s">
+        <v>326</v>
+      </c>
+      <c r="F108" s="312" t="s">
         <v>327</v>
       </c>
-      <c r="F107" s="312"/>
-    </row>
-    <row r="108" spans="2:8" ht="13.9">
-      <c r="E108" s="308" t="s">
+    </row>
+    <row r="109" spans="2:8" ht="13.9">
+      <c r="E109" s="308" t="s">
+        <v>326</v>
+      </c>
+      <c r="F109" s="312" t="s">
         <v>328</v>
       </c>
-      <c r="F108" s="313" t="s">
+    </row>
+    <row r="110" spans="2:8" ht="13.9">
+      <c r="E110" s="309" t="s">
+        <v>326</v>
+      </c>
+      <c r="F110" s="313" t="s">
         <v>329</v>
-      </c>
-    </row>
-    <row r="109" spans="2:8" ht="13.9">
-      <c r="E109" s="309" t="s">
-        <v>328</v>
-      </c>
-      <c r="F109" s="313" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="110" spans="2:8" ht="13.9">
-      <c r="E110" s="310" t="s">
-        <v>328</v>
-      </c>
-      <c r="F110" s="314" t="s">
-        <v>331</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/opportunities/0398.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0398.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61570251-3FA5-564C-926F-C86D97A387A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06098EA8-6C95-BF45-948D-99EEED7239A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5180" yWindow="6600" windowWidth="17120" windowHeight="10760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3874,6 +3874,9 @@
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3909,9 +3912,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4220,7 +4220,7 @@
       <c r="C1" s="44">
         <v>45786</v>
       </c>
-      <c r="D1" s="358" t="s">
+      <c r="D1" s="346" t="s">
         <v>461</v>
       </c>
       <c r="E1" s="320" t="s">
@@ -4375,13 +4375,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="346" t="s">
+      <c r="B18" s="347" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="346"/>
-      <c r="D18" s="346"/>
-      <c r="E18" s="346"/>
-      <c r="F18" s="346"/>
+      <c r="C18" s="347"/>
+      <c r="D18" s="347"/>
+      <c r="E18" s="347"/>
+      <c r="F18" s="347"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B20" s="45" t="s">
@@ -4581,22 +4581,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="346" t="s">
+      <c r="B36" s="347" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="346"/>
-      <c r="D36" s="346"/>
-      <c r="E36" s="346"/>
-      <c r="F36" s="346"/>
+      <c r="C36" s="347"/>
+      <c r="D36" s="347"/>
+      <c r="E36" s="347"/>
+      <c r="F36" s="347"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B37" s="348" t="s">
+      <c r="B37" s="349" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="348"/>
-      <c r="D37" s="348"/>
-      <c r="E37" s="348"/>
-      <c r="F37" s="348"/>
+      <c r="C37" s="349"/>
+      <c r="D37" s="349"/>
+      <c r="E37" s="349"/>
+      <c r="F37" s="349"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B39" s="232" t="s">
@@ -4608,13 +4608,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B40" s="347" t="s">
+      <c r="B40" s="348" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="347"/>
-      <c r="D40" s="347"/>
-      <c r="E40" s="347"/>
-      <c r="F40" s="347"/>
+      <c r="C40" s="348"/>
+      <c r="D40" s="348"/>
+      <c r="E40" s="348"/>
+      <c r="F40" s="348"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B41" s="47" t="s">
@@ -4634,13 +4634,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B43" s="347" t="s">
+      <c r="B43" s="348" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="347"/>
-      <c r="D43" s="347"/>
-      <c r="E43" s="347"/>
-      <c r="F43" s="347"/>
+      <c r="C43" s="348"/>
+      <c r="D43" s="348"/>
+      <c r="E43" s="348"/>
+      <c r="F43" s="348"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B44" s="47" t="s">
@@ -4669,13 +4669,13 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B47" s="347" t="s">
+      <c r="B47" s="348" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="347"/>
-      <c r="D47" s="347"/>
-      <c r="E47" s="347"/>
-      <c r="F47" s="347"/>
+      <c r="C47" s="348"/>
+      <c r="D47" s="348"/>
+      <c r="E47" s="348"/>
+      <c r="F47" s="348"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B48" s="47" t="s">
@@ -4691,13 +4691,13 @@
       </c>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B50" s="347" t="s">
+      <c r="B50" s="348" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="347"/>
-      <c r="D50" s="347"/>
-      <c r="E50" s="347"/>
-      <c r="F50" s="347"/>
+      <c r="C50" s="348"/>
+      <c r="D50" s="348"/>
+      <c r="E50" s="348"/>
+      <c r="F50" s="348"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B51" s="47" t="s">
@@ -4761,13 +4761,13 @@
       </c>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B58" s="347" t="s">
+      <c r="B58" s="348" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="347"/>
-      <c r="D58" s="347"/>
-      <c r="E58" s="347"/>
-      <c r="F58" s="347"/>
+      <c r="C58" s="348"/>
+      <c r="D58" s="348"/>
+      <c r="E58" s="348"/>
+      <c r="F58" s="348"/>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B59" s="47" t="s">
@@ -4783,13 +4783,13 @@
       </c>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B61" s="347" t="s">
+      <c r="B61" s="348" t="s">
         <v>339</v>
       </c>
-      <c r="C61" s="350"/>
-      <c r="D61" s="350"/>
-      <c r="E61" s="350"/>
-      <c r="F61" s="350"/>
+      <c r="C61" s="351"/>
+      <c r="D61" s="351"/>
+      <c r="E61" s="351"/>
+      <c r="F61" s="351"/>
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B62" s="47" t="s">
@@ -4805,22 +4805,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B64" s="346" t="s">
+      <c r="B64" s="347" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="346"/>
-      <c r="D64" s="346"/>
-      <c r="E64" s="346"/>
-      <c r="F64" s="346"/>
+      <c r="C64" s="347"/>
+      <c r="D64" s="347"/>
+      <c r="E64" s="347"/>
+      <c r="F64" s="347"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B65" s="346" t="s">
+      <c r="B65" s="347" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="346"/>
-      <c r="D65" s="346"/>
-      <c r="E65" s="346"/>
-      <c r="F65" s="346"/>
+      <c r="C65" s="347"/>
+      <c r="D65" s="347"/>
+      <c r="E65" s="347"/>
+      <c r="F65" s="347"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B67" s="47" t="s">
@@ -4889,22 +4889,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="17"/>
-      <c r="B74" s="346" t="s">
+      <c r="B74" s="347" t="s">
         <v>363</v>
       </c>
-      <c r="C74" s="346"/>
-      <c r="D74" s="346"/>
-      <c r="E74" s="346"/>
-      <c r="F74" s="346"/>
+      <c r="C74" s="347"/>
+      <c r="D74" s="347"/>
+      <c r="E74" s="347"/>
+      <c r="F74" s="347"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B75" s="348" t="s">
+      <c r="B75" s="349" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="348"/>
-      <c r="D75" s="348"/>
-      <c r="E75" s="348"/>
-      <c r="F75" s="348"/>
+      <c r="C75" s="349"/>
+      <c r="D75" s="349"/>
+      <c r="E75" s="349"/>
+      <c r="F75" s="349"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B77" s="232" t="s">
@@ -4948,22 +4948,22 @@
       <c r="C82" s="122"/>
     </row>
     <row r="83" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B83" s="346" t="s">
+      <c r="B83" s="347" t="s">
         <v>364</v>
       </c>
-      <c r="C83" s="346"/>
-      <c r="D83" s="346"/>
-      <c r="E83" s="346"/>
-      <c r="F83" s="346"/>
+      <c r="C83" s="347"/>
+      <c r="D83" s="347"/>
+      <c r="E83" s="347"/>
+      <c r="F83" s="347"/>
     </row>
     <row r="84" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B84" s="346" t="s">
+      <c r="B84" s="347" t="s">
         <v>365</v>
       </c>
-      <c r="C84" s="346"/>
-      <c r="D84" s="346"/>
-      <c r="E84" s="346"/>
-      <c r="F84" s="346"/>
+      <c r="C84" s="347"/>
+      <c r="D84" s="347"/>
+      <c r="E84" s="347"/>
+      <c r="F84" s="347"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B86" s="47" t="s">
@@ -5000,13 +5000,13 @@
       <c r="A90" s="231"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B91" s="346" t="s">
+      <c r="B91" s="347" t="s">
         <v>366</v>
       </c>
-      <c r="C91" s="346"/>
-      <c r="D91" s="346"/>
-      <c r="E91" s="346"/>
-      <c r="F91" s="346"/>
+      <c r="C91" s="347"/>
+      <c r="D91" s="347"/>
+      <c r="E91" s="347"/>
+      <c r="F91" s="347"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B92" s="1" t="s">
@@ -5019,13 +5019,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B95" s="346" t="s">
+      <c r="B95" s="347" t="s">
         <v>345</v>
       </c>
-      <c r="C95" s="346"/>
-      <c r="D95" s="346"/>
-      <c r="E95" s="346"/>
-      <c r="F95" s="346"/>
+      <c r="C95" s="347"/>
+      <c r="D95" s="347"/>
+      <c r="E95" s="347"/>
+      <c r="F95" s="347"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B96" s="47" t="s">
@@ -5156,13 +5156,13 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B111" s="346" t="s">
+      <c r="B111" s="347" t="s">
         <v>367</v>
       </c>
-      <c r="C111" s="346"/>
-      <c r="D111" s="346"/>
-      <c r="E111" s="346"/>
-      <c r="F111" s="346"/>
+      <c r="C111" s="347"/>
+      <c r="D111" s="347"/>
+      <c r="E111" s="347"/>
+      <c r="F111" s="347"/>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B113" s="47" t="s">
@@ -5201,13 +5201,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B118" s="347" t="s">
+      <c r="B118" s="348" t="s">
         <v>368</v>
       </c>
-      <c r="C118" s="347"/>
-      <c r="D118" s="347"/>
-      <c r="E118" s="347"/>
-      <c r="F118" s="347"/>
+      <c r="C118" s="348"/>
+      <c r="D118" s="348"/>
+      <c r="E118" s="348"/>
+      <c r="F118" s="348"/>
     </row>
     <row r="120" spans="1:6" ht="14" x14ac:dyDescent="0.2">
       <c r="B120" s="255" t="s">
@@ -5350,13 +5350,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B129" s="351" t="s">
+      <c r="B129" s="352" t="s">
         <v>371</v>
       </c>
-      <c r="C129" s="351"/>
-      <c r="D129" s="351"/>
-      <c r="E129" s="351"/>
-      <c r="F129" s="351"/>
+      <c r="C129" s="352"/>
+      <c r="D129" s="352"/>
+      <c r="E129" s="352"/>
+      <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A131" s="244" t="s">
@@ -5369,22 +5369,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B133" s="349" t="s">
+      <c r="B133" s="350" t="s">
         <v>369</v>
       </c>
-      <c r="C133" s="349"/>
-      <c r="D133" s="349"/>
-      <c r="E133" s="349"/>
-      <c r="F133" s="349"/>
+      <c r="C133" s="350"/>
+      <c r="D133" s="350"/>
+      <c r="E133" s="350"/>
+      <c r="F133" s="350"/>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B134" s="346" t="s">
+      <c r="B134" s="347" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="346"/>
-      <c r="D134" s="346"/>
-      <c r="E134" s="346"/>
-      <c r="F134" s="346"/>
+      <c r="C134" s="347"/>
+      <c r="D134" s="347"/>
+      <c r="E134" s="347"/>
+      <c r="F134" s="347"/>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B135" s="232" t="s">
@@ -5717,13 +5717,13 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B174" s="353" t="s">
+      <c r="B174" s="354" t="s">
         <v>377</v>
       </c>
-      <c r="C174" s="346"/>
-      <c r="D174" s="346"/>
-      <c r="E174" s="346"/>
-      <c r="F174" s="346"/>
+      <c r="C174" s="347"/>
+      <c r="D174" s="347"/>
+      <c r="E174" s="347"/>
+      <c r="F174" s="347"/>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B176" s="232" t="s">
@@ -5731,13 +5731,13 @@
       </c>
     </row>
     <row r="177" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B177" s="350" t="s">
+      <c r="B177" s="351" t="s">
         <v>381</v>
       </c>
-      <c r="C177" s="350"/>
-      <c r="D177" s="350"/>
-      <c r="E177" s="350"/>
-      <c r="F177" s="350"/>
+      <c r="C177" s="351"/>
+      <c r="D177" s="351"/>
+      <c r="E177" s="351"/>
+      <c r="F177" s="351"/>
     </row>
     <row r="178" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B178" s="236" t="s">
@@ -5760,13 +5760,13 @@
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B183" s="347" t="s">
+      <c r="B183" s="348" t="s">
         <v>382</v>
       </c>
-      <c r="C183" s="347"/>
-      <c r="D183" s="347"/>
-      <c r="E183" s="347"/>
-      <c r="F183" s="347"/>
+      <c r="C183" s="348"/>
+      <c r="D183" s="348"/>
+      <c r="E183" s="348"/>
+      <c r="F183" s="348"/>
     </row>
     <row r="185" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B185" s="1" t="s">
@@ -5774,22 +5774,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B186" s="352" t="s">
+      <c r="B186" s="353" t="s">
         <v>383</v>
       </c>
-      <c r="C186" s="352"/>
-      <c r="D186" s="352"/>
-      <c r="E186" s="352"/>
-      <c r="F186" s="352"/>
+      <c r="C186" s="353"/>
+      <c r="D186" s="353"/>
+      <c r="E186" s="353"/>
+      <c r="F186" s="353"/>
     </row>
     <row r="187" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B187" s="352" t="s">
+      <c r="B187" s="353" t="s">
         <v>384</v>
       </c>
-      <c r="C187" s="352"/>
-      <c r="D187" s="352"/>
-      <c r="E187" s="352"/>
-      <c r="F187" s="352"/>
+      <c r="C187" s="353"/>
+      <c r="D187" s="353"/>
+      <c r="E187" s="353"/>
+      <c r="F187" s="353"/>
     </row>
     <row r="189" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B189" s="1" t="s">
@@ -15414,10 +15414,10 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="354" t="s">
+      <c r="E6" s="355" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="354"/>
+      <c r="F6" s="355"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.15">
@@ -15432,8 +15432,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="354"/>
-      <c r="F7" s="354"/>
+      <c r="E7" s="355"/>
+      <c r="F7" s="355"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.15">
@@ -15448,8 +15448,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="354"/>
-      <c r="F8" s="354"/>
+      <c r="E8" s="355"/>
+      <c r="F8" s="355"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.15">
@@ -15464,8 +15464,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="354"/>
-      <c r="F9" s="354"/>
+      <c r="E9" s="355"/>
+      <c r="F9" s="355"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.15">
@@ -16944,8 +16944,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="354"/>
-      <c r="F6" s="354"/>
+      <c r="E6" s="355"/>
+      <c r="F6" s="355"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.15">
@@ -18410,11 +18410,11 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="356" t="str">
+      <c r="E7" s="357" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 東方表行集團(0398.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="356"/>
+      <c r="F7" s="357"/>
       <c r="H7" s="269">
         <v>4</v>
       </c>
@@ -18435,8 +18435,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="356"/>
-      <c r="F8" s="356"/>
+      <c r="E8" s="357"/>
+      <c r="F8" s="357"/>
       <c r="H8" s="269">
         <v>5</v>
       </c>
@@ -18457,8 +18457,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
+      <c r="E9" s="357"/>
+      <c r="F9" s="357"/>
       <c r="H9" s="269">
         <v>6</v>
       </c>
@@ -18468,8 +18468,8 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="E10" s="356"/>
-      <c r="F10" s="356"/>
+      <c r="E10" s="357"/>
+      <c r="F10" s="357"/>
       <c r="H10" s="269">
         <v>7</v>
       </c>
@@ -18482,8 +18482,8 @@
       <c r="B11" s="160" t="s">
         <v>448</v>
       </c>
-      <c r="E11" s="356"/>
-      <c r="F11" s="356"/>
+      <c r="E11" s="357"/>
+      <c r="F11" s="357"/>
       <c r="H11" s="269">
         <v>8</v>
       </c>
@@ -18501,8 +18501,8 @@
         <v>1.2656410607081225E-2</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="356"/>
-      <c r="F12" s="356"/>
+      <c r="E12" s="357"/>
+      <c r="F12" s="357"/>
       <c r="H12" s="269">
         <v>9</v>
       </c>
@@ -18519,8 +18519,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>3.5687612277801151E-2</v>
       </c>
-      <c r="E13" s="356"/>
-      <c r="F13" s="356"/>
+      <c r="E13" s="357"/>
+      <c r="F13" s="357"/>
       <c r="H13" s="269">
         <v>10</v>
       </c>
@@ -18537,8 +18537,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>1.5957752466103425E-2</v>
       </c>
-      <c r="E14" s="356"/>
-      <c r="F14" s="356"/>
+      <c r="E14" s="357"/>
+      <c r="F14" s="357"/>
     </row>
     <row r="16" spans="2:9" ht="16" x14ac:dyDescent="0.25">
       <c r="B16" s="36" t="s">
@@ -18564,21 +18564,21 @@
       <c r="C18" s="151">
         <v>10</v>
       </c>
-      <c r="E18" s="356" t="s">
+      <c r="E18" s="357" t="s">
         <v>331</v>
       </c>
-      <c r="F18" s="357"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="E19" s="357"/>
-      <c r="F19" s="357"/>
+      <c r="E19" s="358"/>
+      <c r="F19" s="358"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B20" s="160" t="s">
         <v>304</v>
       </c>
-      <c r="E20" s="357"/>
-      <c r="F20" s="357"/>
+      <c r="E20" s="358"/>
+      <c r="F20" s="358"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B21" s="100" t="s">
@@ -18592,8 +18592,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="357"/>
-      <c r="F21" s="357"/>
+      <c r="E21" s="358"/>
+      <c r="F21" s="358"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B22" s="100" t="s">
@@ -18607,8 +18607,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="357"/>
-      <c r="F22" s="357"/>
+      <c r="E22" s="358"/>
+      <c r="F22" s="358"/>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B24" s="160" t="s">
@@ -18628,8 +18628,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="355"/>
-      <c r="F25" s="355"/>
+      <c r="E25" s="356"/>
+      <c r="F25" s="356"/>
     </row>
     <row r="26" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B26" s="119" t="s">
@@ -18639,8 +18639,8 @@
         <v>0.04</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="355"/>
-      <c r="F26" s="355"/>
+      <c r="E26" s="356"/>
+      <c r="F26" s="356"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B27" s="100" t="s">
@@ -18654,8 +18654,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="355"/>
-      <c r="F27" s="355"/>
+      <c r="E27" s="356"/>
+      <c r="F27" s="356"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B28" s="100" t="s">
@@ -18665,8 +18665,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="355"/>
-      <c r="F28" s="355"/>
+      <c r="E28" s="356"/>
+      <c r="F28" s="356"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B30" s="160" t="s">
@@ -18686,8 +18686,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="355"/>
-      <c r="F31" s="355"/>
+      <c r="E31" s="356"/>
+      <c r="F31" s="356"/>
     </row>
     <row r="32" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B32" s="119" t="s">
@@ -18697,8 +18697,8 @@
         <v>0.02</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="355"/>
-      <c r="F32" s="355"/>
+      <c r="E32" s="356"/>
+      <c r="F32" s="356"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B33" s="100" t="s">
@@ -18712,8 +18712,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="355"/>
-      <c r="F33" s="355"/>
+      <c r="E33" s="356"/>
+      <c r="F33" s="356"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B34" s="100" t="s">
@@ -18723,8 +18723,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="355"/>
-      <c r="F34" s="355"/>
+      <c r="E34" s="356"/>
+      <c r="F34" s="356"/>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B36" s="160" t="s">
@@ -18744,8 +18744,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="355"/>
-      <c r="F37" s="355"/>
+      <c r="E37" s="356"/>
+      <c r="F37" s="356"/>
     </row>
     <row r="38" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B38" s="119" t="s">
@@ -18755,8 +18755,8 @@
         <v>0.06</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="355"/>
-      <c r="F38" s="355"/>
+      <c r="E38" s="356"/>
+      <c r="F38" s="356"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B39" s="100" t="s">
@@ -18770,8 +18770,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="355"/>
-      <c r="F39" s="355"/>
+      <c r="E39" s="356"/>
+      <c r="F39" s="356"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B40" s="100" t="s">
@@ -18782,8 +18782,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="355"/>
-      <c r="F40" s="355"/>
+      <c r="E40" s="356"/>
+      <c r="F40" s="356"/>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B42" s="100" t="s">
@@ -18845,8 +18845,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="355"/>
-      <c r="F49" s="355"/>
+      <c r="E49" s="356"/>
+      <c r="F49" s="356"/>
     </row>
     <row r="50" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B50" s="119" t="s">
@@ -18856,8 +18856,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="355"/>
-      <c r="F50" s="355"/>
+      <c r="E50" s="356"/>
+      <c r="F50" s="356"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B51" s="100" t="s">
@@ -18871,8 +18871,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="355"/>
-      <c r="F51" s="355"/>
+      <c r="E51" s="356"/>
+      <c r="F51" s="356"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B52" s="100" t="s">
@@ -18882,8 +18882,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="355"/>
-      <c r="F52" s="355"/>
+      <c r="E52" s="356"/>
+      <c r="F52" s="356"/>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B54" s="160" t="s">
@@ -18903,8 +18903,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="355"/>
-      <c r="F55" s="355"/>
+      <c r="E55" s="356"/>
+      <c r="F55" s="356"/>
     </row>
     <row r="56" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B56" s="119" t="s">
@@ -18914,8 +18914,8 @@
         <v>0.1</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="355"/>
-      <c r="F56" s="355"/>
+      <c r="E56" s="356"/>
+      <c r="F56" s="356"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B57" s="100" t="s">
@@ -18929,8 +18929,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="355"/>
-      <c r="F57" s="355"/>
+      <c r="E57" s="356"/>
+      <c r="F57" s="356"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B58" s="100" t="s">
@@ -18940,8 +18940,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="355"/>
-      <c r="F58" s="355"/>
+      <c r="E58" s="356"/>
+      <c r="F58" s="356"/>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B60" s="100" t="s">

--- a/financial_models/opportunities/0398.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0398.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06098EA8-6C95-BF45-948D-99EEED7239A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC256139-B525-43B9-903B-703FD7B06BCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5180" yWindow="6600" windowWidth="17120" windowHeight="10760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -38,17 +38,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -2502,7 +2491,7 @@
     <numFmt numFmtId="179" formatCode="0\x"/>
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
   </numFmts>
-  <fonts count="59" x14ac:knownFonts="1">
+  <fonts count="59">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3915,7 +3904,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4204,7 +4193,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J192"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
@@ -4213,7 +4202,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10">
       <c r="B1" s="3" t="s">
         <v>41</v>
       </c>
@@ -4230,7 +4219,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="244" t="s">
         <v>268</v>
       </c>
@@ -4244,7 +4233,7 @@
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
         <v>416</v>
       </c>
@@ -4253,7 +4242,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
         <v>316</v>
       </c>
@@ -4261,7 +4250,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
         <v>0</v>
       </c>
@@ -4270,7 +4259,7 @@
       </c>
       <c r="E6" s="48"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
         <v>308</v>
       </c>
@@ -4280,7 +4269,7 @@
       <c r="D7" s="48"/>
       <c r="E7" s="48"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10">
       <c r="B8" s="1" t="s">
         <v>269</v>
       </c>
@@ -4290,17 +4279,17 @@
       </c>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:10">
       <c r="E9" s="34"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
         <v>419</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
         <v>418</v>
       </c>
@@ -4312,7 +4301,7 @@
       </c>
       <c r="E11" s="34"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:10">
       <c r="B12" s="4" t="s">
         <v>95</v>
       </c>
@@ -4322,7 +4311,7 @@
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
         <v>417</v>
       </c>
@@ -4332,7 +4321,7 @@
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
         <v>421</v>
       </c>
@@ -4346,7 +4335,7 @@
       </c>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
         <v>420</v>
       </c>
@@ -4360,7 +4349,7 @@
       </c>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:10">
       <c r="B16" s="4" t="s">
         <v>1</v>
       </c>
@@ -4370,11 +4359,11 @@
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:6">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:6" ht="24.5" customHeight="1">
       <c r="B18" s="347" t="s">
         <v>360</v>
       </c>
@@ -4383,14 +4372,14 @@
       <c r="E18" s="347"/>
       <c r="F18" s="347"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
         <v>307</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
         <v>349</v>
       </c>
@@ -4405,7 +4394,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:6">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
@@ -4418,7 +4407,7 @@
       </c>
       <c r="E22" s="343"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
         <v>435</v>
       </c>
@@ -4426,7 +4415,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
         <v>436</v>
       </c>
@@ -4434,7 +4423,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
         <v>348</v>
       </c>
@@ -4450,28 +4439,28 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:6">
       <c r="B26" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (HKD) :</v>
       </c>
       <c r="C26" s="334">
         <f>C127</f>
-        <v>4.9623808252376094</v>
+        <v>5.2246962590200807</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>400</v>
       </c>
       <c r="E26" s="331">
         <f ca="1">Scenarios!C87</f>
-        <v>0.14834835832623461</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
+        <v>0.1671769416467408</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
         <v>434</v>
       </c>
@@ -4490,13 +4479,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
         <v>426</v>
       </c>
       <c r="C29" s="340">
         <f>C144</f>
-        <v>2.0118297468067095</v>
+        <v>2.2556276815093281</v>
       </c>
       <c r="D29" s="340" t="str">
         <f>D144</f>
@@ -4506,16 +4495,16 @@
         <v>425</v>
       </c>
       <c r="F29" s="332">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
+        <v>0.3674</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
         <v>427</v>
       </c>
       <c r="C30" s="341">
         <f>C152</f>
-        <v>3.012815450868831</v>
+        <v>3.1582019073444916</v>
       </c>
       <c r="D30" s="341" t="str">
         <f>D152</f>
@@ -4528,13 +4517,13 @@
         <v>0.21740000000000001</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C31" s="341">
         <f>C160</f>
-        <v>4.2691663056616189</v>
+        <v>4.5385417708791076</v>
       </c>
       <c r="D31" s="341" t="str">
         <f>D160</f>
@@ -4544,16 +4533,16 @@
         <v>437</v>
       </c>
       <c r="F31" s="342">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.15">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
         <v>429</v>
       </c>
       <c r="C32" s="341">
         <f>C168</f>
-        <v>3.8656512307065762</v>
+        <v>4.0536685441183486</v>
       </c>
       <c r="D32" s="341" t="str">
         <f>D168</f>
@@ -4566,11 +4555,11 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:6">
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
     </row>
-    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="13.9">
       <c r="A34" s="244" t="s">
         <v>355</v>
       </c>
@@ -4580,7 +4569,7 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:6" ht="24.5" customHeight="1">
       <c r="B36" s="347" t="s">
         <v>361</v>
       </c>
@@ -4589,7 +4578,7 @@
       <c r="E36" s="347"/>
       <c r="F36" s="347"/>
     </row>
-    <row r="37" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:6" ht="24.5" customHeight="1">
       <c r="B37" s="349" t="s">
         <v>340</v>
       </c>
@@ -4598,7 +4587,7 @@
       <c r="E37" s="349"/>
       <c r="F37" s="349"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:6">
       <c r="B39" s="232" t="s">
         <v>231</v>
       </c>
@@ -4607,7 +4596,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:6" ht="24.5" customHeight="1">
       <c r="B40" s="348" t="s">
         <v>232</v>
       </c>
@@ -4616,7 +4605,7 @@
       <c r="E40" s="348"/>
       <c r="F40" s="348"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
         <v>233</v>
       </c>
@@ -4629,11 +4618,11 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:6">
       <c r="B42" s="47"/>
       <c r="C42" s="76"/>
     </row>
-    <row r="43" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:6" ht="24.5" customHeight="1">
       <c r="B43" s="348" t="s">
         <v>234</v>
       </c>
@@ -4642,7 +4631,7 @@
       <c r="E43" s="348"/>
       <c r="F43" s="348"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
         <v>235</v>
       </c>
@@ -4655,7 +4644,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:6">
       <c r="B45" s="52" t="s">
         <v>236</v>
       </c>
@@ -4668,7 +4657,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:6">
       <c r="B47" s="348" t="s">
         <v>237</v>
       </c>
@@ -4677,7 +4666,7 @@
       <c r="E47" s="348"/>
       <c r="F47" s="348"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
         <v>238</v>
       </c>
@@ -4690,7 +4679,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:6">
       <c r="B50" s="348" t="s">
         <v>241</v>
       </c>
@@ -4699,7 +4688,7 @@
       <c r="E50" s="348"/>
       <c r="F50" s="348"/>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
         <v>341</v>
       </c>
@@ -4714,7 +4703,7 @@
       <c r="E51" s="311"/>
       <c r="F51" s="311"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
         <v>342</v>
       </c>
@@ -4729,7 +4718,7 @@
       <c r="E52" s="311"/>
       <c r="F52" s="311"/>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
         <v>239</v>
       </c>
@@ -4742,12 +4731,12 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="1" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
         <v>266</v>
       </c>
@@ -4760,7 +4749,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:6">
       <c r="B58" s="348" t="s">
         <v>242</v>
       </c>
@@ -4769,7 +4758,7 @@
       <c r="E58" s="348"/>
       <c r="F58" s="348"/>
     </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
         <v>240</v>
       </c>
@@ -4782,7 +4771,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:6">
       <c r="B61" s="348" t="s">
         <v>339</v>
       </c>
@@ -4791,7 +4780,7 @@
       <c r="E61" s="351"/>
       <c r="F61" s="351"/>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
         <v>243</v>
       </c>
@@ -4804,7 +4793,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:6" ht="24.5" customHeight="1">
       <c r="B64" s="347" t="s">
         <v>344</v>
       </c>
@@ -4813,7 +4802,7 @@
       <c r="E64" s="347"/>
       <c r="F64" s="347"/>
     </row>
-    <row r="65" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:6" ht="24.5" customHeight="1">
       <c r="B65" s="347" t="s">
         <v>362</v>
       </c>
@@ -4822,7 +4811,7 @@
       <c r="E65" s="347"/>
       <c r="F65" s="347"/>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
         <v>271</v>
       </c>
@@ -4835,7 +4824,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:6">
       <c r="B68" s="47" t="s">
         <v>249</v>
       </c>
@@ -4848,7 +4837,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:6">
       <c r="B69" s="249" t="s">
         <v>391</v>
       </c>
@@ -4858,7 +4847,7 @@
       </c>
       <c r="F69" s="344"/>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:6">
       <c r="B70" s="249" t="s">
         <v>309</v>
       </c>
@@ -4874,7 +4863,7 @@
         <v>0.45076368583801485</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" ht="13.9">
       <c r="A72" s="244" t="s">
         <v>356</v>
       </c>
@@ -4884,10 +4873,10 @@
       <c r="E72" s="36"/>
       <c r="F72" s="36"/>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:6">
       <c r="A73" s="231"/>
     </row>
-    <row r="74" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:6" ht="24.5" customHeight="1">
       <c r="A74" s="17"/>
       <c r="B74" s="347" t="s">
         <v>363</v>
@@ -4897,7 +4886,7 @@
       <c r="E74" s="347"/>
       <c r="F74" s="347"/>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:6">
       <c r="B75" s="349" t="s">
         <v>253</v>
       </c>
@@ -4906,21 +4895,21 @@
       <c r="E75" s="349"/>
       <c r="F75" s="349"/>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:6">
       <c r="B77" s="232" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:6">
       <c r="B78" s="1" t="s">
         <v>432</v>
       </c>
       <c r="C78" s="92">
         <f>F31</f>
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6">
       <c r="B79" s="1" t="s">
         <v>431</v>
       </c>
@@ -4929,25 +4918,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:6">
       <c r="B80" s="80" t="s">
         <v>248</v>
       </c>
       <c r="C80" s="258">
         <f>F31+C79</f>
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
       <c r="C81" s="122"/>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:6">
       <c r="B82" s="321" t="s">
         <v>357</v>
       </c>
       <c r="C82" s="122"/>
     </row>
-    <row r="83" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:6" ht="24.5" customHeight="1">
       <c r="B83" s="347" t="s">
         <v>364</v>
       </c>
@@ -4956,7 +4945,7 @@
       <c r="E83" s="347"/>
       <c r="F83" s="347"/>
     </row>
-    <row r="84" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:6" ht="24.5" customHeight="1">
       <c r="B84" s="347" t="s">
         <v>365</v>
       </c>
@@ -4965,7 +4954,7 @@
       <c r="E84" s="347"/>
       <c r="F84" s="347"/>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
         <v>252</v>
       </c>
@@ -4973,20 +4962,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:6">
       <c r="B87" s="47" t="s">
         <v>281</v>
       </c>
       <c r="C87" s="245">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.5495317175460563</v>
+        <v>3.78616716538246</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="89" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" ht="13.9">
       <c r="A89" s="244" t="s">
         <v>358</v>
       </c>
@@ -4996,10 +4985,10 @@
       <c r="E89" s="36"/>
       <c r="F89" s="36"/>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:6">
       <c r="A90" s="231"/>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:6">
       <c r="B91" s="347" t="s">
         <v>366</v>
       </c>
@@ -5008,17 +4997,17 @@
       <c r="E91" s="347"/>
       <c r="F91" s="347"/>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:6">
       <c r="B94" s="232" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:6" ht="24.5" customHeight="1">
       <c r="B95" s="347" t="s">
         <v>345</v>
       </c>
@@ -5027,7 +5016,7 @@
       <c r="E95" s="347"/>
       <c r="F95" s="347"/>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
         <v>256</v>
       </c>
@@ -5040,7 +5029,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="97" spans="2:6">
       <c r="B97" s="47" t="s">
         <v>282</v>
       </c>
@@ -5053,7 +5042,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="98" spans="2:6">
       <c r="B98" s="325" t="s">
         <v>405</v>
       </c>
@@ -5062,7 +5051,7 @@
         <v>0.40000523965699897</v>
       </c>
     </row>
-    <row r="99" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="99" spans="2:6">
       <c r="B99" s="325" t="s">
         <v>406</v>
       </c>
@@ -5071,7 +5060,7 @@
         <v>0.10646655543311496</v>
       </c>
     </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="100" spans="2:6">
       <c r="B100" s="325" t="s">
         <v>408</v>
       </c>
@@ -5080,12 +5069,12 @@
         <v>0.9804830051022897</v>
       </c>
     </row>
-    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:6">
       <c r="B102" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:6">
       <c r="B103" s="47" t="s">
         <v>265</v>
       </c>
@@ -5098,7 +5087,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:6">
       <c r="B104" s="47" t="s">
         <v>267</v>
       </c>
@@ -5111,7 +5100,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="105" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="105" spans="2:6">
       <c r="B105" s="47" t="s">
         <v>283</v>
       </c>
@@ -5124,12 +5113,12 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="107" spans="2:6">
       <c r="B107" s="1" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
         <v>258</v>
       </c>
@@ -5142,7 +5131,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="109" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
         <v>284</v>
       </c>
@@ -5155,7 +5144,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="111" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="2:6" ht="24.5" customHeight="1">
       <c r="B111" s="347" t="s">
         <v>367</v>
       </c>
@@ -5164,20 +5153,20 @@
       <c r="E111" s="347"/>
       <c r="F111" s="347"/>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
         <v>450</v>
       </c>
       <c r="C113" s="245">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>4.3931077563825554</v>
+        <v>4.6297432042189586</v>
       </c>
       <c r="D113" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:6">
       <c r="B114" s="325" t="s">
         <v>407</v>
       </c>
@@ -5190,7 +5179,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" ht="13.9">
       <c r="A116" s="244" t="s">
         <v>359</v>
       </c>
@@ -5200,7 +5189,7 @@
       <c r="E116" s="36"/>
       <c r="F116" s="36"/>
     </row>
-    <row r="118" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:6" ht="24.5" customHeight="1">
       <c r="B118" s="348" t="s">
         <v>368</v>
       </c>
@@ -5209,7 +5198,7 @@
       <c r="E118" s="348"/>
       <c r="F118" s="348"/>
     </row>
-    <row r="120" spans="1:6" ht="14" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:6" ht="12.4">
       <c r="B120" s="255" t="s">
         <v>118</v>
       </c>
@@ -5226,7 +5215,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:6">
       <c r="B121" s="250" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
@@ -5241,14 +5230,14 @@
       </c>
       <c r="E121" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>7.02 HKD</v>
+        <v>7.4 HKD</v>
       </c>
       <c r="F121" s="254">
         <f>DCF!F74</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:6">
       <c r="B122" s="240" t="str">
         <f>DCF!B75</f>
         <v>Optimistic</v>
@@ -5263,14 +5252,14 @@
       </c>
       <c r="E122" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>5.15 HKD</v>
+        <v>5.42 HKD</v>
       </c>
       <c r="F122" s="243">
         <f>DCF!F75</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:6">
       <c r="B123" s="240" t="str">
         <f>DCF!B76</f>
         <v>Base</v>
@@ -5285,14 +5274,14 @@
       </c>
       <c r="E123" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>4.87 HKD</v>
+        <v>5.13 HKD</v>
       </c>
       <c r="F123" s="243">
         <f>DCF!F76</f>
         <v>0.53999999999999992</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:6">
       <c r="B124" s="240" t="str">
         <f>DCF!B77</f>
         <v>Pessimistic</v>
@@ -5307,14 +5296,14 @@
       </c>
       <c r="E124" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>4.62 HKD</v>
+        <v>4.87 HKD</v>
       </c>
       <c r="F124" s="243">
         <f>DCF!F77</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:6">
       <c r="B125" s="240" t="str">
         <f>DCF!B78</f>
         <v>Devil's advocate</v>
@@ -5329,27 +5318,27 @@
       </c>
       <c r="E125" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>4.39 HKD</v>
+        <v>4.63 HKD</v>
       </c>
       <c r="F125" s="243">
         <f>DCF!F78</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:6">
       <c r="B127" s="233" t="s">
         <v>259</v>
       </c>
       <c r="C127" s="239">
         <f>Scenarios!C60</f>
-        <v>4.9623808252376094</v>
+        <v>5.2246962590200807</v>
       </c>
       <c r="D127" s="234" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="129" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:6" ht="24.5" customHeight="1">
       <c r="B129" s="352" t="s">
         <v>371</v>
       </c>
@@ -5358,7 +5347,7 @@
       <c r="E129" s="352"/>
       <c r="F129" s="352"/>
     </row>
-    <row r="131" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="244" t="s">
         <v>403</v>
       </c>
@@ -5368,7 +5357,7 @@
       <c r="E131" s="36"/>
       <c r="F131" s="36"/>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:6">
       <c r="B133" s="350" t="s">
         <v>369</v>
       </c>
@@ -5377,7 +5366,7 @@
       <c r="E133" s="350"/>
       <c r="F133" s="350"/>
     </row>
-    <row r="134" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:6" ht="24.5" customHeight="1">
       <c r="B134" s="347" t="s">
         <v>370</v>
       </c>
@@ -5386,12 +5375,12 @@
       <c r="E134" s="347"/>
       <c r="F134" s="347"/>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:6">
       <c r="B135" s="232" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:6">
       <c r="B136" s="1" t="s">
         <v>264</v>
       </c>
@@ -5400,16 +5389,16 @@
         <v>3</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:6">
       <c r="B137" s="1" t="s">
         <v>277</v>
       </c>
       <c r="C137" s="246">
         <f>F29</f>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0.3674</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6">
       <c r="B138" s="234" t="s">
         <v>262</v>
       </c>
@@ -5422,7 +5411,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:6">
       <c r="B140" s="232" t="s">
         <v>410</v>
       </c>
@@ -5435,49 +5424,49 @@
         <v/>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
         <v>409</v>
       </c>
       <c r="C141" s="326">
         <f>F29</f>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0.3674</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
       <c r="B142" s="234" t="str">
         <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C142" s="238">
         <f>Scenarios!C81</f>
-        <v>0.20338192419825066</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0.21212919287870191</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
       <c r="B143" s="234" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C143" s="238">
         <f>Scenarios!C82</f>
-        <v>1.8084478226084586</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.15">
+        <v>2.0434984886306262</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6">
       <c r="B144" s="80" t="s">
         <v>261</v>
       </c>
       <c r="C144" s="237">
         <f>Scenarios!C83</f>
-        <v>2.0118297468067095</v>
+        <v>2.2556276815093281</v>
       </c>
       <c r="D144" s="330" t="str">
         <f>IF($D$11="","",C144*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="145" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="145" spans="2:4">
       <c r="B145" s="281" t="s">
         <v>417</v>
       </c>
@@ -5490,21 +5479,21 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="146" spans="2:4">
       <c r="B146" s="236" t="s">
         <v>263</v>
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F83</f>
-        <v>0.59458376580552363</v>
-      </c>
-    </row>
-    <row r="148" spans="2:4" x14ac:dyDescent="0.15">
+        <v>0.56827582510368113</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4">
       <c r="B148" s="232" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="149" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="149" spans="2:4">
       <c r="B149" s="1" t="s">
         <v>412</v>
       </c>
@@ -5513,7 +5502,7 @@
         <v>0.21740000000000001</v>
       </c>
     </row>
-    <row r="150" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="150" spans="2:4">
       <c r="B150" s="234" t="str">
         <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5523,30 +5512,30 @@
         <v>0.2624513054547119</v>
       </c>
     </row>
-    <row r="151" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="151" spans="2:4">
       <c r="B151" s="234" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C151" s="238">
         <f>Scenarios!C92</f>
-        <v>2.7503641454141192</v>
-      </c>
-    </row>
-    <row r="152" spans="2:4" x14ac:dyDescent="0.15">
+        <v>2.8957506018897798</v>
+      </c>
+    </row>
+    <row r="152" spans="2:4">
       <c r="B152" s="80" t="s">
         <v>261</v>
       </c>
       <c r="C152" s="237">
         <f>Scenarios!C93</f>
-        <v>3.012815450868831</v>
+        <v>3.1582019073444916</v>
       </c>
       <c r="D152" s="330" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="153" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="153" spans="2:4">
       <c r="B153" s="281" t="s">
         <v>417</v>
       </c>
@@ -5559,63 +5548,63 @@
         <v/>
       </c>
     </row>
-    <row r="154" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="154" spans="2:4">
       <c r="B154" s="236" t="s">
         <v>263</v>
       </c>
       <c r="C154" s="92">
         <f>Scenarios!F93</f>
-        <v>0.3928689560570815</v>
-      </c>
-    </row>
-    <row r="156" spans="2:4" x14ac:dyDescent="0.15">
+        <v>0.39552430404120198</v>
+      </c>
+    </row>
+    <row r="156" spans="2:4">
       <c r="B156" s="232" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="157" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="157" spans="2:4">
       <c r="B157" s="1" t="s">
         <v>411</v>
       </c>
       <c r="C157" s="92">
         <f>Scenarios!C96</f>
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="158" spans="2:4" x14ac:dyDescent="0.15">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="158" spans="2:4">
       <c r="B158" s="234" t="str">
         <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C158" s="238">
         <f>Scenarios!C97</f>
-        <v>0.32986841436772868</v>
-      </c>
-    </row>
-    <row r="159" spans="2:4" x14ac:dyDescent="0.15">
+        <v>0.33286729470361087</v>
+      </c>
+    </row>
+    <row r="159" spans="2:4">
       <c r="B159" s="234" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C159" s="238">
         <f>Scenarios!C98</f>
-        <v>3.9392978912938901</v>
-      </c>
-    </row>
-    <row r="160" spans="2:4" x14ac:dyDescent="0.15">
+        <v>4.2056744761754965</v>
+      </c>
+    </row>
+    <row r="160" spans="2:4">
       <c r="B160" s="80" t="s">
         <v>402</v>
       </c>
       <c r="C160" s="237">
         <f>Scenarios!C99</f>
-        <v>4.2691663056616189</v>
+        <v>4.5385417708791076</v>
       </c>
       <c r="D160" s="330" t="str">
         <f>IF($D$11="","",C160*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:6">
       <c r="B161" s="281" t="s">
         <v>417</v>
       </c>
@@ -5628,21 +5617,21 @@
         <v/>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:6">
       <c r="B162" s="236" t="s">
         <v>263</v>
       </c>
       <c r="C162" s="92">
         <f>Scenarios!F99</f>
-        <v>0.13969393804894004</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0.13132906759055596</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
       <c r="B164" s="232" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:6">
       <c r="B165" s="1" t="s">
         <v>424</v>
       </c>
@@ -5651,7 +5640,7 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="166" spans="1:6">
       <c r="B166" s="234" t="str">
         <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5661,30 +5650,30 @@
         <v>0.30881320012014707</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="167" spans="1:6">
       <c r="B167" s="234" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C167" s="238">
         <f>Scenarios!C104</f>
-        <v>3.5568380305864293</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.15">
+        <v>3.7448553439982017</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6">
       <c r="B168" s="80" t="s">
         <v>402</v>
       </c>
       <c r="C168" s="237">
         <f>Scenarios!C105</f>
-        <v>3.8656512307065762</v>
+        <v>4.0536685441183486</v>
       </c>
       <c r="D168" s="330" t="str">
         <f>IF($D$11="","",C168*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:6">
       <c r="B169" s="281" t="s">
         <v>417</v>
       </c>
@@ -5697,16 +5686,16 @@
         <v/>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:6">
       <c r="B170" s="236" t="s">
         <v>263</v>
       </c>
       <c r="C170" s="92">
         <f>Scenarios!F105</f>
-        <v>0.22106689885075603</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+        <v>0.22401578084943807</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" ht="13.9">
       <c r="A172" s="244" t="s">
         <v>375</v>
       </c>
@@ -5716,7 +5705,7 @@
       <c r="E172" s="36"/>
       <c r="F172" s="36"/>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="174" spans="1:6">
       <c r="B174" s="354" t="s">
         <v>377</v>
       </c>
@@ -5725,12 +5714,12 @@
       <c r="E174" s="347"/>
       <c r="F174" s="347"/>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="176" spans="1:6">
       <c r="B176" s="232" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="177" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="177" spans="2:6">
       <c r="B177" s="351" t="s">
         <v>381</v>
       </c>
@@ -5739,27 +5728,27 @@
       <c r="E177" s="351"/>
       <c r="F177" s="351"/>
     </row>
-    <row r="178" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="178" spans="2:6">
       <c r="B178" s="236" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="179" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="179" spans="2:6">
       <c r="B179" s="236" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="180" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="180" spans="2:6">
       <c r="B180" s="236" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="182" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="182" spans="2:6">
       <c r="B182" s="1" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="183" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="183" spans="2:6" ht="46.5" customHeight="1">
       <c r="B183" s="348" t="s">
         <v>382</v>
       </c>
@@ -5768,12 +5757,12 @@
       <c r="E183" s="348"/>
       <c r="F183" s="348"/>
     </row>
-    <row r="185" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="186" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="186" spans="2:6" ht="24.5" customHeight="1">
       <c r="B186" s="353" t="s">
         <v>383</v>
       </c>
@@ -5782,7 +5771,7 @@
       <c r="E186" s="353"/>
       <c r="F186" s="353"/>
     </row>
-    <row r="187" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="187" spans="2:6" ht="24.5" customHeight="1">
       <c r="B187" s="353" t="s">
         <v>384</v>
       </c>
@@ -5791,22 +5780,22 @@
       <c r="E187" s="353"/>
       <c r="F187" s="353"/>
     </row>
-    <row r="189" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="190" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="190" spans="2:6">
       <c r="B190" s="236" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="191" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="191" spans="2:6">
       <c r="B191" s="236" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="192" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="192" spans="2:6">
       <c r="B192" s="236" t="s">
         <v>389</v>
       </c>
@@ -5867,15 +5856,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
     <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.83203125" style="1"/>
+    <col min="14" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
         <v>HKD</v>
@@ -5924,7 +5913,7 @@
         <v>41729</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>98</v>
       </c>
@@ -5940,7 +5929,7 @@
       <c r="L2" s="37"/>
       <c r="M2" s="37"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
         <v>27</v>
       </c>
@@ -5948,7 +5937,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:13">
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
@@ -5982,7 +5971,7 @@
       <c r="L4" s="181"/>
       <c r="M4" s="181"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
@@ -6016,7 +6005,7 @@
       <c r="L5" s="181"/>
       <c r="M5" s="181"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
@@ -6050,7 +6039,7 @@
       <c r="L6" s="181"/>
       <c r="M6" s="181"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
@@ -6084,7 +6073,7 @@
       <c r="L7" s="188"/>
       <c r="M7" s="188"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
@@ -6100,7 +6089,7 @@
       <c r="L8" s="181"/>
       <c r="M8" s="181"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
         <v>160</v>
       </c>
@@ -6116,7 +6105,7 @@
       <c r="L9" s="181"/>
       <c r="M9" s="181"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
         <v>168</v>
       </c>
@@ -6132,7 +6121,7 @@
       <c r="L10" s="181"/>
       <c r="M10" s="181"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
         <v>159</v>
       </c>
@@ -6148,7 +6137,7 @@
       <c r="L11" s="181"/>
       <c r="M11" s="181"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
@@ -6182,7 +6171,7 @@
       <c r="L12" s="181"/>
       <c r="M12" s="181"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
@@ -6198,7 +6187,7 @@
       <c r="L13" s="181"/>
       <c r="M13" s="181"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
@@ -6232,7 +6221,7 @@
       <c r="L14" s="181"/>
       <c r="M14" s="181"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
@@ -6266,7 +6255,7 @@
       <c r="L15" s="182"/>
       <c r="M15" s="182"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
@@ -6300,13 +6289,13 @@
       <c r="L16" s="181"/>
       <c r="M16" s="181"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:13">
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
@@ -6322,7 +6311,7 @@
       <c r="L19" s="181"/>
       <c r="M19" s="181"/>
     </row>
-    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
@@ -6338,7 +6327,7 @@
       <c r="L20" s="181"/>
       <c r="M20" s="181"/>
     </row>
-    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
@@ -6354,7 +6343,7 @@
       <c r="L21" s="181"/>
       <c r="M21" s="181"/>
     </row>
-    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
         <v>372</v>
       </c>
@@ -6388,7 +6377,7 @@
       <c r="L22" s="181"/>
       <c r="M22" s="181"/>
     </row>
-    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
         <v>374</v>
       </c>
@@ -6422,7 +6411,7 @@
       <c r="L23" s="181"/>
       <c r="M23" s="181"/>
     </row>
-    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
         <v>373</v>
       </c>
@@ -6456,7 +6445,7 @@
       <c r="L24" s="181"/>
       <c r="M24" s="181"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:13">
       <c r="B25" s="24" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (HKD)</v>
@@ -6485,7 +6474,7 @@
       <c r="L25" s="39"/>
       <c r="M25" s="39"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
@@ -6493,7 +6482,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:13">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
@@ -6528,7 +6517,7 @@
       <c r="L28" s="181"/>
       <c r="M28" s="181"/>
     </row>
-    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
@@ -6563,7 +6552,7 @@
       <c r="L29" s="181"/>
       <c r="M29" s="181"/>
     </row>
-    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
@@ -6598,7 +6587,7 @@
       <c r="L30" s="182"/>
       <c r="M30" s="182"/>
     </row>
-    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
@@ -6633,7 +6622,7 @@
       <c r="L31" s="182"/>
       <c r="M31" s="182"/>
     </row>
-    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
         <v>173</v>
       </c>
@@ -6668,7 +6657,7 @@
       <c r="L32" s="182"/>
       <c r="M32" s="182"/>
     </row>
-    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
         <v>82</v>
       </c>
@@ -6684,12 +6673,12 @@
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:13">
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
@@ -6738,7 +6727,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:13">
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
@@ -6787,7 +6776,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:13">
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
@@ -6836,7 +6825,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:13">
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
@@ -6885,7 +6874,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:13">
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
@@ -6934,7 +6923,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:13">
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
@@ -6983,7 +6972,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:13">
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
@@ -7032,7 +7021,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
         <v>153</v>
       </c>
@@ -7081,7 +7070,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
         <v>169</v>
       </c>
@@ -7130,7 +7119,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:13">
       <c r="B45" s="40" t="s">
         <v>68</v>
       </c>
@@ -7179,7 +7168,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:13">
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
@@ -7228,7 +7217,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:13">
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
@@ -7277,7 +7266,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:13">
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
@@ -7326,12 +7315,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:13">
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
@@ -7380,7 +7369,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:13">
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
@@ -7429,12 +7418,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:13">
       <c r="B54" s="175" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
         <v>160</v>
       </c>
@@ -7483,7 +7472,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
         <v>168</v>
       </c>
@@ -7532,7 +7521,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
         <v>159</v>
       </c>
@@ -7581,7 +7570,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
         <v>161</v>
       </c>
@@ -7630,13 +7619,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:13">
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
@@ -7685,7 +7674,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:13">
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
@@ -7734,7 +7723,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:13">
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
@@ -7783,7 +7772,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
         <v>394</v>
       </c>
@@ -7832,7 +7821,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:13">
       <c r="B65" s="24" t="s">
         <v>36</v>
       </c>
@@ -7881,12 +7870,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:13">
       <c r="B67" s="91" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:13">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -7936,7 +7925,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:13">
       <c r="B69" s="31" t="s">
         <v>58</v>
       </c>
@@ -7985,7 +7974,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:13">
       <c r="B70" s="80" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -8035,7 +8024,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
         <v>169</v>
       </c>
@@ -8084,7 +8073,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:13">
       <c r="B72" s="80" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -8134,7 +8123,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="36" t="s">
         <v>83</v>
       </c>
@@ -8150,13 +8139,13 @@
       <c r="L74" s="37"/>
       <c r="M74" s="37"/>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
         <v>28</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:13">
       <c r="B76" s="26" t="s">
         <v>3</v>
       </c>
@@ -8205,7 +8194,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:13">
       <c r="B77" s="93" t="s">
         <v>86</v>
       </c>
@@ -8239,7 +8228,7 @@
       <c r="L77" s="324"/>
       <c r="M77" s="324"/>
     </row>
-    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
         <v>87</v>
       </c>
@@ -8273,7 +8262,7 @@
       <c r="L78" s="324"/>
       <c r="M78" s="324"/>
     </row>
-    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
@@ -8322,7 +8311,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:13">
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
@@ -8403,7 +8392,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
@@ -8414,7 +8403,7 @@
     <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="18" t="s">
         <v>37</v>
       </c>
@@ -8430,7 +8419,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
         <v>157</v>
       </c>
@@ -8441,7 +8430,7 @@
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
         <v>185</v>
       </c>
@@ -8461,7 +8450,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
@@ -8483,7 +8472,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
@@ -8504,7 +8493,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="15" customHeight="1">
       <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
@@ -8525,7 +8514,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
         <v>69</v>
       </c>
@@ -8546,7 +8535,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
         <v>174</v>
       </c>
@@ -8567,7 +8556,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
@@ -8588,7 +8577,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="15" customHeight="1">
       <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
@@ -8600,7 +8589,7 @@
       </c>
       <c r="H10" s="286"/>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
@@ -8612,7 +8601,7 @@
       </c>
       <c r="H11" s="286"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
         <v>72</v>
       </c>
@@ -8636,12 +8625,12 @@
         <v>986959.8</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="15" customHeight="1">
       <c r="F13" s="80"/>
       <c r="G13" s="81"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
         <v>184</v>
       </c>
@@ -8661,7 +8650,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
         <v>73</v>
       </c>
@@ -8681,7 +8670,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
@@ -8702,7 +8691,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
         <v>69</v>
       </c>
@@ -8722,7 +8711,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
         <v>174</v>
       </c>
@@ -8742,7 +8731,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
         <v>26</v>
       </c>
@@ -8764,7 +8753,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
         <v>18</v>
       </c>
@@ -8784,7 +8773,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
@@ -8804,7 +8793,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
         <v>20</v>
       </c>
@@ -8816,7 +8805,7 @@
       </c>
       <c r="H22" s="286"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
         <v>21</v>
       </c>
@@ -8828,7 +8817,7 @@
       </c>
       <c r="H23" s="286"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
         <v>74</v>
       </c>
@@ -8852,7 +8841,7 @@
         <v>41890.299999999996</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
         <v>201</v>
       </c>
@@ -8869,7 +8858,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8" ht="15" customHeight="1">
       <c r="B27" s="4" t="s">
         <v>5</v>
       </c>
@@ -8888,7 +8877,7 @@
         <v>815566.8</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8" ht="15" customHeight="1">
       <c r="B28" s="4" t="s">
         <v>6</v>
       </c>
@@ -8903,7 +8892,7 @@
       </c>
       <c r="H28" s="207"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8" ht="15" customHeight="1">
       <c r="B29" s="4" t="s">
         <v>7</v>
       </c>
@@ -8922,7 +8911,7 @@
         <v>813801.8</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8" ht="15" customHeight="1">
       <c r="B30" s="2" t="s">
         <v>8</v>
       </c>
@@ -8938,7 +8927,7 @@
       </c>
       <c r="H30" s="207"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
         <v>204</v>
       </c>
@@ -8955,7 +8944,7 @@
       </c>
       <c r="H31" s="207"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8" ht="15" customHeight="1">
       <c r="B32" s="4" t="s">
         <v>9</v>
       </c>
@@ -8975,7 +8964,7 @@
         <v>1548448.8</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8" ht="15" customHeight="1">
       <c r="B33" s="83" t="s">
         <v>4</v>
       </c>
@@ -8986,7 +8975,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="214"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8" ht="15" customHeight="1">
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="215" t="s">
@@ -8999,7 +8988,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
         <v>202</v>
       </c>
@@ -9018,7 +9007,7 @@
         <v>519598.69999999995</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8" ht="15" customHeight="1">
       <c r="B36" s="4" t="s">
         <v>13</v>
       </c>
@@ -9034,7 +9023,7 @@
       </c>
       <c r="H36" s="214"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8" ht="15" customHeight="1">
       <c r="B37" s="4" t="s">
         <v>14</v>
       </c>
@@ -9050,7 +9039,7 @@
       </c>
       <c r="H37" s="214"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8" ht="15" customHeight="1">
       <c r="B38" s="4" t="s">
         <v>15</v>
       </c>
@@ -9066,7 +9055,7 @@
       </c>
       <c r="H38" s="214"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8" ht="15" customHeight="1">
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
@@ -9085,7 +9074,7 @@
         <v>41963.600000000006</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="80" t="s">
         <v>205</v>
       </c>
@@ -9105,7 +9094,7 @@
         <v>1028850.1000000001</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8" ht="15" customHeight="1">
       <c r="B41" s="4" t="s">
         <v>17</v>
       </c>
@@ -9125,7 +9114,7 @@
         <v>1009942.2000000001</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="83" t="s">
         <v>22</v>
       </c>
@@ -9144,7 +9133,7 @@
         <v>18907.900000000001</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="79" t="s">
         <v>97</v>
       </c>
@@ -9155,7 +9144,7 @@
       <c r="G44" s="37"/>
       <c r="H44" s="37"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
         <v>272</v>
       </c>
@@ -9169,7 +9158,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
         <v>274</v>
       </c>
@@ -9183,7 +9172,7 @@
       </c>
       <c r="F46" s="275"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (HKD)</v>
@@ -9198,10 +9187,10 @@
       </c>
       <c r="F47" s="275"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8" ht="15" customHeight="1">
       <c r="F48" s="275"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="158" t="s">
         <v>144</v>
       </c>
@@ -9214,7 +9203,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="275"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
         <v>94</v>
       </c>
@@ -9228,7 +9217,7 @@
       </c>
       <c r="F50" s="275"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
         <v>177</v>
       </c>
@@ -9239,10 +9228,10 @@
       </c>
       <c r="F51" s="275"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:8" ht="15" customHeight="1">
       <c r="F52" s="275"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="158" t="s">
         <v>143</v>
       </c>
@@ -9254,7 +9243,7 @@
       </c>
       <c r="F53" s="275"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
         <v>140</v>
       </c>
@@ -9268,7 +9257,7 @@
       </c>
       <c r="F54" s="275"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
         <v>142</v>
       </c>
@@ -9282,10 +9271,10 @@
       </c>
       <c r="F55" s="275"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:8" ht="15" customHeight="1">
       <c r="F56" s="275"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="158" t="s">
         <v>176</v>
       </c>
@@ -9297,7 +9286,7 @@
       </c>
       <c r="F57" s="275"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
         <v>90</v>
       </c>
@@ -9308,7 +9297,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
         <v>93</v>
       </c>
@@ -9319,10 +9308,10 @@
       </c>
       <c r="F59" s="275"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:8" ht="15" customHeight="1">
       <c r="F60" s="275"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="158" t="s">
         <v>275</v>
       </c>
@@ -9334,7 +9323,7 @@
       </c>
       <c r="F61" s="275"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
         <v>246</v>
       </c>
@@ -9350,7 +9339,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="79" t="s">
         <v>194</v>
       </c>
@@ -9361,7 +9350,7 @@
       <c r="G64" s="37"/>
       <c r="H64" s="37"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
         <v>189</v>
       </c>
@@ -9375,7 +9364,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="105" t="s">
         <v>188</v>
       </c>
@@ -9391,7 +9380,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="105" t="s">
         <v>178</v>
       </c>
@@ -9401,7 +9390,7 @@
       </c>
       <c r="F67" s="275"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
         <v>182</v>
       </c>
@@ -9411,7 +9400,7 @@
       </c>
       <c r="F68" s="275"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
         <v>180</v>
       </c>
@@ -9421,7 +9410,7 @@
       </c>
       <c r="F69" s="275"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
         <v>189</v>
       </c>
@@ -9431,10 +9420,10 @@
       </c>
       <c r="F70" s="275"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6" ht="15" customHeight="1">
       <c r="F71" s="275"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="277" t="s">
         <v>319</v>
       </c>
@@ -9446,7 +9435,7 @@
       </c>
       <c r="F72" s="275"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
         <v>318</v>
       </c>
@@ -9462,7 +9451,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="279" t="s">
         <v>322</v>
       </c>
@@ -9478,7 +9467,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
         <v>321</v>
       </c>
@@ -9491,7 +9480,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="281" t="s">
         <v>323</v>
       </c>
@@ -9504,10 +9493,10 @@
         <v>324</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6" ht="15" customHeight="1">
       <c r="F77" s="275"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>190</v>
       </c>
@@ -9519,7 +9508,7 @@
       </c>
       <c r="F78" s="275"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
         <v>179</v>
       </c>
@@ -9533,7 +9522,7 @@
       </c>
       <c r="F79" s="275"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
         <v>183</v>
       </c>
@@ -9547,7 +9536,7 @@
       </c>
       <c r="F80" s="275"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
         <v>181</v>
       </c>
@@ -9561,7 +9550,7 @@
       </c>
       <c r="F81" s="275"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
         <v>190</v>
       </c>
@@ -9575,7 +9564,7 @@
       </c>
       <c r="F82" s="275"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
         <v>289</v>
       </c>
@@ -9586,7 +9575,7 @@
       <c r="G84" s="37"/>
       <c r="H84" s="37"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
         <v>290</v>
       </c>
@@ -9594,7 +9583,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="260" t="s">
         <v>287</v>
       </c>
@@ -9611,7 +9600,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="260" t="s">
         <v>288</v>
       </c>
@@ -9628,7 +9617,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="261" t="s">
         <v>190</v>
       </c>
@@ -9645,7 +9634,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
         <v>292</v>
       </c>
@@ -9676,19 +9665,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
     <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
     <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
     <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
@@ -9745,7 +9734,7 @@
         <v>41729</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
         <v>100</v>
@@ -9768,7 +9757,7 @@
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>66</v>
@@ -9782,7 +9771,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
         <v>2</v>
@@ -9839,7 +9828,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>46</v>
@@ -9894,7 +9883,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
         <v>48</v>
@@ -9949,7 +9938,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>45</v>
@@ -10004,7 +9993,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
         <v>153</v>
@@ -10061,7 +10050,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
         <v>65</v>
@@ -10116,7 +10105,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>81</v>
@@ -10171,7 +10160,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
         <v>195</v>
@@ -10228,7 +10217,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>68</v>
@@ -10283,7 +10272,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
         <v>165</v>
@@ -10338,7 +10327,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
         <v>63</v>
@@ -10393,7 +10382,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
         <v>244</v>
@@ -10450,7 +10439,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
         <v>155</v>
@@ -10507,7 +10496,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
         <v>52</v>
@@ -10533,7 +10522,7 @@
       <c r="P17" s="194"/>
       <c r="Q17" s="194"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>99</v>
@@ -10558,7 +10547,7 @@
       <c r="P18" s="195"/>
       <c r="Q18" s="195"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
@@ -10615,7 +10604,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1">
       <c r="A20" s="10"/>
       <c r="B20" s="27"/>
       <c r="C20" s="62"/>
@@ -10634,7 +10623,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
         <v>206</v>
@@ -10657,7 +10646,7 @@
       <c r="P21" s="37"/>
       <c r="Q21" s="37"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
         <v>46</v>
@@ -10678,7 +10667,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
         <v>43</v>
@@ -10735,7 +10724,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
         <v>62</v>
@@ -10792,7 +10781,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
         <v>46</v>
@@ -10849,18 +10838,18 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
       <c r="E26" s="293"/>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>207</v>
       </c>
       <c r="E27" s="293"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
         <v>43</v>
@@ -10919,7 +10908,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="68" t="str">
         <f>B24</f>
@@ -10979,7 +10968,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
         <v>46</v>
@@ -11034,18 +11023,18 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
       <c r="E31" s="293"/>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
       <c r="E32" s="293"/>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
         <v>175</v>
@@ -11102,7 +11091,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
         <v>49</v>
@@ -11161,7 +11150,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
         <v>45</v>
@@ -11218,18 +11207,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
       <c r="E36" s="293"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>208</v>
       </c>
       <c r="E37" s="293"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="2" t="str">
         <f>B33</f>
@@ -11287,7 +11276,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1">
       <c r="A39" s="10"/>
       <c r="B39" s="27" t="str">
         <f>B34</f>
@@ -11345,7 +11334,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
         <v>45</v>
@@ -11400,18 +11389,18 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
       <c r="E41" s="293"/>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>209</v>
       </c>
       <c r="E42" s="293"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>172</v>
@@ -11469,10 +11458,10 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1">
       <c r="A44" s="10"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
         <v>210</v>
@@ -11495,14 +11484,14 @@
       <c r="P45" s="37"/>
       <c r="Q45" s="37"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
       <c r="E46" s="293"/>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
         <v>39</v>
@@ -11557,7 +11546,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
         <v>346</v>
@@ -11612,7 +11601,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="313" t="s">
         <v>343</v>
@@ -11669,7 +11658,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
         <v>68</v>
@@ -11724,11 +11713,11 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
       <c r="E51" s="293"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>156</v>
@@ -11738,7 +11727,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
         <v>89</v>
@@ -11765,7 +11754,7 @@
       <c r="P53" s="170"/>
       <c r="Q53" s="170"/>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
         <v>88</v>
@@ -11792,7 +11781,7 @@
       <c r="P54" s="170"/>
       <c r="Q54" s="170"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
         <v>91</v>
@@ -11847,11 +11836,11 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
       <c r="E56" s="293"/>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>169</v>
@@ -11861,7 +11850,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
         <v>168</v>
@@ -11916,7 +11905,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
         <v>160</v>
@@ -11971,7 +11960,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
         <v>159</v>
@@ -12026,7 +12015,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
         <v>195</v>
@@ -12081,7 +12070,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
         <v>161</v>
@@ -12137,7 +12126,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
         <v>196</v>
@@ -12192,11 +12181,11 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
       <c r="E64" s="293"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>170</v>
@@ -12206,7 +12195,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
         <v>168</v>
@@ -12231,7 +12220,7 @@
       <c r="P66" s="176"/>
       <c r="Q66" s="176"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
         <v>158</v>
@@ -12256,7 +12245,7 @@
       <c r="P67" s="176"/>
       <c r="Q67" s="176"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
         <v>159</v>
@@ -12281,7 +12270,7 @@
       <c r="P68" s="176"/>
       <c r="Q68" s="176"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
         <v>195</v>
@@ -12308,10 +12297,10 @@
       <c r="P69" s="176"/>
       <c r="Q69" s="176"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1">
       <c r="A70" s="10"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
         <v>213</v>
@@ -12334,7 +12323,7 @@
       <c r="P71" s="37"/>
       <c r="Q71" s="37"/>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
         <v>217</v>
@@ -12355,7 +12344,7 @@
       <c r="P72" s="12"/>
       <c r="Q72" s="12"/>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
         <v>46</v>
@@ -12412,7 +12401,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
         <v>48</v>
@@ -12469,7 +12458,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
         <v>45</v>
@@ -12526,7 +12515,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
         <v>153</v>
@@ -12583,7 +12572,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
         <v>65</v>
@@ -12640,7 +12629,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>81</v>
@@ -12699,7 +12688,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
         <v>154</v>
@@ -12756,7 +12745,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
         <v>68</v>
@@ -12813,7 +12802,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
         <v>165</v>
@@ -12870,7 +12859,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>63</v>
@@ -12927,7 +12916,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1">
       <c r="A83" s="10"/>
       <c r="B83" s="40" t="str">
         <f>B15</f>
@@ -12985,7 +12974,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
         <v>155</v>
@@ -13042,7 +13031,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
         <v>52</v>
@@ -13068,7 +13057,7 @@
       <c r="P85" s="248"/>
       <c r="Q85" s="248"/>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
         <v>99</v>
@@ -13092,7 +13081,7 @@
       <c r="P86" s="170"/>
       <c r="Q86" s="170"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
         <v>141</v>
@@ -13149,18 +13138,18 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
       <c r="E88" s="293"/>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>215</v>
       </c>
       <c r="E89" s="293"/>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -13216,7 +13205,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -13272,7 +13261,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>214</v>
@@ -13327,7 +13316,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
         <v>310</v>
@@ -13382,11 +13371,11 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="E94" s="293"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
       <c r="B95" s="158" t="s">
         <v>85</v>
@@ -13407,7 +13396,7 @@
       <c r="P95" s="12"/>
       <c r="Q95" s="12"/>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
         <v>145</v>
@@ -13464,7 +13453,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
       <c r="B97" s="70" t="s">
         <v>165</v>
@@ -13521,10 +13510,10 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="10"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
         <v>216</v>
@@ -13547,7 +13536,7 @@
       <c r="P99" s="37"/>
       <c r="Q99" s="37"/>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1">
       <c r="A100" s="10"/>
       <c r="B100" s="64" t="s">
         <v>28</v>
@@ -13557,7 +13546,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="26" t="s">
         <v>3</v>
@@ -13614,7 +13603,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="93" t="s">
         <v>211</v>
@@ -13671,7 +13660,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
         <v>212</v>
@@ -13728,7 +13717,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
         <v>40</v>
@@ -13785,7 +13774,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
         <v>30</v>
@@ -13842,11 +13831,11 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="E106" s="293"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
       <c r="B107" s="91" t="s">
         <v>221</v>
@@ -13869,7 +13858,7 @@
       <c r="P107" s="12"/>
       <c r="Q107" s="12"/>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
         <v>218</v>
@@ -13926,7 +13915,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
         <v>219</v>
@@ -13983,7 +13972,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
         <v>69</v>
@@ -14010,18 +13999,18 @@
       <c r="P110" s="223"/>
       <c r="Q110" s="223"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="E111" s="293"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
       <c r="E112" s="293"/>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>392</v>
@@ -14073,7 +14062,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
         <v>393</v>
@@ -14125,11 +14114,11 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="E115" s="293"/>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
       <c r="B116" s="91" t="s">
         <v>38</v>
@@ -14183,7 +14172,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="A117" s="10"/>
       <c r="B117" s="7" t="s">
         <v>222</v>
@@ -14238,7 +14227,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="B118" s="7" t="s">
         <v>84</v>
       </c>
@@ -14292,7 +14281,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="B119" s="7" t="s">
         <v>92</v>
       </c>
@@ -14348,7 +14337,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1">
       <c r="A120" s="10"/>
       <c r="B120" s="70" t="s">
         <v>223</v>
@@ -14405,7 +14394,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="27"/>
       <c r="C121" s="62"/>
@@ -14424,7 +14413,7 @@
       <c r="P121" s="12"/>
       <c r="Q121" s="12"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
       <c r="B122" s="54" t="s">
         <v>224</v>
@@ -14447,7 +14436,7 @@
       <c r="P122" s="37"/>
       <c r="Q122" s="37"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
       <c r="B123" s="179" t="s">
         <v>171</v>
@@ -14468,7 +14457,7 @@
       <c r="P123" s="12"/>
       <c r="Q123" s="12"/>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -14526,7 +14515,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
         <v>270</v>
@@ -14583,7 +14572,7 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
         <v>395</v>
       </c>
@@ -14633,688 +14622,688 @@
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -15336,16 +15325,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H94"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="6" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>55</v>
       </c>
@@ -15357,7 +15346,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
         <v>164</v>
       </c>
@@ -15370,7 +15359,7 @@
       </c>
       <c r="H3" s="121"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
         <v>129</v>
       </c>
@@ -15391,24 +15380,24 @@
       </c>
       <c r="H4" s="121"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8">
       <c r="B5" s="225" t="s">
         <v>124</v>
       </c>
       <c r="C5" s="226">
         <f>Equity_Cost</f>
-        <v>0.08</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="E5" s="149"/>
       <c r="H5" s="121"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1">
       <c r="B6" s="150" t="s">
         <v>229</v>
       </c>
       <c r="C6" s="230">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>1729893.4738949155</v>
+        <v>1845219.70548791</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -15420,7 +15409,7 @@
       <c r="F6" s="355"/>
       <c r="H6" s="121"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8">
       <c r="B7" s="149" t="s">
         <v>225</v>
       </c>
@@ -15436,7 +15425,7 @@
       <c r="F7" s="355"/>
       <c r="H7" s="121"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8">
       <c r="B8" s="149" t="s">
         <v>226</v>
       </c>
@@ -15452,7 +15441,7 @@
       <c r="F8" s="355"/>
       <c r="H8" s="121"/>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8">
       <c r="B9" s="225" t="s">
         <v>191</v>
       </c>
@@ -15468,13 +15457,13 @@
       <c r="F9" s="355"/>
       <c r="H9" s="121"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="150" t="s">
         <v>228</v>
       </c>
       <c r="C10" s="230">
         <f>C6-C7+C8+C9</f>
-        <v>2141017.1939912266</v>
+        <v>2256343.4255842208</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15482,7 +15471,7 @@
       </c>
       <c r="H10" s="121"/>
     </row>
-    <row r="11" spans="2:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:8" ht="13.15" thickBot="1">
       <c r="B11" s="228" t="s">
         <v>167</v>
       </c>
@@ -15496,13 +15485,13 @@
       </c>
       <c r="H11" s="121"/>
     </row>
-    <row r="12" spans="2:8" ht="14" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="13.5" thickTop="1">
       <c r="B12" s="150" t="s">
         <v>103</v>
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>4.3931077563825554</v>
+        <v>4.6297432042189586</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15510,10 +15499,10 @@
       </c>
       <c r="H12" s="121"/>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8">
       <c r="H13" s="121"/>
     </row>
-    <row r="14" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:8" ht="13.9">
       <c r="B14" s="36" t="s">
         <v>230</v>
       </c>
@@ -15523,13 +15512,13 @@
       <c r="F14" s="37"/>
       <c r="H14" s="121"/>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="120" t="s">
         <v>136</v>
       </c>
       <c r="H15" s="121"/>
     </row>
-    <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="13.25" customHeight="1">
       <c r="B16" s="153" t="s">
         <v>134</v>
       </c>
@@ -15539,7 +15528,7 @@
       </c>
       <c r="H16" s="121"/>
     </row>
-    <row r="17" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8" ht="13.25" customHeight="1">
       <c r="B17" s="119" t="s">
         <v>135</v>
       </c>
@@ -15549,13 +15538,13 @@
       </c>
       <c r="H17" s="121"/>
     </row>
-    <row r="18" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8" ht="13.25" customHeight="1">
       <c r="B18" s="154" t="s">
         <v>107</v>
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>4.9627512619545433</v>
+        <v>5.2239059043697216</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15563,10 +15552,10 @@
       </c>
       <c r="H18" s="121"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8">
       <c r="H19" s="121"/>
     </row>
-    <row r="20" spans="2:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:8" ht="13.15">
       <c r="B20" s="129" t="s">
         <v>108</v>
       </c>
@@ -15584,7 +15573,7 @@
       </c>
       <c r="H20" s="121"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8">
       <c r="B21" s="123">
         <v>1</v>
       </c>
@@ -15598,15 +15587,15 @@
       </c>
       <c r="E21" s="125">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
-        <v>0.92592592592592582</v>
+        <v>0.93023255813953487</v>
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>134108.37326630831</v>
+        <v>134732.13314196558</v>
       </c>
       <c r="H21" s="121"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8">
       <c r="B22" s="123">
         <v>2</v>
       </c>
@@ -15620,15 +15609,15 @@
       </c>
       <c r="E22" s="125">
         <f t="shared" si="0"/>
-        <v>0.85733882030178321</v>
+        <v>0.86533261222282321</v>
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>129957.82725598633</v>
+        <v>131169.54869562571</v>
       </c>
       <c r="H22" s="121"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8">
       <c r="B23" s="123">
         <v>3</v>
       </c>
@@ -15642,15 +15631,15 @@
       </c>
       <c r="E23" s="125">
         <f t="shared" si="0"/>
-        <v>0.79383224102016958</v>
+        <v>0.80496056950960304</v>
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>125935.73729776772</v>
+        <v>127701.16603798557</v>
       </c>
       <c r="H23" s="121"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8">
       <c r="B24" s="123">
         <v>4</v>
       </c>
@@ -15664,15 +15653,15 @@
       </c>
       <c r="E24" s="125">
         <f t="shared" si="0"/>
-        <v>0.73502985279645328</v>
+        <v>0.7488005297763749</v>
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>122038.12778042427</v>
+        <v>124324.49428717894</v>
       </c>
       <c r="H24" s="121"/>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:8">
       <c r="B25" s="123">
         <v>5</v>
       </c>
@@ -15686,15 +15675,15 @@
       </c>
       <c r="E25" s="125">
         <f t="shared" si="0"/>
-        <v>0.68058319703375303</v>
+        <v>0.69655863235011617</v>
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>118261.14613468942</v>
+        <v>121037.10842518952</v>
       </c>
       <c r="H25" s="121"/>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8">
       <c r="B26" s="123">
         <v>6</v>
       </c>
@@ -15708,15 +15697,15 @@
       </c>
       <c r="E26" s="125">
         <f t="shared" si="0"/>
-        <v>0.63016962688310452</v>
+        <v>0.64796151846522443</v>
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>114601.05902520868</v>
+        <v>117836.64755628027</v>
       </c>
       <c r="H26" s="121"/>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8">
       <c r="B27" s="123">
         <v>7</v>
       </c>
@@ -15730,15 +15719,15 @@
       </c>
       <c r="E27" s="125">
         <f t="shared" si="0"/>
-        <v>0.58349039526213387</v>
+        <v>0.60275490089788319</v>
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>111054.24866034648</v>
+        <v>114720.81321147336</v>
       </c>
       <c r="H27" s="121"/>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8">
       <c r="B28" s="123">
         <v>8</v>
       </c>
@@ -15752,15 +15741,15 @@
       </c>
       <c r="E28" s="125">
         <f t="shared" si="0"/>
-        <v>0.54026888450197574</v>
+        <v>0.56070223339337966</v>
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>107617.20921620082</v>
+        <v>111687.36769786292</v>
       </c>
       <c r="H28" s="121"/>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8">
       <c r="B29" s="123">
         <v>9</v>
       </c>
@@ -15774,15 +15763,15 @@
       </c>
       <c r="E29" s="125">
         <f t="shared" si="0"/>
-        <v>0.50024896713145905</v>
+        <v>0.52158347292407414</v>
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>104286.54337129265</v>
+        <v>108734.13249157557</v>
       </c>
       <c r="H29" s="121"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8">
       <c r="B30" s="123">
         <v>10</v>
       </c>
@@ -15796,15 +15785,15 @@
       </c>
       <c r="E30" s="125">
         <f t="shared" si="0"/>
-        <v>0.46319348808468425</v>
+        <v>0.48519392830146441</v>
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>101058.95894850302</v>
+        <v>105858.98667322374</v>
       </c>
       <c r="H30" s="121"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8">
       <c r="B31" s="123">
         <v>11</v>
       </c>
@@ -15826,7 +15815,7 @@
       </c>
       <c r="H31" s="121"/>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8">
       <c r="B32" s="123">
         <v>12</v>
       </c>
@@ -15848,7 +15837,7 @@
       </c>
       <c r="H32" s="121"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8">
       <c r="B33" s="123">
         <v>13</v>
       </c>
@@ -15870,7 +15859,7 @@
       </c>
       <c r="H33" s="121"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8">
       <c r="B34" s="123">
         <v>14</v>
       </c>
@@ -15892,7 +15881,7 @@
       </c>
       <c r="H34" s="121"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8">
       <c r="B35" s="123">
         <v>15</v>
       </c>
@@ -15914,7 +15903,7 @@
       </c>
       <c r="H35" s="121"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8">
       <c r="B36" s="123">
         <v>16</v>
       </c>
@@ -15936,7 +15925,7 @@
       </c>
       <c r="H36" s="121"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8">
       <c r="B37" s="123">
         <v>17</v>
       </c>
@@ -15958,7 +15947,7 @@
       </c>
       <c r="H37" s="121"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8">
       <c r="B38" s="123">
         <v>18</v>
       </c>
@@ -15980,7 +15969,7 @@
       </c>
       <c r="H38" s="121"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8">
       <c r="B39" s="123">
         <v>19</v>
       </c>
@@ -16002,7 +15991,7 @@
       </c>
       <c r="H39" s="121"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8">
       <c r="B40" s="123">
         <v>20</v>
       </c>
@@ -16024,7 +16013,7 @@
       </c>
       <c r="H40" s="121"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8">
       <c r="B41" s="123">
         <v>21</v>
       </c>
@@ -16046,7 +16035,7 @@
       </c>
       <c r="H41" s="121"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8">
       <c r="B42" s="123">
         <v>22</v>
       </c>
@@ -16068,7 +16057,7 @@
       </c>
       <c r="H42" s="121"/>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:8">
       <c r="B43" s="123">
         <v>23</v>
       </c>
@@ -16090,7 +16079,7 @@
       </c>
       <c r="H43" s="121"/>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8">
       <c r="B44" s="123">
         <v>24</v>
       </c>
@@ -16112,7 +16101,7 @@
       </c>
       <c r="H44" s="121"/>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8">
       <c r="B45" s="123">
         <v>25</v>
       </c>
@@ -16134,7 +16123,7 @@
       </c>
       <c r="H45" s="121"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8">
       <c r="B46" s="123">
         <v>26</v>
       </c>
@@ -16156,7 +16145,7 @@
       </c>
       <c r="H46" s="121"/>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8">
       <c r="B47" s="123">
         <v>27</v>
       </c>
@@ -16178,7 +16167,7 @@
       </c>
       <c r="H47" s="121"/>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8">
       <c r="B48" s="123">
         <v>28</v>
       </c>
@@ -16200,7 +16189,7 @@
       </c>
       <c r="H48" s="121"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:8">
       <c r="B49" s="123">
         <v>29</v>
       </c>
@@ -16222,7 +16211,7 @@
       </c>
       <c r="H49" s="121"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:8">
       <c r="B50" s="123">
         <v>30</v>
       </c>
@@ -16244,13 +16233,13 @@
       </c>
       <c r="H50" s="121"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:8">
       <c r="B51" s="127" t="s">
         <v>132</v>
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>1810463.0390951624</v>
+        <v>1931160.57503484</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -16258,30 +16247,30 @@
       </c>
       <c r="E51" s="125">
         <f>1/(1+Equity_Cost)^C17</f>
-        <v>0.46319348808468425</v>
+        <v>0.48519392830146441</v>
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>838594.69012688636</v>
+        <v>936987.38558206894</v>
       </c>
       <c r="H51" s="121"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:8">
       <c r="C52" s="115"/>
       <c r="E52" s="128" t="s">
         <v>101</v>
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>2007513.9210836142</v>
+        <v>2134789.7838004301</v>
       </c>
       <c r="H52" s="121"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:8">
       <c r="C53" s="115"/>
       <c r="H53" s="121"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:8" ht="13.15">
       <c r="B54" s="120" t="s">
         <v>130</v>
       </c>
@@ -16291,10 +16280,10 @@
       <c r="F54" s="118"/>
       <c r="H54" s="121"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>2007513.9210836142</v>
+        <v>2134789.7838004301</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -16318,141 +16307,141 @@
       </c>
       <c r="H55" s="121"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:8" ht="13.15">
       <c r="A56" s="144">
         <v>5</v>
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>1729893.4738949153</v>
+        <v>1845219.7054879102</v>
       </c>
       <c r="C56" s="124">
-        <v>1785708.8928911716</v>
+        <v>1903732.5510763344</v>
       </c>
       <c r="D56" s="124">
-        <v>1843195.959329494</v>
+        <v>1963949.9900522388</v>
       </c>
       <c r="E56" s="124">
-        <v>1902428.0304998513</v>
+        <v>2025946.9564576221</v>
       </c>
       <c r="F56" s="124">
-        <v>2026432.0090457182</v>
+        <v>2155590.8587459349</v>
       </c>
       <c r="H56" s="121"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:8" ht="13.15">
       <c r="A57" s="144">
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>1729893.4738949151</v>
+        <v>1845219.7054879104</v>
       </c>
       <c r="C57" s="124">
-        <v>1841575.7090680972</v>
+        <v>1961755.5456893134</v>
       </c>
       <c r="D57" s="124">
-        <v>1964451.5281177529</v>
+        <v>2089897.2573272167</v>
       </c>
       <c r="E57" s="124">
-        <v>2099860.5577511135</v>
+        <v>2231038.337726613</v>
       </c>
       <c r="F57" s="124">
-        <v>2414400.4768588506</v>
+        <v>2558688.7194257439</v>
       </c>
       <c r="H57" s="121"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:8" ht="13.15">
       <c r="A58" s="144">
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>1729893.4738949146</v>
+        <v>1845219.7054879102</v>
       </c>
       <c r="C58" s="124">
-        <v>1910726.3845036193</v>
+        <v>2035219.4517333307</v>
       </c>
       <c r="D58" s="124">
-        <v>2122523.5390752279</v>
+        <v>2257845.7291086544</v>
       </c>
       <c r="E58" s="124">
-        <v>2371436.6161577431</v>
+        <v>2519612.9100684039</v>
       </c>
       <c r="F58" s="124">
-        <v>3011527.175947086</v>
+        <v>3193331.3278640071</v>
       </c>
       <c r="H58" s="121"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:8" ht="13.15">
       <c r="A59" s="145">
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>1729893.4738949148</v>
+        <v>1845219.7054879109</v>
       </c>
       <c r="C59" s="124">
-        <v>1981179.833248463</v>
+        <v>2111806.7723140484</v>
       </c>
       <c r="D59" s="124">
-        <v>2292660.563024424</v>
+        <v>2442814.7330809613</v>
       </c>
       <c r="E59" s="124">
-        <v>2681231.080611133</v>
+        <v>2856451.9377206154</v>
       </c>
       <c r="F59" s="124">
-        <v>3783007.973053663</v>
+        <v>4032363.9187480891</v>
       </c>
       <c r="H59" s="121"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:8" ht="13.15">
       <c r="A60" s="145">
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>1729893.4738949146</v>
+        <v>1845219.7054879111</v>
       </c>
       <c r="C60" s="124">
-        <v>2046705.4500437151</v>
+        <v>2184700.2252792544</v>
       </c>
       <c r="D60" s="124">
-        <v>2460251.3195536938</v>
+        <v>2629270.087203749</v>
       </c>
       <c r="E60" s="124">
-        <v>3005886.2600892317</v>
+        <v>3217694.2785887066</v>
       </c>
       <c r="F60" s="124">
-        <v>4708230.947662564</v>
+        <v>5062122.4857187551</v>
       </c>
       <c r="H60" s="121"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:8" ht="13.15">
       <c r="A61" s="145">
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>1729893.4738949146</v>
+        <v>1845219.7054879111</v>
       </c>
       <c r="C61" s="124">
-        <v>2104508.1592063867</v>
+        <v>2250506.6958236932</v>
       </c>
       <c r="D61" s="124">
-        <v>2617201.548270294</v>
+        <v>2807972.9740084624</v>
       </c>
       <c r="E61" s="124">
-        <v>3330500.1822488499</v>
+        <v>3587344.5103175333</v>
       </c>
       <c r="F61" s="124">
-        <v>5776538.6434068419</v>
+        <v>6278979.7610744182</v>
       </c>
       <c r="H61" s="121"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:8">
       <c r="C62" s="115"/>
       <c r="D62" s="115"/>
       <c r="E62" s="115"/>
       <c r="F62" s="115"/>
       <c r="H62" s="121"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:8" ht="13.15">
       <c r="B63" s="120" t="s">
         <v>131</v>
       </c>
@@ -16462,7 +16451,7 @@
       <c r="F63" s="115"/>
       <c r="H63" s="121"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:8" ht="13.15">
       <c r="B64" s="133">
         <f>B55</f>
         <v>0</v>
@@ -16485,193 +16474,193 @@
       </c>
       <c r="H64" s="121"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:8" ht="13.15">
       <c r="A65" s="144">
         <v>0</v>
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>4.3931077563825554</v>
+        <v>4.6297432042189586</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>4.3931077563825554</v>
+        <v>4.6297432042189586</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>4.3931077563825554</v>
+        <v>4.6297432042189586</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>4.3931077563825554</v>
+        <v>4.6297432042189586</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>4.3931077563825554</v>
+        <v>4.6297432042189586</v>
       </c>
       <c r="H65" s="121"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:8" ht="13.15">
       <c r="A66" s="144">
         <f t="shared" ref="A66:A71" si="3">A56</f>
         <v>5</v>
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>4.3931077563825554</v>
+        <v>4.6297432042189586</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>4.5076342304372039</v>
+        <v>4.7498044706692903</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>4.6255907224124426</v>
+        <v>4.8733633561266227</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>4.7471277525752029</v>
+        <v>5.0005736161619252</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>5.0015688852765301</v>
+        <v>5.2665871887333653</v>
       </c>
       <c r="H66" s="121"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:8" ht="13.15">
       <c r="A67" s="144">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>4.3931077563825545</v>
+        <v>4.6297432042189595</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>4.6222661652764234</v>
+        <v>4.8688606222958182</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>4.874392451442584</v>
+        <v>5.1317918817422639</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>5.1522353664999905</v>
+        <v>5.4213962701549159</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>5.7976331532165988</v>
+        <v>6.0936951369103287</v>
       </c>
       <c r="H67" s="121"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:8" ht="13.15">
       <c r="A68" s="144">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>4.3931077563825536</v>
+        <v>4.6297432042189586</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>4.7641549690970848</v>
+        <v>5.0195996524922535</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>5.1987370570595708</v>
+        <v>5.4764017877842672</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>5.7094765189682208</v>
+        <v>6.0135163127250619</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>7.0228647583946318</v>
+        <v>7.3959048405435714</v>
       </c>
       <c r="H68" s="121"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:8" ht="13.15">
       <c r="A69" s="145">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>4.3931077563825536</v>
+        <v>4.6297432042189595</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>4.9087169058314153</v>
+        <v>5.1767475507099672</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>5.5478376068621236</v>
+        <v>5.855935762719934</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>6.3451372079594659</v>
+        <v>6.7046691671646572</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>8.6058498381879662</v>
+        <v>9.1174980128054646</v>
       </c>
       <c r="H69" s="121"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:8" ht="13.15">
       <c r="A70" s="145">
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>4.3931077563825536</v>
+        <v>4.6297432042189604</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>5.0431675287376008</v>
+        <v>5.3263160803367615</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>5.8917135245675158</v>
+        <v>6.2385195479948647</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>7.0112902828239596</v>
+        <v>7.4458946622495441</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>10.504295230193707</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
+        <v>11.230437768943993</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="13.15">
       <c r="A71" s="145">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>4.3931077563825536</v>
+        <v>4.6297432042189604</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>5.1617716813222341</v>
+        <v>5.4613429810922911</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>6.2137563690042601</v>
+        <v>6.605196210056719</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>7.6773587026719818</v>
+        <v>8.2043721302091832</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>12.696333125801839</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" ht="14" x14ac:dyDescent="0.2">
+        <v>13.727281395318631</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="13.15">
       <c r="B73" s="172" t="s">
         <v>118</v>
       </c>
@@ -16688,7 +16677,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:8">
       <c r="B74" s="128" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -16703,14 +16692,14 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>7.0228647583946318</v>
+        <v>7.3959048405435714</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:8">
       <c r="B75" s="128" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -16725,7 +16714,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>5.1522353664999905</v>
+        <v>5.4213962701549159</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16733,7 +16722,7 @@
       </c>
       <c r="H75" s="121"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:8">
       <c r="B76" s="128" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -16748,7 +16737,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>4.874392451442584</v>
+        <v>5.1317918817422639</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16756,7 +16745,7 @@
       </c>
       <c r="H76" s="121"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:8">
       <c r="B77" s="128" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -16771,7 +16760,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>4.6222661652764234</v>
+        <v>4.8688606222958182</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16779,7 +16768,7 @@
       </c>
       <c r="H77" s="121"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:8">
       <c r="B78" s="128" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -16794,21 +16783,21 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>4.3931077563825536</v>
+        <v>4.6297432042189586</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:8">
       <c r="B79" s="156"/>
       <c r="C79" s="156"/>
       <c r="D79" s="156"/>
       <c r="E79" s="156"/>
       <c r="F79" s="157"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:8">
       <c r="B80" s="156" t="s">
         <v>311</v>
       </c>
@@ -16816,23 +16805,23 @@
         <v>106</v>
       </c>
     </row>
-    <row r="81" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="81" spans="3:3">
       <c r="C81" s="156" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="82" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="82" spans="3:3">
       <c r="C82" s="156" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="92" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="92" spans="3:3">
       <c r="C92" s="116"/>
     </row>
-    <row r="93" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="93" spans="3:3">
       <c r="C93" s="116"/>
     </row>
-    <row r="94" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="94" spans="3:3">
       <c r="C94" s="116"/>
     </row>
   </sheetData>
@@ -16866,16 +16855,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="6" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>444</v>
       </c>
@@ -16887,7 +16876,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
         <v>443</v>
       </c>
@@ -16900,7 +16889,7 @@
       </c>
       <c r="H3" s="121"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
         <v>441</v>
       </c>
@@ -16921,24 +16910,24 @@
       </c>
       <c r="H4" s="121"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8">
       <c r="B5" s="225" t="s">
         <v>124</v>
       </c>
       <c r="C5" s="226">
         <f>Equity_Cost</f>
-        <v>0.08</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="E5" s="149"/>
       <c r="H5" s="121"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1">
       <c r="B6" s="150" t="s">
         <v>442</v>
       </c>
       <c r="C6" s="230">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>779773.15839999996</v>
+        <v>831758.03562666674</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -16948,13 +16937,13 @@
       <c r="F6" s="355"/>
       <c r="H6" s="121"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="13.15">
       <c r="B7" s="150" t="s">
         <v>445</v>
       </c>
       <c r="C7" s="112">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>1.5999999999999999</v>
+        <v>1.706666666666667</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -16962,10 +16951,10 @@
       </c>
       <c r="H7" s="121"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8">
       <c r="H8" s="121"/>
     </row>
-    <row r="9" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" ht="13.9">
       <c r="B9" s="36" t="s">
         <v>230</v>
       </c>
@@ -16975,13 +16964,13 @@
       <c r="F9" s="37"/>
       <c r="H9" s="121"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="120" t="s">
         <v>136</v>
       </c>
       <c r="H10" s="121"/>
     </row>
-    <row r="11" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="13.25" customHeight="1">
       <c r="B11" s="153" t="s">
         <v>134</v>
       </c>
@@ -16991,7 +16980,7 @@
       </c>
       <c r="H11" s="121"/>
     </row>
-    <row r="12" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="13.25" customHeight="1">
       <c r="B12" s="119" t="s">
         <v>135</v>
       </c>
@@ -17001,13 +16990,13 @@
       </c>
       <c r="H12" s="121"/>
     </row>
-    <row r="13" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="13.25" customHeight="1">
       <c r="B13" s="154" t="s">
         <v>107</v>
       </c>
       <c r="C13" s="141">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>1.8567746061853174</v>
+        <v>1.9744936353740918</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -17015,10 +17004,10 @@
       </c>
       <c r="H13" s="121"/>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8">
       <c r="H14" s="121"/>
     </row>
-    <row r="15" spans="2:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="129" t="s">
         <v>108</v>
       </c>
@@ -17036,7 +17025,7 @@
       </c>
       <c r="H15" s="121"/>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8">
       <c r="B16" s="123">
         <v>1</v>
       </c>
@@ -17050,15 +17039,15 @@
       </c>
       <c r="E16" s="125">
         <f t="shared" ref="E16:E45" si="0">IF($C$12&lt;B16,0,1/(1+Equity_Cost)^B16)</f>
-        <v>0.92592592592592582</v>
+        <v>0.93023255813953487</v>
       </c>
       <c r="F16" s="126">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>60451.184635261445</v>
+        <v>60732.352935890573</v>
       </c>
       <c r="H16" s="121"/>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8">
       <c r="B17" s="123">
         <v>2</v>
       </c>
@@ -17072,15 +17061,15 @@
       </c>
       <c r="E17" s="125">
         <f t="shared" si="0"/>
-        <v>0.85733882030178321</v>
+        <v>0.86533261222282321</v>
       </c>
       <c r="F17" s="126">
         <f t="shared" si="1"/>
-        <v>58580.26921740843</v>
+        <v>59126.469239749225</v>
       </c>
       <c r="H17" s="121"/>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8">
       <c r="B18" s="123">
         <v>3</v>
       </c>
@@ -17094,15 +17083,15 @@
       </c>
       <c r="E18" s="125">
         <f t="shared" si="0"/>
-        <v>0.79383224102016958</v>
+        <v>0.80496056950960304</v>
       </c>
       <c r="F18" s="126">
         <f t="shared" si="1"/>
-        <v>56767.257123069743</v>
+        <v>57563.04828909471</v>
       </c>
       <c r="H18" s="121"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8">
       <c r="B19" s="123">
         <v>4</v>
       </c>
@@ -17116,15 +17105,15 @@
       </c>
       <c r="E19" s="125">
         <f t="shared" si="0"/>
-        <v>0.73502985279645328</v>
+        <v>0.7488005297763749</v>
       </c>
       <c r="F19" s="126">
         <f t="shared" si="1"/>
-        <v>55010.356291074691</v>
+        <v>56040.967284836006</v>
       </c>
       <c r="H19" s="121"/>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8">
       <c r="B20" s="123">
         <v>5</v>
       </c>
@@ -17138,15 +17127,15 @@
       </c>
       <c r="E20" s="125">
         <f t="shared" si="0"/>
-        <v>0.68058319703375303</v>
+        <v>0.69655863235011617</v>
       </c>
       <c r="F20" s="126">
         <f t="shared" si="1"/>
-        <v>53307.830123100714</v>
+        <v>54559.133116913879</v>
       </c>
       <c r="H20" s="121"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8">
       <c r="B21" s="123">
         <v>6</v>
       </c>
@@ -17160,15 +17149,15 @@
       </c>
       <c r="E21" s="125">
         <f t="shared" si="0"/>
-        <v>0.63016962688310452</v>
+        <v>0.64796151846522443</v>
       </c>
       <c r="F21" s="126">
         <f t="shared" si="1"/>
-        <v>51657.995767142966</v>
+        <v>53116.481579264007</v>
       </c>
       <c r="H21" s="121"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8">
       <c r="B22" s="123">
         <v>7</v>
       </c>
@@ -17182,15 +17171,15 @@
       </c>
       <c r="E22" s="125">
         <f t="shared" si="0"/>
-        <v>0.58349039526213387</v>
+        <v>0.60275490089788319</v>
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>50059.222454109207</v>
+        <v>51711.97660553817</v>
       </c>
       <c r="H22" s="121"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8">
       <c r="B23" s="123">
         <v>8</v>
       </c>
@@ -17204,15 +17193,15 @@
       </c>
       <c r="E23" s="125">
         <f t="shared" si="0"/>
-        <v>0.54026888450197574</v>
+        <v>0.56070223339337966</v>
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>48509.929885895472</v>
+        <v>50344.609525034335</v>
       </c>
       <c r="H23" s="121"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8">
       <c r="B24" s="123">
         <v>9</v>
       </c>
@@ -17226,15 +17215,15 @@
       </c>
       <c r="E24" s="125">
         <f t="shared" si="0"/>
-        <v>0.50024896713145905</v>
+        <v>0.52158347292407414</v>
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>47008.586673349877</v>
+        <v>49013.39833830166</v>
       </c>
       <c r="H24" s="121"/>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:8">
       <c r="B25" s="123">
         <v>10</v>
       </c>
@@ -17248,15 +17237,15 @@
       </c>
       <c r="E25" s="125">
         <f t="shared" si="0"/>
-        <v>0.46319348808468425</v>
+        <v>0.48519392830146441</v>
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>45553.708822579865</v>
+        <v>47717.387011899635</v>
       </c>
       <c r="H25" s="121"/>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8">
       <c r="B26" s="123">
         <v>11</v>
       </c>
@@ -17278,7 +17267,7 @@
       </c>
       <c r="H26" s="121"/>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8">
       <c r="B27" s="123">
         <v>12</v>
       </c>
@@ -17300,7 +17289,7 @@
       </c>
       <c r="H27" s="121"/>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8">
       <c r="B28" s="123">
         <v>13</v>
       </c>
@@ -17322,7 +17311,7 @@
       </c>
       <c r="H28" s="121"/>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8">
       <c r="B29" s="123">
         <v>14</v>
       </c>
@@ -17344,7 +17333,7 @@
       </c>
       <c r="H29" s="121"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8">
       <c r="B30" s="123">
         <v>15</v>
       </c>
@@ -17366,7 +17355,7 @@
       </c>
       <c r="H30" s="121"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8">
       <c r="B31" s="123">
         <v>16</v>
       </c>
@@ -17388,7 +17377,7 @@
       </c>
       <c r="H31" s="121"/>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8">
       <c r="B32" s="123">
         <v>17</v>
       </c>
@@ -17410,7 +17399,7 @@
       </c>
       <c r="H32" s="121"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8">
       <c r="B33" s="123">
         <v>18</v>
       </c>
@@ -17432,7 +17421,7 @@
       </c>
       <c r="H33" s="121"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8">
       <c r="B34" s="123">
         <v>19</v>
       </c>
@@ -17454,7 +17443,7 @@
       </c>
       <c r="H34" s="121"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8">
       <c r="B35" s="123">
         <v>20</v>
       </c>
@@ -17476,7 +17465,7 @@
       </c>
       <c r="H35" s="121"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8">
       <c r="B36" s="123">
         <v>21</v>
       </c>
@@ -17498,7 +17487,7 @@
       </c>
       <c r="H36" s="121"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8">
       <c r="B37" s="123">
         <v>22</v>
       </c>
@@ -17520,7 +17509,7 @@
       </c>
       <c r="H37" s="121"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8">
       <c r="B38" s="123">
         <v>23</v>
       </c>
@@ -17542,7 +17531,7 @@
       </c>
       <c r="H38" s="121"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8">
       <c r="B39" s="123">
         <v>24</v>
       </c>
@@ -17564,7 +17553,7 @@
       </c>
       <c r="H39" s="121"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8">
       <c r="B40" s="123">
         <v>25</v>
       </c>
@@ -17586,7 +17575,7 @@
       </c>
       <c r="H40" s="121"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8">
       <c r="B41" s="123">
         <v>26</v>
       </c>
@@ -17608,7 +17597,7 @@
       </c>
       <c r="H41" s="121"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8">
       <c r="B42" s="123">
         <v>27</v>
       </c>
@@ -17630,7 +17619,7 @@
       </c>
       <c r="H42" s="121"/>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:8">
       <c r="B43" s="123">
         <v>28</v>
       </c>
@@ -17652,7 +17641,7 @@
       </c>
       <c r="H43" s="121"/>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8">
       <c r="B44" s="123">
         <v>29</v>
       </c>
@@ -17674,7 +17663,7 @@
       </c>
       <c r="H44" s="121"/>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8">
       <c r="B45" s="123">
         <v>30</v>
       </c>
@@ -17696,13 +17685,13 @@
       </c>
       <c r="H45" s="121"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8">
       <c r="B46" s="127" t="s">
         <v>132</v>
       </c>
       <c r="C46" s="124">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>816090.9925760295</v>
+        <v>870497.05874776491</v>
       </c>
       <c r="D46" s="140">
         <f>Terminal_Growth</f>
@@ -17710,30 +17699,30 @@
       </c>
       <c r="E46" s="125">
         <f>1/(1+Equity_Cost)^C12</f>
-        <v>0.46319348808468425</v>
+        <v>0.48519392830146441</v>
       </c>
       <c r="F46" s="126">
         <f t="shared" si="1"/>
-        <v>378008.03344578325</v>
+        <v>422359.88750869868</v>
       </c>
       <c r="H46" s="121"/>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8">
       <c r="C47" s="115"/>
       <c r="E47" s="128" t="s">
         <v>101</v>
       </c>
       <c r="F47" s="138">
         <f>SUM(F16:F46)</f>
-        <v>904914.3744387757</v>
+        <v>962285.7114352209</v>
       </c>
       <c r="H47" s="121"/>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8">
       <c r="C48" s="115"/>
       <c r="H48" s="121"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:8" ht="13.15">
       <c r="B49" s="120" t="s">
         <v>130</v>
       </c>
@@ -17743,10 +17732,10 @@
       <c r="F49" s="118"/>
       <c r="H49" s="121"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="134">
         <f>F47</f>
-        <v>904914.3744387757</v>
+        <v>962285.7114352209</v>
       </c>
       <c r="B50" s="132">
         <f>C73</f>
@@ -17770,141 +17759,141 @@
       </c>
       <c r="H50" s="121"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:8" ht="13.15">
       <c r="A51" s="144">
         <v>5</v>
       </c>
       <c r="B51" s="124">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
-        <v>779773.15839999984</v>
+        <v>831758.03562666674</v>
       </c>
       <c r="C51" s="124">
-        <v>804932.72239334544</v>
+        <v>858133.50157297554</v>
       </c>
       <c r="D51" s="124">
-        <v>830845.8043490987</v>
+        <v>885277.33631747996</v>
       </c>
       <c r="E51" s="124">
-        <v>857545.47106966842</v>
+        <v>913223.31740514631</v>
       </c>
       <c r="F51" s="124">
-        <v>913441.96149758133</v>
+        <v>971662.08064704936</v>
       </c>
       <c r="H51" s="121"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:8" ht="13.15">
       <c r="A52" s="144">
         <v>10</v>
       </c>
       <c r="B52" s="124">
-        <v>779773.15839999961</v>
+        <v>831758.03562666685</v>
       </c>
       <c r="C52" s="124">
-        <v>830115.45436929131</v>
+        <v>884288.16048808116</v>
       </c>
       <c r="D52" s="124">
-        <v>885503.41146447905</v>
+        <v>942049.79073557456</v>
       </c>
       <c r="E52" s="124">
-        <v>946540.88475776184</v>
+        <v>1005671.0643595662</v>
       </c>
       <c r="F52" s="124">
-        <v>1088324.0580379562</v>
+        <v>1153363.9580804987</v>
       </c>
       <c r="H52" s="121"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:8" ht="13.15">
       <c r="A53" s="144">
         <v>15</v>
       </c>
       <c r="B53" s="124">
-        <v>779773.15839999961</v>
+        <v>831758.03562666685</v>
       </c>
       <c r="C53" s="124">
-        <v>861286.06770679553</v>
+        <v>917403.0215525399</v>
       </c>
       <c r="D53" s="124">
-        <v>956756.53375149774</v>
+        <v>1017754.8629066374</v>
       </c>
       <c r="E53" s="124">
-        <v>1068957.5098304939</v>
+        <v>1135750.0022274808</v>
       </c>
       <c r="F53" s="124">
-        <v>1357487.0898312563</v>
+        <v>1439437.7994499826</v>
       </c>
       <c r="H53" s="121"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:8" ht="13.15">
       <c r="A54" s="145">
         <v>20</v>
       </c>
       <c r="B54" s="124">
-        <v>779773.15839999937</v>
+        <v>831758.03562666685</v>
       </c>
       <c r="C54" s="124">
-        <v>893043.92394302087</v>
+        <v>951925.80446596188</v>
       </c>
       <c r="D54" s="124">
-        <v>1033448.1257643478</v>
+        <v>1101132.1729029811</v>
       </c>
       <c r="E54" s="124">
-        <v>1208601.604479718</v>
+        <v>1287584.8038660842</v>
       </c>
       <c r="F54" s="124">
-        <v>1705242.6174882664</v>
+        <v>1817643.2226551105</v>
       </c>
       <c r="H54" s="121"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="145">
         <v>25</v>
       </c>
       <c r="B55" s="124">
-        <v>779773.15839999926</v>
+        <v>831758.03562666697</v>
       </c>
       <c r="C55" s="124">
-        <v>922580.49248645816</v>
+        <v>984783.52599801798</v>
       </c>
       <c r="D55" s="124">
-        <v>1108991.9528898629</v>
+        <v>1185179.4755716014</v>
       </c>
       <c r="E55" s="124">
-        <v>1354944.3698076683</v>
+        <v>1450419.7329165381</v>
       </c>
       <c r="F55" s="124">
-        <v>2122299.5357449865</v>
+        <v>2281820.9898260799</v>
       </c>
       <c r="H55" s="121"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:8" ht="13.15">
       <c r="A56" s="145">
         <v>30</v>
       </c>
       <c r="B56" s="124">
-        <v>779773.15839999926</v>
+        <v>831758.03562666709</v>
       </c>
       <c r="C56" s="124">
-        <v>948635.85472004674</v>
+        <v>1014446.6932126199</v>
       </c>
       <c r="D56" s="124">
-        <v>1179739.4164792774</v>
+        <v>1265732.2474975877</v>
       </c>
       <c r="E56" s="124">
-        <v>1501268.5378346723</v>
+        <v>1617044.6338415002</v>
       </c>
       <c r="F56" s="124">
-        <v>2603853.8502877932</v>
+        <v>2830336.0604042024</v>
       </c>
       <c r="H56" s="121"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:8">
       <c r="C57" s="115"/>
       <c r="D57" s="115"/>
       <c r="E57" s="115"/>
       <c r="F57" s="115"/>
       <c r="H57" s="121"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:8" ht="13.15">
       <c r="B58" s="120" t="s">
         <v>131</v>
       </c>
@@ -17914,7 +17903,7 @@
       <c r="F58" s="115"/>
       <c r="H58" s="121"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:8" ht="13.15">
       <c r="B59" s="133">
         <f>B50</f>
         <v>0</v>
@@ -17937,193 +17926,193 @@
       </c>
       <c r="H59" s="121"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:8" ht="13.15">
       <c r="A60" s="144">
         <v>0</v>
       </c>
       <c r="B60" s="125">
         <f>C7</f>
-        <v>1.5999999999999999</v>
+        <v>1.706666666666667</v>
       </c>
       <c r="C60" s="125">
         <f>C7</f>
-        <v>1.5999999999999999</v>
+        <v>1.706666666666667</v>
       </c>
       <c r="D60" s="125">
         <f>C7</f>
-        <v>1.5999999999999999</v>
+        <v>1.706666666666667</v>
       </c>
       <c r="E60" s="142">
         <f>C7</f>
-        <v>1.5999999999999999</v>
+        <v>1.706666666666667</v>
       </c>
       <c r="F60" s="125">
         <f>C7</f>
-        <v>1.5999999999999999</v>
+        <v>1.706666666666667</v>
       </c>
       <c r="H60" s="121"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:8" ht="13.15">
       <c r="A61" s="144">
         <f t="shared" ref="A61:A66" si="3">A51</f>
         <v>5</v>
       </c>
       <c r="B61" s="125">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>1.5999999999999996</v>
+        <v>1.7066666666666668</v>
       </c>
       <c r="C61" s="125">
         <f t="shared" si="4"/>
-        <v>1.6516243755709052</v>
+        <v>1.7607859256581984</v>
       </c>
       <c r="D61" s="125">
         <f t="shared" si="4"/>
-        <v>1.7047948786621865</v>
+        <v>1.8164817842849821</v>
       </c>
       <c r="E61" s="125">
         <f t="shared" si="4"/>
-        <v>1.7595793583441579</v>
+        <v>1.8738235499749079</v>
       </c>
       <c r="F61" s="125">
         <f t="shared" si="4"/>
-        <v>1.874272181149407</v>
+        <v>1.9937328084301487</v>
       </c>
       <c r="H61" s="121"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:8" ht="13.15">
       <c r="A62" s="144">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="B62" s="125">
         <f t="shared" si="4"/>
-        <v>1.5999999999999992</v>
+        <v>1.706666666666667</v>
       </c>
       <c r="C62" s="125">
         <f t="shared" si="4"/>
-        <v>1.7032962890337753</v>
+        <v>1.814452115387061</v>
       </c>
       <c r="D62" s="125">
         <f t="shared" si="4"/>
-        <v>1.8169456630826835</v>
+        <v>1.9329719790171729</v>
       </c>
       <c r="E62" s="125">
         <f t="shared" si="4"/>
-        <v>1.942187159557939</v>
+        <v>2.0635151205729243</v>
       </c>
       <c r="F62" s="125">
         <f t="shared" si="4"/>
-        <v>2.2331090447300141</v>
+        <v>2.3665630357363145</v>
       </c>
       <c r="H62" s="121"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:8" ht="13.15">
       <c r="A63" s="144">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="B63" s="125">
         <f t="shared" si="4"/>
-        <v>1.5999999999999992</v>
+        <v>1.706666666666667</v>
       </c>
       <c r="C63" s="125">
         <f t="shared" si="4"/>
-        <v>1.7672546092231236</v>
+        <v>1.8823997962380541</v>
       </c>
       <c r="D63" s="125">
         <f t="shared" si="4"/>
-        <v>1.9631484329922742</v>
+        <v>2.0883096104409584</v>
       </c>
       <c r="E63" s="125">
         <f t="shared" si="4"/>
-        <v>2.1933712353451411</v>
+        <v>2.3304213334204054</v>
       </c>
       <c r="F63" s="125">
         <f t="shared" si="4"/>
-        <v>2.7853989590852914</v>
+        <v>2.9535518814800641</v>
       </c>
       <c r="H63" s="121"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:8" ht="13.15">
       <c r="A64" s="145">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="B64" s="125">
         <f t="shared" si="4"/>
-        <v>1.5999999999999988</v>
+        <v>1.706666666666667</v>
       </c>
       <c r="C64" s="125">
         <f t="shared" si="4"/>
-        <v>1.8324178806573721</v>
+        <v>1.9532363620603679</v>
       </c>
       <c r="D64" s="125">
         <f t="shared" si="4"/>
-        <v>2.1205102835493506</v>
+        <v>2.2593897438837125</v>
       </c>
       <c r="E64" s="125">
         <f t="shared" si="4"/>
-        <v>2.4799039904571676</v>
+        <v>2.6419679415650617</v>
       </c>
       <c r="F64" s="125">
         <f t="shared" si="4"/>
-        <v>3.4989511482795179</v>
+        <v>3.729583565322395</v>
       </c>
       <c r="H64" s="121"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:8" ht="13.15">
       <c r="A65" s="145">
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
       <c r="B65" s="125">
         <f t="shared" si="4"/>
-        <v>1.5999999999999985</v>
+        <v>1.7066666666666672</v>
       </c>
       <c r="C65" s="125">
         <f t="shared" si="4"/>
-        <v>1.8930233390017814</v>
+        <v>2.0206564237603137</v>
       </c>
       <c r="D65" s="125">
         <f t="shared" si="4"/>
-        <v>2.2755170596851628</v>
+        <v>2.4318446210761007</v>
       </c>
       <c r="E65" s="125">
         <f t="shared" si="4"/>
-        <v>2.7801816058154141</v>
+        <v>2.9760854777666337</v>
       </c>
       <c r="F65" s="125">
         <f t="shared" si="4"/>
-        <v>4.3547013905422194</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
+        <v>4.6820200777530729</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="13.15">
       <c r="A66" s="145">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="B66" s="125">
         <f t="shared" si="4"/>
-        <v>1.5999999999999985</v>
+        <v>1.7066666666666674</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>1.9464857839765248</v>
+        <v>2.0815216472321598</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>2.420682279241229</v>
+        <v>2.5971291447778824</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>3.080421061766411</v>
+        <v>3.3179795768492051</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>5.3427924718631461</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" ht="14" x14ac:dyDescent="0.2">
+        <v>5.8075065137388604</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="13.15">
       <c r="B68" s="172" t="s">
         <v>118</v>
       </c>
@@ -18140,7 +18129,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:8">
       <c r="B69" s="128" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -18155,14 +18144,14 @@
       </c>
       <c r="E69" s="136">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>2.7853989590852914</v>
+        <v>2.9535518814800641</v>
       </c>
       <c r="F69" s="143">
         <f>Scenarios!C58</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:8">
       <c r="B70" s="128" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -18177,7 +18166,7 @@
       </c>
       <c r="E70" s="136">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>1.942187159557939</v>
+        <v>2.0635151205729243</v>
       </c>
       <c r="F70" s="143">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18185,7 +18174,7 @@
       </c>
       <c r="H70" s="121"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:8">
       <c r="B71" s="128" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -18200,7 +18189,7 @@
       </c>
       <c r="E71" s="136">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>1.8169456630826835</v>
+        <v>1.9329719790171729</v>
       </c>
       <c r="F71" s="143">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18208,7 +18197,7 @@
       </c>
       <c r="H71" s="121"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:8">
       <c r="B72" s="128" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -18223,7 +18212,7 @@
       </c>
       <c r="E72" s="136">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>1.7032962890337753</v>
+        <v>1.814452115387061</v>
       </c>
       <c r="F72" s="143">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -18231,7 +18220,7 @@
       </c>
       <c r="H72" s="121"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:8">
       <c r="B73" s="128" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -18246,21 +18235,21 @@
       </c>
       <c r="E73" s="136">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>1.5999999999999992</v>
+        <v>1.706666666666667</v>
       </c>
       <c r="F73" s="143">
         <f>Scenarios!C52</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:8">
       <c r="B74" s="156"/>
       <c r="C74" s="156"/>
       <c r="D74" s="156"/>
       <c r="E74" s="156"/>
       <c r="F74" s="157"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:8">
       <c r="B75" s="156" t="s">
         <v>311</v>
       </c>
@@ -18268,23 +18257,23 @@
         <v>106</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:8">
       <c r="C76" s="156" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:8">
       <c r="C77" s="156" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="87" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="87" spans="3:3">
       <c r="C87" s="116"/>
     </row>
-    <row r="88" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="88" spans="3:3">
       <c r="C88" s="116"/>
     </row>
-    <row r="89" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="89" spans="3:3">
       <c r="C89" s="116"/>
     </row>
   </sheetData>
@@ -18314,7 +18303,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
@@ -18324,7 +18313,7 @@
     <col min="8" max="9" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:9" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>146</v>
       </c>
@@ -18337,7 +18326,7 @@
       </c>
       <c r="I2" s="271"/>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="160" t="s">
         <v>149</v>
       </c>
@@ -18349,7 +18338,7 @@
         <v>-3.57</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:9">
       <c r="B4" s="153" t="s">
         <v>147</v>
       </c>
@@ -18369,7 +18358,7 @@
         <v>0.128</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:9">
       <c r="H5" s="269">
         <v>2</v>
       </c>
@@ -18378,7 +18367,7 @@
         <v>0.128</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:9" ht="13.15">
       <c r="B6" s="160" t="s">
         <v>96</v>
       </c>
@@ -18395,10 +18384,10 @@
       </c>
       <c r="I6" s="125">
         <f t="shared" si="0"/>
-        <v>5.0903808252376095</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>5.3526962590200808</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" ht="12.75" customHeight="1">
       <c r="B7" s="100" t="s">
         <v>276</v>
       </c>
@@ -18423,7 +18412,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:9">
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
@@ -18445,7 +18434,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:9">
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
@@ -18467,7 +18456,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:9">
       <c r="E10" s="357"/>
       <c r="F10" s="357"/>
       <c r="H10" s="269">
@@ -18478,7 +18467,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="160" t="s">
         <v>448</v>
       </c>
@@ -18492,7 +18481,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="14" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:9">
       <c r="B12" s="119" t="s">
         <v>145</v>
       </c>
@@ -18511,7 +18500,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:9">
       <c r="B13" s="149" t="s">
         <v>153</v>
       </c>
@@ -18529,7 +18518,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:9">
       <c r="B14" s="100" t="s">
         <v>66</v>
       </c>
@@ -18540,7 +18529,7 @@
       <c r="E14" s="357"/>
       <c r="F14" s="357"/>
     </row>
-    <row r="16" spans="2:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
         <v>163</v>
       </c>
@@ -18549,7 +18538,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="37"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:6" ht="13.15">
       <c r="B17" s="109" t="s">
         <v>152</v>
       </c>
@@ -18557,7 +18546,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:6">
       <c r="B18" s="153" t="s">
         <v>134</v>
       </c>
@@ -18569,18 +18558,18 @@
       </c>
       <c r="F18" s="358"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:6">
       <c r="E19" s="358"/>
       <c r="F19" s="358"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
         <v>304</v>
       </c>
       <c r="E20" s="358"/>
       <c r="F20" s="358"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
         <v>278</v>
       </c>
@@ -18595,13 +18584,13 @@
       <c r="E21" s="358"/>
       <c r="F21" s="358"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
         <v>279</v>
       </c>
       <c r="C22" s="161">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>4.3931077563825554</v>
+        <v>4.6297432042189586</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -18610,7 +18599,7 @@
       <c r="E22" s="358"/>
       <c r="F22" s="358"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
         <v>116</v>
       </c>
@@ -18619,7 +18608,7 @@
       </c>
       <c r="F24" s="160"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:6">
       <c r="B25" s="153" t="s">
         <v>134</v>
       </c>
@@ -18631,7 +18620,7 @@
       <c r="E25" s="356"/>
       <c r="F25" s="356"/>
     </row>
-    <row r="26" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
         <v>135</v>
       </c>
@@ -18642,13 +18631,13 @@
       <c r="E26" s="356"/>
       <c r="F26" s="356"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C27" s="161">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>4.874392451442584</v>
+        <v>5.1317918817422639</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -18657,7 +18646,7 @@
       <c r="E27" s="356"/>
       <c r="F27" s="356"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
         <v>148</v>
       </c>
@@ -18668,7 +18657,7 @@
       <c r="E28" s="356"/>
       <c r="F28" s="356"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
         <v>117</v>
       </c>
@@ -18677,7 +18666,7 @@
       </c>
       <c r="F30" s="160"/>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:6">
       <c r="B31" s="153" t="s">
         <v>134</v>
       </c>
@@ -18689,7 +18678,7 @@
       <c r="E31" s="356"/>
       <c r="F31" s="356"/>
     </row>
-    <row r="32" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
         <v>135</v>
       </c>
@@ -18700,13 +18689,13 @@
       <c r="E32" s="356"/>
       <c r="F32" s="356"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C33" s="161">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>4.6222661652764234</v>
+        <v>4.8688606222958182</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -18715,7 +18704,7 @@
       <c r="E33" s="356"/>
       <c r="F33" s="356"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
         <v>148</v>
       </c>
@@ -18726,7 +18715,7 @@
       <c r="E34" s="356"/>
       <c r="F34" s="356"/>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
         <v>115</v>
       </c>
@@ -18735,7 +18724,7 @@
       </c>
       <c r="F36" s="160"/>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:6">
       <c r="B37" s="153" t="s">
         <v>134</v>
       </c>
@@ -18747,7 +18736,7 @@
       <c r="E37" s="356"/>
       <c r="F37" s="356"/>
     </row>
-    <row r="38" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
         <v>135</v>
       </c>
@@ -18758,13 +18747,13 @@
       <c r="E38" s="356"/>
       <c r="F38" s="356"/>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C39" s="161">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>5.1522353664999905</v>
+        <v>5.4213962701549159</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -18773,7 +18762,7 @@
       <c r="E39" s="356"/>
       <c r="F39" s="356"/>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
         <v>148</v>
       </c>
@@ -18785,20 +18774,20 @@
       <c r="E40" s="356"/>
       <c r="F40" s="356"/>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
         <v>121</v>
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>4.8795357772208332</v>
+        <v>5.1371265075355055</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:6" ht="13.9">
       <c r="B44" s="36" t="s">
         <v>162</v>
       </c>
@@ -18807,12 +18796,12 @@
       <c r="E44" s="37"/>
       <c r="F44" s="37"/>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:6" ht="13.15">
       <c r="B45" s="109" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:6">
       <c r="B46" s="153" t="s">
         <v>134</v>
       </c>
@@ -18822,12 +18811,12 @@
       <c r="E46" s="100"/>
       <c r="F46" s="100"/>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:6" ht="13.15">
       <c r="B47" s="160"/>
       <c r="E47" s="160"/>
       <c r="F47" s="160"/>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:6" ht="13.15">
       <c r="B48" s="160" t="s">
         <v>166</v>
       </c>
@@ -18836,7 +18825,7 @@
       </c>
       <c r="F48" s="160"/>
     </row>
-    <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:6" ht="12.75" customHeight="1">
       <c r="B49" s="153" t="s">
         <v>134</v>
       </c>
@@ -18848,7 +18837,7 @@
       <c r="E49" s="356"/>
       <c r="F49" s="356"/>
     </row>
-    <row r="50" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
         <v>135</v>
       </c>
@@ -18859,13 +18848,13 @@
       <c r="E50" s="356"/>
       <c r="F50" s="356"/>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C51" s="161">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>4.3931077563825536</v>
+        <v>4.6297432042189586</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -18874,7 +18863,7 @@
       <c r="E51" s="356"/>
       <c r="F51" s="356"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
         <v>148</v>
       </c>
@@ -18885,7 +18874,7 @@
       <c r="E52" s="356"/>
       <c r="F52" s="356"/>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
         <v>317</v>
       </c>
@@ -18894,7 +18883,7 @@
       </c>
       <c r="F54" s="160"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="153" t="s">
         <v>134</v>
       </c>
@@ -18906,7 +18895,7 @@
       <c r="E55" s="356"/>
       <c r="F55" s="356"/>
     </row>
-    <row r="56" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
         <v>135</v>
       </c>
@@ -18917,13 +18906,13 @@
       <c r="E56" s="356"/>
       <c r="F56" s="356"/>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C57" s="161">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>7.0228647583946318</v>
+        <v>7.3959048405435714</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -18932,7 +18921,7 @@
       <c r="E57" s="356"/>
       <c r="F57" s="356"/>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
         <v>148</v>
       </c>
@@ -18943,13 +18932,13 @@
       <c r="E58" s="356"/>
       <c r="F58" s="356"/>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
         <v>121</v>
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>4.9623808252376094</v>
+        <v>5.2246962590200807</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -18963,7 +18952,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
         <v>350</v>
       </c>
@@ -18972,7 +18961,7 @@
       <c r="E62" s="37"/>
       <c r="F62" s="37"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
         <v>305</v>
       </c>
@@ -18980,7 +18969,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:6">
       <c r="B64" s="153" t="s">
         <v>134</v>
       </c>
@@ -18993,7 +18982,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="65" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6">
       <c r="B65" s="119" t="s">
         <v>135</v>
       </c>
@@ -19005,13 +18994,13 @@
         <v>313</v>
       </c>
     </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6">
       <c r="B66" s="100" t="s">
         <v>103</v>
       </c>
       <c r="C66" s="161">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>4.9627512619545433</v>
+        <v>5.2239059043697216</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -19021,7 +19010,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
         <v>351</v>
       </c>
@@ -19029,7 +19018,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
         <v>306</v>
       </c>
@@ -19039,7 +19028,7 @@
       </c>
       <c r="E69" s="135"/>
     </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
         <v>294</v>
       </c>
@@ -19051,7 +19040,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
         <v>293</v>
       </c>
@@ -19061,7 +19050,7 @@
       </c>
       <c r="E71" s="273"/>
     </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
         <v>285</v>
       </c>
@@ -19074,10 +19063,10 @@
       </c>
       <c r="F72" s="319">
         <f>BS!D89/C60</f>
-        <v>0.16999421619281041</v>
-      </c>
-    </row>
-    <row r="74" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+        <v>0.16145934558016128</v>
+      </c>
+    </row>
+    <row r="74" spans="2:6" ht="13.9">
       <c r="B74" s="36" t="s">
         <v>128</v>
       </c>
@@ -19086,12 +19075,12 @@
       <c r="E74" s="37"/>
       <c r="F74" s="37"/>
     </row>
-    <row r="75" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="13.15">
       <c r="B75" s="109" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6">
       <c r="B76" s="268" t="s">
         <v>298</v>
       </c>
@@ -19101,7 +19090,7 @@
       </c>
       <c r="D76" s="135"/>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6">
       <c r="B77" s="100" t="s">
         <v>112</v>
       </c>
@@ -19114,49 +19103,49 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6">
       <c r="B80" s="149" t="s">
         <v>300</v>
       </c>
       <c r="C80" s="168">
         <f>Thesis!F29</f>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.3674</v>
+      </c>
+    </row>
+    <row r="81" spans="2:8">
       <c r="B81" s="100" t="s">
         <v>122</v>
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.20338192419825066</v>
+        <v>0.21212919287870191</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
       <c r="F81" s="100"/>
     </row>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8">
       <c r="B82" s="100" t="s">
         <v>123</v>
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>1.8084478226084586</v>
+        <v>2.0434984886306262</v>
       </c>
       <c r="D82" s="117"/>
     </row>
-    <row r="83" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="83" spans="2:8" ht="13.15">
       <c r="B83" s="111" t="s">
         <v>102</v>
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>2.0118297468067095</v>
+        <v>2.2556276815093281</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19167,18 +19156,18 @@
       </c>
       <c r="F83" s="319">
         <f>(1-C83/C60)</f>
-        <v>0.59458376580552363</v>
-      </c>
-    </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.56827582510368113</v>
+      </c>
+    </row>
+    <row r="84" spans="2:8">
       <c r="E84" s="121"/>
     </row>
-    <row r="85" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8">
       <c r="B86" s="149" t="s">
         <v>301</v>
       </c>
@@ -19191,24 +19180,24 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
         <v>299</v>
       </c>
       <c r="C87" s="259">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.14834835832623461</v>
-      </c>
-    </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.1671769416467408</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8">
       <c r="B88" s="100"/>
     </row>
-    <row r="89" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
         <v>415</v>
       </c>
@@ -19217,7 +19206,7 @@
         <v>0.21740000000000001</v>
       </c>
     </row>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="91" spans="2:8">
       <c r="B91" s="100" t="s">
         <v>122</v>
       </c>
@@ -19229,23 +19218,23 @@
       <c r="E91" s="100"/>
       <c r="F91" s="100"/>
     </row>
-    <row r="92" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
         <v>123</v>
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>2.7503641454141192</v>
+        <v>2.8957506018897798</v>
       </c>
       <c r="D92" s="117"/>
     </row>
-    <row r="93" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="93" spans="2:8" ht="13.15">
       <c r="B93" s="111" t="s">
         <v>102</v>
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>3.012815450868831</v>
+        <v>3.1582019073444916</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19256,58 +19245,58 @@
       </c>
       <c r="F93" s="319">
         <f>(1-C93/C60)</f>
-        <v>0.3928689560570815</v>
-      </c>
-    </row>
-    <row r="95" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.39552430404120198</v>
+      </c>
+    </row>
+    <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
         <v>398</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="306"/>
     </row>
-    <row r="96" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
         <v>404</v>
       </c>
       <c r="C96" s="135">
         <f>Thesis!F31</f>
-        <v>0.08</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="306"/>
     </row>
-    <row r="97" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
         <v>122</v>
       </c>
       <c r="C97" s="117">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>0.32986841436772868</v>
+        <v>0.33286729470361087</v>
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
       <c r="H97" s="306"/>
     </row>
-    <row r="98" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
         <v>123</v>
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>3.9392978912938901</v>
+        <v>4.2056744761754965</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
       <c r="H98" s="306"/>
     </row>
-    <row r="99" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="111" t="s">
         <v>399</v>
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>4.2691663056616189</v>
+        <v>4.5385417708791076</v>
       </c>
       <c r="D99" t="s">
         <v>397</v>
@@ -19317,18 +19306,18 @@
       </c>
       <c r="F99" s="319">
         <f>(1-C99/C60)</f>
-        <v>0.13969393804894004</v>
-      </c>
-    </row>
-    <row r="100" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.13132906759055596</v>
+      </c>
+    </row>
+    <row r="100" spans="2:8">
       <c r="B100" s="100"/>
     </row>
-    <row r="101" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="102" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:8">
       <c r="B102" s="149" t="s">
         <v>422</v>
       </c>
@@ -19337,7 +19326,7 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="103" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:8">
       <c r="B103" s="100" t="s">
         <v>122</v>
       </c>
@@ -19347,23 +19336,23 @@
       </c>
       <c r="D103" s="117"/>
     </row>
-    <row r="104" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:8">
       <c r="B104" s="100" t="s">
         <v>123</v>
       </c>
       <c r="C104" s="117">
         <f>C60/(1+C102)^C76</f>
-        <v>3.5568380305864293</v>
+        <v>3.7448553439982017</v>
       </c>
       <c r="D104" s="117"/>
     </row>
-    <row r="105" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="111" t="s">
         <v>399</v>
       </c>
       <c r="C105" s="112">
         <f>C103+C104</f>
-        <v>3.8656512307065762</v>
+        <v>4.0536685441183486</v>
       </c>
       <c r="D105" t="s">
         <v>397</v>
@@ -19373,19 +19362,19 @@
       </c>
       <c r="F105" s="319">
         <f>(1-C105/C66)</f>
-        <v>0.22106689885075603</v>
-      </c>
-    </row>
-    <row r="106" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.22401578084943807</v>
+      </c>
+    </row>
+    <row r="106" spans="2:8">
       <c r="B106" s="100"/>
     </row>
-    <row r="107" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:8" ht="14.65">
       <c r="E107" s="310" t="s">
         <v>325</v>
       </c>
       <c r="F107" s="307"/>
     </row>
-    <row r="108" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:8" ht="13.9">
       <c r="E108" s="303" t="s">
         <v>326</v>
       </c>
@@ -19393,7 +19382,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="109" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:8" ht="13.9">
       <c r="E109" s="304" t="s">
         <v>326</v>
       </c>
@@ -19401,7 +19390,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="110" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:8" ht="13.9">
       <c r="E110" s="305" t="s">
         <v>326</v>
       </c>

--- a/financial_models/opportunities/0398.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0398.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC256139-B525-43B9-903B-703FD7B06BCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90F018A7-4E48-4248-B836-3809FE68F9B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3866,29 +3866,29 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4306,7 +4306,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>3.57</v>
+        <v>3.59</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4327,7 +4327,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>1739.8688596799998</v>
+        <v>1749.6160241599998</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4364,13 +4364,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="347" t="s">
+      <c r="B18" s="349" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="347"/>
-      <c r="D18" s="347"/>
-      <c r="E18" s="347"/>
-      <c r="F18" s="347"/>
+      <c r="C18" s="349"/>
+      <c r="D18" s="349"/>
+      <c r="E18" s="349"/>
+      <c r="F18" s="349"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="E26" s="331">
         <f ca="1">Scenarios!C87</f>
-        <v>0.1671769416467408</v>
+        <v>0.16494017618254819</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4570,22 +4570,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="347" t="s">
+      <c r="B36" s="349" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="347"/>
-      <c r="D36" s="347"/>
-      <c r="E36" s="347"/>
-      <c r="F36" s="347"/>
+      <c r="C36" s="349"/>
+      <c r="D36" s="349"/>
+      <c r="E36" s="349"/>
+      <c r="F36" s="349"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="349" t="s">
+      <c r="B37" s="352" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="349"/>
-      <c r="D37" s="349"/>
-      <c r="E37" s="349"/>
-      <c r="F37" s="349"/>
+      <c r="C37" s="352"/>
+      <c r="D37" s="352"/>
+      <c r="E37" s="352"/>
+      <c r="F37" s="352"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="232" t="s">
@@ -4597,13 +4597,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="348" t="s">
+      <c r="B40" s="350" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="348"/>
-      <c r="D40" s="348"/>
-      <c r="E40" s="348"/>
-      <c r="F40" s="348"/>
+      <c r="C40" s="350"/>
+      <c r="D40" s="350"/>
+      <c r="E40" s="350"/>
+      <c r="F40" s="350"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4623,13 +4623,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="348" t="s">
+      <c r="B43" s="350" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="348"/>
-      <c r="D43" s="348"/>
-      <c r="E43" s="348"/>
-      <c r="F43" s="348"/>
+      <c r="C43" s="350"/>
+      <c r="D43" s="350"/>
+      <c r="E43" s="350"/>
+      <c r="F43" s="350"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4658,13 +4658,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="348" t="s">
+      <c r="B47" s="350" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="348"/>
-      <c r="D47" s="348"/>
-      <c r="E47" s="348"/>
-      <c r="F47" s="348"/>
+      <c r="C47" s="350"/>
+      <c r="D47" s="350"/>
+      <c r="E47" s="350"/>
+      <c r="F47" s="350"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4680,13 +4680,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="348" t="s">
+      <c r="B50" s="350" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="348"/>
-      <c r="D50" s="348"/>
-      <c r="E50" s="348"/>
-      <c r="F50" s="348"/>
+      <c r="C50" s="350"/>
+      <c r="D50" s="350"/>
+      <c r="E50" s="350"/>
+      <c r="F50" s="350"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4750,13 +4750,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="348" t="s">
+      <c r="B58" s="350" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="348"/>
-      <c r="D58" s="348"/>
-      <c r="E58" s="348"/>
-      <c r="F58" s="348"/>
+      <c r="C58" s="350"/>
+      <c r="D58" s="350"/>
+      <c r="E58" s="350"/>
+      <c r="F58" s="350"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4772,7 +4772,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="348" t="s">
+      <c r="B61" s="350" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="351"/>
@@ -4794,22 +4794,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="347" t="s">
+      <c r="B64" s="349" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="347"/>
-      <c r="D64" s="347"/>
-      <c r="E64" s="347"/>
-      <c r="F64" s="347"/>
+      <c r="C64" s="349"/>
+      <c r="D64" s="349"/>
+      <c r="E64" s="349"/>
+      <c r="F64" s="349"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="347" t="s">
+      <c r="B65" s="349" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="347"/>
-      <c r="D65" s="347"/>
-      <c r="E65" s="347"/>
-      <c r="F65" s="347"/>
+      <c r="C65" s="349"/>
+      <c r="D65" s="349"/>
+      <c r="E65" s="349"/>
+      <c r="F65" s="349"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4843,7 +4843,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>7.9541327003833207E-2</v>
+        <v>7.9098199833895419E-2</v>
       </c>
       <c r="F69" s="344"/>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.5854341736694682E-2</v>
+        <v>3.5654596100278553E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>449</v>
@@ -4878,22 +4878,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.5" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="347" t="s">
+      <c r="B74" s="349" t="s">
         <v>363</v>
       </c>
-      <c r="C74" s="347"/>
-      <c r="D74" s="347"/>
-      <c r="E74" s="347"/>
-      <c r="F74" s="347"/>
+      <c r="C74" s="349"/>
+      <c r="D74" s="349"/>
+      <c r="E74" s="349"/>
+      <c r="F74" s="349"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="349" t="s">
+      <c r="B75" s="352" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="349"/>
-      <c r="D75" s="349"/>
-      <c r="E75" s="349"/>
-      <c r="F75" s="349"/>
+      <c r="C75" s="352"/>
+      <c r="D75" s="352"/>
+      <c r="E75" s="352"/>
+      <c r="F75" s="352"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="232" t="s">
@@ -4937,22 +4937,22 @@
       <c r="C82" s="122"/>
     </row>
     <row r="83" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B83" s="347" t="s">
+      <c r="B83" s="349" t="s">
         <v>364</v>
       </c>
-      <c r="C83" s="347"/>
-      <c r="D83" s="347"/>
-      <c r="E83" s="347"/>
-      <c r="F83" s="347"/>
+      <c r="C83" s="349"/>
+      <c r="D83" s="349"/>
+      <c r="E83" s="349"/>
+      <c r="F83" s="349"/>
     </row>
     <row r="84" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B84" s="347" t="s">
+      <c r="B84" s="349" t="s">
         <v>365</v>
       </c>
-      <c r="C84" s="347"/>
-      <c r="D84" s="347"/>
-      <c r="E84" s="347"/>
-      <c r="F84" s="347"/>
+      <c r="C84" s="349"/>
+      <c r="D84" s="349"/>
+      <c r="E84" s="349"/>
+      <c r="F84" s="349"/>
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
@@ -4989,13 +4989,13 @@
       <c r="A90" s="231"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="B91" s="347" t="s">
+      <c r="B91" s="349" t="s">
         <v>366</v>
       </c>
-      <c r="C91" s="347"/>
-      <c r="D91" s="347"/>
-      <c r="E91" s="347"/>
-      <c r="F91" s="347"/>
+      <c r="C91" s="349"/>
+      <c r="D91" s="349"/>
+      <c r="E91" s="349"/>
+      <c r="F91" s="349"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
@@ -5008,13 +5008,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B95" s="347" t="s">
+      <c r="B95" s="349" t="s">
         <v>345</v>
       </c>
-      <c r="C95" s="347"/>
-      <c r="D95" s="347"/>
-      <c r="E95" s="347"/>
-      <c r="F95" s="347"/>
+      <c r="C95" s="349"/>
+      <c r="D95" s="349"/>
+      <c r="E95" s="349"/>
+      <c r="F95" s="349"/>
     </row>
     <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
@@ -5145,13 +5145,13 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B111" s="347" t="s">
+      <c r="B111" s="349" t="s">
         <v>367</v>
       </c>
-      <c r="C111" s="347"/>
-      <c r="D111" s="347"/>
-      <c r="E111" s="347"/>
-      <c r="F111" s="347"/>
+      <c r="C111" s="349"/>
+      <c r="D111" s="349"/>
+      <c r="E111" s="349"/>
+      <c r="F111" s="349"/>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
@@ -5190,13 +5190,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B118" s="348" t="s">
+      <c r="B118" s="350" t="s">
         <v>368</v>
       </c>
-      <c r="C118" s="348"/>
-      <c r="D118" s="348"/>
-      <c r="E118" s="348"/>
-      <c r="F118" s="348"/>
+      <c r="C118" s="350"/>
+      <c r="D118" s="350"/>
+      <c r="E118" s="350"/>
+      <c r="F118" s="350"/>
     </row>
     <row r="120" spans="1:6" ht="12.4">
       <c r="B120" s="255" t="s">
@@ -5339,13 +5339,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B129" s="352" t="s">
+      <c r="B129" s="353" t="s">
         <v>371</v>
       </c>
-      <c r="C129" s="352"/>
-      <c r="D129" s="352"/>
-      <c r="E129" s="352"/>
-      <c r="F129" s="352"/>
+      <c r="C129" s="353"/>
+      <c r="D129" s="353"/>
+      <c r="E129" s="353"/>
+      <c r="F129" s="353"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="244" t="s">
@@ -5358,22 +5358,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="350" t="s">
+      <c r="B133" s="354" t="s">
         <v>369</v>
       </c>
-      <c r="C133" s="350"/>
-      <c r="D133" s="350"/>
-      <c r="E133" s="350"/>
-      <c r="F133" s="350"/>
+      <c r="C133" s="354"/>
+      <c r="D133" s="354"/>
+      <c r="E133" s="354"/>
+      <c r="F133" s="354"/>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="347" t="s">
+      <c r="B134" s="349" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="347"/>
-      <c r="D134" s="347"/>
-      <c r="E134" s="347"/>
-      <c r="F134" s="347"/>
+      <c r="C134" s="349"/>
+      <c r="D134" s="349"/>
+      <c r="E134" s="349"/>
+      <c r="F134" s="349"/>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="232" t="s">
@@ -5706,13 +5706,13 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="354" t="s">
+      <c r="B174" s="348" t="s">
         <v>377</v>
       </c>
-      <c r="C174" s="347"/>
-      <c r="D174" s="347"/>
-      <c r="E174" s="347"/>
-      <c r="F174" s="347"/>
+      <c r="C174" s="349"/>
+      <c r="D174" s="349"/>
+      <c r="E174" s="349"/>
+      <c r="F174" s="349"/>
     </row>
     <row r="176" spans="1:6">
       <c r="B176" s="232" t="s">
@@ -5749,13 +5749,13 @@
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B183" s="348" t="s">
+      <c r="B183" s="350" t="s">
         <v>382</v>
       </c>
-      <c r="C183" s="348"/>
-      <c r="D183" s="348"/>
-      <c r="E183" s="348"/>
-      <c r="F183" s="348"/>
+      <c r="C183" s="350"/>
+      <c r="D183" s="350"/>
+      <c r="E183" s="350"/>
+      <c r="F183" s="350"/>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
@@ -5763,22 +5763,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B186" s="353" t="s">
+      <c r="B186" s="347" t="s">
         <v>383</v>
       </c>
-      <c r="C186" s="353"/>
-      <c r="D186" s="353"/>
-      <c r="E186" s="353"/>
-      <c r="F186" s="353"/>
+      <c r="C186" s="347"/>
+      <c r="D186" s="347"/>
+      <c r="E186" s="347"/>
+      <c r="F186" s="347"/>
     </row>
     <row r="187" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B187" s="353" t="s">
+      <c r="B187" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C187" s="353"/>
-      <c r="D187" s="353"/>
-      <c r="E187" s="353"/>
-      <c r="F187" s="353"/>
+      <c r="C187" s="347"/>
+      <c r="D187" s="347"/>
+      <c r="E187" s="347"/>
+      <c r="F187" s="347"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
@@ -5802,17 +5802,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5829,6 +5818,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -13323,24 +13323,24 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.5854341736694682E-2</v>
+        <v>3.5654596100278553E-2</v>
       </c>
       <c r="E93" s="293"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.5854341736694682E-2</v>
+        <v>3.5654596100278553E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>4.2857142857142858E-2</v>
+        <v>4.2618384401114207E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>5.2100840336134456E-2</v>
+        <v>5.1810584958217269E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>4.145658263305322E-2</v>
+        <v>4.1225626740947076E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
@@ -14522,46 +14522,46 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.9541327003833207E-2</v>
+        <v>7.9098199833895419E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="290"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.11171704057956958</v>
+        <v>0.11109466152341599</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.14338436981157476</v>
+        <v>0.14258557109396153</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.15459038680045631</v>
+        <v>0.15372915901883816</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.10653504082720994</v>
+        <v>0.10594153085045668</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>6.4976161491155357E-2</v>
+        <v>6.461417730457511E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>5.9514255585357487E-2</v>
+        <v>5.9182699843934879E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>5.5854209620070649E-2</v>
+        <v>5.5543044106866911E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>-3.8100572713389552E-3</v>
+        <v>-3.7888313255376241E-3</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>-3.2382900404552634E-2</v>
+        <v>-3.2202494274165154E-2</v>
       </c>
       <c r="P125" s="77" t="str">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
@@ -14579,39 +14579,39 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14434995982754242</v>
+        <v>0.14354578177836391</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16985418088024942</v>
+        <v>0.16890791803411989</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.20862262002134993</v>
+        <v>0.20746037701287443</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1337020308776517</v>
+        <v>0.13295717276691268</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.6963488626509656E-2</v>
+        <v>5.6646143285971999E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9338738222712035E-2</v>
+        <v>7.8896739681081324E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9710030574090068E-2</v>
+        <v>7.9265963551393176E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.2518467184708342E-3</v>
+        <v>9.2003043969194655E-3</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-9.0575792033535368E-3</v>
+        <v>-9.0071191520813727E-3</v>
       </c>
       <c r="P126" s="23" t="str">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18335,7 +18335,7 @@
       </c>
       <c r="I3" s="125">
         <f>-Market_Price</f>
-        <v>-3.57</v>
+        <v>-3.59</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18575,7 +18575,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>3.57</v>
+        <v>3.59</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19173,7 +19173,7 @@
       </c>
       <c r="C86" s="117">
         <f>Market_Price</f>
-        <v>3.57</v>
+        <v>3.59</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19186,7 +19186,7 @@
       </c>
       <c r="C87" s="259">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.1671769416467408</v>
+        <v>0.16494017618254819</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0398.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0398.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C895146-082F-4977-A326-51D5AEF0AD3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4743C88C-1B7D-45A3-91B9-327C97609074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3865,29 +3865,29 @@
     <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4305,7 +4305,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>3.59</v>
+        <v>3.6</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>1749.6160241599998</v>
+        <v>1754.4896064000002</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4363,13 +4363,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="349" t="s">
+      <c r="B18" s="347" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="349"/>
-      <c r="D18" s="349"/>
-      <c r="E18" s="349"/>
-      <c r="F18" s="349"/>
+      <c r="C18" s="347"/>
+      <c r="D18" s="347"/>
+      <c r="E18" s="347"/>
+      <c r="F18" s="347"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="E26" s="304">
         <f ca="1">Scenarios!C87</f>
-        <v>0.16494017618254819</v>
+        <v>0.16382813843087729</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4569,22 +4569,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="349" t="s">
+      <c r="B36" s="347" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="349"/>
-      <c r="D36" s="349"/>
-      <c r="E36" s="349"/>
-      <c r="F36" s="349"/>
+      <c r="C36" s="347"/>
+      <c r="D36" s="347"/>
+      <c r="E36" s="347"/>
+      <c r="F36" s="347"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="352" t="s">
+      <c r="B37" s="349" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="352"/>
-      <c r="D37" s="352"/>
-      <c r="E37" s="352"/>
-      <c r="F37" s="352"/>
+      <c r="C37" s="349"/>
+      <c r="D37" s="349"/>
+      <c r="E37" s="349"/>
+      <c r="F37" s="349"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4596,13 +4596,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="350" t="s">
+      <c r="B40" s="348" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="350"/>
-      <c r="D40" s="350"/>
-      <c r="E40" s="350"/>
-      <c r="F40" s="350"/>
+      <c r="C40" s="348"/>
+      <c r="D40" s="348"/>
+      <c r="E40" s="348"/>
+      <c r="F40" s="348"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4622,13 +4622,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="350" t="s">
+      <c r="B43" s="348" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="350"/>
-      <c r="D43" s="350"/>
-      <c r="E43" s="350"/>
-      <c r="F43" s="350"/>
+      <c r="C43" s="348"/>
+      <c r="D43" s="348"/>
+      <c r="E43" s="348"/>
+      <c r="F43" s="348"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4657,13 +4657,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="350" t="s">
+      <c r="B47" s="348" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="350"/>
-      <c r="D47" s="350"/>
-      <c r="E47" s="350"/>
-      <c r="F47" s="350"/>
+      <c r="C47" s="348"/>
+      <c r="D47" s="348"/>
+      <c r="E47" s="348"/>
+      <c r="F47" s="348"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4679,13 +4679,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="350" t="s">
+      <c r="B50" s="348" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="350"/>
-      <c r="D50" s="350"/>
-      <c r="E50" s="350"/>
-      <c r="F50" s="350"/>
+      <c r="C50" s="348"/>
+      <c r="D50" s="348"/>
+      <c r="E50" s="348"/>
+      <c r="F50" s="348"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4749,13 +4749,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="350" t="s">
+      <c r="B58" s="348" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="350"/>
-      <c r="D58" s="350"/>
-      <c r="E58" s="350"/>
-      <c r="F58" s="350"/>
+      <c r="C58" s="348"/>
+      <c r="D58" s="348"/>
+      <c r="E58" s="348"/>
+      <c r="F58" s="348"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4771,7 +4771,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="350" t="s">
+      <c r="B61" s="348" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="351"/>
@@ -4793,22 +4793,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="349" t="s">
+      <c r="B64" s="347" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="349"/>
-      <c r="D64" s="349"/>
-      <c r="E64" s="349"/>
-      <c r="F64" s="349"/>
+      <c r="C64" s="347"/>
+      <c r="D64" s="347"/>
+      <c r="E64" s="347"/>
+      <c r="F64" s="347"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="349" t="s">
+      <c r="B65" s="347" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="349"/>
-      <c r="D65" s="349"/>
-      <c r="E65" s="349"/>
-      <c r="F65" s="349"/>
+      <c r="C65" s="347"/>
+      <c r="D65" s="347"/>
+      <c r="E65" s="347"/>
+      <c r="F65" s="347"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>7.9098199833895419E-2</v>
+        <v>7.8878482612134579E-2</v>
       </c>
       <c r="F69" s="317"/>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.5654596100278553E-2</v>
+        <v>3.5555555555555556E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>449</v>
@@ -4877,22 +4877,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.5" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="349" t="s">
+      <c r="B74" s="347" t="s">
         <v>363</v>
       </c>
-      <c r="C74" s="349"/>
-      <c r="D74" s="349"/>
-      <c r="E74" s="349"/>
-      <c r="F74" s="349"/>
+      <c r="C74" s="347"/>
+      <c r="D74" s="347"/>
+      <c r="E74" s="347"/>
+      <c r="F74" s="347"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="352" t="s">
+      <c r="B75" s="349" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="352"/>
-      <c r="D75" s="352"/>
-      <c r="E75" s="352"/>
-      <c r="F75" s="352"/>
+      <c r="C75" s="349"/>
+      <c r="D75" s="349"/>
+      <c r="E75" s="349"/>
+      <c r="F75" s="349"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="210" t="s">
@@ -4936,22 +4936,22 @@
       <c r="C82" s="121"/>
     </row>
     <row r="83" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B83" s="349" t="s">
+      <c r="B83" s="347" t="s">
         <v>364</v>
       </c>
-      <c r="C83" s="349"/>
-      <c r="D83" s="349"/>
-      <c r="E83" s="349"/>
-      <c r="F83" s="349"/>
+      <c r="C83" s="347"/>
+      <c r="D83" s="347"/>
+      <c r="E83" s="347"/>
+      <c r="F83" s="347"/>
     </row>
     <row r="84" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B84" s="349" t="s">
+      <c r="B84" s="347" t="s">
         <v>365</v>
       </c>
-      <c r="C84" s="349"/>
-      <c r="D84" s="349"/>
-      <c r="E84" s="349"/>
-      <c r="F84" s="349"/>
+      <c r="C84" s="347"/>
+      <c r="D84" s="347"/>
+      <c r="E84" s="347"/>
+      <c r="F84" s="347"/>
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
@@ -4988,13 +4988,13 @@
       <c r="A90" s="209"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="B91" s="349" t="s">
+      <c r="B91" s="347" t="s">
         <v>366</v>
       </c>
-      <c r="C91" s="349"/>
-      <c r="D91" s="349"/>
-      <c r="E91" s="349"/>
-      <c r="F91" s="349"/>
+      <c r="C91" s="347"/>
+      <c r="D91" s="347"/>
+      <c r="E91" s="347"/>
+      <c r="F91" s="347"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
@@ -5007,13 +5007,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B95" s="349" t="s">
+      <c r="B95" s="347" t="s">
         <v>345</v>
       </c>
-      <c r="C95" s="349"/>
-      <c r="D95" s="349"/>
-      <c r="E95" s="349"/>
-      <c r="F95" s="349"/>
+      <c r="C95" s="347"/>
+      <c r="D95" s="347"/>
+      <c r="E95" s="347"/>
+      <c r="F95" s="347"/>
     </row>
     <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
@@ -5144,13 +5144,13 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B111" s="349" t="s">
+      <c r="B111" s="347" t="s">
         <v>367</v>
       </c>
-      <c r="C111" s="349"/>
-      <c r="D111" s="349"/>
-      <c r="E111" s="349"/>
-      <c r="F111" s="349"/>
+      <c r="C111" s="347"/>
+      <c r="D111" s="347"/>
+      <c r="E111" s="347"/>
+      <c r="F111" s="347"/>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
@@ -5189,13 +5189,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B118" s="350" t="s">
+      <c r="B118" s="348" t="s">
         <v>368</v>
       </c>
-      <c r="C118" s="350"/>
-      <c r="D118" s="350"/>
-      <c r="E118" s="350"/>
-      <c r="F118" s="350"/>
+      <c r="C118" s="348"/>
+      <c r="D118" s="348"/>
+      <c r="E118" s="348"/>
+      <c r="F118" s="348"/>
     </row>
     <row r="120" spans="1:6" ht="12.4">
       <c r="B120" s="233" t="s">
@@ -5338,13 +5338,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B129" s="353" t="s">
+      <c r="B129" s="352" t="s">
         <v>371</v>
       </c>
-      <c r="C129" s="353"/>
-      <c r="D129" s="353"/>
-      <c r="E129" s="353"/>
-      <c r="F129" s="353"/>
+      <c r="C129" s="352"/>
+      <c r="D129" s="352"/>
+      <c r="E129" s="352"/>
+      <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="222" t="s">
@@ -5357,22 +5357,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="354" t="s">
+      <c r="B133" s="350" t="s">
         <v>369</v>
       </c>
-      <c r="C133" s="354"/>
-      <c r="D133" s="354"/>
-      <c r="E133" s="354"/>
-      <c r="F133" s="354"/>
+      <c r="C133" s="350"/>
+      <c r="D133" s="350"/>
+      <c r="E133" s="350"/>
+      <c r="F133" s="350"/>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="349" t="s">
+      <c r="B134" s="347" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="349"/>
-      <c r="D134" s="349"/>
-      <c r="E134" s="349"/>
-      <c r="F134" s="349"/>
+      <c r="C134" s="347"/>
+      <c r="D134" s="347"/>
+      <c r="E134" s="347"/>
+      <c r="F134" s="347"/>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="210" t="s">
@@ -5705,13 +5705,13 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="348" t="s">
+      <c r="B174" s="354" t="s">
         <v>377</v>
       </c>
-      <c r="C174" s="349"/>
-      <c r="D174" s="349"/>
-      <c r="E174" s="349"/>
-      <c r="F174" s="349"/>
+      <c r="C174" s="347"/>
+      <c r="D174" s="347"/>
+      <c r="E174" s="347"/>
+      <c r="F174" s="347"/>
     </row>
     <row r="176" spans="1:6">
       <c r="B176" s="210" t="s">
@@ -5748,13 +5748,13 @@
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B183" s="350" t="s">
+      <c r="B183" s="348" t="s">
         <v>382</v>
       </c>
-      <c r="C183" s="350"/>
-      <c r="D183" s="350"/>
-      <c r="E183" s="350"/>
-      <c r="F183" s="350"/>
+      <c r="C183" s="348"/>
+      <c r="D183" s="348"/>
+      <c r="E183" s="348"/>
+      <c r="F183" s="348"/>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
@@ -5762,22 +5762,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B186" s="347" t="s">
+      <c r="B186" s="353" t="s">
         <v>383</v>
       </c>
-      <c r="C186" s="347"/>
-      <c r="D186" s="347"/>
-      <c r="E186" s="347"/>
-      <c r="F186" s="347"/>
+      <c r="C186" s="353"/>
+      <c r="D186" s="353"/>
+      <c r="E186" s="353"/>
+      <c r="F186" s="353"/>
     </row>
     <row r="187" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B187" s="347" t="s">
+      <c r="B187" s="353" t="s">
         <v>384</v>
       </c>
-      <c r="C187" s="347"/>
-      <c r="D187" s="347"/>
-      <c r="E187" s="347"/>
-      <c r="F187" s="347"/>
+      <c r="C187" s="353"/>
+      <c r="D187" s="353"/>
+      <c r="E187" s="353"/>
+      <c r="F187" s="353"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
@@ -5801,6 +5801,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5817,17 +5828,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13325,24 +13325,24 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.5654596100278553E-2</v>
+        <v>3.5555555555555556E-2</v>
       </c>
       <c r="E93" s="270"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.5654596100278553E-2</v>
+        <v>3.5555555555555556E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>4.2618384401114207E-2</v>
+        <v>4.2499999999999996E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>5.1810584958217269E-2</v>
+        <v>5.1666666666666666E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>4.1225626740947076E-2</v>
+        <v>4.1111111111111105E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
@@ -14524,46 +14524,46 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.9098199833895419E-2</v>
+        <v>7.8878482612134579E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="267"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.11109466152341599</v>
+        <v>0.1107860652414065</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.14258557109396153</v>
+        <v>0.14218950006314496</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.15372915901883816</v>
+        <v>0.15330213357711917</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.10594153085045668</v>
+        <v>0.10564724882031652</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>6.461417730457511E-2</v>
+        <v>6.4434693478729058E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>5.9182699843934879E-2</v>
+        <v>5.9018303455479502E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>5.5543044106866911E-2</v>
+        <v>5.5388757873236723E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>-3.7888313255376241E-3</v>
+        <v>-3.7783067940777969E-3</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>-3.2202494274165154E-2</v>
+        <v>-3.211304290118136E-2</v>
       </c>
       <c r="P125" s="77" t="str">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
@@ -14581,39 +14581,39 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14354578177836391</v>
+        <v>0.14314704349564619</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16890791803411989</v>
+        <v>0.16843872937291399</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.20746037701287443</v>
+        <v>0.20688409818783865</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13295717276691268</v>
+        <v>0.1325878472870046</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.6646143285971999E-2</v>
+        <v>5.6488792887955407E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8896739681081324E-2</v>
+        <v>7.8677582070856081E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9265963551393176E-2</v>
+        <v>7.9045780319305967E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.2003043969194655E-3</v>
+        <v>9.1747479958169103E-3</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-9.0071191520813727E-3</v>
+        <v>-8.9820993766589231E-3</v>
       </c>
       <c r="P126" s="23" t="str">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18337,7 +18337,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-3.59</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18577,7 +18577,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>3.59</v>
+        <v>3.6</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19175,7 +19175,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>3.59</v>
+        <v>3.6</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19188,7 +19188,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.16494017618254819</v>
+        <v>0.16382813843087729</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0398.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0398.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B558978A-A268-4D8C-BAEF-790A69B50BE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C950D7D-4CA7-429B-9E20-9F15DD6F5F9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3879,29 +3879,29 @@
     <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4319,7 +4319,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>1754.4896064000002</v>
+        <v>1749.6160241599998</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4377,13 +4377,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="350" t="s">
+      <c r="B18" s="348" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="350"/>
-      <c r="D18" s="350"/>
-      <c r="E18" s="350"/>
-      <c r="F18" s="350"/>
+      <c r="C18" s="348"/>
+      <c r="D18" s="348"/>
+      <c r="E18" s="348"/>
+      <c r="F18" s="348"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.16382813843087729</v>
+        <v>0.16494017618254819</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4583,22 +4583,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="350" t="s">
+      <c r="B36" s="348" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="350"/>
-      <c r="D36" s="350"/>
-      <c r="E36" s="350"/>
-      <c r="F36" s="350"/>
+      <c r="C36" s="348"/>
+      <c r="D36" s="348"/>
+      <c r="E36" s="348"/>
+      <c r="F36" s="348"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="353" t="s">
+      <c r="B37" s="350" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="353"/>
-      <c r="D37" s="353"/>
-      <c r="E37" s="353"/>
-      <c r="F37" s="353"/>
+      <c r="C37" s="350"/>
+      <c r="D37" s="350"/>
+      <c r="E37" s="350"/>
+      <c r="F37" s="350"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4610,13 +4610,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="351" t="s">
+      <c r="B40" s="349" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="351"/>
-      <c r="D40" s="351"/>
-      <c r="E40" s="351"/>
-      <c r="F40" s="351"/>
+      <c r="C40" s="349"/>
+      <c r="D40" s="349"/>
+      <c r="E40" s="349"/>
+      <c r="F40" s="349"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4636,13 +4636,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="351" t="s">
+      <c r="B43" s="349" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="351"/>
-      <c r="D43" s="351"/>
-      <c r="E43" s="351"/>
-      <c r="F43" s="351"/>
+      <c r="C43" s="349"/>
+      <c r="D43" s="349"/>
+      <c r="E43" s="349"/>
+      <c r="F43" s="349"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4671,13 +4671,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="351" t="s">
+      <c r="B47" s="349" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="351"/>
-      <c r="D47" s="351"/>
-      <c r="E47" s="351"/>
-      <c r="F47" s="351"/>
+      <c r="C47" s="349"/>
+      <c r="D47" s="349"/>
+      <c r="E47" s="349"/>
+      <c r="F47" s="349"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4693,13 +4693,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="351" t="s">
+      <c r="B50" s="349" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="351"/>
-      <c r="D50" s="351"/>
-      <c r="E50" s="351"/>
-      <c r="F50" s="351"/>
+      <c r="C50" s="349"/>
+      <c r="D50" s="349"/>
+      <c r="E50" s="349"/>
+      <c r="F50" s="349"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4763,13 +4763,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="351" t="s">
+      <c r="B58" s="349" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="351"/>
-      <c r="D58" s="351"/>
-      <c r="E58" s="351"/>
-      <c r="F58" s="351"/>
+      <c r="C58" s="349"/>
+      <c r="D58" s="349"/>
+      <c r="E58" s="349"/>
+      <c r="F58" s="349"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4785,7 +4785,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="351" t="s">
+      <c r="B61" s="349" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="352"/>
@@ -4807,22 +4807,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="350" t="s">
+      <c r="B64" s="348" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="350"/>
-      <c r="D64" s="350"/>
-      <c r="E64" s="350"/>
-      <c r="F64" s="350"/>
+      <c r="C64" s="348"/>
+      <c r="D64" s="348"/>
+      <c r="E64" s="348"/>
+      <c r="F64" s="348"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="350" t="s">
+      <c r="B65" s="348" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="350"/>
-      <c r="D65" s="350"/>
-      <c r="E65" s="350"/>
-      <c r="F65" s="350"/>
+      <c r="C65" s="348"/>
+      <c r="D65" s="348"/>
+      <c r="E65" s="348"/>
+      <c r="F65" s="348"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>7.8878482612134579E-2</v>
+        <v>7.9098199833895419E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.5555555555555556E-2</v>
+        <v>3.5654596100278553E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4957,22 +4957,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="350" t="s">
+      <c r="B80" s="348" t="s">
         <v>363</v>
       </c>
-      <c r="C80" s="350"/>
-      <c r="D80" s="350"/>
-      <c r="E80" s="350"/>
-      <c r="F80" s="350"/>
+      <c r="C80" s="348"/>
+      <c r="D80" s="348"/>
+      <c r="E80" s="348"/>
+      <c r="F80" s="348"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="353" t="s">
+      <c r="B81" s="350" t="s">
         <v>253</v>
       </c>
-      <c r="C81" s="353"/>
-      <c r="D81" s="353"/>
-      <c r="E81" s="353"/>
-      <c r="F81" s="353"/>
+      <c r="C81" s="350"/>
+      <c r="D81" s="350"/>
+      <c r="E81" s="350"/>
+      <c r="F81" s="350"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5016,22 +5016,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="350" t="s">
+      <c r="B89" s="348" t="s">
         <v>364</v>
       </c>
-      <c r="C89" s="350"/>
-      <c r="D89" s="350"/>
-      <c r="E89" s="350"/>
-      <c r="F89" s="350"/>
+      <c r="C89" s="348"/>
+      <c r="D89" s="348"/>
+      <c r="E89" s="348"/>
+      <c r="F89" s="348"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="350" t="s">
+      <c r="B90" s="348" t="s">
         <v>365</v>
       </c>
-      <c r="C90" s="350"/>
-      <c r="D90" s="350"/>
-      <c r="E90" s="350"/>
-      <c r="F90" s="350"/>
+      <c r="C90" s="348"/>
+      <c r="D90" s="348"/>
+      <c r="E90" s="348"/>
+      <c r="F90" s="348"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5068,13 +5068,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="350" t="s">
+      <c r="B97" s="348" t="s">
         <v>366</v>
       </c>
-      <c r="C97" s="350"/>
-      <c r="D97" s="350"/>
-      <c r="E97" s="350"/>
-      <c r="F97" s="350"/>
+      <c r="C97" s="348"/>
+      <c r="D97" s="348"/>
+      <c r="E97" s="348"/>
+      <c r="F97" s="348"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5087,13 +5087,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="350" t="s">
+      <c r="B101" s="348" t="s">
         <v>345</v>
       </c>
-      <c r="C101" s="350"/>
-      <c r="D101" s="350"/>
-      <c r="E101" s="350"/>
-      <c r="F101" s="350"/>
+      <c r="C101" s="348"/>
+      <c r="D101" s="348"/>
+      <c r="E101" s="348"/>
+      <c r="F101" s="348"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5215,13 +5215,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="350" t="s">
+      <c r="B116" s="348" t="s">
         <v>367</v>
       </c>
-      <c r="C116" s="350"/>
-      <c r="D116" s="350"/>
-      <c r="E116" s="350"/>
-      <c r="F116" s="350"/>
+      <c r="C116" s="348"/>
+      <c r="D116" s="348"/>
+      <c r="E116" s="348"/>
+      <c r="F116" s="348"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5260,13 +5260,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="351" t="s">
+      <c r="B123" s="349" t="s">
         <v>368</v>
       </c>
-      <c r="C123" s="351"/>
-      <c r="D123" s="351"/>
-      <c r="E123" s="351"/>
-      <c r="F123" s="351"/>
+      <c r="C123" s="349"/>
+      <c r="D123" s="349"/>
+      <c r="E123" s="349"/>
+      <c r="F123" s="349"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5409,13 +5409,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="354" t="s">
+      <c r="B134" s="353" t="s">
         <v>371</v>
       </c>
-      <c r="C134" s="354"/>
-      <c r="D134" s="354"/>
-      <c r="E134" s="354"/>
-      <c r="F134" s="354"/>
+      <c r="C134" s="353"/>
+      <c r="D134" s="353"/>
+      <c r="E134" s="353"/>
+      <c r="F134" s="353"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5428,22 +5428,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="355" t="s">
+      <c r="B138" s="351" t="s">
         <v>369</v>
       </c>
-      <c r="C138" s="355"/>
-      <c r="D138" s="355"/>
-      <c r="E138" s="355"/>
-      <c r="F138" s="355"/>
+      <c r="C138" s="351"/>
+      <c r="D138" s="351"/>
+      <c r="E138" s="351"/>
+      <c r="F138" s="351"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="350" t="s">
+      <c r="B139" s="348" t="s">
         <v>370</v>
       </c>
-      <c r="C139" s="350"/>
-      <c r="D139" s="350"/>
-      <c r="E139" s="350"/>
-      <c r="F139" s="350"/>
+      <c r="C139" s="348"/>
+      <c r="D139" s="348"/>
+      <c r="E139" s="348"/>
+      <c r="F139" s="348"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5776,13 +5776,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="349" t="s">
+      <c r="B179" s="355" t="s">
         <v>377</v>
       </c>
-      <c r="C179" s="350"/>
-      <c r="D179" s="350"/>
-      <c r="E179" s="350"/>
-      <c r="F179" s="350"/>
+      <c r="C179" s="348"/>
+      <c r="D179" s="348"/>
+      <c r="E179" s="348"/>
+      <c r="F179" s="348"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5819,13 +5819,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="351" t="s">
+      <c r="B188" s="349" t="s">
         <v>382</v>
       </c>
-      <c r="C188" s="351"/>
-      <c r="D188" s="351"/>
-      <c r="E188" s="351"/>
-      <c r="F188" s="351"/>
+      <c r="C188" s="349"/>
+      <c r="D188" s="349"/>
+      <c r="E188" s="349"/>
+      <c r="F188" s="349"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5833,22 +5833,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="348" t="s">
+      <c r="B191" s="354" t="s">
         <v>383</v>
       </c>
-      <c r="C191" s="348"/>
-      <c r="D191" s="348"/>
-      <c r="E191" s="348"/>
-      <c r="F191" s="348"/>
+      <c r="C191" s="354"/>
+      <c r="D191" s="354"/>
+      <c r="E191" s="354"/>
+      <c r="F191" s="354"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="348" t="s">
+      <c r="B192" s="354" t="s">
         <v>384</v>
       </c>
-      <c r="C192" s="348"/>
-      <c r="D192" s="348"/>
-      <c r="E192" s="348"/>
-      <c r="F192" s="348"/>
+      <c r="C192" s="354"/>
+      <c r="D192" s="354"/>
+      <c r="E192" s="354"/>
+      <c r="F192" s="354"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5872,6 +5872,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5888,17 +5899,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13396,24 +13396,24 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.5555555555555556E-2</v>
+        <v>3.5654596100278553E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.5555555555555556E-2</v>
+        <v>3.5654596100278553E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>4.2499999999999996E-2</v>
+        <v>4.2618384401114207E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>5.1666666666666666E-2</v>
+        <v>5.1810584958217269E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>4.1111111111111105E-2</v>
+        <v>4.1225626740947076E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
@@ -14595,46 +14595,46 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.8878482612134579E-2</v>
+        <v>7.9098199833895419E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.1107860652414065</v>
+        <v>0.11109466152341599</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.14218950006314496</v>
+        <v>0.14258557109396153</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.15330213357711917</v>
+        <v>0.15372915901883816</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.10564724882031652</v>
+        <v>0.10594153085045668</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>6.4434693478729058E-2</v>
+        <v>6.461417730457511E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>5.9018303455479502E-2</v>
+        <v>5.9182699843934879E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>5.5388757873236723E-2</v>
+        <v>5.5543044106866911E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>-3.7783067940777969E-3</v>
+        <v>-3.7888313255376241E-3</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>-3.211304290118136E-2</v>
+        <v>-3.2202494274165154E-2</v>
       </c>
       <c r="P125" s="77" t="str">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
@@ -14652,39 +14652,39 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14314704349564619</v>
+        <v>0.14354578177836391</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16843872937291399</v>
+        <v>0.16890791803411989</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.20688409818783865</v>
+        <v>0.20746037701287443</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1325878472870046</v>
+        <v>0.13295717276691268</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.6488792887955407E-2</v>
+        <v>5.6646143285971999E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8677582070856081E-2</v>
+        <v>7.8896739681081324E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9045780319305967E-2</v>
+        <v>7.9265963551393176E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.1747479958169103E-3</v>
+        <v>9.2003043969194655E-3</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-8.9820993766589231E-3</v>
+        <v>-9.0071191520813727E-3</v>
       </c>
       <c r="P126" s="23" t="str">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18408,7 +18408,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-3.6</v>
+        <v>-3.59</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18648,7 +18648,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19246,7 +19246,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19259,7 +19259,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.16382813843087729</v>
+        <v>0.16494017618254819</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0398.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0398.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C950D7D-4CA7-429B-9E20-9F15DD6F5F9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FAFC190-8E5D-4931-A42B-E80A9FFA5598}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -2480,7 +2480,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="17">
+  <numFmts count="18">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0.00&quot;x&quot;"/>
@@ -2498,6 +2498,7 @@
     <numFmt numFmtId="178" formatCode="0.0\x"/>
     <numFmt numFmtId="179" formatCode="0\x"/>
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
+    <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
   <fonts count="59">
     <font>
@@ -3146,7 +3147,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="360">
+  <cellXfs count="369">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3818,36 +3819,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="37" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="37" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
     <xf numFmtId="37" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3862,10 +3840,6 @@
     </xf>
     <xf numFmtId="37" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="37" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="37" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="37" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="37" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -3877,6 +3851,48 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="181" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4377,13 +4393,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="348" t="s">
+      <c r="B18" s="357" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="348"/>
-      <c r="D18" s="348"/>
-      <c r="E18" s="348"/>
-      <c r="F18" s="348"/>
+      <c r="C18" s="357"/>
+      <c r="D18" s="357"/>
+      <c r="E18" s="357"/>
+      <c r="F18" s="357"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4583,22 +4599,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="348" t="s">
+      <c r="B36" s="357" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="348"/>
-      <c r="D36" s="348"/>
-      <c r="E36" s="348"/>
-      <c r="F36" s="348"/>
+      <c r="C36" s="357"/>
+      <c r="D36" s="357"/>
+      <c r="E36" s="357"/>
+      <c r="F36" s="357"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="350" t="s">
+      <c r="B37" s="359" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="350"/>
-      <c r="D37" s="350"/>
-      <c r="E37" s="350"/>
-      <c r="F37" s="350"/>
+      <c r="C37" s="359"/>
+      <c r="D37" s="359"/>
+      <c r="E37" s="359"/>
+      <c r="F37" s="359"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4610,19 +4626,19 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="349" t="s">
+      <c r="B40" s="358" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="349"/>
-      <c r="D40" s="349"/>
-      <c r="E40" s="349"/>
-      <c r="F40" s="349"/>
+      <c r="C40" s="358"/>
+      <c r="D40" s="358"/>
+      <c r="E40" s="358"/>
+      <c r="F40" s="358"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
         <v>233</v>
       </c>
-      <c r="C41" s="76">
+      <c r="C41" s="355">
         <f>Normalized_FCF!C8</f>
         <v>198948.88436097838</v>
       </c>
@@ -4636,19 +4652,19 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="349" t="s">
+      <c r="B43" s="358" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="349"/>
-      <c r="D43" s="349"/>
-      <c r="E43" s="349"/>
-      <c r="F43" s="349"/>
+      <c r="C43" s="358"/>
+      <c r="D43" s="358"/>
+      <c r="E43" s="358"/>
+      <c r="F43" s="358"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
         <v>235</v>
       </c>
-      <c r="C44" s="76">
+      <c r="C44" s="355">
         <f>Normalized_FCF!C9</f>
         <v>0</v>
       </c>
@@ -4661,7 +4677,7 @@
       <c r="B45" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="C45" s="76">
+      <c r="C45" s="355">
         <f>Normalized_FCF!C10</f>
         <v>0</v>
       </c>
@@ -4671,19 +4687,19 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="349" t="s">
+      <c r="B47" s="358" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="349"/>
-      <c r="D47" s="349"/>
-      <c r="E47" s="349"/>
-      <c r="F47" s="349"/>
+      <c r="C47" s="358"/>
+      <c r="D47" s="358"/>
+      <c r="E47" s="358"/>
+      <c r="F47" s="358"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
         <v>238</v>
       </c>
-      <c r="C48" s="76">
+      <c r="C48" s="355">
         <f>Normalized_FCF!C11</f>
         <v>0</v>
       </c>
@@ -4693,19 +4709,19 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="349" t="s">
+      <c r="B50" s="358" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="349"/>
-      <c r="D50" s="349"/>
-      <c r="E50" s="349"/>
-      <c r="F50" s="349"/>
+      <c r="C50" s="358"/>
+      <c r="D50" s="358"/>
+      <c r="E50" s="358"/>
+      <c r="F50" s="358"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
         <v>341</v>
       </c>
-      <c r="C51" s="340">
+      <c r="C51" s="356">
         <f>Normalized_FCF!C48</f>
         <v>0</v>
       </c>
@@ -4720,7 +4736,7 @@
       <c r="B52" s="47" t="s">
         <v>342</v>
       </c>
-      <c r="C52" s="340">
+      <c r="C52" s="356">
         <f>Normalized_FCF!C47</f>
         <v>-13663</v>
       </c>
@@ -4735,7 +4751,7 @@
       <c r="B53" s="47" t="s">
         <v>239</v>
       </c>
-      <c r="C53" s="76">
+      <c r="C53" s="355">
         <f>Normalized_FCF!C12</f>
         <v>-13663</v>
       </c>
@@ -4753,7 +4769,7 @@
       <c r="B56" s="47" t="s">
         <v>266</v>
       </c>
-      <c r="C56" s="76">
+      <c r="C56" s="355">
         <f>Normalized_FCF!C15</f>
         <v>-572.93535914055167</v>
       </c>
@@ -4763,19 +4779,19 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="349" t="s">
+      <c r="B58" s="358" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="349"/>
-      <c r="D58" s="349"/>
-      <c r="E58" s="349"/>
-      <c r="F58" s="349"/>
+      <c r="C58" s="358"/>
+      <c r="D58" s="358"/>
+      <c r="E58" s="358"/>
+      <c r="F58" s="358"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="C59" s="76">
+      <c r="C59" s="355">
         <f>Normalized_FCF!C14</f>
         <v>-46321.471090244595</v>
       </c>
@@ -4785,19 +4801,19 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="349" t="s">
+      <c r="B61" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C61" s="352"/>
-      <c r="D61" s="352"/>
-      <c r="E61" s="352"/>
-      <c r="F61" s="352"/>
+      <c r="C61" s="361"/>
+      <c r="D61" s="361"/>
+      <c r="E61" s="361"/>
+      <c r="F61" s="361"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
         <v>243</v>
       </c>
-      <c r="C62" s="76">
+      <c r="C62" s="355">
         <f>Normalized_FCF!C17</f>
         <v>0</v>
       </c>
@@ -4807,28 +4823,28 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="348" t="s">
+      <c r="B64" s="357" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="348"/>
-      <c r="D64" s="348"/>
-      <c r="E64" s="348"/>
-      <c r="F64" s="348"/>
+      <c r="C64" s="357"/>
+      <c r="D64" s="357"/>
+      <c r="E64" s="357"/>
+      <c r="F64" s="357"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="348" t="s">
+      <c r="B65" s="357" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="348"/>
-      <c r="D65" s="348"/>
-      <c r="E65" s="348"/>
-      <c r="F65" s="348"/>
+      <c r="C65" s="357"/>
+      <c r="D65" s="357"/>
+      <c r="E65" s="357"/>
+      <c r="F65" s="357"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
         <v>271</v>
       </c>
-      <c r="C67" s="76">
+      <c r="C67" s="355">
         <f>Normalized_FCF!G19</f>
         <v>194373</v>
       </c>
@@ -4841,7 +4857,7 @@
       <c r="B68" s="47" t="s">
         <v>249</v>
       </c>
-      <c r="C68" s="76">
+      <c r="C68" s="355">
         <f>Normalized_FCF!C19</f>
         <v>138391.47791159325</v>
       </c>
@@ -4880,10 +4896,10 @@
       <c r="B72" s="210" t="s">
         <v>451</v>
       </c>
-      <c r="C72" s="344" t="s">
+      <c r="C72" s="329" t="s">
         <v>453</v>
       </c>
-      <c r="D72" s="344" t="s">
+      <c r="D72" s="329" t="s">
         <v>454</v>
       </c>
     </row>
@@ -4905,11 +4921,11 @@
         <f>Normalized_FCF!B117</f>
         <v>Pre-tax Profit/Sales</v>
       </c>
-      <c r="C74" s="343">
+      <c r="C74" s="328">
         <f>Normalized_FCF!C117</f>
         <v>5.8835781303360896E-2</v>
       </c>
-      <c r="D74" s="343">
+      <c r="D74" s="328">
         <f>Normalized_FCF!G117</f>
         <v>9.3537135473147709E-2</v>
       </c>
@@ -4919,11 +4935,11 @@
         <f>Normalized_FCF!B118</f>
         <v>Sales/Total Assets</v>
       </c>
-      <c r="C75" s="345">
+      <c r="C75" s="330">
         <f>Normalized_FCF!C118</f>
         <v>1.2277297326073906</v>
       </c>
-      <c r="D75" s="345">
+      <c r="D75" s="330">
         <f>Normalized_FCF!G118</f>
         <v>1.4185842608933972</v>
       </c>
@@ -4933,11 +4949,11 @@
         <f>Normalized_FCF!B119</f>
         <v>Total Assets/Equity</v>
       </c>
-      <c r="C76" s="345">
+      <c r="C76" s="330">
         <f>Normalized_FCF!C119</f>
         <v>1.4000052396569989</v>
       </c>
-      <c r="D76" s="345">
+      <c r="D76" s="330">
         <f>Normalized_FCF!G119</f>
         <v>1.4000052396569989</v>
       </c>
@@ -4957,22 +4973,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="348" t="s">
+      <c r="B80" s="357" t="s">
         <v>363</v>
       </c>
-      <c r="C80" s="348"/>
-      <c r="D80" s="348"/>
-      <c r="E80" s="348"/>
-      <c r="F80" s="348"/>
+      <c r="C80" s="357"/>
+      <c r="D80" s="357"/>
+      <c r="E80" s="357"/>
+      <c r="F80" s="357"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="350" t="s">
+      <c r="B81" s="359" t="s">
         <v>253</v>
       </c>
-      <c r="C81" s="350"/>
-      <c r="D81" s="350"/>
-      <c r="E81" s="350"/>
-      <c r="F81" s="350"/>
+      <c r="C81" s="359"/>
+      <c r="D81" s="359"/>
+      <c r="E81" s="359"/>
+      <c r="F81" s="359"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5016,22 +5032,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="348" t="s">
+      <c r="B89" s="357" t="s">
         <v>364</v>
       </c>
-      <c r="C89" s="348"/>
-      <c r="D89" s="348"/>
-      <c r="E89" s="348"/>
-      <c r="F89" s="348"/>
+      <c r="C89" s="357"/>
+      <c r="D89" s="357"/>
+      <c r="E89" s="357"/>
+      <c r="F89" s="357"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="348" t="s">
+      <c r="B90" s="357" t="s">
         <v>365</v>
       </c>
-      <c r="C90" s="348"/>
-      <c r="D90" s="348"/>
-      <c r="E90" s="348"/>
-      <c r="F90" s="348"/>
+      <c r="C90" s="357"/>
+      <c r="D90" s="357"/>
+      <c r="E90" s="357"/>
+      <c r="F90" s="357"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5068,13 +5084,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="348" t="s">
+      <c r="B97" s="357" t="s">
         <v>366</v>
       </c>
-      <c r="C97" s="348"/>
-      <c r="D97" s="348"/>
-      <c r="E97" s="348"/>
-      <c r="F97" s="348"/>
+      <c r="C97" s="357"/>
+      <c r="D97" s="357"/>
+      <c r="E97" s="357"/>
+      <c r="F97" s="357"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5087,19 +5103,19 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="348" t="s">
+      <c r="B101" s="357" t="s">
         <v>345</v>
       </c>
-      <c r="C101" s="348"/>
-      <c r="D101" s="348"/>
-      <c r="E101" s="348"/>
-      <c r="F101" s="348"/>
+      <c r="C101" s="357"/>
+      <c r="D101" s="357"/>
+      <c r="E101" s="357"/>
+      <c r="F101" s="357"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="C102" s="76">
+      <c r="C102" s="355">
         <f>DCF!C7</f>
         <v>195066</v>
       </c>
@@ -5125,7 +5141,7 @@
       <c r="B104" s="296" t="s">
         <v>405</v>
       </c>
-      <c r="C104" s="346">
+      <c r="C104" s="331">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
         <v>0.10646655543311496</v>
       </c>
@@ -5134,7 +5150,7 @@
       <c r="B105" s="296" t="s">
         <v>407</v>
       </c>
-      <c r="C105" s="347">
+      <c r="C105" s="332">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
         <v>0.9804830051022897</v>
       </c>
@@ -5148,7 +5164,7 @@
       <c r="B108" s="47" t="s">
         <v>265</v>
       </c>
-      <c r="C108" s="76">
+      <c r="C108" s="355">
         <f>BS!C66</f>
         <v>1089388</v>
       </c>
@@ -5161,7 +5177,7 @@
       <c r="B109" s="47" t="s">
         <v>267</v>
       </c>
-      <c r="C109" s="76">
+      <c r="C109" s="355">
         <f>DCF!C8</f>
         <v>587281.82009631116</v>
       </c>
@@ -5192,7 +5208,7 @@
       <c r="B113" s="47" t="s">
         <v>258</v>
       </c>
-      <c r="C113" s="76">
+      <c r="C113" s="355">
         <f>DCF!C9</f>
         <v>18907.900000000001</v>
       </c>
@@ -5215,13 +5231,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="348" t="s">
+      <c r="B116" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C116" s="348"/>
-      <c r="D116" s="348"/>
-      <c r="E116" s="348"/>
-      <c r="F116" s="348"/>
+      <c r="C116" s="357"/>
+      <c r="D116" s="357"/>
+      <c r="E116" s="357"/>
+      <c r="F116" s="357"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5260,13 +5276,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="349" t="s">
+      <c r="B123" s="358" t="s">
         <v>368</v>
       </c>
-      <c r="C123" s="349"/>
-      <c r="D123" s="349"/>
-      <c r="E123" s="349"/>
-      <c r="F123" s="349"/>
+      <c r="C123" s="358"/>
+      <c r="D123" s="358"/>
+      <c r="E123" s="358"/>
+      <c r="F123" s="358"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5409,13 +5425,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="353" t="s">
+      <c r="B134" s="362" t="s">
         <v>371</v>
       </c>
-      <c r="C134" s="353"/>
-      <c r="D134" s="353"/>
-      <c r="E134" s="353"/>
-      <c r="F134" s="353"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5428,22 +5444,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="351" t="s">
+      <c r="B138" s="360" t="s">
         <v>369</v>
       </c>
-      <c r="C138" s="351"/>
-      <c r="D138" s="351"/>
-      <c r="E138" s="351"/>
-      <c r="F138" s="351"/>
+      <c r="C138" s="360"/>
+      <c r="D138" s="360"/>
+      <c r="E138" s="360"/>
+      <c r="F138" s="360"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="348" t="s">
+      <c r="B139" s="357" t="s">
         <v>370</v>
       </c>
-      <c r="C139" s="348"/>
-      <c r="D139" s="348"/>
-      <c r="E139" s="348"/>
-      <c r="F139" s="348"/>
+      <c r="C139" s="357"/>
+      <c r="D139" s="357"/>
+      <c r="E139" s="357"/>
+      <c r="F139" s="357"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5776,13 +5792,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="355" t="s">
+      <c r="B179" s="364" t="s">
         <v>377</v>
       </c>
-      <c r="C179" s="348"/>
-      <c r="D179" s="348"/>
-      <c r="E179" s="348"/>
-      <c r="F179" s="348"/>
+      <c r="C179" s="357"/>
+      <c r="D179" s="357"/>
+      <c r="E179" s="357"/>
+      <c r="F179" s="357"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5790,13 +5806,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="352" t="s">
+      <c r="B182" s="361" t="s">
         <v>381</v>
       </c>
-      <c r="C182" s="352"/>
-      <c r="D182" s="352"/>
-      <c r="E182" s="352"/>
-      <c r="F182" s="352"/>
+      <c r="C182" s="361"/>
+      <c r="D182" s="361"/>
+      <c r="E182" s="361"/>
+      <c r="F182" s="361"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -5819,13 +5835,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="349" t="s">
+      <c r="B188" s="358" t="s">
         <v>382</v>
       </c>
-      <c r="C188" s="349"/>
-      <c r="D188" s="349"/>
-      <c r="E188" s="349"/>
-      <c r="F188" s="349"/>
+      <c r="C188" s="358"/>
+      <c r="D188" s="358"/>
+      <c r="E188" s="358"/>
+      <c r="F188" s="358"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5833,22 +5849,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="354" t="s">
+      <c r="B191" s="363" t="s">
         <v>383</v>
       </c>
-      <c r="C191" s="354"/>
-      <c r="D191" s="354"/>
-      <c r="E191" s="354"/>
-      <c r="F191" s="354"/>
+      <c r="C191" s="363"/>
+      <c r="D191" s="363"/>
+      <c r="E191" s="363"/>
+      <c r="F191" s="363"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="354" t="s">
+      <c r="B192" s="363" t="s">
         <v>384</v>
       </c>
-      <c r="C192" s="354"/>
-      <c r="D192" s="354"/>
-      <c r="E192" s="354"/>
-      <c r="F192" s="354"/>
+      <c r="C192" s="363"/>
+      <c r="D192" s="363"/>
+      <c r="E192" s="363"/>
+      <c r="F192" s="363"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6014,353 +6030,353 @@
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="334">
+      <c r="C4" s="321">
         <v>3638758</v>
       </c>
-      <c r="D4" s="334">
+      <c r="D4" s="321">
         <v>3704677</v>
       </c>
-      <c r="E4" s="334">
+      <c r="E4" s="321">
         <v>3639774</v>
       </c>
-      <c r="F4" s="334">
+      <c r="F4" s="321">
         <v>3504022</v>
       </c>
-      <c r="G4" s="334">
+      <c r="G4" s="321">
         <v>2352683</v>
       </c>
-      <c r="H4" s="334">
+      <c r="H4" s="321">
         <v>2437184</v>
       </c>
-      <c r="I4" s="334">
+      <c r="I4" s="321">
         <v>2891692</v>
       </c>
-      <c r="J4" s="334">
+      <c r="J4" s="321">
         <v>3142295</v>
       </c>
-      <c r="K4" s="334">
+      <c r="K4" s="321">
         <v>3031752</v>
       </c>
-      <c r="L4" s="334"/>
-      <c r="M4" s="334"/>
+      <c r="L4" s="321"/>
+      <c r="M4" s="321"/>
     </row>
     <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="334">
+      <c r="C5" s="321">
         <v>2488028</v>
       </c>
-      <c r="D5" s="334">
+      <c r="D5" s="321">
         <v>2515967</v>
       </c>
-      <c r="E5" s="334">
+      <c r="E5" s="321">
         <v>2459489</v>
       </c>
-      <c r="F5" s="334">
+      <c r="F5" s="321">
         <v>2541906</v>
       </c>
-      <c r="G5" s="334">
+      <c r="G5" s="321">
         <v>1707356</v>
       </c>
-      <c r="H5" s="334">
+      <c r="H5" s="321">
         <v>1834224</v>
       </c>
-      <c r="I5" s="334">
+      <c r="I5" s="321">
         <v>2284817</v>
       </c>
-      <c r="J5" s="334">
+      <c r="J5" s="321">
         <v>2634028</v>
       </c>
-      <c r="K5" s="334">
+      <c r="K5" s="321">
         <v>2546147</v>
       </c>
-      <c r="L5" s="334"/>
-      <c r="M5" s="334"/>
+      <c r="L5" s="321"/>
+      <c r="M5" s="321"/>
     </row>
     <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="334">
+      <c r="C6" s="321">
         <v>796708</v>
       </c>
-      <c r="D6" s="334">
+      <c r="D6" s="321">
         <v>780002</v>
       </c>
-      <c r="E6" s="334">
+      <c r="E6" s="321">
         <v>748422</v>
       </c>
-      <c r="F6" s="334">
+      <c r="F6" s="321">
         <v>643444</v>
       </c>
-      <c r="G6" s="334">
+      <c r="G6" s="321">
         <v>489743</v>
       </c>
-      <c r="H6" s="334">
+      <c r="H6" s="321">
         <v>475518</v>
       </c>
-      <c r="I6" s="334">
+      <c r="I6" s="321">
         <v>481847</v>
       </c>
-      <c r="J6" s="334">
+      <c r="J6" s="321">
         <v>501814</v>
       </c>
-      <c r="K6" s="334">
+      <c r="K6" s="321">
         <v>531963</v>
       </c>
-      <c r="L6" s="334"/>
-      <c r="M6" s="334"/>
+      <c r="L6" s="321"/>
+      <c r="M6" s="321"/>
     </row>
     <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="335">
+      <c r="C7" s="322">
         <v>543502</v>
       </c>
-      <c r="D7" s="335">
+      <c r="D7" s="322">
         <v>527090</v>
       </c>
-      <c r="E7" s="335">
+      <c r="E7" s="322">
         <v>504718</v>
       </c>
-      <c r="F7" s="335">
+      <c r="F7" s="322">
         <v>431450</v>
       </c>
-      <c r="G7" s="335">
+      <c r="G7" s="322">
         <v>334415</v>
       </c>
-      <c r="H7" s="335">
+      <c r="H7" s="322">
         <v>197943</v>
       </c>
-      <c r="I7" s="335">
+      <c r="I7" s="322">
         <v>206424</v>
       </c>
-      <c r="J7" s="335">
+      <c r="J7" s="322">
         <v>190447</v>
       </c>
-      <c r="K7" s="335">
+      <c r="K7" s="322">
         <v>199533</v>
       </c>
-      <c r="L7" s="335"/>
-      <c r="M7" s="335"/>
+      <c r="L7" s="322"/>
+      <c r="M7" s="322"/>
     </row>
     <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="334"/>
-      <c r="D8" s="334"/>
-      <c r="E8" s="334"/>
-      <c r="F8" s="334"/>
-      <c r="G8" s="334"/>
-      <c r="H8" s="334"/>
-      <c r="I8" s="334"/>
-      <c r="J8" s="334"/>
-      <c r="K8" s="334"/>
-      <c r="L8" s="334"/>
-      <c r="M8" s="334"/>
+      <c r="C8" s="321"/>
+      <c r="D8" s="321"/>
+      <c r="E8" s="321"/>
+      <c r="F8" s="321"/>
+      <c r="G8" s="321"/>
+      <c r="H8" s="321"/>
+      <c r="I8" s="321"/>
+      <c r="J8" s="321"/>
+      <c r="K8" s="321"/>
+      <c r="L8" s="321"/>
+      <c r="M8" s="321"/>
     </row>
     <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="C9" s="334"/>
-      <c r="D9" s="334"/>
-      <c r="E9" s="334"/>
-      <c r="F9" s="334"/>
-      <c r="G9" s="334"/>
-      <c r="H9" s="334"/>
-      <c r="I9" s="334"/>
-      <c r="J9" s="334"/>
-      <c r="K9" s="334"/>
-      <c r="L9" s="334"/>
-      <c r="M9" s="334"/>
+      <c r="C9" s="321"/>
+      <c r="D9" s="321"/>
+      <c r="E9" s="321"/>
+      <c r="F9" s="321"/>
+      <c r="G9" s="321"/>
+      <c r="H9" s="321"/>
+      <c r="I9" s="321"/>
+      <c r="J9" s="321"/>
+      <c r="K9" s="321"/>
+      <c r="L9" s="321"/>
+      <c r="M9" s="321"/>
     </row>
     <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
         <v>168</v>
       </c>
-      <c r="C10" s="334"/>
-      <c r="D10" s="334"/>
-      <c r="E10" s="334"/>
-      <c r="F10" s="334"/>
-      <c r="G10" s="334"/>
-      <c r="H10" s="334"/>
-      <c r="I10" s="334"/>
-      <c r="J10" s="334"/>
-      <c r="K10" s="334"/>
-      <c r="L10" s="334"/>
-      <c r="M10" s="334"/>
+      <c r="C10" s="321"/>
+      <c r="D10" s="321"/>
+      <c r="E10" s="321"/>
+      <c r="F10" s="321"/>
+      <c r="G10" s="321"/>
+      <c r="H10" s="321"/>
+      <c r="I10" s="321"/>
+      <c r="J10" s="321"/>
+      <c r="K10" s="321"/>
+      <c r="L10" s="321"/>
+      <c r="M10" s="321"/>
     </row>
     <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
         <v>159</v>
       </c>
-      <c r="C11" s="334"/>
-      <c r="D11" s="334"/>
-      <c r="E11" s="334"/>
-      <c r="F11" s="334"/>
-      <c r="G11" s="334"/>
-      <c r="H11" s="334"/>
-      <c r="I11" s="334"/>
-      <c r="J11" s="334"/>
-      <c r="K11" s="334"/>
-      <c r="L11" s="334"/>
-      <c r="M11" s="334"/>
+      <c r="C11" s="321"/>
+      <c r="D11" s="321"/>
+      <c r="E11" s="321"/>
+      <c r="F11" s="321"/>
+      <c r="G11" s="321"/>
+      <c r="H11" s="321"/>
+      <c r="I11" s="321"/>
+      <c r="J11" s="321"/>
+      <c r="K11" s="321"/>
+      <c r="L11" s="321"/>
+      <c r="M11" s="321"/>
     </row>
     <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="334">
+      <c r="C12" s="321">
         <v>13663</v>
       </c>
-      <c r="D12" s="334">
+      <c r="D12" s="321">
         <v>14612</v>
       </c>
-      <c r="E12" s="334">
+      <c r="E12" s="321">
         <v>12033</v>
       </c>
-      <c r="F12" s="334">
+      <c r="F12" s="321">
         <v>10203</v>
       </c>
-      <c r="G12" s="334">
+      <c r="G12" s="321">
         <v>14210</v>
       </c>
-      <c r="H12" s="334">
+      <c r="H12" s="321">
         <v>1959</v>
       </c>
-      <c r="I12" s="334">
+      <c r="I12" s="321">
         <v>1843</v>
       </c>
-      <c r="J12" s="334">
+      <c r="J12" s="321">
         <v>3730</v>
       </c>
-      <c r="K12" s="334">
+      <c r="K12" s="321">
         <v>6942</v>
       </c>
-      <c r="L12" s="334"/>
-      <c r="M12" s="334"/>
+      <c r="L12" s="321"/>
+      <c r="M12" s="321"/>
     </row>
     <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="334"/>
-      <c r="D13" s="334"/>
-      <c r="E13" s="334"/>
-      <c r="F13" s="334"/>
-      <c r="G13" s="334"/>
-      <c r="H13" s="334"/>
-      <c r="I13" s="334"/>
-      <c r="J13" s="334"/>
-      <c r="K13" s="334"/>
-      <c r="L13" s="334"/>
-      <c r="M13" s="334"/>
+      <c r="C13" s="321"/>
+      <c r="D13" s="321"/>
+      <c r="E13" s="321"/>
+      <c r="F13" s="321"/>
+      <c r="G13" s="321"/>
+      <c r="H13" s="321"/>
+      <c r="I13" s="321"/>
+      <c r="J13" s="321"/>
+      <c r="K13" s="321"/>
+      <c r="L13" s="321"/>
+      <c r="M13" s="321"/>
     </row>
     <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="334">
+      <c r="C14" s="321">
         <v>145324</v>
       </c>
-      <c r="D14" s="334">
+      <c r="D14" s="321">
         <v>144534</v>
       </c>
-      <c r="E14" s="334">
+      <c r="E14" s="321">
         <v>150461</v>
       </c>
-      <c r="F14" s="334">
+      <c r="F14" s="321">
         <v>123112</v>
       </c>
-      <c r="G14" s="334">
+      <c r="G14" s="321">
         <v>28324</v>
       </c>
-      <c r="H14" s="334">
+      <c r="H14" s="321">
         <v>21936</v>
       </c>
-      <c r="I14" s="334">
+      <c r="I14" s="321">
         <v>26006</v>
       </c>
-      <c r="J14" s="334">
+      <c r="J14" s="321">
         <v>9352</v>
       </c>
-      <c r="K14" s="334">
+      <c r="K14" s="321">
         <v>3042</v>
       </c>
-      <c r="L14" s="334"/>
-      <c r="M14" s="334"/>
+      <c r="L14" s="321"/>
+      <c r="M14" s="321"/>
     </row>
     <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="336">
+      <c r="C15" s="323">
         <v>251150</v>
       </c>
-      <c r="D15" s="336">
+      <c r="D15" s="323">
         <v>295524</v>
       </c>
-      <c r="E15" s="336">
+      <c r="E15" s="323">
         <v>362976</v>
       </c>
-      <c r="F15" s="336">
+      <c r="F15" s="323">
         <v>232624</v>
       </c>
-      <c r="G15" s="336">
+      <c r="G15" s="323">
         <v>99109</v>
       </c>
-      <c r="H15" s="336">
+      <c r="H15" s="323">
         <v>138039</v>
       </c>
-      <c r="I15" s="336">
+      <c r="I15" s="323">
         <v>138685</v>
       </c>
-      <c r="J15" s="336">
+      <c r="J15" s="323">
         <v>16097</v>
       </c>
-      <c r="K15" s="336">
+      <c r="K15" s="323">
         <v>-15759</v>
       </c>
-      <c r="L15" s="336"/>
-      <c r="M15" s="336"/>
+      <c r="L15" s="323"/>
+      <c r="M15" s="323"/>
     </row>
     <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="334">
+      <c r="C16" s="321">
         <v>662</v>
       </c>
-      <c r="D16" s="334">
+      <c r="D16" s="321">
         <v>92</v>
       </c>
-      <c r="E16" s="334">
+      <c r="E16" s="321">
         <v>402</v>
       </c>
-      <c r="F16" s="334">
+      <c r="F16" s="321">
         <v>-632</v>
       </c>
-      <c r="G16" s="334">
+      <c r="G16" s="321">
         <v>-1192</v>
       </c>
-      <c r="H16" s="334">
+      <c r="H16" s="321">
         <v>-60</v>
       </c>
-      <c r="I16" s="334">
+      <c r="I16" s="321">
         <v>-78</v>
       </c>
-      <c r="J16" s="334">
+      <c r="J16" s="321">
         <v>-286</v>
       </c>
-      <c r="K16" s="334">
+      <c r="K16" s="321">
         <v>-231</v>
       </c>
-      <c r="L16" s="334"/>
-      <c r="M16" s="334"/>
+      <c r="L16" s="321"/>
+      <c r="M16" s="321"/>
     </row>
     <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
@@ -6372,151 +6388,151 @@
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="334"/>
-      <c r="D19" s="334"/>
-      <c r="E19" s="334"/>
-      <c r="F19" s="334"/>
-      <c r="G19" s="334"/>
-      <c r="H19" s="334"/>
-      <c r="I19" s="334"/>
-      <c r="J19" s="334"/>
-      <c r="K19" s="334"/>
-      <c r="L19" s="334"/>
-      <c r="M19" s="334"/>
+      <c r="C19" s="321"/>
+      <c r="D19" s="321"/>
+      <c r="E19" s="321"/>
+      <c r="F19" s="321"/>
+      <c r="G19" s="321"/>
+      <c r="H19" s="321"/>
+      <c r="I19" s="321"/>
+      <c r="J19" s="321"/>
+      <c r="K19" s="321"/>
+      <c r="L19" s="321"/>
+      <c r="M19" s="321"/>
     </row>
     <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C20" s="334"/>
-      <c r="D20" s="334"/>
-      <c r="E20" s="334"/>
-      <c r="F20" s="334"/>
-      <c r="G20" s="334"/>
-      <c r="H20" s="334"/>
-      <c r="I20" s="334"/>
-      <c r="J20" s="334"/>
-      <c r="K20" s="334"/>
-      <c r="L20" s="334"/>
-      <c r="M20" s="334"/>
+      <c r="C20" s="321"/>
+      <c r="D20" s="321"/>
+      <c r="E20" s="321"/>
+      <c r="F20" s="321"/>
+      <c r="G20" s="321"/>
+      <c r="H20" s="321"/>
+      <c r="I20" s="321"/>
+      <c r="J20" s="321"/>
+      <c r="K20" s="321"/>
+      <c r="L20" s="321"/>
+      <c r="M20" s="321"/>
     </row>
     <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="334"/>
-      <c r="D21" s="334"/>
-      <c r="E21" s="334"/>
-      <c r="F21" s="334"/>
-      <c r="G21" s="334"/>
-      <c r="H21" s="334"/>
-      <c r="I21" s="334"/>
-      <c r="J21" s="334"/>
-      <c r="K21" s="334"/>
-      <c r="L21" s="334"/>
-      <c r="M21" s="334"/>
+      <c r="C21" s="321"/>
+      <c r="D21" s="321"/>
+      <c r="E21" s="321"/>
+      <c r="F21" s="321"/>
+      <c r="G21" s="321"/>
+      <c r="H21" s="321"/>
+      <c r="I21" s="321"/>
+      <c r="J21" s="321"/>
+      <c r="K21" s="321"/>
+      <c r="L21" s="321"/>
+      <c r="M21" s="321"/>
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
         <v>372</v>
       </c>
-      <c r="C22" s="334">
+      <c r="C22" s="321">
         <v>346987</v>
       </c>
-      <c r="D22" s="334">
+      <c r="D22" s="321">
         <v>421974</v>
       </c>
-      <c r="E22" s="334">
+      <c r="E22" s="321">
         <v>732665</v>
       </c>
-      <c r="F22" s="334">
+      <c r="F22" s="321">
         <v>643498</v>
       </c>
-      <c r="G22" s="334">
+      <c r="G22" s="321">
         <v>306436</v>
       </c>
-      <c r="H22" s="334">
+      <c r="H22" s="321">
         <v>269780</v>
       </c>
-      <c r="I22" s="334">
+      <c r="I22" s="321">
         <v>503072</v>
       </c>
-      <c r="J22" s="334">
+      <c r="J22" s="321">
         <v>266577</v>
       </c>
-      <c r="K22" s="334">
+      <c r="K22" s="321">
         <v>204101</v>
       </c>
-      <c r="L22" s="334"/>
-      <c r="M22" s="334"/>
+      <c r="L22" s="321"/>
+      <c r="M22" s="321"/>
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
         <v>374</v>
       </c>
-      <c r="C23" s="334">
+      <c r="C23" s="321">
         <v>-67837</v>
       </c>
-      <c r="D23" s="334">
+      <c r="D23" s="321">
         <v>-37092</v>
       </c>
-      <c r="E23" s="334">
+      <c r="E23" s="321">
         <v>-77565</v>
       </c>
-      <c r="F23" s="334">
+      <c r="F23" s="321">
         <v>-47993</v>
       </c>
-      <c r="G23" s="334">
+      <c r="G23" s="321">
         <v>-48419</v>
       </c>
-      <c r="H23" s="334">
+      <c r="H23" s="321">
         <v>-39236</v>
       </c>
-      <c r="I23" s="334">
+      <c r="I23" s="321">
         <v>-17998</v>
       </c>
-      <c r="J23" s="334">
+      <c r="J23" s="321">
         <v>89956</v>
       </c>
-      <c r="K23" s="334">
+      <c r="K23" s="321">
         <v>-13332</v>
       </c>
-      <c r="L23" s="334"/>
-      <c r="M23" s="334"/>
+      <c r="L23" s="321"/>
+      <c r="M23" s="321"/>
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
         <v>373</v>
       </c>
-      <c r="C24" s="334">
+      <c r="C24" s="321">
         <v>-423459</v>
       </c>
-      <c r="D24" s="334">
+      <c r="D24" s="321">
         <v>-530752</v>
       </c>
-      <c r="E24" s="334">
+      <c r="E24" s="321">
         <v>-458369</v>
       </c>
-      <c r="F24" s="334">
+      <c r="F24" s="321">
         <v>-497885</v>
       </c>
-      <c r="G24" s="334">
+      <c r="G24" s="321">
         <v>-381840</v>
       </c>
-      <c r="H24" s="334">
+      <c r="H24" s="321">
         <v>-209528</v>
       </c>
-      <c r="I24" s="334">
+      <c r="I24" s="321">
         <v>-69431</v>
       </c>
-      <c r="J24" s="334">
+      <c r="J24" s="321">
         <v>-114101</v>
       </c>
-      <c r="K24" s="334">
+      <c r="K24" s="321">
         <v>-126118</v>
       </c>
-      <c r="L24" s="334"/>
-      <c r="M24" s="334"/>
+      <c r="L24" s="321"/>
+      <c r="M24" s="321"/>
     </row>
     <row r="25" spans="2:13">
       <c r="B25" s="24" t="str">
@@ -6559,176 +6575,176 @@
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="323">
+      <c r="C28" s="318">
         <f>BS!C4</f>
         <v>348607</v>
       </c>
-      <c r="D28" s="334">
+      <c r="D28" s="321">
         <v>262508</v>
       </c>
-      <c r="E28" s="334">
+      <c r="E28" s="321">
         <v>179615</v>
       </c>
-      <c r="F28" s="334">
+      <c r="F28" s="321">
         <v>260527</v>
       </c>
-      <c r="G28" s="334">
+      <c r="G28" s="321">
         <v>80876</v>
       </c>
-      <c r="H28" s="334">
+      <c r="H28" s="321">
         <v>86046</v>
       </c>
-      <c r="I28" s="334">
+      <c r="I28" s="321">
         <v>108938</v>
       </c>
-      <c r="J28" s="334">
+      <c r="J28" s="321">
         <v>91351</v>
       </c>
-      <c r="K28" s="334">
+      <c r="K28" s="321">
         <v>88852</v>
       </c>
-      <c r="L28" s="334"/>
-      <c r="M28" s="334"/>
+      <c r="L28" s="321"/>
+      <c r="M28" s="321"/>
     </row>
     <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="323">
+      <c r="C29" s="318">
         <f>BS!C6</f>
         <v>506592</v>
       </c>
-      <c r="D29" s="334">
+      <c r="D29" s="321">
         <v>422202</v>
       </c>
-      <c r="E29" s="334">
+      <c r="E29" s="321">
         <v>483625</v>
       </c>
-      <c r="F29" s="334">
+      <c r="F29" s="321">
         <v>622768</v>
       </c>
-      <c r="G29" s="334">
+      <c r="G29" s="321">
         <v>798693</v>
       </c>
-      <c r="H29" s="334">
+      <c r="H29" s="321">
         <v>823654</v>
       </c>
-      <c r="I29" s="334">
+      <c r="I29" s="321">
         <v>1001069</v>
       </c>
-      <c r="J29" s="334">
+      <c r="J29" s="321">
         <v>1275897</v>
       </c>
-      <c r="K29" s="334">
+      <c r="K29" s="321">
         <v>1569528</v>
       </c>
-      <c r="L29" s="334"/>
-      <c r="M29" s="334"/>
+      <c r="L29" s="321"/>
+      <c r="M29" s="321"/>
     </row>
     <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="C30" s="324">
+      <c r="C30" s="319">
         <f>BS!C33+BS!C42</f>
         <v>732882</v>
       </c>
-      <c r="D30" s="336">
+      <c r="D30" s="323">
         <v>723327</v>
       </c>
-      <c r="E30" s="336">
+      <c r="E30" s="323">
         <v>843108</v>
       </c>
-      <c r="F30" s="336">
+      <c r="F30" s="323">
         <v>736981</v>
       </c>
-      <c r="G30" s="336">
+      <c r="G30" s="323">
         <v>430335</v>
       </c>
-      <c r="H30" s="336">
+      <c r="H30" s="323">
         <v>194628</v>
       </c>
-      <c r="I30" s="336">
+      <c r="I30" s="323">
         <v>222985</v>
       </c>
-      <c r="J30" s="336">
+      <c r="J30" s="323">
         <v>207724</v>
       </c>
-      <c r="K30" s="336">
+      <c r="K30" s="323">
         <v>376010</v>
       </c>
-      <c r="L30" s="336"/>
-      <c r="M30" s="336"/>
+      <c r="L30" s="323"/>
+      <c r="M30" s="323"/>
     </row>
     <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="324">
+      <c r="C31" s="319">
         <f>BS!G27</f>
         <v>1832181</v>
       </c>
-      <c r="D31" s="336">
+      <c r="D31" s="323">
         <v>1895931</v>
       </c>
-      <c r="E31" s="336">
+      <c r="E31" s="323">
         <v>2036167</v>
       </c>
-      <c r="F31" s="336">
+      <c r="F31" s="323">
         <v>1990549</v>
       </c>
-      <c r="G31" s="336">
+      <c r="G31" s="323">
         <v>2083286</v>
       </c>
-      <c r="H31" s="336">
+      <c r="H31" s="323">
         <v>2213601</v>
       </c>
-      <c r="I31" s="336">
+      <c r="I31" s="323">
         <v>2316952</v>
       </c>
-      <c r="J31" s="336">
+      <c r="J31" s="323">
         <v>2147014</v>
       </c>
-      <c r="K31" s="336">
+      <c r="K31" s="323">
         <v>2157572</v>
       </c>
-      <c r="L31" s="336"/>
-      <c r="M31" s="336"/>
+      <c r="L31" s="323"/>
+      <c r="M31" s="323"/>
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="C32" s="323">
+      <c r="C32" s="318">
         <f>BS!G28</f>
         <v>1765</v>
       </c>
-      <c r="D32" s="334">
+      <c r="D32" s="321">
         <v>1186</v>
       </c>
-      <c r="E32" s="334">
+      <c r="E32" s="321">
         <v>1160</v>
       </c>
-      <c r="F32" s="334">
+      <c r="F32" s="321">
         <v>-946</v>
       </c>
-      <c r="G32" s="334">
+      <c r="G32" s="321">
         <v>-325</v>
       </c>
-      <c r="H32" s="334">
+      <c r="H32" s="321">
         <v>868</v>
       </c>
-      <c r="I32" s="334">
+      <c r="I32" s="321">
         <v>975</v>
       </c>
-      <c r="J32" s="334">
+      <c r="J32" s="321">
         <v>1008</v>
       </c>
-      <c r="K32" s="334">
+      <c r="K32" s="321">
         <v>1054</v>
       </c>
-      <c r="L32" s="334"/>
-      <c r="M32" s="334"/>
+      <c r="L32" s="321"/>
+      <c r="M32" s="321"/>
     </row>
     <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
@@ -6755,47 +6771,47 @@
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C36" s="323">
+      <c r="C36" s="318">
         <f t="shared" ref="C36:M36" si="1">IF(C$4="","",C4)</f>
         <v>3638758</v>
       </c>
-      <c r="D36" s="323">
+      <c r="D36" s="318">
         <f t="shared" si="1"/>
         <v>3704677</v>
       </c>
-      <c r="E36" s="323">
+      <c r="E36" s="318">
         <f t="shared" si="1"/>
         <v>3639774</v>
       </c>
-      <c r="F36" s="323">
+      <c r="F36" s="318">
         <f t="shared" si="1"/>
         <v>3504022</v>
       </c>
-      <c r="G36" s="323">
+      <c r="G36" s="318">
         <f t="shared" si="1"/>
         <v>2352683</v>
       </c>
-      <c r="H36" s="323">
+      <c r="H36" s="318">
         <f t="shared" si="1"/>
         <v>2437184</v>
       </c>
-      <c r="I36" s="323">
+      <c r="I36" s="318">
         <f t="shared" si="1"/>
         <v>2891692</v>
       </c>
-      <c r="J36" s="323">
+      <c r="J36" s="318">
         <f t="shared" si="1"/>
         <v>3142295</v>
       </c>
-      <c r="K36" s="323">
+      <c r="K36" s="318">
         <f t="shared" si="1"/>
         <v>3031752</v>
       </c>
-      <c r="L36" s="323" t="str">
+      <c r="L36" s="318" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="M36" s="323" t="str">
+      <c r="M36" s="318" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -6804,47 +6820,47 @@
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="C37" s="323">
+      <c r="C37" s="318">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
         <v>-2488028</v>
       </c>
-      <c r="D37" s="323">
+      <c r="D37" s="318">
         <f t="shared" si="2"/>
         <v>-2515967</v>
       </c>
-      <c r="E37" s="323">
+      <c r="E37" s="318">
         <f t="shared" si="2"/>
         <v>-2459489</v>
       </c>
-      <c r="F37" s="323">
+      <c r="F37" s="318">
         <f t="shared" si="2"/>
         <v>-2541906</v>
       </c>
-      <c r="G37" s="323">
+      <c r="G37" s="318">
         <f t="shared" si="2"/>
         <v>-1707356</v>
       </c>
-      <c r="H37" s="323">
+      <c r="H37" s="318">
         <f t="shared" si="2"/>
         <v>-1834224</v>
       </c>
-      <c r="I37" s="323">
+      <c r="I37" s="318">
         <f t="shared" si="2"/>
         <v>-2284817</v>
       </c>
-      <c r="J37" s="323">
+      <c r="J37" s="318">
         <f t="shared" si="2"/>
         <v>-2634028</v>
       </c>
-      <c r="K37" s="323">
+      <c r="K37" s="318">
         <f t="shared" si="2"/>
         <v>-2546147</v>
       </c>
-      <c r="L37" s="323" t="str">
+      <c r="L37" s="318" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="M37" s="323" t="str">
+      <c r="M37" s="318" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -6853,47 +6869,47 @@
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="C38" s="319">
+      <c r="C38" s="317">
         <f>IF(C36="","",C36+C37)</f>
         <v>1150730</v>
       </c>
-      <c r="D38" s="319">
+      <c r="D38" s="317">
         <f t="shared" ref="D38" si="3">IF(D36="","",D36+D37)</f>
         <v>1188710</v>
       </c>
-      <c r="E38" s="319">
+      <c r="E38" s="317">
         <f t="shared" ref="E38" si="4">IF(E36="","",E36+E37)</f>
         <v>1180285</v>
       </c>
-      <c r="F38" s="319">
+      <c r="F38" s="317">
         <f t="shared" ref="F38" si="5">IF(F36="","",F36+F37)</f>
         <v>962116</v>
       </c>
-      <c r="G38" s="319">
+      <c r="G38" s="317">
         <f t="shared" ref="G38" si="6">IF(G36="","",G36+G37)</f>
         <v>645327</v>
       </c>
-      <c r="H38" s="319">
+      <c r="H38" s="317">
         <f t="shared" ref="H38" si="7">IF(H36="","",H36+H37)</f>
         <v>602960</v>
       </c>
-      <c r="I38" s="319">
+      <c r="I38" s="317">
         <f t="shared" ref="I38" si="8">IF(I36="","",I36+I37)</f>
         <v>606875</v>
       </c>
-      <c r="J38" s="319">
+      <c r="J38" s="317">
         <f t="shared" ref="J38" si="9">IF(J36="","",J36+J37)</f>
         <v>508267</v>
       </c>
-      <c r="K38" s="319">
+      <c r="K38" s="317">
         <f t="shared" ref="K38" si="10">IF(K36="","",K36+K37)</f>
         <v>485605</v>
       </c>
-      <c r="L38" s="319" t="str">
+      <c r="L38" s="317" t="str">
         <f t="shared" ref="L38" si="11">IF(L36="","",L36+L37)</f>
         <v/>
       </c>
-      <c r="M38" s="319" t="str">
+      <c r="M38" s="317" t="str">
         <f t="shared" ref="M38" si="12">IF(M36="","",M36+M37)</f>
         <v/>
       </c>
@@ -6902,47 +6918,47 @@
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C39" s="323">
+      <c r="C39" s="318">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
         <v>-796708</v>
       </c>
-      <c r="D39" s="323">
+      <c r="D39" s="318">
         <f t="shared" si="13"/>
         <v>-780002</v>
       </c>
-      <c r="E39" s="323">
+      <c r="E39" s="318">
         <f t="shared" si="13"/>
         <v>-748422</v>
       </c>
-      <c r="F39" s="323">
+      <c r="F39" s="318">
         <f t="shared" si="13"/>
         <v>-643444</v>
       </c>
-      <c r="G39" s="323">
+      <c r="G39" s="318">
         <f t="shared" si="13"/>
         <v>-489743</v>
       </c>
-      <c r="H39" s="323">
+      <c r="H39" s="318">
         <f t="shared" si="13"/>
         <v>-475518</v>
       </c>
-      <c r="I39" s="323">
+      <c r="I39" s="318">
         <f t="shared" si="13"/>
         <v>-481847</v>
       </c>
-      <c r="J39" s="323">
+      <c r="J39" s="318">
         <f t="shared" si="13"/>
         <v>-501814</v>
       </c>
-      <c r="K39" s="323">
+      <c r="K39" s="318">
         <f t="shared" si="13"/>
         <v>-531963</v>
       </c>
-      <c r="L39" s="323" t="str">
+      <c r="L39" s="318" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="M39" s="323" t="str">
+      <c r="M39" s="318" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -6951,47 +6967,47 @@
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="C40" s="333">
+      <c r="C40" s="320">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
         <v>-543502</v>
       </c>
-      <c r="D40" s="333">
+      <c r="D40" s="320">
         <f t="shared" si="14"/>
         <v>-527090</v>
       </c>
-      <c r="E40" s="333">
+      <c r="E40" s="320">
         <f t="shared" si="14"/>
         <v>-504718</v>
       </c>
-      <c r="F40" s="333">
+      <c r="F40" s="320">
         <f t="shared" si="14"/>
         <v>-431450</v>
       </c>
-      <c r="G40" s="333">
+      <c r="G40" s="320">
         <f t="shared" si="14"/>
         <v>-334415</v>
       </c>
-      <c r="H40" s="333">
+      <c r="H40" s="320">
         <f t="shared" si="14"/>
         <v>-197943</v>
       </c>
-      <c r="I40" s="333">
+      <c r="I40" s="320">
         <f t="shared" si="14"/>
         <v>-206424</v>
       </c>
-      <c r="J40" s="333">
+      <c r="J40" s="320">
         <f t="shared" si="14"/>
         <v>-190447</v>
       </c>
-      <c r="K40" s="333">
+      <c r="K40" s="320">
         <f t="shared" si="14"/>
         <v>-199533</v>
       </c>
-      <c r="L40" s="333" t="str">
+      <c r="L40" s="320" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="M40" s="333" t="str">
+      <c r="M40" s="320" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
@@ -7000,47 +7016,47 @@
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="C41" s="333">
+      <c r="C41" s="320">
         <f>IF(C$4="","",C39-C40)</f>
         <v>-253206</v>
       </c>
-      <c r="D41" s="333">
+      <c r="D41" s="320">
         <f t="shared" ref="D41:M41" si="15">IF(D$4="","",D39-D40)</f>
         <v>-252912</v>
       </c>
-      <c r="E41" s="333">
+      <c r="E41" s="320">
         <f t="shared" si="15"/>
         <v>-243704</v>
       </c>
-      <c r="F41" s="333">
+      <c r="F41" s="320">
         <f t="shared" si="15"/>
         <v>-211994</v>
       </c>
-      <c r="G41" s="333">
+      <c r="G41" s="320">
         <f t="shared" si="15"/>
         <v>-155328</v>
       </c>
-      <c r="H41" s="333">
+      <c r="H41" s="320">
         <f t="shared" si="15"/>
         <v>-277575</v>
       </c>
-      <c r="I41" s="333">
+      <c r="I41" s="320">
         <f t="shared" si="15"/>
         <v>-275423</v>
       </c>
-      <c r="J41" s="333">
+      <c r="J41" s="320">
         <f t="shared" si="15"/>
         <v>-311367</v>
       </c>
-      <c r="K41" s="333">
+      <c r="K41" s="320">
         <f t="shared" si="15"/>
         <v>-332430</v>
       </c>
-      <c r="L41" s="333" t="str">
+      <c r="L41" s="320" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="M41" s="333" t="str">
+      <c r="M41" s="320" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
@@ -7049,47 +7065,47 @@
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="C42" s="323">
+      <c r="C42" s="318">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
         <v>0</v>
       </c>
-      <c r="D42" s="323">
+      <c r="D42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="E42" s="323">
+      <c r="E42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="F42" s="323">
+      <c r="F42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="G42" s="323">
+      <c r="G42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="H42" s="323">
+      <c r="H42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="I42" s="323">
+      <c r="I42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="J42" s="323">
+      <c r="J42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="K42" s="323">
+      <c r="K42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="L42" s="323" t="str">
+      <c r="L42" s="318" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="M42" s="323" t="str">
+      <c r="M42" s="318" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
@@ -7098,47 +7114,47 @@
       <c r="B43" s="43" t="s">
         <v>153</v>
       </c>
-      <c r="C43" s="324">
+      <c r="C43" s="319">
         <f>IF(C$4="","",C38+C39+C42)</f>
         <v>354022</v>
       </c>
-      <c r="D43" s="324">
+      <c r="D43" s="319">
         <f t="shared" ref="D43:M43" si="17">IF(D$4="","",D38+D39+D42)</f>
         <v>408708</v>
       </c>
-      <c r="E43" s="324">
+      <c r="E43" s="319">
         <f t="shared" si="17"/>
         <v>431863</v>
       </c>
-      <c r="F43" s="324">
+      <c r="F43" s="319">
         <f t="shared" si="17"/>
         <v>318672</v>
       </c>
-      <c r="G43" s="324">
+      <c r="G43" s="319">
         <f t="shared" si="17"/>
         <v>155584</v>
       </c>
-      <c r="H43" s="324">
+      <c r="H43" s="319">
         <f t="shared" si="17"/>
         <v>127442</v>
       </c>
-      <c r="I43" s="324">
+      <c r="I43" s="319">
         <f t="shared" si="17"/>
         <v>125028</v>
       </c>
-      <c r="J43" s="324">
+      <c r="J43" s="319">
         <f t="shared" si="17"/>
         <v>6453</v>
       </c>
-      <c r="K43" s="324">
+      <c r="K43" s="319">
         <f t="shared" si="17"/>
         <v>-46358</v>
       </c>
-      <c r="L43" s="324" t="str">
+      <c r="L43" s="319" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="M43" s="324" t="str">
+      <c r="M43" s="319" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
@@ -7245,47 +7261,47 @@
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="C46" s="323">
+      <c r="C46" s="318">
         <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
         <v>-145324</v>
       </c>
-      <c r="D46" s="323">
+      <c r="D46" s="318">
         <f t="shared" si="20"/>
         <v>-144534</v>
       </c>
-      <c r="E46" s="323">
+      <c r="E46" s="318">
         <f t="shared" si="20"/>
         <v>-150461</v>
       </c>
-      <c r="F46" s="323">
+      <c r="F46" s="318">
         <f t="shared" si="20"/>
         <v>-123112</v>
       </c>
-      <c r="G46" s="323">
+      <c r="G46" s="318">
         <f t="shared" si="20"/>
         <v>-28324</v>
       </c>
-      <c r="H46" s="323">
+      <c r="H46" s="318">
         <f t="shared" si="20"/>
         <v>-21936</v>
       </c>
-      <c r="I46" s="323">
+      <c r="I46" s="318">
         <f t="shared" si="20"/>
         <v>-26006</v>
       </c>
-      <c r="J46" s="323">
+      <c r="J46" s="318">
         <f t="shared" si="20"/>
         <v>-9352</v>
       </c>
-      <c r="K46" s="323">
+      <c r="K46" s="318">
         <f t="shared" si="20"/>
         <v>-3042</v>
       </c>
-      <c r="L46" s="323" t="str">
+      <c r="L46" s="318" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="M46" s="323" t="str">
+      <c r="M46" s="318" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
@@ -7294,47 +7310,47 @@
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="C47" s="324">
+      <c r="C47" s="319">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
         <v>251150</v>
       </c>
-      <c r="D47" s="324">
+      <c r="D47" s="319">
         <f t="shared" si="21"/>
         <v>295524</v>
       </c>
-      <c r="E47" s="324">
+      <c r="E47" s="319">
         <f t="shared" si="21"/>
         <v>362976</v>
       </c>
-      <c r="F47" s="324">
+      <c r="F47" s="319">
         <f t="shared" si="21"/>
         <v>232624</v>
       </c>
-      <c r="G47" s="324">
+      <c r="G47" s="319">
         <f t="shared" si="21"/>
         <v>99109</v>
       </c>
-      <c r="H47" s="324">
+      <c r="H47" s="319">
         <f t="shared" si="21"/>
         <v>138039</v>
       </c>
-      <c r="I47" s="324">
+      <c r="I47" s="319">
         <f t="shared" si="21"/>
         <v>138685</v>
       </c>
-      <c r="J47" s="324">
+      <c r="J47" s="319">
         <f t="shared" si="21"/>
         <v>16097</v>
       </c>
-      <c r="K47" s="324">
+      <c r="K47" s="319">
         <f t="shared" si="21"/>
         <v>-15759</v>
       </c>
-      <c r="L47" s="324" t="str">
+      <c r="L47" s="319" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="M47" s="324" t="str">
+      <c r="M47" s="319" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
@@ -7343,47 +7359,47 @@
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="C48" s="323">
+      <c r="C48" s="318">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
         <v>-662</v>
       </c>
-      <c r="D48" s="323">
+      <c r="D48" s="318">
         <f t="shared" si="22"/>
         <v>-92</v>
       </c>
-      <c r="E48" s="323">
+      <c r="E48" s="318">
         <f t="shared" si="22"/>
         <v>-402</v>
       </c>
-      <c r="F48" s="323">
+      <c r="F48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="G48" s="323">
+      <c r="G48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="H48" s="323">
+      <c r="H48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="I48" s="323">
+      <c r="I48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="J48" s="323">
+      <c r="J48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="K48" s="323">
+      <c r="K48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="L48" s="323" t="str">
+      <c r="L48" s="318" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="M48" s="323" t="str">
+      <c r="M48" s="318" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -7397,47 +7413,47 @@
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="C51" s="323">
+      <c r="C51" s="318">
         <f t="shared" ref="C51:M51" si="23">IF(C$4="","",-C12)</f>
         <v>-13663</v>
       </c>
-      <c r="D51" s="323">
+      <c r="D51" s="318">
         <f t="shared" si="23"/>
         <v>-14612</v>
       </c>
-      <c r="E51" s="323">
+      <c r="E51" s="318">
         <f t="shared" si="23"/>
         <v>-12033</v>
       </c>
-      <c r="F51" s="323">
+      <c r="F51" s="318">
         <f t="shared" si="23"/>
         <v>-10203</v>
       </c>
-      <c r="G51" s="323">
+      <c r="G51" s="318">
         <f t="shared" si="23"/>
         <v>-14210</v>
       </c>
-      <c r="H51" s="323">
+      <c r="H51" s="318">
         <f t="shared" si="23"/>
         <v>-1959</v>
       </c>
-      <c r="I51" s="323">
+      <c r="I51" s="318">
         <f t="shared" si="23"/>
         <v>-1843</v>
       </c>
-      <c r="J51" s="323">
+      <c r="J51" s="318">
         <f t="shared" si="23"/>
         <v>-3730</v>
       </c>
-      <c r="K51" s="323">
+      <c r="K51" s="318">
         <f t="shared" si="23"/>
         <v>-6942</v>
       </c>
-      <c r="L51" s="323" t="str">
+      <c r="L51" s="318" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="M51" s="323" t="str">
+      <c r="M51" s="318" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
@@ -7446,47 +7462,47 @@
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="C52" s="323">
+      <c r="C52" s="318">
         <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
         <v>0</v>
       </c>
-      <c r="D52" s="323">
+      <c r="D52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="E52" s="323">
+      <c r="E52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="F52" s="323">
+      <c r="F52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="G52" s="323">
+      <c r="G52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="H52" s="323">
+      <c r="H52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="I52" s="323">
+      <c r="I52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="J52" s="323">
+      <c r="J52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="K52" s="323">
+      <c r="K52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="L52" s="323" t="str">
+      <c r="L52" s="318" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="M52" s="323" t="str">
+      <c r="M52" s="318" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
@@ -7702,47 +7718,47 @@
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="C61" s="323">
+      <c r="C61" s="318">
         <f>IF(C$4="","",-C19)</f>
         <v>0</v>
       </c>
-      <c r="D61" s="323">
+      <c r="D61" s="318">
         <f t="shared" ref="D61:M61" si="29">IF(D$4="","",-D19)</f>
         <v>0</v>
       </c>
-      <c r="E61" s="323">
+      <c r="E61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="F61" s="323">
+      <c r="F61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="G61" s="323">
+      <c r="G61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="H61" s="323">
+      <c r="H61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="I61" s="323">
+      <c r="I61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="J61" s="323">
+      <c r="J61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="K61" s="323">
+      <c r="K61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="L61" s="323" t="str">
+      <c r="L61" s="318" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
-      <c r="M61" s="323" t="str">
+      <c r="M61" s="318" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
@@ -7751,47 +7767,47 @@
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C62" s="323">
+      <c r="C62" s="318">
         <f>IF(C$4="","",IF(C20=0,C61,-C20))</f>
         <v>0</v>
       </c>
-      <c r="D62" s="323">
+      <c r="D62" s="318">
         <f t="shared" ref="D62:M62" si="30">IF(D$4="","",IF(D20=0,D61,-D20))</f>
         <v>0</v>
       </c>
-      <c r="E62" s="323">
+      <c r="E62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="F62" s="323">
+      <c r="F62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="G62" s="323">
+      <c r="G62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="H62" s="323">
+      <c r="H62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="I62" s="323">
+      <c r="I62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="J62" s="323">
+      <c r="J62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="K62" s="323">
+      <c r="K62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="L62" s="323" t="str">
+      <c r="L62" s="318" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
-      <c r="M62" s="323" t="str">
+      <c r="M62" s="318" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
@@ -7800,47 +7816,47 @@
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C63" s="323">
+      <c r="C63" s="318">
         <f>IF(C$4="","",-C21)</f>
         <v>0</v>
       </c>
-      <c r="D63" s="323">
+      <c r="D63" s="318">
         <f t="shared" ref="D63:M63" si="31">IF(D$4="","",-D21)</f>
         <v>0</v>
       </c>
-      <c r="E63" s="323">
+      <c r="E63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="F63" s="323">
+      <c r="F63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="G63" s="323">
+      <c r="G63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="H63" s="323">
+      <c r="H63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="I63" s="323">
+      <c r="I63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="J63" s="323">
+      <c r="J63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="K63" s="323">
+      <c r="K63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="L63" s="323" t="str">
+      <c r="L63" s="318" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
-      <c r="M63" s="323" t="str">
+      <c r="M63" s="318" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
@@ -7849,47 +7865,47 @@
       <c r="B64" s="27" t="s">
         <v>394</v>
       </c>
-      <c r="C64" s="323">
+      <c r="C64" s="318">
         <f>IF(C$4="","",C22+C23+C24)</f>
         <v>-144309</v>
       </c>
-      <c r="D64" s="323">
+      <c r="D64" s="318">
         <f t="shared" ref="D64:M64" si="32">IF(D$4="","",D22+D23+D24)</f>
         <v>-145870</v>
       </c>
-      <c r="E64" s="323">
+      <c r="E64" s="318">
         <f t="shared" si="32"/>
         <v>196731</v>
       </c>
-      <c r="F64" s="323">
+      <c r="F64" s="318">
         <f t="shared" si="32"/>
         <v>97620</v>
       </c>
-      <c r="G64" s="323">
+      <c r="G64" s="318">
         <f t="shared" si="32"/>
         <v>-123823</v>
       </c>
-      <c r="H64" s="323">
+      <c r="H64" s="318">
         <f t="shared" si="32"/>
         <v>21016</v>
       </c>
-      <c r="I64" s="323">
+      <c r="I64" s="318">
         <f t="shared" si="32"/>
         <v>415643</v>
       </c>
-      <c r="J64" s="323">
+      <c r="J64" s="318">
         <f t="shared" si="32"/>
         <v>242432</v>
       </c>
-      <c r="K64" s="323">
+      <c r="K64" s="318">
         <f t="shared" si="32"/>
         <v>64651</v>
       </c>
-      <c r="L64" s="323" t="str">
+      <c r="L64" s="318" t="str">
         <f t="shared" si="32"/>
         <v/>
       </c>
-      <c r="M64" s="323" t="str">
+      <c r="M64" s="318" t="str">
         <f t="shared" si="32"/>
         <v/>
       </c>
@@ -8271,115 +8287,115 @@
       <c r="B77" s="93" t="s">
         <v>86</v>
       </c>
-      <c r="C77" s="333">
+      <c r="C77" s="320">
         <f t="shared" ref="C77:H78" si="40">IF(C$4="","",C28)</f>
         <v>348607</v>
       </c>
-      <c r="D77" s="333">
+      <c r="D77" s="320">
         <f t="shared" si="40"/>
         <v>262508</v>
       </c>
-      <c r="E77" s="333">
+      <c r="E77" s="320">
         <f t="shared" si="40"/>
         <v>179615</v>
       </c>
-      <c r="F77" s="333">
+      <c r="F77" s="320">
         <f t="shared" si="40"/>
         <v>260527</v>
       </c>
-      <c r="G77" s="333">
+      <c r="G77" s="320">
         <f t="shared" si="40"/>
         <v>80876</v>
       </c>
-      <c r="H77" s="333">
+      <c r="H77" s="320">
         <f t="shared" si="40"/>
         <v>86046</v>
       </c>
-      <c r="I77" s="337"/>
-      <c r="J77" s="337"/>
-      <c r="K77" s="337"/>
-      <c r="L77" s="337"/>
-      <c r="M77" s="337"/>
+      <c r="I77" s="324"/>
+      <c r="J77" s="324"/>
+      <c r="K77" s="324"/>
+      <c r="L77" s="324"/>
+      <c r="M77" s="324"/>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
         <v>87</v>
       </c>
-      <c r="C78" s="333">
+      <c r="C78" s="320">
         <f t="shared" si="40"/>
         <v>506592</v>
       </c>
-      <c r="D78" s="333">
+      <c r="D78" s="320">
         <f t="shared" si="40"/>
         <v>422202</v>
       </c>
-      <c r="E78" s="333">
+      <c r="E78" s="320">
         <f t="shared" si="40"/>
         <v>483625</v>
       </c>
-      <c r="F78" s="333">
+      <c r="F78" s="320">
         <f t="shared" si="40"/>
         <v>622768</v>
       </c>
-      <c r="G78" s="333">
+      <c r="G78" s="320">
         <f t="shared" si="40"/>
         <v>798693</v>
       </c>
-      <c r="H78" s="333">
+      <c r="H78" s="320">
         <f t="shared" si="40"/>
         <v>823654</v>
       </c>
-      <c r="I78" s="337"/>
-      <c r="J78" s="337"/>
-      <c r="K78" s="337"/>
-      <c r="L78" s="337"/>
-      <c r="M78" s="337"/>
+      <c r="I78" s="324"/>
+      <c r="J78" s="324"/>
+      <c r="K78" s="324"/>
+      <c r="L78" s="324"/>
+      <c r="M78" s="324"/>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="C79" s="323">
+      <c r="C79" s="318">
         <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C30)</f>
         <v>732882</v>
       </c>
-      <c r="D79" s="323">
+      <c r="D79" s="318">
         <f t="shared" si="41"/>
         <v>723327</v>
       </c>
-      <c r="E79" s="323">
+      <c r="E79" s="318">
         <f t="shared" si="41"/>
         <v>843108</v>
       </c>
-      <c r="F79" s="323">
+      <c r="F79" s="318">
         <f t="shared" si="41"/>
         <v>736981</v>
       </c>
-      <c r="G79" s="323">
+      <c r="G79" s="318">
         <f t="shared" si="41"/>
         <v>430335</v>
       </c>
-      <c r="H79" s="323">
+      <c r="H79" s="318">
         <f t="shared" si="41"/>
         <v>194628</v>
       </c>
-      <c r="I79" s="323">
+      <c r="I79" s="318">
         <f t="shared" si="41"/>
         <v>222985</v>
       </c>
-      <c r="J79" s="323">
+      <c r="J79" s="318">
         <f t="shared" si="41"/>
         <v>207724</v>
       </c>
-      <c r="K79" s="323">
+      <c r="K79" s="318">
         <f t="shared" si="41"/>
         <v>376010</v>
       </c>
-      <c r="L79" s="323" t="str">
+      <c r="L79" s="318" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
-      <c r="M79" s="323" t="str">
+      <c r="M79" s="318" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
@@ -8388,47 +8404,47 @@
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="C80" s="323">
+      <c r="C80" s="318">
         <f t="shared" ref="C80:M80" si="42">IF(C$4="","",C31)</f>
         <v>1832181</v>
       </c>
-      <c r="D80" s="323">
+      <c r="D80" s="318">
         <f t="shared" si="42"/>
         <v>1895931</v>
       </c>
-      <c r="E80" s="323">
+      <c r="E80" s="318">
         <f t="shared" si="42"/>
         <v>2036167</v>
       </c>
-      <c r="F80" s="323">
+      <c r="F80" s="318">
         <f t="shared" si="42"/>
         <v>1990549</v>
       </c>
-      <c r="G80" s="323">
+      <c r="G80" s="318">
         <f t="shared" si="42"/>
         <v>2083286</v>
       </c>
-      <c r="H80" s="323">
+      <c r="H80" s="318">
         <f t="shared" si="42"/>
         <v>2213601</v>
       </c>
-      <c r="I80" s="323">
+      <c r="I80" s="318">
         <f t="shared" si="42"/>
         <v>2316952</v>
       </c>
-      <c r="J80" s="323">
+      <c r="J80" s="318">
         <f t="shared" si="42"/>
         <v>2147014</v>
       </c>
-      <c r="K80" s="323">
+      <c r="K80" s="318">
         <f t="shared" si="42"/>
         <v>2157572</v>
       </c>
-      <c r="L80" s="323" t="str">
+      <c r="L80" s="318" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="M80" s="323" t="str">
+      <c r="M80" s="318" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
@@ -9512,11 +9528,11 @@
       <c r="B73" s="105" t="s">
         <v>318</v>
       </c>
-      <c r="C73" s="76">
+      <c r="C73" s="355">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
         <v>-278926.48772266664</v>
       </c>
-      <c r="D73" s="76">
+      <c r="D73" s="355">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
         <v>-251053.08995184439</v>
       </c>
@@ -9544,8 +9560,8 @@
       <c r="B75" s="80" t="s">
         <v>321</v>
       </c>
-      <c r="C75" s="341"/>
-      <c r="D75" s="342">
+      <c r="C75" s="326"/>
+      <c r="D75" s="327">
         <f>MAX(-D73*D76,G5)</f>
         <v>502106.17990368878</v>
       </c>
@@ -9849,54 +9865,54 @@
       <c r="B4" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="317">
+      <c r="C4" s="333">
         <f>AVERAGE(G4:O4)</f>
         <v>3149204.111111111</v>
       </c>
       <c r="D4" s="57"/>
       <c r="E4" s="266"/>
       <c r="F4" s="57"/>
-      <c r="G4" s="323">
+      <c r="G4" s="339">
         <f>Data!C36</f>
         <v>3638758</v>
       </c>
-      <c r="H4" s="323">
+      <c r="H4" s="339">
         <f>Data!D36</f>
         <v>3704677</v>
       </c>
-      <c r="I4" s="323">
+      <c r="I4" s="339">
         <f>Data!E36</f>
         <v>3639774</v>
       </c>
-      <c r="J4" s="323">
+      <c r="J4" s="339">
         <f>Data!F36</f>
         <v>3504022</v>
       </c>
-      <c r="K4" s="323">
+      <c r="K4" s="339">
         <f>Data!G36</f>
         <v>2352683</v>
       </c>
-      <c r="L4" s="323">
+      <c r="L4" s="339">
         <f>Data!H36</f>
         <v>2437184</v>
       </c>
-      <c r="M4" s="323">
+      <c r="M4" s="339">
         <f>Data!I36</f>
         <v>2891692</v>
       </c>
-      <c r="N4" s="323">
+      <c r="N4" s="339">
         <f>Data!J36</f>
         <v>3142295</v>
       </c>
-      <c r="O4" s="323">
+      <c r="O4" s="339">
         <f>Data!K36</f>
         <v>3031752</v>
       </c>
-      <c r="P4" s="323" t="str">
+      <c r="P4" s="339" t="str">
         <f>Data!L36</f>
         <v/>
       </c>
-      <c r="Q4" s="323" t="str">
+      <c r="Q4" s="339" t="str">
         <f>Data!M36</f>
         <v/>
       </c>
@@ -9906,52 +9922,52 @@
       <c r="B5" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="318">
+      <c r="C5" s="334">
         <f>C25</f>
         <v>-2697049.2267501326</v>
       </c>
       <c r="E5" s="268"/>
-      <c r="G5" s="323">
+      <c r="G5" s="339">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
         <v>-3031530</v>
       </c>
-      <c r="H5" s="323">
+      <c r="H5" s="339">
         <f t="shared" si="1"/>
         <v>-3043057</v>
       </c>
-      <c r="I5" s="323">
+      <c r="I5" s="339">
         <f t="shared" si="1"/>
         <v>-2964207</v>
       </c>
-      <c r="J5" s="323">
+      <c r="J5" s="339">
         <f t="shared" si="1"/>
         <v>-2973356</v>
       </c>
-      <c r="K5" s="323">
+      <c r="K5" s="339">
         <f t="shared" si="1"/>
         <v>-2041771</v>
       </c>
-      <c r="L5" s="323">
+      <c r="L5" s="339">
         <f t="shared" si="1"/>
         <v>-2032167</v>
       </c>
-      <c r="M5" s="323">
+      <c r="M5" s="339">
         <f t="shared" si="1"/>
         <v>-2491241</v>
       </c>
-      <c r="N5" s="323">
+      <c r="N5" s="339">
         <f t="shared" si="1"/>
         <v>-2824475</v>
       </c>
-      <c r="O5" s="323">
+      <c r="O5" s="339">
         <f t="shared" si="1"/>
         <v>-2745680</v>
       </c>
-      <c r="P5" s="323" t="str">
+      <c r="P5" s="339" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q5" s="323" t="str">
+      <c r="Q5" s="339" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -9961,52 +9977,52 @@
       <c r="B6" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="319">
+      <c r="C6" s="335">
         <f>C4+C5</f>
         <v>452154.88436097838</v>
       </c>
       <c r="E6" s="268"/>
-      <c r="G6" s="319">
+      <c r="G6" s="335">
         <f>IF(G4="","",G4+G5)</f>
         <v>607228</v>
       </c>
-      <c r="H6" s="319">
+      <c r="H6" s="335">
         <f t="shared" ref="H6:Q6" si="2">IF(H4="","",H4+H5)</f>
         <v>661620</v>
       </c>
-      <c r="I6" s="319">
+      <c r="I6" s="335">
         <f t="shared" si="2"/>
         <v>675567</v>
       </c>
-      <c r="J6" s="319">
+      <c r="J6" s="335">
         <f t="shared" si="2"/>
         <v>530666</v>
       </c>
-      <c r="K6" s="319">
+      <c r="K6" s="335">
         <f t="shared" si="2"/>
         <v>310912</v>
       </c>
-      <c r="L6" s="319">
+      <c r="L6" s="335">
         <f t="shared" si="2"/>
         <v>405017</v>
       </c>
-      <c r="M6" s="319">
+      <c r="M6" s="335">
         <f t="shared" si="2"/>
         <v>400451</v>
       </c>
-      <c r="N6" s="319">
+      <c r="N6" s="335">
         <f t="shared" si="2"/>
         <v>317820</v>
       </c>
-      <c r="O6" s="319">
+      <c r="O6" s="335">
         <f t="shared" si="2"/>
         <v>286072</v>
       </c>
-      <c r="P6" s="319" t="str">
+      <c r="P6" s="335" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="Q6" s="319" t="str">
+      <c r="Q6" s="335" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -10016,52 +10032,52 @@
       <c r="B7" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="318">
+      <c r="C7" s="334">
         <f>C35</f>
         <v>-253206</v>
       </c>
       <c r="E7" s="268"/>
-      <c r="G7" s="318">
+      <c r="G7" s="334">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
         <v>-253206</v>
       </c>
-      <c r="H7" s="318">
+      <c r="H7" s="334">
         <f t="shared" si="3"/>
         <v>-252912</v>
       </c>
-      <c r="I7" s="318">
+      <c r="I7" s="334">
         <f t="shared" si="3"/>
         <v>-243704</v>
       </c>
-      <c r="J7" s="318">
+      <c r="J7" s="334">
         <f t="shared" si="3"/>
         <v>-211994</v>
       </c>
-      <c r="K7" s="318">
+      <c r="K7" s="334">
         <f t="shared" si="3"/>
         <v>-155328</v>
       </c>
-      <c r="L7" s="318">
+      <c r="L7" s="334">
         <f t="shared" si="3"/>
         <v>-277575</v>
       </c>
-      <c r="M7" s="318">
+      <c r="M7" s="334">
         <f t="shared" si="3"/>
         <v>-275423</v>
       </c>
-      <c r="N7" s="318">
+      <c r="N7" s="334">
         <f t="shared" si="3"/>
         <v>-311367</v>
       </c>
-      <c r="O7" s="318">
+      <c r="O7" s="334">
         <f t="shared" si="3"/>
         <v>-332430</v>
       </c>
-      <c r="P7" s="318" t="str">
+      <c r="P7" s="334" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="Q7" s="318" t="str">
+      <c r="Q7" s="334" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -10071,54 +10087,54 @@
       <c r="B8" s="29" t="s">
         <v>153</v>
       </c>
-      <c r="C8" s="320">
+      <c r="C8" s="336">
         <f>C6+C7</f>
         <v>198948.88436097838</v>
       </c>
       <c r="D8" s="59"/>
       <c r="E8" s="274"/>
       <c r="F8" s="59"/>
-      <c r="G8" s="319">
+      <c r="G8" s="335">
         <f>IF(G$4="","",G6+G7)</f>
         <v>354022</v>
       </c>
-      <c r="H8" s="319">
+      <c r="H8" s="335">
         <f t="shared" ref="H8:Q8" si="4">IF(H$4="","",H6+H7)</f>
         <v>408708</v>
       </c>
-      <c r="I8" s="319">
+      <c r="I8" s="335">
         <f t="shared" si="4"/>
         <v>431863</v>
       </c>
-      <c r="J8" s="319">
+      <c r="J8" s="335">
         <f t="shared" si="4"/>
         <v>318672</v>
       </c>
-      <c r="K8" s="319">
+      <c r="K8" s="335">
         <f t="shared" si="4"/>
         <v>155584</v>
       </c>
-      <c r="L8" s="319">
+      <c r="L8" s="335">
         <f t="shared" si="4"/>
         <v>127442</v>
       </c>
-      <c r="M8" s="319">
+      <c r="M8" s="335">
         <f t="shared" si="4"/>
         <v>125028</v>
       </c>
-      <c r="N8" s="319">
+      <c r="N8" s="335">
         <f t="shared" si="4"/>
         <v>6453</v>
       </c>
-      <c r="O8" s="319">
+      <c r="O8" s="335">
         <f t="shared" si="4"/>
         <v>-46358</v>
       </c>
-      <c r="P8" s="319" t="str">
+      <c r="P8" s="335" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Q8" s="319" t="str">
+      <c r="Q8" s="335" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -10128,52 +10144,52 @@
       <c r="B9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C9" s="318">
+      <c r="C9" s="334">
         <f>BS!$G$39*BS!D58</f>
         <v>0</v>
       </c>
       <c r="E9" s="268"/>
-      <c r="G9" s="318">
+      <c r="G9" s="334">
         <f>IF(Data!C61="","",-Data!C61)</f>
         <v>0</v>
       </c>
-      <c r="H9" s="318">
+      <c r="H9" s="334">
         <f>IF(Data!D61="","",-Data!D61)</f>
         <v>0</v>
       </c>
-      <c r="I9" s="318">
+      <c r="I9" s="334">
         <f>IF(Data!E61="","",-Data!E61)</f>
         <v>0</v>
       </c>
-      <c r="J9" s="318">
+      <c r="J9" s="334">
         <f>IF(Data!F61="","",-Data!F61)</f>
         <v>0</v>
       </c>
-      <c r="K9" s="318">
+      <c r="K9" s="334">
         <f>IF(Data!G61="","",-Data!G61)</f>
         <v>0</v>
       </c>
-      <c r="L9" s="318">
+      <c r="L9" s="334">
         <f>IF(Data!H61="","",-Data!H61)</f>
         <v>0</v>
       </c>
-      <c r="M9" s="318">
+      <c r="M9" s="334">
         <f>IF(Data!I61="","",-Data!I61)</f>
         <v>0</v>
       </c>
-      <c r="N9" s="318">
+      <c r="N9" s="334">
         <f>IF(Data!J61="","",-Data!J61)</f>
         <v>0</v>
       </c>
-      <c r="O9" s="318">
+      <c r="O9" s="334">
         <f>IF(Data!K61="","",-Data!K61)</f>
         <v>0</v>
       </c>
-      <c r="P9" s="318" t="str">
+      <c r="P9" s="334" t="str">
         <f>IF(Data!L61="","",-Data!L61)</f>
         <v/>
       </c>
-      <c r="Q9" s="318" t="str">
+      <c r="Q9" s="334" t="str">
         <f>IF(Data!M61="","",-Data!M61)</f>
         <v/>
       </c>
@@ -10183,52 +10199,52 @@
       <c r="B10" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C10" s="318">
+      <c r="C10" s="334">
         <f>-C4*C78</f>
         <v>0</v>
       </c>
       <c r="E10" s="268"/>
-      <c r="G10" s="318">
+      <c r="G10" s="334">
         <f>Data!C62</f>
         <v>0</v>
       </c>
-      <c r="H10" s="318">
+      <c r="H10" s="334">
         <f>Data!D62</f>
         <v>0</v>
       </c>
-      <c r="I10" s="318">
+      <c r="I10" s="334">
         <f>Data!E62</f>
         <v>0</v>
       </c>
-      <c r="J10" s="318">
+      <c r="J10" s="334">
         <f>Data!F62</f>
         <v>0</v>
       </c>
-      <c r="K10" s="318">
+      <c r="K10" s="334">
         <f>Data!G62</f>
         <v>0</v>
       </c>
-      <c r="L10" s="318">
+      <c r="L10" s="334">
         <f>Data!H62</f>
         <v>0</v>
       </c>
-      <c r="M10" s="318">
+      <c r="M10" s="334">
         <f>Data!I62</f>
         <v>0</v>
       </c>
-      <c r="N10" s="318">
+      <c r="N10" s="334">
         <f>Data!J62</f>
         <v>0</v>
       </c>
-      <c r="O10" s="318">
+      <c r="O10" s="334">
         <f>Data!K62</f>
         <v>0</v>
       </c>
-      <c r="P10" s="318" t="str">
+      <c r="P10" s="334" t="str">
         <f>Data!L62</f>
         <v/>
       </c>
-      <c r="Q10" s="318" t="str">
+      <c r="Q10" s="334" t="str">
         <f>Data!M62</f>
         <v/>
       </c>
@@ -10238,54 +10254,54 @@
       <c r="B11" s="31" t="s">
         <v>195</v>
       </c>
-      <c r="C11" s="321">
+      <c r="C11" s="337">
         <f>C63</f>
         <v>0</v>
       </c>
       <c r="D11" s="168"/>
       <c r="E11" s="267"/>
       <c r="F11" s="168"/>
-      <c r="G11" s="324">
+      <c r="G11" s="340">
         <f>G61</f>
         <v>0</v>
       </c>
-      <c r="H11" s="324">
+      <c r="H11" s="340">
         <f t="shared" ref="H11:Q11" si="5">H61</f>
         <v>0</v>
       </c>
-      <c r="I11" s="324">
+      <c r="I11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J11" s="324">
+      <c r="J11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K11" s="324">
+      <c r="K11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L11" s="324">
+      <c r="L11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="M11" s="324">
+      <c r="M11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N11" s="324">
+      <c r="N11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O11" s="324">
+      <c r="O11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="P11" s="324" t="str">
+      <c r="P11" s="340" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Q11" s="324" t="str">
+      <c r="Q11" s="340" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -10295,52 +10311,52 @@
       <c r="B12" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C12" s="318">
+      <c r="C12" s="334">
         <f>C50</f>
         <v>-13663</v>
       </c>
       <c r="E12" s="268"/>
-      <c r="G12" s="318">
+      <c r="G12" s="334">
         <f>G50</f>
         <v>-13663</v>
       </c>
-      <c r="H12" s="318">
+      <c r="H12" s="334">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
         <v>-14612</v>
       </c>
-      <c r="I12" s="318">
+      <c r="I12" s="334">
         <f t="shared" si="6"/>
         <v>-12033</v>
       </c>
-      <c r="J12" s="318">
+      <c r="J12" s="334">
         <f t="shared" si="6"/>
         <v>-10203</v>
       </c>
-      <c r="K12" s="318">
+      <c r="K12" s="334">
         <f t="shared" si="6"/>
         <v>-14210</v>
       </c>
-      <c r="L12" s="318">
+      <c r="L12" s="334">
         <f t="shared" si="6"/>
         <v>-1959</v>
       </c>
-      <c r="M12" s="318">
+      <c r="M12" s="334">
         <f t="shared" si="6"/>
         <v>-1843</v>
       </c>
-      <c r="N12" s="318">
+      <c r="N12" s="334">
         <f t="shared" si="6"/>
         <v>-3730</v>
       </c>
-      <c r="O12" s="318">
+      <c r="O12" s="334">
         <f t="shared" si="6"/>
         <v>-6942</v>
       </c>
-      <c r="P12" s="318" t="str">
+      <c r="P12" s="334" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Q12" s="318" t="str">
+      <c r="Q12" s="334" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -10350,52 +10366,52 @@
       <c r="B13" s="70" t="s">
         <v>165</v>
       </c>
-      <c r="C13" s="319">
+      <c r="C13" s="335">
         <f>SUM(C8:C12)</f>
         <v>185285.88436097838</v>
       </c>
       <c r="E13" s="268"/>
-      <c r="G13" s="319">
+      <c r="G13" s="335">
         <f>IF(G$4="","",SUM(G8:G12))</f>
         <v>340359</v>
       </c>
-      <c r="H13" s="319">
+      <c r="H13" s="335">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
         <v>394096</v>
       </c>
-      <c r="I13" s="319">
+      <c r="I13" s="335">
         <f t="shared" si="7"/>
         <v>419830</v>
       </c>
-      <c r="J13" s="319">
+      <c r="J13" s="335">
         <f t="shared" si="7"/>
         <v>308469</v>
       </c>
-      <c r="K13" s="319">
+      <c r="K13" s="335">
         <f t="shared" si="7"/>
         <v>141374</v>
       </c>
-      <c r="L13" s="319">
+      <c r="L13" s="335">
         <f t="shared" si="7"/>
         <v>125483</v>
       </c>
-      <c r="M13" s="319">
+      <c r="M13" s="335">
         <f t="shared" si="7"/>
         <v>123185</v>
       </c>
-      <c r="N13" s="319">
+      <c r="N13" s="335">
         <f t="shared" si="7"/>
         <v>2723</v>
       </c>
-      <c r="O13" s="319">
+      <c r="O13" s="335">
         <f t="shared" si="7"/>
         <v>-53300</v>
       </c>
-      <c r="P13" s="319" t="str">
+      <c r="P13" s="335" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="Q13" s="319" t="str">
+      <c r="Q13" s="335" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -10405,52 +10421,52 @@
       <c r="B14" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C14" s="318">
+      <c r="C14" s="334">
         <f>-SUM(C8+C11,C12)*C43</f>
         <v>-46321.471090244595</v>
       </c>
       <c r="E14" s="268"/>
-      <c r="G14" s="318">
+      <c r="G14" s="334">
         <f>Data!C46</f>
         <v>-145324</v>
       </c>
-      <c r="H14" s="318">
+      <c r="H14" s="334">
         <f>Data!D46</f>
         <v>-144534</v>
       </c>
-      <c r="I14" s="318">
+      <c r="I14" s="334">
         <f>Data!E46</f>
         <v>-150461</v>
       </c>
-      <c r="J14" s="318">
+      <c r="J14" s="334">
         <f>Data!F46</f>
         <v>-123112</v>
       </c>
-      <c r="K14" s="318">
+      <c r="K14" s="334">
         <f>Data!G46</f>
         <v>-28324</v>
       </c>
-      <c r="L14" s="318">
+      <c r="L14" s="334">
         <f>Data!H46</f>
         <v>-21936</v>
       </c>
-      <c r="M14" s="318">
+      <c r="M14" s="334">
         <f>Data!I46</f>
         <v>-26006</v>
       </c>
-      <c r="N14" s="318">
+      <c r="N14" s="334">
         <f>Data!J46</f>
         <v>-9352</v>
       </c>
-      <c r="O14" s="318">
+      <c r="O14" s="334">
         <f>Data!K46</f>
         <v>-3042</v>
       </c>
-      <c r="P14" s="318" t="str">
+      <c r="P14" s="334" t="str">
         <f>Data!L46</f>
         <v/>
       </c>
-      <c r="Q14" s="318" t="str">
+      <c r="Q14" s="334" t="str">
         <f>Data!M46</f>
         <v/>
       </c>
@@ -10460,54 +10476,54 @@
       <c r="B15" s="40" t="s">
         <v>244</v>
       </c>
-      <c r="C15" s="318">
+      <c r="C15" s="334">
         <f>-C4*C83</f>
         <v>-572.93535914055167</v>
       </c>
       <c r="D15" s="60"/>
       <c r="E15" s="275"/>
       <c r="F15" s="60"/>
-      <c r="G15" s="323">
+      <c r="G15" s="339">
         <f>Data!C48</f>
         <v>-662</v>
       </c>
-      <c r="H15" s="323">
+      <c r="H15" s="339">
         <f>Data!D48</f>
         <v>-92</v>
       </c>
-      <c r="I15" s="323">
+      <c r="I15" s="339">
         <f>Data!E48</f>
         <v>-402</v>
       </c>
-      <c r="J15" s="323">
+      <c r="J15" s="339">
         <f>Data!F48</f>
         <v>0</v>
       </c>
-      <c r="K15" s="323">
+      <c r="K15" s="339">
         <f>Data!G48</f>
         <v>0</v>
       </c>
-      <c r="L15" s="323">
+      <c r="L15" s="339">
         <f>Data!H48</f>
         <v>0</v>
       </c>
-      <c r="M15" s="323">
+      <c r="M15" s="339">
         <f>Data!I48</f>
         <v>0</v>
       </c>
-      <c r="N15" s="323">
+      <c r="N15" s="339">
         <f>Data!J48</f>
         <v>0</v>
       </c>
-      <c r="O15" s="323">
+      <c r="O15" s="339">
         <f>Data!K48</f>
         <v>0</v>
       </c>
-      <c r="P15" s="323" t="str">
+      <c r="P15" s="339" t="str">
         <f>Data!L48</f>
         <v/>
       </c>
-      <c r="Q15" s="323" t="str">
+      <c r="Q15" s="339" t="str">
         <f>Data!M48</f>
         <v/>
       </c>
@@ -10517,54 +10533,54 @@
       <c r="B16" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="C16" s="322">
+      <c r="C16" s="338">
         <f>SUM(C13:C15)</f>
         <v>138391.47791159325</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="276"/>
       <c r="F16" s="61"/>
-      <c r="G16" s="319">
+      <c r="G16" s="335">
         <f>IF(G$4="","",SUM(G13:G15))</f>
         <v>194373</v>
       </c>
-      <c r="H16" s="319">
+      <c r="H16" s="335">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
         <v>249470</v>
       </c>
-      <c r="I16" s="319">
+      <c r="I16" s="335">
         <f t="shared" si="8"/>
         <v>268967</v>
       </c>
-      <c r="J16" s="319">
+      <c r="J16" s="335">
         <f t="shared" si="8"/>
         <v>185357</v>
       </c>
-      <c r="K16" s="319">
+      <c r="K16" s="335">
         <f t="shared" si="8"/>
         <v>113050</v>
       </c>
-      <c r="L16" s="319">
+      <c r="L16" s="335">
         <f t="shared" si="8"/>
         <v>103547</v>
       </c>
-      <c r="M16" s="319">
+      <c r="M16" s="335">
         <f t="shared" si="8"/>
         <v>97179</v>
       </c>
-      <c r="N16" s="319">
+      <c r="N16" s="335">
         <f t="shared" si="8"/>
         <v>-6629</v>
       </c>
-      <c r="O16" s="319">
+      <c r="O16" s="335">
         <f t="shared" si="8"/>
         <v>-56342</v>
       </c>
-      <c r="P16" s="319" t="str">
+      <c r="P16" s="335" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="Q16" s="319" t="str">
+      <c r="Q16" s="335" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -10574,7 +10590,7 @@
       <c r="B17" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="318">
+      <c r="C17" s="334">
         <f>-C4*C85</f>
         <v>0</v>
       </c>
@@ -10583,24 +10599,24 @@
         <v>332</v>
       </c>
       <c r="F17" s="58"/>
-      <c r="G17" s="325"/>
-      <c r="H17" s="325"/>
-      <c r="I17" s="325"/>
-      <c r="J17" s="325"/>
-      <c r="K17" s="325"/>
-      <c r="L17" s="325"/>
-      <c r="M17" s="325"/>
-      <c r="N17" s="325"/>
-      <c r="O17" s="325"/>
-      <c r="P17" s="325"/>
-      <c r="Q17" s="325"/>
+      <c r="G17" s="341"/>
+      <c r="H17" s="341"/>
+      <c r="I17" s="341"/>
+      <c r="J17" s="341"/>
+      <c r="K17" s="341"/>
+      <c r="L17" s="341"/>
+      <c r="M17" s="341"/>
+      <c r="N17" s="341"/>
+      <c r="O17" s="341"/>
+      <c r="P17" s="341"/>
+      <c r="Q17" s="341"/>
     </row>
     <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="C18" s="318">
+      <c r="C18" s="334">
         <v>0</v>
       </c>
       <c r="D18" s="58"/>
@@ -10608,71 +10624,71 @@
         <v>333</v>
       </c>
       <c r="F18" s="58"/>
-      <c r="G18" s="326"/>
-      <c r="H18" s="326"/>
-      <c r="I18" s="326"/>
-      <c r="J18" s="326"/>
-      <c r="K18" s="326"/>
-      <c r="L18" s="326"/>
-      <c r="M18" s="326"/>
-      <c r="N18" s="326"/>
-      <c r="O18" s="326"/>
-      <c r="P18" s="326"/>
-      <c r="Q18" s="326"/>
+      <c r="G18" s="342"/>
+      <c r="H18" s="342"/>
+      <c r="I18" s="342"/>
+      <c r="J18" s="342"/>
+      <c r="K18" s="342"/>
+      <c r="L18" s="342"/>
+      <c r="M18" s="342"/>
+      <c r="N18" s="342"/>
+      <c r="O18" s="342"/>
+      <c r="P18" s="342"/>
+      <c r="Q18" s="342"/>
     </row>
     <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="C19" s="319">
+      <c r="C19" s="335">
         <f>C16+C17</f>
         <v>138391.47791159325</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="265"/>
       <c r="F19" s="27"/>
-      <c r="G19" s="324">
+      <c r="G19" s="340">
         <f>IF(G$4="","",G16+G17)</f>
         <v>194373</v>
       </c>
-      <c r="H19" s="324">
+      <c r="H19" s="340">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
         <v>249470</v>
       </c>
-      <c r="I19" s="324">
+      <c r="I19" s="340">
         <f t="shared" si="9"/>
         <v>268967</v>
       </c>
-      <c r="J19" s="324">
+      <c r="J19" s="340">
         <f t="shared" si="9"/>
         <v>185357</v>
       </c>
-      <c r="K19" s="324">
+      <c r="K19" s="340">
         <f t="shared" si="9"/>
         <v>113050</v>
       </c>
-      <c r="L19" s="324">
+      <c r="L19" s="340">
         <f t="shared" si="9"/>
         <v>103547</v>
       </c>
-      <c r="M19" s="324">
+      <c r="M19" s="340">
         <f t="shared" si="9"/>
         <v>97179</v>
       </c>
-      <c r="N19" s="324">
+      <c r="N19" s="340">
         <f t="shared" si="9"/>
         <v>-6629</v>
       </c>
-      <c r="O19" s="324">
+      <c r="O19" s="340">
         <f t="shared" si="9"/>
         <v>-56342</v>
       </c>
-      <c r="P19" s="324" t="str">
+      <c r="P19" s="340" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="Q19" s="324" t="str">
+      <c r="Q19" s="340" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -10745,54 +10761,54 @@
       <c r="B23" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="327">
+      <c r="C23" s="343">
         <f>-C4*C28</f>
         <v>-2226669.2968957396</v>
       </c>
       <c r="D23" s="58"/>
       <c r="E23" s="267"/>
       <c r="F23" s="58"/>
-      <c r="G23" s="323">
+      <c r="G23" s="339">
         <f>Data!C37</f>
         <v>-2488028</v>
       </c>
-      <c r="H23" s="323">
+      <c r="H23" s="339">
         <f>Data!D37</f>
         <v>-2515967</v>
       </c>
-      <c r="I23" s="323">
+      <c r="I23" s="339">
         <f>Data!E37</f>
         <v>-2459489</v>
       </c>
-      <c r="J23" s="323">
+      <c r="J23" s="339">
         <f>Data!F37</f>
         <v>-2541906</v>
       </c>
-      <c r="K23" s="323">
+      <c r="K23" s="339">
         <f>Data!G37</f>
         <v>-1707356</v>
       </c>
-      <c r="L23" s="323">
+      <c r="L23" s="339">
         <f>Data!H37</f>
         <v>-1834224</v>
       </c>
-      <c r="M23" s="323">
+      <c r="M23" s="339">
         <f>Data!I37</f>
         <v>-2284817</v>
       </c>
-      <c r="N23" s="323">
+      <c r="N23" s="339">
         <f>Data!J37</f>
         <v>-2634028</v>
       </c>
-      <c r="O23" s="323">
+      <c r="O23" s="339">
         <f>Data!K37</f>
         <v>-2546147</v>
       </c>
-      <c r="P23" s="323" t="str">
+      <c r="P23" s="339" t="str">
         <f>Data!L37</f>
         <v/>
       </c>
-      <c r="Q23" s="323" t="str">
+      <c r="Q23" s="339" t="str">
         <f>Data!M37</f>
         <v/>
       </c>
@@ -10802,54 +10818,54 @@
       <c r="B24" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="C24" s="318">
+      <c r="C24" s="334">
         <f>-C4*C29</f>
         <v>-470379.92985439295</v>
       </c>
       <c r="D24" s="27"/>
       <c r="E24" s="265"/>
       <c r="F24" s="27"/>
-      <c r="G24" s="323">
+      <c r="G24" s="339">
         <f>Data!C40</f>
         <v>-543502</v>
       </c>
-      <c r="H24" s="323">
+      <c r="H24" s="339">
         <f>Data!D40</f>
         <v>-527090</v>
       </c>
-      <c r="I24" s="323">
+      <c r="I24" s="339">
         <f>Data!E40</f>
         <v>-504718</v>
       </c>
-      <c r="J24" s="323">
+      <c r="J24" s="339">
         <f>Data!F40</f>
         <v>-431450</v>
       </c>
-      <c r="K24" s="323">
+      <c r="K24" s="339">
         <f>Data!G40</f>
         <v>-334415</v>
       </c>
-      <c r="L24" s="323">
+      <c r="L24" s="339">
         <f>Data!H40</f>
         <v>-197943</v>
       </c>
-      <c r="M24" s="323">
+      <c r="M24" s="339">
         <f>Data!I40</f>
         <v>-206424</v>
       </c>
-      <c r="N24" s="323">
+      <c r="N24" s="339">
         <f>Data!J40</f>
         <v>-190447</v>
       </c>
-      <c r="O24" s="323">
+      <c r="O24" s="339">
         <f>Data!K40</f>
         <v>-199533</v>
       </c>
-      <c r="P24" s="323" t="str">
+      <c r="P24" s="339" t="str">
         <f>Data!L40</f>
         <v/>
       </c>
-      <c r="Q24" s="323" t="str">
+      <c r="Q24" s="339" t="str">
         <f>Data!M40</f>
         <v/>
       </c>
@@ -10859,54 +10875,54 @@
       <c r="B25" s="70" t="s">
         <v>46</v>
       </c>
-      <c r="C25" s="319">
+      <c r="C25" s="335">
         <f>C23+C24</f>
         <v>-2697049.2267501326</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="273"/>
       <c r="F25" s="9"/>
-      <c r="G25" s="319">
+      <c r="G25" s="335">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
         <v>-3031530</v>
       </c>
-      <c r="H25" s="319">
+      <c r="H25" s="335">
         <f t="shared" si="10"/>
         <v>-3043057</v>
       </c>
-      <c r="I25" s="319">
+      <c r="I25" s="335">
         <f t="shared" si="10"/>
         <v>-2964207</v>
       </c>
-      <c r="J25" s="319">
+      <c r="J25" s="335">
         <f t="shared" si="10"/>
         <v>-2973356</v>
       </c>
-      <c r="K25" s="319">
+      <c r="K25" s="335">
         <f t="shared" si="10"/>
         <v>-2041771</v>
       </c>
-      <c r="L25" s="319">
+      <c r="L25" s="335">
         <f t="shared" si="10"/>
         <v>-2032167</v>
       </c>
-      <c r="M25" s="319">
+      <c r="M25" s="335">
         <f t="shared" si="10"/>
         <v>-2491241</v>
       </c>
-      <c r="N25" s="319">
+      <c r="N25" s="335">
         <f t="shared" si="10"/>
         <v>-2824475</v>
       </c>
-      <c r="O25" s="319">
+      <c r="O25" s="335">
         <f t="shared" si="10"/>
         <v>-2745680</v>
       </c>
-      <c r="P25" s="319" t="str">
+      <c r="P25" s="335" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="Q25" s="319" t="str">
+      <c r="Q25" s="335" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
@@ -11112,54 +11128,54 @@
       <c r="B33" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="C33" s="328">
+      <c r="C33" s="346">
         <f>G33</f>
         <v>-253206</v>
       </c>
       <c r="E33" s="266" t="s">
         <v>334</v>
       </c>
-      <c r="G33" s="318">
+      <c r="G33" s="334">
         <f>Data!C41</f>
         <v>-253206</v>
       </c>
-      <c r="H33" s="318">
+      <c r="H33" s="334">
         <f>Data!D41</f>
         <v>-252912</v>
       </c>
-      <c r="I33" s="318">
+      <c r="I33" s="334">
         <f>Data!E41</f>
         <v>-243704</v>
       </c>
-      <c r="J33" s="318">
+      <c r="J33" s="334">
         <f>Data!F41</f>
         <v>-211994</v>
       </c>
-      <c r="K33" s="318">
+      <c r="K33" s="334">
         <f>Data!G41</f>
         <v>-155328</v>
       </c>
-      <c r="L33" s="318">
+      <c r="L33" s="334">
         <f>Data!H41</f>
         <v>-277575</v>
       </c>
-      <c r="M33" s="318">
+      <c r="M33" s="334">
         <f>Data!I41</f>
         <v>-275423</v>
       </c>
-      <c r="N33" s="318">
+      <c r="N33" s="334">
         <f>Data!J41</f>
         <v>-311367</v>
       </c>
-      <c r="O33" s="318">
+      <c r="O33" s="334">
         <f>Data!K41</f>
         <v>-332430</v>
       </c>
-      <c r="P33" s="318" t="str">
+      <c r="P33" s="334" t="str">
         <f>Data!L41</f>
         <v/>
       </c>
-      <c r="Q33" s="318" t="str">
+      <c r="Q33" s="334" t="str">
         <f>Data!M41</f>
         <v/>
       </c>
@@ -11169,7 +11185,7 @@
       <c r="B34" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="C34" s="328">
+      <c r="C34" s="346">
         <f>AVERAGE(G34:J34)</f>
         <v>0</v>
       </c>
@@ -11178,47 +11194,47 @@
         <v>334</v>
       </c>
       <c r="F34" s="58"/>
-      <c r="G34" s="323">
+      <c r="G34" s="339">
         <f>Data!C42</f>
         <v>0</v>
       </c>
-      <c r="H34" s="323">
+      <c r="H34" s="339">
         <f>Data!D42</f>
         <v>0</v>
       </c>
-      <c r="I34" s="323">
+      <c r="I34" s="339">
         <f>Data!E42</f>
         <v>0</v>
       </c>
-      <c r="J34" s="323">
+      <c r="J34" s="339">
         <f>Data!F42</f>
         <v>0</v>
       </c>
-      <c r="K34" s="323">
+      <c r="K34" s="339">
         <f>Data!G42</f>
         <v>0</v>
       </c>
-      <c r="L34" s="323">
+      <c r="L34" s="339">
         <f>Data!H42</f>
         <v>0</v>
       </c>
-      <c r="M34" s="323">
+      <c r="M34" s="339">
         <f>Data!I42</f>
         <v>0</v>
       </c>
-      <c r="N34" s="323">
+      <c r="N34" s="339">
         <f>Data!J42</f>
         <v>0</v>
       </c>
-      <c r="O34" s="323">
+      <c r="O34" s="339">
         <f>Data!K42</f>
         <v>0</v>
       </c>
-      <c r="P34" s="323" t="str">
+      <c r="P34" s="339" t="str">
         <f>Data!L42</f>
         <v/>
       </c>
-      <c r="Q34" s="323" t="str">
+      <c r="Q34" s="339" t="str">
         <f>Data!M42</f>
         <v/>
       </c>
@@ -11228,54 +11244,54 @@
       <c r="B35" s="70" t="s">
         <v>45</v>
       </c>
-      <c r="C35" s="319">
+      <c r="C35" s="335">
         <f>C33+C34</f>
         <v>-253206</v>
       </c>
       <c r="D35" s="58"/>
       <c r="E35" s="267"/>
       <c r="F35" s="58"/>
-      <c r="G35" s="319">
+      <c r="G35" s="335">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
         <v>-253206</v>
       </c>
-      <c r="H35" s="319">
+      <c r="H35" s="335">
         <f t="shared" si="14"/>
         <v>-252912</v>
       </c>
-      <c r="I35" s="319">
+      <c r="I35" s="335">
         <f t="shared" si="14"/>
         <v>-243704</v>
       </c>
-      <c r="J35" s="319">
+      <c r="J35" s="335">
         <f t="shared" si="14"/>
         <v>-211994</v>
       </c>
-      <c r="K35" s="319">
+      <c r="K35" s="335">
         <f t="shared" si="14"/>
         <v>-155328</v>
       </c>
-      <c r="L35" s="319">
+      <c r="L35" s="335">
         <f t="shared" si="14"/>
         <v>-277575</v>
       </c>
-      <c r="M35" s="319">
+      <c r="M35" s="335">
         <f t="shared" si="14"/>
         <v>-275423</v>
       </c>
-      <c r="N35" s="319">
+      <c r="N35" s="335">
         <f t="shared" si="14"/>
         <v>-311367</v>
       </c>
-      <c r="O35" s="319">
+      <c r="O35" s="335">
         <f t="shared" si="14"/>
         <v>-332430</v>
       </c>
-      <c r="P35" s="319" t="str">
+      <c r="P35" s="335" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="Q35" s="319" t="str">
+      <c r="Q35" s="335" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
@@ -11569,52 +11585,52 @@
       <c r="B47" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C47" s="318">
+      <c r="C47" s="334">
         <f>-BS!G31*Normalized_FCF!C54</f>
         <v>-13663</v>
       </c>
       <c r="E47" s="268"/>
-      <c r="G47" s="318">
+      <c r="G47" s="334">
         <f>Data!C51</f>
         <v>-13663</v>
       </c>
-      <c r="H47" s="318">
+      <c r="H47" s="334">
         <f>Data!D51</f>
         <v>-14612</v>
       </c>
-      <c r="I47" s="318">
+      <c r="I47" s="334">
         <f>Data!E51</f>
         <v>-12033</v>
       </c>
-      <c r="J47" s="318">
+      <c r="J47" s="334">
         <f>Data!F51</f>
         <v>-10203</v>
       </c>
-      <c r="K47" s="318">
+      <c r="K47" s="334">
         <f>Data!G51</f>
         <v>-14210</v>
       </c>
-      <c r="L47" s="318">
+      <c r="L47" s="334">
         <f>Data!H51</f>
         <v>-1959</v>
       </c>
-      <c r="M47" s="318">
+      <c r="M47" s="334">
         <f>Data!I51</f>
         <v>-1843</v>
       </c>
-      <c r="N47" s="318">
+      <c r="N47" s="334">
         <f>Data!J51</f>
         <v>-3730</v>
       </c>
-      <c r="O47" s="318">
+      <c r="O47" s="334">
         <f>Data!K51</f>
         <v>-6942</v>
       </c>
-      <c r="P47" s="318" t="str">
+      <c r="P47" s="334" t="str">
         <f>Data!L51</f>
         <v/>
       </c>
-      <c r="Q47" s="318" t="str">
+      <c r="Q47" s="334" t="str">
         <f>Data!M51</f>
         <v/>
       </c>
@@ -11624,52 +11640,52 @@
       <c r="B48" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="C48" s="318">
+      <c r="C48" s="334">
         <f>BS!D75*C53</f>
         <v>0</v>
       </c>
       <c r="E48" s="268"/>
-      <c r="G48" s="327">
+      <c r="G48" s="343">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>0</v>
       </c>
-      <c r="H48" s="327">
+      <c r="H48" s="343">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v>0</v>
       </c>
-      <c r="I48" s="327">
+      <c r="I48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="J48" s="327">
+      <c r="J48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="K48" s="327">
+      <c r="K48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="L48" s="327">
+      <c r="L48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="M48" s="327">
+      <c r="M48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="N48" s="327">
+      <c r="N48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="O48" s="327">
+      <c r="O48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="P48" s="327" t="str">
+      <c r="P48" s="343" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="Q48" s="327" t="str">
+      <c r="Q48" s="343" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
@@ -11679,54 +11695,54 @@
       <c r="B49" s="287" t="s">
         <v>343</v>
       </c>
-      <c r="C49" s="329">
+      <c r="C49" s="348">
         <f>BS!$C$66*C53</f>
         <v>0</v>
       </c>
       <c r="D49" s="288"/>
       <c r="E49" s="289"/>
       <c r="F49" s="288"/>
-      <c r="G49" s="329">
+      <c r="G49" s="348">
         <f>Data!C52</f>
         <v>0</v>
       </c>
-      <c r="H49" s="329">
+      <c r="H49" s="348">
         <f>Data!D52</f>
         <v>0</v>
       </c>
-      <c r="I49" s="329">
+      <c r="I49" s="348">
         <f>Data!E52</f>
         <v>0</v>
       </c>
-      <c r="J49" s="329">
+      <c r="J49" s="348">
         <f>Data!F52</f>
         <v>0</v>
       </c>
-      <c r="K49" s="329">
+      <c r="K49" s="348">
         <f>Data!G52</f>
         <v>0</v>
       </c>
-      <c r="L49" s="329">
+      <c r="L49" s="348">
         <f>Data!H52</f>
         <v>0</v>
       </c>
-      <c r="M49" s="329">
+      <c r="M49" s="348">
         <f>Data!I52</f>
         <v>0</v>
       </c>
-      <c r="N49" s="329">
+      <c r="N49" s="348">
         <f>Data!J52</f>
         <v>0</v>
       </c>
-      <c r="O49" s="329">
+      <c r="O49" s="348">
         <f>Data!K52</f>
         <v>0</v>
       </c>
-      <c r="P49" s="329" t="str">
+      <c r="P49" s="348" t="str">
         <f>Data!L52</f>
         <v/>
       </c>
-      <c r="Q49" s="329" t="str">
+      <c r="Q49" s="348" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -11736,52 +11752,52 @@
       <c r="B50" s="70" t="s">
         <v>68</v>
       </c>
-      <c r="C50" s="319">
+      <c r="C50" s="335">
         <f>C47+C48</f>
         <v>-13663</v>
       </c>
       <c r="E50" s="268"/>
-      <c r="G50" s="319">
+      <c r="G50" s="335">
         <f>IF(G$4="","",(G47+G48))</f>
         <v>-13663</v>
       </c>
-      <c r="H50" s="319">
+      <c r="H50" s="335">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
         <v>-14612</v>
       </c>
-      <c r="I50" s="319">
+      <c r="I50" s="335">
         <f t="shared" si="20"/>
         <v>-12033</v>
       </c>
-      <c r="J50" s="319">
+      <c r="J50" s="335">
         <f t="shared" si="20"/>
         <v>-10203</v>
       </c>
-      <c r="K50" s="319">
+      <c r="K50" s="335">
         <f t="shared" si="20"/>
         <v>-14210</v>
       </c>
-      <c r="L50" s="319">
+      <c r="L50" s="335">
         <f t="shared" si="20"/>
         <v>-1959</v>
       </c>
-      <c r="M50" s="319">
+      <c r="M50" s="335">
         <f t="shared" si="20"/>
         <v>-1843</v>
       </c>
-      <c r="N50" s="319">
+      <c r="N50" s="335">
         <f t="shared" si="20"/>
         <v>-3730</v>
       </c>
-      <c r="O50" s="319">
+      <c r="O50" s="335">
         <f t="shared" si="20"/>
         <v>-6942</v>
       </c>
-      <c r="P50" s="319" t="str">
+      <c r="P50" s="335" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="Q50" s="319" t="str">
+      <c r="Q50" s="335" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
@@ -11928,52 +11944,52 @@
       <c r="B58" s="40" t="s">
         <v>168</v>
       </c>
-      <c r="C58" s="318">
+      <c r="C58" s="334">
         <f>BS!$C67*C66</f>
         <v>0</v>
       </c>
       <c r="E58" s="268"/>
-      <c r="G58" s="318">
+      <c r="G58" s="334">
         <f>Data!C56</f>
         <v>0</v>
       </c>
-      <c r="H58" s="318">
+      <c r="H58" s="334">
         <f>Data!D56</f>
         <v>0</v>
       </c>
-      <c r="I58" s="318">
+      <c r="I58" s="334">
         <f>Data!E56</f>
         <v>0</v>
       </c>
-      <c r="J58" s="318">
+      <c r="J58" s="334">
         <f>Data!F56</f>
         <v>0</v>
       </c>
-      <c r="K58" s="318">
+      <c r="K58" s="334">
         <f>Data!G56</f>
         <v>0</v>
       </c>
-      <c r="L58" s="318">
+      <c r="L58" s="334">
         <f>Data!H56</f>
         <v>0</v>
       </c>
-      <c r="M58" s="318">
+      <c r="M58" s="334">
         <f>Data!I56</f>
         <v>0</v>
       </c>
-      <c r="N58" s="318">
+      <c r="N58" s="334">
         <f>Data!J56</f>
         <v>0</v>
       </c>
-      <c r="O58" s="318">
+      <c r="O58" s="334">
         <f>Data!K56</f>
         <v>0</v>
       </c>
-      <c r="P58" s="318" t="str">
+      <c r="P58" s="334" t="str">
         <f>Data!L56</f>
         <v/>
       </c>
-      <c r="Q58" s="318" t="str">
+      <c r="Q58" s="334" t="str">
         <f>Data!M56</f>
         <v/>
       </c>
@@ -11983,52 +11999,52 @@
       <c r="B59" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="C59" s="318">
+      <c r="C59" s="334">
         <f>BS!$C68*C67</f>
         <v>0</v>
       </c>
       <c r="E59" s="268"/>
-      <c r="G59" s="318">
+      <c r="G59" s="334">
         <f>Data!C55</f>
         <v>0</v>
       </c>
-      <c r="H59" s="318">
+      <c r="H59" s="334">
         <f>Data!D55</f>
         <v>0</v>
       </c>
-      <c r="I59" s="318">
+      <c r="I59" s="334">
         <f>Data!E55</f>
         <v>0</v>
       </c>
-      <c r="J59" s="318">
+      <c r="J59" s="334">
         <f>Data!F55</f>
         <v>0</v>
       </c>
-      <c r="K59" s="318">
+      <c r="K59" s="334">
         <f>Data!G55</f>
         <v>0</v>
       </c>
-      <c r="L59" s="318">
+      <c r="L59" s="334">
         <f>Data!H55</f>
         <v>0</v>
       </c>
-      <c r="M59" s="318">
+      <c r="M59" s="334">
         <f>Data!I55</f>
         <v>0</v>
       </c>
-      <c r="N59" s="318">
+      <c r="N59" s="334">
         <f>Data!J55</f>
         <v>0</v>
       </c>
-      <c r="O59" s="318">
+      <c r="O59" s="334">
         <f>Data!K55</f>
         <v>0</v>
       </c>
-      <c r="P59" s="318" t="str">
+      <c r="P59" s="334" t="str">
         <f>Data!L55</f>
         <v/>
       </c>
-      <c r="Q59" s="318" t="str">
+      <c r="Q59" s="334" t="str">
         <f>Data!M55</f>
         <v/>
       </c>
@@ -12038,52 +12054,52 @@
       <c r="B60" s="40" t="s">
         <v>159</v>
       </c>
-      <c r="C60" s="318">
+      <c r="C60" s="334">
         <f>BS!$C69*C68</f>
         <v>0</v>
       </c>
       <c r="E60" s="268"/>
-      <c r="G60" s="318">
+      <c r="G60" s="334">
         <f>Data!C57</f>
         <v>0</v>
       </c>
-      <c r="H60" s="318">
+      <c r="H60" s="334">
         <f>Data!D57</f>
         <v>0</v>
       </c>
-      <c r="I60" s="318">
+      <c r="I60" s="334">
         <f>Data!E57</f>
         <v>0</v>
       </c>
-      <c r="J60" s="318">
+      <c r="J60" s="334">
         <f>Data!F57</f>
         <v>0</v>
       </c>
-      <c r="K60" s="318">
+      <c r="K60" s="334">
         <f>Data!G57</f>
         <v>0</v>
       </c>
-      <c r="L60" s="318">
+      <c r="L60" s="334">
         <f>Data!H57</f>
         <v>0</v>
       </c>
-      <c r="M60" s="318">
+      <c r="M60" s="334">
         <f>Data!I57</f>
         <v>0</v>
       </c>
-      <c r="N60" s="318">
+      <c r="N60" s="334">
         <f>Data!J57</f>
         <v>0</v>
       </c>
-      <c r="O60" s="318">
+      <c r="O60" s="334">
         <f>Data!K57</f>
         <v>0</v>
       </c>
-      <c r="P60" s="318" t="str">
+      <c r="P60" s="334" t="str">
         <f>Data!L57</f>
         <v/>
       </c>
-      <c r="Q60" s="318" t="str">
+      <c r="Q60" s="334" t="str">
         <f>Data!M57</f>
         <v/>
       </c>
@@ -12093,52 +12109,52 @@
       <c r="B61" s="31" t="s">
         <v>195</v>
       </c>
-      <c r="C61" s="319">
+      <c r="C61" s="335">
         <f>SUM(C58:C60)</f>
         <v>0</v>
       </c>
       <c r="E61" s="268"/>
-      <c r="G61" s="319">
+      <c r="G61" s="335">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
         <v>0</v>
       </c>
-      <c r="H61" s="319">
+      <c r="H61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="I61" s="319">
+      <c r="I61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="J61" s="319">
+      <c r="J61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="K61" s="319">
+      <c r="K61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="L61" s="319">
+      <c r="L61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="M61" s="319">
+      <c r="M61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="N61" s="319">
+      <c r="N61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="O61" s="319">
+      <c r="O61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="P61" s="319" t="str">
+      <c r="P61" s="335" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="Q61" s="319" t="str">
+      <c r="Q61" s="335" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -12148,53 +12164,53 @@
       <c r="B62" s="40" t="s">
         <v>161</v>
       </c>
-      <c r="C62" s="330">
+      <c r="C62" s="349">
         <v>0</v>
       </c>
       <c r="E62" s="266" t="s">
         <v>338</v>
       </c>
-      <c r="G62" s="318">
+      <c r="G62" s="334">
         <f>Data!C58</f>
         <v>56115</v>
       </c>
-      <c r="H62" s="318">
+      <c r="H62" s="334">
         <f>Data!D58</f>
         <v>45962</v>
       </c>
-      <c r="I62" s="318">
+      <c r="I62" s="334">
         <f>Data!E58</f>
         <v>93607</v>
       </c>
-      <c r="J62" s="318">
+      <c r="J62" s="334">
         <f>Data!F58</f>
         <v>47267</v>
       </c>
-      <c r="K62" s="318">
+      <c r="K62" s="334">
         <f>Data!G58</f>
         <v>-13941</v>
       </c>
-      <c r="L62" s="318">
+      <c r="L62" s="334">
         <f>Data!H58</f>
         <v>34492</v>
       </c>
-      <c r="M62" s="318">
+      <c r="M62" s="334">
         <f>Data!I58</f>
         <v>41506</v>
       </c>
-      <c r="N62" s="318">
+      <c r="N62" s="334">
         <f>Data!J58</f>
         <v>22726</v>
       </c>
-      <c r="O62" s="318">
+      <c r="O62" s="334">
         <f>Data!K58</f>
         <v>40583</v>
       </c>
-      <c r="P62" s="318" t="str">
+      <c r="P62" s="334" t="str">
         <f>Data!L58</f>
         <v/>
       </c>
-      <c r="Q62" s="318" t="str">
+      <c r="Q62" s="334" t="str">
         <f>Data!M58</f>
         <v/>
       </c>
@@ -12204,52 +12220,52 @@
       <c r="B63" s="31" t="s">
         <v>196</v>
       </c>
-      <c r="C63" s="319">
+      <c r="C63" s="335">
         <f>C61+C62</f>
         <v>0</v>
       </c>
       <c r="E63" s="268"/>
-      <c r="G63" s="319">
+      <c r="G63" s="335">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
         <v>56115</v>
       </c>
-      <c r="H63" s="319">
+      <c r="H63" s="335">
         <f t="shared" si="23"/>
         <v>45962</v>
       </c>
-      <c r="I63" s="319">
+      <c r="I63" s="335">
         <f t="shared" si="23"/>
         <v>93607</v>
       </c>
-      <c r="J63" s="319">
+      <c r="J63" s="335">
         <f t="shared" si="23"/>
         <v>47267</v>
       </c>
-      <c r="K63" s="319">
+      <c r="K63" s="335">
         <f t="shared" si="23"/>
         <v>-13941</v>
       </c>
-      <c r="L63" s="319">
+      <c r="L63" s="335">
         <f t="shared" si="23"/>
         <v>34492</v>
       </c>
-      <c r="M63" s="319">
+      <c r="M63" s="335">
         <f t="shared" si="23"/>
         <v>41506</v>
       </c>
-      <c r="N63" s="319">
+      <c r="N63" s="335">
         <f t="shared" si="23"/>
         <v>22726</v>
       </c>
-      <c r="O63" s="319">
+      <c r="O63" s="335">
         <f t="shared" si="23"/>
         <v>40583</v>
       </c>
-      <c r="P63" s="319" t="str">
+      <c r="P63" s="335" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="Q63" s="319" t="str">
+      <c r="Q63" s="335" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
@@ -13624,54 +13640,54 @@
       <c r="B101" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C101" s="331">
+      <c r="C101" s="350">
         <f>BS!G32</f>
         <v>2565063</v>
       </c>
       <c r="D101" s="26"/>
       <c r="E101" s="269"/>
       <c r="F101" s="26"/>
-      <c r="G101" s="323">
+      <c r="G101" s="339">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
         <v>2565063</v>
       </c>
-      <c r="H101" s="323">
+      <c r="H101" s="339">
         <f t="shared" si="42"/>
         <v>2619258</v>
       </c>
-      <c r="I101" s="323">
+      <c r="I101" s="339">
         <f t="shared" si="42"/>
         <v>2879275</v>
       </c>
-      <c r="J101" s="323">
+      <c r="J101" s="339">
         <f t="shared" si="42"/>
         <v>2727530</v>
       </c>
-      <c r="K101" s="323">
+      <c r="K101" s="339">
         <f t="shared" si="42"/>
         <v>2513621</v>
       </c>
-      <c r="L101" s="323">
+      <c r="L101" s="339">
         <f t="shared" si="42"/>
         <v>2408229</v>
       </c>
-      <c r="M101" s="323">
+      <c r="M101" s="339">
         <f t="shared" si="42"/>
         <v>2539937</v>
       </c>
-      <c r="N101" s="323">
+      <c r="N101" s="339">
         <f t="shared" si="42"/>
         <v>2354738</v>
       </c>
-      <c r="O101" s="323">
+      <c r="O101" s="339">
         <f t="shared" si="42"/>
         <v>2533582</v>
       </c>
-      <c r="P101" s="323" t="str">
+      <c r="P101" s="339" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="Q101" s="323" t="str">
+      <c r="Q101" s="339" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
@@ -13681,54 +13697,54 @@
       <c r="B102" s="93" t="s">
         <v>211</v>
       </c>
-      <c r="C102" s="332">
+      <c r="C102" s="351">
         <f>BS!C4</f>
         <v>348607</v>
       </c>
       <c r="D102" s="89"/>
       <c r="E102" s="270"/>
       <c r="F102" s="89"/>
-      <c r="G102" s="333">
+      <c r="G102" s="352">
         <f>IF(G$4="","",Data!D77)</f>
         <v>262508</v>
       </c>
-      <c r="H102" s="333">
+      <c r="H102" s="352">
         <f>IF(H$4="","",Data!E77)</f>
         <v>179615</v>
       </c>
-      <c r="I102" s="333">
+      <c r="I102" s="352">
         <f>IF(I$4="","",Data!F77)</f>
         <v>260527</v>
       </c>
-      <c r="J102" s="333">
+      <c r="J102" s="352">
         <f>IF(J$4="","",Data!G77)</f>
         <v>80876</v>
       </c>
-      <c r="K102" s="333">
+      <c r="K102" s="352">
         <f>IF(K$4="","",Data!H77)</f>
         <v>86046</v>
       </c>
-      <c r="L102" s="333">
+      <c r="L102" s="352">
         <f>IF(L$4="","",Data!I77)</f>
         <v>0</v>
       </c>
-      <c r="M102" s="333">
+      <c r="M102" s="352">
         <f>IF(M$4="","",Data!J77)</f>
         <v>0</v>
       </c>
-      <c r="N102" s="333">
+      <c r="N102" s="352">
         <f>IF(N$4="","",Data!K77)</f>
         <v>0</v>
       </c>
-      <c r="O102" s="333">
+      <c r="O102" s="352">
         <f>IF(O$4="","",Data!L77)</f>
         <v>0</v>
       </c>
-      <c r="P102" s="333" t="str">
+      <c r="P102" s="352" t="str">
         <f>IF(P$4="","",Data!M77)</f>
         <v/>
       </c>
-      <c r="Q102" s="333" t="str">
+      <c r="Q102" s="352" t="str">
         <f>IF(Q$4="","",Data!N77)</f>
         <v/>
       </c>
@@ -13738,54 +13754,54 @@
       <c r="B103" s="93" t="s">
         <v>212</v>
       </c>
-      <c r="C103" s="332">
+      <c r="C103" s="351">
         <f>BS!C6+BS!C7</f>
         <v>506592</v>
       </c>
       <c r="D103" s="89"/>
       <c r="E103" s="270"/>
       <c r="F103" s="89"/>
-      <c r="G103" s="333">
+      <c r="G103" s="352">
         <f>IF(G$4="","",Data!D78)</f>
         <v>422202</v>
       </c>
-      <c r="H103" s="333">
+      <c r="H103" s="352">
         <f>IF(H$4="","",Data!E78)</f>
         <v>483625</v>
       </c>
-      <c r="I103" s="333">
+      <c r="I103" s="352">
         <f>IF(I$4="","",Data!F78)</f>
         <v>622768</v>
       </c>
-      <c r="J103" s="333">
+      <c r="J103" s="352">
         <f>IF(J$4="","",Data!G78)</f>
         <v>798693</v>
       </c>
-      <c r="K103" s="333">
+      <c r="K103" s="352">
         <f>IF(K$4="","",Data!H78)</f>
         <v>823654</v>
       </c>
-      <c r="L103" s="333">
+      <c r="L103" s="352">
         <f>IF(L$4="","",Data!I78)</f>
         <v>0</v>
       </c>
-      <c r="M103" s="333">
+      <c r="M103" s="352">
         <f>IF(M$4="","",Data!J78)</f>
         <v>0</v>
       </c>
-      <c r="N103" s="333">
+      <c r="N103" s="352">
         <f>IF(N$4="","",Data!K78)</f>
         <v>0</v>
       </c>
-      <c r="O103" s="333">
+      <c r="O103" s="352">
         <f>IF(O$4="","",Data!L78)</f>
         <v>0</v>
       </c>
-      <c r="P103" s="333" t="str">
+      <c r="P103" s="352" t="str">
         <f>IF(P$4="","",Data!M78)</f>
         <v/>
       </c>
-      <c r="Q103" s="333" t="str">
+      <c r="Q103" s="352" t="str">
         <f>IF(Q$4="","",Data!N78)</f>
         <v/>
       </c>
@@ -13795,54 +13811,54 @@
       <c r="B104" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="C104" s="331">
+      <c r="C104" s="350">
         <f>BS!G30</f>
         <v>732882</v>
       </c>
       <c r="D104" s="26"/>
       <c r="E104" s="269"/>
       <c r="F104" s="26"/>
-      <c r="G104" s="323">
+      <c r="G104" s="339">
         <f>Data!C79</f>
         <v>732882</v>
       </c>
-      <c r="H104" s="323">
+      <c r="H104" s="339">
         <f>Data!D79</f>
         <v>723327</v>
       </c>
-      <c r="I104" s="323">
+      <c r="I104" s="339">
         <f>Data!E79</f>
         <v>843108</v>
       </c>
-      <c r="J104" s="323">
+      <c r="J104" s="339">
         <f>Data!F79</f>
         <v>736981</v>
       </c>
-      <c r="K104" s="323">
+      <c r="K104" s="339">
         <f>Data!G79</f>
         <v>430335</v>
       </c>
-      <c r="L104" s="323">
+      <c r="L104" s="339">
         <f>Data!H79</f>
         <v>194628</v>
       </c>
-      <c r="M104" s="323">
+      <c r="M104" s="339">
         <f>Data!I79</f>
         <v>222985</v>
       </c>
-      <c r="N104" s="323">
+      <c r="N104" s="339">
         <f>Data!J79</f>
         <v>207724</v>
       </c>
-      <c r="O104" s="323">
+      <c r="O104" s="339">
         <f>Data!K79</f>
         <v>376010</v>
       </c>
-      <c r="P104" s="323" t="str">
+      <c r="P104" s="339" t="str">
         <f>Data!L79</f>
         <v/>
       </c>
-      <c r="Q104" s="323" t="str">
+      <c r="Q104" s="339" t="str">
         <f>Data!M79</f>
         <v/>
       </c>
@@ -13852,54 +13868,54 @@
       <c r="B105" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="C105" s="331">
+      <c r="C105" s="350">
         <f>BS!G27</f>
         <v>1832181</v>
       </c>
       <c r="D105" s="26"/>
       <c r="E105" s="269"/>
       <c r="F105" s="26"/>
-      <c r="G105" s="323">
+      <c r="G105" s="339">
         <f>Data!C80</f>
         <v>1832181</v>
       </c>
-      <c r="H105" s="323">
+      <c r="H105" s="339">
         <f>Data!D80</f>
         <v>1895931</v>
       </c>
-      <c r="I105" s="323">
+      <c r="I105" s="339">
         <f>Data!E80</f>
         <v>2036167</v>
       </c>
-      <c r="J105" s="323">
+      <c r="J105" s="339">
         <f>Data!F80</f>
         <v>1990549</v>
       </c>
-      <c r="K105" s="323">
+      <c r="K105" s="339">
         <f>Data!G80</f>
         <v>2083286</v>
       </c>
-      <c r="L105" s="323">
+      <c r="L105" s="339">
         <f>Data!H80</f>
         <v>2213601</v>
       </c>
-      <c r="M105" s="323">
+      <c r="M105" s="339">
         <f>Data!I80</f>
         <v>2316952</v>
       </c>
-      <c r="N105" s="323">
+      <c r="N105" s="339">
         <f>Data!J80</f>
         <v>2147014</v>
       </c>
-      <c r="O105" s="323">
+      <c r="O105" s="339">
         <f>Data!K80</f>
         <v>2157572</v>
       </c>
-      <c r="P105" s="323" t="str">
+      <c r="P105" s="339" t="str">
         <f>Data!L80</f>
         <v/>
       </c>
-      <c r="Q105" s="323" t="str">
+      <c r="Q105" s="339" t="str">
         <f>Data!M80</f>
         <v/>
       </c>
@@ -15397,7 +15413,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:H94"/>
+  <dimension ref="A2:Q105"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
@@ -15436,7 +15452,7 @@
       <c r="B4" s="100" t="s">
         <v>129</v>
       </c>
-      <c r="C4" s="114">
+      <c r="C4" s="344">
         <f>Normalized_FCF!C19</f>
         <v>138391.47791159325</v>
       </c>
@@ -15468,7 +15484,7 @@
       <c r="B6" s="149" t="s">
         <v>229</v>
       </c>
-      <c r="C6" s="338">
+      <c r="C6" s="353">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
         <v>1845219.70548791</v>
       </c>
@@ -15476,17 +15492,17 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="356" t="s">
+      <c r="E6" s="365" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="356"/>
+      <c r="F6" s="365"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
       <c r="B7" s="148" t="s">
         <v>225</v>
       </c>
-      <c r="C7" s="114">
+      <c r="C7" s="344">
         <f>BS!G31</f>
         <v>195066</v>
       </c>
@@ -15494,15 +15510,15 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="356"/>
-      <c r="F7" s="356"/>
+      <c r="E7" s="365"/>
+      <c r="F7" s="365"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="148" t="s">
         <v>226</v>
       </c>
-      <c r="C8" s="114">
+      <c r="C8" s="344">
         <f>BS!D66</f>
         <v>587281.82009631116</v>
       </c>
@@ -15510,15 +15526,15 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="356"/>
-      <c r="F8" s="356"/>
+      <c r="E8" s="365"/>
+      <c r="F8" s="365"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="205" t="s">
         <v>191</v>
       </c>
-      <c r="C9" s="339">
+      <c r="C9" s="354">
         <f>BS!H42</f>
         <v>18907.900000000001</v>
       </c>
@@ -15526,15 +15542,15 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
+      <c r="E9" s="365"/>
+      <c r="F9" s="365"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="149" t="s">
         <v>228</v>
       </c>
-      <c r="C10" s="338">
+      <c r="C10" s="353">
         <f>C6-C7+C8+C9</f>
         <v>2256343.4255842208</v>
       </c>
@@ -15601,7 +15617,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:8" ht="13.25" customHeight="1">
+    <row r="17" spans="2:17" ht="13.25" customHeight="1">
       <c r="B17" s="118" t="s">
         <v>135</v>
       </c>
@@ -15611,7 +15627,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:8" ht="13.25" customHeight="1">
+    <row r="18" spans="2:17" ht="13.25" customHeight="1">
       <c r="B18" s="153" t="s">
         <v>107</v>
       </c>
@@ -15625,10 +15641,10 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:8">
+    <row r="19" spans="2:17">
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:8" ht="13.15">
+    <row r="20" spans="2:17" ht="13.15">
       <c r="B20" s="128" t="s">
         <v>108</v>
       </c>
@@ -15646,7 +15662,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:8">
+    <row r="21" spans="2:17">
       <c r="B21" s="122">
         <v>1</v>
       </c>
@@ -15668,7 +15684,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:8">
+    <row r="22" spans="2:17">
       <c r="B22" s="122">
         <v>2</v>
       </c>
@@ -15690,7 +15706,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:8">
+    <row r="23" spans="2:17">
       <c r="B23" s="122">
         <v>3</v>
       </c>
@@ -15710,9 +15726,19 @@
         <f t="shared" si="1"/>
         <v>127701.16603798557</v>
       </c>
-      <c r="H23" s="120"/>
-    </row>
-    <row r="24" spans="2:8">
+      <c r="G23" s="344"/>
+      <c r="H23" s="345"/>
+      <c r="I23" s="344"/>
+      <c r="J23" s="344"/>
+      <c r="K23" s="344"/>
+      <c r="L23" s="344"/>
+      <c r="M23" s="344"/>
+      <c r="N23" s="344"/>
+      <c r="O23" s="344"/>
+      <c r="P23" s="344"/>
+      <c r="Q23" s="344"/>
+    </row>
+    <row r="24" spans="2:17">
       <c r="B24" s="122">
         <v>4</v>
       </c>
@@ -15732,9 +15758,19 @@
         <f t="shared" si="1"/>
         <v>124324.49428717894</v>
       </c>
-      <c r="H24" s="120"/>
-    </row>
-    <row r="25" spans="2:8">
+      <c r="G24" s="344"/>
+      <c r="H24" s="345"/>
+      <c r="I24" s="344"/>
+      <c r="J24" s="344"/>
+      <c r="K24" s="344"/>
+      <c r="L24" s="344"/>
+      <c r="M24" s="344"/>
+      <c r="N24" s="344"/>
+      <c r="O24" s="344"/>
+      <c r="P24" s="344"/>
+      <c r="Q24" s="344"/>
+    </row>
+    <row r="25" spans="2:17">
       <c r="B25" s="122">
         <v>5</v>
       </c>
@@ -15754,9 +15790,19 @@
         <f t="shared" si="1"/>
         <v>121037.10842518952</v>
       </c>
-      <c r="H25" s="120"/>
-    </row>
-    <row r="26" spans="2:8">
+      <c r="G25" s="344"/>
+      <c r="H25" s="345"/>
+      <c r="I25" s="344"/>
+      <c r="J25" s="344"/>
+      <c r="K25" s="344"/>
+      <c r="L25" s="344"/>
+      <c r="M25" s="344"/>
+      <c r="N25" s="344"/>
+      <c r="O25" s="344"/>
+      <c r="P25" s="344"/>
+      <c r="Q25" s="344"/>
+    </row>
+    <row r="26" spans="2:17">
       <c r="B26" s="122">
         <v>6</v>
       </c>
@@ -15778,7 +15824,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:8">
+    <row r="27" spans="2:17">
       <c r="B27" s="122">
         <v>7</v>
       </c>
@@ -15800,7 +15846,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:8">
+    <row r="28" spans="2:17">
       <c r="B28" s="122">
         <v>8</v>
       </c>
@@ -15822,7 +15868,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:8">
+    <row r="29" spans="2:17">
       <c r="B29" s="122">
         <v>9</v>
       </c>
@@ -15844,7 +15890,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:8">
+    <row r="30" spans="2:17">
       <c r="B30" s="122">
         <v>10</v>
       </c>
@@ -15866,7 +15912,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:8">
+    <row r="31" spans="2:17">
       <c r="B31" s="122">
         <v>11</v>
       </c>
@@ -15888,7 +15934,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:8">
+    <row r="32" spans="2:17">
       <c r="B32" s="122">
         <v>12</v>
       </c>
@@ -15910,11 +15956,11 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:8">
+    <row r="33" spans="2:17">
       <c r="B33" s="122">
         <v>13</v>
       </c>
-      <c r="C33" s="123">
+      <c r="C33" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -15930,13 +15976,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H33" s="120"/>
-    </row>
-    <row r="34" spans="2:8">
+      <c r="G33" s="344"/>
+      <c r="H33" s="345"/>
+      <c r="I33" s="344"/>
+      <c r="J33" s="344"/>
+      <c r="K33" s="344"/>
+      <c r="L33" s="344"/>
+      <c r="M33" s="344"/>
+      <c r="N33" s="344"/>
+      <c r="O33" s="344"/>
+      <c r="P33" s="344"/>
+      <c r="Q33" s="344"/>
+    </row>
+    <row r="34" spans="2:17">
       <c r="B34" s="122">
         <v>14</v>
       </c>
-      <c r="C34" s="123">
+      <c r="C34" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -15952,13 +16008,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H34" s="120"/>
-    </row>
-    <row r="35" spans="2:8">
+      <c r="G34" s="344"/>
+      <c r="H34" s="345"/>
+      <c r="I34" s="344"/>
+      <c r="J34" s="344"/>
+      <c r="K34" s="344"/>
+      <c r="L34" s="344"/>
+      <c r="M34" s="344"/>
+      <c r="N34" s="344"/>
+      <c r="O34" s="344"/>
+      <c r="P34" s="344"/>
+      <c r="Q34" s="344"/>
+    </row>
+    <row r="35" spans="2:17">
       <c r="B35" s="122">
         <v>15</v>
       </c>
-      <c r="C35" s="123">
+      <c r="C35" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -15974,9 +16040,19 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H35" s="120"/>
-    </row>
-    <row r="36" spans="2:8">
+      <c r="G35" s="344"/>
+      <c r="H35" s="345"/>
+      <c r="I35" s="344"/>
+      <c r="J35" s="344"/>
+      <c r="K35" s="344"/>
+      <c r="L35" s="344"/>
+      <c r="M35" s="344"/>
+      <c r="N35" s="344"/>
+      <c r="O35" s="344"/>
+      <c r="P35" s="344"/>
+      <c r="Q35" s="344"/>
+    </row>
+    <row r="36" spans="2:17">
       <c r="B36" s="122">
         <v>16</v>
       </c>
@@ -15998,7 +16074,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:8">
+    <row r="37" spans="2:17">
       <c r="B37" s="122">
         <v>17</v>
       </c>
@@ -16020,7 +16096,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:8">
+    <row r="38" spans="2:17">
       <c r="B38" s="122">
         <v>18</v>
       </c>
@@ -16042,7 +16118,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:8">
+    <row r="39" spans="2:17">
       <c r="B39" s="122">
         <v>19</v>
       </c>
@@ -16064,7 +16140,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:8">
+    <row r="40" spans="2:17">
       <c r="B40" s="122">
         <v>20</v>
       </c>
@@ -16086,7 +16162,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:8">
+    <row r="41" spans="2:17">
       <c r="B41" s="122">
         <v>21</v>
       </c>
@@ -16108,7 +16184,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:8">
+    <row r="42" spans="2:17">
       <c r="B42" s="122">
         <v>22</v>
       </c>
@@ -16130,7 +16206,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:8">
+    <row r="43" spans="2:17">
       <c r="B43" s="122">
         <v>23</v>
       </c>
@@ -16152,7 +16228,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:8">
+    <row r="44" spans="2:17">
       <c r="B44" s="122">
         <v>24</v>
       </c>
@@ -16174,7 +16250,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:8">
+    <row r="45" spans="2:17">
       <c r="B45" s="122">
         <v>25</v>
       </c>
@@ -16196,7 +16272,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:8">
+    <row r="46" spans="2:17">
       <c r="B46" s="122">
         <v>26</v>
       </c>
@@ -16218,11 +16294,11 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:8">
+    <row r="47" spans="2:17">
       <c r="B47" s="122">
         <v>27</v>
       </c>
-      <c r="C47" s="123">
+      <c r="C47" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16238,13 +16314,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H47" s="120"/>
-    </row>
-    <row r="48" spans="2:8">
+      <c r="G47" s="344"/>
+      <c r="H47" s="345"/>
+      <c r="I47" s="344"/>
+      <c r="J47" s="344"/>
+      <c r="K47" s="344"/>
+      <c r="L47" s="344"/>
+      <c r="M47" s="344"/>
+      <c r="N47" s="344"/>
+      <c r="O47" s="344"/>
+      <c r="P47" s="344"/>
+      <c r="Q47" s="344"/>
+    </row>
+    <row r="48" spans="2:17">
       <c r="B48" s="122">
         <v>28</v>
       </c>
-      <c r="C48" s="123">
+      <c r="C48" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16260,13 +16346,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H48" s="120"/>
-    </row>
-    <row r="49" spans="1:8">
+      <c r="G48" s="344"/>
+      <c r="H48" s="345"/>
+      <c r="I48" s="344"/>
+      <c r="J48" s="344"/>
+      <c r="K48" s="344"/>
+      <c r="L48" s="344"/>
+      <c r="M48" s="344"/>
+      <c r="N48" s="344"/>
+      <c r="O48" s="344"/>
+      <c r="P48" s="344"/>
+      <c r="Q48" s="344"/>
+    </row>
+    <row r="49" spans="1:17">
       <c r="B49" s="122">
         <v>29</v>
       </c>
-      <c r="C49" s="123">
+      <c r="C49" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16282,13 +16378,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H49" s="120"/>
-    </row>
-    <row r="50" spans="1:8">
+      <c r="G49" s="344"/>
+      <c r="H49" s="345"/>
+      <c r="I49" s="344"/>
+      <c r="J49" s="344"/>
+      <c r="K49" s="344"/>
+      <c r="L49" s="344"/>
+      <c r="M49" s="344"/>
+      <c r="N49" s="344"/>
+      <c r="O49" s="344"/>
+      <c r="P49" s="344"/>
+      <c r="Q49" s="344"/>
+    </row>
+    <row r="50" spans="1:17">
       <c r="B50" s="122">
         <v>30</v>
       </c>
-      <c r="C50" s="123">
+      <c r="C50" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16304,9 +16410,19 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H50" s="120"/>
-    </row>
-    <row r="51" spans="1:8">
+      <c r="G50" s="344"/>
+      <c r="H50" s="345"/>
+      <c r="I50" s="344"/>
+      <c r="J50" s="344"/>
+      <c r="K50" s="344"/>
+      <c r="L50" s="344"/>
+      <c r="M50" s="344"/>
+      <c r="N50" s="344"/>
+      <c r="O50" s="344"/>
+      <c r="P50" s="344"/>
+      <c r="Q50" s="344"/>
+    </row>
+    <row r="51" spans="1:17">
       <c r="B51" s="126" t="s">
         <v>132</v>
       </c>
@@ -16328,7 +16444,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:17">
       <c r="C52" s="114"/>
       <c r="E52" s="127" t="s">
         <v>101</v>
@@ -16339,11 +16455,11 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:17">
       <c r="C53" s="114"/>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:8" ht="13.15">
+    <row r="54" spans="1:17" ht="13.15">
       <c r="B54" s="119" t="s">
         <v>130</v>
       </c>
@@ -16353,7 +16469,7 @@
       <c r="F54" s="117"/>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:8" ht="13.15">
+    <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
         <v>2134789.7838004301</v>
@@ -16380,7 +16496,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:8" ht="13.15">
+    <row r="56" spans="1:17" ht="13.15">
       <c r="A56" s="143">
         <v>5</v>
       </c>
@@ -16402,7 +16518,7 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:8" ht="13.15">
+    <row r="57" spans="1:17" ht="13.15">
       <c r="A57" s="143">
         <v>10</v>
       </c>
@@ -16423,14 +16539,14 @@
       </c>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:8" ht="13.15">
+    <row r="58" spans="1:17" ht="13.15">
       <c r="A58" s="143">
         <v>15</v>
       </c>
       <c r="B58" s="123">
         <v>1845219.7054879102</v>
       </c>
-      <c r="C58" s="123">
+      <c r="C58" s="347">
         <v>2035219.4517333307</v>
       </c>
       <c r="D58" s="123">
@@ -16442,16 +16558,26 @@
       <c r="F58" s="123">
         <v>3193331.3278640071</v>
       </c>
-      <c r="H58" s="120"/>
-    </row>
-    <row r="59" spans="1:8" ht="13.15">
+      <c r="G58" s="344"/>
+      <c r="H58" s="345"/>
+      <c r="I58" s="344"/>
+      <c r="J58" s="344"/>
+      <c r="K58" s="344"/>
+      <c r="L58" s="344"/>
+      <c r="M58" s="344"/>
+      <c r="N58" s="344"/>
+      <c r="O58" s="344"/>
+      <c r="P58" s="344"/>
+      <c r="Q58" s="344"/>
+    </row>
+    <row r="59" spans="1:17" ht="13.15">
       <c r="A59" s="144">
         <v>20</v>
       </c>
       <c r="B59" s="123">
         <v>1845219.7054879109</v>
       </c>
-      <c r="C59" s="123">
+      <c r="C59" s="347">
         <v>2111806.7723140484</v>
       </c>
       <c r="D59" s="123">
@@ -16463,16 +16589,26 @@
       <c r="F59" s="123">
         <v>4032363.9187480891</v>
       </c>
-      <c r="H59" s="120"/>
-    </row>
-    <row r="60" spans="1:8" ht="13.15">
+      <c r="G59" s="344"/>
+      <c r="H59" s="345"/>
+      <c r="I59" s="344"/>
+      <c r="J59" s="344"/>
+      <c r="K59" s="344"/>
+      <c r="L59" s="344"/>
+      <c r="M59" s="344"/>
+      <c r="N59" s="344"/>
+      <c r="O59" s="344"/>
+      <c r="P59" s="344"/>
+      <c r="Q59" s="344"/>
+    </row>
+    <row r="60" spans="1:17" ht="13.15">
       <c r="A60" s="144">
         <v>25</v>
       </c>
       <c r="B60" s="123">
         <v>1845219.7054879111</v>
       </c>
-      <c r="C60" s="123">
+      <c r="C60" s="347">
         <v>2184700.2252792544</v>
       </c>
       <c r="D60" s="123">
@@ -16484,16 +16620,26 @@
       <c r="F60" s="123">
         <v>5062122.4857187551</v>
       </c>
-      <c r="H60" s="120"/>
-    </row>
-    <row r="61" spans="1:8" ht="13.15">
+      <c r="G60" s="344"/>
+      <c r="H60" s="345"/>
+      <c r="I60" s="344"/>
+      <c r="J60" s="344"/>
+      <c r="K60" s="344"/>
+      <c r="L60" s="344"/>
+      <c r="M60" s="344"/>
+      <c r="N60" s="344"/>
+      <c r="O60" s="344"/>
+      <c r="P60" s="344"/>
+      <c r="Q60" s="344"/>
+    </row>
+    <row r="61" spans="1:17" ht="13.15">
       <c r="A61" s="144">
         <v>30</v>
       </c>
       <c r="B61" s="123">
         <v>1845219.7054879111</v>
       </c>
-      <c r="C61" s="123">
+      <c r="C61" s="347">
         <v>2250506.6958236932</v>
       </c>
       <c r="D61" s="123">
@@ -16505,26 +16651,56 @@
       <c r="F61" s="123">
         <v>6278979.7610744182</v>
       </c>
-      <c r="H61" s="120"/>
-    </row>
-    <row r="62" spans="1:8">
-      <c r="C62" s="114"/>
+      <c r="G61" s="344"/>
+      <c r="H61" s="345"/>
+      <c r="I61" s="344"/>
+      <c r="J61" s="344"/>
+      <c r="K61" s="344"/>
+      <c r="L61" s="344"/>
+      <c r="M61" s="344"/>
+      <c r="N61" s="344"/>
+      <c r="O61" s="344"/>
+      <c r="P61" s="344"/>
+      <c r="Q61" s="344"/>
+    </row>
+    <row r="62" spans="1:17">
+      <c r="C62" s="344"/>
       <c r="D62" s="114"/>
       <c r="E62" s="114"/>
       <c r="F62" s="114"/>
-      <c r="H62" s="120"/>
-    </row>
-    <row r="63" spans="1:8" ht="13.15">
+      <c r="G62" s="344"/>
+      <c r="H62" s="345"/>
+      <c r="I62" s="344"/>
+      <c r="J62" s="344"/>
+      <c r="K62" s="344"/>
+      <c r="L62" s="344"/>
+      <c r="M62" s="344"/>
+      <c r="N62" s="344"/>
+      <c r="O62" s="344"/>
+      <c r="P62" s="344"/>
+      <c r="Q62" s="344"/>
+    </row>
+    <row r="63" spans="1:17" ht="13.15">
       <c r="B63" s="119" t="s">
         <v>131</v>
       </c>
-      <c r="C63" s="114"/>
+      <c r="C63" s="344"/>
       <c r="D63" s="114"/>
       <c r="E63" s="114"/>
       <c r="F63" s="114"/>
-      <c r="H63" s="120"/>
-    </row>
-    <row r="64" spans="1:8" ht="13.15">
+      <c r="G63" s="344"/>
+      <c r="H63" s="345"/>
+      <c r="I63" s="344"/>
+      <c r="J63" s="344"/>
+      <c r="K63" s="344"/>
+      <c r="L63" s="344"/>
+      <c r="M63" s="344"/>
+      <c r="N63" s="344"/>
+      <c r="O63" s="344"/>
+      <c r="P63" s="344"/>
+      <c r="Q63" s="344"/>
+    </row>
+    <row r="64" spans="1:17" ht="13.15">
       <c r="B64" s="132">
         <f>B55</f>
         <v>0</v>
@@ -16896,6 +17072,76 @@
     </row>
     <row r="94" spans="3:3">
       <c r="C94" s="115"/>
+    </row>
+    <row r="101" spans="3:17">
+      <c r="C101" s="344"/>
+      <c r="G101" s="344"/>
+      <c r="H101" s="344"/>
+      <c r="I101" s="344"/>
+      <c r="J101" s="344"/>
+      <c r="K101" s="344"/>
+      <c r="L101" s="344"/>
+      <c r="M101" s="344"/>
+      <c r="N101" s="344"/>
+      <c r="O101" s="344"/>
+      <c r="P101" s="344"/>
+      <c r="Q101" s="344"/>
+    </row>
+    <row r="102" spans="3:17">
+      <c r="C102" s="344"/>
+      <c r="G102" s="344"/>
+      <c r="H102" s="344"/>
+      <c r="I102" s="344"/>
+      <c r="J102" s="344"/>
+      <c r="K102" s="344"/>
+      <c r="L102" s="344"/>
+      <c r="M102" s="344"/>
+      <c r="N102" s="344"/>
+      <c r="O102" s="344"/>
+      <c r="P102" s="344"/>
+      <c r="Q102" s="344"/>
+    </row>
+    <row r="103" spans="3:17">
+      <c r="C103" s="344"/>
+      <c r="G103" s="344"/>
+      <c r="H103" s="344"/>
+      <c r="I103" s="344"/>
+      <c r="J103" s="344"/>
+      <c r="K103" s="344"/>
+      <c r="L103" s="344"/>
+      <c r="M103" s="344"/>
+      <c r="N103" s="344"/>
+      <c r="O103" s="344"/>
+      <c r="P103" s="344"/>
+      <c r="Q103" s="344"/>
+    </row>
+    <row r="104" spans="3:17">
+      <c r="C104" s="344"/>
+      <c r="G104" s="344"/>
+      <c r="H104" s="344"/>
+      <c r="I104" s="344"/>
+      <c r="J104" s="344"/>
+      <c r="K104" s="344"/>
+      <c r="L104" s="344"/>
+      <c r="M104" s="344"/>
+      <c r="N104" s="344"/>
+      <c r="O104" s="344"/>
+      <c r="P104" s="344"/>
+      <c r="Q104" s="344"/>
+    </row>
+    <row r="105" spans="3:17">
+      <c r="C105" s="344"/>
+      <c r="G105" s="344"/>
+      <c r="H105" s="344"/>
+      <c r="I105" s="344"/>
+      <c r="J105" s="344"/>
+      <c r="K105" s="344"/>
+      <c r="L105" s="344"/>
+      <c r="M105" s="344"/>
+      <c r="N105" s="344"/>
+      <c r="O105" s="344"/>
+      <c r="P105" s="344"/>
+      <c r="Q105" s="344"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -16998,7 +17244,7 @@
       <c r="B6" s="149" t="s">
         <v>441</v>
       </c>
-      <c r="C6" s="338">
+      <c r="C6" s="325">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
         <v>831758.03562666674</v>
       </c>
@@ -17006,8 +17252,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="356"/>
-      <c r="F6" s="356"/>
+      <c r="E6" s="365"/>
+      <c r="F6" s="365"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
@@ -18464,7 +18710,7 @@
       <c r="B7" s="100" t="s">
         <v>276</v>
       </c>
-      <c r="C7" s="114">
+      <c r="C7" s="344">
         <f>Normalized_FCF!G8</f>
         <v>354022</v>
       </c>
@@ -18472,11 +18718,11 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="358" t="str">
+      <c r="E7" s="367" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 東方表行集團(0398.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="358"/>
+      <c r="F7" s="367"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -18489,7 +18735,7 @@
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
-      <c r="C8" s="114">
+      <c r="C8" s="344">
         <f>Normalized_FCF!G19</f>
         <v>194373</v>
       </c>
@@ -18497,8 +18743,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="358"/>
-      <c r="F8" s="358"/>
+      <c r="E8" s="367"/>
+      <c r="F8" s="367"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -18511,7 +18757,7 @@
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="114">
+      <c r="C9" s="344">
         <f>Normalized_FCF!C19</f>
         <v>138391.47791159325</v>
       </c>
@@ -18519,8 +18765,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="358"/>
-      <c r="F9" s="358"/>
+      <c r="E9" s="367"/>
+      <c r="F9" s="367"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -18530,8 +18776,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="358"/>
-      <c r="F10" s="358"/>
+      <c r="E10" s="367"/>
+      <c r="F10" s="367"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -18544,8 +18790,8 @@
       <c r="B11" s="159" t="s">
         <v>447</v>
       </c>
-      <c r="E11" s="358"/>
-      <c r="F11" s="358"/>
+      <c r="E11" s="367"/>
+      <c r="F11" s="367"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -18563,8 +18809,8 @@
         <v>1.2656410607081225E-2</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="358"/>
-      <c r="F12" s="358"/>
+      <c r="E12" s="367"/>
+      <c r="F12" s="367"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -18581,8 +18827,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>3.5687612277801151E-2</v>
       </c>
-      <c r="E13" s="358"/>
-      <c r="F13" s="358"/>
+      <c r="E13" s="367"/>
+      <c r="F13" s="367"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -18599,8 +18845,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>1.5957752466103425E-2</v>
       </c>
-      <c r="E14" s="358"/>
-      <c r="F14" s="358"/>
+      <c r="E14" s="367"/>
+      <c r="F14" s="367"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -18626,21 +18872,21 @@
       <c r="C18" s="150">
         <v>10</v>
       </c>
-      <c r="E18" s="358" t="s">
+      <c r="E18" s="367" t="s">
         <v>331</v>
       </c>
-      <c r="F18" s="359"/>
+      <c r="F18" s="368"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="359"/>
-      <c r="F19" s="359"/>
+      <c r="E19" s="368"/>
+      <c r="F19" s="368"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
         <v>304</v>
       </c>
-      <c r="E20" s="359"/>
-      <c r="F20" s="359"/>
+      <c r="E20" s="368"/>
+      <c r="F20" s="368"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -18654,8 +18900,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="359"/>
-      <c r="F21" s="359"/>
+      <c r="E21" s="368"/>
+      <c r="F21" s="368"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -18669,8 +18915,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="359"/>
-      <c r="F22" s="359"/>
+      <c r="E22" s="368"/>
+      <c r="F22" s="368"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
@@ -18690,8 +18936,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="357"/>
-      <c r="F25" s="357"/>
+      <c r="E25" s="366"/>
+      <c r="F25" s="366"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
@@ -18701,8 +18947,8 @@
         <v>0.04</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="357"/>
-      <c r="F26" s="357"/>
+      <c r="E26" s="366"/>
+      <c r="F26" s="366"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -18716,8 +18962,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="357"/>
-      <c r="F27" s="357"/>
+      <c r="E27" s="366"/>
+      <c r="F27" s="366"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -18727,8 +18973,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="357"/>
-      <c r="F28" s="357"/>
+      <c r="E28" s="366"/>
+      <c r="F28" s="366"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
@@ -18748,8 +18994,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="357"/>
-      <c r="F31" s="357"/>
+      <c r="E31" s="366"/>
+      <c r="F31" s="366"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
@@ -18759,8 +19005,8 @@
         <v>0.02</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="357"/>
-      <c r="F32" s="357"/>
+      <c r="E32" s="366"/>
+      <c r="F32" s="366"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -18774,8 +19020,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="357"/>
-      <c r="F33" s="357"/>
+      <c r="E33" s="366"/>
+      <c r="F33" s="366"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -18785,8 +19031,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="357"/>
-      <c r="F34" s="357"/>
+      <c r="E34" s="366"/>
+      <c r="F34" s="366"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
@@ -18806,8 +19052,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="357"/>
-      <c r="F37" s="357"/>
+      <c r="E37" s="366"/>
+      <c r="F37" s="366"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
@@ -18817,8 +19063,8 @@
         <v>0.06</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="357"/>
-      <c r="F38" s="357"/>
+      <c r="E38" s="366"/>
+      <c r="F38" s="366"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -18832,8 +19078,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="357"/>
-      <c r="F39" s="357"/>
+      <c r="E39" s="366"/>
+      <c r="F39" s="366"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -18844,8 +19090,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="E40" s="366"/>
+      <c r="F40" s="366"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -18907,8 +19153,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="357"/>
-      <c r="F49" s="357"/>
+      <c r="E49" s="366"/>
+      <c r="F49" s="366"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
@@ -18918,8 +19164,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="E50" s="366"/>
+      <c r="F50" s="366"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -18933,8 +19179,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="357"/>
-      <c r="F51" s="357"/>
+      <c r="E51" s="366"/>
+      <c r="F51" s="366"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -18944,8 +19190,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="357"/>
-      <c r="F52" s="357"/>
+      <c r="E52" s="366"/>
+      <c r="F52" s="366"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
@@ -18965,8 +19211,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="357"/>
-      <c r="F55" s="357"/>
+      <c r="E55" s="366"/>
+      <c r="F55" s="366"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
@@ -18976,8 +19222,8 @@
         <v>0.1</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="357"/>
-      <c r="F56" s="357"/>
+      <c r="E56" s="366"/>
+      <c r="F56" s="366"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -18991,8 +19237,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="357"/>
-      <c r="F57" s="357"/>
+      <c r="E57" s="366"/>
+      <c r="F57" s="366"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -19002,8 +19248,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="E58" s="366"/>
+      <c r="F58" s="366"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">

--- a/financial_models/opportunities/0398.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0398.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FAFC190-8E5D-4931-A42B-E80A9FFA5598}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9023315-EDC9-4668-A3E2-1833840B2FD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3895,29 +3895,29 @@
     <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4393,13 +4393,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="357" t="s">
+      <c r="B18" s="359" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="357"/>
-      <c r="D18" s="357"/>
-      <c r="E18" s="357"/>
-      <c r="F18" s="357"/>
+      <c r="C18" s="359"/>
+      <c r="D18" s="359"/>
+      <c r="E18" s="359"/>
+      <c r="F18" s="359"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4599,22 +4599,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="357" t="s">
+      <c r="B36" s="359" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="357"/>
-      <c r="D36" s="357"/>
-      <c r="E36" s="357"/>
-      <c r="F36" s="357"/>
+      <c r="C36" s="359"/>
+      <c r="D36" s="359"/>
+      <c r="E36" s="359"/>
+      <c r="F36" s="359"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="359" t="s">
+      <c r="B37" s="362" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="359"/>
-      <c r="D37" s="359"/>
-      <c r="E37" s="359"/>
-      <c r="F37" s="359"/>
+      <c r="C37" s="362"/>
+      <c r="D37" s="362"/>
+      <c r="E37" s="362"/>
+      <c r="F37" s="362"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4626,13 +4626,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="358" t="s">
+      <c r="B40" s="360" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="358"/>
-      <c r="D40" s="358"/>
-      <c r="E40" s="358"/>
-      <c r="F40" s="358"/>
+      <c r="C40" s="360"/>
+      <c r="D40" s="360"/>
+      <c r="E40" s="360"/>
+      <c r="F40" s="360"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4652,13 +4652,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="358" t="s">
+      <c r="B43" s="360" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="358"/>
-      <c r="D43" s="358"/>
-      <c r="E43" s="358"/>
-      <c r="F43" s="358"/>
+      <c r="C43" s="360"/>
+      <c r="D43" s="360"/>
+      <c r="E43" s="360"/>
+      <c r="F43" s="360"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4687,13 +4687,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="358" t="s">
+      <c r="B47" s="360" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="358"/>
-      <c r="D47" s="358"/>
-      <c r="E47" s="358"/>
-      <c r="F47" s="358"/>
+      <c r="C47" s="360"/>
+      <c r="D47" s="360"/>
+      <c r="E47" s="360"/>
+      <c r="F47" s="360"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4709,13 +4709,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="358" t="s">
+      <c r="B50" s="360" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="358"/>
-      <c r="D50" s="358"/>
-      <c r="E50" s="358"/>
-      <c r="F50" s="358"/>
+      <c r="C50" s="360"/>
+      <c r="D50" s="360"/>
+      <c r="E50" s="360"/>
+      <c r="F50" s="360"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4779,13 +4779,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="358" t="s">
+      <c r="B58" s="360" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="358"/>
-      <c r="D58" s="358"/>
-      <c r="E58" s="358"/>
-      <c r="F58" s="358"/>
+      <c r="C58" s="360"/>
+      <c r="D58" s="360"/>
+      <c r="E58" s="360"/>
+      <c r="F58" s="360"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4801,7 +4801,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="358" t="s">
+      <c r="B61" s="360" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="361"/>
@@ -4823,22 +4823,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="357" t="s">
+      <c r="B64" s="359" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="357"/>
-      <c r="D64" s="357"/>
-      <c r="E64" s="357"/>
-      <c r="F64" s="357"/>
+      <c r="C64" s="359"/>
+      <c r="D64" s="359"/>
+      <c r="E64" s="359"/>
+      <c r="F64" s="359"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="357" t="s">
+      <c r="B65" s="359" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="357"/>
-      <c r="D65" s="357"/>
-      <c r="E65" s="357"/>
-      <c r="F65" s="357"/>
+      <c r="C65" s="359"/>
+      <c r="D65" s="359"/>
+      <c r="E65" s="359"/>
+      <c r="F65" s="359"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4973,22 +4973,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="357" t="s">
+      <c r="B80" s="359" t="s">
         <v>363</v>
       </c>
-      <c r="C80" s="357"/>
-      <c r="D80" s="357"/>
-      <c r="E80" s="357"/>
-      <c r="F80" s="357"/>
+      <c r="C80" s="359"/>
+      <c r="D80" s="359"/>
+      <c r="E80" s="359"/>
+      <c r="F80" s="359"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="359" t="s">
+      <c r="B81" s="362" t="s">
         <v>253</v>
       </c>
-      <c r="C81" s="359"/>
-      <c r="D81" s="359"/>
-      <c r="E81" s="359"/>
-      <c r="F81" s="359"/>
+      <c r="C81" s="362"/>
+      <c r="D81" s="362"/>
+      <c r="E81" s="362"/>
+      <c r="F81" s="362"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5032,22 +5032,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="357" t="s">
+      <c r="B89" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C89" s="357"/>
-      <c r="D89" s="357"/>
-      <c r="E89" s="357"/>
-      <c r="F89" s="357"/>
+      <c r="C89" s="359"/>
+      <c r="D89" s="359"/>
+      <c r="E89" s="359"/>
+      <c r="F89" s="359"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="357" t="s">
+      <c r="B90" s="359" t="s">
         <v>365</v>
       </c>
-      <c r="C90" s="357"/>
-      <c r="D90" s="357"/>
-      <c r="E90" s="357"/>
-      <c r="F90" s="357"/>
+      <c r="C90" s="359"/>
+      <c r="D90" s="359"/>
+      <c r="E90" s="359"/>
+      <c r="F90" s="359"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5084,13 +5084,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="357" t="s">
+      <c r="B97" s="359" t="s">
         <v>366</v>
       </c>
-      <c r="C97" s="357"/>
-      <c r="D97" s="357"/>
-      <c r="E97" s="357"/>
-      <c r="F97" s="357"/>
+      <c r="C97" s="359"/>
+      <c r="D97" s="359"/>
+      <c r="E97" s="359"/>
+      <c r="F97" s="359"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5103,13 +5103,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="357" t="s">
+      <c r="B101" s="359" t="s">
         <v>345</v>
       </c>
-      <c r="C101" s="357"/>
-      <c r="D101" s="357"/>
-      <c r="E101" s="357"/>
-      <c r="F101" s="357"/>
+      <c r="C101" s="359"/>
+      <c r="D101" s="359"/>
+      <c r="E101" s="359"/>
+      <c r="F101" s="359"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5231,13 +5231,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="357" t="s">
+      <c r="B116" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C116" s="357"/>
-      <c r="D116" s="357"/>
-      <c r="E116" s="357"/>
-      <c r="F116" s="357"/>
+      <c r="C116" s="359"/>
+      <c r="D116" s="359"/>
+      <c r="E116" s="359"/>
+      <c r="F116" s="359"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5276,13 +5276,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="358" t="s">
+      <c r="B123" s="360" t="s">
         <v>368</v>
       </c>
-      <c r="C123" s="358"/>
-      <c r="D123" s="358"/>
-      <c r="E123" s="358"/>
-      <c r="F123" s="358"/>
+      <c r="C123" s="360"/>
+      <c r="D123" s="360"/>
+      <c r="E123" s="360"/>
+      <c r="F123" s="360"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5425,13 +5425,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="363" t="s">
         <v>371</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5444,22 +5444,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="360" t="s">
+      <c r="B138" s="364" t="s">
         <v>369</v>
       </c>
-      <c r="C138" s="360"/>
-      <c r="D138" s="360"/>
-      <c r="E138" s="360"/>
-      <c r="F138" s="360"/>
+      <c r="C138" s="364"/>
+      <c r="D138" s="364"/>
+      <c r="E138" s="364"/>
+      <c r="F138" s="364"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="357" t="s">
+      <c r="B139" s="359" t="s">
         <v>370</v>
       </c>
-      <c r="C139" s="357"/>
-      <c r="D139" s="357"/>
-      <c r="E139" s="357"/>
-      <c r="F139" s="357"/>
+      <c r="C139" s="359"/>
+      <c r="D139" s="359"/>
+      <c r="E139" s="359"/>
+      <c r="F139" s="359"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5792,13 +5792,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="364" t="s">
+      <c r="B179" s="358" t="s">
         <v>377</v>
       </c>
-      <c r="C179" s="357"/>
-      <c r="D179" s="357"/>
-      <c r="E179" s="357"/>
-      <c r="F179" s="357"/>
+      <c r="C179" s="359"/>
+      <c r="D179" s="359"/>
+      <c r="E179" s="359"/>
+      <c r="F179" s="359"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5835,13 +5835,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="358" t="s">
+      <c r="B188" s="360" t="s">
         <v>382</v>
       </c>
-      <c r="C188" s="358"/>
-      <c r="D188" s="358"/>
-      <c r="E188" s="358"/>
-      <c r="F188" s="358"/>
+      <c r="C188" s="360"/>
+      <c r="D188" s="360"/>
+      <c r="E188" s="360"/>
+      <c r="F188" s="360"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5849,22 +5849,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="363" t="s">
+      <c r="B191" s="357" t="s">
         <v>383</v>
       </c>
-      <c r="C191" s="363"/>
-      <c r="D191" s="363"/>
-      <c r="E191" s="363"/>
-      <c r="F191" s="363"/>
+      <c r="C191" s="357"/>
+      <c r="D191" s="357"/>
+      <c r="E191" s="357"/>
+      <c r="F191" s="357"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="363" t="s">
+      <c r="B192" s="357" t="s">
         <v>384</v>
       </c>
-      <c r="C192" s="363"/>
-      <c r="D192" s="363"/>
-      <c r="E192" s="363"/>
-      <c r="F192" s="363"/>
+      <c r="C192" s="357"/>
+      <c r="D192" s="357"/>
+      <c r="E192" s="357"/>
+      <c r="F192" s="357"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5888,17 +5888,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5915,6 +5904,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">

--- a/financial_models/opportunities/0398.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0398.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8476F03-B48B-424B-81D0-C657DB53EB70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2909F0C3-1D7F-9145-931B-FC4683FB18D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-100" yWindow="-100" windowWidth="17120" windowHeight="10760" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -38,6 +38,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -2499,7 +2510,7 @@
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
     <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="59">
+  <fonts count="59" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3891,30 +3902,30 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3929,7 +3940,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4218,16 +4229,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J197"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.73046875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="25.73046875" style="1" customWidth="1"/>
-    <col min="5" max="6" width="15.73046875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.6640625" style="1" customWidth="1"/>
+    <col min="5" max="6" width="15.6640625" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B1" s="3" t="s">
         <v>41</v>
       </c>
@@ -4244,7 +4255,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="13.9">
+    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
       <c r="A2" s="222" t="s">
         <v>267</v>
       </c>
@@ -4258,7 +4269,7 @@
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B4" s="45" t="s">
         <v>414</v>
       </c>
@@ -4267,7 +4278,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="12.4">
+    <row r="5" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="B5" s="4" t="s">
         <v>315</v>
       </c>
@@ -4275,7 +4286,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
         <v>0</v>
       </c>
@@ -4284,7 +4295,7 @@
       </c>
       <c r="E6" s="48"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B7" s="2" t="s">
         <v>307</v>
       </c>
@@ -4294,7 +4305,7 @@
       <c r="D7" s="48"/>
       <c r="E7" s="48"/>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B8" s="1" t="s">
         <v>268</v>
       </c>
@@ -4304,17 +4315,17 @@
       </c>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
       <c r="E9" s="34"/>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B10" s="45" t="s">
         <v>417</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B11" s="1" t="s">
         <v>416</v>
       </c>
@@ -4326,17 +4337,17 @@
       </c>
       <c r="E11" s="34"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B12" s="4" t="s">
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B13" s="1" t="s">
         <v>415</v>
       </c>
@@ -4346,13 +4357,13 @@
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B14" s="4" t="s">
         <v>419</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>1744.7424419200001</v>
+        <v>1754.4896064000002</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4360,7 +4371,7 @@
       </c>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B15" s="4" t="s">
         <v>418</v>
       </c>
@@ -4374,7 +4385,7 @@
       </c>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B16" s="4" t="s">
         <v>1</v>
       </c>
@@ -4384,27 +4395,27 @@
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="2:6">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+    <row r="18" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
-    </row>
-    <row r="20" spans="2:6">
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B20" s="45" t="s">
         <v>306</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="2:6">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B21" s="2" t="s">
         <v>348</v>
       </c>
@@ -4419,7 +4430,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="22" spans="2:6">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
@@ -4432,7 +4443,7 @@
       </c>
       <c r="E22" s="313"/>
     </row>
-    <row r="23" spans="2:6">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B23" s="1" t="s">
         <v>433</v>
       </c>
@@ -4440,7 +4451,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="24" spans="2:6">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B24" s="1" t="s">
         <v>434</v>
       </c>
@@ -4448,7 +4459,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="25" spans="2:6">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B25" s="4" t="s">
         <v>347</v>
       </c>
@@ -4464,7 +4475,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="2:6">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B26" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (HKD) :</v>
@@ -4478,14 +4489,14 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.166056434583427</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6">
+        <v>0.16382813843087729</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="2:6">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B28" s="45" t="s">
         <v>432</v>
       </c>
@@ -4504,7 +4515,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="2:6">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B29" s="1" t="s">
         <v>424</v>
       </c>
@@ -4523,7 +4534,7 @@
         <v>0.3674</v>
       </c>
     </row>
-    <row r="30" spans="2:6">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B30" s="1" t="s">
         <v>425</v>
       </c>
@@ -4542,7 +4553,7 @@
         <v>0.21740000000000001</v>
       </c>
     </row>
-    <row r="31" spans="2:6">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B31" s="1" t="s">
         <v>426</v>
       </c>
@@ -4561,7 +4572,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="32" spans="2:6">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B32" s="1" t="s">
         <v>427</v>
       </c>
@@ -4580,11 +4591,11 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
     </row>
-    <row r="34" spans="1:6" ht="13.9">
+    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A34" s="222" t="s">
         <v>354</v>
       </c>
@@ -4594,25 +4605,25 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+    <row r="36" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
-    </row>
-    <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
-    </row>
-    <row r="39" spans="1:6">
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B39" s="210" t="s">
         <v>230</v>
       </c>
@@ -4621,16 +4632,16 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+    <row r="40" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
-    </row>
-    <row r="41" spans="1:6">
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B41" s="47" t="s">
         <v>232</v>
       </c>
@@ -4643,20 +4654,20 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B42" s="47"/>
       <c r="C42" s="76"/>
     </row>
-    <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+    <row r="43" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
-    </row>
-    <row r="44" spans="1:6">
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B44" s="47" t="s">
         <v>234</v>
       </c>
@@ -4669,7 +4680,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B45" s="52" t="s">
         <v>235</v>
       </c>
@@ -4682,16 +4693,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
-    </row>
-    <row r="48" spans="1:6">
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B48" s="47" t="s">
         <v>237</v>
       </c>
@@ -4704,16 +4715,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+    <row r="50" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
-    </row>
-    <row r="51" spans="2:6">
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
+    </row>
+    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B51" s="47" t="s">
         <v>340</v>
       </c>
@@ -4728,7 +4739,7 @@
       <c r="E51" s="286"/>
       <c r="F51" s="286"/>
     </row>
-    <row r="52" spans="2:6">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B52" s="47" t="s">
         <v>341</v>
       </c>
@@ -4743,7 +4754,7 @@
       <c r="E52" s="286"/>
       <c r="F52" s="286"/>
     </row>
-    <row r="53" spans="2:6">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B53" s="47" t="s">
         <v>238</v>
       </c>
@@ -4756,12 +4767,12 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="55" spans="2:6">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B55" s="1" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="56" spans="2:6">
+    <row r="56" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B56" s="47" t="s">
         <v>265</v>
       </c>
@@ -4774,16 +4785,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
-    </row>
-    <row r="59" spans="2:6">
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B59" s="47" t="s">
         <v>239</v>
       </c>
@@ -4796,8 +4807,8 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4805,7 +4816,7 @@
       <c r="E61" s="360"/>
       <c r="F61" s="360"/>
     </row>
-    <row r="62" spans="2:6">
+    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B62" s="47" t="s">
         <v>242</v>
       </c>
@@ -4818,25 +4829,25 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+    <row r="64" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
-    </row>
-    <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
-    </row>
-    <row r="67" spans="1:6">
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B67" s="47" t="s">
         <v>270</v>
       </c>
@@ -4849,7 +4860,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B68" s="47" t="s">
         <v>248</v>
       </c>
@@ -4862,23 +4873,23 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B69" s="227" t="s">
         <v>390</v>
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>7.9319144526168853E-2</v>
+        <v>7.8878482612134579E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
-    <row r="70" spans="1:6">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B70" s="227" t="s">
         <v>308</v>
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.5754189944134075E-2</v>
+        <v>3.5555555555555556E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>447</v>
@@ -4888,7 +4899,7 @@
         <v>0.45076368583801485</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B72" s="210" t="s">
         <v>450</v>
       </c>
@@ -4899,7 +4910,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B73" s="47" t="s">
         <v>451</v>
       </c>
@@ -4912,7 +4923,7 @@
         <v>0.18576712671946713</v>
       </c>
     </row>
-    <row r="74" spans="1:6">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B74" s="259" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Pre-tax Profit/Sales</v>
@@ -4926,7 +4937,7 @@
         <v>9.3537135473147709E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B75" s="259" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Sales/Total Assets</v>
@@ -4940,7 +4951,7 @@
         <v>1.4185842608933972</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B76" s="259" t="str">
         <f>Normalized_FCF!B119</f>
         <v>Total Assets/Equity</v>
@@ -4954,7 +4965,7 @@
         <v>1.4000052396569989</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="13.9">
+    <row r="78" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A78" s="222" t="s">
         <v>355</v>
       </c>
@@ -4964,34 +4975,34 @@
       <c r="E78" s="36"/>
       <c r="F78" s="36"/>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A79" s="209"/>
     </row>
-    <row r="80" spans="1:6" ht="24.6" customHeight="1">
+    <row r="80" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
-    </row>
-    <row r="83" spans="1:6">
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B83" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B84" s="1" t="s">
         <v>430</v>
       </c>
@@ -5000,7 +5011,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B85" s="1" t="s">
         <v>429</v>
       </c>
@@ -5009,7 +5020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B86" s="80" t="s">
         <v>247</v>
       </c>
@@ -5018,34 +5029,34 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
       <c r="C87" s="121"/>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B88" s="293" t="s">
         <v>356</v>
       </c>
       <c r="C88" s="121"/>
     </row>
-    <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+    <row r="89" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
-    </row>
-    <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
+    </row>
+    <row r="90" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
-    </row>
-    <row r="92" spans="1:6">
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B92" s="47" t="s">
         <v>251</v>
       </c>
@@ -5053,7 +5064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B93" s="47" t="s">
         <v>280</v>
       </c>
@@ -5066,7 +5077,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="13.9">
+    <row r="95" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A95" s="222" t="s">
         <v>357</v>
       </c>
@@ -5076,38 +5087,38 @@
       <c r="E95" s="36"/>
       <c r="F95" s="36"/>
     </row>
-    <row r="96" spans="1:6">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A96" s="209"/>
     </row>
-    <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
-    </row>
-    <row r="98" spans="2:6">
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
+    </row>
+    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B98" s="1" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="100" spans="2:6">
+    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B100" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+    <row r="101" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
-    </row>
-    <row r="102" spans="2:6">
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
+    </row>
+    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B102" s="47" t="s">
         <v>255</v>
       </c>
@@ -5120,7 +5131,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="103" spans="2:6">
+    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B103" s="47" t="s">
         <v>281</v>
       </c>
@@ -5133,7 +5144,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="104" spans="2:6">
+    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B104" s="296" t="s">
         <v>404</v>
       </c>
@@ -5142,7 +5153,7 @@
         <v>0.10646655543311496</v>
       </c>
     </row>
-    <row r="105" spans="2:6">
+    <row r="105" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B105" s="296" t="s">
         <v>406</v>
       </c>
@@ -5151,12 +5162,12 @@
         <v>0.9804830051022897</v>
       </c>
     </row>
-    <row r="107" spans="2:6">
+    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B107" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="108" spans="2:6">
+    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B108" s="47" t="s">
         <v>264</v>
       </c>
@@ -5169,7 +5180,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="109" spans="2:6">
+    <row r="109" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B109" s="47" t="s">
         <v>266</v>
       </c>
@@ -5182,7 +5193,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="110" spans="2:6">
+    <row r="110" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B110" s="47" t="s">
         <v>282</v>
       </c>
@@ -5195,12 +5206,12 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="112" spans="2:6">
+    <row r="112" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B112" s="1" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B113" s="47" t="s">
         <v>257</v>
       </c>
@@ -5213,7 +5224,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="114" spans="1:6">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B114" s="47" t="s">
         <v>283</v>
       </c>
@@ -5226,16 +5237,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+    <row r="116" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
-    </row>
-    <row r="118" spans="1:6">
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B118" s="47" t="s">
         <v>448</v>
       </c>
@@ -5248,7 +5259,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B119" s="296" t="s">
         <v>405</v>
       </c>
@@ -5261,7 +5272,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="13.9">
+    <row r="121" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A121" s="222" t="s">
         <v>358</v>
       </c>
@@ -5271,16 +5282,16 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+    <row r="123" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
-    </row>
-    <row r="125" spans="1:6" ht="12.4">
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
+    </row>
+    <row r="125" spans="1:6" ht="14" x14ac:dyDescent="0.2">
       <c r="B125" s="233" t="s">
         <v>117</v>
       </c>
@@ -5297,7 +5308,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="126" spans="1:6">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B126" s="228" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
@@ -5319,7 +5330,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B127" s="218" t="str">
         <f>DCF!B75</f>
         <v>Optimistic</v>
@@ -5341,7 +5352,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="128" spans="1:6">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B128" s="218" t="str">
         <f>DCF!B76</f>
         <v>Base</v>
@@ -5363,7 +5374,7 @@
         <v>0.53999999999999992</v>
       </c>
     </row>
-    <row r="129" spans="1:6">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B129" s="218" t="str">
         <f>DCF!B77</f>
         <v>Pessimistic</v>
@@ -5385,7 +5396,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="130" spans="1:6">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B130" s="218" t="str">
         <f>DCF!B78</f>
         <v>Devil's advocate</v>
@@ -5407,7 +5418,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="132" spans="1:6">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B132" s="211" t="s">
         <v>258</v>
       </c>
@@ -5420,16 +5431,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="362" t="s">
+    <row r="134" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
-    </row>
-    <row r="136" spans="1:6" ht="13.9">
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
+    </row>
+    <row r="136" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A136" s="222" t="s">
         <v>402</v>
       </c>
@@ -5439,30 +5450,30 @@
       <c r="E136" s="36"/>
       <c r="F136" s="36"/>
     </row>
-    <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
-    </row>
-    <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
+    </row>
+    <row r="139" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
-    </row>
-    <row r="140" spans="1:6">
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B140" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B141" s="1" t="s">
         <v>263</v>
       </c>
@@ -5471,7 +5482,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:6">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B142" s="1" t="s">
         <v>276</v>
       </c>
@@ -5480,7 +5491,7 @@
         <v>0.3674</v>
       </c>
     </row>
-    <row r="143" spans="1:6">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B143" s="212" t="s">
         <v>261</v>
       </c>
@@ -5493,7 +5504,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="145" spans="2:4">
+    <row r="145" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B145" s="210" t="s">
         <v>408</v>
       </c>
@@ -5506,7 +5517,7 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="2:4">
+    <row r="146" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B146" s="1" t="s">
         <v>407</v>
       </c>
@@ -5515,7 +5526,7 @@
         <v>0.3674</v>
       </c>
     </row>
-    <row r="147" spans="2:4">
+    <row r="147" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B147" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5525,7 +5536,7 @@
         <v>0.21212919287870191</v>
       </c>
     </row>
-    <row r="148" spans="2:4">
+    <row r="148" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B148" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5535,7 +5546,7 @@
         <v>2.0434984886306262</v>
       </c>
     </row>
-    <row r="149" spans="2:4">
+    <row r="149" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B149" s="80" t="s">
         <v>260</v>
       </c>
@@ -5548,7 +5559,7 @@
         <v/>
       </c>
     </row>
-    <row r="150" spans="2:4">
+    <row r="150" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B150" s="259" t="s">
         <v>415</v>
       </c>
@@ -5561,7 +5572,7 @@
         <v/>
       </c>
     </row>
-    <row r="151" spans="2:4">
+    <row r="151" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B151" s="214" t="s">
         <v>262</v>
       </c>
@@ -5570,12 +5581,12 @@
         <v>0.56827582510368113</v>
       </c>
     </row>
-    <row r="153" spans="2:4">
+    <row r="153" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B153" s="210" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="154" spans="2:4">
+    <row r="154" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B154" s="1" t="s">
         <v>410</v>
       </c>
@@ -5584,7 +5595,7 @@
         <v>0.21740000000000001</v>
       </c>
     </row>
-    <row r="155" spans="2:4">
+    <row r="155" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B155" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5594,7 +5605,7 @@
         <v>0.2624513054547119</v>
       </c>
     </row>
-    <row r="156" spans="2:4">
+    <row r="156" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B156" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5604,7 +5615,7 @@
         <v>2.8957506018897798</v>
       </c>
     </row>
-    <row r="157" spans="2:4">
+    <row r="157" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B157" s="80" t="s">
         <v>260</v>
       </c>
@@ -5617,7 +5628,7 @@
         <v/>
       </c>
     </row>
-    <row r="158" spans="2:4">
+    <row r="158" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B158" s="259" t="s">
         <v>415</v>
       </c>
@@ -5630,7 +5641,7 @@
         <v/>
       </c>
     </row>
-    <row r="159" spans="2:4">
+    <row r="159" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B159" s="214" t="s">
         <v>262</v>
       </c>
@@ -5639,12 +5650,12 @@
         <v>0.39552430404120198</v>
       </c>
     </row>
-    <row r="161" spans="2:4">
+    <row r="161" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B161" s="210" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="162" spans="2:4">
+    <row r="162" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B162" s="1" t="s">
         <v>409</v>
       </c>
@@ -5653,7 +5664,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="163" spans="2:4">
+    <row r="163" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B163" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5663,7 +5674,7 @@
         <v>0.33286729470361087</v>
       </c>
     </row>
-    <row r="164" spans="2:4">
+    <row r="164" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B164" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5673,7 +5684,7 @@
         <v>4.2056744761754965</v>
       </c>
     </row>
-    <row r="165" spans="2:4">
+    <row r="165" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B165" s="80" t="s">
         <v>401</v>
       </c>
@@ -5686,7 +5697,7 @@
         <v/>
       </c>
     </row>
-    <row r="166" spans="2:4">
+    <row r="166" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B166" s="259" t="s">
         <v>415</v>
       </c>
@@ -5699,7 +5710,7 @@
         <v/>
       </c>
     </row>
-    <row r="167" spans="2:4">
+    <row r="167" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B167" s="214" t="s">
         <v>262</v>
       </c>
@@ -5708,12 +5719,12 @@
         <v>0.13132906759055596</v>
       </c>
     </row>
-    <row r="169" spans="2:4">
+    <row r="169" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B169" s="210" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="170" spans="2:4">
+    <row r="170" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B170" s="1" t="s">
         <v>422</v>
       </c>
@@ -5722,7 +5733,7 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="171" spans="2:4">
+    <row r="171" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B171" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5732,7 +5743,7 @@
         <v>0.30881320012014707</v>
       </c>
     </row>
-    <row r="172" spans="2:4">
+    <row r="172" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B172" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5742,7 +5753,7 @@
         <v>3.7448553439982017</v>
       </c>
     </row>
-    <row r="173" spans="2:4">
+    <row r="173" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B173" s="80" t="s">
         <v>401</v>
       </c>
@@ -5755,7 +5766,7 @@
         <v/>
       </c>
     </row>
-    <row r="174" spans="2:4">
+    <row r="174" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B174" s="259" t="s">
         <v>415</v>
       </c>
@@ -5768,7 +5779,7 @@
         <v/>
       </c>
     </row>
-    <row r="175" spans="2:4">
+    <row r="175" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B175" s="214" t="s">
         <v>262</v>
       </c>
@@ -5777,7 +5788,7 @@
         <v>0.22401578084943807</v>
       </c>
     </row>
-    <row r="177" spans="1:6" ht="13.9">
+    <row r="177" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A177" s="222" t="s">
         <v>374</v>
       </c>
@@ -5787,21 +5798,21 @@
       <c r="E177" s="36"/>
       <c r="F177" s="36"/>
     </row>
-    <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
-    </row>
-    <row r="181" spans="1:6">
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B181" s="210" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="182" spans="1:6">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B182" s="360" t="s">
         <v>380</v>
       </c>
@@ -5810,80 +5821,91 @@
       <c r="E182" s="360"/>
       <c r="F182" s="360"/>
     </row>
-    <row r="183" spans="1:6">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B183" s="214" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="184" spans="1:6">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B184" s="214" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="185" spans="1:6">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B185" s="214" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="187" spans="1:6">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B187" s="1" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+    <row r="188" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
-    </row>
-    <row r="190" spans="1:6">
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B190" s="1" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="356" t="s">
+    <row r="191" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
-    </row>
-    <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
+    </row>
+    <row r="192" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
-    </row>
-    <row r="194" spans="2:2">
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
+    </row>
+    <row r="194" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B194" s="1" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="195" spans="2:2">
+    <row r="195" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B195" s="214" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="196" spans="2:2">
+    <row r="196" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B196" s="214" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="197" spans="2:2">
+    <row r="197" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B197" s="214" t="s">
         <v>388</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5900,17 +5922,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -5941,15 +5952,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="11.65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
-    <col min="2" max="2" width="27.265625" style="1" customWidth="1"/>
-    <col min="3" max="13" width="20.73046875" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.86328125" style="1"/>
+    <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
+    <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13">
+    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
         <v>HKD</v>
@@ -5998,7 +6009,7 @@
         <v>41729</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="13.9">
+    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>97</v>
       </c>
@@ -6014,7 +6025,7 @@
       <c r="L2" s="37"/>
       <c r="M2" s="37"/>
     </row>
-    <row r="3" spans="2:13">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B3" s="16" t="s">
         <v>27</v>
       </c>
@@ -6022,7 +6033,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="2:13">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
@@ -6056,7 +6067,7 @@
       <c r="L4" s="351"/>
       <c r="M4" s="351"/>
     </row>
-    <row r="5" spans="2:13">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
@@ -6090,7 +6101,7 @@
       <c r="L5" s="351"/>
       <c r="M5" s="351"/>
     </row>
-    <row r="6" spans="2:13">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
@@ -6124,7 +6135,7 @@
       <c r="L6" s="351"/>
       <c r="M6" s="351"/>
     </row>
-    <row r="7" spans="2:13">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
@@ -6158,7 +6169,7 @@
       <c r="L7" s="352"/>
       <c r="M7" s="352"/>
     </row>
-    <row r="8" spans="2:13">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
@@ -6174,7 +6185,7 @@
       <c r="L8" s="351"/>
       <c r="M8" s="351"/>
     </row>
-    <row r="9" spans="2:13">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B9" s="40" t="s">
         <v>159</v>
       </c>
@@ -6190,7 +6201,7 @@
       <c r="L9" s="351"/>
       <c r="M9" s="351"/>
     </row>
-    <row r="10" spans="2:13">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B10" s="40" t="s">
         <v>167</v>
       </c>
@@ -6206,7 +6217,7 @@
       <c r="L10" s="351"/>
       <c r="M10" s="351"/>
     </row>
-    <row r="11" spans="2:13">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B11" s="40" t="s">
         <v>158</v>
       </c>
@@ -6222,7 +6233,7 @@
       <c r="L11" s="351"/>
       <c r="M11" s="351"/>
     </row>
-    <row r="12" spans="2:13">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
@@ -6256,7 +6267,7 @@
       <c r="L12" s="351"/>
       <c r="M12" s="351"/>
     </row>
-    <row r="13" spans="2:13">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
@@ -6272,7 +6283,7 @@
       <c r="L13" s="351"/>
       <c r="M13" s="351"/>
     </row>
-    <row r="14" spans="2:13">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
@@ -6306,7 +6317,7 @@
       <c r="L14" s="351"/>
       <c r="M14" s="351"/>
     </row>
-    <row r="15" spans="2:13">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
@@ -6340,7 +6351,7 @@
       <c r="L15" s="353"/>
       <c r="M15" s="353"/>
     </row>
-    <row r="16" spans="2:13">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
@@ -6374,13 +6385,13 @@
       <c r="L16" s="351"/>
       <c r="M16" s="351"/>
     </row>
-    <row r="18" spans="2:13">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B18" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13">
+    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
@@ -6396,7 +6407,7 @@
       <c r="L19" s="351"/>
       <c r="M19" s="351"/>
     </row>
-    <row r="20" spans="2:13">
+    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
@@ -6412,7 +6423,7 @@
       <c r="L20" s="351"/>
       <c r="M20" s="351"/>
     </row>
-    <row r="21" spans="2:13">
+    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
@@ -6428,7 +6439,7 @@
       <c r="L21" s="351"/>
       <c r="M21" s="351"/>
     </row>
-    <row r="22" spans="2:13">
+    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B22" s="27" t="s">
         <v>371</v>
       </c>
@@ -6462,7 +6473,7 @@
       <c r="L22" s="351"/>
       <c r="M22" s="351"/>
     </row>
-    <row r="23" spans="2:13">
+    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B23" s="27" t="s">
         <v>373</v>
       </c>
@@ -6496,7 +6507,7 @@
       <c r="L23" s="351"/>
       <c r="M23" s="351"/>
     </row>
-    <row r="24" spans="2:13">
+    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B24" s="27" t="s">
         <v>372</v>
       </c>
@@ -6530,7 +6541,7 @@
       <c r="L24" s="351"/>
       <c r="M24" s="351"/>
     </row>
-    <row r="25" spans="2:13">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B25" s="24" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (HKD)</v>
@@ -6559,7 +6570,7 @@
       <c r="L25" s="39"/>
       <c r="M25" s="39"/>
     </row>
-    <row r="27" spans="2:13">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
@@ -6567,7 +6578,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="28" spans="2:13">
+    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
@@ -6602,7 +6613,7 @@
       <c r="L28" s="351"/>
       <c r="M28" s="351"/>
     </row>
-    <row r="29" spans="2:13">
+    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
@@ -6637,7 +6648,7 @@
       <c r="L29" s="351"/>
       <c r="M29" s="351"/>
     </row>
-    <row r="30" spans="2:13">
+    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
@@ -6672,7 +6683,7 @@
       <c r="L30" s="353"/>
       <c r="M30" s="353"/>
     </row>
-    <row r="31" spans="2:13">
+    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
@@ -6707,7 +6718,7 @@
       <c r="L31" s="353"/>
       <c r="M31" s="353"/>
     </row>
-    <row r="32" spans="2:13">
+    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B32" s="26" t="s">
         <v>172</v>
       </c>
@@ -6742,7 +6753,7 @@
       <c r="L32" s="351"/>
       <c r="M32" s="351"/>
     </row>
-    <row r="34" spans="2:13" ht="13.9">
+    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B34" s="36" t="s">
         <v>81</v>
       </c>
@@ -6758,12 +6769,12 @@
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
     </row>
-    <row r="35" spans="2:13">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B35" s="16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="2:13">
+    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
@@ -6812,7 +6823,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
@@ -6861,7 +6872,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13">
+    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
@@ -6910,7 +6921,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
@@ -6959,7 +6970,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13">
+    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
@@ -7008,7 +7019,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13">
+    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
@@ -7057,7 +7068,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
@@ -7106,7 +7117,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B43" s="43" t="s">
         <v>152</v>
       </c>
@@ -7155,7 +7166,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B44" s="43" t="s">
         <v>168</v>
       </c>
@@ -7204,7 +7215,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B45" s="40" t="s">
         <v>68</v>
       </c>
@@ -7253,7 +7264,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
@@ -7302,7 +7313,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
@@ -7351,7 +7362,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
@@ -7400,12 +7411,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13">
+    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B50" s="16" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="2:13">
+    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
@@ -7454,7 +7465,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13">
+    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
@@ -7503,12 +7514,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13">
+    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B54" s="174" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="55" spans="2:13">
+    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B55" s="40" t="s">
         <v>159</v>
       </c>
@@ -7557,7 +7568,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13">
+    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B56" s="40" t="s">
         <v>167</v>
       </c>
@@ -7606,7 +7617,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13">
+    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B57" s="40" t="s">
         <v>158</v>
       </c>
@@ -7655,7 +7666,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13">
+    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B58" s="40" t="s">
         <v>160</v>
       </c>
@@ -7704,13 +7715,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13">
+    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B60" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13">
+    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
@@ -7759,7 +7770,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13">
+    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
@@ -7808,7 +7819,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13">
+    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
@@ -7857,7 +7868,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13">
+    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B64" s="27" t="s">
         <v>393</v>
       </c>
@@ -7906,7 +7917,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13">
+    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B65" s="24" t="s">
         <v>36</v>
       </c>
@@ -7955,12 +7966,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B67" s="91" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="68" spans="2:13">
+    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -8010,7 +8021,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13">
+    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B69" s="31" t="s">
         <v>58</v>
       </c>
@@ -8059,7 +8070,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13">
+    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B70" s="80" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -8109,7 +8120,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13">
+    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B71" s="43" t="s">
         <v>168</v>
       </c>
@@ -8139,7 +8150,7 @@
       </c>
       <c r="I71" s="101">
         <f t="shared" si="37"/>
-        <v>0.82636627651148453</v>
+        <v>0.82636627651148475</v>
       </c>
       <c r="J71" s="101">
         <f t="shared" si="37"/>
@@ -8158,7 +8169,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13">
+    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B72" s="80" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -8208,7 +8219,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="13.9">
+    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B74" s="36" t="s">
         <v>82</v>
       </c>
@@ -8224,13 +8235,13 @@
       <c r="L74" s="37"/>
       <c r="M74" s="37"/>
     </row>
-    <row r="75" spans="2:13">
+    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B75" s="16" t="s">
         <v>28</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13">
+    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B76" s="26" t="s">
         <v>3</v>
       </c>
@@ -8279,7 +8290,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13">
+    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B77" s="93" t="s">
         <v>85</v>
       </c>
@@ -8313,7 +8324,7 @@
       <c r="L77" s="355"/>
       <c r="M77" s="355"/>
     </row>
-    <row r="78" spans="2:13">
+    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B78" s="93" t="s">
         <v>86</v>
       </c>
@@ -8347,7 +8358,7 @@
       <c r="L78" s="355"/>
       <c r="M78" s="355"/>
     </row>
-    <row r="79" spans="2:13">
+    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
@@ -8396,7 +8407,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13">
+    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
@@ -8477,18 +8488,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.265625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="18.73046875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.73046875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="25.265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="18.73046875" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="12.265625" style="1"/>
+    <col min="3" max="4" width="18.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="18.6640625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1">
+    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B1" s="18" t="s">
         <v>37</v>
       </c>
@@ -8504,7 +8515,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1">
+    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B2" s="79" t="s">
         <v>156</v>
       </c>
@@ -8515,7 +8526,7 @@
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1">
+    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B3" s="16" t="s">
         <v>184</v>
       </c>
@@ -8535,7 +8546,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1">
+    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
@@ -8557,7 +8568,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1">
+    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
@@ -8578,7 +8589,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1">
+    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
@@ -8599,7 +8610,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1">
+    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="1" t="s">
         <v>69</v>
       </c>
@@ -8620,7 +8631,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1">
+    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="1" t="s">
         <v>173</v>
       </c>
@@ -8641,7 +8652,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1">
+    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
@@ -8662,7 +8673,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1">
+    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
@@ -8674,7 +8685,7 @@
       </c>
       <c r="H10" s="262"/>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1">
+    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
@@ -8686,7 +8697,7 @@
       </c>
       <c r="H11" s="262"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1">
+    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="80" t="s">
         <v>72</v>
       </c>
@@ -8710,12 +8721,12 @@
         <v>986959.8</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1">
+    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F13" s="80"/>
       <c r="G13" s="81"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1">
+    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="16" t="s">
         <v>183</v>
       </c>
@@ -8735,7 +8746,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1">
+    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="4" t="s">
         <v>454</v>
       </c>
@@ -8755,7 +8766,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1">
+    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
@@ -8776,7 +8787,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1">
+    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1" t="s">
         <v>69</v>
       </c>
@@ -8796,7 +8807,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1">
+    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="4" t="s">
         <v>173</v>
       </c>
@@ -8816,7 +8827,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1">
+    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="4" t="s">
         <v>26</v>
       </c>
@@ -8838,7 +8849,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1">
+    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="4" t="s">
         <v>18</v>
       </c>
@@ -8858,7 +8869,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1">
+    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
@@ -8878,7 +8889,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1">
+    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="4" t="s">
         <v>20</v>
       </c>
@@ -8890,7 +8901,7 @@
       </c>
       <c r="H22" s="262"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1">
+    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="4" t="s">
         <v>21</v>
       </c>
@@ -8902,7 +8913,7 @@
       </c>
       <c r="H23" s="262"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1">
+    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="80" t="s">
         <v>73</v>
       </c>
@@ -8926,7 +8937,7 @@
         <v>41890.299999999996</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1">
+    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="16" t="s">
         <v>200</v>
       </c>
@@ -8943,7 +8954,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1">
+    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="4" t="s">
         <v>5</v>
       </c>
@@ -8962,7 +8973,7 @@
         <v>815566.8</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1">
+    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="4" t="s">
         <v>6</v>
       </c>
@@ -8977,7 +8988,7 @@
       </c>
       <c r="H28" s="188"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1">
+    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="4" t="s">
         <v>7</v>
       </c>
@@ -8996,7 +9007,7 @@
         <v>813801.8</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1">
+    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="2" t="s">
         <v>8</v>
       </c>
@@ -9012,7 +9023,7 @@
       </c>
       <c r="H30" s="188"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1">
+    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="80" t="s">
         <v>203</v>
       </c>
@@ -9029,7 +9040,7 @@
       </c>
       <c r="H31" s="188"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1">
+    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="4" t="s">
         <v>9</v>
       </c>
@@ -9049,7 +9060,7 @@
         <v>1548448.8</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1">
+    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B33" s="83" t="s">
         <v>4</v>
       </c>
@@ -9060,7 +9071,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="195"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1">
+    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="196" t="s">
@@ -9073,7 +9084,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1">
+    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B35" s="16" t="s">
         <v>201</v>
       </c>
@@ -9092,7 +9103,7 @@
         <v>519598.69999999995</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1">
+    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B36" s="4" t="s">
         <v>13</v>
       </c>
@@ -9108,7 +9119,7 @@
       </c>
       <c r="H36" s="195"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1">
+    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B37" s="4" t="s">
         <v>14</v>
       </c>
@@ -9124,7 +9135,7 @@
       </c>
       <c r="H37" s="195"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1">
+    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="4" t="s">
         <v>15</v>
       </c>
@@ -9140,7 +9151,7 @@
       </c>
       <c r="H38" s="195"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1">
+    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
@@ -9159,7 +9170,7 @@
         <v>41963.600000000006</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1">
+    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B40" s="80" t="s">
         <v>204</v>
       </c>
@@ -9179,7 +9190,7 @@
         <v>1028850.1000000001</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1">
+    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B41" s="4" t="s">
         <v>17</v>
       </c>
@@ -9199,7 +9210,7 @@
         <v>1009942.2000000001</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1">
+    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B42" s="83" t="s">
         <v>22</v>
       </c>
@@ -9218,7 +9229,7 @@
         <v>18907.900000000001</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1">
+    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B44" s="79" t="s">
         <v>96</v>
       </c>
@@ -9229,7 +9240,7 @@
       <c r="G44" s="37"/>
       <c r="H44" s="37"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1">
+    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B45" s="16" t="s">
         <v>271</v>
       </c>
@@ -9243,7 +9254,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1">
+    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="1" t="s">
         <v>273</v>
       </c>
@@ -9257,7 +9268,7 @@
       </c>
       <c r="F46" s="253"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1">
+    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (HKD)</v>
@@ -9272,10 +9283,10 @@
       </c>
       <c r="F47" s="253"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1">
+    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F48" s="253"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1">
+    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B49" s="157" t="s">
         <v>143</v>
       </c>
@@ -9288,7 +9299,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="253"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1">
+    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B50" s="8" t="s">
         <v>93</v>
       </c>
@@ -9302,7 +9313,7 @@
       </c>
       <c r="F50" s="253"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1">
+    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B51" s="1" t="s">
         <v>176</v>
       </c>
@@ -9313,10 +9324,10 @@
       </c>
       <c r="F51" s="253"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1">
+    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F52" s="253"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1">
+    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B53" s="157" t="s">
         <v>142</v>
       </c>
@@ -9328,7 +9339,7 @@
       </c>
       <c r="F53" s="253"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1">
+    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B54" s="1" t="s">
         <v>139</v>
       </c>
@@ -9342,7 +9353,7 @@
       </c>
       <c r="F54" s="253"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1">
+    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B55" s="1" t="s">
         <v>141</v>
       </c>
@@ -9356,10 +9367,10 @@
       </c>
       <c r="F55" s="253"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1">
+    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F56" s="253"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1">
+    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B57" s="157" t="s">
         <v>175</v>
       </c>
@@ -9371,7 +9382,7 @@
       </c>
       <c r="F57" s="253"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1">
+    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B58" s="2" t="s">
         <v>89</v>
       </c>
@@ -9382,7 +9393,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1">
+    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B59" s="1" t="s">
         <v>92</v>
       </c>
@@ -9393,10 +9404,10 @@
       </c>
       <c r="F59" s="253"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1">
+    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F60" s="253"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1">
+    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B61" s="157" t="s">
         <v>274</v>
       </c>
@@ -9408,7 +9419,7 @@
       </c>
       <c r="F61" s="253"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1">
+    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B62" s="1" t="s">
         <v>245</v>
       </c>
@@ -9424,7 +9435,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1">
+    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B64" s="79" t="s">
         <v>193</v>
       </c>
@@ -9435,7 +9446,7 @@
       <c r="G64" s="37"/>
       <c r="H64" s="37"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1">
+    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B65" s="16" t="s">
         <v>188</v>
       </c>
@@ -9449,7 +9460,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1">
+    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B66" s="105" t="s">
         <v>187</v>
       </c>
@@ -9465,7 +9476,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1">
+    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B67" s="105" t="s">
         <v>177</v>
       </c>
@@ -9475,7 +9486,7 @@
       </c>
       <c r="F67" s="253"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1">
+    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B68" s="105" t="s">
         <v>181</v>
       </c>
@@ -9485,7 +9496,7 @@
       </c>
       <c r="F68" s="253"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1">
+    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B69" s="105" t="s">
         <v>179</v>
       </c>
@@ -9495,7 +9506,7 @@
       </c>
       <c r="F69" s="253"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1">
+    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B70" s="80" t="s">
         <v>188</v>
       </c>
@@ -9505,10 +9516,10 @@
       </c>
       <c r="F70" s="253"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1">
+    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F71" s="253"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1">
+    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B72" s="255" t="s">
         <v>318</v>
       </c>
@@ -9520,7 +9531,7 @@
       </c>
       <c r="F72" s="253"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1">
+    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B73" s="105" t="s">
         <v>317</v>
       </c>
@@ -9536,7 +9547,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1">
+    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B74" s="257" t="s">
         <v>321</v>
       </c>
@@ -9552,7 +9563,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1">
+    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B75" s="80" t="s">
         <v>320</v>
       </c>
@@ -9565,7 +9576,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1">
+    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B76" s="259" t="s">
         <v>322</v>
       </c>
@@ -9578,10 +9589,10 @@
         <v>323</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1">
+    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F77" s="253"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1">
+    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B78" s="16" t="s">
         <v>189</v>
       </c>
@@ -9593,7 +9604,7 @@
       </c>
       <c r="F78" s="253"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1">
+    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B79" s="105" t="s">
         <v>178</v>
       </c>
@@ -9607,7 +9618,7 @@
       </c>
       <c r="F79" s="253"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1">
+    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B80" s="105" t="s">
         <v>182</v>
       </c>
@@ -9621,7 +9632,7 @@
       </c>
       <c r="F80" s="253"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1">
+    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B81" s="105" t="s">
         <v>180</v>
       </c>
@@ -9635,7 +9646,7 @@
       </c>
       <c r="F81" s="253"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1">
+    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B82" s="80" t="s">
         <v>189</v>
       </c>
@@ -9649,7 +9660,7 @@
       </c>
       <c r="F82" s="253"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1">
+    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B84" s="79" t="s">
         <v>288</v>
       </c>
@@ -9660,7 +9671,7 @@
       <c r="G84" s="37"/>
       <c r="H84" s="37"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1">
+    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B85" s="16" t="s">
         <v>289</v>
       </c>
@@ -9668,7 +9679,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1">
+    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B86" s="238" t="s">
         <v>286</v>
       </c>
@@ -9685,7 +9696,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1">
+    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B87" s="238" t="s">
         <v>287</v>
       </c>
@@ -9702,7 +9713,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1">
+    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B88" s="239" t="s">
         <v>189</v>
       </c>
@@ -9719,7 +9730,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1">
+    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B89" s="80" t="s">
         <v>291</v>
       </c>
@@ -9750,19 +9761,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="1.265625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="26.265625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.73046875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="2.73046875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="2.73046875" style="2" customWidth="1"/>
-    <col min="7" max="17" width="20.73046875" style="2" customWidth="1"/>
-    <col min="18" max="16384" width="12.265625" style="2"/>
+    <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
+    <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
+    <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
@@ -9819,7 +9830,7 @@
         <v>41729</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
         <v>99</v>
@@ -9842,7 +9853,7 @@
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>66</v>
@@ -9856,7 +9867,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
         <v>2</v>
@@ -9913,7 +9924,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>46</v>
@@ -9968,7 +9979,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
         <v>48</v>
@@ -10023,7 +10034,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>45</v>
@@ -10078,7 +10089,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
         <v>152</v>
@@ -10135,7 +10146,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
         <v>65</v>
@@ -10190,7 +10201,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>80</v>
@@ -10245,7 +10256,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
         <v>194</v>
@@ -10302,7 +10313,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>68</v>
@@ -10357,7 +10368,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
         <v>164</v>
@@ -10412,7 +10423,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
         <v>63</v>
@@ -10467,7 +10478,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
         <v>243</v>
@@ -10524,7 +10535,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
         <v>154</v>
@@ -10581,7 +10592,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
         <v>52</v>
@@ -10607,7 +10618,7 @@
       <c r="P17" s="335"/>
       <c r="Q17" s="335"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>98</v>
@@ -10632,7 +10643,7 @@
       <c r="P18" s="336"/>
       <c r="Q18" s="336"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
@@ -10689,7 +10700,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="10"/>
       <c r="B20" s="27"/>
       <c r="C20" s="62"/>
@@ -10708,7 +10719,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
         <v>205</v>
@@ -10731,7 +10742,7 @@
       <c r="P21" s="37"/>
       <c r="Q21" s="37"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
         <v>46</v>
@@ -10752,7 +10763,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
         <v>43</v>
@@ -10809,7 +10820,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
         <v>62</v>
@@ -10866,7 +10877,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
         <v>46</v>
@@ -10923,18 +10934,18 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="10"/>
       <c r="E26" s="268"/>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>206</v>
       </c>
       <c r="E27" s="268"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
         <v>43</v>
@@ -10993,7 +11004,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="10"/>
       <c r="B29" s="68" t="str">
         <f>B24</f>
@@ -11053,7 +11064,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
         <v>46</v>
@@ -11108,18 +11119,18 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="10"/>
       <c r="E31" s="268"/>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
       <c r="E32" s="268"/>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
         <v>174</v>
@@ -11176,7 +11187,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
         <v>49</v>
@@ -11235,7 +11246,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
         <v>45</v>
@@ -11292,18 +11303,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="10"/>
       <c r="E36" s="268"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>207</v>
       </c>
       <c r="E37" s="268"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="10"/>
       <c r="B38" s="2" t="str">
         <f>B33</f>
@@ -11361,7 +11372,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="10"/>
       <c r="B39" s="27" t="str">
         <f>B34</f>
@@ -11419,7 +11430,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
         <v>45</v>
@@ -11474,18 +11485,18 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="10"/>
       <c r="E41" s="268"/>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>208</v>
       </c>
       <c r="E42" s="268"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>171</v>
@@ -11543,10 +11554,10 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="10"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
         <v>209</v>
@@ -11569,14 +11580,14 @@
       <c r="P45" s="37"/>
       <c r="Q45" s="37"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
       <c r="E46" s="268"/>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
         <v>39</v>
@@ -11631,7 +11642,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
         <v>345</v>
@@ -11686,7 +11697,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="10"/>
       <c r="B49" s="287" t="s">
         <v>342</v>
@@ -11743,7 +11754,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
         <v>68</v>
@@ -11798,11 +11809,11 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="10"/>
       <c r="E51" s="268"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>155</v>
@@ -11812,7 +11823,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
         <v>88</v>
@@ -11839,7 +11850,7 @@
       <c r="P53" s="169"/>
       <c r="Q53" s="169"/>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
         <v>87</v>
@@ -11866,7 +11877,7 @@
       <c r="P54" s="169"/>
       <c r="Q54" s="169"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
         <v>90</v>
@@ -11921,11 +11932,11 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="10"/>
       <c r="E56" s="268"/>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>168</v>
@@ -11935,7 +11946,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
         <v>167</v>
@@ -11990,7 +12001,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
         <v>159</v>
@@ -12045,7 +12056,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
         <v>158</v>
@@ -12100,7 +12111,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
         <v>194</v>
@@ -12155,7 +12166,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
         <v>160</v>
@@ -12211,7 +12222,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
         <v>195</v>
@@ -12266,11 +12277,11 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="10"/>
       <c r="E64" s="268"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>169</v>
@@ -12280,7 +12291,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
         <v>167</v>
@@ -12305,7 +12316,7 @@
       <c r="P66" s="175"/>
       <c r="Q66" s="175"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
         <v>157</v>
@@ -12330,7 +12341,7 @@
       <c r="P67" s="175"/>
       <c r="Q67" s="175"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
         <v>158</v>
@@ -12355,7 +12366,7 @@
       <c r="P68" s="175"/>
       <c r="Q68" s="175"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
         <v>194</v>
@@ -12382,10 +12393,10 @@
       <c r="P69" s="175"/>
       <c r="Q69" s="175"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="10"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
         <v>212</v>
@@ -12408,7 +12419,7 @@
       <c r="P71" s="37"/>
       <c r="Q71" s="37"/>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
         <v>216</v>
@@ -12429,7 +12440,7 @@
       <c r="P72" s="12"/>
       <c r="Q72" s="12"/>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
         <v>46</v>
@@ -12486,7 +12497,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
         <v>48</v>
@@ -12543,7 +12554,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
         <v>45</v>
@@ -12600,7 +12611,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
         <v>152</v>
@@ -12657,7 +12668,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
         <v>65</v>
@@ -12714,7 +12725,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>80</v>
@@ -12773,7 +12784,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
         <v>153</v>
@@ -12830,7 +12841,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
         <v>68</v>
@@ -12887,7 +12898,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
         <v>164</v>
@@ -12944,7 +12955,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>63</v>
@@ -13001,7 +13012,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="10"/>
       <c r="B83" s="40" t="str">
         <f>B15</f>
@@ -13059,7 +13070,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
         <v>154</v>
@@ -13116,7 +13127,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
         <v>52</v>
@@ -13142,7 +13153,7 @@
       <c r="P85" s="226"/>
       <c r="Q85" s="226"/>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
         <v>98</v>
@@ -13166,7 +13177,7 @@
       <c r="P86" s="169"/>
       <c r="Q86" s="169"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
         <v>140</v>
@@ -13223,18 +13234,18 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="10"/>
       <c r="E88" s="268"/>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>214</v>
       </c>
       <c r="E89" s="268"/>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -13290,7 +13301,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -13346,7 +13357,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>213</v>
@@ -13401,31 +13412,31 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
         <v>309</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.5754189944134075E-2</v>
+        <v>3.5555555555555556E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.5754189944134075E-2</v>
+        <v>3.5555555555555556E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>4.2737430167597762E-2</v>
+        <v>4.2499999999999996E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>5.1955307262569833E-2</v>
+        <v>5.1666666666666666E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>4.1340782122905026E-2</v>
+        <v>4.1111111111111105E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
@@ -13456,11 +13467,11 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="10"/>
       <c r="E94" s="268"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="10"/>
       <c r="B95" s="157" t="s">
         <v>84</v>
@@ -13481,7 +13492,7 @@
       <c r="P95" s="12"/>
       <c r="Q95" s="12"/>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
         <v>144</v>
@@ -13538,7 +13549,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="10"/>
       <c r="B97" s="70" t="s">
         <v>164</v>
@@ -13595,10 +13606,10 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="10"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
         <v>215</v>
@@ -13621,7 +13632,7 @@
       <c r="P99" s="37"/>
       <c r="Q99" s="37"/>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="10"/>
       <c r="B100" s="64" t="s">
         <v>28</v>
@@ -13631,7 +13642,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="10"/>
       <c r="B101" s="26" t="s">
         <v>3</v>
@@ -13688,7 +13699,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="10"/>
       <c r="B102" s="93" t="s">
         <v>210</v>
@@ -13745,7 +13756,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
         <v>211</v>
@@ -13802,7 +13813,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
         <v>40</v>
@@ -13859,7 +13870,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
         <v>30</v>
@@ -13916,11 +13927,11 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="10"/>
       <c r="E106" s="268"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="10"/>
       <c r="B107" s="91" t="s">
         <v>220</v>
@@ -13943,7 +13954,7 @@
       <c r="P107" s="12"/>
       <c r="Q107" s="12"/>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
         <v>217</v>
@@ -14000,7 +14011,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
         <v>218</v>
@@ -14057,7 +14068,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
         <v>69</v>
@@ -14084,18 +14095,18 @@
       <c r="P110" s="204"/>
       <c r="Q110" s="204"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="10"/>
       <c r="E111" s="268"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
       <c r="E112" s="268"/>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>391</v>
@@ -14147,7 +14158,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
         <v>392</v>
@@ -14199,11 +14210,11 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="10"/>
       <c r="E115" s="268"/>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="10"/>
       <c r="B116" s="91" t="s">
         <v>38</v>
@@ -14257,7 +14268,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A117" s="10"/>
       <c r="B117" s="7" t="s">
         <v>221</v>
@@ -14312,7 +14323,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B118" s="7" t="s">
         <v>83</v>
       </c>
@@ -14366,7 +14377,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B119" s="7" t="s">
         <v>91</v>
       </c>
@@ -14422,7 +14433,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="10"/>
       <c r="B120" s="70" t="s">
         <v>222</v>
@@ -14479,7 +14490,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A121" s="10"/>
       <c r="B121" s="27"/>
       <c r="C121" s="62"/>
@@ -14498,7 +14509,7 @@
       <c r="P121" s="12"/>
       <c r="Q121" s="12"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="10"/>
       <c r="B122" s="54" t="s">
         <v>223</v>
@@ -14521,7 +14532,7 @@
       <c r="P122" s="37"/>
       <c r="Q122" s="37"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="10"/>
       <c r="B123" s="178" t="s">
         <v>170</v>
@@ -14542,7 +14553,7 @@
       <c r="P123" s="12"/>
       <c r="Q123" s="12"/>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="10"/>
       <c r="B124" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -14600,53 +14611,53 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
         <v>269</v>
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.9319144526168853E-2</v>
+        <v>7.8878482612134579E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.11140498180700094</v>
+        <v>0.1107860652414065</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.14298385481210107</v>
+        <v>0.14218950006314496</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.15415857007754999</v>
+        <v>0.15330213357711917</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.10623745691428477</v>
+        <v>0.10564724882031652</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>6.4794663833358829E-2</v>
+        <v>6.4434693478729058E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>5.9348014647968218E-2</v>
+        <v>5.9018303455479502E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>5.5698192274763185E-2</v>
+        <v>5.5388757873236723E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>-3.7994146532625891E-3</v>
+        <v>-3.7783067940777969E-3</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>-3.2292445375489635E-2</v>
+        <v>-3.211304290118136E-2</v>
       </c>
       <c r="P125" s="77" t="str">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
@@ -14657,46 +14668,46 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1">
+    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B126" s="2" t="s">
         <v>394</v>
       </c>
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14394674764925317</v>
+        <v>0.14314704349564619</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16937972786103084</v>
+        <v>0.16843872937291399</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.20803987527268691</v>
+        <v>0.20688409818783865</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13332856151765823</v>
+        <v>0.1325878472870046</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.6804372736491471E-2</v>
+        <v>5.6488792887955407E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9117121635497736E-2</v>
+        <v>7.8677582070856081E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9487376857402647E-2</v>
+        <v>7.9045780319305967E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.2260035712125356E-3</v>
+        <v>9.1747479958169103E-3</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-9.0322787027855098E-3</v>
+        <v>-8.9820993766589231E-3</v>
       </c>
       <c r="P126" s="23" t="str">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -14707,688 +14718,688 @@
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
-    <row r="129" ht="15.75" customHeight="1"/>
-    <row r="130" ht="15.75" customHeight="1"/>
-    <row r="131" ht="15.75" customHeight="1"/>
-    <row r="132" ht="15.75" customHeight="1"/>
-    <row r="133" ht="15.75" customHeight="1"/>
-    <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
-    <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
-    <row r="140" ht="15.75" customHeight="1"/>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
-    <row r="145" ht="15.75" customHeight="1"/>
-    <row r="146" ht="15.75" customHeight="1"/>
-    <row r="147" ht="15.75" customHeight="1"/>
-    <row r="148" ht="15.75" customHeight="1"/>
-    <row r="149" ht="15.75" customHeight="1"/>
-    <row r="150" ht="15.75" customHeight="1"/>
-    <row r="151" ht="15.75" customHeight="1"/>
-    <row r="152" ht="15.75" customHeight="1"/>
-    <row r="153" ht="15.75" customHeight="1"/>
-    <row r="154" ht="15.75" customHeight="1"/>
-    <row r="155" ht="15.75" customHeight="1"/>
-    <row r="156" ht="15.75" customHeight="1"/>
-    <row r="157" ht="15.75" customHeight="1"/>
-    <row r="158" ht="15.75" customHeight="1"/>
-    <row r="159" ht="15.75" customHeight="1"/>
-    <row r="160" ht="15.75" customHeight="1"/>
-    <row r="161" ht="15.75" customHeight="1"/>
-    <row r="162" ht="15.75" customHeight="1"/>
-    <row r="163" ht="15.75" customHeight="1"/>
-    <row r="164" ht="15.75" customHeight="1"/>
-    <row r="165" ht="15.75" customHeight="1"/>
-    <row r="166" ht="15.75" customHeight="1"/>
-    <row r="167" ht="15.75" customHeight="1"/>
-    <row r="168" ht="15.75" customHeight="1"/>
-    <row r="169" ht="15.75" customHeight="1"/>
-    <row r="170" ht="15.75" customHeight="1"/>
-    <row r="171" ht="15.75" customHeight="1"/>
-    <row r="172" ht="15.75" customHeight="1"/>
-    <row r="173" ht="15.75" customHeight="1"/>
-    <row r="174" ht="15.75" customHeight="1"/>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
-    <row r="177" ht="15.75" customHeight="1"/>
-    <row r="178" ht="15.75" customHeight="1"/>
-    <row r="179" ht="15.75" customHeight="1"/>
-    <row r="180" ht="15.75" customHeight="1"/>
-    <row r="181" ht="15.75" customHeight="1"/>
-    <row r="182" ht="15.75" customHeight="1"/>
-    <row r="183" ht="15.75" customHeight="1"/>
-    <row r="184" ht="15.75" customHeight="1"/>
-    <row r="185" ht="15.75" customHeight="1"/>
-    <row r="186" ht="15.75" customHeight="1"/>
-    <row r="187" ht="15.75" customHeight="1"/>
-    <row r="188" ht="15.75" customHeight="1"/>
-    <row r="189" ht="15.75" customHeight="1"/>
-    <row r="190" ht="15.75" customHeight="1"/>
-    <row r="191" ht="15.75" customHeight="1"/>
-    <row r="192" ht="15.75" customHeight="1"/>
-    <row r="193" ht="15.75" customHeight="1"/>
-    <row r="194" ht="15.75" customHeight="1"/>
-    <row r="195" ht="15.75" customHeight="1"/>
-    <row r="196" ht="15.75" customHeight="1"/>
-    <row r="197" ht="15.75" customHeight="1"/>
-    <row r="198" ht="15.75" customHeight="1"/>
-    <row r="199" ht="15.75" customHeight="1"/>
-    <row r="200" ht="15.75" customHeight="1"/>
-    <row r="201" ht="15.75" customHeight="1"/>
-    <row r="202" ht="15.75" customHeight="1"/>
-    <row r="203" ht="15.75" customHeight="1"/>
-    <row r="204" ht="15.75" customHeight="1"/>
-    <row r="205" ht="15.75" customHeight="1"/>
-    <row r="206" ht="15.75" customHeight="1"/>
-    <row r="207" ht="15.75" customHeight="1"/>
-    <row r="208" ht="15.75" customHeight="1"/>
-    <row r="209" ht="15.75" customHeight="1"/>
-    <row r="210" ht="15.75" customHeight="1"/>
-    <row r="211" ht="15.75" customHeight="1"/>
-    <row r="212" ht="15.75" customHeight="1"/>
-    <row r="213" ht="15.75" customHeight="1"/>
-    <row r="214" ht="15.75" customHeight="1"/>
-    <row r="215" ht="15.75" customHeight="1"/>
-    <row r="216" ht="15.75" customHeight="1"/>
-    <row r="217" ht="15.75" customHeight="1"/>
-    <row r="218" ht="15.75" customHeight="1"/>
-    <row r="219" ht="15.75" customHeight="1"/>
-    <row r="220" ht="15.75" customHeight="1"/>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -15410,16 +15421,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:Q105"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.1328125" customWidth="1"/>
-    <col min="2" max="2" width="24.73046875" customWidth="1"/>
-    <col min="3" max="6" width="20.73046875" customWidth="1"/>
-    <col min="7" max="7" width="5.73046875" customWidth="1"/>
-    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="5.6640625" customWidth="1"/>
+    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="13.9">
+    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>55</v>
       </c>
@@ -15431,7 +15442,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="13.15">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B3" s="109" t="s">
         <v>163</v>
       </c>
@@ -15444,7 +15455,7 @@
       </c>
       <c r="H3" s="120"/>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B4" s="100" t="s">
         <v>128</v>
       </c>
@@ -15465,7 +15476,7 @@
       </c>
       <c r="H4" s="120"/>
     </row>
-    <row r="5" spans="2:8">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B5" s="205" t="s">
         <v>123</v>
       </c>
@@ -15476,7 +15487,7 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.35" customHeight="1">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="149" t="s">
         <v>228</v>
       </c>
@@ -15494,7 +15505,7 @@
       <c r="F6" s="364"/>
       <c r="H6" s="120"/>
     </row>
-    <row r="7" spans="2:8">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B7" s="148" t="s">
         <v>224</v>
       </c>
@@ -15510,7 +15521,7 @@
       <c r="F7" s="364"/>
       <c r="H7" s="120"/>
     </row>
-    <row r="8" spans="2:8">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B8" s="148" t="s">
         <v>225</v>
       </c>
@@ -15526,7 +15537,7 @@
       <c r="F8" s="364"/>
       <c r="H8" s="120"/>
     </row>
-    <row r="9" spans="2:8">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B9" s="205" t="s">
         <v>190</v>
       </c>
@@ -15542,7 +15553,7 @@
       <c r="F9" s="364"/>
       <c r="H9" s="120"/>
     </row>
-    <row r="10" spans="2:8" ht="13.15">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B10" s="149" t="s">
         <v>227</v>
       </c>
@@ -15556,7 +15567,7 @@
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="13.15" thickBot="1">
+    <row r="11" spans="2:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B11" s="207" t="s">
         <v>166</v>
       </c>
@@ -15570,7 +15581,7 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="13.5" thickTop="1">
+    <row r="12" spans="2:8" ht="14" thickTop="1" x14ac:dyDescent="0.15">
       <c r="B12" s="149" t="s">
         <v>102</v>
       </c>
@@ -15584,10 +15595,10 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.15">
       <c r="H13" s="120"/>
     </row>
-    <row r="14" spans="2:8" ht="13.9">
+    <row r="14" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B14" s="36" t="s">
         <v>229</v>
       </c>
@@ -15597,13 +15608,13 @@
       <c r="F14" s="37"/>
       <c r="H14" s="120"/>
     </row>
-    <row r="15" spans="2:8" ht="13.15">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B15" s="119" t="s">
         <v>135</v>
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8" ht="13.35" customHeight="1">
+    <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="152" t="s">
         <v>133</v>
       </c>
@@ -15613,7 +15624,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:17" ht="13.35" customHeight="1">
+    <row r="17" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="118" t="s">
         <v>134</v>
       </c>
@@ -15623,7 +15634,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:17" ht="13.35" customHeight="1">
+    <row r="18" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="153" t="s">
         <v>106</v>
       </c>
@@ -15637,10 +15648,10 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:17">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.15">
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:17" ht="13.15">
+    <row r="20" spans="2:17" ht="14" x14ac:dyDescent="0.2">
       <c r="B20" s="128" t="s">
         <v>107</v>
       </c>
@@ -15658,7 +15669,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:17">
+    <row r="21" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B21" s="122">
         <v>1</v>
       </c>
@@ -15680,7 +15691,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:17">
+    <row r="22" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B22" s="122">
         <v>2</v>
       </c>
@@ -15702,7 +15713,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:17">
+    <row r="23" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B23" s="122">
         <v>3</v>
       </c>
@@ -15734,7 +15745,7 @@
       <c r="P23" s="338"/>
       <c r="Q23" s="338"/>
     </row>
-    <row r="24" spans="2:17">
+    <row r="24" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B24" s="122">
         <v>4</v>
       </c>
@@ -15766,7 +15777,7 @@
       <c r="P24" s="338"/>
       <c r="Q24" s="338"/>
     </row>
-    <row r="25" spans="2:17">
+    <row r="25" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B25" s="122">
         <v>5</v>
       </c>
@@ -15798,7 +15809,7 @@
       <c r="P25" s="338"/>
       <c r="Q25" s="338"/>
     </row>
-    <row r="26" spans="2:17">
+    <row r="26" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B26" s="122">
         <v>6</v>
       </c>
@@ -15820,7 +15831,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:17">
+    <row r="27" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B27" s="122">
         <v>7</v>
       </c>
@@ -15842,7 +15853,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:17">
+    <row r="28" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B28" s="122">
         <v>8</v>
       </c>
@@ -15864,7 +15875,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:17">
+    <row r="29" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B29" s="122">
         <v>9</v>
       </c>
@@ -15886,7 +15897,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:17">
+    <row r="30" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B30" s="122">
         <v>10</v>
       </c>
@@ -15908,7 +15919,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:17">
+    <row r="31" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B31" s="122">
         <v>11</v>
       </c>
@@ -15930,7 +15941,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:17">
+    <row r="32" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B32" s="122">
         <v>12</v>
       </c>
@@ -15952,7 +15963,7 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:17">
+    <row r="33" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B33" s="122">
         <v>13</v>
       </c>
@@ -15984,7 +15995,7 @@
       <c r="P33" s="338"/>
       <c r="Q33" s="338"/>
     </row>
-    <row r="34" spans="2:17">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B34" s="122">
         <v>14</v>
       </c>
@@ -16016,7 +16027,7 @@
       <c r="P34" s="338"/>
       <c r="Q34" s="338"/>
     </row>
-    <row r="35" spans="2:17">
+    <row r="35" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B35" s="122">
         <v>15</v>
       </c>
@@ -16048,7 +16059,7 @@
       <c r="P35" s="338"/>
       <c r="Q35" s="338"/>
     </row>
-    <row r="36" spans="2:17">
+    <row r="36" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B36" s="122">
         <v>16</v>
       </c>
@@ -16070,7 +16081,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:17">
+    <row r="37" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B37" s="122">
         <v>17</v>
       </c>
@@ -16092,7 +16103,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:17">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B38" s="122">
         <v>18</v>
       </c>
@@ -16114,7 +16125,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:17">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B39" s="122">
         <v>19</v>
       </c>
@@ -16136,7 +16147,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:17">
+    <row r="40" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B40" s="122">
         <v>20</v>
       </c>
@@ -16158,7 +16169,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:17">
+    <row r="41" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B41" s="122">
         <v>21</v>
       </c>
@@ -16180,7 +16191,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:17">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B42" s="122">
         <v>22</v>
       </c>
@@ -16202,7 +16213,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:17">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B43" s="122">
         <v>23</v>
       </c>
@@ -16224,7 +16235,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:17">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B44" s="122">
         <v>24</v>
       </c>
@@ -16246,7 +16257,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:17">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B45" s="122">
         <v>25</v>
       </c>
@@ -16268,7 +16279,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:17">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B46" s="122">
         <v>26</v>
       </c>
@@ -16290,7 +16301,7 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:17">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B47" s="122">
         <v>27</v>
       </c>
@@ -16322,7 +16333,7 @@
       <c r="P47" s="338"/>
       <c r="Q47" s="338"/>
     </row>
-    <row r="48" spans="2:17">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B48" s="122">
         <v>28</v>
       </c>
@@ -16354,7 +16365,7 @@
       <c r="P48" s="338"/>
       <c r="Q48" s="338"/>
     </row>
-    <row r="49" spans="1:17">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B49" s="122">
         <v>29</v>
       </c>
@@ -16386,7 +16397,7 @@
       <c r="P49" s="338"/>
       <c r="Q49" s="338"/>
     </row>
-    <row r="50" spans="1:17">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B50" s="122">
         <v>30</v>
       </c>
@@ -16418,7 +16429,7 @@
       <c r="P50" s="338"/>
       <c r="Q50" s="338"/>
     </row>
-    <row r="51" spans="1:17">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B51" s="126" t="s">
         <v>131</v>
       </c>
@@ -16440,7 +16451,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:17">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.15">
       <c r="C52" s="114"/>
       <c r="E52" s="127" t="s">
         <v>100</v>
@@ -16451,11 +16462,11 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:17">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.15">
       <c r="C53" s="114"/>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:17" ht="13.15">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B54" s="119" t="s">
         <v>129</v>
       </c>
@@ -16465,7 +16476,7 @@
       <c r="F54" s="117"/>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:17" ht="13.15">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A55" s="133">
         <f>F52</f>
         <v>2134789.7838004301</v>
@@ -16492,7 +16503,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:17" ht="13.15">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A56" s="143">
         <v>5</v>
       </c>
@@ -16514,7 +16525,7 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:17" ht="13.15">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A57" s="143">
         <v>10</v>
       </c>
@@ -16535,7 +16546,7 @@
       </c>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:17" ht="13.15">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A58" s="143">
         <v>15</v>
       </c>
@@ -16566,7 +16577,7 @@
       <c r="P58" s="338"/>
       <c r="Q58" s="338"/>
     </row>
-    <row r="59" spans="1:17" ht="13.15">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A59" s="144">
         <v>20</v>
       </c>
@@ -16597,7 +16608,7 @@
       <c r="P59" s="338"/>
       <c r="Q59" s="338"/>
     </row>
-    <row r="60" spans="1:17" ht="13.15">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A60" s="144">
         <v>25</v>
       </c>
@@ -16628,7 +16639,7 @@
       <c r="P60" s="338"/>
       <c r="Q60" s="338"/>
     </row>
-    <row r="61" spans="1:17" ht="13.15">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A61" s="144">
         <v>30</v>
       </c>
@@ -16659,7 +16670,7 @@
       <c r="P61" s="338"/>
       <c r="Q61" s="338"/>
     </row>
-    <row r="62" spans="1:17">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.15">
       <c r="C62" s="338"/>
       <c r="D62" s="114"/>
       <c r="E62" s="114"/>
@@ -16676,7 +16687,7 @@
       <c r="P62" s="338"/>
       <c r="Q62" s="338"/>
     </row>
-    <row r="63" spans="1:17" ht="13.15">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B63" s="119" t="s">
         <v>130</v>
       </c>
@@ -16696,7 +16707,7 @@
       <c r="P63" s="338"/>
       <c r="Q63" s="338"/>
     </row>
-    <row r="64" spans="1:17" ht="13.15">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B64" s="132">
         <f>B55</f>
         <v>0</v>
@@ -16719,7 +16730,7 @@
       </c>
       <c r="H64" s="120"/>
     </row>
-    <row r="65" spans="1:8" ht="13.15">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A65" s="143">
         <v>0</v>
       </c>
@@ -16745,7 +16756,7 @@
       </c>
       <c r="H65" s="120"/>
     </row>
-    <row r="66" spans="1:8" ht="13.15">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A66" s="143">
         <f t="shared" ref="A66:A71" si="3">A56</f>
         <v>5</v>
@@ -16772,7 +16783,7 @@
       </c>
       <c r="H66" s="120"/>
     </row>
-    <row r="67" spans="1:8" ht="13.15">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A67" s="143">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -16799,7 +16810,7 @@
       </c>
       <c r="H67" s="120"/>
     </row>
-    <row r="68" spans="1:8" ht="13.15">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A68" s="143">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -16826,7 +16837,7 @@
       </c>
       <c r="H68" s="120"/>
     </row>
-    <row r="69" spans="1:8" ht="13.15">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A69" s="144">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -16853,7 +16864,7 @@
       </c>
       <c r="H69" s="120"/>
     </row>
-    <row r="70" spans="1:8" ht="13.15">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A70" s="144">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -16879,7 +16890,7 @@
         <v>11.230437768943993</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="13.15">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A71" s="144">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -16905,7 +16916,7 @@
         <v>13.727281395318631</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="13.15">
+    <row r="73" spans="1:8" ht="14" x14ac:dyDescent="0.2">
       <c r="B73" s="171" t="s">
         <v>117</v>
       </c>
@@ -16922,7 +16933,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B74" s="127" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -16944,7 +16955,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B75" s="127" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -16967,7 +16978,7 @@
       </c>
       <c r="H75" s="120"/>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B76" s="127" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -16990,7 +17001,7 @@
       </c>
       <c r="H76" s="120"/>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B77" s="127" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -17013,7 +17024,7 @@
       </c>
       <c r="H77" s="120"/>
     </row>
-    <row r="78" spans="1:8">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B78" s="127" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -17035,14 +17046,14 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="79" spans="1:8">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B79" s="155"/>
       <c r="C79" s="155"/>
       <c r="D79" s="155"/>
       <c r="E79" s="155"/>
       <c r="F79" s="156"/>
     </row>
-    <row r="80" spans="1:8">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B80" s="155" t="s">
         <v>310</v>
       </c>
@@ -17050,26 +17061,26 @@
         <v>105</v>
       </c>
     </row>
-    <row r="81" spans="3:3">
+    <row r="81" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C81" s="155" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="82" spans="3:3">
+    <row r="82" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C82" s="155" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="92" spans="3:3">
+    <row r="92" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C92" s="115"/>
     </row>
-    <row r="93" spans="3:3">
+    <row r="93" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C93" s="115"/>
     </row>
-    <row r="94" spans="3:3">
+    <row r="94" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C94" s="115"/>
     </row>
-    <row r="101" spans="3:17">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C101" s="338"/>
       <c r="G101" s="338"/>
       <c r="H101" s="338"/>
@@ -17083,7 +17094,7 @@
       <c r="P101" s="338"/>
       <c r="Q101" s="338"/>
     </row>
-    <row r="102" spans="3:17">
+    <row r="102" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C102" s="338"/>
       <c r="G102" s="338"/>
       <c r="H102" s="338"/>
@@ -17097,7 +17108,7 @@
       <c r="P102" s="338"/>
       <c r="Q102" s="338"/>
     </row>
-    <row r="103" spans="3:17">
+    <row r="103" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C103" s="338"/>
       <c r="G103" s="338"/>
       <c r="H103" s="338"/>
@@ -17111,7 +17122,7 @@
       <c r="P103" s="338"/>
       <c r="Q103" s="338"/>
     </row>
-    <row r="104" spans="3:17">
+    <row r="104" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C104" s="338"/>
       <c r="G104" s="338"/>
       <c r="H104" s="338"/>
@@ -17125,7 +17136,7 @@
       <c r="P104" s="338"/>
       <c r="Q104" s="338"/>
     </row>
-    <row r="105" spans="3:17">
+    <row r="105" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C105" s="338"/>
       <c r="G105" s="338"/>
       <c r="H105" s="338"/>
@@ -17170,16 +17181,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H89"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.1328125" customWidth="1"/>
-    <col min="2" max="2" width="24.73046875" customWidth="1"/>
-    <col min="3" max="6" width="20.73046875" customWidth="1"/>
-    <col min="7" max="7" width="5.73046875" customWidth="1"/>
-    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="5.6640625" customWidth="1"/>
+    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="13.9">
+    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>442</v>
       </c>
@@ -17191,7 +17202,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="13.15">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B3" s="109" t="s">
         <v>441</v>
       </c>
@@ -17204,7 +17215,7 @@
       </c>
       <c r="H3" s="120"/>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B4" s="100" t="s">
         <v>439</v>
       </c>
@@ -17225,7 +17236,7 @@
       </c>
       <c r="H4" s="120"/>
     </row>
-    <row r="5" spans="2:8">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B5" s="205" t="s">
         <v>123</v>
       </c>
@@ -17236,7 +17247,7 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.35" customHeight="1">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="149" t="s">
         <v>440</v>
       </c>
@@ -17252,7 +17263,7 @@
       <c r="F6" s="364"/>
       <c r="H6" s="120"/>
     </row>
-    <row r="7" spans="2:8" ht="13.15">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B7" s="149" t="s">
         <v>443</v>
       </c>
@@ -17266,10 +17277,10 @@
       </c>
       <c r="H7" s="120"/>
     </row>
-    <row r="8" spans="2:8">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
       <c r="H8" s="120"/>
     </row>
-    <row r="9" spans="2:8" ht="13.9">
+    <row r="9" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B9" s="36" t="s">
         <v>229</v>
       </c>
@@ -17279,13 +17290,13 @@
       <c r="F9" s="37"/>
       <c r="H9" s="120"/>
     </row>
-    <row r="10" spans="2:8" ht="13.15">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B10" s="119" t="s">
         <v>135</v>
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="13.35" customHeight="1">
+    <row r="11" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="152" t="s">
         <v>133</v>
       </c>
@@ -17295,7 +17306,7 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="13.35" customHeight="1">
+    <row r="12" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="118" t="s">
         <v>134</v>
       </c>
@@ -17305,7 +17316,7 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8" ht="13.35" customHeight="1">
+    <row r="13" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="153" t="s">
         <v>106</v>
       </c>
@@ -17319,10 +17330,10 @@
       </c>
       <c r="H13" s="120"/>
     </row>
-    <row r="14" spans="2:8">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.15">
       <c r="H14" s="120"/>
     </row>
-    <row r="15" spans="2:8" ht="13.15">
+    <row r="15" spans="2:8" ht="14" x14ac:dyDescent="0.2">
       <c r="B15" s="128" t="s">
         <v>107</v>
       </c>
@@ -17340,7 +17351,7 @@
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B16" s="122">
         <v>1</v>
       </c>
@@ -17362,7 +17373,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:8">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B17" s="122">
         <v>2</v>
       </c>
@@ -17384,7 +17395,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:8">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B18" s="122">
         <v>3</v>
       </c>
@@ -17406,7 +17417,7 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:8">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B19" s="122">
         <v>4</v>
       </c>
@@ -17428,7 +17439,7 @@
       </c>
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:8">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B20" s="122">
         <v>5</v>
       </c>
@@ -17450,7 +17461,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:8">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B21" s="122">
         <v>6</v>
       </c>
@@ -17472,7 +17483,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:8">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B22" s="122">
         <v>7</v>
       </c>
@@ -17494,7 +17505,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:8">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B23" s="122">
         <v>8</v>
       </c>
@@ -17516,7 +17527,7 @@
       </c>
       <c r="H23" s="120"/>
     </row>
-    <row r="24" spans="2:8">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B24" s="122">
         <v>9</v>
       </c>
@@ -17538,7 +17549,7 @@
       </c>
       <c r="H24" s="120"/>
     </row>
-    <row r="25" spans="2:8">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B25" s="122">
         <v>10</v>
       </c>
@@ -17560,7 +17571,7 @@
       </c>
       <c r="H25" s="120"/>
     </row>
-    <row r="26" spans="2:8">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B26" s="122">
         <v>11</v>
       </c>
@@ -17582,7 +17593,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:8">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B27" s="122">
         <v>12</v>
       </c>
@@ -17604,7 +17615,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:8">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B28" s="122">
         <v>13</v>
       </c>
@@ -17626,7 +17637,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:8">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B29" s="122">
         <v>14</v>
       </c>
@@ -17648,7 +17659,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:8">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B30" s="122">
         <v>15</v>
       </c>
@@ -17670,7 +17681,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:8">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B31" s="122">
         <v>16</v>
       </c>
@@ -17692,7 +17703,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:8">
+    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B32" s="122">
         <v>17</v>
       </c>
@@ -17714,7 +17725,7 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:8">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B33" s="122">
         <v>18</v>
       </c>
@@ -17736,7 +17747,7 @@
       </c>
       <c r="H33" s="120"/>
     </row>
-    <row r="34" spans="2:8">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B34" s="122">
         <v>19</v>
       </c>
@@ -17758,7 +17769,7 @@
       </c>
       <c r="H34" s="120"/>
     </row>
-    <row r="35" spans="2:8">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B35" s="122">
         <v>20</v>
       </c>
@@ -17780,7 +17791,7 @@
       </c>
       <c r="H35" s="120"/>
     </row>
-    <row r="36" spans="2:8">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B36" s="122">
         <v>21</v>
       </c>
@@ -17802,7 +17813,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:8">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B37" s="122">
         <v>22</v>
       </c>
@@ -17824,7 +17835,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:8">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B38" s="122">
         <v>23</v>
       </c>
@@ -17846,7 +17857,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:8">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B39" s="122">
         <v>24</v>
       </c>
@@ -17868,7 +17879,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:8">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B40" s="122">
         <v>25</v>
       </c>
@@ -17890,7 +17901,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:8">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B41" s="122">
         <v>26</v>
       </c>
@@ -17912,7 +17923,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:8">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B42" s="122">
         <v>27</v>
       </c>
@@ -17934,7 +17945,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:8">
+    <row r="43" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B43" s="122">
         <v>28</v>
       </c>
@@ -17956,7 +17967,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:8">
+    <row r="44" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B44" s="122">
         <v>29</v>
       </c>
@@ -17978,7 +17989,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:8">
+    <row r="45" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B45" s="122">
         <v>30</v>
       </c>
@@ -18000,7 +18011,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:8">
+    <row r="46" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B46" s="126" t="s">
         <v>131</v>
       </c>
@@ -18022,7 +18033,7 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:8">
+    <row r="47" spans="2:8" x14ac:dyDescent="0.15">
       <c r="C47" s="114"/>
       <c r="E47" s="127" t="s">
         <v>100</v>
@@ -18033,11 +18044,11 @@
       </c>
       <c r="H47" s="120"/>
     </row>
-    <row r="48" spans="2:8">
+    <row r="48" spans="2:8" x14ac:dyDescent="0.15">
       <c r="C48" s="114"/>
       <c r="H48" s="120"/>
     </row>
-    <row r="49" spans="1:8" ht="13.15">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B49" s="119" t="s">
         <v>129</v>
       </c>
@@ -18047,7 +18058,7 @@
       <c r="F49" s="117"/>
       <c r="H49" s="120"/>
     </row>
-    <row r="50" spans="1:8" ht="13.15">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A50" s="133">
         <f>F47</f>
         <v>962285.7114352209</v>
@@ -18074,7 +18085,7 @@
       </c>
       <c r="H50" s="120"/>
     </row>
-    <row r="51" spans="1:8" ht="13.15">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A51" s="143">
         <v>5</v>
       </c>
@@ -18096,7 +18107,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:8" ht="13.15">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A52" s="143">
         <v>10</v>
       </c>
@@ -18117,7 +18128,7 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:8" ht="13.15">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A53" s="143">
         <v>15</v>
       </c>
@@ -18138,7 +18149,7 @@
       </c>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:8" ht="13.15">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A54" s="144">
         <v>20</v>
       </c>
@@ -18159,7 +18170,7 @@
       </c>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:8" ht="13.15">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A55" s="144">
         <v>25</v>
       </c>
@@ -18180,7 +18191,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:8" ht="13.15">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A56" s="144">
         <v>30</v>
       </c>
@@ -18201,14 +18212,14 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
       <c r="C57" s="114"/>
       <c r="D57" s="114"/>
       <c r="E57" s="114"/>
       <c r="F57" s="114"/>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:8" ht="13.15">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B58" s="119" t="s">
         <v>130</v>
       </c>
@@ -18218,7 +18229,7 @@
       <c r="F58" s="114"/>
       <c r="H58" s="120"/>
     </row>
-    <row r="59" spans="1:8" ht="13.15">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B59" s="132">
         <f>B50</f>
         <v>0</v>
@@ -18241,7 +18252,7 @@
       </c>
       <c r="H59" s="120"/>
     </row>
-    <row r="60" spans="1:8" ht="13.15">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A60" s="143">
         <v>0</v>
       </c>
@@ -18267,7 +18278,7 @@
       </c>
       <c r="H60" s="120"/>
     </row>
-    <row r="61" spans="1:8" ht="13.15">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A61" s="143">
         <f t="shared" ref="A61:A66" si="3">A51</f>
         <v>5</v>
@@ -18294,7 +18305,7 @@
       </c>
       <c r="H61" s="120"/>
     </row>
-    <row r="62" spans="1:8" ht="13.15">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A62" s="143">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -18321,7 +18332,7 @@
       </c>
       <c r="H62" s="120"/>
     </row>
-    <row r="63" spans="1:8" ht="13.15">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A63" s="143">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -18348,7 +18359,7 @@
       </c>
       <c r="H63" s="120"/>
     </row>
-    <row r="64" spans="1:8" ht="13.15">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A64" s="144">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -18375,7 +18386,7 @@
       </c>
       <c r="H64" s="120"/>
     </row>
-    <row r="65" spans="1:8" ht="13.15">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A65" s="144">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -18401,7 +18412,7 @@
         <v>4.6820200777530729</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="13.15">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A66" s="144">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -18427,7 +18438,7 @@
         <v>5.8075065137388604</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="13.15">
+    <row r="68" spans="1:8" ht="14" x14ac:dyDescent="0.2">
       <c r="B68" s="171" t="s">
         <v>117</v>
       </c>
@@ -18444,7 +18455,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B69" s="127" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -18466,7 +18477,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B70" s="127" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -18489,7 +18500,7 @@
       </c>
       <c r="H70" s="120"/>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B71" s="127" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -18512,7 +18523,7 @@
       </c>
       <c r="H71" s="120"/>
     </row>
-    <row r="72" spans="1:8">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B72" s="127" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -18535,7 +18546,7 @@
       </c>
       <c r="H72" s="120"/>
     </row>
-    <row r="73" spans="1:8">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B73" s="127" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -18557,14 +18568,14 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B74" s="155"/>
       <c r="C74" s="155"/>
       <c r="D74" s="155"/>
       <c r="E74" s="155"/>
       <c r="F74" s="156"/>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B75" s="155" t="s">
         <v>310</v>
       </c>
@@ -18572,23 +18583,23 @@
         <v>105</v>
       </c>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
       <c r="C76" s="155" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
       <c r="C77" s="155" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="87" spans="3:3">
+    <row r="87" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C87" s="115"/>
     </row>
-    <row r="88" spans="3:3">
+    <row r="88" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C88" s="115"/>
     </row>
-    <row r="89" spans="3:3">
+    <row r="89" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C89" s="115"/>
     </row>
   </sheetData>
@@ -18618,17 +18629,17 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.73046875" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" customWidth="1"/>
     <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.73046875" customWidth="1"/>
-    <col min="5" max="6" width="42.73046875" customWidth="1"/>
-    <col min="8" max="9" width="15.73046875" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" customWidth="1"/>
+    <col min="5" max="6" width="42.6640625" customWidth="1"/>
+    <col min="8" max="9" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="13.9">
+    <row r="2" spans="2:9" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>145</v>
       </c>
@@ -18641,7 +18652,7 @@
       </c>
       <c r="I2" s="249"/>
     </row>
-    <row r="3" spans="2:9" ht="13.15">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B3" s="159" t="s">
         <v>148</v>
       </c>
@@ -18650,10 +18661,10 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-3.58</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9">
+        <v>-3.6</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B4" s="152" t="s">
         <v>146</v>
       </c>
@@ -18673,7 +18684,7 @@
         <v>0.128</v>
       </c>
     </row>
-    <row r="5" spans="2:9">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.15">
       <c r="H5" s="247">
         <v>2</v>
       </c>
@@ -18682,7 +18693,7 @@
         <v>0.128</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="13.15">
+    <row r="6" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B6" s="159" t="s">
         <v>95</v>
       </c>
@@ -18702,7 +18713,7 @@
         <v>5.3526962590200808</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="12.75" customHeight="1">
+    <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="100" t="s">
         <v>275</v>
       </c>
@@ -18727,7 +18738,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="2:9">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
@@ -18749,7 +18760,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="2:9">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
@@ -18771,7 +18782,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="2:9">
+    <row r="10" spans="2:9" x14ac:dyDescent="0.15">
       <c r="E10" s="366"/>
       <c r="F10" s="366"/>
       <c r="H10" s="247">
@@ -18782,7 +18793,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="2:9" ht="13.15">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B11" s="159" t="s">
         <v>446</v>
       </c>
@@ -18796,7 +18807,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="2:9">
+    <row r="12" spans="2:9" ht="14" x14ac:dyDescent="0.15">
       <c r="B12" s="118" t="s">
         <v>144</v>
       </c>
@@ -18815,7 +18826,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="2:9">
+    <row r="13" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B13" s="148" t="s">
         <v>152</v>
       </c>
@@ -18833,7 +18844,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="2:9">
+    <row r="14" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B14" s="100" t="s">
         <v>66</v>
       </c>
@@ -18844,7 +18855,7 @@
       <c r="E14" s="366"/>
       <c r="F14" s="366"/>
     </row>
-    <row r="16" spans="2:9" ht="13.9">
+    <row r="16" spans="2:9" ht="16" x14ac:dyDescent="0.25">
       <c r="B16" s="36" t="s">
         <v>162</v>
       </c>
@@ -18853,7 +18864,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="37"/>
     </row>
-    <row r="17" spans="2:6" ht="13.15">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B17" s="109" t="s">
         <v>151</v>
       </c>
@@ -18861,7 +18872,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="18" spans="2:6">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B18" s="152" t="s">
         <v>133</v>
       </c>
@@ -18873,24 +18884,24 @@
       </c>
       <c r="F18" s="367"/>
     </row>
-    <row r="19" spans="2:6">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.15">
       <c r="E19" s="367"/>
       <c r="F19" s="367"/>
     </row>
-    <row r="20" spans="2:6" ht="13.15">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B20" s="159" t="s">
         <v>303</v>
       </c>
       <c r="E20" s="367"/>
       <c r="F20" s="367"/>
     </row>
-    <row r="21" spans="2:6">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B21" s="100" t="s">
         <v>277</v>
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -18899,7 +18910,7 @@
       <c r="E21" s="367"/>
       <c r="F21" s="367"/>
     </row>
-    <row r="22" spans="2:6">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B22" s="100" t="s">
         <v>278</v>
       </c>
@@ -18914,7 +18925,7 @@
       <c r="E22" s="367"/>
       <c r="F22" s="367"/>
     </row>
-    <row r="24" spans="2:6" ht="13.15">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B24" s="159" t="s">
         <v>115</v>
       </c>
@@ -18923,7 +18934,7 @@
       </c>
       <c r="F24" s="159"/>
     </row>
-    <row r="25" spans="2:6">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B25" s="152" t="s">
         <v>133</v>
       </c>
@@ -18935,7 +18946,7 @@
       <c r="E25" s="365"/>
       <c r="F25" s="365"/>
     </row>
-    <row r="26" spans="2:6">
+    <row r="26" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B26" s="118" t="s">
         <v>134</v>
       </c>
@@ -18946,7 +18957,7 @@
       <c r="E26" s="365"/>
       <c r="F26" s="365"/>
     </row>
-    <row r="27" spans="2:6">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B27" s="100" t="s">
         <v>113</v>
       </c>
@@ -18961,7 +18972,7 @@
       <c r="E27" s="365"/>
       <c r="F27" s="365"/>
     </row>
-    <row r="28" spans="2:6">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B28" s="100" t="s">
         <v>147</v>
       </c>
@@ -18972,7 +18983,7 @@
       <c r="E28" s="365"/>
       <c r="F28" s="365"/>
     </row>
-    <row r="30" spans="2:6" ht="13.15">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B30" s="159" t="s">
         <v>116</v>
       </c>
@@ -18981,7 +18992,7 @@
       </c>
       <c r="F30" s="159"/>
     </row>
-    <row r="31" spans="2:6">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B31" s="152" t="s">
         <v>133</v>
       </c>
@@ -18993,7 +19004,7 @@
       <c r="E31" s="365"/>
       <c r="F31" s="365"/>
     </row>
-    <row r="32" spans="2:6">
+    <row r="32" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B32" s="118" t="s">
         <v>134</v>
       </c>
@@ -19004,7 +19015,7 @@
       <c r="E32" s="365"/>
       <c r="F32" s="365"/>
     </row>
-    <row r="33" spans="2:6">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B33" s="100" t="s">
         <v>113</v>
       </c>
@@ -19019,7 +19030,7 @@
       <c r="E33" s="365"/>
       <c r="F33" s="365"/>
     </row>
-    <row r="34" spans="2:6">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B34" s="100" t="s">
         <v>147</v>
       </c>
@@ -19030,7 +19041,7 @@
       <c r="E34" s="365"/>
       <c r="F34" s="365"/>
     </row>
-    <row r="36" spans="2:6" ht="13.15">
+    <row r="36" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B36" s="159" t="s">
         <v>114</v>
       </c>
@@ -19039,7 +19050,7 @@
       </c>
       <c r="F36" s="159"/>
     </row>
-    <row r="37" spans="2:6">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B37" s="152" t="s">
         <v>133</v>
       </c>
@@ -19051,7 +19062,7 @@
       <c r="E37" s="365"/>
       <c r="F37" s="365"/>
     </row>
-    <row r="38" spans="2:6">
+    <row r="38" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B38" s="118" t="s">
         <v>134</v>
       </c>
@@ -19062,7 +19073,7 @@
       <c r="E38" s="365"/>
       <c r="F38" s="365"/>
     </row>
-    <row r="39" spans="2:6">
+    <row r="39" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B39" s="100" t="s">
         <v>113</v>
       </c>
@@ -19077,7 +19088,7 @@
       <c r="E39" s="365"/>
       <c r="F39" s="365"/>
     </row>
-    <row r="40" spans="2:6">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B40" s="100" t="s">
         <v>147</v>
       </c>
@@ -19089,7 +19100,7 @@
       <c r="E40" s="365"/>
       <c r="F40" s="365"/>
     </row>
-    <row r="42" spans="2:6" ht="13.15">
+    <row r="42" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B42" s="100" t="s">
         <v>120</v>
       </c>
@@ -19102,7 +19113,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="13.9">
+    <row r="44" spans="2:6" ht="16" x14ac:dyDescent="0.25">
       <c r="B44" s="36" t="s">
         <v>161</v>
       </c>
@@ -19111,12 +19122,12 @@
       <c r="E44" s="37"/>
       <c r="F44" s="37"/>
     </row>
-    <row r="45" spans="2:6" ht="13.15">
+    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B45" s="109" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="46" spans="2:6">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B46" s="152" t="s">
         <v>133</v>
       </c>
@@ -19126,12 +19137,12 @@
       <c r="E46" s="100"/>
       <c r="F46" s="100"/>
     </row>
-    <row r="47" spans="2:6" ht="13.15">
+    <row r="47" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B47" s="159"/>
       <c r="E47" s="159"/>
       <c r="F47" s="159"/>
     </row>
-    <row r="48" spans="2:6" ht="13.15">
+    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B48" s="159" t="s">
         <v>165</v>
       </c>
@@ -19140,7 +19151,7 @@
       </c>
       <c r="F48" s="159"/>
     </row>
-    <row r="49" spans="2:6" ht="12.75" customHeight="1">
+    <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B49" s="152" t="s">
         <v>133</v>
       </c>
@@ -19152,7 +19163,7 @@
       <c r="E49" s="365"/>
       <c r="F49" s="365"/>
     </row>
-    <row r="50" spans="2:6">
+    <row r="50" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B50" s="118" t="s">
         <v>134</v>
       </c>
@@ -19163,7 +19174,7 @@
       <c r="E50" s="365"/>
       <c r="F50" s="365"/>
     </row>
-    <row r="51" spans="2:6">
+    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B51" s="100" t="s">
         <v>113</v>
       </c>
@@ -19178,7 +19189,7 @@
       <c r="E51" s="365"/>
       <c r="F51" s="365"/>
     </row>
-    <row r="52" spans="2:6">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B52" s="100" t="s">
         <v>147</v>
       </c>
@@ -19189,7 +19200,7 @@
       <c r="E52" s="365"/>
       <c r="F52" s="365"/>
     </row>
-    <row r="54" spans="2:6" ht="13.15">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B54" s="159" t="s">
         <v>316</v>
       </c>
@@ -19198,7 +19209,7 @@
       </c>
       <c r="F54" s="159"/>
     </row>
-    <row r="55" spans="2:6">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B55" s="152" t="s">
         <v>133</v>
       </c>
@@ -19210,7 +19221,7 @@
       <c r="E55" s="365"/>
       <c r="F55" s="365"/>
     </row>
-    <row r="56" spans="2:6">
+    <row r="56" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B56" s="118" t="s">
         <v>134</v>
       </c>
@@ -19221,7 +19232,7 @@
       <c r="E56" s="365"/>
       <c r="F56" s="365"/>
     </row>
-    <row r="57" spans="2:6">
+    <row r="57" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B57" s="100" t="s">
         <v>113</v>
       </c>
@@ -19236,7 +19247,7 @@
       <c r="E57" s="365"/>
       <c r="F57" s="365"/>
     </row>
-    <row r="58" spans="2:6">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B58" s="100" t="s">
         <v>147</v>
       </c>
@@ -19247,7 +19258,7 @@
       <c r="E58" s="365"/>
       <c r="F58" s="365"/>
     </row>
-    <row r="60" spans="2:6" ht="13.15">
+    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B60" s="100" t="s">
         <v>120</v>
       </c>
@@ -19267,7 +19278,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="2:6" ht="13.9">
+    <row r="62" spans="2:6" ht="16" x14ac:dyDescent="0.25">
       <c r="B62" s="36" t="s">
         <v>349</v>
       </c>
@@ -19276,7 +19287,7 @@
       <c r="E62" s="37"/>
       <c r="F62" s="37"/>
     </row>
-    <row r="63" spans="2:6" ht="13.15">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B63" s="109" t="s">
         <v>304</v>
       </c>
@@ -19284,7 +19295,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="64" spans="2:6">
+    <row r="64" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B64" s="152" t="s">
         <v>133</v>
       </c>
@@ -19297,7 +19308,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="65" spans="2:6">
+    <row r="65" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B65" s="118" t="s">
         <v>134</v>
       </c>
@@ -19309,7 +19320,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="66" spans="2:6">
+    <row r="66" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B66" s="100" t="s">
         <v>102</v>
       </c>
@@ -19325,7 +19336,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="68" spans="2:6" ht="13.15">
+    <row r="68" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B68" s="109" t="s">
         <v>350</v>
       </c>
@@ -19333,7 +19344,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="69" spans="2:6">
+    <row r="69" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B69" s="100" t="s">
         <v>305</v>
       </c>
@@ -19343,7 +19354,7 @@
       </c>
       <c r="E69" s="134"/>
     </row>
-    <row r="70" spans="2:6">
+    <row r="70" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B70" s="100" t="s">
         <v>293</v>
       </c>
@@ -19355,7 +19366,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="71" spans="2:6">
+    <row r="71" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B71" s="100" t="s">
         <v>292</v>
       </c>
@@ -19365,7 +19376,7 @@
       </c>
       <c r="E71" s="251"/>
     </row>
-    <row r="72" spans="2:6">
+    <row r="72" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B72" s="100" t="s">
         <v>284</v>
       </c>
@@ -19381,7 +19392,7 @@
         <v>0.16145934558016128</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="13.9">
+    <row r="74" spans="2:6" ht="16" x14ac:dyDescent="0.25">
       <c r="B74" s="36" t="s">
         <v>127</v>
       </c>
@@ -19390,12 +19401,12 @@
       <c r="E74" s="37"/>
       <c r="F74" s="37"/>
     </row>
-    <row r="75" spans="2:6" ht="13.15">
+    <row r="75" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B75" s="109" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="76" spans="2:6">
+    <row r="76" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B76" s="246" t="s">
         <v>297</v>
       </c>
@@ -19405,7 +19416,7 @@
       </c>
       <c r="D76" s="134"/>
     </row>
-    <row r="77" spans="2:6">
+    <row r="77" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B77" s="100" t="s">
         <v>111</v>
       </c>
@@ -19418,12 +19429,12 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="79" spans="2:6" ht="13.15">
+    <row r="79" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B79" s="109" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="80" spans="2:6">
+    <row r="80" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B80" s="148" t="s">
         <v>299</v>
       </c>
@@ -19432,7 +19443,7 @@
         <v>0.3674</v>
       </c>
     </row>
-    <row r="81" spans="2:8">
+    <row r="81" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B81" s="100" t="s">
         <v>121</v>
       </c>
@@ -19444,7 +19455,7 @@
       <c r="E81" s="100"/>
       <c r="F81" s="100"/>
     </row>
-    <row r="82" spans="2:8">
+    <row r="82" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B82" s="100" t="s">
         <v>122</v>
       </c>
@@ -19454,7 +19465,7 @@
       </c>
       <c r="D82" s="116"/>
     </row>
-    <row r="83" spans="2:8" ht="13.15">
+    <row r="83" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B83" s="110" t="s">
         <v>101</v>
       </c>
@@ -19474,45 +19485,45 @@
         <v>0.56827582510368113</v>
       </c>
     </row>
-    <row r="84" spans="2:8">
+    <row r="84" spans="2:8" x14ac:dyDescent="0.15">
       <c r="E84" s="120"/>
     </row>
-    <row r="85" spans="2:8" ht="13.15">
+    <row r="85" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B85" s="109" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="86" spans="2:8">
+    <row r="86" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B86" s="148" t="s">
         <v>300</v>
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="13.15">
+    <row r="87" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B87" s="100" t="s">
         <v>298</v>
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.166056434583427</v>
-      </c>
-    </row>
-    <row r="88" spans="2:8">
+        <v>0.16382813843087729</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B88" s="100"/>
     </row>
-    <row r="89" spans="2:8" ht="13.15">
+    <row r="89" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B89" s="109" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="90" spans="2:8">
+    <row r="90" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B90" s="148" t="s">
         <v>413</v>
       </c>
@@ -19521,7 +19532,7 @@
         <v>0.21740000000000001</v>
       </c>
     </row>
-    <row r="91" spans="2:8">
+    <row r="91" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B91" s="100" t="s">
         <v>121</v>
       </c>
@@ -19533,7 +19544,7 @@
       <c r="E91" s="100"/>
       <c r="F91" s="100"/>
     </row>
-    <row r="92" spans="2:8">
+    <row r="92" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B92" s="100" t="s">
         <v>122</v>
       </c>
@@ -19543,7 +19554,7 @@
       </c>
       <c r="D92" s="116"/>
     </row>
-    <row r="93" spans="2:8" ht="13.15">
+    <row r="93" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B93" s="110" t="s">
         <v>101</v>
       </c>
@@ -19563,14 +19574,14 @@
         <v>0.39552430404120198</v>
       </c>
     </row>
-    <row r="95" spans="2:8" ht="13.15">
+    <row r="95" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B95" s="109" t="s">
         <v>397</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="281"/>
     </row>
-    <row r="96" spans="2:8">
+    <row r="96" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B96" s="148" t="s">
         <v>403</v>
       </c>
@@ -19581,7 +19592,7 @@
       <c r="G96" s="2"/>
       <c r="H96" s="281"/>
     </row>
-    <row r="97" spans="2:8">
+    <row r="97" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B97" s="100" t="s">
         <v>121</v>
       </c>
@@ -19593,7 +19604,7 @@
       <c r="G97" s="2"/>
       <c r="H97" s="281"/>
     </row>
-    <row r="98" spans="2:8">
+    <row r="98" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B98" s="100" t="s">
         <v>122</v>
       </c>
@@ -19605,7 +19616,7 @@
       <c r="G98" s="2"/>
       <c r="H98" s="281"/>
     </row>
-    <row r="99" spans="2:8" ht="13.15">
+    <row r="99" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B99" s="110" t="s">
         <v>398</v>
       </c>
@@ -19624,15 +19635,15 @@
         <v>0.13132906759055596</v>
       </c>
     </row>
-    <row r="100" spans="2:8">
+    <row r="100" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B100" s="100"/>
     </row>
-    <row r="101" spans="2:8" ht="13.15">
+    <row r="101" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B101" s="109" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="102" spans="2:8">
+    <row r="102" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B102" s="148" t="s">
         <v>420</v>
       </c>
@@ -19641,7 +19652,7 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="103" spans="2:8">
+    <row r="103" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B103" s="100" t="s">
         <v>121</v>
       </c>
@@ -19651,7 +19662,7 @@
       </c>
       <c r="D103" s="116"/>
     </row>
-    <row r="104" spans="2:8">
+    <row r="104" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B104" s="100" t="s">
         <v>122</v>
       </c>
@@ -19661,7 +19672,7 @@
       </c>
       <c r="D104" s="116"/>
     </row>
-    <row r="105" spans="2:8" ht="13.15">
+    <row r="105" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B105" s="110" t="s">
         <v>398</v>
       </c>
@@ -19680,16 +19691,16 @@
         <v>0.22401578084943807</v>
       </c>
     </row>
-    <row r="106" spans="2:8">
+    <row r="106" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B106" s="100"/>
     </row>
-    <row r="107" spans="2:8" ht="14.65">
+    <row r="107" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="E107" s="285" t="s">
         <v>324</v>
       </c>
       <c r="F107" s="282"/>
     </row>
-    <row r="108" spans="2:8" ht="13.9">
+    <row r="108" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="E108" s="278" t="s">
         <v>325</v>
       </c>
@@ -19697,7 +19708,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="109" spans="2:8" ht="13.9">
+    <row r="109" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="E109" s="279" t="s">
         <v>325</v>
       </c>
@@ -19705,7 +19716,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="110" spans="2:8" ht="13.9">
+    <row r="110" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="E110" s="280" t="s">
         <v>325</v>
       </c>

--- a/financial_models/opportunities/0398.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0398.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2909F0C3-1D7F-9145-931B-FC4683FB18D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8221FA10-23E7-4E1A-98F9-5A5F8C16108B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-100" yWindow="-100" windowWidth="17120" windowHeight="10760" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -38,17 +38,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -2510,7 +2499,7 @@
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
     <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="59" x14ac:knownFonts="1">
+  <fonts count="59">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3902,29 +3891,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3940,7 +3929,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4229,7 +4218,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J197"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
@@ -4238,7 +4227,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10">
       <c r="B1" s="3" t="s">
         <v>41</v>
       </c>
@@ -4255,7 +4244,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="222" t="s">
         <v>267</v>
       </c>
@@ -4269,7 +4258,7 @@
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
         <v>414</v>
       </c>
@@ -4278,7 +4267,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
         <v>315</v>
       </c>
@@ -4286,7 +4275,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
         <v>0</v>
       </c>
@@ -4295,7 +4284,7 @@
       </c>
       <c r="E6" s="48"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
         <v>307</v>
       </c>
@@ -4305,7 +4294,7 @@
       <c r="D7" s="48"/>
       <c r="E7" s="48"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10">
       <c r="B8" s="1" t="s">
         <v>268</v>
       </c>
@@ -4315,17 +4304,17 @@
       </c>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:10">
       <c r="E9" s="34"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
         <v>417</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
         <v>416</v>
       </c>
@@ -4337,17 +4326,17 @@
       </c>
       <c r="E11" s="34"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:10">
       <c r="B12" s="4" t="s">
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>3.6</v>
+        <v>3.57</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
         <v>415</v>
       </c>
@@ -4357,13 +4346,13 @@
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
         <v>419</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>1754.4896064000002</v>
+        <v>1739.8688596799998</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4371,7 +4360,7 @@
       </c>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
         <v>418</v>
       </c>
@@ -4385,7 +4374,7 @@
       </c>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:10">
       <c r="B16" s="4" t="s">
         <v>1</v>
       </c>
@@ -4395,27 +4384,27 @@
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:6">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="356" t="s">
+    <row r="18" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
+    </row>
+    <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
         <v>306</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
         <v>348</v>
       </c>
@@ -4430,7 +4419,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:6">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
@@ -4443,7 +4432,7 @@
       </c>
       <c r="E22" s="313"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
         <v>433</v>
       </c>
@@ -4451,7 +4440,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
         <v>434</v>
       </c>
@@ -4459,7 +4448,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
         <v>347</v>
       </c>
@@ -4475,7 +4464,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:6">
       <c r="B26" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (HKD) :</v>
@@ -4489,14 +4478,14 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.16382813843087729</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
+        <v>0.1671769416467408</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
         <v>432</v>
       </c>
@@ -4515,7 +4504,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
         <v>424</v>
       </c>
@@ -4534,7 +4523,7 @@
         <v>0.3674</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
         <v>425</v>
       </c>
@@ -4553,7 +4542,7 @@
         <v>0.21740000000000001</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
         <v>426</v>
       </c>
@@ -4572,7 +4561,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
         <v>427</v>
       </c>
@@ -4591,11 +4580,11 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:6">
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
     </row>
-    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="13.9">
       <c r="A34" s="222" t="s">
         <v>354</v>
       </c>
@@ -4605,25 +4594,25 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="356" t="s">
+    <row r="36" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
-    </row>
-    <row r="37" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B37" s="358" t="s">
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
+    </row>
+    <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
         <v>230</v>
       </c>
@@ -4632,16 +4621,16 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B40" s="357" t="s">
+    <row r="40" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
+    </row>
+    <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
         <v>232</v>
       </c>
@@ -4654,20 +4643,20 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:6">
       <c r="B42" s="47"/>
       <c r="C42" s="76"/>
     </row>
-    <row r="43" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B43" s="357" t="s">
+    <row r="43" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
+    </row>
+    <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
         <v>234</v>
       </c>
@@ -4680,7 +4669,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:6">
       <c r="B45" s="52" t="s">
         <v>235</v>
       </c>
@@ -4693,16 +4682,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B47" s="357" t="s">
+    <row r="47" spans="1:6">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
+    </row>
+    <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
         <v>237</v>
       </c>
@@ -4715,16 +4704,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B50" s="357" t="s">
+    <row r="50" spans="2:6">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
-    </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
+    </row>
+    <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
         <v>340</v>
       </c>
@@ -4739,7 +4728,7 @@
       <c r="E51" s="286"/>
       <c r="F51" s="286"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
         <v>341</v>
       </c>
@@ -4754,7 +4743,7 @@
       <c r="E52" s="286"/>
       <c r="F52" s="286"/>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
         <v>238</v>
       </c>
@@ -4767,12 +4756,12 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="1" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
         <v>265</v>
       </c>
@@ -4785,16 +4774,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B58" s="357" t="s">
+    <row r="58" spans="2:6">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
-    </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
+    </row>
+    <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
         <v>239</v>
       </c>
@@ -4807,8 +4796,8 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B61" s="357" t="s">
+    <row r="61" spans="2:6">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4816,7 +4805,7 @@
       <c r="E61" s="360"/>
       <c r="F61" s="360"/>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
         <v>242</v>
       </c>
@@ -4829,25 +4818,25 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B64" s="356" t="s">
+    <row r="64" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
-    </row>
-    <row r="65" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B65" s="356" t="s">
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
+    </row>
+    <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
         <v>270</v>
       </c>
@@ -4860,7 +4849,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:6">
       <c r="B68" s="47" t="s">
         <v>248</v>
       </c>
@@ -4873,23 +4862,23 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:6">
       <c r="B69" s="227" t="s">
         <v>390</v>
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>7.8878482612134579E-2</v>
+        <v>7.9541327003833207E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:6">
       <c r="B70" s="227" t="s">
         <v>308</v>
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.5555555555555556E-2</v>
+        <v>3.5854341736694682E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>447</v>
@@ -4899,7 +4888,7 @@
         <v>0.45076368583801485</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:6">
       <c r="B72" s="210" t="s">
         <v>450</v>
       </c>
@@ -4910,7 +4899,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:6">
       <c r="B73" s="47" t="s">
         <v>451</v>
       </c>
@@ -4923,7 +4912,7 @@
         <v>0.18576712671946713</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:6">
       <c r="B74" s="259" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Pre-tax Profit/Sales</v>
@@ -4937,7 +4926,7 @@
         <v>9.3537135473147709E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:6">
       <c r="B75" s="259" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Sales/Total Assets</v>
@@ -4951,7 +4940,7 @@
         <v>1.4185842608933972</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:6">
       <c r="B76" s="259" t="str">
         <f>Normalized_FCF!B119</f>
         <v>Total Assets/Equity</v>
@@ -4965,7 +4954,7 @@
         <v>1.4000052396569989</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" ht="13.9">
       <c r="A78" s="222" t="s">
         <v>355</v>
       </c>
@@ -4975,34 +4964,34 @@
       <c r="E78" s="36"/>
       <c r="F78" s="36"/>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:6">
       <c r="A79" s="209"/>
     </row>
-    <row r="80" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B81" s="358" t="s">
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
+    </row>
+    <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:6">
       <c r="B84" s="1" t="s">
         <v>430</v>
       </c>
@@ -5011,7 +5000,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:6">
       <c r="B85" s="1" t="s">
         <v>429</v>
       </c>
@@ -5020,7 +5009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:6">
       <c r="B86" s="80" t="s">
         <v>247</v>
       </c>
@@ -5029,34 +5018,34 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:6">
       <c r="C87" s="121"/>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:6">
       <c r="B88" s="293" t="s">
         <v>356</v>
       </c>
       <c r="C88" s="121"/>
     </row>
-    <row r="89" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B89" s="356" t="s">
+    <row r="89" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
-    </row>
-    <row r="90" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B90" s="356" t="s">
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
+    </row>
+    <row r="90" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
+    </row>
+    <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
         <v>251</v>
       </c>
@@ -5064,7 +5053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:6">
       <c r="B93" s="47" t="s">
         <v>280</v>
       </c>
@@ -5077,7 +5066,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" ht="13.9">
       <c r="A95" s="222" t="s">
         <v>357</v>
       </c>
@@ -5087,38 +5076,38 @@
       <c r="E95" s="36"/>
       <c r="F95" s="36"/>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:6">
       <c r="A96" s="209"/>
     </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B97" s="356" t="s">
+    <row r="97" spans="2:6">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
-    </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
+    </row>
+    <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="100" spans="2:6">
       <c r="B100" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="101" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B101" s="356" t="s">
+    <row r="101" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
-    </row>
-    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
+    </row>
+    <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
         <v>255</v>
       </c>
@@ -5131,7 +5120,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:6">
       <c r="B103" s="47" t="s">
         <v>281</v>
       </c>
@@ -5144,7 +5133,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:6">
       <c r="B104" s="296" t="s">
         <v>404</v>
       </c>
@@ -5153,7 +5142,7 @@
         <v>0.10646655543311496</v>
       </c>
     </row>
-    <row r="105" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="105" spans="2:6">
       <c r="B105" s="296" t="s">
         <v>406</v>
       </c>
@@ -5162,12 +5151,12 @@
         <v>0.9804830051022897</v>
       </c>
     </row>
-    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="107" spans="2:6">
       <c r="B107" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
         <v>264</v>
       </c>
@@ -5180,7 +5169,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="109" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
         <v>266</v>
       </c>
@@ -5193,7 +5182,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="110" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="110" spans="2:6">
       <c r="B110" s="47" t="s">
         <v>282</v>
       </c>
@@ -5206,12 +5195,12 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="112" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="112" spans="2:6">
       <c r="B112" s="1" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
         <v>257</v>
       </c>
@@ -5224,7 +5213,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:6">
       <c r="B114" s="47" t="s">
         <v>283</v>
       </c>
@@ -5237,16 +5226,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B116" s="356" t="s">
+    <row r="116" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
+    </row>
+    <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
         <v>448</v>
       </c>
@@ -5259,7 +5248,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:6">
       <c r="B119" s="296" t="s">
         <v>405</v>
       </c>
@@ -5272,7 +5261,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="222" t="s">
         <v>358</v>
       </c>
@@ -5282,16 +5271,16 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B123" s="357" t="s">
+    <row r="123" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
-    </row>
-    <row r="125" spans="1:6" ht="14" x14ac:dyDescent="0.2">
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
+    </row>
+    <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
         <v>117</v>
       </c>
@@ -5308,7 +5297,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:6">
       <c r="B126" s="228" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
@@ -5330,7 +5319,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:6">
       <c r="B127" s="218" t="str">
         <f>DCF!B75</f>
         <v>Optimistic</v>
@@ -5352,7 +5341,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:6">
       <c r="B128" s="218" t="str">
         <f>DCF!B76</f>
         <v>Base</v>
@@ -5374,7 +5363,7 @@
         <v>0.53999999999999992</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:6">
       <c r="B129" s="218" t="str">
         <f>DCF!B77</f>
         <v>Pessimistic</v>
@@ -5396,7 +5385,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:6">
       <c r="B130" s="218" t="str">
         <f>DCF!B78</f>
         <v>Devil's advocate</v>
@@ -5418,7 +5407,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:6">
       <c r="B132" s="211" t="s">
         <v>258</v>
       </c>
@@ -5431,16 +5420,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B134" s="361" t="s">
+    <row r="134" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B134" s="362" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
-    </row>
-    <row r="136" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
+    </row>
+    <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
         <v>402</v>
       </c>
@@ -5450,30 +5439,30 @@
       <c r="E136" s="36"/>
       <c r="F136" s="36"/>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B138" s="359" t="s">
+    <row r="138" spans="1:6">
+      <c r="B138" s="363" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
-    </row>
-    <row r="139" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B139" s="356" t="s">
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
+    </row>
+    <row r="139" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B139" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
+    </row>
+    <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
         <v>263</v>
       </c>
@@ -5482,7 +5471,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:6">
       <c r="B142" s="1" t="s">
         <v>276</v>
       </c>
@@ -5491,7 +5480,7 @@
         <v>0.3674</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:6">
       <c r="B143" s="212" t="s">
         <v>261</v>
       </c>
@@ -5504,7 +5493,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="145" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="145" spans="2:4">
       <c r="B145" s="210" t="s">
         <v>408</v>
       </c>
@@ -5517,7 +5506,7 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="146" spans="2:4">
       <c r="B146" s="1" t="s">
         <v>407</v>
       </c>
@@ -5526,7 +5515,7 @@
         <v>0.3674</v>
       </c>
     </row>
-    <row r="147" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="147" spans="2:4">
       <c r="B147" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5536,7 +5525,7 @@
         <v>0.21212919287870191</v>
       </c>
     </row>
-    <row r="148" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="148" spans="2:4">
       <c r="B148" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5546,7 +5535,7 @@
         <v>2.0434984886306262</v>
       </c>
     </row>
-    <row r="149" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="149" spans="2:4">
       <c r="B149" s="80" t="s">
         <v>260</v>
       </c>
@@ -5559,7 +5548,7 @@
         <v/>
       </c>
     </row>
-    <row r="150" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="150" spans="2:4">
       <c r="B150" s="259" t="s">
         <v>415</v>
       </c>
@@ -5572,7 +5561,7 @@
         <v/>
       </c>
     </row>
-    <row r="151" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="151" spans="2:4">
       <c r="B151" s="214" t="s">
         <v>262</v>
       </c>
@@ -5581,12 +5570,12 @@
         <v>0.56827582510368113</v>
       </c>
     </row>
-    <row r="153" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="153" spans="2:4">
       <c r="B153" s="210" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="154" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="154" spans="2:4">
       <c r="B154" s="1" t="s">
         <v>410</v>
       </c>
@@ -5595,7 +5584,7 @@
         <v>0.21740000000000001</v>
       </c>
     </row>
-    <row r="155" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="155" spans="2:4">
       <c r="B155" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5605,7 +5594,7 @@
         <v>0.2624513054547119</v>
       </c>
     </row>
-    <row r="156" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="156" spans="2:4">
       <c r="B156" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5615,7 +5604,7 @@
         <v>2.8957506018897798</v>
       </c>
     </row>
-    <row r="157" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="157" spans="2:4">
       <c r="B157" s="80" t="s">
         <v>260</v>
       </c>
@@ -5628,7 +5617,7 @@
         <v/>
       </c>
     </row>
-    <row r="158" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="158" spans="2:4">
       <c r="B158" s="259" t="s">
         <v>415</v>
       </c>
@@ -5641,7 +5630,7 @@
         <v/>
       </c>
     </row>
-    <row r="159" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="159" spans="2:4">
       <c r="B159" s="214" t="s">
         <v>262</v>
       </c>
@@ -5650,12 +5639,12 @@
         <v>0.39552430404120198</v>
       </c>
     </row>
-    <row r="161" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="161" spans="2:4">
       <c r="B161" s="210" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="162" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="162" spans="2:4">
       <c r="B162" s="1" t="s">
         <v>409</v>
       </c>
@@ -5664,7 +5653,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="163" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="163" spans="2:4">
       <c r="B163" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5674,7 +5663,7 @@
         <v>0.33286729470361087</v>
       </c>
     </row>
-    <row r="164" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="164" spans="2:4">
       <c r="B164" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5684,7 +5673,7 @@
         <v>4.2056744761754965</v>
       </c>
     </row>
-    <row r="165" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="165" spans="2:4">
       <c r="B165" s="80" t="s">
         <v>401</v>
       </c>
@@ -5697,7 +5686,7 @@
         <v/>
       </c>
     </row>
-    <row r="166" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="166" spans="2:4">
       <c r="B166" s="259" t="s">
         <v>415</v>
       </c>
@@ -5710,7 +5699,7 @@
         <v/>
       </c>
     </row>
-    <row r="167" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="167" spans="2:4">
       <c r="B167" s="214" t="s">
         <v>262</v>
       </c>
@@ -5719,12 +5708,12 @@
         <v>0.13132906759055596</v>
       </c>
     </row>
-    <row r="169" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="169" spans="2:4">
       <c r="B169" s="210" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="170" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="170" spans="2:4">
       <c r="B170" s="1" t="s">
         <v>422</v>
       </c>
@@ -5733,7 +5722,7 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="171" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="171" spans="2:4">
       <c r="B171" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5743,7 +5732,7 @@
         <v>0.30881320012014707</v>
       </c>
     </row>
-    <row r="172" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="172" spans="2:4">
       <c r="B172" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5753,7 +5742,7 @@
         <v>3.7448553439982017</v>
       </c>
     </row>
-    <row r="173" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="173" spans="2:4">
       <c r="B173" s="80" t="s">
         <v>401</v>
       </c>
@@ -5766,7 +5755,7 @@
         <v/>
       </c>
     </row>
-    <row r="174" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="174" spans="2:4">
       <c r="B174" s="259" t="s">
         <v>415</v>
       </c>
@@ -5779,7 +5768,7 @@
         <v/>
       </c>
     </row>
-    <row r="175" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="175" spans="2:4">
       <c r="B175" s="214" t="s">
         <v>262</v>
       </c>
@@ -5788,7 +5777,7 @@
         <v>0.22401578084943807</v>
       </c>
     </row>
-    <row r="177" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:6" ht="13.9">
       <c r="A177" s="222" t="s">
         <v>374</v>
       </c>
@@ -5798,21 +5787,21 @@
       <c r="E177" s="36"/>
       <c r="F177" s="36"/>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B179" s="363" t="s">
+    <row r="179" spans="1:6">
+      <c r="B179" s="357" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
-    </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
+    </row>
+    <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="182" spans="1:6">
       <c r="B182" s="360" t="s">
         <v>380</v>
       </c>
@@ -5821,91 +5810,80 @@
       <c r="E182" s="360"/>
       <c r="F182" s="360"/>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="184" spans="1:6">
       <c r="B184" s="214" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="185" spans="1:6">
       <c r="B185" s="214" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="187" spans="1:6">
       <c r="B187" s="1" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="188" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B188" s="357" t="s">
+    <row r="188" spans="1:6" ht="46.5" customHeight="1">
+      <c r="B188" s="359" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
-    </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
+    </row>
+    <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="191" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B191" s="362" t="s">
+    <row r="191" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
-    </row>
-    <row r="192" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B192" s="362" t="s">
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
+    </row>
+    <row r="192" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B192" s="356" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
-    </row>
-    <row r="194" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
+    </row>
+    <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="195" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="195" spans="2:2">
       <c r="B195" s="214" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="196" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="196" spans="2:2">
       <c r="B196" s="214" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="197" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="197" spans="2:2">
       <c r="B197" s="214" t="s">
         <v>388</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5922,6 +5900,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -5952,15 +5941,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
     <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.83203125" style="1"/>
+    <col min="14" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
         <v>HKD</v>
@@ -6009,7 +5998,7 @@
         <v>41729</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>97</v>
       </c>
@@ -6025,7 +6014,7 @@
       <c r="L2" s="37"/>
       <c r="M2" s="37"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
         <v>27</v>
       </c>
@@ -6033,7 +6022,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:13">
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
@@ -6067,7 +6056,7 @@
       <c r="L4" s="351"/>
       <c r="M4" s="351"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
@@ -6101,7 +6090,7 @@
       <c r="L5" s="351"/>
       <c r="M5" s="351"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
@@ -6135,7 +6124,7 @@
       <c r="L6" s="351"/>
       <c r="M6" s="351"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
@@ -6169,7 +6158,7 @@
       <c r="L7" s="352"/>
       <c r="M7" s="352"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
@@ -6185,7 +6174,7 @@
       <c r="L8" s="351"/>
       <c r="M8" s="351"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
         <v>159</v>
       </c>
@@ -6201,7 +6190,7 @@
       <c r="L9" s="351"/>
       <c r="M9" s="351"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
         <v>167</v>
       </c>
@@ -6217,7 +6206,7 @@
       <c r="L10" s="351"/>
       <c r="M10" s="351"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
         <v>158</v>
       </c>
@@ -6233,7 +6222,7 @@
       <c r="L11" s="351"/>
       <c r="M11" s="351"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
@@ -6267,7 +6256,7 @@
       <c r="L12" s="351"/>
       <c r="M12" s="351"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
@@ -6283,7 +6272,7 @@
       <c r="L13" s="351"/>
       <c r="M13" s="351"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
@@ -6317,7 +6306,7 @@
       <c r="L14" s="351"/>
       <c r="M14" s="351"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
@@ -6351,7 +6340,7 @@
       <c r="L15" s="353"/>
       <c r="M15" s="353"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
@@ -6385,13 +6374,13 @@
       <c r="L16" s="351"/>
       <c r="M16" s="351"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:13">
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
@@ -6407,7 +6396,7 @@
       <c r="L19" s="351"/>
       <c r="M19" s="351"/>
     </row>
-    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
@@ -6423,7 +6412,7 @@
       <c r="L20" s="351"/>
       <c r="M20" s="351"/>
     </row>
-    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
@@ -6439,7 +6428,7 @@
       <c r="L21" s="351"/>
       <c r="M21" s="351"/>
     </row>
-    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
         <v>371</v>
       </c>
@@ -6473,7 +6462,7 @@
       <c r="L22" s="351"/>
       <c r="M22" s="351"/>
     </row>
-    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
         <v>373</v>
       </c>
@@ -6507,7 +6496,7 @@
       <c r="L23" s="351"/>
       <c r="M23" s="351"/>
     </row>
-    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
         <v>372</v>
       </c>
@@ -6541,7 +6530,7 @@
       <c r="L24" s="351"/>
       <c r="M24" s="351"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:13">
       <c r="B25" s="24" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (HKD)</v>
@@ -6570,7 +6559,7 @@
       <c r="L25" s="39"/>
       <c r="M25" s="39"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
@@ -6578,7 +6567,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:13">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
@@ -6613,7 +6602,7 @@
       <c r="L28" s="351"/>
       <c r="M28" s="351"/>
     </row>
-    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
@@ -6648,7 +6637,7 @@
       <c r="L29" s="351"/>
       <c r="M29" s="351"/>
     </row>
-    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
@@ -6683,7 +6672,7 @@
       <c r="L30" s="353"/>
       <c r="M30" s="353"/>
     </row>
-    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
@@ -6718,7 +6707,7 @@
       <c r="L31" s="353"/>
       <c r="M31" s="353"/>
     </row>
-    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
         <v>172</v>
       </c>
@@ -6753,7 +6742,7 @@
       <c r="L32" s="351"/>
       <c r="M32" s="351"/>
     </row>
-    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
         <v>81</v>
       </c>
@@ -6769,12 +6758,12 @@
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:13">
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
@@ -6823,7 +6812,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:13">
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
@@ -6872,7 +6861,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:13">
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
@@ -6921,7 +6910,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:13">
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
@@ -6970,7 +6959,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:13">
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
@@ -7019,7 +7008,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:13">
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
@@ -7068,7 +7057,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:13">
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
@@ -7117,7 +7106,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
         <v>152</v>
       </c>
@@ -7166,7 +7155,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
         <v>168</v>
       </c>
@@ -7215,7 +7204,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:13">
       <c r="B45" s="40" t="s">
         <v>68</v>
       </c>
@@ -7264,7 +7253,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:13">
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
@@ -7313,7 +7302,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:13">
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
@@ -7362,7 +7351,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:13">
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
@@ -7411,12 +7400,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:13">
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
@@ -7465,7 +7454,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:13">
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
@@ -7514,12 +7503,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:13">
       <c r="B54" s="174" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
         <v>159</v>
       </c>
@@ -7568,7 +7557,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
         <v>167</v>
       </c>
@@ -7617,7 +7606,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
         <v>158</v>
       </c>
@@ -7666,7 +7655,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
         <v>160</v>
       </c>
@@ -7715,13 +7704,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:13">
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
@@ -7770,7 +7759,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:13">
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
@@ -7819,7 +7808,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:13">
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
@@ -7868,7 +7857,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
         <v>393</v>
       </c>
@@ -7917,7 +7906,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:13">
       <c r="B65" s="24" t="s">
         <v>36</v>
       </c>
@@ -7966,12 +7955,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:13">
       <c r="B67" s="91" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:13">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -8021,7 +8010,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:13">
       <c r="B69" s="31" t="s">
         <v>58</v>
       </c>
@@ -8070,7 +8059,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:13">
       <c r="B70" s="80" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -8120,7 +8109,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
         <v>168</v>
       </c>
@@ -8169,7 +8158,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:13">
       <c r="B72" s="80" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -8219,7 +8208,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="36" t="s">
         <v>82</v>
       </c>
@@ -8235,13 +8224,13 @@
       <c r="L74" s="37"/>
       <c r="M74" s="37"/>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
         <v>28</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:13">
       <c r="B76" s="26" t="s">
         <v>3</v>
       </c>
@@ -8290,7 +8279,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:13">
       <c r="B77" s="93" t="s">
         <v>85</v>
       </c>
@@ -8324,7 +8313,7 @@
       <c r="L77" s="355"/>
       <c r="M77" s="355"/>
     </row>
-    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
         <v>86</v>
       </c>
@@ -8358,7 +8347,7 @@
       <c r="L78" s="355"/>
       <c r="M78" s="355"/>
     </row>
-    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
@@ -8407,7 +8396,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:13">
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
@@ -8488,7 +8477,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
@@ -8499,7 +8488,7 @@
     <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="18" t="s">
         <v>37</v>
       </c>
@@ -8515,7 +8504,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
         <v>156</v>
       </c>
@@ -8526,7 +8515,7 @@
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
         <v>184</v>
       </c>
@@ -8546,7 +8535,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
@@ -8568,7 +8557,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
@@ -8589,7 +8578,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="15" customHeight="1">
       <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
@@ -8610,7 +8599,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
         <v>69</v>
       </c>
@@ -8631,7 +8620,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
         <v>173</v>
       </c>
@@ -8652,7 +8641,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
@@ -8673,7 +8662,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="15" customHeight="1">
       <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
@@ -8685,7 +8674,7 @@
       </c>
       <c r="H10" s="262"/>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
@@ -8697,7 +8686,7 @@
       </c>
       <c r="H11" s="262"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
         <v>72</v>
       </c>
@@ -8721,12 +8710,12 @@
         <v>986959.8</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="15" customHeight="1">
       <c r="F13" s="80"/>
       <c r="G13" s="81"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
         <v>183</v>
       </c>
@@ -8746,7 +8735,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
         <v>454</v>
       </c>
@@ -8766,7 +8755,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
@@ -8787,7 +8776,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
         <v>69</v>
       </c>
@@ -8807,7 +8796,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
         <v>173</v>
       </c>
@@ -8827,7 +8816,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
         <v>26</v>
       </c>
@@ -8849,7 +8838,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
         <v>18</v>
       </c>
@@ -8869,7 +8858,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
@@ -8889,7 +8878,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
         <v>20</v>
       </c>
@@ -8901,7 +8890,7 @@
       </c>
       <c r="H22" s="262"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
         <v>21</v>
       </c>
@@ -8913,7 +8902,7 @@
       </c>
       <c r="H23" s="262"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
         <v>73</v>
       </c>
@@ -8937,7 +8926,7 @@
         <v>41890.299999999996</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
         <v>200</v>
       </c>
@@ -8954,7 +8943,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8" ht="15" customHeight="1">
       <c r="B27" s="4" t="s">
         <v>5</v>
       </c>
@@ -8973,7 +8962,7 @@
         <v>815566.8</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8" ht="15" customHeight="1">
       <c r="B28" s="4" t="s">
         <v>6</v>
       </c>
@@ -8988,7 +8977,7 @@
       </c>
       <c r="H28" s="188"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8" ht="15" customHeight="1">
       <c r="B29" s="4" t="s">
         <v>7</v>
       </c>
@@ -9007,7 +8996,7 @@
         <v>813801.8</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8" ht="15" customHeight="1">
       <c r="B30" s="2" t="s">
         <v>8</v>
       </c>
@@ -9023,7 +9012,7 @@
       </c>
       <c r="H30" s="188"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
         <v>203</v>
       </c>
@@ -9040,7 +9029,7 @@
       </c>
       <c r="H31" s="188"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8" ht="15" customHeight="1">
       <c r="B32" s="4" t="s">
         <v>9</v>
       </c>
@@ -9060,7 +9049,7 @@
         <v>1548448.8</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8" ht="15" customHeight="1">
       <c r="B33" s="83" t="s">
         <v>4</v>
       </c>
@@ -9071,7 +9060,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="195"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8" ht="15" customHeight="1">
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="196" t="s">
@@ -9084,7 +9073,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
         <v>201</v>
       </c>
@@ -9103,7 +9092,7 @@
         <v>519598.69999999995</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8" ht="15" customHeight="1">
       <c r="B36" s="4" t="s">
         <v>13</v>
       </c>
@@ -9119,7 +9108,7 @@
       </c>
       <c r="H36" s="195"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8" ht="15" customHeight="1">
       <c r="B37" s="4" t="s">
         <v>14</v>
       </c>
@@ -9135,7 +9124,7 @@
       </c>
       <c r="H37" s="195"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8" ht="15" customHeight="1">
       <c r="B38" s="4" t="s">
         <v>15</v>
       </c>
@@ -9151,7 +9140,7 @@
       </c>
       <c r="H38" s="195"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8" ht="15" customHeight="1">
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
@@ -9170,7 +9159,7 @@
         <v>41963.600000000006</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="80" t="s">
         <v>204</v>
       </c>
@@ -9190,7 +9179,7 @@
         <v>1028850.1000000001</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8" ht="15" customHeight="1">
       <c r="B41" s="4" t="s">
         <v>17</v>
       </c>
@@ -9210,7 +9199,7 @@
         <v>1009942.2000000001</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="83" t="s">
         <v>22</v>
       </c>
@@ -9229,7 +9218,7 @@
         <v>18907.900000000001</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="79" t="s">
         <v>96</v>
       </c>
@@ -9240,7 +9229,7 @@
       <c r="G44" s="37"/>
       <c r="H44" s="37"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
         <v>271</v>
       </c>
@@ -9254,7 +9243,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
         <v>273</v>
       </c>
@@ -9268,7 +9257,7 @@
       </c>
       <c r="F46" s="253"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (HKD)</v>
@@ -9283,10 +9272,10 @@
       </c>
       <c r="F47" s="253"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8" ht="15" customHeight="1">
       <c r="F48" s="253"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="157" t="s">
         <v>143</v>
       </c>
@@ -9299,7 +9288,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="253"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
         <v>93</v>
       </c>
@@ -9313,7 +9302,7 @@
       </c>
       <c r="F50" s="253"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
         <v>176</v>
       </c>
@@ -9324,10 +9313,10 @@
       </c>
       <c r="F51" s="253"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:8" ht="15" customHeight="1">
       <c r="F52" s="253"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="157" t="s">
         <v>142</v>
       </c>
@@ -9339,7 +9328,7 @@
       </c>
       <c r="F53" s="253"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
         <v>139</v>
       </c>
@@ -9353,7 +9342,7 @@
       </c>
       <c r="F54" s="253"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
         <v>141</v>
       </c>
@@ -9367,10 +9356,10 @@
       </c>
       <c r="F55" s="253"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:8" ht="15" customHeight="1">
       <c r="F56" s="253"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="157" t="s">
         <v>175</v>
       </c>
@@ -9382,7 +9371,7 @@
       </c>
       <c r="F57" s="253"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
         <v>89</v>
       </c>
@@ -9393,7 +9382,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
         <v>92</v>
       </c>
@@ -9404,10 +9393,10 @@
       </c>
       <c r="F59" s="253"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:8" ht="15" customHeight="1">
       <c r="F60" s="253"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="157" t="s">
         <v>274</v>
       </c>
@@ -9419,7 +9408,7 @@
       </c>
       <c r="F61" s="253"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
         <v>245</v>
       </c>
@@ -9435,7 +9424,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="79" t="s">
         <v>193</v>
       </c>
@@ -9446,7 +9435,7 @@
       <c r="G64" s="37"/>
       <c r="H64" s="37"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
         <v>188</v>
       </c>
@@ -9460,7 +9449,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="105" t="s">
         <v>187</v>
       </c>
@@ -9476,7 +9465,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="105" t="s">
         <v>177</v>
       </c>
@@ -9486,7 +9475,7 @@
       </c>
       <c r="F67" s="253"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
         <v>181</v>
       </c>
@@ -9496,7 +9485,7 @@
       </c>
       <c r="F68" s="253"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
         <v>179</v>
       </c>
@@ -9506,7 +9495,7 @@
       </c>
       <c r="F69" s="253"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
         <v>188</v>
       </c>
@@ -9516,10 +9505,10 @@
       </c>
       <c r="F70" s="253"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6" ht="15" customHeight="1">
       <c r="F71" s="253"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="255" t="s">
         <v>318</v>
       </c>
@@ -9531,7 +9520,7 @@
       </c>
       <c r="F72" s="253"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
         <v>317</v>
       </c>
@@ -9547,7 +9536,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="257" t="s">
         <v>321</v>
       </c>
@@ -9563,7 +9552,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
         <v>320</v>
       </c>
@@ -9576,7 +9565,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="259" t="s">
         <v>322</v>
       </c>
@@ -9589,10 +9578,10 @@
         <v>323</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6" ht="15" customHeight="1">
       <c r="F77" s="253"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>189</v>
       </c>
@@ -9604,7 +9593,7 @@
       </c>
       <c r="F78" s="253"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
         <v>178</v>
       </c>
@@ -9618,7 +9607,7 @@
       </c>
       <c r="F79" s="253"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
         <v>182</v>
       </c>
@@ -9632,7 +9621,7 @@
       </c>
       <c r="F80" s="253"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
         <v>180</v>
       </c>
@@ -9646,7 +9635,7 @@
       </c>
       <c r="F81" s="253"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
         <v>189</v>
       </c>
@@ -9660,7 +9649,7 @@
       </c>
       <c r="F82" s="253"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
         <v>288</v>
       </c>
@@ -9671,7 +9660,7 @@
       <c r="G84" s="37"/>
       <c r="H84" s="37"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
         <v>289</v>
       </c>
@@ -9679,7 +9668,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="238" t="s">
         <v>286</v>
       </c>
@@ -9696,7 +9685,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="238" t="s">
         <v>287</v>
       </c>
@@ -9713,7 +9702,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="239" t="s">
         <v>189</v>
       </c>
@@ -9730,7 +9719,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
         <v>291</v>
       </c>
@@ -9761,19 +9750,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
     <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
     <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
     <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
@@ -9830,7 +9819,7 @@
         <v>41729</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
         <v>99</v>
@@ -9853,7 +9842,7 @@
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>66</v>
@@ -9867,7 +9856,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
         <v>2</v>
@@ -9924,7 +9913,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>46</v>
@@ -9979,7 +9968,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
         <v>48</v>
@@ -10034,7 +10023,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>45</v>
@@ -10089,7 +10078,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
         <v>152</v>
@@ -10146,7 +10135,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
         <v>65</v>
@@ -10201,7 +10190,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>80</v>
@@ -10256,7 +10245,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
         <v>194</v>
@@ -10313,7 +10302,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>68</v>
@@ -10368,7 +10357,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
         <v>164</v>
@@ -10423,7 +10412,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
         <v>63</v>
@@ -10478,7 +10467,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
         <v>243</v>
@@ -10535,7 +10524,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
         <v>154</v>
@@ -10592,7 +10581,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
         <v>52</v>
@@ -10618,7 +10607,7 @@
       <c r="P17" s="335"/>
       <c r="Q17" s="335"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>98</v>
@@ -10643,7 +10632,7 @@
       <c r="P18" s="336"/>
       <c r="Q18" s="336"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
@@ -10700,7 +10689,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1">
       <c r="A20" s="10"/>
       <c r="B20" s="27"/>
       <c r="C20" s="62"/>
@@ -10719,7 +10708,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
         <v>205</v>
@@ -10742,7 +10731,7 @@
       <c r="P21" s="37"/>
       <c r="Q21" s="37"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
         <v>46</v>
@@ -10763,7 +10752,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
         <v>43</v>
@@ -10820,7 +10809,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
         <v>62</v>
@@ -10877,7 +10866,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
         <v>46</v>
@@ -10934,18 +10923,18 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
       <c r="E26" s="268"/>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>206</v>
       </c>
       <c r="E27" s="268"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
         <v>43</v>
@@ -11004,7 +10993,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="68" t="str">
         <f>B24</f>
@@ -11064,7 +11053,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
         <v>46</v>
@@ -11119,18 +11108,18 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
       <c r="E31" s="268"/>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
       <c r="E32" s="268"/>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
         <v>174</v>
@@ -11187,7 +11176,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
         <v>49</v>
@@ -11246,7 +11235,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
         <v>45</v>
@@ -11303,18 +11292,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
       <c r="E36" s="268"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>207</v>
       </c>
       <c r="E37" s="268"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="2" t="str">
         <f>B33</f>
@@ -11372,7 +11361,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1">
       <c r="A39" s="10"/>
       <c r="B39" s="27" t="str">
         <f>B34</f>
@@ -11430,7 +11419,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
         <v>45</v>
@@ -11485,18 +11474,18 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
       <c r="E41" s="268"/>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>208</v>
       </c>
       <c r="E42" s="268"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>171</v>
@@ -11554,10 +11543,10 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1">
       <c r="A44" s="10"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
         <v>209</v>
@@ -11580,14 +11569,14 @@
       <c r="P45" s="37"/>
       <c r="Q45" s="37"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
       <c r="E46" s="268"/>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
         <v>39</v>
@@ -11642,7 +11631,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
         <v>345</v>
@@ -11697,7 +11686,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="287" t="s">
         <v>342</v>
@@ -11754,7 +11743,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
         <v>68</v>
@@ -11809,11 +11798,11 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
       <c r="E51" s="268"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>155</v>
@@ -11823,7 +11812,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
         <v>88</v>
@@ -11850,7 +11839,7 @@
       <c r="P53" s="169"/>
       <c r="Q53" s="169"/>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
         <v>87</v>
@@ -11877,7 +11866,7 @@
       <c r="P54" s="169"/>
       <c r="Q54" s="169"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
         <v>90</v>
@@ -11932,11 +11921,11 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
       <c r="E56" s="268"/>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>168</v>
@@ -11946,7 +11935,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
         <v>167</v>
@@ -12001,7 +11990,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
         <v>159</v>
@@ -12056,7 +12045,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
         <v>158</v>
@@ -12111,7 +12100,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
         <v>194</v>
@@ -12166,7 +12155,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
         <v>160</v>
@@ -12222,7 +12211,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
         <v>195</v>
@@ -12277,11 +12266,11 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
       <c r="E64" s="268"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>169</v>
@@ -12291,7 +12280,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
         <v>167</v>
@@ -12316,7 +12305,7 @@
       <c r="P66" s="175"/>
       <c r="Q66" s="175"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
         <v>157</v>
@@ -12341,7 +12330,7 @@
       <c r="P67" s="175"/>
       <c r="Q67" s="175"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
         <v>158</v>
@@ -12366,7 +12355,7 @@
       <c r="P68" s="175"/>
       <c r="Q68" s="175"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
         <v>194</v>
@@ -12393,10 +12382,10 @@
       <c r="P69" s="175"/>
       <c r="Q69" s="175"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1">
       <c r="A70" s="10"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
         <v>212</v>
@@ -12419,7 +12408,7 @@
       <c r="P71" s="37"/>
       <c r="Q71" s="37"/>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
         <v>216</v>
@@ -12440,7 +12429,7 @@
       <c r="P72" s="12"/>
       <c r="Q72" s="12"/>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
         <v>46</v>
@@ -12497,7 +12486,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
         <v>48</v>
@@ -12554,7 +12543,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
         <v>45</v>
@@ -12611,7 +12600,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
         <v>152</v>
@@ -12668,7 +12657,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
         <v>65</v>
@@ -12725,7 +12714,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>80</v>
@@ -12784,7 +12773,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
         <v>153</v>
@@ -12841,7 +12830,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
         <v>68</v>
@@ -12898,7 +12887,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
         <v>164</v>
@@ -12955,7 +12944,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>63</v>
@@ -13012,7 +13001,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1">
       <c r="A83" s="10"/>
       <c r="B83" s="40" t="str">
         <f>B15</f>
@@ -13070,7 +13059,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
         <v>154</v>
@@ -13127,7 +13116,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
         <v>52</v>
@@ -13153,7 +13142,7 @@
       <c r="P85" s="226"/>
       <c r="Q85" s="226"/>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
         <v>98</v>
@@ -13177,7 +13166,7 @@
       <c r="P86" s="169"/>
       <c r="Q86" s="169"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
         <v>140</v>
@@ -13234,18 +13223,18 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
       <c r="E88" s="268"/>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>214</v>
       </c>
       <c r="E89" s="268"/>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -13301,7 +13290,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -13357,7 +13346,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>213</v>
@@ -13412,31 +13401,31 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
         <v>309</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.5555555555555556E-2</v>
+        <v>3.5854341736694682E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.5555555555555556E-2</v>
+        <v>3.5854341736694682E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>4.2499999999999996E-2</v>
+        <v>4.2857142857142858E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>5.1666666666666666E-2</v>
+        <v>5.2100840336134456E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>4.1111111111111105E-2</v>
+        <v>4.145658263305322E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
@@ -13467,11 +13456,11 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="E94" s="268"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
       <c r="B95" s="157" t="s">
         <v>84</v>
@@ -13492,7 +13481,7 @@
       <c r="P95" s="12"/>
       <c r="Q95" s="12"/>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
         <v>144</v>
@@ -13549,7 +13538,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
       <c r="B97" s="70" t="s">
         <v>164</v>
@@ -13606,10 +13595,10 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="10"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
         <v>215</v>
@@ -13632,7 +13621,7 @@
       <c r="P99" s="37"/>
       <c r="Q99" s="37"/>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1">
       <c r="A100" s="10"/>
       <c r="B100" s="64" t="s">
         <v>28</v>
@@ -13642,7 +13631,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="26" t="s">
         <v>3</v>
@@ -13699,7 +13688,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="93" t="s">
         <v>210</v>
@@ -13756,7 +13745,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
         <v>211</v>
@@ -13813,7 +13802,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
         <v>40</v>
@@ -13870,7 +13859,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
         <v>30</v>
@@ -13927,11 +13916,11 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="E106" s="268"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
       <c r="B107" s="91" t="s">
         <v>220</v>
@@ -13954,7 +13943,7 @@
       <c r="P107" s="12"/>
       <c r="Q107" s="12"/>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
         <v>217</v>
@@ -14011,7 +14000,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
         <v>218</v>
@@ -14068,7 +14057,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
         <v>69</v>
@@ -14095,18 +14084,18 @@
       <c r="P110" s="204"/>
       <c r="Q110" s="204"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="E111" s="268"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
       <c r="E112" s="268"/>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>391</v>
@@ -14158,7 +14147,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
         <v>392</v>
@@ -14210,11 +14199,11 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="E115" s="268"/>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
       <c r="B116" s="91" t="s">
         <v>38</v>
@@ -14268,7 +14257,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="A117" s="10"/>
       <c r="B117" s="7" t="s">
         <v>221</v>
@@ -14323,7 +14312,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="B118" s="7" t="s">
         <v>83</v>
       </c>
@@ -14377,7 +14366,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="B119" s="7" t="s">
         <v>91</v>
       </c>
@@ -14433,7 +14422,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1">
       <c r="A120" s="10"/>
       <c r="B120" s="70" t="s">
         <v>222</v>
@@ -14490,7 +14479,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="27"/>
       <c r="C121" s="62"/>
@@ -14509,7 +14498,7 @@
       <c r="P121" s="12"/>
       <c r="Q121" s="12"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
       <c r="B122" s="54" t="s">
         <v>223</v>
@@ -14532,7 +14521,7 @@
       <c r="P122" s="37"/>
       <c r="Q122" s="37"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
       <c r="B123" s="178" t="s">
         <v>170</v>
@@ -14553,7 +14542,7 @@
       <c r="P123" s="12"/>
       <c r="Q123" s="12"/>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -14611,53 +14600,53 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
         <v>269</v>
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.8878482612134579E-2</v>
+        <v>7.9541327003833207E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.1107860652414065</v>
+        <v>0.11171704057956958</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.14218950006314496</v>
+        <v>0.14338436981157476</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.15330213357711917</v>
+        <v>0.15459038680045631</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.10564724882031652</v>
+        <v>0.10653504082720994</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>6.4434693478729058E-2</v>
+        <v>6.4976161491155357E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>5.9018303455479502E-2</v>
+        <v>5.9514255585357487E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>5.5388757873236723E-2</v>
+        <v>5.5854209620070649E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>-3.7783067940777969E-3</v>
+        <v>-3.8100572713389552E-3</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>-3.211304290118136E-2</v>
+        <v>-3.2382900404552634E-2</v>
       </c>
       <c r="P125" s="77" t="str">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
@@ -14668,46 +14657,46 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
         <v>394</v>
       </c>
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14314704349564619</v>
+        <v>0.14434995982754242</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16843872937291399</v>
+        <v>0.16985418088024942</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.20688409818783865</v>
+        <v>0.20862262002134993</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1325878472870046</v>
+        <v>0.1337020308776517</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.6488792887955407E-2</v>
+        <v>5.6963488626509656E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8677582070856081E-2</v>
+        <v>7.9338738222712035E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9045780319305967E-2</v>
+        <v>7.9710030574090068E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.1747479958169103E-3</v>
+        <v>9.2518467184708342E-3</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-8.9820993766589231E-3</v>
+        <v>-9.0575792033535368E-3</v>
       </c>
       <c r="P126" s="23" t="str">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -14718,688 +14707,688 @@
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -15421,16 +15410,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:Q105"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="6" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>55</v>
       </c>
@@ -15442,7 +15431,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
         <v>163</v>
       </c>
@@ -15455,7 +15444,7 @@
       </c>
       <c r="H3" s="120"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
         <v>128</v>
       </c>
@@ -15476,7 +15465,7 @@
       </c>
       <c r="H4" s="120"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
         <v>123</v>
       </c>
@@ -15487,7 +15476,7 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1">
       <c r="B6" s="149" t="s">
         <v>228</v>
       </c>
@@ -15505,7 +15494,7 @@
       <c r="F6" s="364"/>
       <c r="H6" s="120"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8">
       <c r="B7" s="148" t="s">
         <v>224</v>
       </c>
@@ -15521,7 +15510,7 @@
       <c r="F7" s="364"/>
       <c r="H7" s="120"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8">
       <c r="B8" s="148" t="s">
         <v>225</v>
       </c>
@@ -15537,7 +15526,7 @@
       <c r="F8" s="364"/>
       <c r="H8" s="120"/>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8">
       <c r="B9" s="205" t="s">
         <v>190</v>
       </c>
@@ -15553,7 +15542,7 @@
       <c r="F9" s="364"/>
       <c r="H9" s="120"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="149" t="s">
         <v>227</v>
       </c>
@@ -15567,7 +15556,7 @@
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:8" ht="13.15" thickBot="1">
       <c r="B11" s="207" t="s">
         <v>166</v>
       </c>
@@ -15581,7 +15570,7 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="14" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="13.5" thickTop="1">
       <c r="B12" s="149" t="s">
         <v>102</v>
       </c>
@@ -15595,10 +15584,10 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8">
       <c r="H13" s="120"/>
     </row>
-    <row r="14" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:8" ht="13.9">
       <c r="B14" s="36" t="s">
         <v>229</v>
       </c>
@@ -15608,13 +15597,13 @@
       <c r="F14" s="37"/>
       <c r="H14" s="120"/>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="119" t="s">
         <v>135</v>
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="13.25" customHeight="1">
       <c r="B16" s="152" t="s">
         <v>133</v>
       </c>
@@ -15624,7 +15613,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:17" ht="13.25" customHeight="1">
       <c r="B17" s="118" t="s">
         <v>134</v>
       </c>
@@ -15634,7 +15623,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:17" ht="13.25" customHeight="1">
       <c r="B18" s="153" t="s">
         <v>106</v>
       </c>
@@ -15648,10 +15637,10 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:17">
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:17" ht="14" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:17" ht="13.15">
       <c r="B20" s="128" t="s">
         <v>107</v>
       </c>
@@ -15669,7 +15658,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:17">
       <c r="B21" s="122">
         <v>1</v>
       </c>
@@ -15691,7 +15680,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:17">
       <c r="B22" s="122">
         <v>2</v>
       </c>
@@ -15713,7 +15702,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:17">
       <c r="B23" s="122">
         <v>3</v>
       </c>
@@ -15745,7 +15734,7 @@
       <c r="P23" s="338"/>
       <c r="Q23" s="338"/>
     </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:17">
       <c r="B24" s="122">
         <v>4</v>
       </c>
@@ -15777,7 +15766,7 @@
       <c r="P24" s="338"/>
       <c r="Q24" s="338"/>
     </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:17">
       <c r="B25" s="122">
         <v>5</v>
       </c>
@@ -15809,7 +15798,7 @@
       <c r="P25" s="338"/>
       <c r="Q25" s="338"/>
     </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:17">
       <c r="B26" s="122">
         <v>6</v>
       </c>
@@ -15831,7 +15820,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:17">
       <c r="B27" s="122">
         <v>7</v>
       </c>
@@ -15853,7 +15842,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:17">
       <c r="B28" s="122">
         <v>8</v>
       </c>
@@ -15875,7 +15864,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:17">
       <c r="B29" s="122">
         <v>9</v>
       </c>
@@ -15897,7 +15886,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:17">
       <c r="B30" s="122">
         <v>10</v>
       </c>
@@ -15919,7 +15908,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:17">
       <c r="B31" s="122">
         <v>11</v>
       </c>
@@ -15941,7 +15930,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:17">
       <c r="B32" s="122">
         <v>12</v>
       </c>
@@ -15963,7 +15952,7 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:17">
       <c r="B33" s="122">
         <v>13</v>
       </c>
@@ -15995,7 +15984,7 @@
       <c r="P33" s="338"/>
       <c r="Q33" s="338"/>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:17">
       <c r="B34" s="122">
         <v>14</v>
       </c>
@@ -16027,7 +16016,7 @@
       <c r="P34" s="338"/>
       <c r="Q34" s="338"/>
     </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:17">
       <c r="B35" s="122">
         <v>15</v>
       </c>
@@ -16059,7 +16048,7 @@
       <c r="P35" s="338"/>
       <c r="Q35" s="338"/>
     </row>
-    <row r="36" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:17">
       <c r="B36" s="122">
         <v>16</v>
       </c>
@@ -16081,7 +16070,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:17">
       <c r="B37" s="122">
         <v>17</v>
       </c>
@@ -16103,7 +16092,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:17">
       <c r="B38" s="122">
         <v>18</v>
       </c>
@@ -16125,7 +16114,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:17">
       <c r="B39" s="122">
         <v>19</v>
       </c>
@@ -16147,7 +16136,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:17">
       <c r="B40" s="122">
         <v>20</v>
       </c>
@@ -16169,7 +16158,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:17">
       <c r="B41" s="122">
         <v>21</v>
       </c>
@@ -16191,7 +16180,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:17">
       <c r="B42" s="122">
         <v>22</v>
       </c>
@@ -16213,7 +16202,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:17">
       <c r="B43" s="122">
         <v>23</v>
       </c>
@@ -16235,7 +16224,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:17">
       <c r="B44" s="122">
         <v>24</v>
       </c>
@@ -16257,7 +16246,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:17">
       <c r="B45" s="122">
         <v>25</v>
       </c>
@@ -16279,7 +16268,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:17">
       <c r="B46" s="122">
         <v>26</v>
       </c>
@@ -16301,7 +16290,7 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:17">
       <c r="B47" s="122">
         <v>27</v>
       </c>
@@ -16333,7 +16322,7 @@
       <c r="P47" s="338"/>
       <c r="Q47" s="338"/>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:17">
       <c r="B48" s="122">
         <v>28</v>
       </c>
@@ -16365,7 +16354,7 @@
       <c r="P48" s="338"/>
       <c r="Q48" s="338"/>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:17">
       <c r="B49" s="122">
         <v>29</v>
       </c>
@@ -16397,7 +16386,7 @@
       <c r="P49" s="338"/>
       <c r="Q49" s="338"/>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:17">
       <c r="B50" s="122">
         <v>30</v>
       </c>
@@ -16429,7 +16418,7 @@
       <c r="P50" s="338"/>
       <c r="Q50" s="338"/>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:17">
       <c r="B51" s="126" t="s">
         <v>131</v>
       </c>
@@ -16451,7 +16440,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:17">
       <c r="C52" s="114"/>
       <c r="E52" s="127" t="s">
         <v>100</v>
@@ -16462,11 +16451,11 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:17">
       <c r="C53" s="114"/>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:17" ht="13.15">
       <c r="B54" s="119" t="s">
         <v>129</v>
       </c>
@@ -16476,7 +16465,7 @@
       <c r="F54" s="117"/>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
         <v>2134789.7838004301</v>
@@ -16503,7 +16492,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:17" ht="13.15">
       <c r="A56" s="143">
         <v>5</v>
       </c>
@@ -16525,7 +16514,7 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:17" ht="13.15">
       <c r="A57" s="143">
         <v>10</v>
       </c>
@@ -16546,7 +16535,7 @@
       </c>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:17" ht="13.15">
       <c r="A58" s="143">
         <v>15</v>
       </c>
@@ -16577,7 +16566,7 @@
       <c r="P58" s="338"/>
       <c r="Q58" s="338"/>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:17" ht="13.15">
       <c r="A59" s="144">
         <v>20</v>
       </c>
@@ -16608,7 +16597,7 @@
       <c r="P59" s="338"/>
       <c r="Q59" s="338"/>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:17" ht="13.15">
       <c r="A60" s="144">
         <v>25</v>
       </c>
@@ -16639,7 +16628,7 @@
       <c r="P60" s="338"/>
       <c r="Q60" s="338"/>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:17" ht="13.15">
       <c r="A61" s="144">
         <v>30</v>
       </c>
@@ -16670,7 +16659,7 @@
       <c r="P61" s="338"/>
       <c r="Q61" s="338"/>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:17">
       <c r="C62" s="338"/>
       <c r="D62" s="114"/>
       <c r="E62" s="114"/>
@@ -16687,7 +16676,7 @@
       <c r="P62" s="338"/>
       <c r="Q62" s="338"/>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:17" ht="13.15">
       <c r="B63" s="119" t="s">
         <v>130</v>
       </c>
@@ -16707,7 +16696,7 @@
       <c r="P63" s="338"/>
       <c r="Q63" s="338"/>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:17" ht="13.15">
       <c r="B64" s="132">
         <f>B55</f>
         <v>0</v>
@@ -16730,7 +16719,7 @@
       </c>
       <c r="H64" s="120"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:8" ht="13.15">
       <c r="A65" s="143">
         <v>0</v>
       </c>
@@ -16756,7 +16745,7 @@
       </c>
       <c r="H65" s="120"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:8" ht="13.15">
       <c r="A66" s="143">
         <f t="shared" ref="A66:A71" si="3">A56</f>
         <v>5</v>
@@ -16783,7 +16772,7 @@
       </c>
       <c r="H66" s="120"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:8" ht="13.15">
       <c r="A67" s="143">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -16810,7 +16799,7 @@
       </c>
       <c r="H67" s="120"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:8" ht="13.15">
       <c r="A68" s="143">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -16837,7 +16826,7 @@
       </c>
       <c r="H68" s="120"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:8" ht="13.15">
       <c r="A69" s="144">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -16864,7 +16853,7 @@
       </c>
       <c r="H69" s="120"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:8" ht="13.15">
       <c r="A70" s="144">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -16890,7 +16879,7 @@
         <v>11.230437768943993</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:8" ht="13.15">
       <c r="A71" s="144">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -16916,7 +16905,7 @@
         <v>13.727281395318631</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:8" ht="13.15">
       <c r="B73" s="171" t="s">
         <v>117</v>
       </c>
@@ -16933,7 +16922,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:8">
       <c r="B74" s="127" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -16955,7 +16944,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:8">
       <c r="B75" s="127" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -16978,7 +16967,7 @@
       </c>
       <c r="H75" s="120"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:8">
       <c r="B76" s="127" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -17001,7 +16990,7 @@
       </c>
       <c r="H76" s="120"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:8">
       <c r="B77" s="127" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -17024,7 +17013,7 @@
       </c>
       <c r="H77" s="120"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:8">
       <c r="B78" s="127" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -17046,14 +17035,14 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:8">
       <c r="B79" s="155"/>
       <c r="C79" s="155"/>
       <c r="D79" s="155"/>
       <c r="E79" s="155"/>
       <c r="F79" s="156"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:8">
       <c r="B80" s="155" t="s">
         <v>310</v>
       </c>
@@ -17061,26 +17050,26 @@
         <v>105</v>
       </c>
     </row>
-    <row r="81" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="81" spans="3:3">
       <c r="C81" s="155" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="82" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="82" spans="3:3">
       <c r="C82" s="155" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="92" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="92" spans="3:3">
       <c r="C92" s="115"/>
     </row>
-    <row r="93" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="93" spans="3:3">
       <c r="C93" s="115"/>
     </row>
-    <row r="94" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="94" spans="3:3">
       <c r="C94" s="115"/>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="101" spans="3:17">
       <c r="C101" s="338"/>
       <c r="G101" s="338"/>
       <c r="H101" s="338"/>
@@ -17094,7 +17083,7 @@
       <c r="P101" s="338"/>
       <c r="Q101" s="338"/>
     </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="102" spans="3:17">
       <c r="C102" s="338"/>
       <c r="G102" s="338"/>
       <c r="H102" s="338"/>
@@ -17108,7 +17097,7 @@
       <c r="P102" s="338"/>
       <c r="Q102" s="338"/>
     </row>
-    <row r="103" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="103" spans="3:17">
       <c r="C103" s="338"/>
       <c r="G103" s="338"/>
       <c r="H103" s="338"/>
@@ -17122,7 +17111,7 @@
       <c r="P103" s="338"/>
       <c r="Q103" s="338"/>
     </row>
-    <row r="104" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="104" spans="3:17">
       <c r="C104" s="338"/>
       <c r="G104" s="338"/>
       <c r="H104" s="338"/>
@@ -17136,7 +17125,7 @@
       <c r="P104" s="338"/>
       <c r="Q104" s="338"/>
     </row>
-    <row r="105" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="105" spans="3:17">
       <c r="C105" s="338"/>
       <c r="G105" s="338"/>
       <c r="H105" s="338"/>
@@ -17181,16 +17170,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="6" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>442</v>
       </c>
@@ -17202,7 +17191,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
         <v>441</v>
       </c>
@@ -17215,7 +17204,7 @@
       </c>
       <c r="H3" s="120"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
         <v>439</v>
       </c>
@@ -17236,7 +17225,7 @@
       </c>
       <c r="H4" s="120"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
         <v>123</v>
       </c>
@@ -17247,7 +17236,7 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1">
       <c r="B6" s="149" t="s">
         <v>440</v>
       </c>
@@ -17263,7 +17252,7 @@
       <c r="F6" s="364"/>
       <c r="H6" s="120"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="13.15">
       <c r="B7" s="149" t="s">
         <v>443</v>
       </c>
@@ -17277,10 +17266,10 @@
       </c>
       <c r="H7" s="120"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8">
       <c r="H8" s="120"/>
     </row>
-    <row r="9" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" ht="13.9">
       <c r="B9" s="36" t="s">
         <v>229</v>
       </c>
@@ -17290,13 +17279,13 @@
       <c r="F9" s="37"/>
       <c r="H9" s="120"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="119" t="s">
         <v>135</v>
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="13.25" customHeight="1">
       <c r="B11" s="152" t="s">
         <v>133</v>
       </c>
@@ -17306,7 +17295,7 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="13.25" customHeight="1">
       <c r="B12" s="118" t="s">
         <v>134</v>
       </c>
@@ -17316,7 +17305,7 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="13.25" customHeight="1">
       <c r="B13" s="153" t="s">
         <v>106</v>
       </c>
@@ -17330,10 +17319,10 @@
       </c>
       <c r="H13" s="120"/>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8">
       <c r="H14" s="120"/>
     </row>
-    <row r="15" spans="2:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="128" t="s">
         <v>107</v>
       </c>
@@ -17351,7 +17340,7 @@
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8">
       <c r="B16" s="122">
         <v>1</v>
       </c>
@@ -17373,7 +17362,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8">
       <c r="B17" s="122">
         <v>2</v>
       </c>
@@ -17395,7 +17384,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8">
       <c r="B18" s="122">
         <v>3</v>
       </c>
@@ -17417,7 +17406,7 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8">
       <c r="B19" s="122">
         <v>4</v>
       </c>
@@ -17439,7 +17428,7 @@
       </c>
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8">
       <c r="B20" s="122">
         <v>5</v>
       </c>
@@ -17461,7 +17450,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8">
       <c r="B21" s="122">
         <v>6</v>
       </c>
@@ -17483,7 +17472,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8">
       <c r="B22" s="122">
         <v>7</v>
       </c>
@@ -17505,7 +17494,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8">
       <c r="B23" s="122">
         <v>8</v>
       </c>
@@ -17527,7 +17516,7 @@
       </c>
       <c r="H23" s="120"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8">
       <c r="B24" s="122">
         <v>9</v>
       </c>
@@ -17549,7 +17538,7 @@
       </c>
       <c r="H24" s="120"/>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:8">
       <c r="B25" s="122">
         <v>10</v>
       </c>
@@ -17571,7 +17560,7 @@
       </c>
       <c r="H25" s="120"/>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8">
       <c r="B26" s="122">
         <v>11</v>
       </c>
@@ -17593,7 +17582,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8">
       <c r="B27" s="122">
         <v>12</v>
       </c>
@@ -17615,7 +17604,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8">
       <c r="B28" s="122">
         <v>13</v>
       </c>
@@ -17637,7 +17626,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8">
       <c r="B29" s="122">
         <v>14</v>
       </c>
@@ -17659,7 +17648,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8">
       <c r="B30" s="122">
         <v>15</v>
       </c>
@@ -17681,7 +17670,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8">
       <c r="B31" s="122">
         <v>16</v>
       </c>
@@ -17703,7 +17692,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8">
       <c r="B32" s="122">
         <v>17</v>
       </c>
@@ -17725,7 +17714,7 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8">
       <c r="B33" s="122">
         <v>18</v>
       </c>
@@ -17747,7 +17736,7 @@
       </c>
       <c r="H33" s="120"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8">
       <c r="B34" s="122">
         <v>19</v>
       </c>
@@ -17769,7 +17758,7 @@
       </c>
       <c r="H34" s="120"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8">
       <c r="B35" s="122">
         <v>20</v>
       </c>
@@ -17791,7 +17780,7 @@
       </c>
       <c r="H35" s="120"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8">
       <c r="B36" s="122">
         <v>21</v>
       </c>
@@ -17813,7 +17802,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8">
       <c r="B37" s="122">
         <v>22</v>
       </c>
@@ -17835,7 +17824,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8">
       <c r="B38" s="122">
         <v>23</v>
       </c>
@@ -17857,7 +17846,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8">
       <c r="B39" s="122">
         <v>24</v>
       </c>
@@ -17879,7 +17868,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8">
       <c r="B40" s="122">
         <v>25</v>
       </c>
@@ -17901,7 +17890,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8">
       <c r="B41" s="122">
         <v>26</v>
       </c>
@@ -17923,7 +17912,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8">
       <c r="B42" s="122">
         <v>27</v>
       </c>
@@ -17945,7 +17934,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:8">
       <c r="B43" s="122">
         <v>28</v>
       </c>
@@ -17967,7 +17956,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8">
       <c r="B44" s="122">
         <v>29</v>
       </c>
@@ -17989,7 +17978,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8">
       <c r="B45" s="122">
         <v>30</v>
       </c>
@@ -18011,7 +18000,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8">
       <c r="B46" s="126" t="s">
         <v>131</v>
       </c>
@@ -18033,7 +18022,7 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8">
       <c r="C47" s="114"/>
       <c r="E47" s="127" t="s">
         <v>100</v>
@@ -18044,11 +18033,11 @@
       </c>
       <c r="H47" s="120"/>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8">
       <c r="C48" s="114"/>
       <c r="H48" s="120"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:8" ht="13.15">
       <c r="B49" s="119" t="s">
         <v>129</v>
       </c>
@@ -18058,7 +18047,7 @@
       <c r="F49" s="117"/>
       <c r="H49" s="120"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
         <v>962285.7114352209</v>
@@ -18085,7 +18074,7 @@
       </c>
       <c r="H50" s="120"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:8" ht="13.15">
       <c r="A51" s="143">
         <v>5</v>
       </c>
@@ -18107,7 +18096,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:8" ht="13.15">
       <c r="A52" s="143">
         <v>10</v>
       </c>
@@ -18128,7 +18117,7 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:8" ht="13.15">
       <c r="A53" s="143">
         <v>15</v>
       </c>
@@ -18149,7 +18138,7 @@
       </c>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:8" ht="13.15">
       <c r="A54" s="144">
         <v>20</v>
       </c>
@@ -18170,7 +18159,7 @@
       </c>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="144">
         <v>25</v>
       </c>
@@ -18191,7 +18180,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:8" ht="13.15">
       <c r="A56" s="144">
         <v>30</v>
       </c>
@@ -18212,14 +18201,14 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:8">
       <c r="C57" s="114"/>
       <c r="D57" s="114"/>
       <c r="E57" s="114"/>
       <c r="F57" s="114"/>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:8" ht="13.15">
       <c r="B58" s="119" t="s">
         <v>130</v>
       </c>
@@ -18229,7 +18218,7 @@
       <c r="F58" s="114"/>
       <c r="H58" s="120"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:8" ht="13.15">
       <c r="B59" s="132">
         <f>B50</f>
         <v>0</v>
@@ -18252,7 +18241,7 @@
       </c>
       <c r="H59" s="120"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:8" ht="13.15">
       <c r="A60" s="143">
         <v>0</v>
       </c>
@@ -18278,7 +18267,7 @@
       </c>
       <c r="H60" s="120"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:8" ht="13.15">
       <c r="A61" s="143">
         <f t="shared" ref="A61:A66" si="3">A51</f>
         <v>5</v>
@@ -18305,7 +18294,7 @@
       </c>
       <c r="H61" s="120"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:8" ht="13.15">
       <c r="A62" s="143">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -18332,7 +18321,7 @@
       </c>
       <c r="H62" s="120"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:8" ht="13.15">
       <c r="A63" s="143">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -18359,7 +18348,7 @@
       </c>
       <c r="H63" s="120"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:8" ht="13.15">
       <c r="A64" s="144">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -18386,7 +18375,7 @@
       </c>
       <c r="H64" s="120"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:8" ht="13.15">
       <c r="A65" s="144">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -18412,7 +18401,7 @@
         <v>4.6820200777530729</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:8" ht="13.15">
       <c r="A66" s="144">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -18438,7 +18427,7 @@
         <v>5.8075065137388604</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8" ht="13.15">
       <c r="B68" s="171" t="s">
         <v>117</v>
       </c>
@@ -18455,7 +18444,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:8">
       <c r="B69" s="127" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -18477,7 +18466,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:8">
       <c r="B70" s="127" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -18500,7 +18489,7 @@
       </c>
       <c r="H70" s="120"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:8">
       <c r="B71" s="127" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -18523,7 +18512,7 @@
       </c>
       <c r="H71" s="120"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:8">
       <c r="B72" s="127" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -18546,7 +18535,7 @@
       </c>
       <c r="H72" s="120"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:8">
       <c r="B73" s="127" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -18568,14 +18557,14 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:8">
       <c r="B74" s="155"/>
       <c r="C74" s="155"/>
       <c r="D74" s="155"/>
       <c r="E74" s="155"/>
       <c r="F74" s="156"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:8">
       <c r="B75" s="155" t="s">
         <v>310</v>
       </c>
@@ -18583,23 +18572,23 @@
         <v>105</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:8">
       <c r="C76" s="155" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:8">
       <c r="C77" s="155" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="87" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="87" spans="3:3">
       <c r="C87" s="115"/>
     </row>
-    <row r="88" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="88" spans="3:3">
       <c r="C88" s="115"/>
     </row>
-    <row r="89" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="89" spans="3:3">
       <c r="C89" s="115"/>
     </row>
   </sheetData>
@@ -18629,7 +18618,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
@@ -18639,7 +18628,7 @@
     <col min="8" max="9" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:9" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>145</v>
       </c>
@@ -18652,7 +18641,7 @@
       </c>
       <c r="I2" s="249"/>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="159" t="s">
         <v>148</v>
       </c>
@@ -18661,10 +18650,10 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-3.6</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.15">
+        <v>-3.57</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9">
       <c r="B4" s="152" t="s">
         <v>146</v>
       </c>
@@ -18684,7 +18673,7 @@
         <v>0.128</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:9">
       <c r="H5" s="247">
         <v>2</v>
       </c>
@@ -18693,7 +18682,7 @@
         <v>0.128</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:9" ht="13.15">
       <c r="B6" s="159" t="s">
         <v>95</v>
       </c>
@@ -18713,7 +18702,7 @@
         <v>5.3526962590200808</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:9" ht="12.75" customHeight="1">
       <c r="B7" s="100" t="s">
         <v>275</v>
       </c>
@@ -18738,7 +18727,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:9">
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
@@ -18760,7 +18749,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:9">
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
@@ -18782,7 +18771,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:9">
       <c r="E10" s="366"/>
       <c r="F10" s="366"/>
       <c r="H10" s="247">
@@ -18793,7 +18782,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="159" t="s">
         <v>446</v>
       </c>
@@ -18807,7 +18796,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="14" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:9">
       <c r="B12" s="118" t="s">
         <v>144</v>
       </c>
@@ -18826,7 +18815,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:9">
       <c r="B13" s="148" t="s">
         <v>152</v>
       </c>
@@ -18844,7 +18833,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:9">
       <c r="B14" s="100" t="s">
         <v>66</v>
       </c>
@@ -18855,7 +18844,7 @@
       <c r="E14" s="366"/>
       <c r="F14" s="366"/>
     </row>
-    <row r="16" spans="2:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
         <v>162</v>
       </c>
@@ -18864,7 +18853,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="37"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:6" ht="13.15">
       <c r="B17" s="109" t="s">
         <v>151</v>
       </c>
@@ -18872,7 +18861,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:6">
       <c r="B18" s="152" t="s">
         <v>133</v>
       </c>
@@ -18884,24 +18873,24 @@
       </c>
       <c r="F18" s="367"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:6">
       <c r="E19" s="367"/>
       <c r="F19" s="367"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
         <v>303</v>
       </c>
       <c r="E20" s="367"/>
       <c r="F20" s="367"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
         <v>277</v>
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>3.6</v>
+        <v>3.57</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -18910,7 +18899,7 @@
       <c r="E21" s="367"/>
       <c r="F21" s="367"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
         <v>278</v>
       </c>
@@ -18925,7 +18914,7 @@
       <c r="E22" s="367"/>
       <c r="F22" s="367"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
         <v>115</v>
       </c>
@@ -18934,7 +18923,7 @@
       </c>
       <c r="F24" s="159"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:6">
       <c r="B25" s="152" t="s">
         <v>133</v>
       </c>
@@ -18946,7 +18935,7 @@
       <c r="E25" s="365"/>
       <c r="F25" s="365"/>
     </row>
-    <row r="26" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
         <v>134</v>
       </c>
@@ -18957,7 +18946,7 @@
       <c r="E26" s="365"/>
       <c r="F26" s="365"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
         <v>113</v>
       </c>
@@ -18972,7 +18961,7 @@
       <c r="E27" s="365"/>
       <c r="F27" s="365"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
         <v>147</v>
       </c>
@@ -18983,7 +18972,7 @@
       <c r="E28" s="365"/>
       <c r="F28" s="365"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
         <v>116</v>
       </c>
@@ -18992,7 +18981,7 @@
       </c>
       <c r="F30" s="159"/>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:6">
       <c r="B31" s="152" t="s">
         <v>133</v>
       </c>
@@ -19004,7 +18993,7 @@
       <c r="E31" s="365"/>
       <c r="F31" s="365"/>
     </row>
-    <row r="32" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
         <v>134</v>
       </c>
@@ -19015,7 +19004,7 @@
       <c r="E32" s="365"/>
       <c r="F32" s="365"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
         <v>113</v>
       </c>
@@ -19030,7 +19019,7 @@
       <c r="E33" s="365"/>
       <c r="F33" s="365"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
         <v>147</v>
       </c>
@@ -19041,7 +19030,7 @@
       <c r="E34" s="365"/>
       <c r="F34" s="365"/>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
         <v>114</v>
       </c>
@@ -19050,7 +19039,7 @@
       </c>
       <c r="F36" s="159"/>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:6">
       <c r="B37" s="152" t="s">
         <v>133</v>
       </c>
@@ -19062,7 +19051,7 @@
       <c r="E37" s="365"/>
       <c r="F37" s="365"/>
     </row>
-    <row r="38" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
         <v>134</v>
       </c>
@@ -19073,7 +19062,7 @@
       <c r="E38" s="365"/>
       <c r="F38" s="365"/>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
         <v>113</v>
       </c>
@@ -19088,7 +19077,7 @@
       <c r="E39" s="365"/>
       <c r="F39" s="365"/>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
         <v>147</v>
       </c>
@@ -19100,7 +19089,7 @@
       <c r="E40" s="365"/>
       <c r="F40" s="365"/>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
         <v>120</v>
       </c>
@@ -19113,7 +19102,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:6" ht="13.9">
       <c r="B44" s="36" t="s">
         <v>161</v>
       </c>
@@ -19122,12 +19111,12 @@
       <c r="E44" s="37"/>
       <c r="F44" s="37"/>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:6" ht="13.15">
       <c r="B45" s="109" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:6">
       <c r="B46" s="152" t="s">
         <v>133</v>
       </c>
@@ -19137,12 +19126,12 @@
       <c r="E46" s="100"/>
       <c r="F46" s="100"/>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:6" ht="13.15">
       <c r="B47" s="159"/>
       <c r="E47" s="159"/>
       <c r="F47" s="159"/>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:6" ht="13.15">
       <c r="B48" s="159" t="s">
         <v>165</v>
       </c>
@@ -19151,7 +19140,7 @@
       </c>
       <c r="F48" s="159"/>
     </row>
-    <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:6" ht="12.75" customHeight="1">
       <c r="B49" s="152" t="s">
         <v>133</v>
       </c>
@@ -19163,7 +19152,7 @@
       <c r="E49" s="365"/>
       <c r="F49" s="365"/>
     </row>
-    <row r="50" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
         <v>134</v>
       </c>
@@ -19174,7 +19163,7 @@
       <c r="E50" s="365"/>
       <c r="F50" s="365"/>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
         <v>113</v>
       </c>
@@ -19189,7 +19178,7 @@
       <c r="E51" s="365"/>
       <c r="F51" s="365"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
         <v>147</v>
       </c>
@@ -19200,7 +19189,7 @@
       <c r="E52" s="365"/>
       <c r="F52" s="365"/>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
         <v>316</v>
       </c>
@@ -19209,7 +19198,7 @@
       </c>
       <c r="F54" s="159"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="152" t="s">
         <v>133</v>
       </c>
@@ -19221,7 +19210,7 @@
       <c r="E55" s="365"/>
       <c r="F55" s="365"/>
     </row>
-    <row r="56" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
         <v>134</v>
       </c>
@@ -19232,7 +19221,7 @@
       <c r="E56" s="365"/>
       <c r="F56" s="365"/>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
         <v>113</v>
       </c>
@@ -19247,7 +19236,7 @@
       <c r="E57" s="365"/>
       <c r="F57" s="365"/>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
         <v>147</v>
       </c>
@@ -19258,7 +19247,7 @@
       <c r="E58" s="365"/>
       <c r="F58" s="365"/>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
         <v>120</v>
       </c>
@@ -19278,7 +19267,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
         <v>349</v>
       </c>
@@ -19287,7 +19276,7 @@
       <c r="E62" s="37"/>
       <c r="F62" s="37"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
         <v>304</v>
       </c>
@@ -19295,7 +19284,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:6">
       <c r="B64" s="152" t="s">
         <v>133</v>
       </c>
@@ -19308,7 +19297,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="65" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6">
       <c r="B65" s="118" t="s">
         <v>134</v>
       </c>
@@ -19320,7 +19309,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6">
       <c r="B66" s="100" t="s">
         <v>102</v>
       </c>
@@ -19336,7 +19325,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
         <v>350</v>
       </c>
@@ -19344,7 +19333,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
         <v>305</v>
       </c>
@@ -19354,7 +19343,7 @@
       </c>
       <c r="E69" s="134"/>
     </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
         <v>293</v>
       </c>
@@ -19366,7 +19355,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
         <v>292</v>
       </c>
@@ -19376,7 +19365,7 @@
       </c>
       <c r="E71" s="251"/>
     </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
         <v>284</v>
       </c>
@@ -19392,7 +19381,7 @@
         <v>0.16145934558016128</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:6" ht="13.9">
       <c r="B74" s="36" t="s">
         <v>127</v>
       </c>
@@ -19401,12 +19390,12 @@
       <c r="E74" s="37"/>
       <c r="F74" s="37"/>
     </row>
-    <row r="75" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="13.15">
       <c r="B75" s="109" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6">
       <c r="B76" s="246" t="s">
         <v>297</v>
       </c>
@@ -19416,7 +19405,7 @@
       </c>
       <c r="D76" s="134"/>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6">
       <c r="B77" s="100" t="s">
         <v>111</v>
       </c>
@@ -19429,12 +19418,12 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6">
       <c r="B80" s="148" t="s">
         <v>299</v>
       </c>
@@ -19443,7 +19432,7 @@
         <v>0.3674</v>
       </c>
     </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:8">
       <c r="B81" s="100" t="s">
         <v>121</v>
       </c>
@@ -19455,7 +19444,7 @@
       <c r="E81" s="100"/>
       <c r="F81" s="100"/>
     </row>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8">
       <c r="B82" s="100" t="s">
         <v>122</v>
       </c>
@@ -19465,7 +19454,7 @@
       </c>
       <c r="D82" s="116"/>
     </row>
-    <row r="83" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="83" spans="2:8" ht="13.15">
       <c r="B83" s="110" t="s">
         <v>101</v>
       </c>
@@ -19485,45 +19474,45 @@
         <v>0.56827582510368113</v>
       </c>
     </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:8">
       <c r="E84" s="120"/>
     </row>
-    <row r="85" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8">
       <c r="B86" s="148" t="s">
         <v>300</v>
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>3.6</v>
+        <v>3.57</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
         <v>298</v>
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.16382813843087729</v>
-      </c>
-    </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.1671769416467408</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8">
       <c r="B88" s="100"/>
     </row>
-    <row r="89" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="90" spans="2:8">
       <c r="B90" s="148" t="s">
         <v>413</v>
       </c>
@@ -19532,7 +19521,7 @@
         <v>0.21740000000000001</v>
       </c>
     </row>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="91" spans="2:8">
       <c r="B91" s="100" t="s">
         <v>121</v>
       </c>
@@ -19544,7 +19533,7 @@
       <c r="E91" s="100"/>
       <c r="F91" s="100"/>
     </row>
-    <row r="92" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
         <v>122</v>
       </c>
@@ -19554,7 +19543,7 @@
       </c>
       <c r="D92" s="116"/>
     </row>
-    <row r="93" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="93" spans="2:8" ht="13.15">
       <c r="B93" s="110" t="s">
         <v>101</v>
       </c>
@@ -19574,14 +19563,14 @@
         <v>0.39552430404120198</v>
       </c>
     </row>
-    <row r="95" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
         <v>397</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="281"/>
     </row>
-    <row r="96" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="96" spans="2:8">
       <c r="B96" s="148" t="s">
         <v>403</v>
       </c>
@@ -19592,7 +19581,7 @@
       <c r="G96" s="2"/>
       <c r="H96" s="281"/>
     </row>
-    <row r="97" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
         <v>121</v>
       </c>
@@ -19604,7 +19593,7 @@
       <c r="G97" s="2"/>
       <c r="H97" s="281"/>
     </row>
-    <row r="98" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
         <v>122</v>
       </c>
@@ -19616,7 +19605,7 @@
       <c r="G98" s="2"/>
       <c r="H98" s="281"/>
     </row>
-    <row r="99" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="110" t="s">
         <v>398</v>
       </c>
@@ -19635,15 +19624,15 @@
         <v>0.13132906759055596</v>
       </c>
     </row>
-    <row r="100" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="100" spans="2:8">
       <c r="B100" s="100"/>
     </row>
-    <row r="101" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="102" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:8">
       <c r="B102" s="148" t="s">
         <v>420</v>
       </c>
@@ -19652,7 +19641,7 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="103" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:8">
       <c r="B103" s="100" t="s">
         <v>121</v>
       </c>
@@ -19662,7 +19651,7 @@
       </c>
       <c r="D103" s="116"/>
     </row>
-    <row r="104" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:8">
       <c r="B104" s="100" t="s">
         <v>122</v>
       </c>
@@ -19672,7 +19661,7 @@
       </c>
       <c r="D104" s="116"/>
     </row>
-    <row r="105" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="110" t="s">
         <v>398</v>
       </c>
@@ -19691,16 +19680,16 @@
         <v>0.22401578084943807</v>
       </c>
     </row>
-    <row r="106" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="106" spans="2:8">
       <c r="B106" s="100"/>
     </row>
-    <row r="107" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:8" ht="14.65">
       <c r="E107" s="285" t="s">
         <v>324</v>
       </c>
       <c r="F107" s="282"/>
     </row>
-    <row r="108" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:8" ht="13.9">
       <c r="E108" s="278" t="s">
         <v>325</v>
       </c>
@@ -19708,7 +19697,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="109" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:8" ht="13.9">
       <c r="E109" s="279" t="s">
         <v>325</v>
       </c>
@@ -19716,7 +19705,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="110" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:8" ht="13.9">
       <c r="E110" s="280" t="s">
         <v>325</v>
       </c>

--- a/financial_models/opportunities/0398.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0398.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8221FA10-23E7-4E1A-98F9-5A5F8C16108B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E88D126-4131-4550-AB37-09CB2B94F984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3891,29 +3891,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4331,7 +4331,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>3.57</v>
+        <v>3.58</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>1739.8688596799998</v>
+        <v>1744.7424419200001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4389,13 +4389,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.1671769416467408</v>
+        <v>0.166056434583427</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4595,22 +4595,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4622,13 +4622,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4648,13 +4648,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4683,13 +4683,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4705,13 +4705,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4775,13 +4775,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4797,7 +4797,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4819,22 +4819,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>7.9541327003833207E-2</v>
+        <v>7.9319144526168853E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4878,7 +4878,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.5854341736694682E-2</v>
+        <v>3.5754189944134075E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>447</v>
@@ -4969,22 +4969,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5028,22 +5028,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5080,13 +5080,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5099,13 +5099,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5227,13 +5227,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5272,13 +5272,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5421,13 +5421,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5440,22 +5440,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5788,13 +5788,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5831,13 +5831,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5845,22 +5845,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="356" t="s">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5884,6 +5884,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5900,17 +5911,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13408,24 +13408,24 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.5854341736694682E-2</v>
+        <v>3.5754189944134075E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.5854341736694682E-2</v>
+        <v>3.5754189944134075E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>4.2857142857142858E-2</v>
+        <v>4.2737430167597762E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>5.2100840336134456E-2</v>
+        <v>5.1955307262569833E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>4.145658263305322E-2</v>
+        <v>4.1340782122905026E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
@@ -14607,46 +14607,46 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.9541327003833207E-2</v>
+        <v>7.9319144526168853E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.11171704057956958</v>
+        <v>0.11140498180700094</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.14338436981157476</v>
+        <v>0.14298385481210107</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.15459038680045631</v>
+        <v>0.15415857007754999</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.10653504082720994</v>
+        <v>0.10623745691428477</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>6.4976161491155357E-2</v>
+        <v>6.4794663833358829E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>5.9514255585357487E-2</v>
+        <v>5.9348014647968218E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>5.5854209620070649E-2</v>
+        <v>5.5698192274763185E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>-3.8100572713389552E-3</v>
+        <v>-3.7994146532625891E-3</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>-3.2382900404552634E-2</v>
+        <v>-3.2292445375489635E-2</v>
       </c>
       <c r="P125" s="77" t="str">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
@@ -14664,39 +14664,39 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14434995982754242</v>
+        <v>0.14394674764925317</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16985418088024942</v>
+        <v>0.16937972786103084</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.20862262002134993</v>
+        <v>0.20803987527268691</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1337020308776517</v>
+        <v>0.13332856151765823</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.6963488626509656E-2</v>
+        <v>5.6804372736491471E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9338738222712035E-2</v>
+        <v>7.9117121635497736E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9710030574090068E-2</v>
+        <v>7.9487376857402647E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.2518467184708342E-3</v>
+        <v>9.2260035712125356E-3</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-9.0575792033535368E-3</v>
+        <v>-9.0322787027855098E-3</v>
       </c>
       <c r="P126" s="23" t="str">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18650,7 +18650,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-3.57</v>
+        <v>-3.58</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18890,7 +18890,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>3.57</v>
+        <v>3.58</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19488,7 +19488,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>3.57</v>
+        <v>3.58</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19501,7 +19501,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.1671769416467408</v>
+        <v>0.166056434583427</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0398.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0398.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E88D126-4131-4550-AB37-09CB2B94F984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04B5113C-0EB9-4C98-B6E3-16DE25680CE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3891,29 +3891,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4331,7 +4331,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>3.58</v>
+        <v>3.57</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>1744.7424419200001</v>
+        <v>1739.8688596799998</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4389,13 +4389,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="356" t="s">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.166056434583427</v>
+        <v>0.1671769416467408</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4595,22 +4595,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="356" t="s">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="358" t="s">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4622,13 +4622,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="357" t="s">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4648,13 +4648,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="357" t="s">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4683,13 +4683,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="357" t="s">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4705,13 +4705,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="357" t="s">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4775,13 +4775,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="357" t="s">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4797,7 +4797,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="357" t="s">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4819,22 +4819,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="356" t="s">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="356" t="s">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>7.9319144526168853E-2</v>
+        <v>7.9541327003833207E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4878,7 +4878,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.5754189944134075E-2</v>
+        <v>3.5854341736694682E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>447</v>
@@ -4969,22 +4969,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="358" t="s">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5028,22 +5028,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="356" t="s">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="356" t="s">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5080,13 +5080,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="356" t="s">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5099,13 +5099,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="356" t="s">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5227,13 +5227,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="356" t="s">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5272,13 +5272,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="357" t="s">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5421,13 +5421,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="361" t="s">
+      <c r="B134" s="362" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5440,22 +5440,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="359" t="s">
+      <c r="B138" s="363" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="356" t="s">
+      <c r="B139" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5788,13 +5788,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="363" t="s">
+      <c r="B179" s="357" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5831,13 +5831,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="357" t="s">
+      <c r="B188" s="359" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5845,22 +5845,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="362" t="s">
+      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="362" t="s">
+      <c r="B192" s="356" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5884,17 +5884,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5911,6 +5900,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13408,24 +13408,24 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.5754189944134075E-2</v>
+        <v>3.5854341736694682E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.5754189944134075E-2</v>
+        <v>3.5854341736694682E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>4.2737430167597762E-2</v>
+        <v>4.2857142857142858E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>5.1955307262569833E-2</v>
+        <v>5.2100840336134456E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>4.1340782122905026E-2</v>
+        <v>4.145658263305322E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
@@ -14607,46 +14607,46 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.9319144526168853E-2</v>
+        <v>7.9541327003833207E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.11140498180700094</v>
+        <v>0.11171704057956958</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.14298385481210107</v>
+        <v>0.14338436981157476</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.15415857007754999</v>
+        <v>0.15459038680045631</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.10623745691428477</v>
+        <v>0.10653504082720994</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>6.4794663833358829E-2</v>
+        <v>6.4976161491155357E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>5.9348014647968218E-2</v>
+        <v>5.9514255585357487E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>5.5698192274763185E-2</v>
+        <v>5.5854209620070649E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>-3.7994146532625891E-3</v>
+        <v>-3.8100572713389552E-3</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>-3.2292445375489635E-2</v>
+        <v>-3.2382900404552634E-2</v>
       </c>
       <c r="P125" s="77" t="str">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
@@ -14664,39 +14664,39 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14394674764925317</v>
+        <v>0.14434995982754242</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16937972786103084</v>
+        <v>0.16985418088024942</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.20803987527268691</v>
+        <v>0.20862262002134993</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13332856151765823</v>
+        <v>0.1337020308776517</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.6804372736491471E-2</v>
+        <v>5.6963488626509656E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9117121635497736E-2</v>
+        <v>7.9338738222712035E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9487376857402647E-2</v>
+        <v>7.9710030574090068E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.2260035712125356E-3</v>
+        <v>9.2518467184708342E-3</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-9.0322787027855098E-3</v>
+        <v>-9.0575792033535368E-3</v>
       </c>
       <c r="P126" s="23" t="str">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18650,7 +18650,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-3.58</v>
+        <v>-3.57</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18890,7 +18890,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>3.58</v>
+        <v>3.57</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19488,7 +19488,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>3.58</v>
+        <v>3.57</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19501,7 +19501,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.166056434583427</v>
+        <v>0.1671769416467408</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0398.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0398.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04B5113C-0EB9-4C98-B6E3-16DE25680CE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8846DBEC-2932-4086-86A1-231F78DC728E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3891,29 +3891,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4331,7 +4331,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>3.57</v>
+        <v>3.54</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>1739.8688596799998</v>
+        <v>1725.2481129600001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4389,13 +4389,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.1671769416467408</v>
+        <v>0.17056423895080175</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4595,22 +4595,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4622,13 +4622,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4648,13 +4648,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4683,13 +4683,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4705,13 +4705,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4775,13 +4775,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4797,7 +4797,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4819,22 +4819,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>7.9541327003833207E-2</v>
+        <v>8.0215406046238558E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4878,7 +4878,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.5854341736694682E-2</v>
+        <v>3.6158192090395481E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>447</v>
@@ -4969,22 +4969,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5028,22 +5028,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5080,13 +5080,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5099,13 +5099,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5227,13 +5227,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5272,13 +5272,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5421,13 +5421,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5440,22 +5440,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5788,13 +5788,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5831,13 +5831,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5845,22 +5845,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="356" t="s">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5884,6 +5884,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5900,17 +5911,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13408,24 +13408,24 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.5854341736694682E-2</v>
+        <v>3.6158192090395481E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.5854341736694682E-2</v>
+        <v>3.6158192090395481E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>4.2857142857142858E-2</v>
+        <v>4.3220338983050846E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>5.2100840336134456E-2</v>
+        <v>5.254237288135593E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>4.145658263305322E-2</v>
+        <v>4.1807909604519772E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
@@ -14607,46 +14607,46 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.9541327003833207E-2</v>
+        <v>8.0215406046238558E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.11171704057956958</v>
+        <v>0.11266379516075237</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.14338436981157476</v>
+        <v>0.14459949158963895</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.15459038680045631</v>
+        <v>0.15590047482418898</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.10653504082720994</v>
+        <v>0.10743788015625409</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>6.4976161491155357E-2</v>
+        <v>6.5526806927521081E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>5.9514255585357487E-2</v>
+        <v>6.0018613683538481E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>5.5854209620070649E-2</v>
+        <v>5.6327550379562774E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>-3.8100572713389552E-3</v>
+        <v>-3.8423458922825053E-3</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>-3.2382900404552634E-2</v>
+        <v>-3.265733176391325E-2</v>
       </c>
       <c r="P125" s="77" t="str">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
@@ -14664,39 +14664,39 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14434995982754242</v>
+        <v>0.14557326457184361</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16985418088024942</v>
+        <v>0.17129362309109897</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.20862262002134993</v>
+        <v>0.21039060832661557</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1337020308776517</v>
+        <v>0.13483509893593687</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.6963488626509656E-2</v>
+        <v>5.7446230055547873E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9338738222712035E-2</v>
+        <v>8.0011100411040093E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9710030574090068E-2</v>
+        <v>8.0385539307768789E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.2518467184708342E-3</v>
+        <v>9.3302521991358404E-3</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-9.0575792033535368E-3</v>
+        <v>-9.1343383491446686E-3</v>
       </c>
       <c r="P126" s="23" t="str">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18650,7 +18650,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-3.57</v>
+        <v>-3.54</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18890,7 +18890,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>3.57</v>
+        <v>3.54</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19488,7 +19488,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>3.57</v>
+        <v>3.54</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19501,7 +19501,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.1671769416467408</v>
+        <v>0.17056423895080175</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0398.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0398.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8846DBEC-2932-4086-86A1-231F78DC728E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F50B650-881D-4B49-92F8-BF6DDACE45E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3891,29 +3891,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4331,7 +4331,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>3.54</v>
+        <v>3.58</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>1725.2481129600001</v>
+        <v>1744.7424419200001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4389,13 +4389,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="356" t="s">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.17056423895080175</v>
+        <v>0.166056434583427</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4595,22 +4595,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="356" t="s">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="358" t="s">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4622,13 +4622,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="357" t="s">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4648,13 +4648,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="357" t="s">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4683,13 +4683,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="357" t="s">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4705,13 +4705,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="357" t="s">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4775,13 +4775,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="357" t="s">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4797,7 +4797,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="357" t="s">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4819,22 +4819,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="356" t="s">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="356" t="s">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>8.0215406046238558E-2</v>
+        <v>7.9319144526168853E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4878,7 +4878,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.6158192090395481E-2</v>
+        <v>3.5754189944134075E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>447</v>
@@ -4969,22 +4969,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="358" t="s">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5028,22 +5028,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="356" t="s">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="356" t="s">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5080,13 +5080,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="356" t="s">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5099,13 +5099,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="356" t="s">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5227,13 +5227,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="356" t="s">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5272,13 +5272,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="357" t="s">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5421,13 +5421,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="361" t="s">
+      <c r="B134" s="362" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5440,22 +5440,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="359" t="s">
+      <c r="B138" s="363" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="356" t="s">
+      <c r="B139" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5788,13 +5788,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="363" t="s">
+      <c r="B179" s="357" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5831,13 +5831,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="357" t="s">
+      <c r="B188" s="359" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5845,22 +5845,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="362" t="s">
+      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="362" t="s">
+      <c r="B192" s="356" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5884,17 +5884,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5911,6 +5900,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13408,24 +13408,24 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.6158192090395481E-2</v>
+        <v>3.5754189944134075E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.6158192090395481E-2</v>
+        <v>3.5754189944134075E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>4.3220338983050846E-2</v>
+        <v>4.2737430167597762E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>5.254237288135593E-2</v>
+        <v>5.1955307262569833E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>4.1807909604519772E-2</v>
+        <v>4.1340782122905026E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
@@ -14607,46 +14607,46 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.0215406046238558E-2</v>
+        <v>7.9319144526168853E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.11266379516075237</v>
+        <v>0.11140498180700094</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.14459949158963895</v>
+        <v>0.14298385481210107</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.15590047482418898</v>
+        <v>0.15415857007754999</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.10743788015625409</v>
+        <v>0.10623745691428477</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>6.5526806927521081E-2</v>
+        <v>6.4794663833358829E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>6.0018613683538481E-2</v>
+        <v>5.9348014647968218E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>5.6327550379562774E-2</v>
+        <v>5.5698192274763185E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>-3.8423458922825053E-3</v>
+        <v>-3.7994146532625891E-3</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>-3.265733176391325E-2</v>
+        <v>-3.2292445375489635E-2</v>
       </c>
       <c r="P125" s="77" t="str">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
@@ -14664,39 +14664,39 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14557326457184361</v>
+        <v>0.14394674764925317</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.17129362309109897</v>
+        <v>0.16937972786103084</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.21039060832661557</v>
+        <v>0.20803987527268691</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13483509893593687</v>
+        <v>0.13332856151765823</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.7446230055547873E-2</v>
+        <v>5.6804372736491471E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.0011100411040093E-2</v>
+        <v>7.9117121635497736E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.0385539307768789E-2</v>
+        <v>7.9487376857402647E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.3302521991358404E-3</v>
+        <v>9.2260035712125356E-3</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-9.1343383491446686E-3</v>
+        <v>-9.0322787027855098E-3</v>
       </c>
       <c r="P126" s="23" t="str">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18650,7 +18650,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-3.54</v>
+        <v>-3.58</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18890,7 +18890,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>3.54</v>
+        <v>3.58</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19488,7 +19488,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>3.54</v>
+        <v>3.58</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19501,7 +19501,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.17056423895080175</v>
+        <v>0.166056434583427</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0398.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0398.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F50B650-881D-4B49-92F8-BF6DDACE45E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C06DC33C-CA32-4D3D-B12E-A86BAF39BDC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3891,29 +3891,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4331,7 +4331,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>3.58</v>
+        <v>3.59</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>1744.7424419200001</v>
+        <v>1749.6160241599998</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4389,13 +4389,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.166056434583427</v>
+        <v>0.16494017618254819</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4595,22 +4595,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4622,13 +4622,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4648,13 +4648,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4683,13 +4683,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4705,13 +4705,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4775,13 +4775,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4797,7 +4797,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4819,22 +4819,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>7.9319144526168853E-2</v>
+        <v>7.9098199833895419E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4878,7 +4878,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.5754189944134075E-2</v>
+        <v>3.5654596100278553E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>447</v>
@@ -4969,22 +4969,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5028,22 +5028,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5080,13 +5080,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5099,13 +5099,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5227,13 +5227,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5272,13 +5272,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5421,13 +5421,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5440,22 +5440,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5788,13 +5788,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5831,13 +5831,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5845,22 +5845,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="356" t="s">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5884,6 +5884,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5900,17 +5911,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13408,24 +13408,24 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.5754189944134075E-2</v>
+        <v>3.5654596100278553E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.5754189944134075E-2</v>
+        <v>3.5654596100278553E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>4.2737430167597762E-2</v>
+        <v>4.2618384401114207E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>5.1955307262569833E-2</v>
+        <v>5.1810584958217269E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>4.1340782122905026E-2</v>
+        <v>4.1225626740947076E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
@@ -14607,46 +14607,46 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.9319144526168853E-2</v>
+        <v>7.9098199833895419E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.11140498180700094</v>
+        <v>0.11109466152341599</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.14298385481210107</v>
+        <v>0.14258557109396153</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.15415857007754999</v>
+        <v>0.15372915901883816</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.10623745691428477</v>
+        <v>0.10594153085045668</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>6.4794663833358829E-2</v>
+        <v>6.461417730457511E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>5.9348014647968218E-2</v>
+        <v>5.9182699843934879E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>5.5698192274763185E-2</v>
+        <v>5.5543044106866911E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>-3.7994146532625891E-3</v>
+        <v>-3.7888313255376241E-3</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>-3.2292445375489635E-2</v>
+        <v>-3.2202494274165154E-2</v>
       </c>
       <c r="P125" s="77" t="str">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
@@ -14664,39 +14664,39 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14394674764925317</v>
+        <v>0.14354578177836391</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16937972786103084</v>
+        <v>0.16890791803411989</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.20803987527268691</v>
+        <v>0.20746037701287443</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13332856151765823</v>
+        <v>0.13295717276691268</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.6804372736491471E-2</v>
+        <v>5.6646143285971999E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9117121635497736E-2</v>
+        <v>7.8896739681081324E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9487376857402647E-2</v>
+        <v>7.9265963551393176E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.2260035712125356E-3</v>
+        <v>9.2003043969194655E-3</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-9.0322787027855098E-3</v>
+        <v>-9.0071191520813727E-3</v>
       </c>
       <c r="P126" s="23" t="str">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18650,7 +18650,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-3.58</v>
+        <v>-3.59</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18890,7 +18890,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>3.58</v>
+        <v>3.59</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19488,7 +19488,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>3.58</v>
+        <v>3.59</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19501,7 +19501,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.166056434583427</v>
+        <v>0.16494017618254819</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0398.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0398.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C06DC33C-CA32-4D3D-B12E-A86BAF39BDC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{296C5191-FD67-4559-AA13-2D4808DCE6DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3891,29 +3891,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4331,7 +4331,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>3.59</v>
+        <v>3.6</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>1749.6160241599998</v>
+        <v>1754.4896064000002</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4389,13 +4389,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="356" t="s">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.16494017618254819</v>
+        <v>0.16382813843087729</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4595,22 +4595,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="356" t="s">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="358" t="s">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4622,13 +4622,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="357" t="s">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4648,13 +4648,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="357" t="s">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4683,13 +4683,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="357" t="s">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4705,13 +4705,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="357" t="s">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4775,13 +4775,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="357" t="s">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4797,7 +4797,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="357" t="s">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4819,22 +4819,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="356" t="s">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="356" t="s">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>7.9098199833895419E-2</v>
+        <v>7.8878482612134579E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4878,7 +4878,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.5654596100278553E-2</v>
+        <v>3.5555555555555556E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>447</v>
@@ -4969,22 +4969,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="358" t="s">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5028,22 +5028,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="356" t="s">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="356" t="s">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5080,13 +5080,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="356" t="s">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5099,13 +5099,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="356" t="s">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5227,13 +5227,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="356" t="s">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5272,13 +5272,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="357" t="s">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5421,13 +5421,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="361" t="s">
+      <c r="B134" s="362" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5440,22 +5440,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="359" t="s">
+      <c r="B138" s="363" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="356" t="s">
+      <c r="B139" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5788,13 +5788,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="363" t="s">
+      <c r="B179" s="357" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5831,13 +5831,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="357" t="s">
+      <c r="B188" s="359" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5845,22 +5845,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="362" t="s">
+      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="362" t="s">
+      <c r="B192" s="356" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5884,17 +5884,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5911,6 +5900,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13408,24 +13408,24 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.5654596100278553E-2</v>
+        <v>3.5555555555555556E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.5654596100278553E-2</v>
+        <v>3.5555555555555556E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>4.2618384401114207E-2</v>
+        <v>4.2499999999999996E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>5.1810584958217269E-2</v>
+        <v>5.1666666666666666E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>4.1225626740947076E-2</v>
+        <v>4.1111111111111105E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
@@ -14607,46 +14607,46 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.9098199833895419E-2</v>
+        <v>7.8878482612134579E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.11109466152341599</v>
+        <v>0.1107860652414065</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.14258557109396153</v>
+        <v>0.14218950006314496</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.15372915901883816</v>
+        <v>0.15330213357711917</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.10594153085045668</v>
+        <v>0.10564724882031652</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>6.461417730457511E-2</v>
+        <v>6.4434693478729058E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>5.9182699843934879E-2</v>
+        <v>5.9018303455479502E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>5.5543044106866911E-2</v>
+        <v>5.5388757873236723E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>-3.7888313255376241E-3</v>
+        <v>-3.7783067940777969E-3</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>-3.2202494274165154E-2</v>
+        <v>-3.211304290118136E-2</v>
       </c>
       <c r="P125" s="77" t="str">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
@@ -14664,39 +14664,39 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14354578177836391</v>
+        <v>0.14314704349564619</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16890791803411989</v>
+        <v>0.16843872937291399</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.20746037701287443</v>
+        <v>0.20688409818783865</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.13295717276691268</v>
+        <v>0.1325878472870046</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.6646143285971999E-2</v>
+        <v>5.6488792887955407E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8896739681081324E-2</v>
+        <v>7.8677582070856081E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9265963551393176E-2</v>
+        <v>7.9045780319305967E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.2003043969194655E-3</v>
+        <v>9.1747479958169103E-3</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-9.0071191520813727E-3</v>
+        <v>-8.9820993766589231E-3</v>
       </c>
       <c r="P126" s="23" t="str">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18650,7 +18650,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-3.59</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18890,7 +18890,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>3.59</v>
+        <v>3.6</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19488,7 +19488,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>3.59</v>
+        <v>3.6</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19501,7 +19501,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.16494017618254819</v>
+        <v>0.16382813843087729</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0398.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0398.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{296C5191-FD67-4559-AA13-2D4808DCE6DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D50B1B61-D324-4F09-B94B-1A1A9DED6DF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3891,29 +3891,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4389,13 +4389,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4595,22 +4595,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4622,13 +4622,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4648,13 +4648,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4683,13 +4683,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4705,13 +4705,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4775,13 +4775,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4797,7 +4797,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4819,22 +4819,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4969,22 +4969,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5028,22 +5028,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5080,13 +5080,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5099,13 +5099,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5227,13 +5227,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5272,13 +5272,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5421,13 +5421,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5440,22 +5440,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5788,13 +5788,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5831,13 +5831,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5845,22 +5845,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="356" t="s">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5884,6 +5884,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5900,17 +5911,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">

--- a/financial_models/opportunities/0398.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0398.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D50B1B61-D324-4F09-B94B-1A1A9DED6DF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09E233BF-4E58-4716-AD89-CC84AF81EF44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3891,29 +3891,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4331,7 +4331,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>3.6</v>
+        <v>3.63</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>1754.4896064000002</v>
+        <v>1769.1103531199999</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4389,13 +4389,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="356" t="s">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.16382813843087729</v>
+        <v>0.16051707285873706</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4595,22 +4595,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="356" t="s">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="358" t="s">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4622,13 +4622,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="357" t="s">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4648,13 +4648,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="357" t="s">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4683,13 +4683,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="357" t="s">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4705,13 +4705,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="357" t="s">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4775,13 +4775,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="357" t="s">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4797,7 +4797,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="357" t="s">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4819,22 +4819,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="356" t="s">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="356" t="s">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>7.8878482612134579E-2</v>
+        <v>7.8226594326083893E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4878,7 +4878,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.5555555555555556E-2</v>
+        <v>3.526170798898072E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>447</v>
@@ -4969,22 +4969,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="358" t="s">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5028,22 +5028,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="356" t="s">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="356" t="s">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5080,13 +5080,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="356" t="s">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5099,13 +5099,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="356" t="s">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5227,13 +5227,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="356" t="s">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5272,13 +5272,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="357" t="s">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5421,13 +5421,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="361" t="s">
+      <c r="B134" s="362" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5440,22 +5440,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="359" t="s">
+      <c r="B138" s="363" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="356" t="s">
+      <c r="B139" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5788,13 +5788,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="363" t="s">
+      <c r="B179" s="357" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5831,13 +5831,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="357" t="s">
+      <c r="B188" s="359" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5845,22 +5845,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="362" t="s">
+      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="362" t="s">
+      <c r="B192" s="356" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5884,17 +5884,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5911,6 +5900,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13408,24 +13408,24 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.5555555555555556E-2</v>
+        <v>3.526170798898072E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.5555555555555556E-2</v>
+        <v>3.526170798898072E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>4.2499999999999996E-2</v>
+        <v>4.2148760330578509E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>5.1666666666666666E-2</v>
+        <v>5.1239669421487603E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>4.1111111111111105E-2</v>
+        <v>4.077134986225895E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
@@ -14607,46 +14607,46 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.8878482612134579E-2</v>
+        <v>7.8226594326083893E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.1107860652414065</v>
+        <v>0.10987047792536181</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.14218950006314496</v>
+        <v>0.14101438022791238</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.15330213357711917</v>
+        <v>0.15203517379549009</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.10564724882031652</v>
+        <v>0.10477413106147093</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>6.4434693478729058E-2</v>
+        <v>6.3902175350805682E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>5.9018303455479502E-2</v>
+        <v>5.8530548881467276E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>5.5388757873236723E-2</v>
+        <v>5.4930999543705845E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>-3.7783067940777969E-3</v>
+        <v>-3.747081118093683E-3</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>-3.211304290118136E-2</v>
+        <v>-3.1847645852411267E-2</v>
       </c>
       <c r="P125" s="77" t="str">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
@@ -14664,39 +14664,39 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14314704349564619</v>
+        <v>0.14196401007832682</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.16843872937291399</v>
+        <v>0.16704667375826182</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.20688409818783865</v>
+        <v>0.20517431225240199</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1325878472870046</v>
+        <v>0.13149207995405415</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.6488792887955407E-2</v>
+        <v>5.6021943359955778E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8677582070856081E-2</v>
+        <v>7.8027354119857284E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9045780319305967E-2</v>
+        <v>7.839250940757618E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.1747479958169103E-3</v>
+        <v>9.0989236322151189E-3</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-8.9820993766589231E-3</v>
+        <v>-8.9078671504055438E-3</v>
       </c>
       <c r="P126" s="23" t="str">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18650,7 +18650,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-3.6</v>
+        <v>-3.63</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18890,7 +18890,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>3.6</v>
+        <v>3.63</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19488,7 +19488,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>3.6</v>
+        <v>3.63</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19501,7 +19501,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.16382813843087729</v>
+        <v>0.16051707285873706</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0398.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0398.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09E233BF-4E58-4716-AD89-CC84AF81EF44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{287BA7E2-D75C-4A41-80C3-435A25D5A639}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -25,6 +25,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DDM!$B$68:$H$68</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
+    <definedName name="dividend_tax_rate">Normalized_FCF!$C$93</definedName>
     <definedName name="Equity_Cost">Thesis!$C$86</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="465">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -465,10 +466,6 @@
   <si>
     <t>PV of FCFE</t>
     <phoneticPr fontId="28" type="noConversion"/>
-  </si>
-  <si>
-    <t>Annual Dividend per share</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>HGP</t>
@@ -1497,14 +1494,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Dividend/Market Cap =</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dividend Yield</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Note of the formulas:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2445,6 +2434,18 @@
     <t>LT AR and Prepayments</t>
   </si>
   <si>
+    <t>Dividend after tax Yield</t>
+  </si>
+  <si>
+    <t>Dividend tax rate</t>
+  </si>
+  <si>
+    <t>After tax Dividend/Market Cap =</t>
+  </si>
+  <si>
+    <t>After-tax Dividend per share</t>
+  </si>
+  <si>
     <t>Y</t>
   </si>
   <si>
@@ -2467,9 +2468,6 @@
   </si>
   <si>
     <t>Latest Asset Value</t>
-  </si>
-  <si>
-    <t>Notes</t>
   </si>
   <si>
     <t>Historical Average or D&amp;A</t>
@@ -3146,7 +3144,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="368">
+  <cellXfs count="370">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3891,6 +3889,10 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4220,10 +4222,10 @@
   <dimension ref="A1:J197"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="25.6640625" style="1" customWidth="1"/>
-    <col min="5" max="6" width="15.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.73046875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.73046875" style="1" customWidth="1"/>
+    <col min="5" max="6" width="15.73046875" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -4235,18 +4237,18 @@
         <v>45786</v>
       </c>
       <c r="D1" s="316" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="E1" s="292" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="F1" s="254" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="222" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -4260,7 +4262,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4269,10 +4271,10 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C5" s="294" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4286,7 +4288,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C7" s="250">
         <v>6</v>
@@ -4296,7 +4298,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="B8" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C8" s="33">
         <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
@@ -4309,20 +4311,20 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4338,17 +4340,17 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
@@ -4362,7 +4364,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
@@ -4388,35 +4390,35 @@
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="358" t="s">
-        <v>359</v>
-      </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+    <row r="18" spans="2:6" ht="24.6" customHeight="1">
+      <c r="B18" s="360" t="s">
+        <v>356</v>
+      </c>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
         <v xml:space="preserve">Low Growth </v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="E21" s="308" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="22" spans="2:6">
@@ -4424,7 +4426,7 @@
         <v>56</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D22" s="1" t="str">
         <f>IF(valuation_method="DDM","DDM Terminal Value","")</f>
@@ -4434,26 +4436,26 @@
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C23" s="262" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C24" s="262" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C25" s="48" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="D25" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
@@ -4474,7 +4476,7 @@
         <v>5.2246962590200807</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
@@ -4487,7 +4489,7 @@
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="C28" s="309" t="str">
         <f>C145&amp;" ("&amp;Market_currency&amp;")"</f>
@@ -4498,7 +4500,7 @@
         <v/>
       </c>
       <c r="E28" s="305" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="F28" s="303">
         <v>3</v>
@@ -4506,7 +4508,7 @@
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C29" s="310">
         <f>C149</f>
@@ -4517,7 +4519,7 @@
         <v/>
       </c>
       <c r="E29" s="306" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="F29" s="302">
         <v>0.3674</v>
@@ -4525,7 +4527,7 @@
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="C30" s="311">
         <f>C157</f>
@@ -4536,7 +4538,7 @@
         <v/>
       </c>
       <c r="E30" s="307" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="F30" s="312">
         <v>0.21740000000000001</v>
@@ -4544,7 +4546,7 @@
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C31" s="311">
         <f>C165</f>
@@ -4555,7 +4557,7 @@
         <v/>
       </c>
       <c r="E31" s="307" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="F31" s="312">
         <v>7.4999999999999997E-2</v>
@@ -4563,7 +4565,7 @@
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="C32" s="311">
         <f>C173</f>
@@ -4574,7 +4576,7 @@
         <v/>
       </c>
       <c r="E32" s="307" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="F32" s="312">
         <v>0.1174</v>
@@ -4586,7 +4588,7 @@
     </row>
     <row r="34" spans="1:6" ht="13.9">
       <c r="A34" s="222" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B34" s="36"/>
       <c r="C34" s="36"/>
@@ -4594,45 +4596,45 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="358" t="s">
-        <v>360</v>
-      </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
-    </row>
-    <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="361" t="s">
-        <v>339</v>
-      </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+    <row r="36" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B36" s="360" t="s">
+        <v>357</v>
+      </c>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B37" s="363" t="s">
+        <v>336</v>
+      </c>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C39" s="108">
         <f>scaling_factor</f>
         <v>1000</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="359" t="s">
-        <v>231</v>
-      </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+    <row r="40" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B40" s="361" t="s">
+        <v>230</v>
+      </c>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C41" s="349">
         <f>Normalized_FCF!C8</f>
@@ -4647,18 +4649,18 @@
       <c r="B42" s="47"/>
       <c r="C42" s="76"/>
     </row>
-    <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="359" t="s">
-        <v>233</v>
-      </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+    <row r="43" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B43" s="361" t="s">
+        <v>232</v>
+      </c>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C44" s="349">
         <f>Normalized_FCF!C9</f>
@@ -4671,7 +4673,7 @@
     </row>
     <row r="45" spans="1:6">
       <c r="B45" s="52" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C45" s="349">
         <f>Normalized_FCF!C10</f>
@@ -4683,17 +4685,17 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
-        <v>236</v>
-      </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="B47" s="361" t="s">
+        <v>235</v>
+      </c>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C48" s="349">
         <f>Normalized_FCF!C11</f>
@@ -4705,17 +4707,17 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
-        <v>240</v>
-      </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="B50" s="361" t="s">
+        <v>239</v>
+      </c>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C51" s="350">
         <f>Normalized_FCF!C48</f>
@@ -4730,7 +4732,7 @@
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C52" s="350">
         <f>Normalized_FCF!C47</f>
@@ -4745,7 +4747,7 @@
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C53" s="349">
         <f>Normalized_FCF!C12</f>
@@ -4758,12 +4760,12 @@
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C56" s="349">
         <f>Normalized_FCF!C15</f>
@@ -4775,17 +4777,17 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
-        <v>241</v>
-      </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="B58" s="361" t="s">
+        <v>240</v>
+      </c>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C59" s="349">
         <f>Normalized_FCF!C14</f>
@@ -4797,17 +4799,17 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
-        <v>338</v>
-      </c>
-      <c r="C61" s="360"/>
-      <c r="D61" s="360"/>
-      <c r="E61" s="360"/>
-      <c r="F61" s="360"/>
+      <c r="B61" s="361" t="s">
+        <v>335</v>
+      </c>
+      <c r="C61" s="362"/>
+      <c r="D61" s="362"/>
+      <c r="E61" s="362"/>
+      <c r="F61" s="362"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C62" s="349">
         <f>Normalized_FCF!C17</f>
@@ -4818,27 +4820,27 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="358" t="s">
-        <v>343</v>
-      </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
-    </row>
-    <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="358" t="s">
-        <v>361</v>
-      </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+    <row r="64" spans="2:6" ht="24.6" customHeight="1">
+      <c r="B64" s="360" t="s">
+        <v>340</v>
+      </c>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B65" s="360" t="s">
+        <v>358</v>
+      </c>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C67" s="349">
         <f>Normalized_FCF!G19</f>
@@ -4851,7 +4853,7 @@
     </row>
     <row r="68" spans="1:6">
       <c r="B68" s="47" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C68" s="349">
         <f>Normalized_FCF!C19</f>
@@ -4864,24 +4866,24 @@
     </row>
     <row r="69" spans="1:6">
       <c r="B69" s="227" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="C69" s="92">
-        <f>Normalized_FCF!C125</f>
+        <f>Normalized_FCF!C126</f>
         <v>7.8226594326083893E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
     <row r="70" spans="1:6">
       <c r="B70" s="227" t="s">
-        <v>308</v>
+        <v>454</v>
       </c>
       <c r="C70" s="92">
-        <f>Normalized_FCF!C93</f>
+        <f>Normalized_FCF!C94</f>
         <v>3.526170798898072E-2</v>
       </c>
       <c r="E70" s="47" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
@@ -4890,73 +4892,73 @@
     </row>
     <row r="72" spans="1:6">
       <c r="B72" s="210" t="s">
+        <v>447</v>
+      </c>
+      <c r="C72" s="323" t="s">
+        <v>449</v>
+      </c>
+      <c r="D72" s="323" t="s">
         <v>450</v>
-      </c>
-      <c r="C72" s="323" t="s">
-        <v>452</v>
-      </c>
-      <c r="D72" s="323" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="B73" s="47" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C73" s="92">
-        <f>Normalized_FCF!C120</f>
+        <f>Normalized_FCF!C121</f>
         <v>0.10112859174992994</v>
       </c>
       <c r="D73" s="92">
-        <f>Normalized_FCF!G120</f>
+        <f>Normalized_FCF!G121</f>
         <v>0.18576712671946713</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="B74" s="259" t="str">
-        <f>Normalized_FCF!B117</f>
+        <f>Normalized_FCF!B118</f>
         <v>Pre-tax Profit/Sales</v>
       </c>
       <c r="C74" s="322">
-        <f>Normalized_FCF!C117</f>
+        <f>Normalized_FCF!C118</f>
         <v>5.8835781303360896E-2</v>
       </c>
       <c r="D74" s="322">
-        <f>Normalized_FCF!G117</f>
+        <f>Normalized_FCF!G118</f>
         <v>9.3537135473147709E-2</v>
       </c>
     </row>
     <row r="75" spans="1:6">
       <c r="B75" s="259" t="str">
-        <f>Normalized_FCF!B118</f>
+        <f>Normalized_FCF!B119</f>
         <v>Sales/Total Assets</v>
       </c>
       <c r="C75" s="324">
-        <f>Normalized_FCF!C118</f>
+        <f>Normalized_FCF!C119</f>
         <v>1.2277297326073906</v>
       </c>
       <c r="D75" s="324">
-        <f>Normalized_FCF!G118</f>
+        <f>Normalized_FCF!G119</f>
         <v>1.4185842608933972</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="259" t="str">
-        <f>Normalized_FCF!B119</f>
+        <f>Normalized_FCF!B120</f>
         <v>Total Assets/Equity</v>
       </c>
       <c r="C76" s="324">
-        <f>Normalized_FCF!C119</f>
+        <f>Normalized_FCF!C120</f>
         <v>1.4000052396569989</v>
       </c>
       <c r="D76" s="324">
-        <f>Normalized_FCF!G119</f>
+        <f>Normalized_FCF!G120</f>
         <v>1.4000052396569989</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="13.9">
       <c r="A78" s="222" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B78" s="36"/>
       <c r="C78" s="36"/>
@@ -4967,33 +4969,33 @@
     <row r="79" spans="1:6">
       <c r="A79" s="209"/>
     </row>
-    <row r="80" spans="1:6" ht="24.5" customHeight="1">
+    <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
-        <v>362</v>
-      </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="B80" s="360" t="s">
+        <v>359</v>
+      </c>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
-        <v>252</v>
-      </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="B81" s="363" t="s">
+        <v>251</v>
+      </c>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="B84" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C84" s="92">
         <f>F31</f>
@@ -5002,7 +5004,7 @@
     </row>
     <row r="85" spans="1:6">
       <c r="B85" s="1" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C85" s="92">
         <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
@@ -5011,7 +5013,7 @@
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="80" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C86" s="236">
         <f>F31+C85</f>
@@ -5023,31 +5025,31 @@
     </row>
     <row r="88" spans="1:6">
       <c r="B88" s="293" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C88" s="121"/>
     </row>
-    <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="358" t="s">
-        <v>363</v>
-      </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
-    </row>
-    <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="358" t="s">
-        <v>364</v>
-      </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+    <row r="89" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B89" s="360" t="s">
+        <v>360</v>
+      </c>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
+    </row>
+    <row r="90" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B90" s="360" t="s">
+        <v>361</v>
+      </c>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C92" s="236">
         <v>0</v>
@@ -5055,7 +5057,7 @@
     </row>
     <row r="93" spans="1:6">
       <c r="B93" s="47" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5068,7 +5070,7 @@
     </row>
     <row r="95" spans="1:6" ht="13.9">
       <c r="A95" s="222" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B95" s="36"/>
       <c r="C95" s="36"/>
@@ -5080,36 +5082,36 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
-        <v>365</v>
-      </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="B97" s="360" t="s">
+        <v>362</v>
+      </c>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="210" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="358" t="s">
-        <v>344</v>
-      </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+        <v>229</v>
+      </c>
+    </row>
+    <row r="101" spans="2:6" ht="24.6" customHeight="1">
+      <c r="B101" s="360" t="s">
+        <v>341</v>
+      </c>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C102" s="349">
         <f>DCF!C7</f>
@@ -5122,7 +5124,7 @@
     </row>
     <row r="103" spans="2:6">
       <c r="B103" s="47" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5135,7 +5137,7 @@
     </row>
     <row r="104" spans="2:6">
       <c r="B104" s="296" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C104" s="325">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
@@ -5144,7 +5146,7 @@
     </row>
     <row r="105" spans="2:6">
       <c r="B105" s="296" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C105" s="326">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
@@ -5153,12 +5155,12 @@
     </row>
     <row r="107" spans="2:6">
       <c r="B107" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C108" s="349">
         <f>BS!C66</f>
@@ -5171,7 +5173,7 @@
     </row>
     <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
@@ -5184,7 +5186,7 @@
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="47" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5197,12 +5199,12 @@
     </row>
     <row r="112" spans="2:6">
       <c r="B112" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C113" s="349">
         <f>DCF!C9</f>
@@ -5215,7 +5217,7 @@
     </row>
     <row r="114" spans="1:6">
       <c r="B114" s="47" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5226,18 +5228,18 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="358" t="s">
-        <v>366</v>
-      </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+    <row r="116" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B116" s="360" t="s">
+        <v>363</v>
+      </c>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
@@ -5250,7 +5252,7 @@
     </row>
     <row r="119" spans="1:6">
       <c r="B119" s="296" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
@@ -5263,7 +5265,7 @@
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="222" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B121" s="36"/>
       <c r="C121" s="36"/>
@@ -5271,30 +5273,30 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="359" t="s">
-        <v>367</v>
-      </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+    <row r="123" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B123" s="361" t="s">
+        <v>364</v>
+      </c>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C125" s="233" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D125" s="233" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E125" s="233" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F125" s="233" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -5409,7 +5411,7 @@
     </row>
     <row r="132" spans="1:6">
       <c r="B132" s="211" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
@@ -5420,18 +5422,18 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
-        <v>370</v>
-      </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+    <row r="134" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B134" s="364" t="s">
+        <v>367</v>
+      </c>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B136" s="36"/>
       <c r="C136" s="36"/>
@@ -5440,31 +5442,31 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
-        <v>368</v>
-      </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
-    </row>
-    <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="358" t="s">
-        <v>369</v>
-      </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="B138" s="365" t="s">
+        <v>365</v>
+      </c>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
+    </row>
+    <row r="139" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B139" s="360" t="s">
+        <v>366</v>
+      </c>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C141" s="225">
         <f>F28</f>
@@ -5473,7 +5475,7 @@
     </row>
     <row r="142" spans="1:6">
       <c r="B142" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C142" s="224">
         <f>F29</f>
@@ -5482,7 +5484,7 @@
     </row>
     <row r="143" spans="1:6">
       <c r="B143" s="212" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
@@ -5495,7 +5497,7 @@
     </row>
     <row r="145" spans="2:4">
       <c r="B145" s="210" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C145" s="241" t="str">
         <f>C11</f>
@@ -5508,7 +5510,7 @@
     </row>
     <row r="146" spans="2:4">
       <c r="B146" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C146" s="297">
         <f>F29</f>
@@ -5537,7 +5539,7 @@
     </row>
     <row r="149" spans="2:4">
       <c r="B149" s="80" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
@@ -5550,7 +5552,7 @@
     </row>
     <row r="150" spans="2:4">
       <c r="B150" s="259" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C150" s="298" t="str">
         <f>Market_currency</f>
@@ -5563,7 +5565,7 @@
     </row>
     <row r="151" spans="2:4">
       <c r="B151" s="214" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
@@ -5572,12 +5574,12 @@
     </row>
     <row r="153" spans="2:4">
       <c r="B153" s="210" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="154" spans="2:4">
       <c r="B154" s="1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C154" s="297">
         <f>Scenarios!C90</f>
@@ -5606,7 +5608,7 @@
     </row>
     <row r="157" spans="2:4">
       <c r="B157" s="80" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
@@ -5619,7 +5621,7 @@
     </row>
     <row r="158" spans="2:4">
       <c r="B158" s="259" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C158" s="298" t="str">
         <f>Market_currency</f>
@@ -5632,7 +5634,7 @@
     </row>
     <row r="159" spans="2:4">
       <c r="B159" s="214" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
@@ -5641,12 +5643,12 @@
     </row>
     <row r="161" spans="2:4">
       <c r="B161" s="210" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="162" spans="2:4">
       <c r="B162" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C162" s="92">
         <f>Scenarios!C96</f>
@@ -5675,7 +5677,7 @@
     </row>
     <row r="165" spans="2:4">
       <c r="B165" s="80" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
@@ -5688,7 +5690,7 @@
     </row>
     <row r="166" spans="2:4">
       <c r="B166" s="259" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C166" s="298" t="str">
         <f>Market_currency</f>
@@ -5701,7 +5703,7 @@
     </row>
     <row r="167" spans="2:4">
       <c r="B167" s="214" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
@@ -5710,12 +5712,12 @@
     </row>
     <row r="169" spans="2:4">
       <c r="B169" s="210" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
     </row>
     <row r="170" spans="2:4">
       <c r="B170" s="1" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="C170" s="92">
         <f>F32</f>
@@ -5744,7 +5746,7 @@
     </row>
     <row r="173" spans="2:4">
       <c r="B173" s="80" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
@@ -5757,7 +5759,7 @@
     </row>
     <row r="174" spans="2:4">
       <c r="B174" s="259" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C174" s="298" t="str">
         <f>Market_currency</f>
@@ -5770,7 +5772,7 @@
     </row>
     <row r="175" spans="2:4">
       <c r="B175" s="214" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
@@ -5779,7 +5781,7 @@
     </row>
     <row r="177" spans="1:6" ht="13.9">
       <c r="A177" s="222" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B177" s="36"/>
       <c r="C177" s="36"/>
@@ -5788,98 +5790,98 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
-        <v>376</v>
-      </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="B179" s="359" t="s">
+        <v>373</v>
+      </c>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="360" t="s">
-        <v>380</v>
-      </c>
-      <c r="C182" s="360"/>
-      <c r="D182" s="360"/>
-      <c r="E182" s="360"/>
-      <c r="F182" s="360"/>
+      <c r="B182" s="362" t="s">
+        <v>377</v>
+      </c>
+      <c r="C182" s="362"/>
+      <c r="D182" s="362"/>
+      <c r="E182" s="362"/>
+      <c r="F182" s="362"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
     </row>
     <row r="184" spans="1:6">
       <c r="B184" s="214" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="185" spans="1:6">
       <c r="B185" s="214" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="187" spans="1:6">
       <c r="B187" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
-        <v>381</v>
-      </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="B188" s="361" t="s">
+        <v>378</v>
+      </c>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
-    </row>
-    <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="356" t="s">
-        <v>383</v>
-      </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+    </row>
+    <row r="191" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B191" s="358" t="s">
+        <v>379</v>
+      </c>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
+    </row>
+    <row r="192" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B192" s="358" t="s">
+        <v>380</v>
+      </c>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="195" spans="2:2">
       <c r="B195" s="214" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="196" spans="2:2">
       <c r="B196" s="214" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="197" spans="2:2">
       <c r="B197" s="214" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
   </sheetData>
@@ -5917,7 +5919,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{45F807FD-9E0F-415A-9BBD-D5FB6470B56D}">
       <formula1>"Y, N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C23:C25" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C23:C24" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="C25:D25" xr:uid="{00000000-0002-0000-0000-000001000000}">
@@ -5941,12 +5943,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
-    <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
-    <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.796875" style="1"/>
+    <col min="2" max="2" width="27.265625" style="1" customWidth="1"/>
+    <col min="3" max="13" width="20.73046875" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.86328125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:13">
@@ -6176,7 +6178,7 @@
     </row>
     <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C9" s="351"/>
       <c r="D9" s="351"/>
@@ -6192,7 +6194,7 @@
     </row>
     <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C10" s="351"/>
       <c r="D10" s="351"/>
@@ -6208,7 +6210,7 @@
     </row>
     <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C11" s="351"/>
       <c r="D11" s="351"/>
@@ -6430,7 +6432,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C22" s="351">
         <v>346987</v>
@@ -6464,7 +6466,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C23" s="351">
         <v>-67837</v>
@@ -6498,7 +6500,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C24" s="351">
         <v>-423459</v>
@@ -6564,7 +6566,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -6709,7 +6711,7 @@
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C32" s="333">
         <f>BS!G28</f>
@@ -7108,7 +7110,7 @@
     </row>
     <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C43" s="334">
         <f>IF(C$4="","",C38+C39+C42)</f>
@@ -7157,7 +7159,7 @@
     </row>
     <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C44" s="354">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
@@ -7505,12 +7507,12 @@
     </row>
     <row r="54" spans="2:13">
       <c r="B54" s="174" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C55" s="349">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
@@ -7559,7 +7561,7 @@
     </row>
     <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C56" s="349">
         <f t="shared" ref="C56:M56" si="26">IF(C$4="","",C10)</f>
@@ -7608,7 +7610,7 @@
     </row>
     <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C57" s="349">
         <f t="shared" ref="C57:M57" si="27">IF(C$4="","",C11)</f>
@@ -7657,7 +7659,7 @@
     </row>
     <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C58" s="349">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
@@ -7859,7 +7861,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C64" s="333">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8111,7 +8113,7 @@
     </row>
     <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C71" s="101">
         <f>IF(D$36="","",C44/D44-1)</f>
@@ -8139,7 +8141,7 @@
       </c>
       <c r="I71" s="101">
         <f t="shared" si="37"/>
-        <v>0.82636627651148475</v>
+        <v>0.82636627651148453</v>
       </c>
       <c r="J71" s="101">
         <f t="shared" si="37"/>
@@ -8477,15 +8479,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.265625" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="18.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="25.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="18.6640625" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="12.33203125" style="1"/>
+    <col min="3" max="4" width="18.73046875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.73046875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="18.73046875" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="12.265625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="15" customHeight="1">
@@ -8506,7 +8508,7 @@
     </row>
     <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -8517,19 +8519,19 @@
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C3" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D3" s="183" t="s">
         <v>35</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G3" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H3" s="183" t="s">
         <v>35</v>
@@ -8590,7 +8592,7 @@
       </c>
       <c r="E6" s="25"/>
       <c r="F6" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G6" s="19">
         <v>0</v>
@@ -8611,7 +8613,7 @@
       </c>
       <c r="E7" s="25"/>
       <c r="F7" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G7" s="19">
         <v>10851</v>
@@ -8622,7 +8624,7 @@
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C8" s="19">
         <v>0</v>
@@ -8632,7 +8634,7 @@
       </c>
       <c r="E8" s="25"/>
       <c r="F8" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G8" s="19">
         <v>0</v>
@@ -8653,7 +8655,7 @@
       </c>
       <c r="E9" s="25"/>
       <c r="F9" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G9" s="19">
         <v>0</v>
@@ -8717,19 +8719,19 @@
     </row>
     <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C14" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D14" s="183" t="s">
         <v>35</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G14" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H14" s="183" t="s">
         <v>35</v>
@@ -8737,7 +8739,7 @@
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C15" s="19">
         <v>0</v>
@@ -8766,7 +8768,7 @@
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G16" s="19">
         <f>29657+19498</f>
@@ -8787,7 +8789,7 @@
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G17" s="19">
         <v>0</v>
@@ -8798,7 +8800,7 @@
     </row>
     <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C18" s="19">
         <v>0</v>
@@ -8807,7 +8809,7 @@
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G18" s="19">
         <v>0</v>
@@ -8828,7 +8830,7 @@
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G19" s="19">
         <f>64831+22181</f>
@@ -8849,7 +8851,7 @@
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G20" s="19">
         <v>0</v>
@@ -8869,7 +8871,7 @@
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G21" s="19">
         <v>36961</v>
@@ -8928,16 +8930,16 @@
     </row>
     <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C26" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F26" s="184" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G26" s="185" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H26" s="186" t="s">
         <v>35</v>
@@ -8970,7 +8972,7 @@
         <v>112451</v>
       </c>
       <c r="F28" s="189" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G28" s="12">
         <v>1765</v>
@@ -9014,7 +9016,7 @@
     </row>
     <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C31" s="81">
         <f>SUM(C27:C30)</f>
@@ -9064,10 +9066,10 @@
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="196" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G34" s="197" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H34" s="198" t="s">
         <v>35</v>
@@ -9075,10 +9077,10 @@
     </row>
     <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C35" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F35" s="199" t="s">
         <v>31</v>
@@ -9100,7 +9102,7 @@
         <v>0</v>
       </c>
       <c r="F36" s="190" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G36" s="191">
         <f>C4+C15</f>
@@ -9116,7 +9118,7 @@
         <v>82615</v>
       </c>
       <c r="F37" s="190" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G37" s="191">
         <f>C6</f>
@@ -9132,7 +9134,7 @@
         <v>0</v>
       </c>
       <c r="F38" s="190" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G38" s="191">
         <f>C7+C17</f>
@@ -9161,14 +9163,14 @@
     </row>
     <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="80" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C40" s="81">
         <f>SUM(C36:C39)</f>
         <v>82615</v>
       </c>
       <c r="F40" s="199" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G40" s="193">
         <f>G12+G24</f>
@@ -9188,7 +9190,7 @@
         <v>26420</v>
       </c>
       <c r="F41" s="190" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G41" s="191">
         <f>C70</f>
@@ -9207,7 +9209,7 @@
         <v>109035</v>
       </c>
       <c r="F42" s="201" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G42" s="202">
         <f>C82</f>
@@ -9231,13 +9233,13 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C45" s="234" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D45" s="182" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="F45" s="256" t="s">
         <v>59</v>
@@ -9245,7 +9247,7 @@
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C46" s="76">
         <f>G29</f>
@@ -9277,7 +9279,7 @@
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="157" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C49" s="235" t="s">
         <v>57</v>
@@ -9304,7 +9306,7 @@
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C51" s="181"/>
       <c r="D51" s="92">
@@ -9318,7 +9320,7 @@
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="157" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C53" s="235" t="s">
         <v>57</v>
@@ -9330,7 +9332,7 @@
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C54" s="92">
         <f>Normalized_FCF!C8/G35</f>
@@ -9344,7 +9346,7 @@
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C55" s="92">
         <f>Normalized_FCF!C11/G40</f>
@@ -9361,7 +9363,7 @@
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="157" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C57" s="235" t="s">
         <v>57</v>
@@ -9398,10 +9400,10 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="157" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C61" s="235" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D61" s="197" t="s">
         <v>95</v>
@@ -9410,7 +9412,7 @@
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C62" s="92">
         <f>IF(G28&lt;=0,0,G28/G29)</f>
@@ -9421,12 +9423,12 @@
         <v>9.6426167603430037E-4</v>
       </c>
       <c r="F62" s="253" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="79" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C64" s="37"/>
       <c r="D64" s="37"/>
@@ -9437,13 +9439,13 @@
     </row>
     <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C65" s="234" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D65" s="183" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F65" s="256" t="s">
         <v>59</v>
@@ -9451,7 +9453,7 @@
     </row>
     <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="105" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C66" s="20">
         <f>G4+G5+G15</f>
@@ -9462,12 +9464,12 @@
         <v>587281.82009631116</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="105" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C67" s="20">
         <f>G6+G16</f>
@@ -9477,7 +9479,7 @@
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C68" s="20">
         <f>G18</f>
@@ -9487,7 +9489,7 @@
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C69" s="20">
         <f>G8+G20</f>
@@ -9497,7 +9499,7 @@
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C70" s="81">
         <f>SUM(C66:C69)</f>
@@ -9510,7 +9512,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="255" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C72" s="234" t="s">
         <v>95</v>
@@ -9522,7 +9524,7 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C73" s="349">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -9533,12 +9535,12 @@
         <v>-251053.08995184439</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="257" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C74" s="258">
         <f>-$C$66/C73</f>
@@ -9549,12 +9551,12 @@
         <v>4.3392734190563456</v>
       </c>
       <c r="F74" s="253" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C75" s="320"/>
       <c r="D75" s="321">
@@ -9562,12 +9564,12 @@
         <v>502106.17990368878</v>
       </c>
       <c r="F75" s="253" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="259" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C76" s="260"/>
       <c r="D76" s="290">
@@ -9575,7 +9577,7 @@
         <v>2</v>
       </c>
       <c r="F76" s="253" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
@@ -9583,10 +9585,10 @@
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C78" s="234" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D78" s="183" t="s">
         <v>35</v>
@@ -9595,7 +9597,7 @@
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C79" s="20">
         <f>G7+G17</f>
@@ -9609,7 +9611,7 @@
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C80" s="20">
         <f>G19</f>
@@ -9623,7 +9625,7 @@
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C81" s="20">
         <f>G9+G21</f>
@@ -9637,7 +9639,7 @@
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C82" s="81">
         <f>SUM(C79:C81)</f>
@@ -9651,7 +9653,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9662,15 +9664,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="D85" s="241" t="s">
         <v>289</v>
-      </c>
-      <c r="D85" s="241" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="238" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
@@ -9687,7 +9689,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="238" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
@@ -9704,7 +9706,7 @@
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="239" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
@@ -9721,7 +9723,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
@@ -9749,17 +9751,17 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q808"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:Q809"/>
+  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="1.265625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.265625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.73046875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="2.73046875" style="2" customWidth="1"/>
     <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
-    <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
-    <col min="18" max="16384" width="12.33203125" style="2"/>
+    <col min="6" max="6" width="2.73046875" style="2" customWidth="1"/>
+    <col min="7" max="17" width="20.73046875" style="2" customWidth="1"/>
+    <col min="18" max="16384" width="12.265625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" customHeight="1">
@@ -10081,7 +10083,7 @@
     <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C8" s="330">
         <f>C6+C7</f>
@@ -10248,7 +10250,7 @@
     <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C11" s="331">
         <f>C63</f>
@@ -10360,7 +10362,7 @@
     <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C13" s="329">
         <f>SUM(C8:C12)</f>
@@ -10470,7 +10472,7 @@
     <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C15" s="328">
         <f>-C4*C83</f>
@@ -10527,7 +10529,7 @@
     <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C16" s="332">
         <f>SUM(C13:C15)</f>
@@ -10592,7 +10594,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="267" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="335"/>
@@ -10617,7 +10619,7 @@
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="267" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="336"/>
@@ -10711,7 +10713,7 @@
     <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C21" s="54"/>
       <c r="D21" s="56"/>
@@ -10930,7 +10932,7 @@
     <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E27" s="268"/>
     </row>
@@ -10945,7 +10947,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="266" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -11005,7 +11007,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="266" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -11122,14 +11124,14 @@
     <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C33" s="340">
         <f>G33</f>
         <v>-253206</v>
       </c>
       <c r="E33" s="266" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G33" s="328">
         <f>Data!C41</f>
@@ -11187,7 +11189,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="266" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="333">
@@ -11299,7 +11301,7 @@
     <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E37" s="268"/>
     </row>
@@ -11481,21 +11483,21 @@
     <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E42" s="268"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C43" s="263">
         <v>0.25</v>
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="265" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -11549,7 +11551,7 @@
     <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C45" s="54"/>
       <c r="D45" s="56"/>
@@ -11634,7 +11636,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C48" s="328">
         <f>BS!D75*C53</f>
@@ -11689,7 +11691,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="287" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C49" s="342">
         <f>BS!$C$66*C53</f>
@@ -11805,11 +11807,11 @@
     <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E52" s="268"/>
       <c r="G52" s="97" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="53" spans="1:17" ht="15.75" customHeight="1">
@@ -11822,7 +11824,7 @@
         <v>0</v>
       </c>
       <c r="E53" s="265" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11849,7 +11851,7 @@
         <v>7.0042959818728018E-2</v>
       </c>
       <c r="E54" s="265" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11928,17 +11930,17 @@
     <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E57" s="268"/>
       <c r="G57" s="97" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C58" s="328">
         <f>BS!$C67*C66</f>
@@ -11993,7 +11995,7 @@
     <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C59" s="328">
         <f>BS!$C68*C67</f>
@@ -12048,7 +12050,7 @@
     <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C60" s="328">
         <f>BS!$C69*C68</f>
@@ -12103,7 +12105,7 @@
     <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C61" s="329">
         <f>SUM(C58:C60)</f>
@@ -12158,13 +12160,13 @@
     <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C62" s="343">
         <v>0</v>
       </c>
       <c r="E62" s="266" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="G62" s="328">
         <f>Data!C58</f>
@@ -12214,7 +12216,7 @@
     <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C63" s="329">
         <f>C61+C62</f>
@@ -12273,17 +12275,17 @@
     <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E65" s="268"/>
       <c r="G65" s="97" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C66" s="176">
         <f>G66</f>
@@ -12308,7 +12310,7 @@
     <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C67" s="176">
         <f>G67</f>
@@ -12333,7 +12335,7 @@
     <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C68" s="176">
         <f>G68</f>
@@ -12358,7 +12360,7 @@
     <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C69" s="71">
         <f>C61/BS!C70</f>
@@ -12388,12 +12390,12 @@
     <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>463</v>
+        <v>59</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12411,7 +12413,7 @@
     <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C72" s="62"/>
       <c r="D72" s="27"/>
@@ -12603,7 +12605,7 @@
     <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C76" s="78">
         <f>ABS(C8/C$4)</f>
@@ -12776,7 +12778,7 @@
     <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C79" s="78">
         <f>ABS(C11/C$4)</f>
@@ -12890,7 +12892,7 @@
     <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
@@ -13062,7 +13064,7 @@
     <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
@@ -13169,7 +13171,7 @@
     <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
@@ -13230,7 +13232,7 @@
     <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E89" s="268"/>
     </row>
@@ -13349,7 +13351,7 @@
     <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
@@ -13404,1310 +13406,1330 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="C93" s="23">
-        <f>C90/Market_Price</f>
+        <v>453</v>
+      </c>
+      <c r="C93" s="356">
+        <v>0</v>
+      </c>
+      <c r="E93" s="268"/>
+      <c r="G93" s="357"/>
+      <c r="H93" s="357"/>
+      <c r="I93" s="357"/>
+      <c r="J93" s="357"/>
+      <c r="K93" s="357"/>
+      <c r="L93" s="357"/>
+      <c r="M93" s="357"/>
+      <c r="N93" s="357"/>
+      <c r="O93" s="357"/>
+      <c r="P93" s="357"/>
+      <c r="Q93" s="357"/>
+    </row>
+    <row r="94" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A94" s="10"/>
+      <c r="B94" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C94" s="23">
+        <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
         <v>3.526170798898072E-2</v>
       </c>
-      <c r="E93" s="268"/>
-      <c r="G93" s="23">
-        <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
+      <c r="E94" s="268"/>
+      <c r="G94" s="23">
+        <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
         <v>3.526170798898072E-2</v>
       </c>
-      <c r="H93" s="23">
+      <c r="H94" s="23">
         <f t="shared" si="39"/>
         <v>4.2148760330578509E-2</v>
       </c>
-      <c r="I93" s="23">
+      <c r="I94" s="23">
         <f t="shared" si="39"/>
         <v>5.1239669421487603E-2</v>
       </c>
-      <c r="J93" s="23">
+      <c r="J94" s="23">
         <f t="shared" si="39"/>
         <v>4.077134986225895E-2</v>
       </c>
-      <c r="K93" s="23">
+      <c r="K94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="L93" s="23">
+      <c r="L94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="M93" s="23">
+      <c r="M94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="N93" s="23">
+      <c r="N94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="O93" s="23">
+      <c r="O94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="P93" s="23" t="str">
+      <c r="P94" s="23" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="Q93" s="23" t="str">
+      <c r="Q94" s="23" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-    </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A94" s="10"/>
-      <c r="E94" s="268"/>
     </row>
     <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
-      <c r="B95" s="157" t="s">
-        <v>84</v>
-      </c>
-      <c r="C95" s="62"/>
-      <c r="D95" s="27"/>
-      <c r="E95" s="265"/>
-      <c r="F95" s="27"/>
-      <c r="G95" s="12"/>
-      <c r="H95" s="12"/>
-      <c r="I95" s="12"/>
-      <c r="J95" s="12"/>
-      <c r="K95" s="12"/>
-      <c r="L95" s="12"/>
-      <c r="M95" s="12"/>
-      <c r="N95" s="12"/>
-      <c r="O95" s="12"/>
-      <c r="P95" s="12"/>
-      <c r="Q95" s="12"/>
+      <c r="E95" s="268"/>
     </row>
     <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
-      <c r="B96" s="27" t="s">
-        <v>144</v>
-      </c>
-      <c r="C96" s="77">
-        <f>C4/G4-1</f>
-        <v>-0.13453873241608505</v>
-      </c>
+      <c r="B96" s="157" t="s">
+        <v>84</v>
+      </c>
+      <c r="C96" s="62"/>
       <c r="D96" s="27"/>
       <c r="E96" s="265"/>
       <c r="F96" s="27"/>
-      <c r="G96" s="6">
-        <f t="shared" ref="G96:Q96" si="40">IF(H4="","",G4/H4-1)</f>
-        <v>-1.7793454058208091E-2</v>
-      </c>
-      <c r="H96" s="6">
-        <f t="shared" si="40"/>
-        <v>1.7831601632409155E-2</v>
-      </c>
-      <c r="I96" s="6">
-        <f t="shared" si="40"/>
-        <v>3.8741765890739188E-2</v>
-      </c>
-      <c r="J96" s="6">
-        <f t="shared" si="40"/>
-        <v>0.48937277142734481</v>
-      </c>
-      <c r="K96" s="6">
-        <f t="shared" si="40"/>
-        <v>-3.467157178120317E-2</v>
-      </c>
-      <c r="L96" s="6">
-        <f t="shared" si="40"/>
-        <v>-0.15717718207886588</v>
-      </c>
-      <c r="M96" s="6">
-        <f t="shared" si="40"/>
-        <v>-7.9751582839930668E-2</v>
-      </c>
-      <c r="N96" s="6">
-        <f t="shared" si="40"/>
-        <v>3.6461755447015465E-2</v>
-      </c>
-      <c r="O96" s="6" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="P96" s="6" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="Q96" s="6" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
+      <c r="G96" s="12"/>
+      <c r="H96" s="12"/>
+      <c r="I96" s="12"/>
+      <c r="J96" s="12"/>
+      <c r="K96" s="12"/>
+      <c r="L96" s="12"/>
+      <c r="M96" s="12"/>
+      <c r="N96" s="12"/>
+      <c r="O96" s="12"/>
+      <c r="P96" s="12"/>
+      <c r="Q96" s="12"/>
     </row>
     <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
-      <c r="B97" s="70" t="s">
-        <v>164</v>
+      <c r="B97" s="27" t="s">
+        <v>143</v>
       </c>
       <c r="C97" s="77">
-        <f>C13/G13-1</f>
-        <v>-0.45561632170449917</v>
+        <f>C4/G4-1</f>
+        <v>-0.13453873241608505</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="265"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6"